--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,16 +481,16 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>67989</v>
+        <v>72165</v>
       </c>
       <c r="E2">
         <v>73066</v>
       </c>
       <c r="F2">
-        <v>82989</v>
+        <v>87165</v>
       </c>
       <c r="G2">
-        <v>119504</v>
+        <v>125518</v>
       </c>
       <c r="H2">
         <v>15000</v>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>44051</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>73066</v>
       </c>
       <c r="F3">
-        <v>59051</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>85033</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>72554</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>84028</v>
       </c>
       <c r="F5">
-        <v>87554</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>126078</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>3570</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>54795</v>
       </c>
       <c r="F7">
-        <v>28798</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>41469</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>25228</v>
+        <v>0</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33509</v>
+        <v>35622</v>
       </c>
       <c r="E8">
         <v>73066</v>
       </c>
       <c r="F8">
-        <v>54800</v>
+        <v>53129</v>
       </c>
       <c r="G8">
-        <v>78912</v>
+        <v>76506</v>
       </c>
       <c r="H8">
-        <v>21291</v>
+        <v>17507</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>33985</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>73066</v>
       </c>
       <c r="F9">
-        <v>48985</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>70538</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>45262</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>109608</v>
       </c>
       <c r="F11">
-        <v>66852</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>96267</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>21590</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,16 +925,16 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>81335</v>
+        <v>87338</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>96335</v>
+        <v>102338</v>
       </c>
       <c r="G12">
-        <v>138722</v>
+        <v>147367</v>
       </c>
       <c r="H12">
         <v>15000</v>
@@ -970,19 +970,19 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11017</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>82201</v>
       </c>
       <c r="F13">
-        <v>38017</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>54744</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I13" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>29651</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>73066</v>
       </c>
       <c r="F15">
-        <v>46356</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>66753</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>16705</v>
+        <v>0</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>31040</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>102299</v>
       </c>
       <c r="F21">
-        <v>58040</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>83578</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>162363</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>131533</v>
       </c>
       <c r="F23">
-        <v>177363</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>255403</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20436</v>
+        <v>0</v>
       </c>
       <c r="E27">
         <v>63930</v>
       </c>
       <c r="F27">
-        <v>39107</v>
+        <v>0</v>
       </c>
       <c r="G27">
-        <v>56314</v>
+        <v>0</v>
       </c>
       <c r="H27">
-        <v>18671</v>
+        <v>0</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>65966</v>
+        <v>0</v>
       </c>
       <c r="E28">
         <v>127879</v>
       </c>
       <c r="F28">
-        <v>89932</v>
+        <v>0</v>
       </c>
       <c r="G28">
-        <v>129502</v>
+        <v>0</v>
       </c>
       <c r="H28">
-        <v>23966</v>
+        <v>0</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,19 +1665,19 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>23887</v>
+        <v>0</v>
       </c>
       <c r="E29">
         <v>127879</v>
       </c>
       <c r="F29">
-        <v>50887</v>
+        <v>0</v>
       </c>
       <c r="G29">
-        <v>73277</v>
+        <v>0</v>
       </c>
       <c r="H29">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I29" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131643</v>
+        <v>0</v>
       </c>
       <c r="E30">
         <v>182692</v>
       </c>
       <c r="F30">
-        <v>158643</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>228446</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>51362</v>
+        <v>0</v>
       </c>
       <c r="E31">
         <v>182692</v>
       </c>
       <c r="F31">
-        <v>78362</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>112841</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>62975</v>
+        <v>77472</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>80514</v>
+        <v>92472</v>
       </c>
       <c r="G32">
-        <v>115940</v>
+        <v>133160</v>
       </c>
       <c r="H32">
-        <v>17539</v>
+        <v>15000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>43170</v>
+        <v>0</v>
       </c>
       <c r="E33">
         <v>109608</v>
       </c>
       <c r="F33">
-        <v>66015</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>95062</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>22845</v>
+        <v>0</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>35571</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>127879</v>
       </c>
       <c r="F35">
-        <v>62571</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>90102</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45275</v>
+        <v>47017</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>72275</v>
+        <v>74017</v>
       </c>
       <c r="G36">
-        <v>104076</v>
+        <v>106584</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>32399</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>127879</v>
       </c>
       <c r="F37">
-        <v>59399</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>85535</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>121947</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>237505</v>
       </c>
       <c r="F39">
-        <v>147406</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>212265</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>25459</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>121947</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>237505</v>
       </c>
       <c r="F41">
-        <v>147406</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>212265</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>25459</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2286,19 +2286,19 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38952</v>
+        <v>0</v>
       </c>
       <c r="E43">
         <v>127879</v>
       </c>
       <c r="F43">
-        <v>65952</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>94971</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I43" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>78149</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>182692</v>
       </c>
       <c r="F45">
-        <v>105149</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>151415</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,19 +2457,19 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25306</v>
+        <v>0</v>
       </c>
       <c r="E47">
         <v>109608</v>
       </c>
       <c r="F47">
-        <v>52306</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>75321</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I47" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/311210/Call_of_Duty_Black_Ops_III/","Abrir Steam")</f>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>34525</v>
+        <v>37433</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>54458</v>
+        <v>52433</v>
       </c>
       <c r="G50">
-        <v>78420</v>
+        <v>75504</v>
       </c>
       <c r="H50">
-        <v>19933</v>
+        <v>15000</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>31458</v>
+        <v>0</v>
       </c>
       <c r="E51">
         <v>63930</v>
       </c>
       <c r="F51">
-        <v>46458</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>66900</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>53505</v>
+        <v>0</v>
       </c>
       <c r="E53">
         <v>76720</v>
       </c>
       <c r="F53">
-        <v>68505</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>98647</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>46718</v>
+        <v>53277</v>
       </c>
       <c r="E54">
         <v>127879</v>
       </c>
       <c r="F54">
-        <v>81718</v>
+        <v>80277</v>
       </c>
       <c r="G54">
-        <v>117674</v>
+        <v>115599</v>
       </c>
       <c r="H54">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>49457</v>
+        <v>0</v>
       </c>
       <c r="E55">
         <v>127879</v>
       </c>
       <c r="F55">
-        <v>75655</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>108943</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>26198</v>
+        <v>0</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>59471</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>146150</v>
       </c>
       <c r="F57">
-        <v>86471</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>124518</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>20351</v>
+        <v>21136</v>
       </c>
       <c r="E58">
         <v>36524</v>
       </c>
       <c r="F58">
-        <v>37056</v>
+        <v>36136</v>
       </c>
       <c r="G58">
-        <v>53361</v>
+        <v>52036</v>
       </c>
       <c r="H58">
-        <v>16705</v>
+        <v>15000</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>5900</v>
+        <v>0</v>
       </c>
       <c r="E59">
         <v>36524</v>
       </c>
       <c r="F59">
-        <v>22605</v>
+        <v>0</v>
       </c>
       <c r="G59">
-        <v>32551</v>
+        <v>0</v>
       </c>
       <c r="H59">
-        <v>16705</v>
+        <v>0</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24499</v>
+        <v>26365</v>
       </c>
       <c r="E60">
         <v>49313</v>
       </c>
       <c r="F60">
-        <v>59499</v>
+        <v>41365</v>
       </c>
       <c r="G60">
-        <v>85679</v>
+        <v>59566</v>
       </c>
       <c r="H60">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>38464</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>49313</v>
       </c>
       <c r="F61">
-        <v>53464</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>76988</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3166,19 +3166,19 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12190</v>
+        <v>0</v>
       </c>
       <c r="E63">
         <v>82201</v>
       </c>
       <c r="F63">
-        <v>39190</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>56434</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I63" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1091500/Cyberpunk_2077/","Abrir Steam")</f>
@@ -3252,19 +3252,19 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>29124</v>
+        <v>0</v>
       </c>
       <c r="E65">
         <v>123293</v>
       </c>
       <c r="F65">
-        <v>56124</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>80819</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I65" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1091500/Cyberpunk_2077/","Abrir Steam")</f>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25241</v>
+        <v>23056</v>
       </c>
       <c r="E66">
         <v>91337</v>
       </c>
       <c r="F66">
-        <v>53124</v>
+        <v>50056</v>
       </c>
       <c r="G66">
-        <v>76499</v>
+        <v>72081</v>
       </c>
       <c r="H66">
-        <v>27883</v>
+        <v>27000</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,19 +3341,19 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18124</v>
+        <v>0</v>
       </c>
       <c r="E67">
         <v>91337</v>
       </c>
       <c r="F67">
-        <v>45124</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>64979</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I67" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>56879</v>
+        <v>62221</v>
       </c>
       <c r="E68">
         <v>109608</v>
       </c>
       <c r="F68">
-        <v>82206</v>
+        <v>80212</v>
       </c>
       <c r="G68">
-        <v>118377</v>
+        <v>115505</v>
       </c>
       <c r="H68">
-        <v>25327</v>
+        <v>17991</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>25881</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>109608</v>
       </c>
       <c r="F69">
-        <v>52881</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>76149</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>109592</v>
+        <v>106648</v>
       </c>
       <c r="E70">
         <v>127879</v>
       </c>
       <c r="F70">
-        <v>124724</v>
+        <v>121648</v>
       </c>
       <c r="G70">
-        <v>179603</v>
+        <v>175173</v>
       </c>
       <c r="H70">
-        <v>15132</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>67901</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>127879</v>
       </c>
       <c r="F71">
-        <v>83033</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>119568</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>15132</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3561,16 +3561,16 @@
         <v>15</v>
       </c>
       <c r="D72">
-        <v>18422</v>
+        <v>18529</v>
       </c>
       <c r="E72">
         <v>27388</v>
       </c>
       <c r="F72">
-        <v>33422</v>
+        <v>33529</v>
       </c>
       <c r="G72">
-        <v>48128</v>
+        <v>48282</v>
       </c>
       <c r="H72">
         <v>15000</v>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5253</v>
+        <v>0</v>
       </c>
       <c r="E73">
         <v>27388</v>
       </c>
       <c r="F73">
-        <v>20253</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>29164</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3691,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>90959</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>95904</v>
       </c>
       <c r="F75">
-        <v>105959</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>152581</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>84162</v>
+        <v>86667</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>99655</v>
+        <v>101667</v>
       </c>
       <c r="G76">
-        <v>143503</v>
+        <v>146400</v>
       </c>
       <c r="H76">
-        <v>15493</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>53657</v>
+        <v>0</v>
       </c>
       <c r="E77">
         <v>127879</v>
       </c>
       <c r="F77">
-        <v>77335</v>
+        <v>0</v>
       </c>
       <c r="G77">
-        <v>111362</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>23678</v>
+        <v>0</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>35083</v>
+        <v>0</v>
       </c>
       <c r="E81">
         <v>91337</v>
       </c>
       <c r="F81">
-        <v>55655</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>80143</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>20572</v>
+        <v>0</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84158</v>
+        <v>0</v>
       </c>
       <c r="E83">
         <v>127879</v>
       </c>
       <c r="F83">
-        <v>99158</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>142788</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48157</v>
+        <v>0</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>71297</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>102668</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>23140</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32388</v>
+        <v>0</v>
       </c>
       <c r="E85">
         <v>102299</v>
       </c>
       <c r="F85">
-        <v>58852</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>84747</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>26464</v>
+        <v>0</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>67763</v>
+        <v>149903</v>
       </c>
       <c r="E86">
         <v>146150</v>
       </c>
       <c r="F86">
-        <v>102763</v>
+        <v>164903</v>
       </c>
       <c r="G86">
-        <v>147979</v>
+        <v>237460</v>
       </c>
       <c r="H86">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,19 +4215,19 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>101032</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>146150</v>
       </c>
       <c r="F87">
-        <v>116032</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>167086</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I87" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>166703</v>
+        <v>166418</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>184071</v>
+        <v>181418</v>
       </c>
       <c r="G88">
-        <v>265062</v>
+        <v>261242</v>
       </c>
       <c r="H88">
-        <v>17368</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>85552</v>
+        <v>0</v>
       </c>
       <c r="E89">
         <v>160767</v>
       </c>
       <c r="F89">
-        <v>102920</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>148205</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>17368</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>7711</v>
+        <v>7680</v>
       </c>
       <c r="E90">
         <v>58449</v>
       </c>
       <c r="F90">
-        <v>38060</v>
+        <v>35000</v>
       </c>
       <c r="G90">
-        <v>54806</v>
+        <v>50400</v>
       </c>
       <c r="H90">
-        <v>30349</v>
+        <v>27320</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3162</v>
+        <v>0</v>
       </c>
       <c r="E91">
         <v>58449</v>
       </c>
       <c r="F91">
-        <v>30060</v>
+        <v>0</v>
       </c>
       <c r="G91">
-        <v>43286</v>
+        <v>0</v>
       </c>
       <c r="H91">
-        <v>26898</v>
+        <v>0</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>11544</v>
+        <v>0</v>
       </c>
       <c r="E93">
         <v>27388</v>
       </c>
       <c r="F93">
-        <v>26544</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>38223</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>56879</v>
+        <v>61878</v>
       </c>
       <c r="E96">
         <v>82201</v>
       </c>
       <c r="F96">
-        <v>72197</v>
+        <v>76878</v>
       </c>
       <c r="G96">
-        <v>103964</v>
+        <v>110704</v>
       </c>
       <c r="H96">
-        <v>15318</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>31793</v>
+        <v>0</v>
       </c>
       <c r="E97">
         <v>82201</v>
       </c>
       <c r="F97">
-        <v>50776</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>73117</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>18983</v>
+        <v>0</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,16 +4698,16 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>72119</v>
+        <v>76910</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>87119</v>
+        <v>91910</v>
       </c>
       <c r="G98">
-        <v>125451</v>
+        <v>132350</v>
       </c>
       <c r="H98">
         <v>15000</v>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>58859</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>94991</v>
       </c>
       <c r="F99">
-        <v>73859</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>106357</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>57533</v>
+        <v>71260</v>
       </c>
       <c r="E100">
         <v>106502</v>
       </c>
       <c r="F100">
-        <v>79877</v>
+        <v>86260</v>
       </c>
       <c r="G100">
-        <v>115023</v>
+        <v>124214</v>
       </c>
       <c r="H100">
-        <v>22344</v>
+        <v>15000</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,19 +4834,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>57653</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>106502</v>
       </c>
       <c r="F101">
-        <v>72653</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>104620</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>75047</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>127879</v>
       </c>
       <c r="F105">
-        <v>90047</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>129668</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>104954</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>182692</v>
       </c>
       <c r="F107">
-        <v>119954</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>172734</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,19 +5176,19 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3060</v>
+        <v>0</v>
       </c>
       <c r="E109">
         <v>127879</v>
       </c>
       <c r="F109">
-        <v>30060</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>43286</v>
+        <v>0</v>
       </c>
       <c r="H109">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I109" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3405690/EA_SPORTS_FC_26/","Abrir Steam")</f>
@@ -5263,19 +5263,19 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13329</v>
+        <v>0</v>
       </c>
       <c r="E111">
         <v>164421</v>
       </c>
       <c r="F111">
-        <v>40329</v>
+        <v>0</v>
       </c>
       <c r="G111">
-        <v>58074</v>
+        <v>0</v>
       </c>
       <c r="H111">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I111" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3405690/EA_SPORTS_FC_26/","Abrir Steam")</f>
@@ -5307,16 +5307,16 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>82936</v>
+        <v>81718</v>
       </c>
       <c r="E112">
         <v>87683</v>
       </c>
       <c r="F112">
-        <v>97936</v>
+        <v>96718</v>
       </c>
       <c r="G112">
-        <v>141028</v>
+        <v>139274</v>
       </c>
       <c r="H112">
         <v>15000</v>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>46125</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>87683</v>
       </c>
       <c r="F113">
-        <v>61125</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>88020</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5396,19 +5396,19 @@
         <v>15</v>
       </c>
       <c r="D114">
-        <v>132685</v>
+        <v>0</v>
       </c>
       <c r="E114">
         <v>116916</v>
       </c>
       <c r="F114">
-        <v>147685</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>212666</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I114" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>79944</v>
+        <v>0</v>
       </c>
       <c r="E115">
         <v>116916</v>
       </c>
       <c r="F115">
-        <v>94944</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>136719</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>107150</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>146150</v>
       </c>
       <c r="F117">
-        <v>122150</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>175896</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43521</v>
+        <v>0</v>
       </c>
       <c r="E118">
         <v>58449</v>
       </c>
       <c r="F118">
-        <v>58521</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>84270</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>31011</v>
+        <v>0</v>
       </c>
       <c r="E119">
         <v>58449</v>
       </c>
       <c r="F119">
-        <v>46011</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>66256</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,16 +5658,16 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>65813</v>
+        <v>82624</v>
       </c>
       <c r="E120">
         <v>80374</v>
       </c>
       <c r="F120">
-        <v>80813</v>
+        <v>97624</v>
       </c>
       <c r="G120">
-        <v>116371</v>
+        <v>140579</v>
       </c>
       <c r="H120">
         <v>15000</v>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>50229</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>80374</v>
       </c>
       <c r="F121">
-        <v>65229</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>93930</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>138817</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>91337</v>
       </c>
       <c r="F122">
-        <v>153817</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>221496</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>50988</v>
+        <v>0</v>
       </c>
       <c r="E123">
         <v>91337</v>
       </c>
       <c r="F123">
-        <v>65988</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>95023</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,19 +5833,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13142</v>
+        <v>13846</v>
       </c>
       <c r="E124">
         <v>43832</v>
       </c>
       <c r="F124">
-        <v>32874</v>
+        <v>31263</v>
       </c>
       <c r="G124">
-        <v>47339</v>
+        <v>45019</v>
       </c>
       <c r="H124">
-        <v>19732</v>
+        <v>17417</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>6902</v>
+        <v>0</v>
       </c>
       <c r="E125">
         <v>43832</v>
       </c>
       <c r="F125">
-        <v>25855</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>37231</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>18953</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>30722</v>
+        <v>30814</v>
       </c>
       <c r="E126">
         <v>58449</v>
       </c>
       <c r="F126">
-        <v>45722</v>
+        <v>45814</v>
       </c>
       <c r="G126">
-        <v>65840</v>
+        <v>65972</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>19943</v>
+        <v>0</v>
       </c>
       <c r="E129">
         <v>59892</v>
       </c>
       <c r="F129">
-        <v>37335</v>
+        <v>0</v>
       </c>
       <c r="G129">
-        <v>53762</v>
+        <v>0</v>
       </c>
       <c r="H129">
-        <v>17392</v>
+        <v>0</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>29907</v>
+        <v>0</v>
       </c>
       <c r="E131">
         <v>74619</v>
       </c>
       <c r="F131">
-        <v>47064</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>67772</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>17157</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>35805</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>93931</v>
       </c>
       <c r="F133">
-        <v>56955</v>
+        <v>0</v>
       </c>
       <c r="G133">
-        <v>82015</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>21150</v>
+        <v>0</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>50954</v>
+        <v>0</v>
       </c>
       <c r="E135">
         <v>89510</v>
       </c>
       <c r="F135">
-        <v>65954</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>94974</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>69451</v>
+        <v>0</v>
       </c>
       <c r="E137">
         <v>127879</v>
       </c>
       <c r="F137">
-        <v>84451</v>
+        <v>0</v>
       </c>
       <c r="G137">
-        <v>121609</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>86657</v>
+        <v>0</v>
       </c>
       <c r="E139">
         <v>153458</v>
       </c>
       <c r="F139">
-        <v>101657</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>146386</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>36009</v>
+        <v>37667</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>61505</v>
+        <v>62169</v>
       </c>
       <c r="G140">
-        <v>88567</v>
+        <v>89523</v>
       </c>
       <c r="H140">
-        <v>25496</v>
+        <v>24502</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>23509</v>
+        <v>22853</v>
       </c>
       <c r="E142">
         <v>91337</v>
       </c>
       <c r="F142">
-        <v>58509</v>
+        <v>49853</v>
       </c>
       <c r="G142">
-        <v>84253</v>
+        <v>71788</v>
       </c>
       <c r="H142">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>26090</v>
+        <v>0</v>
       </c>
       <c r="E143">
         <v>91337</v>
       </c>
       <c r="F143">
-        <v>52057</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>74962</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>25967</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>57078</v>
+        <v>44520</v>
       </c>
       <c r="E144">
         <v>91337</v>
       </c>
       <c r="F144">
-        <v>80264</v>
+        <v>64910</v>
       </c>
       <c r="G144">
-        <v>115580</v>
+        <v>93470</v>
       </c>
       <c r="H144">
-        <v>23186</v>
+        <v>20390</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>54795</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>91337</v>
       </c>
       <c r="F145">
-        <v>69795</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>100505</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>60843</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>91337</v>
       </c>
       <c r="F146">
-        <v>95843</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>138014</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>92092</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>91337</v>
       </c>
       <c r="F147">
-        <v>107092</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>154212</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36558</v>
+        <v>36543</v>
       </c>
       <c r="E148">
         <v>62103</v>
       </c>
       <c r="F148">
-        <v>62297</v>
+        <v>51543</v>
       </c>
       <c r="G148">
-        <v>89708</v>
+        <v>74222</v>
       </c>
       <c r="H148">
-        <v>25739</v>
+        <v>15000</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>38730</v>
+        <v>0</v>
       </c>
       <c r="E149">
         <v>62103</v>
       </c>
       <c r="F149">
-        <v>53730</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>77371</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>14842</v>
+        <v>0</v>
       </c>
       <c r="E151">
         <v>82201</v>
       </c>
       <c r="F151">
-        <v>41842</v>
+        <v>0</v>
       </c>
       <c r="G151">
-        <v>60252</v>
+        <v>0</v>
       </c>
       <c r="H151">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>35652</v>
+        <v>37948</v>
       </c>
       <c r="E152">
         <v>73066</v>
       </c>
       <c r="F152">
-        <v>54800</v>
+        <v>54059</v>
       </c>
       <c r="G152">
-        <v>78912</v>
+        <v>77845</v>
       </c>
       <c r="H152">
-        <v>19148</v>
+        <v>16111</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33425</v>
+        <v>0</v>
       </c>
       <c r="E153">
         <v>73066</v>
       </c>
       <c r="F153">
-        <v>48425</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>69732</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>54728</v>
+        <v>57211</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>89728</v>
+        <v>72211</v>
       </c>
       <c r="G154">
-        <v>129208</v>
+        <v>103984</v>
       </c>
       <c r="H154">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>74994</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>73066</v>
       </c>
       <c r="F155">
-        <v>89994</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>129591</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>32116</v>
+        <v>0</v>
       </c>
       <c r="E156">
         <v>27388</v>
       </c>
       <c r="F156">
-        <v>47116</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>67847</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>13244</v>
+        <v>0</v>
       </c>
       <c r="E157">
         <v>27388</v>
       </c>
       <c r="F157">
-        <v>28244</v>
+        <v>0</v>
       </c>
       <c r="G157">
-        <v>40671</v>
+        <v>0</v>
       </c>
       <c r="H157">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>88867</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>84028</v>
       </c>
       <c r="F158">
-        <v>108669</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>156483</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>19802</v>
+        <v>0</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>31615</v>
+        <v>0</v>
       </c>
       <c r="E159">
         <v>84028</v>
       </c>
       <c r="F159">
-        <v>51417</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>74040</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>19802</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>7836</v>
+        <v>7680</v>
       </c>
       <c r="E160">
         <v>54813</v>
       </c>
       <c r="F160">
-        <v>38716</v>
+        <v>35000</v>
       </c>
       <c r="G160">
-        <v>55751</v>
+        <v>50400</v>
       </c>
       <c r="H160">
-        <v>30880</v>
+        <v>27320</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8348</v>
+        <v>0</v>
       </c>
       <c r="E161">
         <v>54813</v>
       </c>
       <c r="F161">
-        <v>30716</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>44231</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>22368</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>73066</v>
       </c>
       <c r="F162">
-        <v>43976</v>
+        <v>37147</v>
       </c>
       <c r="G162">
-        <v>63325</v>
+        <v>53492</v>
       </c>
       <c r="H162">
-        <v>33829</v>
+        <v>27000</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,19 +7547,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>8976</v>
+        <v>0</v>
       </c>
       <c r="E163">
         <v>73066</v>
       </c>
       <c r="F163">
-        <v>35976</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>51805</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>65007</v>
+        <v>84294</v>
       </c>
       <c r="E164">
         <v>68516</v>
       </c>
       <c r="F164">
-        <v>80271</v>
+        <v>99294</v>
       </c>
       <c r="G164">
-        <v>115590</v>
+        <v>142983</v>
       </c>
       <c r="H164">
-        <v>15264</v>
+        <v>15000</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20759</v>
+        <v>0</v>
       </c>
       <c r="E165">
         <v>68516</v>
       </c>
       <c r="F165">
-        <v>41025</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>59076</v>
+        <v>0</v>
       </c>
       <c r="H165">
-        <v>20266</v>
+        <v>0</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>87360</v>
+        <v>0</v>
       </c>
       <c r="E166">
         <v>103231</v>
       </c>
       <c r="F166">
-        <v>107206</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>154377</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>19846</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>44024</v>
+        <v>0</v>
       </c>
       <c r="E167">
         <v>103231</v>
       </c>
       <c r="F167">
-        <v>63870</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>91973</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>19846</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7766,19 +7766,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>75504</v>
+        <v>89071</v>
       </c>
       <c r="E168">
         <v>73066</v>
       </c>
       <c r="F168">
-        <v>102504</v>
+        <v>104071</v>
       </c>
       <c r="G168">
-        <v>147606</v>
+        <v>149862</v>
       </c>
       <c r="H168">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,19 +7811,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8470</v>
+        <v>0</v>
       </c>
       <c r="E169">
         <v>73066</v>
       </c>
       <c r="F169">
-        <v>35470</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>51077</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>56879</v>
+        <v>68981</v>
       </c>
       <c r="E170">
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>80439</v>
+        <v>83981</v>
       </c>
       <c r="G170">
-        <v>115832</v>
+        <v>120933</v>
       </c>
       <c r="H170">
-        <v>23560</v>
+        <v>15000</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>53000</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>109608</v>
       </c>
       <c r="F171">
-        <v>69947</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>100724</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>16947</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>75168</v>
+        <v>90694</v>
       </c>
       <c r="E172">
         <v>146150</v>
       </c>
       <c r="F172">
-        <v>109613</v>
+        <v>108045</v>
       </c>
       <c r="G172">
-        <v>157843</v>
+        <v>155585</v>
       </c>
       <c r="H172">
-        <v>34445</v>
+        <v>17351</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>87125</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>146150</v>
       </c>
       <c r="F173">
-        <v>102125</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>147060</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>46720</v>
+        <v>48032</v>
       </c>
       <c r="E174">
         <v>91337</v>
       </c>
       <c r="F174">
-        <v>68503</v>
+        <v>66315</v>
       </c>
       <c r="G174">
-        <v>98644</v>
+        <v>95494</v>
       </c>
       <c r="H174">
-        <v>21783</v>
+        <v>18283</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>75640</v>
+        <v>0</v>
       </c>
       <c r="E175">
         <v>91337</v>
       </c>
       <c r="F175">
-        <v>90640</v>
+        <v>0</v>
       </c>
       <c r="G175">
-        <v>130522</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>56241</v>
+        <v>0</v>
       </c>
       <c r="E176">
         <v>91337</v>
       </c>
       <c r="F176">
-        <v>71241</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>102587</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>28444</v>
+        <v>26428</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>55444</v>
+        <v>53428</v>
       </c>
       <c r="G178">
-        <v>79839</v>
+        <v>76936</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>24907</v>
+        <v>25116</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>51907</v>
+        <v>52116</v>
       </c>
       <c r="G180">
-        <v>74746</v>
+        <v>75047</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>82280</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>127879</v>
       </c>
       <c r="F182">
-        <v>97622</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>140576</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>15342</v>
+        <v>0</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>61682</v>
+        <v>0</v>
       </c>
       <c r="E183">
         <v>127879</v>
       </c>
       <c r="F183">
-        <v>80545</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>115985</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>18863</v>
+        <v>0</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>111745</v>
+        <v>0</v>
       </c>
       <c r="E184">
         <v>182692</v>
       </c>
       <c r="F184">
-        <v>137019</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>197307</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>25274</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,19 +8517,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>176867</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>182692</v>
       </c>
       <c r="F185">
-        <v>191867</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>276288</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>140195</v>
+        <v>0</v>
       </c>
       <c r="E186">
         <v>237505</v>
       </c>
       <c r="F186">
-        <v>167195</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>240761</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,19 +8604,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>176867</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>182692</v>
       </c>
       <c r="F187">
-        <v>191867</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>276288</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>218431</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>365402</v>
       </c>
       <c r="F188">
-        <v>253431</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>364941</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8691,19 +8691,19 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>348551</v>
+        <v>0</v>
       </c>
       <c r="E189">
         <v>365402</v>
       </c>
       <c r="F189">
-        <v>363551</v>
+        <v>0</v>
       </c>
       <c r="G189">
-        <v>523513</v>
+        <v>0</v>
       </c>
       <c r="H189">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I189" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,19 +8734,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>30627</v>
+        <v>29831</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>65627</v>
+        <v>56831</v>
       </c>
       <c r="G190">
-        <v>94503</v>
+        <v>81837</v>
       </c>
       <c r="H190">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>37760</v>
+        <v>0</v>
       </c>
       <c r="E191">
         <v>95904</v>
       </c>
       <c r="F191">
-        <v>58507</v>
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>84250</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>20747</v>
+        <v>0</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41897</v>
+        <v>41944</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>76897</v>
+        <v>68944</v>
       </c>
       <c r="G192">
-        <v>110732</v>
+        <v>99279</v>
       </c>
       <c r="H192">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8868,19 +8868,19 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>142233</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>123311</v>
       </c>
       <c r="F193">
-        <v>157233</v>
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>226416</v>
+        <v>0</v>
       </c>
       <c r="H193">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I193" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,19 +8911,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>52091</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>79091</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>113891</v>
+        <v>0</v>
       </c>
       <c r="H194">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8955,19 +8955,19 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>142233</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>123311</v>
       </c>
       <c r="F195">
-        <v>157233</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>226416</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I195" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>12597</v>
+        <v>13159</v>
       </c>
       <c r="E196">
         <v>73066</v>
       </c>
       <c r="F196">
-        <v>47597</v>
+        <v>40159</v>
       </c>
       <c r="G196">
-        <v>68540</v>
+        <v>57829</v>
       </c>
       <c r="H196">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>37018</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>73066</v>
       </c>
       <c r="F197">
-        <v>52018</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>74906</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>21230</v>
+        <v>25757</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>56230</v>
+        <v>52757</v>
       </c>
       <c r="G198">
-        <v>80971</v>
+        <v>75970</v>
       </c>
       <c r="H198">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>35083</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>109608</v>
       </c>
       <c r="F199">
-        <v>62083</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>89400</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>13176</v>
+        <v>14096</v>
       </c>
       <c r="E200">
         <v>127879</v>
       </c>
       <c r="F200">
-        <v>48176</v>
+        <v>41096</v>
       </c>
       <c r="G200">
-        <v>69373</v>
+        <v>59178</v>
       </c>
       <c r="H200">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,19 +9222,19 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>14466</v>
+        <v>0</v>
       </c>
       <c r="E201">
         <v>127879</v>
       </c>
       <c r="F201">
-        <v>41466</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>59711</v>
+        <v>0</v>
       </c>
       <c r="H201">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I201" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9266,19 +9266,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>21317</v>
+        <v>22432</v>
       </c>
       <c r="E202">
         <v>146150</v>
       </c>
       <c r="F202">
-        <v>56317</v>
+        <v>49432</v>
       </c>
       <c r="G202">
-        <v>81096</v>
+        <v>71182</v>
       </c>
       <c r="H202">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>27883</v>
+        <v>0</v>
       </c>
       <c r="E203">
         <v>146150</v>
       </c>
       <c r="F203">
-        <v>54883</v>
+        <v>0</v>
       </c>
       <c r="G203">
-        <v>79032</v>
+        <v>0</v>
       </c>
       <c r="H203">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>26397</v>
+        <v>29128</v>
       </c>
       <c r="E204">
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>61397</v>
+        <v>56128</v>
       </c>
       <c r="G204">
-        <v>88412</v>
+        <v>80824</v>
       </c>
       <c r="H204">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>91673</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>182692</v>
       </c>
       <c r="F205">
-        <v>113919</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>164043</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>22246</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>15766</v>
+        <v>15860</v>
       </c>
       <c r="E206">
         <v>58449</v>
       </c>
       <c r="F206">
-        <v>43837</v>
+        <v>38646</v>
       </c>
       <c r="G206">
-        <v>63125</v>
+        <v>55650</v>
       </c>
       <c r="H206">
-        <v>28071</v>
+        <v>22786</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>19154</v>
+        <v>0</v>
       </c>
       <c r="E207">
         <v>58449</v>
       </c>
       <c r="F207">
-        <v>36457</v>
+        <v>0</v>
       </c>
       <c r="G207">
-        <v>52498</v>
+        <v>0</v>
       </c>
       <c r="H207">
-        <v>17303</v>
+        <v>0</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,19 +9578,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22988</v>
+        <v>0</v>
       </c>
       <c r="E209">
         <v>54795</v>
       </c>
       <c r="F209">
-        <v>37988</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>54703</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>44094</v>
+        <v>0</v>
       </c>
       <c r="E211">
         <v>109608</v>
       </c>
       <c r="F211">
-        <v>66385</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>95594</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>22291</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>78358</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>182692</v>
       </c>
       <c r="F213">
-        <v>105358</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>151716</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>26284</v>
+        <v>29019</v>
       </c>
       <c r="E214">
         <v>87683</v>
       </c>
       <c r="F214">
-        <v>61284</v>
+        <v>56019</v>
       </c>
       <c r="G214">
-        <v>88249</v>
+        <v>80667</v>
       </c>
       <c r="H214">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>42717</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>87683</v>
       </c>
       <c r="F215">
-        <v>57717</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>83112</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>54655</v>
+        <v>0</v>
       </c>
       <c r="E216">
         <v>102299</v>
       </c>
       <c r="F216">
-        <v>76724</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>110483</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>22069</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>75587</v>
+        <v>0</v>
       </c>
       <c r="E217">
         <v>102299</v>
       </c>
       <c r="F217">
-        <v>90587</v>
+        <v>0</v>
       </c>
       <c r="G217">
-        <v>130445</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>97007</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>131533</v>
       </c>
       <c r="F219">
-        <v>112007</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>161290</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,16 +10059,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>59365</v>
+        <v>59302</v>
       </c>
       <c r="E220">
         <v>82220</v>
       </c>
       <c r="F220">
-        <v>74365</v>
+        <v>74302</v>
       </c>
       <c r="G220">
-        <v>107086</v>
+        <v>106995</v>
       </c>
       <c r="H220">
         <v>15000</v>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>49200</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>82220</v>
       </c>
       <c r="F221">
-        <v>64200</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>92448</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>71103</v>
+        <v>0</v>
       </c>
       <c r="E222">
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>105457</v>
+        <v>0</v>
       </c>
       <c r="G222">
-        <v>151858</v>
+        <v>0</v>
       </c>
       <c r="H222">
-        <v>34354</v>
+        <v>0</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>76702</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>96836</v>
       </c>
       <c r="F223">
-        <v>91702</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>132051</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16406</v>
+        <v>16203</v>
       </c>
       <c r="E224">
         <v>60276</v>
       </c>
       <c r="F224">
-        <v>41445</v>
+        <v>39605</v>
       </c>
       <c r="G224">
-        <v>59681</v>
+        <v>57031</v>
       </c>
       <c r="H224">
-        <v>25039</v>
+        <v>23402</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>9844</v>
+        <v>0</v>
       </c>
       <c r="E225">
         <v>60276</v>
       </c>
       <c r="F225">
-        <v>33445</v>
+        <v>0</v>
       </c>
       <c r="G225">
-        <v>48161</v>
+        <v>0</v>
       </c>
       <c r="H225">
-        <v>23601</v>
+        <v>0</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>35519</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>73066</v>
       </c>
       <c r="F226">
-        <v>54800</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>78912</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>19281</v>
+        <v>0</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>24382</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>73066</v>
       </c>
       <c r="F227">
-        <v>44249</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>63719</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>19867</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>87142</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>109608</v>
       </c>
       <c r="F228">
-        <v>102142</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>147084</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>14012</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>109608</v>
       </c>
       <c r="F229">
-        <v>41012</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>59057</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19799</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>182692</v>
       </c>
       <c r="F231">
-        <v>46799</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>67391</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10595,13 +10595,13 @@
         <v>52986</v>
       </c>
       <c r="F232">
-        <v>38408</v>
+        <v>34665</v>
       </c>
       <c r="G232">
-        <v>55308</v>
+        <v>49918</v>
       </c>
       <c r="H232">
-        <v>29073</v>
+        <v>25330</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9359</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>52986</v>
       </c>
       <c r="F233">
-        <v>30408</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>43788</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>21049</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,16 +10677,16 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>11864</v>
+        <v>11926</v>
       </c>
       <c r="E234">
         <v>71257</v>
       </c>
       <c r="F234">
-        <v>38864</v>
+        <v>38926</v>
       </c>
       <c r="G234">
-        <v>55964</v>
+        <v>56053</v>
       </c>
       <c r="H234">
         <v>27000</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>15216</v>
+        <v>8351</v>
       </c>
       <c r="E236">
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>35930</v>
+        <v>34717</v>
       </c>
       <c r="G236">
-        <v>51739</v>
+        <v>49992</v>
       </c>
       <c r="H236">
-        <v>20714</v>
+        <v>26366</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>3033</v>
+        <v>0</v>
       </c>
       <c r="E237">
         <v>52986</v>
       </c>
       <c r="F237">
-        <v>27878</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>40144</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>24845</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10853,19 +10853,19 @@
         <v>15</v>
       </c>
       <c r="D238">
-        <v>11294</v>
+        <v>0</v>
       </c>
       <c r="E238">
         <v>52986</v>
       </c>
       <c r="F238">
-        <v>38973</v>
+        <v>0</v>
       </c>
       <c r="G238">
-        <v>56121</v>
+        <v>0</v>
       </c>
       <c r="H238">
-        <v>27679</v>
+        <v>0</v>
       </c>
       <c r="I238" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>10771</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>52986</v>
       </c>
       <c r="F239">
-        <v>30973</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>44601</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>20202</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>34683</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>71257</v>
       </c>
       <c r="F240">
-        <v>53443</v>
+        <v>0</v>
       </c>
       <c r="G240">
-        <v>76958</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>18760</v>
+        <v>0</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>60686</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>71257</v>
       </c>
       <c r="F241">
-        <v>75686</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>108988</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>28441</v>
+        <v>34561</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>53443</v>
+        <v>51890</v>
       </c>
       <c r="G242">
-        <v>76958</v>
+        <v>74722</v>
       </c>
       <c r="H242">
-        <v>25002</v>
+        <v>17329</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11073,19 +11073,19 @@
         <v>17</v>
       </c>
       <c r="D243">
-        <v>88850</v>
+        <v>0</v>
       </c>
       <c r="E243">
         <v>71257</v>
       </c>
       <c r="F243">
-        <v>103850</v>
+        <v>0</v>
       </c>
       <c r="G243">
-        <v>149544</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I243" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,7 +11116,7 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9506</v>
+        <v>9475</v>
       </c>
       <c r="E244">
         <v>27407</v>
@@ -11128,7 +11128,7 @@
         <v>35552</v>
       </c>
       <c r="H244">
-        <v>15183</v>
+        <v>15214</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11817</v>
+        <v>11801</v>
       </c>
       <c r="E246">
         <v>109608</v>
       </c>
       <c r="F246">
-        <v>38817</v>
+        <v>38801</v>
       </c>
       <c r="G246">
-        <v>55896</v>
+        <v>55873</v>
       </c>
       <c r="H246">
         <v>27000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>58876</v>
+        <v>60208</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>74250</v>
+        <v>75208</v>
       </c>
       <c r="G248">
-        <v>106920</v>
+        <v>108300</v>
       </c>
       <c r="H248">
-        <v>15374</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>45331</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>96836</v>
       </c>
       <c r="F249">
-        <v>61898</v>
+        <v>0</v>
       </c>
       <c r="G249">
-        <v>89133</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>16567</v>
+        <v>0</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>68890</v>
+        <v>72274</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>95396</v>
+        <v>87274</v>
       </c>
       <c r="G250">
-        <v>137370</v>
+        <v>125675</v>
       </c>
       <c r="H250">
-        <v>26506</v>
+        <v>15000</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>67953</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>109608</v>
       </c>
       <c r="F251">
-        <v>82953</v>
+        <v>0</v>
       </c>
       <c r="G251">
-        <v>119452</v>
+        <v>0</v>
       </c>
       <c r="H251">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>10962</v>
+        <v>11817</v>
       </c>
       <c r="E252">
         <v>52986</v>
       </c>
       <c r="F252">
-        <v>39740</v>
+        <v>34665</v>
       </c>
       <c r="G252">
-        <v>57226</v>
+        <v>49918</v>
       </c>
       <c r="H252">
-        <v>28778</v>
+        <v>22848</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>47405</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>52986</v>
       </c>
       <c r="F253">
-        <v>62405</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>89863</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>17577</v>
+        <v>16750</v>
       </c>
       <c r="E254">
         <v>71257</v>
       </c>
       <c r="F254">
-        <v>52577</v>
+        <v>43750</v>
       </c>
       <c r="G254">
-        <v>75711</v>
+        <v>63000</v>
       </c>
       <c r="H254">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>60686</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>71257</v>
       </c>
       <c r="F255">
-        <v>75686</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>108988</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>17516</v>
+        <v>0</v>
       </c>
       <c r="E259">
         <v>51141</v>
       </c>
       <c r="F259">
-        <v>32952</v>
+        <v>0</v>
       </c>
       <c r="G259">
-        <v>47451</v>
+        <v>0</v>
       </c>
       <c r="H259">
-        <v>15436</v>
+        <v>0</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62889</v>
+        <v>0</v>
       </c>
       <c r="E261">
         <v>63930</v>
       </c>
       <c r="F261">
-        <v>77889</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>112160</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75640</v>
+        <v>0</v>
       </c>
       <c r="E263">
         <v>73066</v>
       </c>
       <c r="F263">
-        <v>90640</v>
+        <v>0</v>
       </c>
       <c r="G263">
-        <v>130522</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>35066</v>
+        <v>40898</v>
       </c>
       <c r="E264">
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>52158</v>
+        <v>55898</v>
       </c>
       <c r="G264">
-        <v>75108</v>
+        <v>80493</v>
       </c>
       <c r="H264">
-        <v>17092</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>29158</v>
+        <v>0</v>
       </c>
       <c r="E265">
         <v>60276</v>
       </c>
       <c r="F265">
-        <v>44158</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>63588</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,16 +12171,16 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34173</v>
+        <v>36246</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>49173</v>
+        <v>51246</v>
       </c>
       <c r="G268">
-        <v>70809</v>
+        <v>73794</v>
       </c>
       <c r="H268">
         <v>15000</v>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>25167</v>
+        <v>0</v>
       </c>
       <c r="E269">
         <v>60276</v>
       </c>
       <c r="F269">
-        <v>40167</v>
+        <v>0</v>
       </c>
       <c r="G269">
-        <v>57840</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>45575</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>67584</v>
       </c>
       <c r="F270">
-        <v>62000</v>
+        <v>0</v>
       </c>
       <c r="G270">
-        <v>89280</v>
+        <v>0</v>
       </c>
       <c r="H270">
-        <v>16425</v>
+        <v>0</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>26282</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>67584</v>
       </c>
       <c r="F271">
-        <v>42871</v>
+        <v>0</v>
       </c>
       <c r="G271">
-        <v>61734</v>
+        <v>0</v>
       </c>
       <c r="H271">
-        <v>16589</v>
+        <v>0</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>68839</v>
+        <v>70932</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>93929</v>
+        <v>85932</v>
       </c>
       <c r="G272">
-        <v>135258</v>
+        <v>123742</v>
       </c>
       <c r="H272">
-        <v>25090</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,19 +12394,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>20402</v>
+        <v>0</v>
       </c>
       <c r="E273">
         <v>91337</v>
       </c>
       <c r="F273">
-        <v>47402</v>
+        <v>0</v>
       </c>
       <c r="G273">
-        <v>68259</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>21854</v>
       </c>
       <c r="E274">
         <v>127879</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>48854</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>70350</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,19 +12481,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10457</v>
+        <v>0</v>
       </c>
       <c r="E275">
         <v>127879</v>
       </c>
       <c r="F275">
-        <v>37457</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>53938</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152244</v>
+        <v>151917</v>
       </c>
       <c r="E276">
         <v>164421</v>
       </c>
       <c r="F276">
-        <v>179244</v>
+        <v>166917</v>
       </c>
       <c r="G276">
-        <v>258111</v>
+        <v>240360</v>
       </c>
       <c r="H276">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>45767</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>164421</v>
       </c>
       <c r="F277">
-        <v>72767</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>104784</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>55527</v>
+        <v>52590</v>
       </c>
       <c r="E278">
         <v>109608</v>
       </c>
       <c r="F278">
-        <v>77534</v>
+        <v>76360</v>
       </c>
       <c r="G278">
-        <v>111649</v>
+        <v>109958</v>
       </c>
       <c r="H278">
-        <v>22007</v>
+        <v>23770</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>46448</v>
+        <v>0</v>
       </c>
       <c r="E279">
         <v>109608</v>
       </c>
       <c r="F279">
-        <v>67326</v>
+        <v>0</v>
       </c>
       <c r="G279">
-        <v>96949</v>
+        <v>0</v>
       </c>
       <c r="H279">
-        <v>20878</v>
+        <v>0</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>74348</v>
+        <v>72977</v>
       </c>
       <c r="E280">
         <v>127879</v>
       </c>
       <c r="F280">
-        <v>95909</v>
+        <v>92736</v>
       </c>
       <c r="G280">
-        <v>138109</v>
+        <v>133540</v>
       </c>
       <c r="H280">
-        <v>21561</v>
+        <v>19759</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>72659</v>
+        <v>0</v>
       </c>
       <c r="E281">
         <v>127879</v>
       </c>
       <c r="F281">
-        <v>87659</v>
+        <v>0</v>
       </c>
       <c r="G281">
-        <v>126229</v>
+        <v>0</v>
       </c>
       <c r="H281">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23509</v>
+        <v>23805</v>
       </c>
       <c r="E282">
         <v>54795</v>
       </c>
       <c r="F282">
-        <v>41096</v>
+        <v>40180</v>
       </c>
       <c r="G282">
-        <v>59178</v>
+        <v>57859</v>
       </c>
       <c r="H282">
-        <v>17587</v>
+        <v>16375</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>22709</v>
+        <v>0</v>
       </c>
       <c r="E283">
         <v>54795</v>
       </c>
       <c r="F283">
-        <v>37709</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>54301</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>43201</v>
+        <v>0</v>
       </c>
       <c r="E284">
         <v>82220</v>
       </c>
       <c r="F284">
-        <v>61665</v>
+        <v>0</v>
       </c>
       <c r="G284">
-        <v>88798</v>
+        <v>0</v>
       </c>
       <c r="H284">
-        <v>18464</v>
+        <v>0</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12923,19 +12923,19 @@
         <v>17</v>
       </c>
       <c r="D285">
-        <v>118914</v>
+        <v>0</v>
       </c>
       <c r="E285">
         <v>82220</v>
       </c>
       <c r="F285">
-        <v>133914</v>
+        <v>0</v>
       </c>
       <c r="G285">
-        <v>192836</v>
+        <v>0</v>
       </c>
       <c r="H285">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I285" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>19977</v>
+        <v>0</v>
       </c>
       <c r="E287">
         <v>38351</v>
       </c>
       <c r="F287">
-        <v>34977</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>50367</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>30461</v>
+        <v>34358</v>
       </c>
       <c r="E288">
         <v>58449</v>
       </c>
       <c r="F288">
-        <v>47156</v>
+        <v>49358</v>
       </c>
       <c r="G288">
-        <v>67905</v>
+        <v>71076</v>
       </c>
       <c r="H288">
-        <v>16695</v>
+        <v>15000</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>24156</v>
+        <v>0</v>
       </c>
       <c r="E289">
         <v>58449</v>
       </c>
       <c r="F289">
-        <v>39156</v>
+        <v>0</v>
       </c>
       <c r="G289">
-        <v>56385</v>
+        <v>0</v>
       </c>
       <c r="H289">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13143,19 +13143,19 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>10422</v>
+        <v>10662</v>
       </c>
       <c r="E290">
         <v>43832</v>
       </c>
       <c r="F290">
-        <v>32874</v>
+        <v>31095</v>
       </c>
       <c r="G290">
-        <v>47339</v>
+        <v>44777</v>
       </c>
       <c r="H290">
-        <v>22452</v>
+        <v>20433</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>13646</v>
+        <v>0</v>
       </c>
       <c r="E291">
         <v>43832</v>
       </c>
       <c r="F291">
-        <v>28646</v>
+        <v>0</v>
       </c>
       <c r="G291">
-        <v>41250</v>
+        <v>0</v>
       </c>
       <c r="H291">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>40416</v>
+        <v>0</v>
       </c>
       <c r="E292">
         <v>109608</v>
       </c>
       <c r="F292">
-        <v>72058</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>103764</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>31642</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>35659</v>
+        <v>0</v>
       </c>
       <c r="E293">
         <v>109608</v>
       </c>
       <c r="F293">
-        <v>62659</v>
+        <v>0</v>
       </c>
       <c r="G293">
-        <v>90229</v>
+        <v>0</v>
       </c>
       <c r="H293">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>55945</v>
+        <v>0</v>
       </c>
       <c r="E296">
         <v>73066</v>
       </c>
       <c r="F296">
-        <v>86799</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>124991</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>30854</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>60477</v>
+        <v>0</v>
       </c>
       <c r="E297">
         <v>73066</v>
       </c>
       <c r="F297">
-        <v>75477</v>
+        <v>0</v>
       </c>
       <c r="G297">
-        <v>108687</v>
+        <v>0</v>
       </c>
       <c r="H297">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4479</v>
+        <v>0</v>
       </c>
       <c r="E299">
         <v>54795</v>
       </c>
       <c r="F299">
-        <v>29162</v>
+        <v>0</v>
       </c>
       <c r="G299">
-        <v>41993</v>
+        <v>0</v>
       </c>
       <c r="H299">
-        <v>24683</v>
+        <v>0</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10091</v>
+        <v>0</v>
       </c>
       <c r="E301">
         <v>69412</v>
       </c>
       <c r="F301">
-        <v>37091</v>
+        <v>0</v>
       </c>
       <c r="G301">
-        <v>53411</v>
+        <v>0</v>
       </c>
       <c r="H301">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>19200</v>
+        <v>18498</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>46200</v>
+        <v>45498</v>
       </c>
       <c r="G302">
-        <v>66528</v>
+        <v>65517</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>45409</v>
+        <v>44083</v>
       </c>
       <c r="E304">
         <v>109608</v>
       </c>
       <c r="F304">
-        <v>80409</v>
+        <v>71083</v>
       </c>
       <c r="G304">
-        <v>115789</v>
+        <v>102360</v>
       </c>
       <c r="H304">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>54603</v>
+        <v>0</v>
       </c>
       <c r="E305">
         <v>109608</v>
       </c>
       <c r="F305">
-        <v>70588</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>101647</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>15985</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>23530</v>
+        <v>24601</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>58530</v>
+        <v>51601</v>
       </c>
       <c r="G306">
-        <v>84283</v>
+        <v>74305</v>
       </c>
       <c r="H306">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>64328</v>
+        <v>0</v>
       </c>
       <c r="E307">
         <v>109608</v>
       </c>
       <c r="F307">
-        <v>79328</v>
+        <v>0</v>
       </c>
       <c r="G307">
-        <v>114232</v>
+        <v>0</v>
       </c>
       <c r="H307">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>179978</v>
+        <v>0</v>
       </c>
       <c r="E308">
         <v>237505</v>
       </c>
       <c r="F308">
-        <v>194978</v>
+        <v>0</v>
       </c>
       <c r="G308">
-        <v>280768</v>
+        <v>0</v>
       </c>
       <c r="H308">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>147915</v>
+        <v>0</v>
       </c>
       <c r="E309">
         <v>237505</v>
       </c>
       <c r="F309">
-        <v>162915</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>234598</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>78184</v>
+        <v>71275</v>
       </c>
       <c r="E310">
         <v>127879</v>
       </c>
       <c r="F310">
-        <v>95909</v>
+        <v>92055</v>
       </c>
       <c r="G310">
-        <v>138109</v>
+        <v>132559</v>
       </c>
       <c r="H310">
-        <v>17725</v>
+        <v>20780</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>50560</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>127879</v>
       </c>
       <c r="F311">
-        <v>76097</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>109580</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>25537</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>129807</v>
+        <v>0</v>
       </c>
       <c r="E313">
         <v>182692</v>
       </c>
       <c r="F313">
-        <v>144807</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>208522</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>189830</v>
+        <v>0</v>
       </c>
       <c r="E314">
         <v>237505</v>
       </c>
       <c r="F314">
-        <v>211644</v>
+        <v>0</v>
       </c>
       <c r="G314">
-        <v>304767</v>
+        <v>0</v>
       </c>
       <c r="H314">
-        <v>21814</v>
+        <v>0</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,19 +14235,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>169038</v>
+        <v>0</v>
       </c>
       <c r="E315">
         <v>237505</v>
       </c>
       <c r="F315">
-        <v>184038</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>265015</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -925,16 +925,16 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>87338</v>
+        <v>87322</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>102338</v>
+        <v>102322</v>
       </c>
       <c r="G12">
-        <v>147367</v>
+        <v>147344</v>
       </c>
       <c r="H12">
         <v>15000</v>
@@ -1799,16 +1799,16 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>77472</v>
+        <v>77348</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>92472</v>
+        <v>92348</v>
       </c>
       <c r="G32">
-        <v>133160</v>
+        <v>132981</v>
       </c>
       <c r="H32">
         <v>15000</v>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>47017</v>
+        <v>46939</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>74017</v>
+        <v>73939</v>
       </c>
       <c r="G36">
-        <v>106584</v>
+        <v>106472</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2587,16 +2587,16 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>37433</v>
+        <v>37355</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>52433</v>
+        <v>52355</v>
       </c>
       <c r="G50">
-        <v>75504</v>
+        <v>75391</v>
       </c>
       <c r="H50">
         <v>15000</v>
@@ -2947,16 +2947,16 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>21136</v>
+        <v>20886</v>
       </c>
       <c r="E58">
         <v>36524</v>
       </c>
       <c r="F58">
-        <v>36136</v>
+        <v>35886</v>
       </c>
       <c r="G58">
-        <v>52036</v>
+        <v>51676</v>
       </c>
       <c r="H58">
         <v>15000</v>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26365</v>
+        <v>0</v>
       </c>
       <c r="E60">
         <v>49313</v>
       </c>
       <c r="F60">
-        <v>41365</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>59566</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86667</v>
+        <v>0</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>101667</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>146400</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>47158</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>70898</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>102093</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>23740</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>166418</v>
+        <v>0</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>181418</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>261242</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61878</v>
+        <v>0</v>
       </c>
       <c r="E96">
         <v>82201</v>
       </c>
       <c r="F96">
-        <v>76878</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>110704</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,16 +4698,16 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>76910</v>
+        <v>76676</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>91910</v>
+        <v>91676</v>
       </c>
       <c r="G98">
-        <v>132350</v>
+        <v>132013</v>
       </c>
       <c r="H98">
         <v>15000</v>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>167417</v>
       </c>
       <c r="E116">
         <v>146150</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>182417</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>262680</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37667</v>
+        <v>37651</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62169</v>
+        <v>62162</v>
       </c>
       <c r="G140">
-        <v>89523</v>
+        <v>89513</v>
       </c>
       <c r="H140">
-        <v>24502</v>
+        <v>24511</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>22853</v>
+        <v>0</v>
       </c>
       <c r="E142">
         <v>91337</v>
       </c>
       <c r="F142">
-        <v>49853</v>
+        <v>0</v>
       </c>
       <c r="G142">
-        <v>71788</v>
+        <v>0</v>
       </c>
       <c r="H142">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>44520</v>
+        <v>44379</v>
       </c>
       <c r="E144">
         <v>91337</v>
       </c>
       <c r="F144">
-        <v>64910</v>
+        <v>64853</v>
       </c>
       <c r="G144">
-        <v>93470</v>
+        <v>93388</v>
       </c>
       <c r="H144">
-        <v>20390</v>
+        <v>20474</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,16 +6883,16 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36543</v>
+        <v>36527</v>
       </c>
       <c r="E148">
         <v>62103</v>
       </c>
       <c r="F148">
-        <v>51543</v>
+        <v>51527</v>
       </c>
       <c r="G148">
-        <v>74222</v>
+        <v>74199</v>
       </c>
       <c r="H148">
         <v>15000</v>
@@ -7855,16 +7855,16 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>68981</v>
+        <v>68965</v>
       </c>
       <c r="E170">
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>83981</v>
+        <v>83965</v>
       </c>
       <c r="G170">
-        <v>120933</v>
+        <v>120910</v>
       </c>
       <c r="H170">
         <v>15000</v>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48032</v>
+        <v>47845</v>
       </c>
       <c r="E174">
         <v>91337</v>
       </c>
       <c r="F174">
-        <v>66315</v>
+        <v>66240</v>
       </c>
       <c r="G174">
-        <v>95494</v>
+        <v>95386</v>
       </c>
       <c r="H174">
-        <v>18283</v>
+        <v>18395</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26428</v>
+        <v>26381</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>53428</v>
+        <v>53381</v>
       </c>
       <c r="G178">
-        <v>76936</v>
+        <v>76869</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29831</v>
+        <v>29768</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>56831</v>
+        <v>56768</v>
       </c>
       <c r="G190">
-        <v>81837</v>
+        <v>81746</v>
       </c>
       <c r="H190">
         <v>27000</v>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41944</v>
+        <v>41928</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>68944</v>
+        <v>68928</v>
       </c>
       <c r="G192">
-        <v>99279</v>
+        <v>99256</v>
       </c>
       <c r="H192">
         <v>27000</v>
@@ -9356,16 +9356,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>29128</v>
+        <v>29035</v>
       </c>
       <c r="E204">
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>56128</v>
+        <v>56035</v>
       </c>
       <c r="G204">
-        <v>80824</v>
+        <v>80690</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -10059,16 +10059,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>59302</v>
+        <v>59287</v>
       </c>
       <c r="E220">
         <v>82220</v>
       </c>
       <c r="F220">
-        <v>74302</v>
+        <v>74287</v>
       </c>
       <c r="G220">
-        <v>106995</v>
+        <v>106973</v>
       </c>
       <c r="H220">
         <v>15000</v>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>0</v>
+        <v>74491</v>
       </c>
       <c r="E222">
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>89491</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>128867</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16203</v>
+        <v>16578</v>
       </c>
       <c r="E224">
         <v>60276</v>
       </c>
       <c r="F224">
-        <v>39605</v>
+        <v>39755</v>
       </c>
       <c r="G224">
-        <v>57031</v>
+        <v>57247</v>
       </c>
       <c r="H224">
-        <v>23402</v>
+        <v>23177</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10589,7 +10589,7 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9335</v>
+        <v>9382</v>
       </c>
       <c r="E232">
         <v>52986</v>
@@ -10601,7 +10601,7 @@
         <v>49918</v>
       </c>
       <c r="H232">
-        <v>25330</v>
+        <v>25283</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>8351</v>
+        <v>0</v>
       </c>
       <c r="E236">
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>34717</v>
+        <v>0</v>
       </c>
       <c r="G236">
-        <v>49992</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>26366</v>
+        <v>0</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34561</v>
+        <v>0</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>51890</v>
+        <v>0</v>
       </c>
       <c r="G242">
-        <v>74722</v>
+        <v>0</v>
       </c>
       <c r="H242">
-        <v>17329</v>
+        <v>0</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11291,16 +11291,16 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>60208</v>
+        <v>60161</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>75208</v>
+        <v>75161</v>
       </c>
       <c r="G248">
-        <v>108300</v>
+        <v>108232</v>
       </c>
       <c r="H248">
         <v>15000</v>
@@ -11558,16 +11558,16 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>16750</v>
+        <v>16718</v>
       </c>
       <c r="E254">
         <v>71257</v>
       </c>
       <c r="F254">
-        <v>43750</v>
+        <v>43718</v>
       </c>
       <c r="G254">
-        <v>63000</v>
+        <v>62954</v>
       </c>
       <c r="H254">
         <v>27000</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>36246</v>
+        <v>0</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>51246</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>73794</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>21854</v>
+        <v>0</v>
       </c>
       <c r="E274">
         <v>127879</v>
       </c>
       <c r="F274">
-        <v>48854</v>
+        <v>0</v>
       </c>
       <c r="G274">
-        <v>70350</v>
+        <v>0</v>
       </c>
       <c r="H274">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12525,16 +12525,16 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151917</v>
+        <v>151729</v>
       </c>
       <c r="E276">
         <v>164421</v>
       </c>
       <c r="F276">
-        <v>166917</v>
+        <v>166729</v>
       </c>
       <c r="G276">
-        <v>240360</v>
+        <v>240090</v>
       </c>
       <c r="H276">
         <v>15000</v>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>18498</v>
+        <v>18435</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>45498</v>
+        <v>45435</v>
       </c>
       <c r="G302">
-        <v>65517</v>
+        <v>65426</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44083</v>
+        <v>0</v>
       </c>
       <c r="E304">
         <v>109608</v>
       </c>
       <c r="F304">
-        <v>71083</v>
+        <v>0</v>
       </c>
       <c r="G304">
-        <v>102360</v>
+        <v>0</v>
       </c>
       <c r="H304">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24601</v>
+        <v>24476</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>51601</v>
+        <v>51476</v>
       </c>
       <c r="G306">
-        <v>74305</v>
+        <v>74125</v>
       </c>
       <c r="H306">
         <v>27000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>71275</v>
+        <v>0</v>
       </c>
       <c r="E310">
         <v>127879</v>
       </c>
       <c r="F310">
-        <v>92055</v>
+        <v>0</v>
       </c>
       <c r="G310">
-        <v>132559</v>
+        <v>0</v>
       </c>
       <c r="H310">
-        <v>20780</v>
+        <v>0</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,16 +481,16 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72165</v>
+        <v>72149</v>
       </c>
       <c r="E2">
         <v>73066</v>
       </c>
       <c r="F2">
-        <v>87165</v>
+        <v>87149</v>
       </c>
       <c r="G2">
-        <v>125518</v>
+        <v>125495</v>
       </c>
       <c r="H2">
         <v>15000</v>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35622</v>
+        <v>36153</v>
       </c>
       <c r="E8">
         <v>73066</v>
       </c>
       <c r="F8">
-        <v>53129</v>
+        <v>53341</v>
       </c>
       <c r="G8">
-        <v>76506</v>
+        <v>76811</v>
       </c>
       <c r="H8">
-        <v>17507</v>
+        <v>17188</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>87322</v>
+        <v>0</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>102322</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>147344</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -1799,16 +1799,16 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>77348</v>
+        <v>76973</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>92348</v>
+        <v>91973</v>
       </c>
       <c r="G32">
-        <v>132981</v>
+        <v>132441</v>
       </c>
       <c r="H32">
         <v>15000</v>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>46939</v>
+        <v>46643</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>73939</v>
+        <v>73643</v>
       </c>
       <c r="G36">
-        <v>106472</v>
+        <v>106046</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2587,16 +2587,16 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>37355</v>
+        <v>37152</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>52355</v>
+        <v>52152</v>
       </c>
       <c r="G50">
-        <v>75391</v>
+        <v>75099</v>
       </c>
       <c r="H50">
         <v>15000</v>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>20886</v>
+        <v>0</v>
       </c>
       <c r="E58">
         <v>36524</v>
       </c>
       <c r="F58">
-        <v>35886</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>51676</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>62221</v>
+        <v>62206</v>
       </c>
       <c r="E68">
         <v>109608</v>
       </c>
       <c r="F68">
-        <v>80212</v>
+        <v>80206</v>
       </c>
       <c r="G68">
-        <v>115505</v>
+        <v>115497</v>
       </c>
       <c r="H68">
-        <v>17991</v>
+        <v>18000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>106648</v>
+        <v>106632</v>
       </c>
       <c r="E70">
         <v>127879</v>
       </c>
       <c r="F70">
-        <v>121648</v>
+        <v>121632</v>
       </c>
       <c r="G70">
-        <v>175173</v>
+        <v>175150</v>
       </c>
       <c r="H70">
         <v>15000</v>
@@ -3561,19 +3561,19 @@
         <v>15</v>
       </c>
       <c r="D72">
-        <v>18529</v>
+        <v>0</v>
       </c>
       <c r="E72">
         <v>27388</v>
       </c>
       <c r="F72">
-        <v>33529</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>48282</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I72" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>86011</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>101011</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>145456</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47158</v>
+        <v>46955</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>70898</v>
+        <v>70816</v>
       </c>
       <c r="G84">
-        <v>102093</v>
+        <v>101975</v>
       </c>
       <c r="H84">
-        <v>23740</v>
+        <v>23861</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,16 +4171,16 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>149903</v>
+        <v>149887</v>
       </c>
       <c r="E86">
         <v>146150</v>
       </c>
       <c r="F86">
-        <v>164903</v>
+        <v>164887</v>
       </c>
       <c r="G86">
-        <v>237460</v>
+        <v>237437</v>
       </c>
       <c r="H86">
         <v>15000</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>164826</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>179826</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>258949</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>61878</v>
       </c>
       <c r="E96">
         <v>82201</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>76878</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>110704</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,16 +4698,16 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>76676</v>
+        <v>76864</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>91676</v>
+        <v>91864</v>
       </c>
       <c r="G98">
-        <v>132013</v>
+        <v>132284</v>
       </c>
       <c r="H98">
         <v>15000</v>
@@ -4788,16 +4788,16 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>71260</v>
+        <v>71244</v>
       </c>
       <c r="E100">
         <v>106502</v>
       </c>
       <c r="F100">
-        <v>86260</v>
+        <v>86244</v>
       </c>
       <c r="G100">
-        <v>124214</v>
+        <v>124191</v>
       </c>
       <c r="H100">
         <v>15000</v>
@@ -5307,16 +5307,16 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>81718</v>
+        <v>81703</v>
       </c>
       <c r="E112">
         <v>87683</v>
       </c>
       <c r="F112">
-        <v>96718</v>
+        <v>96703</v>
       </c>
       <c r="G112">
-        <v>139274</v>
+        <v>139252</v>
       </c>
       <c r="H112">
         <v>15000</v>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>167417</v>
+        <v>0</v>
       </c>
       <c r="E116">
         <v>146150</v>
       </c>
       <c r="F116">
-        <v>182417</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>262680</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>43349</v>
       </c>
       <c r="E118">
         <v>58449</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>58349</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>84023</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>82624</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>80374</v>
       </c>
       <c r="F120">
-        <v>97624</v>
+        <v>0</v>
       </c>
       <c r="G120">
-        <v>140579</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37651</v>
+        <v>37745</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62162</v>
+        <v>62200</v>
       </c>
       <c r="G140">
-        <v>89513</v>
+        <v>89568</v>
       </c>
       <c r="H140">
-        <v>24511</v>
+        <v>24455</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>44379</v>
+        <v>43786</v>
       </c>
       <c r="E144">
         <v>91337</v>
       </c>
       <c r="F144">
-        <v>64853</v>
+        <v>64616</v>
       </c>
       <c r="G144">
-        <v>93388</v>
+        <v>93047</v>
       </c>
       <c r="H144">
-        <v>20474</v>
+        <v>20830</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37948</v>
+        <v>37932</v>
       </c>
       <c r="E152">
         <v>73066</v>
       </c>
       <c r="F152">
-        <v>54059</v>
+        <v>54053</v>
       </c>
       <c r="G152">
-        <v>77845</v>
+        <v>77836</v>
       </c>
       <c r="H152">
-        <v>16111</v>
+        <v>16121</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>57211</v>
+        <v>0</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>72211</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>103984</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7766,16 +7766,16 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>89071</v>
+        <v>88821</v>
       </c>
       <c r="E168">
         <v>73066</v>
       </c>
       <c r="F168">
-        <v>104071</v>
+        <v>103821</v>
       </c>
       <c r="G168">
-        <v>149862</v>
+        <v>149502</v>
       </c>
       <c r="H168">
         <v>15000</v>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>47845</v>
+        <v>48578</v>
       </c>
       <c r="E174">
         <v>91337</v>
       </c>
       <c r="F174">
-        <v>66240</v>
+        <v>66533</v>
       </c>
       <c r="G174">
-        <v>95386</v>
+        <v>95808</v>
       </c>
       <c r="H174">
-        <v>18395</v>
+        <v>17955</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8298,19 +8298,19 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25116</v>
+        <v>0</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>52116</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>75047</v>
+        <v>0</v>
       </c>
       <c r="H180">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I180" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
@@ -8734,19 +8734,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29768</v>
+        <v>0</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>56768</v>
+        <v>0</v>
       </c>
       <c r="G190">
-        <v>81746</v>
+        <v>0</v>
       </c>
       <c r="H190">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41928</v>
+        <v>0</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>68928</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>99256</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,19 +8911,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>50873</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>77873</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>112137</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,16 +8998,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>13159</v>
+        <v>12800</v>
       </c>
       <c r="E196">
         <v>73066</v>
       </c>
       <c r="F196">
-        <v>40159</v>
+        <v>39800</v>
       </c>
       <c r="G196">
-        <v>57829</v>
+        <v>57312</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>25757</v>
+        <v>25351</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>52757</v>
+        <v>52351</v>
       </c>
       <c r="G198">
-        <v>75970</v>
+        <v>75385</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,16 +9176,16 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>14096</v>
+        <v>14065</v>
       </c>
       <c r="E200">
         <v>127879</v>
       </c>
       <c r="F200">
-        <v>41096</v>
+        <v>41065</v>
       </c>
       <c r="G200">
-        <v>59178</v>
+        <v>59134</v>
       </c>
       <c r="H200">
         <v>27000</v>
@@ -9356,16 +9356,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>29035</v>
+        <v>28738</v>
       </c>
       <c r="E204">
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>56035</v>
+        <v>55738</v>
       </c>
       <c r="G204">
-        <v>80690</v>
+        <v>80263</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -10589,7 +10589,7 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9382</v>
+        <v>9335</v>
       </c>
       <c r="E232">
         <v>52986</v>
@@ -10601,7 +10601,7 @@
         <v>49918</v>
       </c>
       <c r="H232">
-        <v>25283</v>
+        <v>25330</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,19 +10677,19 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>11926</v>
+        <v>0</v>
       </c>
       <c r="E234">
         <v>71257</v>
       </c>
       <c r="F234">
-        <v>38926</v>
+        <v>0</v>
       </c>
       <c r="G234">
-        <v>56053</v>
+        <v>0</v>
       </c>
       <c r="H234">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I234" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>8351</v>
       </c>
       <c r="E236">
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>0</v>
+        <v>34665</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>49918</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>26314</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>34561</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>0</v>
+        <v>51890</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>74722</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>17329</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9475</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>27407</v>
       </c>
       <c r="F244">
-        <v>24689</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>35552</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15214</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>60161</v>
+        <v>0</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>75161</v>
+        <v>0</v>
       </c>
       <c r="G248">
-        <v>108232</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72274</v>
+        <v>0</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>87274</v>
+        <v>0</v>
       </c>
       <c r="G250">
-        <v>125675</v>
+        <v>0</v>
       </c>
       <c r="H250">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11558,16 +11558,16 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>16718</v>
+        <v>17639</v>
       </c>
       <c r="E254">
         <v>71257</v>
       </c>
       <c r="F254">
-        <v>43718</v>
+        <v>44639</v>
       </c>
       <c r="G254">
-        <v>62954</v>
+        <v>64280</v>
       </c>
       <c r="H254">
         <v>27000</v>
@@ -11992,16 +11992,16 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>40898</v>
+        <v>40289</v>
       </c>
       <c r="E264">
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>55898</v>
+        <v>55289</v>
       </c>
       <c r="G264">
-        <v>80493</v>
+        <v>79616</v>
       </c>
       <c r="H264">
         <v>15000</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>36246</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>51246</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>73794</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>70932</v>
+        <v>0</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>85932</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>123742</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>21854</v>
       </c>
       <c r="E274">
         <v>127879</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>48854</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>70350</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151729</v>
+        <v>0</v>
       </c>
       <c r="E276">
         <v>164421</v>
       </c>
       <c r="F276">
-        <v>166729</v>
+        <v>0</v>
       </c>
       <c r="G276">
-        <v>240090</v>
+        <v>0</v>
       </c>
       <c r="H276">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23805</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>54795</v>
       </c>
       <c r="F282">
-        <v>40180</v>
+        <v>0</v>
       </c>
       <c r="G282">
-        <v>57859</v>
+        <v>0</v>
       </c>
       <c r="H282">
-        <v>16375</v>
+        <v>0</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>18435</v>
+        <v>18404</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>45435</v>
+        <v>45404</v>
       </c>
       <c r="G302">
-        <v>65426</v>
+        <v>65382</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24476</v>
+        <v>24757</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>51476</v>
+        <v>51757</v>
       </c>
       <c r="G306">
-        <v>74125</v>
+        <v>74530</v>
       </c>
       <c r="H306">
         <v>27000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>71260</v>
       </c>
       <c r="E310">
         <v>127879</v>
       </c>
       <c r="F310">
-        <v>0</v>
+        <v>92049</v>
       </c>
       <c r="G310">
-        <v>0</v>
+        <v>132551</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>20789</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,16 +481,16 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72149</v>
+        <v>71749</v>
       </c>
       <c r="E2">
         <v>73066</v>
       </c>
       <c r="F2">
-        <v>87149</v>
+        <v>86749</v>
       </c>
       <c r="G2">
-        <v>125495</v>
+        <v>124919</v>
       </c>
       <c r="H2">
         <v>15000</v>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>46488</v>
       </c>
       <c r="E3">
         <v>73066</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>61488</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88543</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>46488</v>
       </c>
       <c r="E5">
         <v>84028</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>61488</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>88543</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>4270</v>
       </c>
       <c r="E7">
         <v>54795</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29078</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>41872</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>24808</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>36153</v>
+        <v>35780</v>
       </c>
       <c r="E8">
         <v>73066</v>
       </c>
       <c r="F8">
-        <v>53341</v>
+        <v>54800</v>
       </c>
       <c r="G8">
-        <v>76811</v>
+        <v>78912</v>
       </c>
       <c r="H8">
-        <v>17188</v>
+        <v>19020</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>30788</v>
       </c>
       <c r="E9">
         <v>73066</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>46811</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>67408</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>16023</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>41228</v>
       </c>
       <c r="E11">
         <v>109608</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>65238</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>93943</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>24010</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>80698</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>95698</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>137805</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,19 +970,19 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>11728</v>
       </c>
       <c r="E13">
         <v>82201</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>38728</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>55768</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I13" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>42484</v>
       </c>
       <c r="E15">
         <v>73066</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>57484</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>82777</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>33080</v>
       </c>
       <c r="E21">
         <v>102299</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>59128</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>85144</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>26048</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>118205</v>
       </c>
       <c r="E23">
         <v>131533</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>133205</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>191815</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>20583</v>
       </c>
       <c r="E27">
         <v>63930</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>39166</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>56399</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>18583</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>74559</v>
       </c>
       <c r="E28">
         <v>127879</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>93369</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>134451</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>18810</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,19 +1665,19 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>25214</v>
       </c>
       <c r="E29">
         <v>127879</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>52214</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>75188</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I29" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>131205</v>
       </c>
       <c r="E30">
         <v>182692</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>146205</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>210535</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>57227</v>
       </c>
       <c r="E31">
         <v>182692</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>84227</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>121287</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,16 +1799,16 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>76973</v>
+        <v>71576</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>91973</v>
+        <v>86576</v>
       </c>
       <c r="G32">
-        <v>132441</v>
+        <v>124669</v>
       </c>
       <c r="H32">
         <v>15000</v>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>41307</v>
       </c>
       <c r="E33">
         <v>109608</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>65270</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>93989</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>23963</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>47414</v>
       </c>
       <c r="E35">
         <v>127879</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>74414</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>107156</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>46643</v>
+        <v>44729</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>73643</v>
+        <v>71729</v>
       </c>
       <c r="G36">
-        <v>106046</v>
+        <v>103290</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>34650</v>
       </c>
       <c r="E37">
         <v>127879</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>61650</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>88776</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>84262</v>
       </c>
       <c r="E39">
         <v>237505</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>111262</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>160217</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>84262</v>
       </c>
       <c r="E41">
         <v>237505</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>111262</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>160217</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2286,19 +2286,19 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>39156</v>
       </c>
       <c r="E43">
         <v>127879</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>66156</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>95265</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I43" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>92395</v>
       </c>
       <c r="E45">
         <v>182692</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>114208</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>164460</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>21813</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,19 +2457,19 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>26831</v>
       </c>
       <c r="E47">
         <v>109608</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>53831</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>77517</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I47" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/311210/Call_of_Duty_Black_Ops_III/","Abrir Steam")</f>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>37152</v>
+        <v>35780</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>52152</v>
+        <v>56661</v>
       </c>
       <c r="G50">
-        <v>75099</v>
+        <v>81592</v>
       </c>
       <c r="H50">
-        <v>15000</v>
+        <v>20881</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>33661</v>
       </c>
       <c r="E51">
         <v>63930</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>48661</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>70072</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>35749</v>
       </c>
       <c r="E53">
         <v>76720</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>50749</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>73079</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>53277</v>
+        <v>48340</v>
       </c>
       <c r="E54">
         <v>127879</v>
       </c>
       <c r="F54">
-        <v>80277</v>
+        <v>83340</v>
       </c>
       <c r="G54">
-        <v>115599</v>
+        <v>120010</v>
       </c>
       <c r="H54">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>52203</v>
       </c>
       <c r="E55">
         <v>127879</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>76754</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>110526</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>24551</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>62769</v>
       </c>
       <c r="E57">
         <v>146150</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>88106</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>126873</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>25337</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="E59">
         <v>36524</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>22845</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>32897</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>16345</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>25151</v>
       </c>
       <c r="E60">
         <v>49313</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>47979</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>69090</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>22828</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>24979</v>
       </c>
       <c r="E61">
         <v>49313</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>39979</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>57570</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3166,19 +3166,19 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>12858</v>
       </c>
       <c r="E63">
         <v>82201</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>39858</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>57396</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I63" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1091500/Cyberpunk_2077/","Abrir Steam")</f>
@@ -3252,19 +3252,19 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>29516</v>
       </c>
       <c r="E65">
         <v>123293</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>56516</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>81383</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I65" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1091500/Cyberpunk_2077/","Abrir Steam")</f>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>23056</v>
+        <v>25026</v>
       </c>
       <c r="E66">
         <v>91337</v>
       </c>
       <c r="F66">
-        <v>50056</v>
+        <v>54123</v>
       </c>
       <c r="G66">
-        <v>72081</v>
+        <v>77937</v>
       </c>
       <c r="H66">
-        <v>27000</v>
+        <v>29097</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,19 +3341,19 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>19123</v>
       </c>
       <c r="E67">
         <v>91337</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>46123</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>66417</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I67" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>62206</v>
+        <v>34446</v>
       </c>
       <c r="E68">
         <v>109608</v>
       </c>
       <c r="F68">
-        <v>80206</v>
+        <v>62773</v>
       </c>
       <c r="G68">
-        <v>115497</v>
+        <v>90393</v>
       </c>
       <c r="H68">
-        <v>18000</v>
+        <v>28327</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>27585</v>
       </c>
       <c r="E69">
         <v>109608</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>54585</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>78602</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>106632</v>
+        <v>45295</v>
       </c>
       <c r="E70">
         <v>127879</v>
       </c>
       <c r="F70">
-        <v>121632</v>
+        <v>80295</v>
       </c>
       <c r="G70">
-        <v>175150</v>
+        <v>115625</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>50805</v>
       </c>
       <c r="E71">
         <v>127879</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>76195</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>109721</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>25390</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>5542</v>
       </c>
       <c r="E73">
         <v>27388</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>20542</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>29580</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3691,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70524</v>
       </c>
       <c r="E75">
         <v>95904</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85524</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>123155</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86011</v>
+        <v>80572</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>101011</v>
+        <v>95774</v>
       </c>
       <c r="G76">
-        <v>145456</v>
+        <v>137915</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>15202</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>50083</v>
       </c>
       <c r="E77">
         <v>127879</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>75906</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>109305</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>25823</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>37036</v>
       </c>
       <c r="E81">
         <v>91337</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>56436</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>81268</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>19400</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>84639</v>
       </c>
       <c r="E83">
         <v>127879</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>99639</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>143480</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46955</v>
+        <v>46912</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>70816</v>
+        <v>70799</v>
       </c>
       <c r="G84">
-        <v>101975</v>
+        <v>101951</v>
       </c>
       <c r="H84">
-        <v>23861</v>
+        <v>23887</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>32782</v>
       </c>
       <c r="E85">
         <v>102299</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>59009</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>84973</v>
       </c>
       <c r="H85">
-        <v>0</v>
+        <v>26227</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,19 +4215,19 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>113966</v>
       </c>
       <c r="E87">
         <v>146150</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>128966</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>185711</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I87" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,16 +4258,16 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>164826</v>
+        <v>159591</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>179826</v>
+        <v>174591</v>
       </c>
       <c r="G88">
-        <v>258949</v>
+        <v>251411</v>
       </c>
       <c r="H88">
         <v>15000</v>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>127076</v>
       </c>
       <c r="E89">
         <v>160767</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>142076</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>204589</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4352,13 +4352,13 @@
         <v>58449</v>
       </c>
       <c r="F90">
-        <v>35000</v>
+        <v>38503</v>
       </c>
       <c r="G90">
-        <v>50400</v>
+        <v>55444</v>
       </c>
       <c r="H90">
-        <v>27320</v>
+        <v>30823</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>4270</v>
       </c>
       <c r="E91">
         <v>58449</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>30503</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>43924</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>26233</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>12168</v>
       </c>
       <c r="E93">
         <v>27388</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>27168</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>39122</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4608,16 +4608,16 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61878</v>
+        <v>61701</v>
       </c>
       <c r="E96">
         <v>82201</v>
       </c>
       <c r="F96">
-        <v>76878</v>
+        <v>76701</v>
       </c>
       <c r="G96">
-        <v>110704</v>
+        <v>110449</v>
       </c>
       <c r="H96">
         <v>15000</v>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>33551</v>
       </c>
       <c r="E97">
         <v>82201</v>
       </c>
       <c r="F97">
-        <v>0</v>
+        <v>51479</v>
       </c>
       <c r="G97">
-        <v>0</v>
+        <v>74130</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>17928</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,16 +4698,16 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>76864</v>
+        <v>74716</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>91864</v>
+        <v>89716</v>
       </c>
       <c r="G98">
-        <v>132284</v>
+        <v>129191</v>
       </c>
       <c r="H98">
         <v>15000</v>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>33551</v>
       </c>
       <c r="E99">
         <v>94991</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>56467</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>81312</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>22916</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>71244</v>
+        <v>61371</v>
       </c>
       <c r="E100">
         <v>106502</v>
       </c>
       <c r="F100">
-        <v>86244</v>
+        <v>79877</v>
       </c>
       <c r="G100">
-        <v>124191</v>
+        <v>115023</v>
       </c>
       <c r="H100">
-        <v>15000</v>
+        <v>18506</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,19 +4834,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>61466</v>
       </c>
       <c r="E101">
         <v>106502</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>76466</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>110111</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>68892</v>
       </c>
       <c r="E105">
         <v>127879</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>83892</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>120804</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>100668</v>
       </c>
       <c r="E107">
         <v>182692</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>117517</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>169224</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>16849</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,19 +5176,19 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>3988</v>
       </c>
       <c r="E109">
         <v>127879</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>30988</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>44623</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I109" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3405690/EA_SPORTS_FC_26/","Abrir Steam")</f>
@@ -5263,19 +5263,19 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>13392</v>
       </c>
       <c r="E111">
         <v>164421</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>40392</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>58164</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I111" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3405690/EA_SPORTS_FC_26/","Abrir Steam")</f>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>48717</v>
       </c>
       <c r="E113">
         <v>87683</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>63717</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>91752</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>85173</v>
       </c>
       <c r="E115">
         <v>116916</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>100173</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>144249</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>111297</v>
       </c>
       <c r="E117">
         <v>146150</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>126297</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>181868</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>32609</v>
       </c>
       <c r="E119">
         <v>58449</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>47609</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>68557</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>60900</v>
       </c>
       <c r="E120">
         <v>80374</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>79179</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>114018</v>
       </c>
       <c r="H120">
-        <v>0</v>
+        <v>18279</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>53851</v>
       </c>
       <c r="E121">
         <v>80374</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>68851</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>99145</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>53176</v>
       </c>
       <c r="E122">
         <v>91337</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>68372</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>98456</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15196</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>27789</v>
       </c>
       <c r="E123">
         <v>91337</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>52737</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>75941</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>24948</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5839,13 +5839,13 @@
         <v>43832</v>
       </c>
       <c r="F124">
-        <v>31263</v>
+        <v>32874</v>
       </c>
       <c r="G124">
-        <v>45019</v>
+        <v>47339</v>
       </c>
       <c r="H124">
-        <v>17417</v>
+        <v>19028</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>7348</v>
       </c>
       <c r="E125">
         <v>43832</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>26034</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>37489</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>18686</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>30814</v>
+        <v>29642</v>
       </c>
       <c r="E126">
         <v>58449</v>
       </c>
       <c r="F126">
-        <v>45814</v>
+        <v>44642</v>
       </c>
       <c r="G126">
-        <v>65972</v>
+        <v>64284</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>20190</v>
       </c>
       <c r="E129">
         <v>59892</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>37434</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>53905</v>
       </c>
       <c r="H129">
-        <v>0</v>
+        <v>17244</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>29799</v>
       </c>
       <c r="E131">
         <v>74619</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>47021</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>67710</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>17222</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>34713</v>
       </c>
       <c r="E133">
         <v>93931</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>56518</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>81386</v>
       </c>
       <c r="H133">
-        <v>0</v>
+        <v>21805</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>53364</v>
       </c>
       <c r="E135">
         <v>89510</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>68364</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>98444</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>73303</v>
       </c>
       <c r="E137">
         <v>127879</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>88303</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>127156</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>91453</v>
       </c>
       <c r="E139">
         <v>153458</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>106453</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>153292</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37745</v>
+        <v>37868</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62200</v>
+        <v>62249</v>
       </c>
       <c r="G140">
-        <v>89568</v>
+        <v>89639</v>
       </c>
       <c r="H140">
-        <v>24455</v>
+        <v>24381</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>26784</v>
       </c>
       <c r="E142">
         <v>91337</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>60574</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>87227</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>33790</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>27381</v>
       </c>
       <c r="E143">
         <v>91337</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>52574</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>75707</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>25193</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>43786</v>
+        <v>44054</v>
       </c>
       <c r="E144">
         <v>91337</v>
       </c>
       <c r="F144">
-        <v>64616</v>
+        <v>68503</v>
       </c>
       <c r="G144">
-        <v>93047</v>
+        <v>98644</v>
       </c>
       <c r="H144">
-        <v>20830</v>
+        <v>24449</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>53270</v>
       </c>
       <c r="E145">
         <v>91337</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>68270</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>98309</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>58357</v>
       </c>
       <c r="E146">
         <v>91337</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>93357</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>134434</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>94294</v>
       </c>
       <c r="E147">
         <v>91337</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>109294</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>157383</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6889,13 +6889,13 @@
         <v>62103</v>
       </c>
       <c r="F148">
-        <v>51527</v>
+        <v>64265</v>
       </c>
       <c r="G148">
-        <v>74199</v>
+        <v>92542</v>
       </c>
       <c r="H148">
-        <v>15000</v>
+        <v>27738</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>40883</v>
       </c>
       <c r="E149">
         <v>62103</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>55883</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>80472</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>15653</v>
       </c>
       <c r="E151">
         <v>82201</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>42653</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>61420</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37932</v>
+        <v>37633</v>
       </c>
       <c r="E152">
         <v>73066</v>
       </c>
       <c r="F152">
-        <v>54053</v>
+        <v>54800</v>
       </c>
       <c r="G152">
-        <v>77836</v>
+        <v>78912</v>
       </c>
       <c r="H152">
-        <v>16121</v>
+        <v>17167</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>33504</v>
       </c>
       <c r="E153">
         <v>73066</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>48504</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>69846</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>56818</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>91818</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>132218</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>69174</v>
       </c>
       <c r="E155">
         <v>73066</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>84174</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>121211</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>12042</v>
       </c>
       <c r="E157">
         <v>27388</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>27042</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>38940</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>85235</v>
       </c>
       <c r="E158">
         <v>84028</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>100235</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>144338</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>36016</v>
       </c>
       <c r="E159">
         <v>84028</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>53177</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>76575</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>17161</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54813</v>
       </c>
       <c r="F160">
-        <v>35000</v>
+        <v>38818</v>
       </c>
       <c r="G160">
-        <v>50400</v>
+        <v>55898</v>
       </c>
       <c r="H160">
-        <v>27320</v>
+        <v>31138</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>8604</v>
       </c>
       <c r="E161">
         <v>54813</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>30818</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>44378</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>22214</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>73066</v>
       </c>
       <c r="F162">
-        <v>37147</v>
+        <v>44247</v>
       </c>
       <c r="G162">
-        <v>53492</v>
+        <v>63716</v>
       </c>
       <c r="H162">
-        <v>27000</v>
+        <v>34100</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,19 +7547,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>9247</v>
       </c>
       <c r="E163">
         <v>73066</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>36247</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>52196</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7591,16 +7591,16 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>84294</v>
+        <v>67337</v>
       </c>
       <c r="E164">
         <v>68516</v>
       </c>
       <c r="F164">
-        <v>99294</v>
+        <v>82337</v>
       </c>
       <c r="G164">
-        <v>142983</v>
+        <v>118565</v>
       </c>
       <c r="H164">
         <v>15000</v>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>20818</v>
       </c>
       <c r="E165">
         <v>68516</v>
       </c>
       <c r="F165">
-        <v>0</v>
+        <v>41048</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>59109</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>20230</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>90416</v>
       </c>
       <c r="E166">
         <v>103231</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>105416</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>151799</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>21902</v>
       </c>
       <c r="E167">
         <v>103231</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>48902</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>70419</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7811,19 +7811,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>8823</v>
       </c>
       <c r="E169">
         <v>73066</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>35823</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>51585</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>68965</v>
+        <v>58859</v>
       </c>
       <c r="E170">
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>83965</v>
+        <v>78867</v>
       </c>
       <c r="G170">
-        <v>120910</v>
+        <v>113568</v>
       </c>
       <c r="H170">
-        <v>15000</v>
+        <v>20008</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>90694</v>
+        <v>77856</v>
       </c>
       <c r="E172">
         <v>146150</v>
       </c>
       <c r="F172">
-        <v>108045</v>
+        <v>108616</v>
       </c>
       <c r="G172">
-        <v>155585</v>
+        <v>156407</v>
       </c>
       <c r="H172">
-        <v>17351</v>
+        <v>30760</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>78626</v>
       </c>
       <c r="E173">
         <v>146150</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>94449</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>136007</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>15823</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48578</v>
+        <v>48796</v>
       </c>
       <c r="E174">
         <v>91337</v>
       </c>
       <c r="F174">
-        <v>66533</v>
+        <v>68503</v>
       </c>
       <c r="G174">
-        <v>95808</v>
+        <v>98644</v>
       </c>
       <c r="H174">
-        <v>17955</v>
+        <v>19707</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>64260</v>
       </c>
       <c r="E175">
         <v>91337</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>79260</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>114134</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>65438</v>
       </c>
       <c r="E176">
         <v>91337</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>80438</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>115831</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26381</v>
+        <v>27444</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>53381</v>
+        <v>54444</v>
       </c>
       <c r="G178">
-        <v>76869</v>
+        <v>78399</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,19 +8298,19 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>25246</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>0</v>
+        <v>52246</v>
       </c>
       <c r="G180">
-        <v>0</v>
+        <v>75234</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I180" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1817190/Marvels_SpiderMan_Miles_Morales/","Abrir Steam")</f>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>100464</v>
       </c>
       <c r="E182">
         <v>127879</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>115464</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>166268</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>0</v>
+        <v>64229</v>
       </c>
       <c r="E183">
         <v>127879</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>81564</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>117452</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>17335</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>144424</v>
       </c>
       <c r="E184">
         <v>182692</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>159424</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>229571</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,19 +8517,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>64339</v>
       </c>
       <c r="E185">
         <v>182692</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>91339</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>131528</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>188384</v>
       </c>
       <c r="E186">
         <v>237505</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>203384</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>292873</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,19 +8604,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>64339</v>
       </c>
       <c r="E187">
         <v>182692</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>91339</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>131528</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>290434</v>
       </c>
       <c r="E188">
         <v>365402</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>325434</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>468625</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8691,19 +8691,19 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>306433</v>
       </c>
       <c r="E189">
         <v>365402</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>321433</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>462864</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I189" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,19 +8734,19 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>31447</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>0</v>
+        <v>66447</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>95684</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I190" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>44462</v>
       </c>
       <c r="E191">
         <v>95904</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>61188</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>88111</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>16726</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>81326</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>116326</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>167509</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50873</v>
+        <v>50978</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>77873</v>
+        <v>77978</v>
       </c>
       <c r="G194">
-        <v>112137</v>
+        <v>112288</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>12800</v>
+        <v>23848</v>
       </c>
       <c r="E196">
         <v>73066</v>
       </c>
       <c r="F196">
-        <v>39800</v>
+        <v>54800</v>
       </c>
       <c r="G196">
-        <v>57312</v>
+        <v>78912</v>
       </c>
       <c r="H196">
-        <v>27000</v>
+        <v>30952</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>32405</v>
       </c>
       <c r="E197">
         <v>73066</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>47458</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>68340</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>15053</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>25351</v>
+        <v>24932</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>52351</v>
+        <v>59932</v>
       </c>
       <c r="G198">
-        <v>75385</v>
+        <v>86302</v>
       </c>
       <c r="H198">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>37366</v>
       </c>
       <c r="E199">
         <v>109608</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>63693</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>91718</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>26327</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>127879</v>
       </c>
       <c r="F200">
-        <v>41065</v>
+        <v>46916</v>
       </c>
       <c r="G200">
-        <v>59134</v>
+        <v>67559</v>
       </c>
       <c r="H200">
-        <v>27000</v>
+        <v>32851</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,19 +9222,19 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>11916</v>
       </c>
       <c r="E201">
         <v>127879</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>38916</v>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>56039</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I201" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9272,13 +9272,13 @@
         <v>146150</v>
       </c>
       <c r="F202">
-        <v>49432</v>
+        <v>57432</v>
       </c>
       <c r="G202">
-        <v>71182</v>
+        <v>82702</v>
       </c>
       <c r="H202">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>22639</v>
       </c>
       <c r="E203">
         <v>146150</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>49639</v>
       </c>
       <c r="G203">
-        <v>0</v>
+        <v>71480</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9362,13 +9362,13 @@
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>55738</v>
+        <v>61188</v>
       </c>
       <c r="G204">
-        <v>80263</v>
+        <v>88111</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>32450</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>26188</v>
       </c>
       <c r="E205">
         <v>182692</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>53188</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>76591</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9451,13 +9451,13 @@
         <v>58449</v>
       </c>
       <c r="F206">
-        <v>38646</v>
+        <v>41712</v>
       </c>
       <c r="G206">
-        <v>55650</v>
+        <v>60065</v>
       </c>
       <c r="H206">
-        <v>22786</v>
+        <v>25852</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>12293</v>
       </c>
       <c r="E207">
         <v>58449</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>33712</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>48545</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>21419</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,19 +9578,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>22953</v>
       </c>
       <c r="E209">
         <v>54795</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>37953</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>54652</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>40302</v>
       </c>
       <c r="E211">
         <v>109608</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>64868</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>93410</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>24566</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>83508</v>
       </c>
       <c r="E213">
         <v>182692</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>110508</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>159132</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>29019</v>
+        <v>29155</v>
       </c>
       <c r="E214">
         <v>87683</v>
       </c>
       <c r="F214">
-        <v>56019</v>
+        <v>60675</v>
       </c>
       <c r="G214">
-        <v>80667</v>
+        <v>87372</v>
       </c>
       <c r="H214">
-        <v>27000</v>
+        <v>31520</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>31196</v>
       </c>
       <c r="E215">
         <v>87683</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>52675</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>75852</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>21479</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>64794</v>
       </c>
       <c r="E216">
         <v>102299</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>99794</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>143703</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>89003</v>
       </c>
       <c r="E217">
         <v>102299</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>104003</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>149764</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>111250</v>
       </c>
       <c r="E219">
         <v>131533</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>126250</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>181800</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10149,16 +10149,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74491</v>
+        <v>73617</v>
       </c>
       <c r="E222">
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>89491</v>
+        <v>88617</v>
       </c>
       <c r="G222">
-        <v>128867</v>
+        <v>127608</v>
       </c>
       <c r="H222">
         <v>15000</v>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>55421</v>
       </c>
       <c r="E223">
         <v>96836</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>70421</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>101406</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10245,13 +10245,13 @@
         <v>60276</v>
       </c>
       <c r="F224">
-        <v>39755</v>
+        <v>41659</v>
       </c>
       <c r="G224">
-        <v>57247</v>
+        <v>59989</v>
       </c>
       <c r="H224">
-        <v>23177</v>
+        <v>25081</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>10378</v>
       </c>
       <c r="E225">
         <v>60276</v>
       </c>
       <c r="F225">
-        <v>0</v>
+        <v>33659</v>
       </c>
       <c r="G225">
-        <v>0</v>
+        <v>48469</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>23281</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>37853</v>
       </c>
       <c r="E226">
         <v>73066</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>54021</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>77790</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>16168</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>25984</v>
       </c>
       <c r="E227">
         <v>73066</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>44889</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>64640</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>18905</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>83571</v>
       </c>
       <c r="E228">
         <v>109608</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>98571</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>141942</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>14271</v>
       </c>
       <c r="E229">
         <v>109608</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>41271</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>59430</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>19452</v>
       </c>
       <c r="E231">
         <v>182692</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>46452</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>66891</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10595,13 +10595,13 @@
         <v>52986</v>
       </c>
       <c r="F232">
-        <v>34665</v>
+        <v>38653</v>
       </c>
       <c r="G232">
-        <v>49918</v>
+        <v>55660</v>
       </c>
       <c r="H232">
-        <v>25330</v>
+        <v>29318</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>9970</v>
       </c>
       <c r="E233">
         <v>52986</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>30653</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>44140</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>20683</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>34665</v>
+        <v>37509</v>
       </c>
       <c r="G236">
-        <v>49918</v>
+        <v>54013</v>
       </c>
       <c r="H236">
-        <v>26314</v>
+        <v>29158</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>7112</v>
       </c>
       <c r="E237">
         <v>52986</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>29509</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>42493</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>22397</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>11445</v>
       </c>
       <c r="E239">
         <v>52986</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>31243</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>44990</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>19798</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>24194</v>
       </c>
       <c r="E240">
         <v>71257</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>53443</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>76958</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>29249</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>70493</v>
       </c>
       <c r="E241">
         <v>71257</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>85493</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>123110</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34561</v>
+        <v>28543</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>51890</v>
+        <v>49483</v>
       </c>
       <c r="G242">
-        <v>74722</v>
+        <v>71256</v>
       </c>
       <c r="H242">
-        <v>17329</v>
+        <v>20940</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11801</v>
+        <v>92850</v>
       </c>
       <c r="E246">
         <v>109608</v>
       </c>
       <c r="F246">
-        <v>38801</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>55873</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>60084</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>75084</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>108121</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>48246</v>
       </c>
       <c r="E249">
         <v>96836</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>63246</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>91074</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>73806</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>0</v>
+        <v>103156</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>148545</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>29350</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>74701</v>
       </c>
       <c r="E251">
         <v>109608</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>89701</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>129169</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11475,13 +11475,13 @@
         <v>52986</v>
       </c>
       <c r="F252">
-        <v>34665</v>
+        <v>39740</v>
       </c>
       <c r="G252">
-        <v>49918</v>
+        <v>57226</v>
       </c>
       <c r="H252">
-        <v>22848</v>
+        <v>27923</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>38638</v>
       </c>
       <c r="E253">
         <v>52986</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>53638</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>77239</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>17639</v>
+        <v>24335</v>
       </c>
       <c r="E254">
         <v>71257</v>
       </c>
       <c r="F254">
-        <v>44639</v>
+        <v>53443</v>
       </c>
       <c r="G254">
-        <v>64280</v>
+        <v>76958</v>
       </c>
       <c r="H254">
-        <v>27000</v>
+        <v>29108</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>69645</v>
       </c>
       <c r="E255">
         <v>71257</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>84645</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>121889</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>12529</v>
       </c>
       <c r="E259">
         <v>51141</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>30957</v>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>44578</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>18428</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>0</v>
+        <v>12529</v>
       </c>
       <c r="E261">
         <v>63930</v>
       </c>
       <c r="F261">
-        <v>0</v>
+        <v>35945</v>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>51761</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>23416</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>0</v>
+        <v>8965</v>
       </c>
       <c r="E263">
         <v>73066</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>35965</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>51790</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,16 +11992,16 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>40289</v>
+        <v>37068</v>
       </c>
       <c r="E264">
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>55289</v>
+        <v>52068</v>
       </c>
       <c r="G264">
-        <v>79616</v>
+        <v>74978</v>
       </c>
       <c r="H264">
         <v>15000</v>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>12686</v>
       </c>
       <c r="E265">
         <v>60276</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>34582</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>49798</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>21896</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,16 +12171,16 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>36246</v>
+        <v>36063</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>51246</v>
+        <v>51063</v>
       </c>
       <c r="G268">
-        <v>73794</v>
+        <v>73531</v>
       </c>
       <c r="H268">
         <v>15000</v>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>24398</v>
       </c>
       <c r="E269">
         <v>60276</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>39398</v>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>56733</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>39172</v>
       </c>
       <c r="E270">
         <v>67584</v>
       </c>
       <c r="F270">
-        <v>0</v>
+        <v>54172</v>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>78008</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>29139</v>
       </c>
       <c r="E271">
         <v>67584</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>44139</v>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>63560</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>71294</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>86294</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>124263</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,19 +12394,19 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>21525</v>
       </c>
       <c r="E273">
         <v>91337</v>
       </c>
       <c r="F273">
-        <v>0</v>
+        <v>48525</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>69876</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I273" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,19 +12481,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>10221</v>
       </c>
       <c r="E275">
         <v>127879</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>37221</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>53598</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>38465</v>
       </c>
       <c r="E277">
         <v>164421</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>65465</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>94270</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>52590</v>
+        <v>52014</v>
       </c>
       <c r="E278">
         <v>109608</v>
       </c>
       <c r="F278">
-        <v>76360</v>
+        <v>78606</v>
       </c>
       <c r="G278">
-        <v>109958</v>
+        <v>113193</v>
       </c>
       <c r="H278">
-        <v>23770</v>
+        <v>26592</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>49015</v>
       </c>
       <c r="E279">
         <v>109608</v>
       </c>
       <c r="F279">
-        <v>0</v>
+        <v>68353</v>
       </c>
       <c r="G279">
-        <v>0</v>
+        <v>98428</v>
       </c>
       <c r="H279">
-        <v>0</v>
+        <v>19338</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>72977</v>
+        <v>69865</v>
       </c>
       <c r="E280">
         <v>127879</v>
       </c>
       <c r="F280">
-        <v>92736</v>
+        <v>91491</v>
       </c>
       <c r="G280">
-        <v>133540</v>
+        <v>131747</v>
       </c>
       <c r="H280">
-        <v>19759</v>
+        <v>21626</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>49015</v>
       </c>
       <c r="E281">
         <v>127879</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>75479</v>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>108690</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>26464</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>24115</v>
       </c>
       <c r="E282">
         <v>54795</v>
       </c>
       <c r="F282">
-        <v>0</v>
+        <v>41096</v>
       </c>
       <c r="G282">
-        <v>0</v>
+        <v>59178</v>
       </c>
       <c r="H282">
-        <v>0</v>
+        <v>16981</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>24586</v>
       </c>
       <c r="E283">
         <v>54795</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>39586</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>57004</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>65814</v>
       </c>
       <c r="E284">
         <v>82220</v>
       </c>
       <c r="F284">
-        <v>0</v>
+        <v>80814</v>
       </c>
       <c r="G284">
-        <v>0</v>
+        <v>116372</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>20928</v>
       </c>
       <c r="E287">
         <v>38351</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>35928</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>51736</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>34358</v>
+        <v>31541</v>
       </c>
       <c r="E288">
         <v>58449</v>
       </c>
       <c r="F288">
-        <v>49358</v>
+        <v>48748</v>
       </c>
       <c r="G288">
-        <v>71076</v>
+        <v>70197</v>
       </c>
       <c r="H288">
-        <v>15000</v>
+        <v>17207</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>25748</v>
       </c>
       <c r="E289">
         <v>58449</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>40748</v>
       </c>
       <c r="G289">
-        <v>0</v>
+        <v>58677</v>
       </c>
       <c r="H289">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13149,13 +13149,13 @@
         <v>43832</v>
       </c>
       <c r="F290">
-        <v>31095</v>
+        <v>32874</v>
       </c>
       <c r="G290">
-        <v>44777</v>
+        <v>47339</v>
       </c>
       <c r="H290">
-        <v>20433</v>
+        <v>22212</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>34132</v>
       </c>
       <c r="E291">
         <v>43832</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>49132</v>
       </c>
       <c r="G291">
-        <v>0</v>
+        <v>70750</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>0</v>
+        <v>41605</v>
       </c>
       <c r="E292">
         <v>109608</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>73537</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>105893</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>31932</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>37994</v>
       </c>
       <c r="E293">
         <v>109608</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>63945</v>
       </c>
       <c r="G293">
-        <v>0</v>
+        <v>92081</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>25951</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>55327</v>
       </c>
       <c r="E296">
         <v>73066</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>90327</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>130071</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>64433</v>
       </c>
       <c r="E297">
         <v>73066</v>
       </c>
       <c r="F297">
-        <v>0</v>
+        <v>79433</v>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>114384</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>4396</v>
       </c>
       <c r="E299">
         <v>54795</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>29129</v>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>41946</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>24733</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>10739</v>
       </c>
       <c r="E301">
         <v>69412</v>
       </c>
       <c r="F301">
-        <v>0</v>
+        <v>37366</v>
       </c>
       <c r="G301">
-        <v>0</v>
+        <v>53807</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>26627</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>18404</v>
+        <v>24147</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>45404</v>
+        <v>51147</v>
       </c>
       <c r="G302">
-        <v>65382</v>
+        <v>73652</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>44305</v>
       </c>
       <c r="E304">
         <v>109608</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>77040</v>
       </c>
       <c r="G304">
-        <v>0</v>
+        <v>110938</v>
       </c>
       <c r="H304">
-        <v>0</v>
+        <v>32735</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>45609</v>
       </c>
       <c r="E305">
         <v>109608</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>66991</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>96467</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>21382</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24757</v>
+        <v>24304</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>51757</v>
+        <v>59304</v>
       </c>
       <c r="G306">
-        <v>74530</v>
+        <v>85398</v>
       </c>
       <c r="H306">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>33410</v>
       </c>
       <c r="E307">
         <v>109608</v>
       </c>
       <c r="F307">
-        <v>0</v>
+        <v>60410</v>
       </c>
       <c r="G307">
-        <v>0</v>
+        <v>86990</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>0</v>
+        <v>190315</v>
       </c>
       <c r="E308">
         <v>237505</v>
       </c>
       <c r="F308">
-        <v>0</v>
+        <v>205315</v>
       </c>
       <c r="G308">
-        <v>0</v>
+        <v>295654</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>141865</v>
       </c>
       <c r="E309">
         <v>237505</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>156865</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>225886</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>71260</v>
+        <v>71655</v>
       </c>
       <c r="E310">
         <v>127879</v>
       </c>
       <c r="F310">
-        <v>92049</v>
+        <v>92207</v>
       </c>
       <c r="G310">
-        <v>132551</v>
+        <v>132778</v>
       </c>
       <c r="H310">
-        <v>20789</v>
+        <v>20552</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>53882</v>
       </c>
       <c r="E311">
         <v>127879</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>77425</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>111492</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>23543</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>110716</v>
       </c>
       <c r="E313">
         <v>182692</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>125716</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>181031</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>139306</v>
       </c>
       <c r="E314">
         <v>237505</v>
       </c>
       <c r="F314">
-        <v>0</v>
+        <v>174306</v>
       </c>
       <c r="G314">
-        <v>0</v>
+        <v>251001</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,19 +14235,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>147973</v>
       </c>
       <c r="E315">
         <v>237505</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>162973</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>234681</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71749</v>
+        <v>71440</v>
       </c>
       <c r="E2">
         <v>73066</v>
       </c>
       <c r="F2">
-        <v>86749</v>
+        <v>86660</v>
       </c>
       <c r="G2">
-        <v>124919</v>
+        <v>124790</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>15220</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46488</v>
+        <v>46399</v>
       </c>
       <c r="E3">
         <v>73066</v>
       </c>
       <c r="F3">
-        <v>61488</v>
+        <v>61399</v>
       </c>
       <c r="G3">
-        <v>88543</v>
+        <v>88415</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -617,16 +617,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>46488</v>
+        <v>46399</v>
       </c>
       <c r="E5">
         <v>84028</v>
       </c>
       <c r="F5">
-        <v>61488</v>
+        <v>61399</v>
       </c>
       <c r="G5">
-        <v>88543</v>
+        <v>88415</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4270</v>
+        <v>4262</v>
       </c>
       <c r="E7">
         <v>54795</v>
       </c>
       <c r="F7">
-        <v>29078</v>
+        <v>29075</v>
       </c>
       <c r="G7">
-        <v>41872</v>
+        <v>41868</v>
       </c>
       <c r="H7">
-        <v>24808</v>
+        <v>24813</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35780</v>
+        <v>35712</v>
       </c>
       <c r="E8">
         <v>73066</v>
       </c>
       <c r="F8">
-        <v>54800</v>
+        <v>54787</v>
       </c>
       <c r="G8">
-        <v>78912</v>
+        <v>78893</v>
       </c>
       <c r="H8">
-        <v>19020</v>
+        <v>19075</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>30788</v>
+        <v>30729</v>
       </c>
       <c r="E9">
         <v>73066</v>
       </c>
       <c r="F9">
-        <v>46811</v>
+        <v>46787</v>
       </c>
       <c r="G9">
-        <v>67408</v>
+        <v>67373</v>
       </c>
       <c r="H9">
-        <v>16023</v>
+        <v>16058</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41228</v>
+        <v>41149</v>
       </c>
       <c r="E11">
         <v>109608</v>
       </c>
       <c r="F11">
-        <v>65238</v>
+        <v>65207</v>
       </c>
       <c r="G11">
-        <v>93943</v>
+        <v>93898</v>
       </c>
       <c r="H11">
-        <v>24010</v>
+        <v>24058</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>80698</v>
+        <v>80544</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>95698</v>
+        <v>95675</v>
       </c>
       <c r="G12">
-        <v>137805</v>
+        <v>137772</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>15131</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11728</v>
+        <v>11705</v>
       </c>
       <c r="E13">
         <v>82201</v>
       </c>
       <c r="F13">
-        <v>38728</v>
+        <v>38705</v>
       </c>
       <c r="G13">
-        <v>55768</v>
+        <v>55735</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,16 +1056,16 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>42484</v>
+        <v>42403</v>
       </c>
       <c r="E15">
         <v>73066</v>
       </c>
       <c r="F15">
-        <v>57484</v>
+        <v>57403</v>
       </c>
       <c r="G15">
-        <v>82777</v>
+        <v>82660</v>
       </c>
       <c r="H15">
         <v>15000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>33080</v>
+        <v>33017</v>
       </c>
       <c r="E21">
         <v>102299</v>
       </c>
       <c r="F21">
-        <v>59128</v>
+        <v>59103</v>
       </c>
       <c r="G21">
-        <v>85144</v>
+        <v>85108</v>
       </c>
       <c r="H21">
-        <v>26048</v>
+        <v>26086</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,16 +1404,16 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>118205</v>
+        <v>117979</v>
       </c>
       <c r="E23">
         <v>131533</v>
       </c>
       <c r="F23">
-        <v>133205</v>
+        <v>132979</v>
       </c>
       <c r="G23">
-        <v>191815</v>
+        <v>191490</v>
       </c>
       <c r="H23">
         <v>15000</v>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20583</v>
+        <v>20543</v>
       </c>
       <c r="E27">
         <v>63930</v>
       </c>
       <c r="F27">
-        <v>39166</v>
+        <v>39150</v>
       </c>
       <c r="G27">
-        <v>56399</v>
+        <v>56376</v>
       </c>
       <c r="H27">
-        <v>18583</v>
+        <v>18607</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74559</v>
+        <v>74417</v>
       </c>
       <c r="E28">
         <v>127879</v>
       </c>
       <c r="F28">
-        <v>93369</v>
+        <v>93321</v>
       </c>
       <c r="G28">
-        <v>134451</v>
+        <v>134382</v>
       </c>
       <c r="H28">
-        <v>18810</v>
+        <v>18904</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25214</v>
+        <v>25166</v>
       </c>
       <c r="E29">
         <v>127879</v>
       </c>
       <c r="F29">
-        <v>52214</v>
+        <v>52166</v>
       </c>
       <c r="G29">
-        <v>75188</v>
+        <v>75119</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131205</v>
+        <v>130954</v>
       </c>
       <c r="E30">
         <v>182692</v>
       </c>
       <c r="F30">
-        <v>146205</v>
+        <v>146456</v>
       </c>
       <c r="G30">
-        <v>210535</v>
+        <v>210897</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>15502</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57227</v>
+        <v>57478</v>
       </c>
       <c r="E31">
         <v>182692</v>
       </c>
       <c r="F31">
-        <v>84227</v>
+        <v>84478</v>
       </c>
       <c r="G31">
-        <v>121287</v>
+        <v>121648</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71576</v>
+        <v>71440</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>86576</v>
+        <v>86544</v>
       </c>
       <c r="G32">
-        <v>124669</v>
+        <v>124623</v>
       </c>
       <c r="H32">
-        <v>15000</v>
+        <v>15104</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>41307</v>
+        <v>41228</v>
       </c>
       <c r="E33">
         <v>109608</v>
       </c>
       <c r="F33">
-        <v>65270</v>
+        <v>65238</v>
       </c>
       <c r="G33">
-        <v>93989</v>
+        <v>93943</v>
       </c>
       <c r="H33">
-        <v>23963</v>
+        <v>24010</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,16 +1935,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>47414</v>
+        <v>47323</v>
       </c>
       <c r="E35">
         <v>127879</v>
       </c>
       <c r="F35">
-        <v>74414</v>
+        <v>74323</v>
       </c>
       <c r="G35">
-        <v>107156</v>
+        <v>107025</v>
       </c>
       <c r="H35">
         <v>27000</v>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44729</v>
+        <v>44644</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>71729</v>
+        <v>72258</v>
       </c>
       <c r="G36">
-        <v>103290</v>
+        <v>104052</v>
       </c>
       <c r="H36">
-        <v>27000</v>
+        <v>27614</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,16 +2025,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>34650</v>
+        <v>35179</v>
       </c>
       <c r="E37">
         <v>127879</v>
       </c>
       <c r="F37">
-        <v>61650</v>
+        <v>62179</v>
       </c>
       <c r="G37">
-        <v>88776</v>
+        <v>89538</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>84262</v>
+        <v>84242</v>
       </c>
       <c r="E39">
         <v>237505</v>
       </c>
       <c r="F39">
-        <v>111262</v>
+        <v>111242</v>
       </c>
       <c r="G39">
-        <v>160217</v>
+        <v>160188</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>84262</v>
+        <v>84242</v>
       </c>
       <c r="E41">
         <v>237505</v>
       </c>
       <c r="F41">
-        <v>111262</v>
+        <v>111242</v>
       </c>
       <c r="G41">
-        <v>160217</v>
+        <v>160188</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>39156</v>
+        <v>39081</v>
       </c>
       <c r="E43">
         <v>127879</v>
       </c>
       <c r="F43">
-        <v>66156</v>
+        <v>66081</v>
       </c>
       <c r="G43">
-        <v>95265</v>
+        <v>95157</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92395</v>
+        <v>91654</v>
       </c>
       <c r="E45">
         <v>182692</v>
       </c>
       <c r="F45">
-        <v>114208</v>
+        <v>113912</v>
       </c>
       <c r="G45">
-        <v>164460</v>
+        <v>164033</v>
       </c>
       <c r="H45">
-        <v>21813</v>
+        <v>22258</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>26831</v>
+        <v>26780</v>
       </c>
       <c r="E47">
         <v>109608</v>
       </c>
       <c r="F47">
-        <v>53831</v>
+        <v>53780</v>
       </c>
       <c r="G47">
-        <v>77517</v>
+        <v>77443</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35780</v>
+        <v>35712</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>56661</v>
+        <v>56220</v>
       </c>
       <c r="G50">
-        <v>81592</v>
+        <v>80957</v>
       </c>
       <c r="H50">
-        <v>20881</v>
+        <v>20508</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33661</v>
+        <v>33220</v>
       </c>
       <c r="E51">
         <v>63930</v>
       </c>
       <c r="F51">
-        <v>48661</v>
+        <v>48220</v>
       </c>
       <c r="G51">
-        <v>70072</v>
+        <v>69437</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2723,16 +2723,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>35749</v>
+        <v>35681</v>
       </c>
       <c r="E53">
         <v>76720</v>
       </c>
       <c r="F53">
-        <v>50749</v>
+        <v>50681</v>
       </c>
       <c r="G53">
-        <v>73079</v>
+        <v>72981</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48340</v>
+        <v>48248</v>
       </c>
       <c r="E54">
         <v>127879</v>
       </c>
       <c r="F54">
-        <v>83340</v>
+        <v>83248</v>
       </c>
       <c r="G54">
-        <v>120010</v>
+        <v>119877</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52203</v>
+        <v>52103</v>
       </c>
       <c r="E55">
         <v>127879</v>
       </c>
       <c r="F55">
-        <v>76754</v>
+        <v>76714</v>
       </c>
       <c r="G55">
-        <v>110526</v>
+        <v>110468</v>
       </c>
       <c r="H55">
-        <v>24551</v>
+        <v>24611</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62769</v>
+        <v>62649</v>
       </c>
       <c r="E57">
         <v>146150</v>
       </c>
       <c r="F57">
-        <v>88106</v>
+        <v>88058</v>
       </c>
       <c r="G57">
-        <v>126873</v>
+        <v>126804</v>
       </c>
       <c r="H57">
-        <v>25337</v>
+        <v>25409</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6500</v>
+        <v>6440</v>
       </c>
       <c r="E59">
         <v>36524</v>
       </c>
       <c r="F59">
-        <v>22845</v>
+        <v>22821</v>
       </c>
       <c r="G59">
-        <v>32897</v>
+        <v>32862</v>
       </c>
       <c r="H59">
-        <v>16345</v>
+        <v>16381</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>25151</v>
+        <v>26185</v>
       </c>
       <c r="E60">
         <v>49313</v>
       </c>
       <c r="F60">
-        <v>47979</v>
+        <v>47931</v>
       </c>
       <c r="G60">
-        <v>69090</v>
+        <v>69021</v>
       </c>
       <c r="H60">
-        <v>22828</v>
+        <v>21746</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24979</v>
+        <v>24931</v>
       </c>
       <c r="E61">
         <v>49313</v>
       </c>
       <c r="F61">
-        <v>39979</v>
+        <v>39931</v>
       </c>
       <c r="G61">
-        <v>57570</v>
+        <v>57501</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12858</v>
+        <v>12834</v>
       </c>
       <c r="E63">
         <v>82201</v>
       </c>
       <c r="F63">
-        <v>39858</v>
+        <v>39834</v>
       </c>
       <c r="G63">
-        <v>57396</v>
+        <v>57361</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>29516</v>
+        <v>29428</v>
       </c>
       <c r="E65">
         <v>123293</v>
       </c>
       <c r="F65">
-        <v>56516</v>
+        <v>56428</v>
       </c>
       <c r="G65">
-        <v>81383</v>
+        <v>81256</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25026</v>
+        <v>24978</v>
       </c>
       <c r="E66">
         <v>91337</v>
       </c>
       <c r="F66">
-        <v>54123</v>
+        <v>54086</v>
       </c>
       <c r="G66">
-        <v>77937</v>
+        <v>77884</v>
       </c>
       <c r="H66">
-        <v>29097</v>
+        <v>29108</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>19123</v>
+        <v>19086</v>
       </c>
       <c r="E67">
         <v>91337</v>
       </c>
       <c r="F67">
-        <v>46123</v>
+        <v>46086</v>
       </c>
       <c r="G67">
-        <v>66417</v>
+        <v>66364</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34446</v>
+        <v>34380</v>
       </c>
       <c r="E68">
         <v>109608</v>
       </c>
       <c r="F68">
-        <v>62773</v>
+        <v>62720</v>
       </c>
       <c r="G68">
-        <v>90393</v>
+        <v>90317</v>
       </c>
       <c r="H68">
-        <v>28327</v>
+        <v>28340</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27585</v>
+        <v>27532</v>
       </c>
       <c r="E69">
         <v>109608</v>
       </c>
       <c r="F69">
-        <v>54585</v>
+        <v>54532</v>
       </c>
       <c r="G69">
-        <v>78602</v>
+        <v>78526</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45295</v>
+        <v>45208</v>
       </c>
       <c r="E70">
         <v>127879</v>
       </c>
       <c r="F70">
-        <v>80295</v>
+        <v>80208</v>
       </c>
       <c r="G70">
-        <v>115625</v>
+        <v>115500</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50805</v>
+        <v>50708</v>
       </c>
       <c r="E71">
         <v>127879</v>
       </c>
       <c r="F71">
-        <v>76195</v>
+        <v>76156</v>
       </c>
       <c r="G71">
-        <v>109721</v>
+        <v>109665</v>
       </c>
       <c r="H71">
-        <v>25390</v>
+        <v>25448</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5542</v>
+        <v>5532</v>
       </c>
       <c r="E73">
         <v>27388</v>
       </c>
       <c r="F73">
-        <v>20542</v>
+        <v>20532</v>
       </c>
       <c r="G73">
-        <v>29580</v>
+        <v>29566</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70524</v>
+        <v>70390</v>
       </c>
       <c r="E75">
         <v>95904</v>
       </c>
       <c r="F75">
-        <v>85524</v>
+        <v>85390</v>
       </c>
       <c r="G75">
-        <v>123155</v>
+        <v>122962</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80572</v>
+        <v>80418</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>95774</v>
+        <v>95713</v>
       </c>
       <c r="G76">
-        <v>137915</v>
+        <v>137827</v>
       </c>
       <c r="H76">
-        <v>15202</v>
+        <v>15295</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>50083</v>
+        <v>49878</v>
       </c>
       <c r="E77">
         <v>127879</v>
       </c>
       <c r="F77">
-        <v>75906</v>
+        <v>75824</v>
       </c>
       <c r="G77">
-        <v>109305</v>
+        <v>109187</v>
       </c>
       <c r="H77">
-        <v>25823</v>
+        <v>25946</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37036</v>
+        <v>36966</v>
       </c>
       <c r="E81">
         <v>91337</v>
       </c>
       <c r="F81">
-        <v>56436</v>
+        <v>56408</v>
       </c>
       <c r="G81">
-        <v>81268</v>
+        <v>81228</v>
       </c>
       <c r="H81">
-        <v>19400</v>
+        <v>19442</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84639</v>
+        <v>84477</v>
       </c>
       <c r="E83">
         <v>127879</v>
       </c>
       <c r="F83">
-        <v>99639</v>
+        <v>99477</v>
       </c>
       <c r="G83">
-        <v>143480</v>
+        <v>143247</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46912</v>
+        <v>46822</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>70799</v>
+        <v>70763</v>
       </c>
       <c r="G84">
-        <v>101951</v>
+        <v>101899</v>
       </c>
       <c r="H84">
-        <v>23887</v>
+        <v>23941</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32782</v>
+        <v>32672</v>
       </c>
       <c r="E85">
         <v>102299</v>
       </c>
       <c r="F85">
-        <v>59009</v>
+        <v>58965</v>
       </c>
       <c r="G85">
-        <v>84973</v>
+        <v>84910</v>
       </c>
       <c r="H85">
-        <v>26227</v>
+        <v>26293</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113966</v>
+        <v>113749</v>
       </c>
       <c r="E87">
         <v>146150</v>
       </c>
       <c r="F87">
-        <v>128966</v>
+        <v>128749</v>
       </c>
       <c r="G87">
-        <v>185711</v>
+        <v>185399</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>159591</v>
+        <v>159286</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>174591</v>
+        <v>174348</v>
       </c>
       <c r="G88">
-        <v>251411</v>
+        <v>251061</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>15062</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127076</v>
+        <v>126833</v>
       </c>
       <c r="E89">
         <v>160767</v>
       </c>
       <c r="F89">
-        <v>142076</v>
+        <v>141833</v>
       </c>
       <c r="G89">
-        <v>204589</v>
+        <v>204240</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4352,13 +4352,13 @@
         <v>58449</v>
       </c>
       <c r="F90">
-        <v>38503</v>
+        <v>38500</v>
       </c>
       <c r="G90">
-        <v>55444</v>
+        <v>55440</v>
       </c>
       <c r="H90">
-        <v>30823</v>
+        <v>30820</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4270</v>
+        <v>4262</v>
       </c>
       <c r="E91">
         <v>58449</v>
       </c>
       <c r="F91">
-        <v>30503</v>
+        <v>30500</v>
       </c>
       <c r="G91">
-        <v>43924</v>
+        <v>43920</v>
       </c>
       <c r="H91">
-        <v>26233</v>
+        <v>26238</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12168</v>
+        <v>12144</v>
       </c>
       <c r="E93">
         <v>27388</v>
       </c>
       <c r="F93">
-        <v>27168</v>
+        <v>27144</v>
       </c>
       <c r="G93">
-        <v>39122</v>
+        <v>39087</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33551</v>
+        <v>33487</v>
       </c>
       <c r="E97">
         <v>82201</v>
       </c>
       <c r="F97">
-        <v>51479</v>
+        <v>51453</v>
       </c>
       <c r="G97">
-        <v>74130</v>
+        <v>74092</v>
       </c>
       <c r="H97">
-        <v>17928</v>
+        <v>17966</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>74716</v>
+        <v>74574</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>89716</v>
+        <v>89690</v>
       </c>
       <c r="G98">
-        <v>129191</v>
+        <v>129154</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>15116</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33551</v>
+        <v>33487</v>
       </c>
       <c r="E99">
         <v>94991</v>
       </c>
       <c r="F99">
-        <v>56467</v>
+        <v>56441</v>
       </c>
       <c r="G99">
-        <v>81312</v>
+        <v>81275</v>
       </c>
       <c r="H99">
-        <v>22916</v>
+        <v>22954</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61371</v>
+        <v>61254</v>
       </c>
       <c r="E100">
         <v>106502</v>
@@ -4800,7 +4800,7 @@
         <v>115023</v>
       </c>
       <c r="H100">
-        <v>18506</v>
+        <v>18623</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61466</v>
+        <v>61348</v>
       </c>
       <c r="E101">
         <v>106502</v>
       </c>
       <c r="F101">
-        <v>76466</v>
+        <v>76348</v>
       </c>
       <c r="G101">
-        <v>110111</v>
+        <v>109941</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68892</v>
+        <v>68760</v>
       </c>
       <c r="E105">
         <v>127879</v>
       </c>
       <c r="F105">
-        <v>83892</v>
+        <v>83760</v>
       </c>
       <c r="G105">
-        <v>120804</v>
+        <v>120614</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>100668</v>
+        <v>100476</v>
       </c>
       <c r="E107">
         <v>182692</v>
       </c>
       <c r="F107">
-        <v>117517</v>
+        <v>117440</v>
       </c>
       <c r="G107">
-        <v>169224</v>
+        <v>169114</v>
       </c>
       <c r="H107">
-        <v>16849</v>
+        <v>16964</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3988</v>
+        <v>4106</v>
       </c>
       <c r="E109">
         <v>127879</v>
       </c>
       <c r="F109">
-        <v>30988</v>
+        <v>31106</v>
       </c>
       <c r="G109">
-        <v>44623</v>
+        <v>44793</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13392</v>
+        <v>13367</v>
       </c>
       <c r="E111">
         <v>164421</v>
       </c>
       <c r="F111">
-        <v>40392</v>
+        <v>40367</v>
       </c>
       <c r="G111">
-        <v>58164</v>
+        <v>58128</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48717</v>
+        <v>48593</v>
       </c>
       <c r="E113">
         <v>87683</v>
       </c>
       <c r="F113">
-        <v>63717</v>
+        <v>63593</v>
       </c>
       <c r="G113">
-        <v>91752</v>
+        <v>91574</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85173</v>
+        <v>85010</v>
       </c>
       <c r="E115">
         <v>116916</v>
       </c>
       <c r="F115">
-        <v>100173</v>
+        <v>100010</v>
       </c>
       <c r="G115">
-        <v>144249</v>
+        <v>144014</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,16 +5526,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>111297</v>
+        <v>110709</v>
       </c>
       <c r="E117">
         <v>146150</v>
       </c>
       <c r="F117">
-        <v>126297</v>
+        <v>125709</v>
       </c>
       <c r="G117">
-        <v>181868</v>
+        <v>181021</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>32609</v>
+        <v>32500</v>
       </c>
       <c r="E119">
         <v>58449</v>
       </c>
       <c r="F119">
-        <v>47609</v>
+        <v>47500</v>
       </c>
       <c r="G119">
-        <v>68557</v>
+        <v>68400</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60900</v>
+        <v>60784</v>
       </c>
       <c r="E120">
         <v>80374</v>
       </c>
       <c r="F120">
-        <v>79179</v>
+        <v>79076</v>
       </c>
       <c r="G120">
-        <v>114018</v>
+        <v>113869</v>
       </c>
       <c r="H120">
-        <v>18279</v>
+        <v>18292</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53851</v>
+        <v>53748</v>
       </c>
       <c r="E121">
         <v>80374</v>
       </c>
       <c r="F121">
-        <v>68851</v>
+        <v>68748</v>
       </c>
       <c r="G121">
-        <v>99145</v>
+        <v>98997</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>53176</v>
+        <v>53074</v>
       </c>
       <c r="E122">
         <v>91337</v>
       </c>
       <c r="F122">
-        <v>68372</v>
+        <v>68351</v>
       </c>
       <c r="G122">
-        <v>98456</v>
+        <v>98425</v>
       </c>
       <c r="H122">
-        <v>15196</v>
+        <v>15277</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>27789</v>
+        <v>27736</v>
       </c>
       <c r="E123">
         <v>91337</v>
       </c>
       <c r="F123">
-        <v>52737</v>
+        <v>52716</v>
       </c>
       <c r="G123">
-        <v>75941</v>
+        <v>75911</v>
       </c>
       <c r="H123">
-        <v>24948</v>
+        <v>24980</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7348</v>
+        <v>7334</v>
       </c>
       <c r="E125">
         <v>43832</v>
       </c>
       <c r="F125">
-        <v>26034</v>
+        <v>26028</v>
       </c>
       <c r="G125">
-        <v>37489</v>
+        <v>37480</v>
       </c>
       <c r="H125">
-        <v>18686</v>
+        <v>18694</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20190</v>
+        <v>20152</v>
       </c>
       <c r="E129">
         <v>59892</v>
       </c>
       <c r="F129">
-        <v>37434</v>
+        <v>37419</v>
       </c>
       <c r="G129">
-        <v>53905</v>
+        <v>53883</v>
       </c>
       <c r="H129">
-        <v>17244</v>
+        <v>17267</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>29799</v>
+        <v>29742</v>
       </c>
       <c r="E131">
         <v>74619</v>
       </c>
       <c r="F131">
-        <v>47021</v>
+        <v>46998</v>
       </c>
       <c r="G131">
-        <v>67710</v>
+        <v>67677</v>
       </c>
       <c r="H131">
-        <v>17222</v>
+        <v>17256</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>34713</v>
+        <v>35116</v>
       </c>
       <c r="E133">
         <v>93931</v>
       </c>
       <c r="F133">
-        <v>56518</v>
+        <v>56679</v>
       </c>
       <c r="G133">
-        <v>81386</v>
+        <v>81618</v>
       </c>
       <c r="H133">
-        <v>21805</v>
+        <v>21563</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53364</v>
+        <v>53262</v>
       </c>
       <c r="E135">
         <v>89510</v>
       </c>
       <c r="F135">
-        <v>68364</v>
+        <v>68262</v>
       </c>
       <c r="G135">
-        <v>98444</v>
+        <v>98297</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>73303</v>
+        <v>73163</v>
       </c>
       <c r="E137">
         <v>127879</v>
       </c>
       <c r="F137">
-        <v>88303</v>
+        <v>88163</v>
       </c>
       <c r="G137">
-        <v>127156</v>
+        <v>126955</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6486,16 +6486,16 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91453</v>
+        <v>91278</v>
       </c>
       <c r="E139">
         <v>153458</v>
       </c>
       <c r="F139">
-        <v>106453</v>
+        <v>106278</v>
       </c>
       <c r="G139">
-        <v>153292</v>
+        <v>153040</v>
       </c>
       <c r="H139">
         <v>15000</v>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37868</v>
+        <v>37796</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62249</v>
+        <v>62220</v>
       </c>
       <c r="G140">
-        <v>89639</v>
+        <v>89597</v>
       </c>
       <c r="H140">
-        <v>24381</v>
+        <v>24424</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26784</v>
+        <v>26733</v>
       </c>
       <c r="E142">
         <v>91337</v>
       </c>
       <c r="F142">
-        <v>60574</v>
+        <v>60553</v>
       </c>
       <c r="G142">
-        <v>87227</v>
+        <v>87196</v>
       </c>
       <c r="H142">
-        <v>33790</v>
+        <v>33820</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27381</v>
+        <v>27328</v>
       </c>
       <c r="E143">
         <v>91337</v>
       </c>
       <c r="F143">
-        <v>52574</v>
+        <v>52553</v>
       </c>
       <c r="G143">
-        <v>75707</v>
+        <v>75676</v>
       </c>
       <c r="H143">
-        <v>25193</v>
+        <v>25225</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>44054</v>
+        <v>43970</v>
       </c>
       <c r="E144">
         <v>91337</v>
@@ -6718,7 +6718,7 @@
         <v>98644</v>
       </c>
       <c r="H144">
-        <v>24449</v>
+        <v>24533</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>53270</v>
+        <v>53278</v>
       </c>
       <c r="E145">
         <v>91337</v>
       </c>
       <c r="F145">
-        <v>68270</v>
+        <v>68278</v>
       </c>
       <c r="G145">
-        <v>98309</v>
+        <v>98320</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58357</v>
+        <v>58245</v>
       </c>
       <c r="E146">
         <v>91337</v>
       </c>
       <c r="F146">
-        <v>93357</v>
+        <v>93245</v>
       </c>
       <c r="G146">
-        <v>134434</v>
+        <v>134273</v>
       </c>
       <c r="H146">
         <v>35000</v>
@@ -6840,16 +6840,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>94294</v>
+        <v>94114</v>
       </c>
       <c r="E147">
         <v>91337</v>
       </c>
       <c r="F147">
-        <v>109294</v>
+        <v>109114</v>
       </c>
       <c r="G147">
-        <v>157383</v>
+        <v>157124</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36527</v>
+        <v>36668</v>
       </c>
       <c r="E148">
         <v>62103</v>
       </c>
       <c r="F148">
-        <v>64265</v>
+        <v>64187</v>
       </c>
       <c r="G148">
-        <v>92542</v>
+        <v>92429</v>
       </c>
       <c r="H148">
-        <v>27738</v>
+        <v>27519</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>40883</v>
+        <v>40805</v>
       </c>
       <c r="E149">
         <v>62103</v>
       </c>
       <c r="F149">
-        <v>55883</v>
+        <v>55805</v>
       </c>
       <c r="G149">
-        <v>80472</v>
+        <v>80359</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -7014,16 +7014,16 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15653</v>
+        <v>15623</v>
       </c>
       <c r="E151">
         <v>82201</v>
       </c>
       <c r="F151">
-        <v>42653</v>
+        <v>42623</v>
       </c>
       <c r="G151">
-        <v>61420</v>
+        <v>61377</v>
       </c>
       <c r="H151">
         <v>27000</v>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37633</v>
+        <v>37561</v>
       </c>
       <c r="E152">
         <v>73066</v>
@@ -7070,7 +7070,7 @@
         <v>78912</v>
       </c>
       <c r="H152">
-        <v>17167</v>
+        <v>17239</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33504</v>
+        <v>33440</v>
       </c>
       <c r="E153">
         <v>73066</v>
       </c>
       <c r="F153">
-        <v>48504</v>
+        <v>48440</v>
       </c>
       <c r="G153">
-        <v>69846</v>
+        <v>69754</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,16 +7148,16 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56818</v>
+        <v>57196</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>91818</v>
+        <v>92196</v>
       </c>
       <c r="G154">
-        <v>132218</v>
+        <v>132762</v>
       </c>
       <c r="H154">
         <v>35000</v>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>69174</v>
+        <v>69042</v>
       </c>
       <c r="E155">
         <v>73066</v>
       </c>
       <c r="F155">
-        <v>84174</v>
+        <v>84042</v>
       </c>
       <c r="G155">
-        <v>121211</v>
+        <v>121020</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>12042</v>
+        <v>12003</v>
       </c>
       <c r="E157">
         <v>27388</v>
       </c>
       <c r="F157">
-        <v>27042</v>
+        <v>27003</v>
       </c>
       <c r="G157">
-        <v>38940</v>
+        <v>38884</v>
       </c>
       <c r="H157">
         <v>15000</v>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>85235</v>
+        <v>85072</v>
       </c>
       <c r="E158">
         <v>84028</v>
       </c>
       <c r="F158">
-        <v>100235</v>
+        <v>100208</v>
       </c>
       <c r="G158">
-        <v>144338</v>
+        <v>144300</v>
       </c>
       <c r="H158">
-        <v>15000</v>
+        <v>15136</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36016</v>
+        <v>35947</v>
       </c>
       <c r="E159">
         <v>84028</v>
       </c>
       <c r="F159">
-        <v>53177</v>
+        <v>53150</v>
       </c>
       <c r="G159">
-        <v>76575</v>
+        <v>76536</v>
       </c>
       <c r="H159">
-        <v>17161</v>
+        <v>17203</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54813</v>
       </c>
       <c r="F160">
-        <v>38818</v>
+        <v>38812</v>
       </c>
       <c r="G160">
-        <v>55898</v>
+        <v>55889</v>
       </c>
       <c r="H160">
-        <v>31138</v>
+        <v>31132</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8604</v>
+        <v>8587</v>
       </c>
       <c r="E161">
         <v>54813</v>
       </c>
       <c r="F161">
-        <v>30818</v>
+        <v>30812</v>
       </c>
       <c r="G161">
-        <v>44378</v>
+        <v>44369</v>
       </c>
       <c r="H161">
-        <v>22214</v>
+        <v>22225</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>73066</v>
       </c>
       <c r="F162">
-        <v>44247</v>
+        <v>44245</v>
       </c>
       <c r="G162">
-        <v>63716</v>
+        <v>63713</v>
       </c>
       <c r="H162">
-        <v>34100</v>
+        <v>34098</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9247</v>
+        <v>9245</v>
       </c>
       <c r="E163">
         <v>73066</v>
       </c>
       <c r="F163">
-        <v>36247</v>
+        <v>36245</v>
       </c>
       <c r="G163">
-        <v>52196</v>
+        <v>52193</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>67337</v>
+        <v>67209</v>
       </c>
       <c r="E164">
         <v>68516</v>
       </c>
       <c r="F164">
-        <v>82337</v>
+        <v>82321</v>
       </c>
       <c r="G164">
-        <v>118565</v>
+        <v>118542</v>
       </c>
       <c r="H164">
-        <v>15000</v>
+        <v>15112</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20818</v>
+        <v>20778</v>
       </c>
       <c r="E165">
         <v>68516</v>
       </c>
       <c r="F165">
-        <v>41048</v>
+        <v>41032</v>
       </c>
       <c r="G165">
-        <v>59109</v>
+        <v>59086</v>
       </c>
       <c r="H165">
-        <v>20230</v>
+        <v>20254</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>90416</v>
+        <v>90244</v>
       </c>
       <c r="E166">
         <v>103231</v>
       </c>
       <c r="F166">
-        <v>105416</v>
+        <v>105374</v>
       </c>
       <c r="G166">
-        <v>151799</v>
+        <v>151739</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>15130</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21902</v>
+        <v>21860</v>
       </c>
       <c r="E167">
         <v>103231</v>
       </c>
       <c r="F167">
-        <v>48902</v>
+        <v>48860</v>
       </c>
       <c r="G167">
-        <v>70419</v>
+        <v>70358</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>73066</v>
       </c>
       <c r="F168">
-        <v>103821</v>
+        <v>103852</v>
       </c>
       <c r="G168">
-        <v>149502</v>
+        <v>149547</v>
       </c>
       <c r="H168">
-        <v>15000</v>
+        <v>15031</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8823</v>
+        <v>8854</v>
       </c>
       <c r="E169">
         <v>73066</v>
       </c>
       <c r="F169">
-        <v>35823</v>
+        <v>35854</v>
       </c>
       <c r="G169">
-        <v>51585</v>
+        <v>51630</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58859</v>
+        <v>58747</v>
       </c>
       <c r="E170">
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>78867</v>
+        <v>81158</v>
       </c>
       <c r="G170">
-        <v>113568</v>
+        <v>116868</v>
       </c>
       <c r="H170">
-        <v>20008</v>
+        <v>22411</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>54563</v>
       </c>
       <c r="E171">
         <v>109608</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>70572</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>101624</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>16009</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77856</v>
+        <v>77708</v>
       </c>
       <c r="E172">
         <v>146150</v>
       </c>
       <c r="F172">
-        <v>108616</v>
+        <v>108556</v>
       </c>
       <c r="G172">
-        <v>156407</v>
+        <v>156321</v>
       </c>
       <c r="H172">
-        <v>30760</v>
+        <v>30848</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78626</v>
+        <v>78475</v>
       </c>
       <c r="E173">
         <v>146150</v>
       </c>
       <c r="F173">
-        <v>94449</v>
+        <v>94389</v>
       </c>
       <c r="G173">
-        <v>136007</v>
+        <v>135920</v>
       </c>
       <c r="H173">
-        <v>15823</v>
+        <v>15914</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>64260</v>
+        <v>64137</v>
       </c>
       <c r="E175">
         <v>91337</v>
       </c>
       <c r="F175">
-        <v>79260</v>
+        <v>79137</v>
       </c>
       <c r="G175">
-        <v>114134</v>
+        <v>113957</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65438</v>
+        <v>65313</v>
       </c>
       <c r="E176">
         <v>91337</v>
       </c>
       <c r="F176">
-        <v>80438</v>
+        <v>80313</v>
       </c>
       <c r="G176">
-        <v>115831</v>
+        <v>115651</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>27444</v>
+        <v>27391</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>54444</v>
+        <v>54391</v>
       </c>
       <c r="G178">
-        <v>78399</v>
+        <v>78323</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25246</v>
+        <v>25197</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>52246</v>
+        <v>52197</v>
       </c>
       <c r="G180">
-        <v>75234</v>
+        <v>75164</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100464</v>
+        <v>100272</v>
       </c>
       <c r="E182">
         <v>127879</v>
       </c>
       <c r="F182">
-        <v>115464</v>
+        <v>115415</v>
       </c>
       <c r="G182">
-        <v>166268</v>
+        <v>166198</v>
       </c>
       <c r="H182">
-        <v>15000</v>
+        <v>15143</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64229</v>
+        <v>64106</v>
       </c>
       <c r="E183">
         <v>127879</v>
       </c>
       <c r="F183">
-        <v>81564</v>
+        <v>81515</v>
       </c>
       <c r="G183">
-        <v>117452</v>
+        <v>117382</v>
       </c>
       <c r="H183">
-        <v>17335</v>
+        <v>17409</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144424</v>
+        <v>144148</v>
       </c>
       <c r="E184">
         <v>182692</v>
       </c>
       <c r="F184">
-        <v>159424</v>
+        <v>159301</v>
       </c>
       <c r="G184">
-        <v>229571</v>
+        <v>229393</v>
       </c>
       <c r="H184">
-        <v>15000</v>
+        <v>15153</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64339</v>
+        <v>64216</v>
       </c>
       <c r="E185">
         <v>182692</v>
       </c>
       <c r="F185">
-        <v>91339</v>
+        <v>91216</v>
       </c>
       <c r="G185">
-        <v>131528</v>
+        <v>131351</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8561,16 +8561,16 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>188384</v>
+        <v>188024</v>
       </c>
       <c r="E186">
         <v>237505</v>
       </c>
       <c r="F186">
-        <v>203384</v>
+        <v>203024</v>
       </c>
       <c r="G186">
-        <v>292873</v>
+        <v>292355</v>
       </c>
       <c r="H186">
         <v>15000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64339</v>
+        <v>64216</v>
       </c>
       <c r="E187">
         <v>182692</v>
       </c>
       <c r="F187">
-        <v>91339</v>
+        <v>91216</v>
       </c>
       <c r="G187">
-        <v>131528</v>
+        <v>131351</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>290434</v>
+        <v>289879</v>
       </c>
       <c r="E188">
         <v>365402</v>
       </c>
       <c r="F188">
-        <v>325434</v>
+        <v>324879</v>
       </c>
       <c r="G188">
-        <v>468625</v>
+        <v>467826</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>306433</v>
+        <v>305847</v>
       </c>
       <c r="E189">
         <v>365402</v>
       </c>
       <c r="F189">
-        <v>321433</v>
+        <v>320847</v>
       </c>
       <c r="G189">
-        <v>462864</v>
+        <v>462020</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>31447</v>
+        <v>31356</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>66447</v>
+        <v>66356</v>
       </c>
       <c r="G190">
-        <v>95684</v>
+        <v>95553</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44462</v>
+        <v>44377</v>
       </c>
       <c r="E191">
         <v>95904</v>
       </c>
       <c r="F191">
-        <v>61188</v>
+        <v>61154</v>
       </c>
       <c r="G191">
-        <v>88111</v>
+        <v>88062</v>
       </c>
       <c r="H191">
-        <v>16726</v>
+        <v>16777</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>81326</v>
+        <v>42998</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>116326</v>
+        <v>77998</v>
       </c>
       <c r="G192">
-        <v>167509</v>
+        <v>112317</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50978</v>
+        <v>50771</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>77978</v>
+        <v>77771</v>
       </c>
       <c r="G194">
-        <v>112288</v>
+        <v>111990</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23848</v>
+        <v>23803</v>
       </c>
       <c r="E196">
         <v>73066</v>
       </c>
       <c r="F196">
-        <v>54800</v>
+        <v>48401</v>
       </c>
       <c r="G196">
-        <v>78912</v>
+        <v>69697</v>
       </c>
       <c r="H196">
-        <v>30952</v>
+        <v>24598</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32405</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>73066</v>
       </c>
       <c r="F197">
-        <v>47458</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>68340</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15053</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>24932</v>
+        <v>24665</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>59932</v>
+        <v>51665</v>
       </c>
       <c r="G198">
-        <v>86302</v>
+        <v>74398</v>
       </c>
       <c r="H198">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37366</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>109608</v>
       </c>
       <c r="F199">
-        <v>63693</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>91718</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>26327</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>127879</v>
       </c>
       <c r="F200">
-        <v>46916</v>
+        <v>46894</v>
       </c>
       <c r="G200">
-        <v>67559</v>
+        <v>67527</v>
       </c>
       <c r="H200">
-        <v>32851</v>
+        <v>32829</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11916</v>
+        <v>11894</v>
       </c>
       <c r="E201">
         <v>127879</v>
       </c>
       <c r="F201">
-        <v>38916</v>
+        <v>38894</v>
       </c>
       <c r="G201">
-        <v>56039</v>
+        <v>56007</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22639</v>
+        <v>22596</v>
       </c>
       <c r="E203">
         <v>146150</v>
       </c>
       <c r="F203">
-        <v>49639</v>
+        <v>49596</v>
       </c>
       <c r="G203">
-        <v>71480</v>
+        <v>71418</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>61188</v>
+        <v>61138</v>
       </c>
       <c r="G204">
-        <v>88111</v>
+        <v>88039</v>
       </c>
       <c r="H204">
-        <v>32450</v>
+        <v>32400</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,16 +9402,16 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26188</v>
+        <v>26138</v>
       </c>
       <c r="E205">
         <v>182692</v>
       </c>
       <c r="F205">
-        <v>53188</v>
+        <v>53138</v>
       </c>
       <c r="G205">
-        <v>76591</v>
+        <v>76519</v>
       </c>
       <c r="H205">
         <v>27000</v>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>15860</v>
+        <v>24210</v>
       </c>
       <c r="E206">
         <v>58449</v>
       </c>
       <c r="F206">
-        <v>41712</v>
+        <v>41986</v>
       </c>
       <c r="G206">
-        <v>60065</v>
+        <v>60460</v>
       </c>
       <c r="H206">
-        <v>25852</v>
+        <v>17776</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12293</v>
+        <v>12270</v>
       </c>
       <c r="E207">
         <v>58449</v>
       </c>
       <c r="F207">
-        <v>33712</v>
+        <v>33703</v>
       </c>
       <c r="G207">
-        <v>48545</v>
+        <v>48532</v>
       </c>
       <c r="H207">
-        <v>21419</v>
+        <v>21433</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22953</v>
+        <v>22910</v>
       </c>
       <c r="E209">
         <v>54795</v>
       </c>
       <c r="F209">
-        <v>37953</v>
+        <v>37910</v>
       </c>
       <c r="G209">
-        <v>54652</v>
+        <v>54590</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40302</v>
+        <v>40225</v>
       </c>
       <c r="E211">
         <v>109608</v>
       </c>
       <c r="F211">
-        <v>64868</v>
+        <v>64837</v>
       </c>
       <c r="G211">
-        <v>93410</v>
+        <v>93365</v>
       </c>
       <c r="H211">
-        <v>24566</v>
+        <v>24612</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,16 +9749,16 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83508</v>
+        <v>83349</v>
       </c>
       <c r="E213">
         <v>182692</v>
       </c>
       <c r="F213">
-        <v>110508</v>
+        <v>110349</v>
       </c>
       <c r="G213">
-        <v>159132</v>
+        <v>158903</v>
       </c>
       <c r="H213">
         <v>27000</v>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>29155</v>
+        <v>29099</v>
       </c>
       <c r="E214">
         <v>87683</v>
       </c>
       <c r="F214">
-        <v>60675</v>
+        <v>60651</v>
       </c>
       <c r="G214">
-        <v>87372</v>
+        <v>87337</v>
       </c>
       <c r="H214">
-        <v>31520</v>
+        <v>31552</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31196</v>
+        <v>31136</v>
       </c>
       <c r="E215">
         <v>87683</v>
       </c>
       <c r="F215">
-        <v>52675</v>
+        <v>52651</v>
       </c>
       <c r="G215">
-        <v>75852</v>
+        <v>75817</v>
       </c>
       <c r="H215">
-        <v>21479</v>
+        <v>21515</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,16 +9881,16 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>64794</v>
+        <v>64592</v>
       </c>
       <c r="E216">
         <v>102299</v>
       </c>
       <c r="F216">
-        <v>99794</v>
+        <v>99592</v>
       </c>
       <c r="G216">
-        <v>143703</v>
+        <v>143412</v>
       </c>
       <c r="H216">
         <v>35000</v>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>89003</v>
+        <v>88833</v>
       </c>
       <c r="E217">
         <v>102299</v>
       </c>
       <c r="F217">
-        <v>104003</v>
+        <v>103833</v>
       </c>
       <c r="G217">
-        <v>149764</v>
+        <v>149520</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111250</v>
+        <v>111038</v>
       </c>
       <c r="E219">
         <v>131533</v>
       </c>
       <c r="F219">
-        <v>126250</v>
+        <v>126038</v>
       </c>
       <c r="G219">
-        <v>181800</v>
+        <v>181495</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10065,13 +10065,13 @@
         <v>82220</v>
       </c>
       <c r="F220">
-        <v>74287</v>
+        <v>76466</v>
       </c>
       <c r="G220">
-        <v>106973</v>
+        <v>110111</v>
       </c>
       <c r="H220">
-        <v>15000</v>
+        <v>17179</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>51492</v>
       </c>
       <c r="E221">
         <v>82220</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>66492</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>95748</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>73617</v>
+        <v>73477</v>
       </c>
       <c r="E222">
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>88617</v>
+        <v>88480</v>
       </c>
       <c r="G222">
-        <v>127608</v>
+        <v>127411</v>
       </c>
       <c r="H222">
-        <v>15000</v>
+        <v>15003</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>55421</v>
+        <v>55284</v>
       </c>
       <c r="E223">
         <v>96836</v>
       </c>
       <c r="F223">
-        <v>70421</v>
+        <v>70284</v>
       </c>
       <c r="G223">
-        <v>101406</v>
+        <v>101209</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>60276</v>
       </c>
       <c r="F224">
-        <v>41659</v>
+        <v>41651</v>
       </c>
       <c r="G224">
-        <v>59989</v>
+        <v>59977</v>
       </c>
       <c r="H224">
-        <v>25081</v>
+        <v>25073</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10378</v>
+        <v>10358</v>
       </c>
       <c r="E225">
         <v>60276</v>
       </c>
       <c r="F225">
-        <v>33659</v>
+        <v>33651</v>
       </c>
       <c r="G225">
-        <v>48469</v>
+        <v>48457</v>
       </c>
       <c r="H225">
-        <v>23281</v>
+        <v>23293</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37853</v>
+        <v>37780</v>
       </c>
       <c r="E226">
         <v>73066</v>
       </c>
       <c r="F226">
-        <v>54021</v>
+        <v>54001</v>
       </c>
       <c r="G226">
-        <v>77790</v>
+        <v>77761</v>
       </c>
       <c r="H226">
-        <v>16168</v>
+        <v>16221</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25984</v>
+        <v>25934</v>
       </c>
       <c r="E227">
         <v>73066</v>
       </c>
       <c r="F227">
-        <v>44889</v>
+        <v>44869</v>
       </c>
       <c r="G227">
-        <v>64640</v>
+        <v>64611</v>
       </c>
       <c r="H227">
-        <v>18905</v>
+        <v>18935</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,16 +10418,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83571</v>
+        <v>83411</v>
       </c>
       <c r="E228">
         <v>109608</v>
       </c>
       <c r="F228">
-        <v>98571</v>
+        <v>98411</v>
       </c>
       <c r="G228">
-        <v>141942</v>
+        <v>141712</v>
       </c>
       <c r="H228">
         <v>15000</v>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>14271</v>
+        <v>13868</v>
       </c>
       <c r="E229">
         <v>109608</v>
       </c>
       <c r="F229">
-        <v>41271</v>
+        <v>40868</v>
       </c>
       <c r="G229">
-        <v>59430</v>
+        <v>58850</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19452</v>
+        <v>19415</v>
       </c>
       <c r="E231">
         <v>182692</v>
       </c>
       <c r="F231">
-        <v>46452</v>
+        <v>46415</v>
       </c>
       <c r="G231">
-        <v>66891</v>
+        <v>66838</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10595,13 +10595,13 @@
         <v>52986</v>
       </c>
       <c r="F232">
-        <v>38653</v>
+        <v>38645</v>
       </c>
       <c r="G232">
-        <v>55660</v>
+        <v>55649</v>
       </c>
       <c r="H232">
-        <v>29318</v>
+        <v>29310</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9970</v>
+        <v>9950</v>
       </c>
       <c r="E233">
         <v>52986</v>
       </c>
       <c r="F233">
-        <v>30653</v>
+        <v>30645</v>
       </c>
       <c r="G233">
-        <v>44140</v>
+        <v>44129</v>
       </c>
       <c r="H233">
-        <v>20683</v>
+        <v>20695</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>37509</v>
+        <v>37504</v>
       </c>
       <c r="G236">
-        <v>54013</v>
+        <v>54006</v>
       </c>
       <c r="H236">
-        <v>29158</v>
+        <v>29153</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>7112</v>
+        <v>7099</v>
       </c>
       <c r="E237">
         <v>52986</v>
       </c>
       <c r="F237">
-        <v>29509</v>
+        <v>29504</v>
       </c>
       <c r="G237">
-        <v>42493</v>
+        <v>42486</v>
       </c>
       <c r="H237">
-        <v>22397</v>
+        <v>22405</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11445</v>
+        <v>11423</v>
       </c>
       <c r="E239">
         <v>52986</v>
       </c>
       <c r="F239">
-        <v>31243</v>
+        <v>31234</v>
       </c>
       <c r="G239">
-        <v>44990</v>
+        <v>44977</v>
       </c>
       <c r="H239">
-        <v>19798</v>
+        <v>19811</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,7 +10941,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24194</v>
+        <v>24147</v>
       </c>
       <c r="E240">
         <v>71257</v>
@@ -10953,7 +10953,7 @@
         <v>76958</v>
       </c>
       <c r="H240">
-        <v>29249</v>
+        <v>29296</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70493</v>
+        <v>69732</v>
       </c>
       <c r="E241">
         <v>71257</v>
       </c>
       <c r="F241">
-        <v>85493</v>
+        <v>84732</v>
       </c>
       <c r="G241">
-        <v>123110</v>
+        <v>122014</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>28543</v>
+        <v>28488</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>49483</v>
+        <v>49461</v>
       </c>
       <c r="G242">
-        <v>71256</v>
+        <v>71224</v>
       </c>
       <c r="H242">
-        <v>20940</v>
+        <v>20973</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92850</v>
+        <v>92672</v>
       </c>
       <c r="E246">
         <v>109608</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>107672</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>155048</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>60084</v>
+        <v>59891</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>75084</v>
+        <v>74961</v>
       </c>
       <c r="G248">
-        <v>108121</v>
+        <v>107944</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>15070</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48246</v>
+        <v>48123</v>
       </c>
       <c r="E249">
         <v>96836</v>
       </c>
       <c r="F249">
-        <v>63246</v>
+        <v>63123</v>
       </c>
       <c r="G249">
-        <v>91074</v>
+        <v>90897</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73806</v>
+        <v>73665</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>103156</v>
+        <v>102480</v>
       </c>
       <c r="G250">
-        <v>148545</v>
+        <v>147571</v>
       </c>
       <c r="H250">
-        <v>29350</v>
+        <v>28815</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>74701</v>
+        <v>74025</v>
       </c>
       <c r="E251">
         <v>109608</v>
       </c>
       <c r="F251">
-        <v>89701</v>
+        <v>89025</v>
       </c>
       <c r="G251">
-        <v>129169</v>
+        <v>128196</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38638</v>
+        <v>38564</v>
       </c>
       <c r="E253">
         <v>52986</v>
       </c>
       <c r="F253">
-        <v>53638</v>
+        <v>53564</v>
       </c>
       <c r="G253">
-        <v>77239</v>
+        <v>77132</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11558,7 +11558,7 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24335</v>
+        <v>24289</v>
       </c>
       <c r="E254">
         <v>71257</v>
@@ -11570,7 +11570,7 @@
         <v>76958</v>
       </c>
       <c r="H254">
-        <v>29108</v>
+        <v>29154</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69645</v>
+        <v>69512</v>
       </c>
       <c r="E255">
         <v>71257</v>
       </c>
       <c r="F255">
-        <v>84645</v>
+        <v>84512</v>
       </c>
       <c r="G255">
-        <v>121889</v>
+        <v>121697</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12529</v>
+        <v>12505</v>
       </c>
       <c r="E259">
         <v>51141</v>
       </c>
       <c r="F259">
-        <v>30957</v>
+        <v>30947</v>
       </c>
       <c r="G259">
-        <v>44578</v>
+        <v>44564</v>
       </c>
       <c r="H259">
-        <v>18428</v>
+        <v>18442</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12529</v>
+        <v>12505</v>
       </c>
       <c r="E261">
         <v>63930</v>
       </c>
       <c r="F261">
-        <v>35945</v>
+        <v>35935</v>
       </c>
       <c r="G261">
-        <v>51761</v>
+        <v>51746</v>
       </c>
       <c r="H261">
-        <v>23416</v>
+        <v>23430</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>8965</v>
+        <v>12505</v>
       </c>
       <c r="E263">
         <v>73066</v>
       </c>
       <c r="F263">
-        <v>35965</v>
+        <v>39498</v>
       </c>
       <c r="G263">
-        <v>51790</v>
+        <v>56877</v>
       </c>
       <c r="H263">
-        <v>27000</v>
+        <v>26993</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>37068</v>
+        <v>39567</v>
       </c>
       <c r="E264">
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>52068</v>
+        <v>63607</v>
       </c>
       <c r="G264">
-        <v>74978</v>
+        <v>91594</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>24040</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>12686</v>
+        <v>31121</v>
       </c>
       <c r="E265">
         <v>60276</v>
       </c>
       <c r="F265">
-        <v>34582</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>49798</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>21896</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>36063</v>
+        <v>35994</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>51063</v>
+        <v>51001</v>
       </c>
       <c r="G268">
-        <v>73531</v>
+        <v>73441</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>15007</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,16 +12216,16 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>24398</v>
+        <v>24336</v>
       </c>
       <c r="E269">
         <v>60276</v>
       </c>
       <c r="F269">
-        <v>39398</v>
+        <v>39336</v>
       </c>
       <c r="G269">
-        <v>56733</v>
+        <v>56644</v>
       </c>
       <c r="H269">
         <v>15000</v>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>39172</v>
+        <v>39097</v>
       </c>
       <c r="E270">
         <v>67584</v>
       </c>
       <c r="F270">
-        <v>54172</v>
+        <v>54117</v>
       </c>
       <c r="G270">
-        <v>78008</v>
+        <v>77928</v>
       </c>
       <c r="H270">
-        <v>15000</v>
+        <v>15020</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29139</v>
+        <v>29084</v>
       </c>
       <c r="E271">
         <v>67584</v>
       </c>
       <c r="F271">
-        <v>44139</v>
+        <v>44084</v>
       </c>
       <c r="G271">
-        <v>63560</v>
+        <v>63481</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71294</v>
+        <v>71157</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>86294</v>
+        <v>86253</v>
       </c>
       <c r="G272">
-        <v>124263</v>
+        <v>124204</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>15096</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21525</v>
+        <v>21484</v>
       </c>
       <c r="E273">
         <v>91337</v>
       </c>
       <c r="F273">
-        <v>48525</v>
+        <v>48484</v>
       </c>
       <c r="G273">
-        <v>69876</v>
+        <v>69817</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10221</v>
+        <v>10201</v>
       </c>
       <c r="E275">
         <v>127879</v>
       </c>
       <c r="F275">
-        <v>37221</v>
+        <v>37201</v>
       </c>
       <c r="G275">
-        <v>53598</v>
+        <v>53569</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>152171</v>
       </c>
       <c r="E276">
         <v>164421</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>167171</v>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>240726</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>38465</v>
+        <v>38392</v>
       </c>
       <c r="E277">
         <v>164421</v>
       </c>
       <c r="F277">
-        <v>65465</v>
+        <v>65392</v>
       </c>
       <c r="G277">
-        <v>94270</v>
+        <v>94164</v>
       </c>
       <c r="H277">
         <v>27000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>52014</v>
+        <v>51915</v>
       </c>
       <c r="E278">
         <v>109608</v>
       </c>
       <c r="F278">
-        <v>78606</v>
+        <v>78569</v>
       </c>
       <c r="G278">
-        <v>113193</v>
+        <v>113139</v>
       </c>
       <c r="H278">
-        <v>26592</v>
+        <v>26654</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49015</v>
+        <v>48922</v>
       </c>
       <c r="E279">
         <v>109608</v>
       </c>
       <c r="F279">
-        <v>68353</v>
+        <v>68316</v>
       </c>
       <c r="G279">
-        <v>98428</v>
+        <v>98375</v>
       </c>
       <c r="H279">
-        <v>19338</v>
+        <v>19394</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>69865</v>
+        <v>69732</v>
       </c>
       <c r="E280">
         <v>127879</v>
       </c>
       <c r="F280">
-        <v>91491</v>
+        <v>91453</v>
       </c>
       <c r="G280">
-        <v>131747</v>
+        <v>131692</v>
       </c>
       <c r="H280">
-        <v>21626</v>
+        <v>21721</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>49015</v>
+        <v>48922</v>
       </c>
       <c r="E281">
         <v>127879</v>
       </c>
       <c r="F281">
-        <v>75479</v>
+        <v>75441</v>
       </c>
       <c r="G281">
-        <v>108690</v>
+        <v>108635</v>
       </c>
       <c r="H281">
-        <v>26464</v>
+        <v>26519</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24115</v>
+        <v>24069</v>
       </c>
       <c r="E282">
         <v>54795</v>
@@ -12803,7 +12803,7 @@
         <v>59178</v>
       </c>
       <c r="H282">
-        <v>16981</v>
+        <v>17027</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24586</v>
+        <v>24492</v>
       </c>
       <c r="E283">
         <v>54795</v>
       </c>
       <c r="F283">
-        <v>39586</v>
+        <v>39492</v>
       </c>
       <c r="G283">
-        <v>57004</v>
+        <v>56868</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65814</v>
+        <v>65689</v>
       </c>
       <c r="E284">
         <v>82220</v>
       </c>
       <c r="F284">
-        <v>80814</v>
+        <v>80689</v>
       </c>
       <c r="G284">
-        <v>116372</v>
+        <v>116192</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20928</v>
+        <v>20888</v>
       </c>
       <c r="E287">
         <v>38351</v>
       </c>
       <c r="F287">
-        <v>35928</v>
+        <v>35888</v>
       </c>
       <c r="G287">
-        <v>51736</v>
+        <v>51679</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31541</v>
+        <v>31481</v>
       </c>
       <c r="E288">
         <v>58449</v>
       </c>
       <c r="F288">
-        <v>48748</v>
+        <v>48699</v>
       </c>
       <c r="G288">
-        <v>70197</v>
+        <v>70127</v>
       </c>
       <c r="H288">
-        <v>17207</v>
+        <v>17218</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25748</v>
+        <v>25699</v>
       </c>
       <c r="E289">
         <v>58449</v>
       </c>
       <c r="F289">
-        <v>40748</v>
+        <v>40699</v>
       </c>
       <c r="G289">
-        <v>58677</v>
+        <v>58607</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34132</v>
+        <v>34067</v>
       </c>
       <c r="E291">
         <v>43832</v>
       </c>
       <c r="F291">
-        <v>49132</v>
+        <v>49067</v>
       </c>
       <c r="G291">
-        <v>70750</v>
+        <v>70656</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>41605</v>
+        <v>41494</v>
       </c>
       <c r="E292">
         <v>109608</v>
       </c>
       <c r="F292">
-        <v>73537</v>
+        <v>73507</v>
       </c>
       <c r="G292">
-        <v>105893</v>
+        <v>105850</v>
       </c>
       <c r="H292">
-        <v>31932</v>
+        <v>32013</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37994</v>
+        <v>37921</v>
       </c>
       <c r="E293">
         <v>109608</v>
       </c>
       <c r="F293">
-        <v>63945</v>
+        <v>63915</v>
       </c>
       <c r="G293">
-        <v>92081</v>
+        <v>92038</v>
       </c>
       <c r="H293">
-        <v>25951</v>
+        <v>25994</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>55327</v>
+        <v>55205</v>
       </c>
       <c r="E296">
         <v>73066</v>
       </c>
       <c r="F296">
-        <v>90327</v>
+        <v>90205</v>
       </c>
       <c r="G296">
-        <v>130071</v>
+        <v>129895</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64433</v>
+        <v>64310</v>
       </c>
       <c r="E297">
         <v>73066</v>
       </c>
       <c r="F297">
-        <v>79433</v>
+        <v>79310</v>
       </c>
       <c r="G297">
-        <v>114384</v>
+        <v>114206</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4396</v>
+        <v>4388</v>
       </c>
       <c r="E299">
         <v>54795</v>
       </c>
       <c r="F299">
-        <v>29129</v>
+        <v>29125</v>
       </c>
       <c r="G299">
-        <v>41946</v>
+        <v>41940</v>
       </c>
       <c r="H299">
-        <v>24733</v>
+        <v>24737</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10739</v>
+        <v>10718</v>
       </c>
       <c r="E301">
         <v>69412</v>
       </c>
       <c r="F301">
-        <v>37366</v>
+        <v>37358</v>
       </c>
       <c r="G301">
-        <v>53807</v>
+        <v>53796</v>
       </c>
       <c r="H301">
-        <v>26627</v>
+        <v>26640</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24147</v>
+        <v>24100</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>51147</v>
+        <v>51100</v>
       </c>
       <c r="G302">
-        <v>73652</v>
+        <v>73584</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44305</v>
+        <v>44221</v>
       </c>
       <c r="E304">
         <v>109608</v>
       </c>
       <c r="F304">
-        <v>77040</v>
+        <v>77004</v>
       </c>
       <c r="G304">
-        <v>110938</v>
+        <v>110886</v>
       </c>
       <c r="H304">
-        <v>32735</v>
+        <v>32783</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45609</v>
+        <v>45521</v>
       </c>
       <c r="E305">
         <v>109608</v>
       </c>
       <c r="F305">
-        <v>66991</v>
+        <v>66955</v>
       </c>
       <c r="G305">
-        <v>96467</v>
+        <v>96415</v>
       </c>
       <c r="H305">
-        <v>21382</v>
+        <v>21434</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24304</v>
+        <v>24241</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>59304</v>
+        <v>59241</v>
       </c>
       <c r="G306">
-        <v>85398</v>
+        <v>85307</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33410</v>
+        <v>33346</v>
       </c>
       <c r="E307">
         <v>109608</v>
       </c>
       <c r="F307">
-        <v>60410</v>
+        <v>60346</v>
       </c>
       <c r="G307">
-        <v>86990</v>
+        <v>86898</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>190315</v>
+        <v>189952</v>
       </c>
       <c r="E308">
         <v>237505</v>
       </c>
       <c r="F308">
-        <v>205315</v>
+        <v>205044</v>
       </c>
       <c r="G308">
-        <v>295654</v>
+        <v>295263</v>
       </c>
       <c r="H308">
-        <v>15000</v>
+        <v>15092</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>141865</v>
+        <v>141594</v>
       </c>
       <c r="E309">
         <v>237505</v>
       </c>
       <c r="F309">
-        <v>156865</v>
+        <v>156594</v>
       </c>
       <c r="G309">
-        <v>225886</v>
+        <v>225495</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53882</v>
+        <v>53779</v>
       </c>
       <c r="E311">
         <v>127879</v>
       </c>
       <c r="F311">
-        <v>77425</v>
+        <v>77384</v>
       </c>
       <c r="G311">
-        <v>111492</v>
+        <v>111433</v>
       </c>
       <c r="H311">
-        <v>23543</v>
+        <v>23605</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110716</v>
+        <v>110505</v>
       </c>
       <c r="E313">
         <v>182692</v>
       </c>
       <c r="F313">
-        <v>125716</v>
+        <v>125505</v>
       </c>
       <c r="G313">
-        <v>181031</v>
+        <v>180727</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>139306</v>
+        <v>139040</v>
       </c>
       <c r="E314">
         <v>237505</v>
       </c>
       <c r="F314">
-        <v>174306</v>
+        <v>174040</v>
       </c>
       <c r="G314">
-        <v>251001</v>
+        <v>250618</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>147973</v>
+        <v>147690</v>
       </c>
       <c r="E315">
         <v>237505</v>
       </c>
       <c r="F315">
-        <v>162973</v>
+        <v>162690</v>
       </c>
       <c r="G315">
-        <v>234681</v>
+        <v>234274</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -487,13 +487,13 @@
         <v>73066</v>
       </c>
       <c r="F2">
-        <v>86660</v>
+        <v>86472</v>
       </c>
       <c r="G2">
-        <v>124790</v>
+        <v>124520</v>
       </c>
       <c r="H2">
-        <v>15220</v>
+        <v>15032</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46399</v>
+        <v>46211</v>
       </c>
       <c r="E3">
         <v>73066</v>
       </c>
       <c r="F3">
-        <v>61399</v>
+        <v>61211</v>
       </c>
       <c r="G3">
-        <v>88415</v>
+        <v>88144</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>80544</v>
+        <v>57054</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>95675</v>
+        <v>92054</v>
       </c>
       <c r="G12">
-        <v>137772</v>
+        <v>132558</v>
       </c>
       <c r="H12">
-        <v>15131</v>
+        <v>35000</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>117979</v>
+        <v>52808</v>
       </c>
       <c r="E23">
         <v>131533</v>
       </c>
       <c r="F23">
-        <v>132979</v>
+        <v>78421</v>
       </c>
       <c r="G23">
-        <v>191490</v>
+        <v>112926</v>
       </c>
       <c r="H23">
-        <v>15000</v>
+        <v>25613</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130954</v>
+        <v>131048</v>
       </c>
       <c r="E30">
         <v>182692</v>
@@ -1721,7 +1721,7 @@
         <v>210897</v>
       </c>
       <c r="H30">
-        <v>15502</v>
+        <v>15408</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>47323</v>
+        <v>52980</v>
       </c>
       <c r="E35">
         <v>127879</v>
       </c>
       <c r="F35">
-        <v>74323</v>
+        <v>77065</v>
       </c>
       <c r="G35">
-        <v>107025</v>
+        <v>110974</v>
       </c>
       <c r="H35">
-        <v>27000</v>
+        <v>24085</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1985,13 +1985,13 @@
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>72258</v>
+        <v>72666</v>
       </c>
       <c r="G36">
-        <v>104052</v>
+        <v>104639</v>
       </c>
       <c r="H36">
-        <v>27614</v>
+        <v>28022</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,16 +2025,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35179</v>
+        <v>35587</v>
       </c>
       <c r="E37">
         <v>127879</v>
       </c>
       <c r="F37">
-        <v>62179</v>
+        <v>62587</v>
       </c>
       <c r="G37">
-        <v>89538</v>
+        <v>90125</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>84242</v>
+        <v>83882</v>
       </c>
       <c r="E39">
         <v>237505</v>
       </c>
       <c r="F39">
-        <v>111242</v>
+        <v>110882</v>
       </c>
       <c r="G39">
-        <v>160188</v>
+        <v>159670</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>84242</v>
+        <v>83882</v>
       </c>
       <c r="E41">
         <v>237505</v>
       </c>
       <c r="F41">
-        <v>111242</v>
+        <v>110882</v>
       </c>
       <c r="G41">
-        <v>160188</v>
+        <v>159670</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>91654</v>
+        <v>92860</v>
       </c>
       <c r="E45">
         <v>182692</v>
       </c>
       <c r="F45">
-        <v>113912</v>
+        <v>114394</v>
       </c>
       <c r="G45">
-        <v>164033</v>
+        <v>164727</v>
       </c>
       <c r="H45">
-        <v>22258</v>
+        <v>21534</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>26780</v>
+        <v>26764</v>
       </c>
       <c r="E47">
         <v>109608</v>
       </c>
       <c r="F47">
-        <v>53780</v>
+        <v>53764</v>
       </c>
       <c r="G47">
-        <v>77443</v>
+        <v>77420</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52103</v>
+        <v>51883</v>
       </c>
       <c r="E55">
         <v>127879</v>
       </c>
       <c r="F55">
-        <v>76714</v>
+        <v>76626</v>
       </c>
       <c r="G55">
-        <v>110468</v>
+        <v>110341</v>
       </c>
       <c r="H55">
-        <v>24611</v>
+        <v>24743</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6440</v>
+        <v>6252</v>
       </c>
       <c r="E59">
         <v>36524</v>
       </c>
       <c r="F59">
-        <v>22821</v>
+        <v>22745</v>
       </c>
       <c r="G59">
-        <v>32862</v>
+        <v>32753</v>
       </c>
       <c r="H59">
-        <v>16381</v>
+        <v>16493</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>29428</v>
+        <v>29225</v>
       </c>
       <c r="E65">
         <v>123293</v>
       </c>
       <c r="F65">
-        <v>56428</v>
+        <v>56225</v>
       </c>
       <c r="G65">
-        <v>81256</v>
+        <v>80964</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,7 +3296,7 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24978</v>
+        <v>24853</v>
       </c>
       <c r="E66">
         <v>91337</v>
@@ -3308,7 +3308,7 @@
         <v>77884</v>
       </c>
       <c r="H66">
-        <v>29108</v>
+        <v>29233</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3385,7 +3385,7 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34380</v>
+        <v>34333</v>
       </c>
       <c r="E68">
         <v>109608</v>
@@ -3397,7 +3397,7 @@
         <v>90317</v>
       </c>
       <c r="H68">
-        <v>28340</v>
+        <v>28387</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>49878</v>
+        <v>49110</v>
       </c>
       <c r="E77">
         <v>127879</v>
       </c>
       <c r="F77">
-        <v>75824</v>
+        <v>75517</v>
       </c>
       <c r="G77">
-        <v>109187</v>
+        <v>108744</v>
       </c>
       <c r="H77">
-        <v>25946</v>
+        <v>26407</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>46822</v>
+        <v>48201</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>70763</v>
+        <v>71315</v>
       </c>
       <c r="G84">
-        <v>101899</v>
+        <v>102694</v>
       </c>
       <c r="H84">
-        <v>23941</v>
+        <v>23114</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32672</v>
+        <v>32468</v>
       </c>
       <c r="E85">
         <v>102299</v>
       </c>
       <c r="F85">
-        <v>58965</v>
+        <v>58884</v>
       </c>
       <c r="G85">
-        <v>84910</v>
+        <v>84793</v>
       </c>
       <c r="H85">
-        <v>26293</v>
+        <v>26416</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4264,13 +4264,13 @@
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>174348</v>
+        <v>174286</v>
       </c>
       <c r="G88">
-        <v>251061</v>
+        <v>250972</v>
       </c>
       <c r="H88">
-        <v>15062</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>126833</v>
+        <v>126441</v>
       </c>
       <c r="E89">
         <v>160767</v>
       </c>
       <c r="F89">
-        <v>141833</v>
+        <v>141441</v>
       </c>
       <c r="G89">
-        <v>204240</v>
+        <v>203675</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -5526,16 +5526,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>110709</v>
+        <v>116710</v>
       </c>
       <c r="E117">
         <v>146150</v>
       </c>
       <c r="F117">
-        <v>125709</v>
+        <v>131710</v>
       </c>
       <c r="G117">
-        <v>181021</v>
+        <v>189662</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>32500</v>
+        <v>31998</v>
       </c>
       <c r="E119">
         <v>58449</v>
       </c>
       <c r="F119">
-        <v>47500</v>
+        <v>46998</v>
       </c>
       <c r="G119">
-        <v>68400</v>
+        <v>67677</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5658,7 +5658,7 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60784</v>
+        <v>60721</v>
       </c>
       <c r="E120">
         <v>80374</v>
@@ -5670,7 +5670,7 @@
         <v>113869</v>
       </c>
       <c r="H120">
-        <v>18292</v>
+        <v>18355</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,7 +5746,7 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>53074</v>
+        <v>46524</v>
       </c>
       <c r="E122">
         <v>91337</v>
@@ -5758,7 +5758,7 @@
         <v>98425</v>
       </c>
       <c r="H122">
-        <v>15277</v>
+        <v>21827</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>29742</v>
+        <v>20152</v>
       </c>
       <c r="E131">
         <v>74619</v>
       </c>
       <c r="F131">
-        <v>46998</v>
+        <v>43162</v>
       </c>
       <c r="G131">
-        <v>67677</v>
+        <v>62153</v>
       </c>
       <c r="H131">
-        <v>17256</v>
+        <v>23010</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>35116</v>
+        <v>34646</v>
       </c>
       <c r="E133">
         <v>93931</v>
       </c>
       <c r="F133">
-        <v>56679</v>
+        <v>56491</v>
       </c>
       <c r="G133">
-        <v>81618</v>
+        <v>81347</v>
       </c>
       <c r="H133">
-        <v>21563</v>
+        <v>21845</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37796</v>
+        <v>37498</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62220</v>
+        <v>62101</v>
       </c>
       <c r="G140">
-        <v>89597</v>
+        <v>89425</v>
       </c>
       <c r="H140">
-        <v>24424</v>
+        <v>24603</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>43970</v>
+        <v>43516</v>
       </c>
       <c r="E144">
         <v>91337</v>
@@ -6718,7 +6718,7 @@
         <v>98644</v>
       </c>
       <c r="H144">
-        <v>24533</v>
+        <v>24987</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>53278</v>
+        <v>80121</v>
       </c>
       <c r="E145">
         <v>91337</v>
       </c>
       <c r="F145">
-        <v>68278</v>
+        <v>95121</v>
       </c>
       <c r="G145">
-        <v>98320</v>
+        <v>136974</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36668</v>
+        <v>36621</v>
       </c>
       <c r="E148">
         <v>62103</v>
@@ -6895,7 +6895,7 @@
         <v>92429</v>
       </c>
       <c r="H148">
-        <v>27519</v>
+        <v>27566</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37561</v>
+        <v>37592</v>
       </c>
       <c r="E152">
         <v>73066</v>
@@ -7070,7 +7070,7 @@
         <v>78912</v>
       </c>
       <c r="H152">
-        <v>17239</v>
+        <v>17208</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,16 +7148,16 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>57196</v>
+        <v>56851</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>92196</v>
+        <v>91851</v>
       </c>
       <c r="G154">
-        <v>132762</v>
+        <v>132265</v>
       </c>
       <c r="H154">
         <v>35000</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>12003</v>
+        <v>11988</v>
       </c>
       <c r="E157">
         <v>27388</v>
       </c>
       <c r="F157">
-        <v>27003</v>
+        <v>26988</v>
       </c>
       <c r="G157">
-        <v>38884</v>
+        <v>38863</v>
       </c>
       <c r="H157">
         <v>15000</v>
@@ -7507,13 +7507,13 @@
         <v>73066</v>
       </c>
       <c r="F162">
-        <v>44245</v>
+        <v>42898</v>
       </c>
       <c r="G162">
-        <v>63713</v>
+        <v>61773</v>
       </c>
       <c r="H162">
-        <v>34098</v>
+        <v>32751</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9245</v>
+        <v>7898</v>
       </c>
       <c r="E163">
         <v>73066</v>
       </c>
       <c r="F163">
-        <v>36245</v>
+        <v>34898</v>
       </c>
       <c r="G163">
-        <v>52193</v>
+        <v>50253</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>73066</v>
       </c>
       <c r="F168">
-        <v>103852</v>
+        <v>103977</v>
       </c>
       <c r="G168">
-        <v>149547</v>
+        <v>149727</v>
       </c>
       <c r="H168">
-        <v>15031</v>
+        <v>15156</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8854</v>
+        <v>8979</v>
       </c>
       <c r="E169">
         <v>73066</v>
       </c>
       <c r="F169">
-        <v>35854</v>
+        <v>35979</v>
       </c>
       <c r="G169">
-        <v>51630</v>
+        <v>51810</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7861,13 +7861,13 @@
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>81158</v>
+        <v>81259</v>
       </c>
       <c r="G170">
-        <v>116868</v>
+        <v>117013</v>
       </c>
       <c r="H170">
-        <v>22411</v>
+        <v>22512</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>54563</v>
+        <v>54782</v>
       </c>
       <c r="E171">
         <v>109608</v>
       </c>
       <c r="F171">
-        <v>70572</v>
+        <v>70660</v>
       </c>
       <c r="G171">
-        <v>101624</v>
+        <v>101750</v>
       </c>
       <c r="H171">
-        <v>16009</v>
+        <v>15878</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>27391</v>
+        <v>26952</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>54391</v>
+        <v>53952</v>
       </c>
       <c r="G178">
-        <v>78323</v>
+        <v>77691</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25197</v>
+        <v>25166</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>52197</v>
+        <v>52166</v>
       </c>
       <c r="G180">
-        <v>75164</v>
+        <v>75119</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>31356</v>
+        <v>31089</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>66356</v>
+        <v>66089</v>
       </c>
       <c r="G190">
-        <v>95553</v>
+        <v>95168</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>42998</v>
+        <v>42951</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>77998</v>
+        <v>77951</v>
       </c>
       <c r="G192">
-        <v>112317</v>
+        <v>112249</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50771</v>
+        <v>50567</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>77771</v>
+        <v>77567</v>
       </c>
       <c r="G194">
-        <v>111990</v>
+        <v>111696</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23803</v>
+        <v>23787</v>
       </c>
       <c r="E196">
         <v>73066</v>
       </c>
       <c r="F196">
-        <v>48401</v>
+        <v>54800</v>
       </c>
       <c r="G196">
-        <v>69697</v>
+        <v>78912</v>
       </c>
       <c r="H196">
-        <v>24598</v>
+        <v>31013</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>32343</v>
       </c>
       <c r="E197">
         <v>73066</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>47433</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>68304</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>15090</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>24665</v>
+        <v>26153</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>51665</v>
+        <v>61153</v>
       </c>
       <c r="G198">
-        <v>74398</v>
+        <v>88060</v>
       </c>
       <c r="H198">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>37310</v>
       </c>
       <c r="E199">
         <v>109608</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>63671</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>91686</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>26361</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9451,13 +9451,13 @@
         <v>58449</v>
       </c>
       <c r="F206">
-        <v>41986</v>
+        <v>42293</v>
       </c>
       <c r="G206">
-        <v>60460</v>
+        <v>60902</v>
       </c>
       <c r="H206">
-        <v>17776</v>
+        <v>18083</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12270</v>
+        <v>13037</v>
       </c>
       <c r="E207">
         <v>58449</v>
       </c>
       <c r="F207">
-        <v>33703</v>
+        <v>34010</v>
       </c>
       <c r="G207">
-        <v>48532</v>
+        <v>48974</v>
       </c>
       <c r="H207">
-        <v>21433</v>
+        <v>20973</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,7 +9792,7 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>29099</v>
+        <v>29084</v>
       </c>
       <c r="E214">
         <v>87683</v>
@@ -9804,7 +9804,7 @@
         <v>87337</v>
       </c>
       <c r="H214">
-        <v>31552</v>
+        <v>31567</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,16 +9881,16 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>64592</v>
+        <v>64435</v>
       </c>
       <c r="E216">
         <v>102299</v>
       </c>
       <c r="F216">
-        <v>99592</v>
+        <v>99435</v>
       </c>
       <c r="G216">
-        <v>143412</v>
+        <v>143186</v>
       </c>
       <c r="H216">
         <v>35000</v>
@@ -10065,13 +10065,13 @@
         <v>82220</v>
       </c>
       <c r="F220">
-        <v>76466</v>
+        <v>76970</v>
       </c>
       <c r="G220">
-        <v>110111</v>
+        <v>110837</v>
       </c>
       <c r="H220">
-        <v>17179</v>
+        <v>17683</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>51492</v>
+        <v>51930</v>
       </c>
       <c r="E221">
         <v>82220</v>
       </c>
       <c r="F221">
-        <v>66492</v>
+        <v>66930</v>
       </c>
       <c r="G221">
-        <v>95748</v>
+        <v>96379</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10155,13 +10155,13 @@
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>88480</v>
+        <v>88699</v>
       </c>
       <c r="G222">
-        <v>127411</v>
+        <v>127727</v>
       </c>
       <c r="H222">
-        <v>15003</v>
+        <v>15222</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>55284</v>
+        <v>55503</v>
       </c>
       <c r="E223">
         <v>96836</v>
       </c>
       <c r="F223">
-        <v>70284</v>
+        <v>70503</v>
       </c>
       <c r="G223">
-        <v>101209</v>
+        <v>101524</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10424,13 +10424,13 @@
         <v>109608</v>
       </c>
       <c r="F228">
-        <v>98411</v>
+        <v>99038</v>
       </c>
       <c r="G228">
-        <v>141712</v>
+        <v>142615</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>15627</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13868</v>
+        <v>14495</v>
       </c>
       <c r="E229">
         <v>109608</v>
       </c>
       <c r="F229">
-        <v>40868</v>
+        <v>41495</v>
       </c>
       <c r="G229">
-        <v>58850</v>
+        <v>59753</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19415</v>
+        <v>19321</v>
       </c>
       <c r="E231">
         <v>182692</v>
       </c>
       <c r="F231">
-        <v>46415</v>
+        <v>46321</v>
       </c>
       <c r="G231">
-        <v>66838</v>
+        <v>66702</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10770,13 +10770,13 @@
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>37504</v>
+        <v>37485</v>
       </c>
       <c r="G236">
-        <v>54006</v>
+        <v>53978</v>
       </c>
       <c r="H236">
-        <v>29153</v>
+        <v>29134</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>7099</v>
+        <v>7052</v>
       </c>
       <c r="E237">
         <v>52986</v>
       </c>
       <c r="F237">
-        <v>29504</v>
+        <v>29485</v>
       </c>
       <c r="G237">
-        <v>42486</v>
+        <v>42458</v>
       </c>
       <c r="H237">
-        <v>22405</v>
+        <v>22433</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>69732</v>
+        <v>70687</v>
       </c>
       <c r="E241">
         <v>71257</v>
       </c>
       <c r="F241">
-        <v>84732</v>
+        <v>85687</v>
       </c>
       <c r="G241">
-        <v>122014</v>
+        <v>123389</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>28488</v>
+        <v>32139</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>49461</v>
+        <v>50921</v>
       </c>
       <c r="G242">
-        <v>71224</v>
+        <v>73326</v>
       </c>
       <c r="H242">
-        <v>20973</v>
+        <v>18782</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59891</v>
+        <v>59765</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>74961</v>
+        <v>75149</v>
       </c>
       <c r="G248">
-        <v>107944</v>
+        <v>108215</v>
       </c>
       <c r="H248">
-        <v>15070</v>
+        <v>15384</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48123</v>
+        <v>48311</v>
       </c>
       <c r="E249">
         <v>96836</v>
       </c>
       <c r="F249">
-        <v>63123</v>
+        <v>63311</v>
       </c>
       <c r="G249">
-        <v>90897</v>
+        <v>91168</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73665</v>
+        <v>73555</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>102480</v>
+        <v>102073</v>
       </c>
       <c r="G250">
-        <v>147571</v>
+        <v>146985</v>
       </c>
       <c r="H250">
-        <v>28815</v>
+        <v>28518</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>74025</v>
+        <v>73618</v>
       </c>
       <c r="E251">
         <v>109608</v>
       </c>
       <c r="F251">
-        <v>89025</v>
+        <v>88618</v>
       </c>
       <c r="G251">
-        <v>128196</v>
+        <v>127610</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38564</v>
+        <v>38580</v>
       </c>
       <c r="E253">
         <v>52986</v>
       </c>
       <c r="F253">
-        <v>53564</v>
+        <v>53580</v>
       </c>
       <c r="G253">
-        <v>77132</v>
+        <v>77155</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12505</v>
+        <v>12442</v>
       </c>
       <c r="E261">
         <v>63930</v>
       </c>
       <c r="F261">
-        <v>35935</v>
+        <v>35910</v>
       </c>
       <c r="G261">
-        <v>51746</v>
+        <v>51710</v>
       </c>
       <c r="H261">
-        <v>23430</v>
+        <v>23468</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11998,13 +11998,13 @@
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>63607</v>
+        <v>54567</v>
       </c>
       <c r="G264">
-        <v>91594</v>
+        <v>78576</v>
       </c>
       <c r="H264">
-        <v>24040</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>31121</v>
+        <v>11517</v>
       </c>
       <c r="E265">
         <v>60276</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>34114</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>49124</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>22597</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12177,13 +12177,13 @@
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>51001</v>
+        <v>50994</v>
       </c>
       <c r="G268">
-        <v>73441</v>
+        <v>73431</v>
       </c>
       <c r="H268">
-        <v>15007</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>24336</v>
+        <v>24147</v>
       </c>
       <c r="E269">
         <v>60276</v>
       </c>
       <c r="F269">
-        <v>39336</v>
+        <v>39166</v>
       </c>
       <c r="G269">
-        <v>56644</v>
+        <v>56399</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>15019</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71157</v>
+        <v>71110</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>86253</v>
+        <v>86174</v>
       </c>
       <c r="G272">
-        <v>124204</v>
+        <v>124091</v>
       </c>
       <c r="H272">
-        <v>15096</v>
+        <v>15064</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21484</v>
+        <v>21405</v>
       </c>
       <c r="E273">
         <v>91337</v>
       </c>
       <c r="F273">
-        <v>48484</v>
+        <v>48405</v>
       </c>
       <c r="G273">
-        <v>69817</v>
+        <v>69703</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12525,7 +12525,7 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152171</v>
+        <v>152030</v>
       </c>
       <c r="E276">
         <v>164421</v>
@@ -12537,7 +12537,7 @@
         <v>240726</v>
       </c>
       <c r="H276">
-        <v>15000</v>
+        <v>15141</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12701,7 +12701,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>69732</v>
+        <v>69449</v>
       </c>
       <c r="E280">
         <v>127879</v>
@@ -12713,7 +12713,7 @@
         <v>131692</v>
       </c>
       <c r="H280">
-        <v>21721</v>
+        <v>22004</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24069</v>
+        <v>24085</v>
       </c>
       <c r="E282">
         <v>54795</v>
@@ -12803,7 +12803,7 @@
         <v>59178</v>
       </c>
       <c r="H282">
-        <v>17027</v>
+        <v>17011</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24492</v>
+        <v>24633</v>
       </c>
       <c r="E283">
         <v>54795</v>
       </c>
       <c r="F283">
-        <v>39492</v>
+        <v>39633</v>
       </c>
       <c r="G283">
-        <v>56868</v>
+        <v>57072</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20888</v>
+        <v>20794</v>
       </c>
       <c r="E287">
         <v>38351</v>
       </c>
       <c r="F287">
-        <v>35888</v>
+        <v>35794</v>
       </c>
       <c r="G287">
-        <v>51679</v>
+        <v>51543</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13059,13 +13059,13 @@
         <v>58449</v>
       </c>
       <c r="F288">
-        <v>48699</v>
+        <v>48652</v>
       </c>
       <c r="G288">
-        <v>70127</v>
+        <v>70059</v>
       </c>
       <c r="H288">
-        <v>17218</v>
+        <v>17171</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25699</v>
+        <v>25652</v>
       </c>
       <c r="E289">
         <v>58449</v>
       </c>
       <c r="F289">
-        <v>40699</v>
+        <v>40652</v>
       </c>
       <c r="G289">
-        <v>58607</v>
+        <v>58539</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13233,7 +13233,7 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>41494</v>
+        <v>43155</v>
       </c>
       <c r="E292">
         <v>109608</v>
@@ -13245,7 +13245,7 @@
         <v>105850</v>
       </c>
       <c r="H292">
-        <v>32013</v>
+        <v>30352</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>55205</v>
+        <v>55033</v>
       </c>
       <c r="E296">
         <v>73066</v>
       </c>
       <c r="F296">
-        <v>90205</v>
+        <v>90033</v>
       </c>
       <c r="G296">
-        <v>129895</v>
+        <v>129648</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24100</v>
+        <v>24868</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>51100</v>
+        <v>51868</v>
       </c>
       <c r="G302">
-        <v>73584</v>
+        <v>74690</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,7 +13756,7 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44221</v>
+        <v>44189</v>
       </c>
       <c r="E304">
         <v>109608</v>
@@ -13768,7 +13768,7 @@
         <v>110886</v>
       </c>
       <c r="H304">
-        <v>32783</v>
+        <v>32815</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -14020,7 +14020,7 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>71655</v>
+        <v>71440</v>
       </c>
       <c r="E310">
         <v>127879</v>
@@ -14032,7 +14032,7 @@
         <v>132778</v>
       </c>
       <c r="H310">
-        <v>20552</v>
+        <v>20767</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -617,16 +617,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>46399</v>
+        <v>46334</v>
       </c>
       <c r="E5">
         <v>84028</v>
       </c>
       <c r="F5">
-        <v>61399</v>
+        <v>61334</v>
       </c>
       <c r="G5">
-        <v>88415</v>
+        <v>88321</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4262</v>
+        <v>4249</v>
       </c>
       <c r="E7">
         <v>54795</v>
       </c>
       <c r="F7">
-        <v>29075</v>
+        <v>29070</v>
       </c>
       <c r="G7">
-        <v>41868</v>
+        <v>41861</v>
       </c>
       <c r="H7">
-        <v>24813</v>
+        <v>24821</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35712</v>
+        <v>33979</v>
       </c>
       <c r="E8">
         <v>73066</v>
       </c>
       <c r="F8">
-        <v>54787</v>
+        <v>54400</v>
       </c>
       <c r="G8">
-        <v>78893</v>
+        <v>78336</v>
       </c>
       <c r="H8">
-        <v>19075</v>
+        <v>20421</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>30729</v>
+        <v>29761</v>
       </c>
       <c r="E9">
         <v>73066</v>
       </c>
       <c r="F9">
-        <v>46787</v>
+        <v>46400</v>
       </c>
       <c r="G9">
-        <v>67373</v>
+        <v>66816</v>
       </c>
       <c r="H9">
-        <v>16058</v>
+        <v>16639</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41149</v>
+        <v>41160</v>
       </c>
       <c r="E11">
         <v>109608</v>
       </c>
       <c r="F11">
-        <v>65207</v>
+        <v>65211</v>
       </c>
       <c r="G11">
-        <v>93898</v>
+        <v>93904</v>
       </c>
       <c r="H11">
-        <v>24058</v>
+        <v>24051</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>57054</v>
+        <v>75405</v>
       </c>
       <c r="E12">
         <v>82201</v>
       </c>
       <c r="F12">
-        <v>92054</v>
+        <v>92046</v>
       </c>
       <c r="G12">
-        <v>132558</v>
+        <v>132546</v>
       </c>
       <c r="H12">
-        <v>35000</v>
+        <v>16641</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11705</v>
+        <v>11697</v>
       </c>
       <c r="E13">
         <v>82201</v>
       </c>
       <c r="F13">
-        <v>38705</v>
+        <v>38697</v>
       </c>
       <c r="G13">
-        <v>55735</v>
+        <v>55724</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>42403</v>
+        <v>8953</v>
       </c>
       <c r="E15">
         <v>73066</v>
       </c>
       <c r="F15">
-        <v>57403</v>
+        <v>35953</v>
       </c>
       <c r="G15">
-        <v>82660</v>
+        <v>51772</v>
       </c>
       <c r="H15">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>33017</v>
+        <v>33022</v>
       </c>
       <c r="E21">
         <v>102299</v>
       </c>
       <c r="F21">
-        <v>59103</v>
+        <v>59105</v>
       </c>
       <c r="G21">
-        <v>85108</v>
+        <v>85111</v>
       </c>
       <c r="H21">
-        <v>26086</v>
+        <v>26083</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52808</v>
+        <v>52826</v>
       </c>
       <c r="E23">
         <v>131533</v>
       </c>
       <c r="F23">
-        <v>78421</v>
+        <v>78428</v>
       </c>
       <c r="G23">
-        <v>112926</v>
+        <v>112936</v>
       </c>
       <c r="H23">
-        <v>25613</v>
+        <v>25602</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20543</v>
+        <v>19459</v>
       </c>
       <c r="E27">
         <v>63930</v>
       </c>
       <c r="F27">
-        <v>39150</v>
+        <v>38717</v>
       </c>
       <c r="G27">
-        <v>56376</v>
+        <v>55752</v>
       </c>
       <c r="H27">
-        <v>18607</v>
+        <v>19258</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74417</v>
+        <v>74308</v>
       </c>
       <c r="E28">
         <v>127879</v>
       </c>
       <c r="F28">
-        <v>93321</v>
+        <v>93290</v>
       </c>
       <c r="G28">
-        <v>134382</v>
+        <v>134338</v>
       </c>
       <c r="H28">
-        <v>18904</v>
+        <v>18982</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25166</v>
+        <v>25135</v>
       </c>
       <c r="E29">
         <v>127879</v>
       </c>
       <c r="F29">
-        <v>52166</v>
+        <v>52135</v>
       </c>
       <c r="G29">
-        <v>75119</v>
+        <v>75074</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131048</v>
+        <v>130661</v>
       </c>
       <c r="E30">
         <v>182692</v>
       </c>
       <c r="F30">
-        <v>146456</v>
+        <v>146477</v>
       </c>
       <c r="G30">
-        <v>210897</v>
+        <v>210927</v>
       </c>
       <c r="H30">
-        <v>15408</v>
+        <v>15816</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57478</v>
+        <v>57499</v>
       </c>
       <c r="E31">
         <v>182692</v>
       </c>
       <c r="F31">
-        <v>84478</v>
+        <v>84499</v>
       </c>
       <c r="G31">
-        <v>121648</v>
+        <v>121679</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71440</v>
+        <v>71485</v>
       </c>
       <c r="E32">
         <v>109608</v>
       </c>
       <c r="F32">
-        <v>86544</v>
+        <v>86548</v>
       </c>
       <c r="G32">
-        <v>124623</v>
+        <v>124629</v>
       </c>
       <c r="H32">
-        <v>15104</v>
+        <v>15063</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>41228</v>
+        <v>41238</v>
       </c>
       <c r="E33">
         <v>109608</v>
       </c>
       <c r="F33">
-        <v>65238</v>
+        <v>65242</v>
       </c>
       <c r="G33">
-        <v>93943</v>
+        <v>93948</v>
       </c>
       <c r="H33">
-        <v>24010</v>
+        <v>24004</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>52980</v>
+        <v>57671</v>
       </c>
       <c r="E35">
         <v>127879</v>
       </c>
       <c r="F35">
-        <v>77065</v>
+        <v>78941</v>
       </c>
       <c r="G35">
-        <v>110974</v>
+        <v>113675</v>
       </c>
       <c r="H35">
-        <v>24085</v>
+        <v>21270</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44644</v>
+        <v>44672</v>
       </c>
       <c r="E36">
         <v>127879</v>
       </c>
       <c r="F36">
-        <v>72666</v>
+        <v>72673</v>
       </c>
       <c r="G36">
-        <v>104639</v>
+        <v>104649</v>
       </c>
       <c r="H36">
-        <v>28022</v>
+        <v>28001</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,16 +2025,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35587</v>
+        <v>35594</v>
       </c>
       <c r="E37">
         <v>127879</v>
       </c>
       <c r="F37">
-        <v>62587</v>
+        <v>62594</v>
       </c>
       <c r="G37">
-        <v>90125</v>
+        <v>90135</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>83882</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>237505</v>
       </c>
       <c r="F39">
-        <v>110882</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>159670</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>83882</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>237505</v>
       </c>
       <c r="F41">
-        <v>110882</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>159670</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>39081</v>
+        <v>39028</v>
       </c>
       <c r="E43">
         <v>127879</v>
       </c>
       <c r="F43">
-        <v>66081</v>
+        <v>66028</v>
       </c>
       <c r="G43">
-        <v>95157</v>
+        <v>95080</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92860</v>
+        <v>92873</v>
       </c>
       <c r="E45">
         <v>182692</v>
       </c>
       <c r="F45">
-        <v>114394</v>
+        <v>114399</v>
       </c>
       <c r="G45">
-        <v>164727</v>
+        <v>164735</v>
       </c>
       <c r="H45">
-        <v>21534</v>
+        <v>21526</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>26764</v>
+        <v>26734</v>
       </c>
       <c r="E47">
         <v>109608</v>
       </c>
       <c r="F47">
-        <v>53764</v>
+        <v>53734</v>
       </c>
       <c r="G47">
-        <v>77420</v>
+        <v>77377</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35712</v>
+        <v>35735</v>
       </c>
       <c r="E50">
         <v>63930</v>
       </c>
       <c r="F50">
-        <v>56220</v>
+        <v>56242</v>
       </c>
       <c r="G50">
-        <v>80957</v>
+        <v>80988</v>
       </c>
       <c r="H50">
-        <v>20508</v>
+        <v>20507</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33220</v>
+        <v>33242</v>
       </c>
       <c r="E51">
         <v>63930</v>
       </c>
       <c r="F51">
-        <v>48220</v>
+        <v>48242</v>
       </c>
       <c r="G51">
-        <v>69437</v>
+        <v>69468</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2723,16 +2723,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>35681</v>
+        <v>35625</v>
       </c>
       <c r="E53">
         <v>76720</v>
       </c>
       <c r="F53">
-        <v>50681</v>
+        <v>50625</v>
       </c>
       <c r="G53">
-        <v>72981</v>
+        <v>72900</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48248</v>
+        <v>48279</v>
       </c>
       <c r="E54">
         <v>127879</v>
       </c>
       <c r="F54">
-        <v>83248</v>
+        <v>83279</v>
       </c>
       <c r="G54">
-        <v>119877</v>
+        <v>119922</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>51883</v>
+        <v>52026</v>
       </c>
       <c r="E55">
         <v>127879</v>
       </c>
       <c r="F55">
-        <v>76626</v>
+        <v>76683</v>
       </c>
       <c r="G55">
-        <v>110341</v>
+        <v>110424</v>
       </c>
       <c r="H55">
-        <v>24743</v>
+        <v>24657</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62649</v>
+        <v>62563</v>
       </c>
       <c r="E57">
         <v>146150</v>
       </c>
       <c r="F57">
-        <v>88058</v>
+        <v>88024</v>
       </c>
       <c r="G57">
-        <v>126804</v>
+        <v>126755</v>
       </c>
       <c r="H57">
-        <v>25409</v>
+        <v>25461</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6252</v>
+        <v>6209</v>
       </c>
       <c r="E59">
         <v>36524</v>
       </c>
       <c r="F59">
-        <v>22745</v>
+        <v>22728</v>
       </c>
       <c r="G59">
-        <v>32753</v>
+        <v>32728</v>
       </c>
       <c r="H59">
-        <v>16493</v>
+        <v>16519</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,7 +3036,7 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26185</v>
+        <v>26154</v>
       </c>
       <c r="E60">
         <v>49313</v>
@@ -3048,7 +3048,7 @@
         <v>69021</v>
       </c>
       <c r="H60">
-        <v>21746</v>
+        <v>21777</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12834</v>
+        <v>12826</v>
       </c>
       <c r="E63">
         <v>82201</v>
       </c>
       <c r="F63">
-        <v>39834</v>
+        <v>39826</v>
       </c>
       <c r="G63">
-        <v>57361</v>
+        <v>57349</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>29225</v>
+        <v>28977</v>
       </c>
       <c r="E65">
         <v>123293</v>
       </c>
       <c r="F65">
-        <v>56225</v>
+        <v>55977</v>
       </c>
       <c r="G65">
-        <v>80964</v>
+        <v>80607</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24853</v>
+        <v>24712</v>
       </c>
       <c r="E66">
         <v>91337</v>
       </c>
       <c r="F66">
-        <v>54086</v>
+        <v>52279</v>
       </c>
       <c r="G66">
-        <v>77884</v>
+        <v>75282</v>
       </c>
       <c r="H66">
-        <v>29233</v>
+        <v>27567</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>19086</v>
+        <v>17279</v>
       </c>
       <c r="E67">
         <v>91337</v>
       </c>
       <c r="F67">
-        <v>46086</v>
+        <v>44279</v>
       </c>
       <c r="G67">
-        <v>66364</v>
+        <v>63762</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34333</v>
+        <v>34339</v>
       </c>
       <c r="E68">
         <v>109608</v>
       </c>
       <c r="F68">
-        <v>62720</v>
+        <v>62722</v>
       </c>
       <c r="G68">
-        <v>90317</v>
+        <v>90320</v>
       </c>
       <c r="H68">
-        <v>28387</v>
+        <v>28383</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27532</v>
+        <v>27534</v>
       </c>
       <c r="E69">
         <v>109608</v>
       </c>
       <c r="F69">
-        <v>54532</v>
+        <v>54534</v>
       </c>
       <c r="G69">
-        <v>78526</v>
+        <v>78529</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45208</v>
+        <v>45143</v>
       </c>
       <c r="E70">
         <v>127879</v>
       </c>
       <c r="F70">
-        <v>80208</v>
+        <v>80143</v>
       </c>
       <c r="G70">
-        <v>115500</v>
+        <v>115406</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,7 +3518,7 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50708</v>
+        <v>50709</v>
       </c>
       <c r="E71">
         <v>127879</v>
@@ -3530,7 +3530,7 @@
         <v>109665</v>
       </c>
       <c r="H71">
-        <v>25448</v>
+        <v>25447</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5532</v>
+        <v>5519</v>
       </c>
       <c r="E73">
         <v>27388</v>
       </c>
       <c r="F73">
-        <v>20532</v>
+        <v>20519</v>
       </c>
       <c r="G73">
-        <v>29566</v>
+        <v>29547</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70390</v>
+        <v>70403</v>
       </c>
       <c r="E75">
         <v>95904</v>
       </c>
       <c r="F75">
-        <v>85390</v>
+        <v>85403</v>
       </c>
       <c r="G75">
-        <v>122962</v>
+        <v>122980</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80418</v>
+        <v>80564</v>
       </c>
       <c r="E76">
         <v>127879</v>
       </c>
       <c r="F76">
-        <v>95713</v>
+        <v>95771</v>
       </c>
       <c r="G76">
-        <v>137827</v>
+        <v>137910</v>
       </c>
       <c r="H76">
-        <v>15295</v>
+        <v>15207</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>49110</v>
+        <v>48373</v>
       </c>
       <c r="E77">
         <v>127879</v>
       </c>
       <c r="F77">
-        <v>75517</v>
+        <v>75222</v>
       </c>
       <c r="G77">
-        <v>108744</v>
+        <v>108320</v>
       </c>
       <c r="H77">
-        <v>26407</v>
+        <v>26849</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36966</v>
+        <v>36911</v>
       </c>
       <c r="E81">
         <v>91337</v>
       </c>
       <c r="F81">
-        <v>56408</v>
+        <v>56386</v>
       </c>
       <c r="G81">
-        <v>81228</v>
+        <v>81196</v>
       </c>
       <c r="H81">
-        <v>19442</v>
+        <v>19475</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84477</v>
+        <v>84358</v>
       </c>
       <c r="E83">
         <v>127879</v>
       </c>
       <c r="F83">
-        <v>99477</v>
+        <v>99358</v>
       </c>
       <c r="G83">
-        <v>143247</v>
+        <v>143076</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48201</v>
+        <v>47934</v>
       </c>
       <c r="E84">
         <v>102299</v>
       </c>
       <c r="F84">
-        <v>71315</v>
+        <v>71235</v>
       </c>
       <c r="G84">
-        <v>102694</v>
+        <v>102578</v>
       </c>
       <c r="H84">
-        <v>23114</v>
+        <v>23301</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32468</v>
+        <v>32269</v>
       </c>
       <c r="E85">
         <v>102299</v>
       </c>
       <c r="F85">
-        <v>58884</v>
+        <v>58804</v>
       </c>
       <c r="G85">
-        <v>84793</v>
+        <v>84678</v>
       </c>
       <c r="H85">
-        <v>26416</v>
+        <v>26535</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4177,13 +4177,13 @@
         <v>146150</v>
       </c>
       <c r="F86">
-        <v>164887</v>
+        <v>164896</v>
       </c>
       <c r="G86">
-        <v>237437</v>
+        <v>237450</v>
       </c>
       <c r="H86">
-        <v>15000</v>
+        <v>15009</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113749</v>
+        <v>113758</v>
       </c>
       <c r="E87">
         <v>146150</v>
       </c>
       <c r="F87">
-        <v>128749</v>
+        <v>128758</v>
       </c>
       <c r="G87">
-        <v>185399</v>
+        <v>185412</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>159286</v>
+        <v>81285</v>
       </c>
       <c r="E88">
         <v>160767</v>
       </c>
       <c r="F88">
-        <v>174286</v>
+        <v>116285</v>
       </c>
       <c r="G88">
-        <v>250972</v>
+        <v>167450</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>126441</v>
+        <v>126271</v>
       </c>
       <c r="E89">
         <v>160767</v>
       </c>
       <c r="F89">
-        <v>141441</v>
+        <v>141271</v>
       </c>
       <c r="G89">
-        <v>203675</v>
+        <v>203430</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4352,13 +4352,13 @@
         <v>58449</v>
       </c>
       <c r="F90">
-        <v>38500</v>
+        <v>38495</v>
       </c>
       <c r="G90">
-        <v>55440</v>
+        <v>55433</v>
       </c>
       <c r="H90">
-        <v>30820</v>
+        <v>30815</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4262</v>
+        <v>4249</v>
       </c>
       <c r="E91">
         <v>58449</v>
       </c>
       <c r="F91">
-        <v>30500</v>
+        <v>30495</v>
       </c>
       <c r="G91">
-        <v>43920</v>
+        <v>43913</v>
       </c>
       <c r="H91">
-        <v>26238</v>
+        <v>26246</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12144</v>
+        <v>12121</v>
       </c>
       <c r="E93">
         <v>27388</v>
       </c>
       <c r="F93">
-        <v>27144</v>
+        <v>27121</v>
       </c>
       <c r="G93">
-        <v>39087</v>
+        <v>39054</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4608,7 +4608,7 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61701</v>
+        <v>61513</v>
       </c>
       <c r="E96">
         <v>82201</v>
@@ -4620,7 +4620,7 @@
         <v>110449</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>15188</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>74574</v>
+        <v>74621</v>
       </c>
       <c r="E98">
         <v>94991</v>
       </c>
       <c r="F98">
-        <v>89690</v>
+        <v>90953</v>
       </c>
       <c r="G98">
-        <v>129154</v>
+        <v>130972</v>
       </c>
       <c r="H98">
-        <v>15116</v>
+        <v>16332</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33487</v>
+        <v>36644</v>
       </c>
       <c r="E99">
         <v>94991</v>
       </c>
       <c r="F99">
-        <v>56441</v>
+        <v>57704</v>
       </c>
       <c r="G99">
-        <v>81275</v>
+        <v>83094</v>
       </c>
       <c r="H99">
-        <v>22954</v>
+        <v>21060</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61254</v>
+        <v>61215</v>
       </c>
       <c r="E100">
         <v>106502</v>
@@ -4800,7 +4800,7 @@
         <v>115023</v>
       </c>
       <c r="H100">
-        <v>18623</v>
+        <v>18662</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61348</v>
+        <v>61356</v>
       </c>
       <c r="E101">
         <v>106502</v>
       </c>
       <c r="F101">
-        <v>76348</v>
+        <v>76356</v>
       </c>
       <c r="G101">
-        <v>109941</v>
+        <v>109953</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68760</v>
+        <v>68788</v>
       </c>
       <c r="E105">
         <v>127879</v>
       </c>
       <c r="F105">
-        <v>83760</v>
+        <v>83788</v>
       </c>
       <c r="G105">
-        <v>120614</v>
+        <v>120655</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,16 +5091,16 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>100476</v>
+        <v>100477</v>
       </c>
       <c r="E107">
         <v>182692</v>
       </c>
       <c r="F107">
-        <v>117440</v>
+        <v>117441</v>
       </c>
       <c r="G107">
-        <v>169114</v>
+        <v>169115</v>
       </c>
       <c r="H107">
         <v>16964</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4106</v>
+        <v>4092</v>
       </c>
       <c r="E109">
         <v>127879</v>
       </c>
       <c r="F109">
-        <v>31106</v>
+        <v>31092</v>
       </c>
       <c r="G109">
-        <v>44793</v>
+        <v>44772</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13367</v>
+        <v>13344</v>
       </c>
       <c r="E111">
         <v>164421</v>
       </c>
       <c r="F111">
-        <v>40367</v>
+        <v>40344</v>
       </c>
       <c r="G111">
-        <v>58128</v>
+        <v>58095</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48593</v>
+        <v>48561</v>
       </c>
       <c r="E113">
         <v>87683</v>
       </c>
       <c r="F113">
-        <v>63593</v>
+        <v>63561</v>
       </c>
       <c r="G113">
-        <v>91574</v>
+        <v>91528</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85010</v>
+        <v>85017</v>
       </c>
       <c r="E115">
         <v>116916</v>
       </c>
       <c r="F115">
-        <v>100010</v>
+        <v>100017</v>
       </c>
       <c r="G115">
-        <v>144014</v>
+        <v>144024</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,16 +5526,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>116710</v>
+        <v>114668</v>
       </c>
       <c r="E117">
         <v>146150</v>
       </c>
       <c r="F117">
-        <v>131710</v>
+        <v>129668</v>
       </c>
       <c r="G117">
-        <v>189662</v>
+        <v>186722</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>31998</v>
+        <v>31689</v>
       </c>
       <c r="E119">
         <v>58449</v>
       </c>
       <c r="F119">
-        <v>46998</v>
+        <v>46689</v>
       </c>
       <c r="G119">
-        <v>67677</v>
+        <v>67232</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60721</v>
+        <v>60713</v>
       </c>
       <c r="E120">
         <v>80374</v>
       </c>
       <c r="F120">
-        <v>79076</v>
+        <v>79079</v>
       </c>
       <c r="G120">
-        <v>113869</v>
+        <v>113874</v>
       </c>
       <c r="H120">
-        <v>18355</v>
+        <v>18366</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53748</v>
+        <v>53751</v>
       </c>
       <c r="E121">
         <v>80374</v>
       </c>
       <c r="F121">
-        <v>68748</v>
+        <v>68751</v>
       </c>
       <c r="G121">
-        <v>98997</v>
+        <v>99001</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>46524</v>
+        <v>46538</v>
       </c>
       <c r="E122">
         <v>91337</v>
       </c>
       <c r="F122">
-        <v>68351</v>
+        <v>68339</v>
       </c>
       <c r="G122">
-        <v>98425</v>
+        <v>98408</v>
       </c>
       <c r="H122">
-        <v>21827</v>
+        <v>21801</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>27736</v>
+        <v>27707</v>
       </c>
       <c r="E123">
         <v>91337</v>
       </c>
       <c r="F123">
-        <v>52716</v>
+        <v>52704</v>
       </c>
       <c r="G123">
-        <v>75911</v>
+        <v>75894</v>
       </c>
       <c r="H123">
-        <v>24980</v>
+        <v>24997</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7334</v>
+        <v>7338</v>
       </c>
       <c r="E125">
         <v>43832</v>
       </c>
       <c r="F125">
-        <v>26028</v>
+        <v>26030</v>
       </c>
       <c r="G125">
-        <v>37480</v>
+        <v>37483</v>
       </c>
       <c r="H125">
-        <v>18694</v>
+        <v>18692</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20152</v>
+        <v>20117</v>
       </c>
       <c r="E129">
         <v>59892</v>
       </c>
       <c r="F129">
-        <v>37419</v>
+        <v>37405</v>
       </c>
       <c r="G129">
-        <v>53883</v>
+        <v>53863</v>
       </c>
       <c r="H129">
-        <v>17267</v>
+        <v>17288</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20152</v>
+        <v>20117</v>
       </c>
       <c r="E131">
         <v>74619</v>
       </c>
       <c r="F131">
-        <v>43162</v>
+        <v>43148</v>
       </c>
       <c r="G131">
-        <v>62153</v>
+        <v>62133</v>
       </c>
       <c r="H131">
-        <v>23010</v>
+        <v>23031</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>34646</v>
+        <v>33210</v>
       </c>
       <c r="E133">
         <v>93931</v>
       </c>
       <c r="F133">
-        <v>56491</v>
+        <v>55917</v>
       </c>
       <c r="G133">
-        <v>81347</v>
+        <v>80520</v>
       </c>
       <c r="H133">
-        <v>21845</v>
+        <v>22707</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53262</v>
+        <v>53187</v>
       </c>
       <c r="E135">
         <v>89510</v>
       </c>
       <c r="F135">
-        <v>68262</v>
+        <v>68187</v>
       </c>
       <c r="G135">
-        <v>98297</v>
+        <v>98189</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>73163</v>
+        <v>73053</v>
       </c>
       <c r="E137">
         <v>127879</v>
       </c>
       <c r="F137">
-        <v>88163</v>
+        <v>88053</v>
       </c>
       <c r="G137">
-        <v>126955</v>
+        <v>126796</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6486,16 +6486,16 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91278</v>
+        <v>91164</v>
       </c>
       <c r="E139">
         <v>153458</v>
       </c>
       <c r="F139">
-        <v>106278</v>
+        <v>106164</v>
       </c>
       <c r="G139">
-        <v>153040</v>
+        <v>152876</v>
       </c>
       <c r="H139">
         <v>15000</v>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37498</v>
+        <v>37287</v>
       </c>
       <c r="E140">
         <v>91337</v>
       </c>
       <c r="F140">
-        <v>62101</v>
+        <v>62017</v>
       </c>
       <c r="G140">
-        <v>89425</v>
+        <v>89304</v>
       </c>
       <c r="H140">
-        <v>24603</v>
+        <v>24730</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26733</v>
+        <v>26687</v>
       </c>
       <c r="E142">
         <v>91337</v>
       </c>
       <c r="F142">
-        <v>60553</v>
+        <v>60541</v>
       </c>
       <c r="G142">
-        <v>87196</v>
+        <v>87179</v>
       </c>
       <c r="H142">
-        <v>33820</v>
+        <v>33854</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27328</v>
+        <v>27299</v>
       </c>
       <c r="E143">
         <v>91337</v>
       </c>
       <c r="F143">
-        <v>52553</v>
+        <v>52541</v>
       </c>
       <c r="G143">
-        <v>75676</v>
+        <v>75659</v>
       </c>
       <c r="H143">
-        <v>25225</v>
+        <v>25242</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>43516</v>
+        <v>42853</v>
       </c>
       <c r="E144">
         <v>91337</v>
@@ -6718,7 +6718,7 @@
         <v>98644</v>
       </c>
       <c r="H144">
-        <v>24987</v>
+        <v>25650</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>80121</v>
+        <v>79513</v>
       </c>
       <c r="E145">
         <v>91337</v>
       </c>
       <c r="F145">
-        <v>95121</v>
+        <v>94513</v>
       </c>
       <c r="G145">
-        <v>136974</v>
+        <v>136099</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58245</v>
+        <v>58251</v>
       </c>
       <c r="E146">
         <v>91337</v>
       </c>
       <c r="F146">
-        <v>93245</v>
+        <v>93251</v>
       </c>
       <c r="G146">
-        <v>134273</v>
+        <v>134281</v>
       </c>
       <c r="H146">
         <v>35000</v>
@@ -6840,16 +6840,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>94114</v>
+        <v>94096</v>
       </c>
       <c r="E147">
         <v>91337</v>
       </c>
       <c r="F147">
-        <v>109114</v>
+        <v>109096</v>
       </c>
       <c r="G147">
-        <v>157124</v>
+        <v>157098</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36621</v>
+        <v>36628</v>
       </c>
       <c r="E148">
         <v>62103</v>
       </c>
       <c r="F148">
-        <v>64187</v>
+        <v>64119</v>
       </c>
       <c r="G148">
-        <v>92429</v>
+        <v>92331</v>
       </c>
       <c r="H148">
-        <v>27566</v>
+        <v>27491</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>40805</v>
+        <v>40737</v>
       </c>
       <c r="E149">
         <v>62103</v>
       </c>
       <c r="F149">
-        <v>55805</v>
+        <v>55737</v>
       </c>
       <c r="G149">
-        <v>80359</v>
+        <v>80261</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -7014,16 +7014,16 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15623</v>
+        <v>15602</v>
       </c>
       <c r="E151">
         <v>82201</v>
       </c>
       <c r="F151">
-        <v>42623</v>
+        <v>42602</v>
       </c>
       <c r="G151">
-        <v>61377</v>
+        <v>61347</v>
       </c>
       <c r="H151">
         <v>27000</v>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37592</v>
+        <v>37538</v>
       </c>
       <c r="E152">
         <v>73066</v>
@@ -7070,7 +7070,7 @@
         <v>78912</v>
       </c>
       <c r="H152">
-        <v>17208</v>
+        <v>17262</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33440</v>
+        <v>33445</v>
       </c>
       <c r="E153">
         <v>73066</v>
       </c>
       <c r="F153">
-        <v>48440</v>
+        <v>48445</v>
       </c>
       <c r="G153">
-        <v>69754</v>
+        <v>69761</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56851</v>
+        <v>56762</v>
       </c>
       <c r="E154">
         <v>73066</v>
       </c>
       <c r="F154">
-        <v>91851</v>
+        <v>84131</v>
       </c>
       <c r="G154">
-        <v>132265</v>
+        <v>121149</v>
       </c>
       <c r="H154">
-        <v>35000</v>
+        <v>27369</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>69042</v>
+        <v>58157</v>
       </c>
       <c r="E155">
         <v>73066</v>
       </c>
       <c r="F155">
-        <v>84042</v>
+        <v>73157</v>
       </c>
       <c r="G155">
-        <v>121020</v>
+        <v>105346</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11988</v>
+        <v>11948</v>
       </c>
       <c r="E157">
         <v>27388</v>
       </c>
       <c r="F157">
-        <v>26988</v>
+        <v>26948</v>
       </c>
       <c r="G157">
-        <v>38863</v>
+        <v>38805</v>
       </c>
       <c r="H157">
         <v>15000</v>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>85072</v>
+        <v>85080</v>
       </c>
       <c r="E158">
         <v>84028</v>
       </c>
       <c r="F158">
-        <v>100208</v>
+        <v>100080</v>
       </c>
       <c r="G158">
-        <v>144300</v>
+        <v>144115</v>
       </c>
       <c r="H158">
-        <v>15136</v>
+        <v>15000</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>35947</v>
+        <v>25668</v>
       </c>
       <c r="E159">
         <v>84028</v>
       </c>
       <c r="F159">
-        <v>53150</v>
+        <v>49038</v>
       </c>
       <c r="G159">
-        <v>76536</v>
+        <v>70615</v>
       </c>
       <c r="H159">
-        <v>17203</v>
+        <v>23370</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54813</v>
       </c>
       <c r="F160">
-        <v>38812</v>
+        <v>38801</v>
       </c>
       <c r="G160">
-        <v>55889</v>
+        <v>55873</v>
       </c>
       <c r="H160">
-        <v>31132</v>
+        <v>31121</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8587</v>
+        <v>8561</v>
       </c>
       <c r="E161">
         <v>54813</v>
       </c>
       <c r="F161">
-        <v>30812</v>
+        <v>30801</v>
       </c>
       <c r="G161">
-        <v>44369</v>
+        <v>44353</v>
       </c>
       <c r="H161">
-        <v>22225</v>
+        <v>22240</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>73066</v>
       </c>
       <c r="F162">
-        <v>42898</v>
+        <v>44079</v>
       </c>
       <c r="G162">
-        <v>61773</v>
+        <v>63474</v>
       </c>
       <c r="H162">
-        <v>32751</v>
+        <v>33932</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>7898</v>
+        <v>9079</v>
       </c>
       <c r="E163">
         <v>73066</v>
       </c>
       <c r="F163">
-        <v>34898</v>
+        <v>36079</v>
       </c>
       <c r="G163">
-        <v>50253</v>
+        <v>51954</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>67209</v>
+        <v>67252</v>
       </c>
       <c r="E164">
         <v>68516</v>
       </c>
       <c r="F164">
-        <v>82321</v>
+        <v>82308</v>
       </c>
       <c r="G164">
-        <v>118542</v>
+        <v>118524</v>
       </c>
       <c r="H164">
-        <v>15112</v>
+        <v>15056</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20778</v>
+        <v>20745</v>
       </c>
       <c r="E165">
         <v>68516</v>
       </c>
       <c r="F165">
-        <v>41032</v>
+        <v>41019</v>
       </c>
       <c r="G165">
-        <v>59086</v>
+        <v>59067</v>
       </c>
       <c r="H165">
-        <v>20254</v>
+        <v>20274</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>90244</v>
+        <v>90301</v>
       </c>
       <c r="E166">
         <v>103231</v>
       </c>
       <c r="F166">
-        <v>105374</v>
+        <v>105356</v>
       </c>
       <c r="G166">
-        <v>151739</v>
+        <v>151713</v>
       </c>
       <c r="H166">
-        <v>15130</v>
+        <v>15055</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21860</v>
+        <v>21842</v>
       </c>
       <c r="E167">
         <v>103231</v>
       </c>
       <c r="F167">
-        <v>48860</v>
+        <v>48842</v>
       </c>
       <c r="G167">
-        <v>70358</v>
+        <v>70332</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>73066</v>
       </c>
       <c r="F168">
-        <v>103977</v>
+        <v>103857</v>
       </c>
       <c r="G168">
-        <v>149727</v>
+        <v>149554</v>
       </c>
       <c r="H168">
-        <v>15156</v>
+        <v>15036</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8979</v>
+        <v>8859</v>
       </c>
       <c r="E169">
         <v>73066</v>
       </c>
       <c r="F169">
-        <v>35979</v>
+        <v>35859</v>
       </c>
       <c r="G169">
-        <v>51810</v>
+        <v>51637</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58747</v>
+        <v>58784</v>
       </c>
       <c r="E170">
         <v>109608</v>
       </c>
       <c r="F170">
-        <v>81259</v>
+        <v>81223</v>
       </c>
       <c r="G170">
-        <v>117013</v>
+        <v>116961</v>
       </c>
       <c r="H170">
-        <v>22512</v>
+        <v>22439</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>54782</v>
+        <v>54692</v>
       </c>
       <c r="E171">
         <v>109608</v>
       </c>
       <c r="F171">
-        <v>70660</v>
+        <v>70624</v>
       </c>
       <c r="G171">
-        <v>101750</v>
+        <v>101699</v>
       </c>
       <c r="H171">
-        <v>15878</v>
+        <v>15932</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77708</v>
+        <v>77757</v>
       </c>
       <c r="E172">
         <v>146150</v>
       </c>
       <c r="F172">
-        <v>108556</v>
+        <v>108557</v>
       </c>
       <c r="G172">
-        <v>156321</v>
+        <v>156322</v>
       </c>
       <c r="H172">
-        <v>30848</v>
+        <v>30800</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78475</v>
+        <v>78478</v>
       </c>
       <c r="E173">
         <v>146150</v>
       </c>
       <c r="F173">
-        <v>94389</v>
+        <v>94390</v>
       </c>
       <c r="G173">
-        <v>135920</v>
+        <v>135922</v>
       </c>
       <c r="H173">
-        <v>15914</v>
+        <v>15912</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48796</v>
+        <v>48655</v>
       </c>
       <c r="E174">
         <v>91337</v>
@@ -8045,7 +8045,7 @@
         <v>98644</v>
       </c>
       <c r="H174">
-        <v>19707</v>
+        <v>19848</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>64137</v>
+        <v>64037</v>
       </c>
       <c r="E175">
         <v>91337</v>
       </c>
       <c r="F175">
-        <v>79137</v>
+        <v>79037</v>
       </c>
       <c r="G175">
-        <v>113957</v>
+        <v>113813</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65313</v>
+        <v>65229</v>
       </c>
       <c r="E176">
         <v>91337</v>
       </c>
       <c r="F176">
-        <v>80313</v>
+        <v>80229</v>
       </c>
       <c r="G176">
-        <v>115651</v>
+        <v>115530</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26952</v>
+        <v>26609</v>
       </c>
       <c r="E178">
         <v>109608</v>
       </c>
       <c r="F178">
-        <v>53952</v>
+        <v>53609</v>
       </c>
       <c r="G178">
-        <v>77691</v>
+        <v>77197</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25166</v>
+        <v>25135</v>
       </c>
       <c r="E180">
         <v>91337</v>
       </c>
       <c r="F180">
-        <v>52166</v>
+        <v>52135</v>
       </c>
       <c r="G180">
-        <v>75119</v>
+        <v>75074</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100272</v>
+        <v>100336</v>
       </c>
       <c r="E182">
         <v>127879</v>
       </c>
       <c r="F182">
-        <v>115415</v>
+        <v>115419</v>
       </c>
       <c r="G182">
-        <v>166198</v>
+        <v>166203</v>
       </c>
       <c r="H182">
-        <v>15143</v>
+        <v>15083</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64106</v>
+        <v>64116</v>
       </c>
       <c r="E183">
         <v>127879</v>
       </c>
       <c r="F183">
-        <v>81515</v>
+        <v>81519</v>
       </c>
       <c r="G183">
-        <v>117382</v>
+        <v>117387</v>
       </c>
       <c r="H183">
-        <v>17409</v>
+        <v>17403</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144148</v>
+        <v>144240</v>
       </c>
       <c r="E184">
         <v>182692</v>
       </c>
       <c r="F184">
-        <v>159301</v>
+        <v>159240</v>
       </c>
       <c r="G184">
-        <v>229393</v>
+        <v>229306</v>
       </c>
       <c r="H184">
-        <v>15153</v>
+        <v>15000</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64216</v>
+        <v>64131</v>
       </c>
       <c r="E185">
         <v>182692</v>
       </c>
       <c r="F185">
-        <v>91216</v>
+        <v>91131</v>
       </c>
       <c r="G185">
-        <v>131351</v>
+        <v>131229</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64216</v>
+        <v>64131</v>
       </c>
       <c r="E187">
         <v>182692</v>
       </c>
       <c r="F187">
-        <v>91216</v>
+        <v>91131</v>
       </c>
       <c r="G187">
-        <v>131351</v>
+        <v>131229</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>289879</v>
+        <v>290064</v>
       </c>
       <c r="E188">
         <v>365402</v>
       </c>
       <c r="F188">
-        <v>324879</v>
+        <v>325064</v>
       </c>
       <c r="G188">
-        <v>467826</v>
+        <v>468092</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>305847</v>
+        <v>305885</v>
       </c>
       <c r="E189">
         <v>365402</v>
       </c>
       <c r="F189">
-        <v>320847</v>
+        <v>320885</v>
       </c>
       <c r="G189">
-        <v>462020</v>
+        <v>462074</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>31089</v>
+        <v>30874</v>
       </c>
       <c r="E190">
         <v>95904</v>
       </c>
       <c r="F190">
-        <v>66089</v>
+        <v>65874</v>
       </c>
       <c r="G190">
-        <v>95168</v>
+        <v>94859</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44377</v>
+        <v>44390</v>
       </c>
       <c r="E191">
         <v>95904</v>
       </c>
       <c r="F191">
-        <v>61154</v>
+        <v>61159</v>
       </c>
       <c r="G191">
-        <v>88062</v>
+        <v>88069</v>
       </c>
       <c r="H191">
-        <v>16777</v>
+        <v>16769</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>42951</v>
+        <v>42948</v>
       </c>
       <c r="E192">
         <v>123311</v>
       </c>
       <c r="F192">
-        <v>77951</v>
+        <v>77948</v>
       </c>
       <c r="G192">
-        <v>112249</v>
+        <v>112245</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50567</v>
+        <v>50537</v>
       </c>
       <c r="E194">
         <v>150900</v>
       </c>
       <c r="F194">
-        <v>77567</v>
+        <v>77537</v>
       </c>
       <c r="G194">
-        <v>111696</v>
+        <v>111653</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8998,7 +8998,7 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23787</v>
+        <v>23755</v>
       </c>
       <c r="E196">
         <v>73066</v>
@@ -9010,7 +9010,7 @@
         <v>78912</v>
       </c>
       <c r="H196">
-        <v>31013</v>
+        <v>31045</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32343</v>
+        <v>32348</v>
       </c>
       <c r="E197">
         <v>73066</v>
       </c>
       <c r="F197">
-        <v>47433</v>
+        <v>47435</v>
       </c>
       <c r="G197">
-        <v>68304</v>
+        <v>68306</v>
       </c>
       <c r="H197">
-        <v>15090</v>
+        <v>15087</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26153</v>
+        <v>26170</v>
       </c>
       <c r="E198">
         <v>109608</v>
       </c>
       <c r="F198">
-        <v>61153</v>
+        <v>61170</v>
       </c>
       <c r="G198">
-        <v>88060</v>
+        <v>88085</v>
       </c>
       <c r="H198">
         <v>35000</v>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37310</v>
+        <v>37318</v>
       </c>
       <c r="E199">
         <v>109608</v>
       </c>
       <c r="F199">
-        <v>63671</v>
+        <v>63674</v>
       </c>
       <c r="G199">
-        <v>91686</v>
+        <v>91691</v>
       </c>
       <c r="H199">
-        <v>26361</v>
+        <v>26356</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>127879</v>
       </c>
       <c r="F200">
-        <v>46894</v>
+        <v>46870</v>
       </c>
       <c r="G200">
-        <v>67527</v>
+        <v>67493</v>
       </c>
       <c r="H200">
-        <v>32829</v>
+        <v>32805</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11894</v>
+        <v>11870</v>
       </c>
       <c r="E201">
         <v>127879</v>
       </c>
       <c r="F201">
-        <v>38894</v>
+        <v>38870</v>
       </c>
       <c r="G201">
-        <v>56007</v>
+        <v>55973</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22596</v>
+        <v>22595</v>
       </c>
       <c r="E203">
         <v>146150</v>
       </c>
       <c r="F203">
-        <v>49596</v>
+        <v>49595</v>
       </c>
       <c r="G203">
-        <v>71418</v>
+        <v>71417</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>182692</v>
       </c>
       <c r="F204">
-        <v>61138</v>
+        <v>61139</v>
       </c>
       <c r="G204">
-        <v>88039</v>
+        <v>88040</v>
       </c>
       <c r="H204">
-        <v>32400</v>
+        <v>32401</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,16 +9402,16 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26138</v>
+        <v>26139</v>
       </c>
       <c r="E205">
         <v>182692</v>
       </c>
       <c r="F205">
-        <v>53138</v>
+        <v>53139</v>
       </c>
       <c r="G205">
-        <v>76519</v>
+        <v>76520</v>
       </c>
       <c r="H205">
         <v>27000</v>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24210</v>
+        <v>24179</v>
       </c>
       <c r="E206">
         <v>58449</v>
       </c>
       <c r="F206">
-        <v>42293</v>
+        <v>42284</v>
       </c>
       <c r="G206">
-        <v>60902</v>
+        <v>60889</v>
       </c>
       <c r="H206">
-        <v>18083</v>
+        <v>18105</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13037</v>
+        <v>13014</v>
       </c>
       <c r="E207">
         <v>58449</v>
       </c>
       <c r="F207">
-        <v>34010</v>
+        <v>34001</v>
       </c>
       <c r="G207">
-        <v>48974</v>
+        <v>48961</v>
       </c>
       <c r="H207">
-        <v>20973</v>
+        <v>20987</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22910</v>
+        <v>22908</v>
       </c>
       <c r="E209">
         <v>54795</v>
       </c>
       <c r="F209">
-        <v>37910</v>
+        <v>37908</v>
       </c>
       <c r="G209">
-        <v>54590</v>
+        <v>54588</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40225</v>
+        <v>40235</v>
       </c>
       <c r="E211">
         <v>109608</v>
       </c>
       <c r="F211">
-        <v>64837</v>
+        <v>64841</v>
       </c>
       <c r="G211">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="H211">
-        <v>24612</v>
+        <v>24606</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,16 +9749,16 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83349</v>
+        <v>83324</v>
       </c>
       <c r="E213">
         <v>182692</v>
       </c>
       <c r="F213">
-        <v>110349</v>
+        <v>110324</v>
       </c>
       <c r="G213">
-        <v>158903</v>
+        <v>158867</v>
       </c>
       <c r="H213">
         <v>27000</v>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>29084</v>
+        <v>29055</v>
       </c>
       <c r="E214">
         <v>87683</v>
       </c>
       <c r="F214">
-        <v>60651</v>
+        <v>60652</v>
       </c>
       <c r="G214">
-        <v>87337</v>
+        <v>87339</v>
       </c>
       <c r="H214">
-        <v>31567</v>
+        <v>31597</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31136</v>
+        <v>31140</v>
       </c>
       <c r="E215">
         <v>87683</v>
       </c>
       <c r="F215">
-        <v>52651</v>
+        <v>52652</v>
       </c>
       <c r="G215">
-        <v>75817</v>
+        <v>75819</v>
       </c>
       <c r="H215">
-        <v>21515</v>
+        <v>21512</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,16 +9881,16 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>64435</v>
+        <v>64272</v>
       </c>
       <c r="E216">
         <v>102299</v>
       </c>
       <c r="F216">
-        <v>99435</v>
+        <v>99272</v>
       </c>
       <c r="G216">
-        <v>143186</v>
+        <v>142952</v>
       </c>
       <c r="H216">
         <v>35000</v>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88833</v>
+        <v>88843</v>
       </c>
       <c r="E217">
         <v>102299</v>
       </c>
       <c r="F217">
-        <v>103833</v>
+        <v>103843</v>
       </c>
       <c r="G217">
-        <v>149520</v>
+        <v>149534</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111038</v>
+        <v>111046</v>
       </c>
       <c r="E219">
         <v>131533</v>
       </c>
       <c r="F219">
-        <v>126038</v>
+        <v>126046</v>
       </c>
       <c r="G219">
-        <v>181495</v>
+        <v>181506</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10065,13 +10065,13 @@
         <v>82220</v>
       </c>
       <c r="F220">
-        <v>76970</v>
+        <v>75686</v>
       </c>
       <c r="G220">
-        <v>110837</v>
+        <v>108988</v>
       </c>
       <c r="H220">
-        <v>17683</v>
+        <v>16399</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>51930</v>
+        <v>50646</v>
       </c>
       <c r="E221">
         <v>82220</v>
       </c>
       <c r="F221">
-        <v>66930</v>
+        <v>65646</v>
       </c>
       <c r="G221">
-        <v>96379</v>
+        <v>94530</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>73477</v>
+        <v>73524</v>
       </c>
       <c r="E222">
         <v>96836</v>
       </c>
       <c r="F222">
-        <v>88699</v>
+        <v>88609</v>
       </c>
       <c r="G222">
-        <v>127727</v>
+        <v>127597</v>
       </c>
       <c r="H222">
-        <v>15222</v>
+        <v>15085</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>55503</v>
+        <v>55413</v>
       </c>
       <c r="E223">
         <v>96836</v>
       </c>
       <c r="F223">
-        <v>70503</v>
+        <v>70413</v>
       </c>
       <c r="G223">
-        <v>101524</v>
+        <v>101395</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>60276</v>
       </c>
       <c r="F224">
-        <v>41651</v>
+        <v>41572</v>
       </c>
       <c r="G224">
-        <v>59977</v>
+        <v>59864</v>
       </c>
       <c r="H224">
-        <v>25073</v>
+        <v>24994</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10358</v>
+        <v>10161</v>
       </c>
       <c r="E225">
         <v>60276</v>
       </c>
       <c r="F225">
-        <v>33651</v>
+        <v>33572</v>
       </c>
       <c r="G225">
-        <v>48457</v>
+        <v>48344</v>
       </c>
       <c r="H225">
-        <v>23293</v>
+        <v>23411</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37780</v>
+        <v>38087</v>
       </c>
       <c r="E226">
         <v>73066</v>
       </c>
       <c r="F226">
-        <v>54001</v>
+        <v>54115</v>
       </c>
       <c r="G226">
-        <v>77761</v>
+        <v>77926</v>
       </c>
       <c r="H226">
-        <v>16221</v>
+        <v>16028</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,16 +10375,16 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25934</v>
+        <v>25935</v>
       </c>
       <c r="E227">
         <v>73066</v>
       </c>
       <c r="F227">
-        <v>44869</v>
+        <v>44870</v>
       </c>
       <c r="G227">
-        <v>64611</v>
+        <v>64613</v>
       </c>
       <c r="H227">
         <v>18935</v>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83411</v>
+        <v>83433</v>
       </c>
       <c r="E228">
         <v>109608</v>
       </c>
       <c r="F228">
-        <v>99038</v>
+        <v>98433</v>
       </c>
       <c r="G228">
-        <v>142615</v>
+        <v>141744</v>
       </c>
       <c r="H228">
-        <v>15627</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>14495</v>
+        <v>13861</v>
       </c>
       <c r="E229">
         <v>109608</v>
       </c>
       <c r="F229">
-        <v>41495</v>
+        <v>40861</v>
       </c>
       <c r="G229">
-        <v>59753</v>
+        <v>58840</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19321</v>
+        <v>19318</v>
       </c>
       <c r="E231">
         <v>182692</v>
       </c>
       <c r="F231">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="G231">
-        <v>66702</v>
+        <v>66698</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10595,13 +10595,13 @@
         <v>52986</v>
       </c>
       <c r="F232">
-        <v>38645</v>
+        <v>38647</v>
       </c>
       <c r="G232">
-        <v>55649</v>
+        <v>55652</v>
       </c>
       <c r="H232">
-        <v>29310</v>
+        <v>29312</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9950</v>
+        <v>9957</v>
       </c>
       <c r="E233">
         <v>52986</v>
       </c>
       <c r="F233">
-        <v>30645</v>
+        <v>30647</v>
       </c>
       <c r="G233">
-        <v>44129</v>
+        <v>44132</v>
       </c>
       <c r="H233">
-        <v>20695</v>
+        <v>20690</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52986</v>
       </c>
       <c r="F236">
-        <v>37485</v>
+        <v>37481</v>
       </c>
       <c r="G236">
-        <v>53978</v>
+        <v>53973</v>
       </c>
       <c r="H236">
-        <v>29134</v>
+        <v>29130</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>7052</v>
+        <v>7040</v>
       </c>
       <c r="E237">
         <v>52986</v>
       </c>
       <c r="F237">
-        <v>29485</v>
+        <v>29481</v>
       </c>
       <c r="G237">
-        <v>42458</v>
+        <v>42453</v>
       </c>
       <c r="H237">
-        <v>22433</v>
+        <v>22441</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11423</v>
+        <v>11415</v>
       </c>
       <c r="E239">
         <v>52986</v>
       </c>
       <c r="F239">
-        <v>31234</v>
+        <v>31231</v>
       </c>
       <c r="G239">
-        <v>44977</v>
+        <v>44973</v>
       </c>
       <c r="H239">
-        <v>19811</v>
+        <v>19816</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,7 +10941,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24147</v>
+        <v>24163</v>
       </c>
       <c r="E240">
         <v>71257</v>
@@ -10953,7 +10953,7 @@
         <v>76958</v>
       </c>
       <c r="H240">
-        <v>29296</v>
+        <v>29280</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70687</v>
+        <v>71767</v>
       </c>
       <c r="E241">
         <v>71257</v>
       </c>
       <c r="F241">
-        <v>85687</v>
+        <v>86767</v>
       </c>
       <c r="G241">
-        <v>123389</v>
+        <v>124944</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>32139</v>
+        <v>32144</v>
       </c>
       <c r="E242">
         <v>71257</v>
       </c>
       <c r="F242">
-        <v>50921</v>
+        <v>50923</v>
       </c>
       <c r="G242">
-        <v>73326</v>
+        <v>73329</v>
       </c>
       <c r="H242">
-        <v>18782</v>
+        <v>18779</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92672</v>
+        <v>92684</v>
       </c>
       <c r="E246">
         <v>109608</v>
       </c>
       <c r="F246">
-        <v>107672</v>
+        <v>107684</v>
       </c>
       <c r="G246">
-        <v>155048</v>
+        <v>155065</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59765</v>
+        <v>59490</v>
       </c>
       <c r="E248">
         <v>96836</v>
       </c>
       <c r="F248">
-        <v>75149</v>
+        <v>75054</v>
       </c>
       <c r="G248">
-        <v>108215</v>
+        <v>108078</v>
       </c>
       <c r="H248">
-        <v>15384</v>
+        <v>15564</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48311</v>
+        <v>48216</v>
       </c>
       <c r="E249">
         <v>96836</v>
       </c>
       <c r="F249">
-        <v>63311</v>
+        <v>63216</v>
       </c>
       <c r="G249">
-        <v>91168</v>
+        <v>91031</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73555</v>
+        <v>73571</v>
       </c>
       <c r="E250">
         <v>109608</v>
       </c>
       <c r="F250">
-        <v>102073</v>
+        <v>102057</v>
       </c>
       <c r="G250">
-        <v>146985</v>
+        <v>146962</v>
       </c>
       <c r="H250">
-        <v>28518</v>
+        <v>28486</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>73618</v>
+        <v>73602</v>
       </c>
       <c r="E251">
         <v>109608</v>
       </c>
       <c r="F251">
-        <v>88618</v>
+        <v>88602</v>
       </c>
       <c r="G251">
-        <v>127610</v>
+        <v>127587</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38580</v>
+        <v>38557</v>
       </c>
       <c r="E253">
         <v>52986</v>
       </c>
       <c r="F253">
-        <v>53580</v>
+        <v>53557</v>
       </c>
       <c r="G253">
-        <v>77155</v>
+        <v>77122</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11558,7 +11558,7 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24289</v>
+        <v>24288</v>
       </c>
       <c r="E254">
         <v>71257</v>
@@ -11570,7 +11570,7 @@
         <v>76958</v>
       </c>
       <c r="H254">
-        <v>29154</v>
+        <v>29155</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69512</v>
+        <v>69525</v>
       </c>
       <c r="E255">
         <v>71257</v>
       </c>
       <c r="F255">
-        <v>84512</v>
+        <v>84525</v>
       </c>
       <c r="G255">
-        <v>121697</v>
+        <v>121716</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12505</v>
+        <v>12481</v>
       </c>
       <c r="E259">
         <v>51141</v>
       </c>
       <c r="F259">
-        <v>30947</v>
+        <v>30938</v>
       </c>
       <c r="G259">
-        <v>44564</v>
+        <v>44551</v>
       </c>
       <c r="H259">
-        <v>18442</v>
+        <v>18457</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12442</v>
+        <v>12481</v>
       </c>
       <c r="E261">
         <v>63930</v>
       </c>
       <c r="F261">
-        <v>35910</v>
+        <v>35925</v>
       </c>
       <c r="G261">
-        <v>51710</v>
+        <v>51732</v>
       </c>
       <c r="H261">
-        <v>23468</v>
+        <v>23444</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12505</v>
+        <v>12481</v>
       </c>
       <c r="E263">
         <v>73066</v>
       </c>
       <c r="F263">
-        <v>39498</v>
+        <v>39481</v>
       </c>
       <c r="G263">
-        <v>56877</v>
+        <v>56853</v>
       </c>
       <c r="H263">
-        <v>26993</v>
+        <v>27000</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39567</v>
+        <v>39561</v>
       </c>
       <c r="E264">
         <v>60276</v>
       </c>
       <c r="F264">
-        <v>54567</v>
+        <v>66578</v>
       </c>
       <c r="G264">
-        <v>78576</v>
+        <v>95872</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>27017</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>11517</v>
+        <v>31125</v>
       </c>
       <c r="E265">
         <v>60276</v>
       </c>
       <c r="F265">
-        <v>34114</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>49124</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>22597</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,16 +12171,16 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35994</v>
+        <v>35954</v>
       </c>
       <c r="E268">
         <v>60276</v>
       </c>
       <c r="F268">
-        <v>50994</v>
+        <v>50954</v>
       </c>
       <c r="G268">
-        <v>73431</v>
+        <v>73374</v>
       </c>
       <c r="H268">
         <v>15000</v>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>24147</v>
+        <v>23943</v>
       </c>
       <c r="E269">
         <v>60276</v>
       </c>
       <c r="F269">
-        <v>39166</v>
+        <v>39085</v>
       </c>
       <c r="G269">
-        <v>56399</v>
+        <v>56282</v>
       </c>
       <c r="H269">
-        <v>15019</v>
+        <v>15142</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>39097</v>
+        <v>39106</v>
       </c>
       <c r="E270">
         <v>67584</v>
       </c>
       <c r="F270">
-        <v>54117</v>
+        <v>54119</v>
       </c>
       <c r="G270">
-        <v>77928</v>
+        <v>77931</v>
       </c>
       <c r="H270">
-        <v>15020</v>
+        <v>15013</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29084</v>
+        <v>29086</v>
       </c>
       <c r="E271">
         <v>67584</v>
       </c>
       <c r="F271">
-        <v>44084</v>
+        <v>44086</v>
       </c>
       <c r="G271">
-        <v>63481</v>
+        <v>63484</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71110</v>
+        <v>71093</v>
       </c>
       <c r="E272">
         <v>91337</v>
       </c>
       <c r="F272">
-        <v>86174</v>
+        <v>86235</v>
       </c>
       <c r="G272">
-        <v>124091</v>
+        <v>124178</v>
       </c>
       <c r="H272">
-        <v>15064</v>
+        <v>15142</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21405</v>
+        <v>21466</v>
       </c>
       <c r="E273">
         <v>91337</v>
       </c>
       <c r="F273">
-        <v>48405</v>
+        <v>48466</v>
       </c>
       <c r="G273">
-        <v>69703</v>
+        <v>69791</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10201</v>
+        <v>10192</v>
       </c>
       <c r="E275">
         <v>127879</v>
       </c>
       <c r="F275">
-        <v>37201</v>
+        <v>37192</v>
       </c>
       <c r="G275">
-        <v>53569</v>
+        <v>53556</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152030</v>
+        <v>151845</v>
       </c>
       <c r="E276">
         <v>164421</v>
       </c>
       <c r="F276">
-        <v>167171</v>
+        <v>167179</v>
       </c>
       <c r="G276">
-        <v>240726</v>
+        <v>240738</v>
       </c>
       <c r="H276">
-        <v>15141</v>
+        <v>15334</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>38392</v>
+        <v>38400</v>
       </c>
       <c r="E277">
         <v>164421</v>
       </c>
       <c r="F277">
-        <v>65392</v>
+        <v>65400</v>
       </c>
       <c r="G277">
-        <v>94164</v>
+        <v>94176</v>
       </c>
       <c r="H277">
         <v>27000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>51915</v>
+        <v>51854</v>
       </c>
       <c r="E278">
         <v>109608</v>
       </c>
       <c r="F278">
-        <v>78569</v>
+        <v>78544</v>
       </c>
       <c r="G278">
-        <v>113139</v>
+        <v>113103</v>
       </c>
       <c r="H278">
-        <v>26654</v>
+        <v>26690</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48922</v>
+        <v>48859</v>
       </c>
       <c r="E279">
         <v>109608</v>
       </c>
       <c r="F279">
-        <v>68316</v>
+        <v>68291</v>
       </c>
       <c r="G279">
-        <v>98375</v>
+        <v>98339</v>
       </c>
       <c r="H279">
-        <v>19394</v>
+        <v>19432</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>69449</v>
+        <v>69635</v>
       </c>
       <c r="E280">
         <v>127879</v>
       </c>
       <c r="F280">
-        <v>91453</v>
+        <v>91428</v>
       </c>
       <c r="G280">
-        <v>131692</v>
+        <v>131656</v>
       </c>
       <c r="H280">
-        <v>22004</v>
+        <v>21793</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48922</v>
+        <v>48859</v>
       </c>
       <c r="E281">
         <v>127879</v>
       </c>
       <c r="F281">
-        <v>75441</v>
+        <v>75416</v>
       </c>
       <c r="G281">
-        <v>108635</v>
+        <v>108599</v>
       </c>
       <c r="H281">
-        <v>26519</v>
+        <v>26557</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24085</v>
+        <v>24084</v>
       </c>
       <c r="E282">
         <v>54795</v>
@@ -12803,7 +12803,7 @@
         <v>59178</v>
       </c>
       <c r="H282">
-        <v>17011</v>
+        <v>17012</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24633</v>
+        <v>24492</v>
       </c>
       <c r="E283">
         <v>54795</v>
       </c>
       <c r="F283">
-        <v>39633</v>
+        <v>39492</v>
       </c>
       <c r="G283">
-        <v>57072</v>
+        <v>56868</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31481</v>
+        <v>31501</v>
       </c>
       <c r="E288">
         <v>58449</v>
       </c>
       <c r="F288">
-        <v>48652</v>
+        <v>48700</v>
       </c>
       <c r="G288">
-        <v>70059</v>
+        <v>70128</v>
       </c>
       <c r="H288">
-        <v>17171</v>
+        <v>17199</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25652</v>
+        <v>25700</v>
       </c>
       <c r="E289">
         <v>58449</v>
       </c>
       <c r="F289">
-        <v>40652</v>
+        <v>40700</v>
       </c>
       <c r="G289">
-        <v>58539</v>
+        <v>58608</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34067</v>
+        <v>34073</v>
       </c>
       <c r="E291">
         <v>43832</v>
       </c>
       <c r="F291">
-        <v>49067</v>
+        <v>49073</v>
       </c>
       <c r="G291">
-        <v>70656</v>
+        <v>70665</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43155</v>
+        <v>43026</v>
       </c>
       <c r="E292">
         <v>109608</v>
       </c>
       <c r="F292">
-        <v>73507</v>
+        <v>73511</v>
       </c>
       <c r="G292">
-        <v>105850</v>
+        <v>105856</v>
       </c>
       <c r="H292">
-        <v>30352</v>
+        <v>30485</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37921</v>
+        <v>37930</v>
       </c>
       <c r="E293">
         <v>109608</v>
       </c>
       <c r="F293">
-        <v>63915</v>
+        <v>63919</v>
       </c>
       <c r="G293">
-        <v>92038</v>
+        <v>92043</v>
       </c>
       <c r="H293">
-        <v>25994</v>
+        <v>25989</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>55033</v>
+        <v>54911</v>
       </c>
       <c r="E296">
         <v>73066</v>
       </c>
       <c r="F296">
-        <v>90033</v>
+        <v>89911</v>
       </c>
       <c r="G296">
-        <v>129648</v>
+        <v>129472</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64310</v>
+        <v>64319</v>
       </c>
       <c r="E297">
         <v>73066</v>
       </c>
       <c r="F297">
-        <v>79310</v>
+        <v>79319</v>
       </c>
       <c r="G297">
-        <v>114206</v>
+        <v>114219</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4388</v>
+        <v>4390</v>
       </c>
       <c r="E299">
         <v>54795</v>
       </c>
       <c r="F299">
-        <v>29125</v>
+        <v>29126</v>
       </c>
       <c r="G299">
-        <v>41940</v>
+        <v>41941</v>
       </c>
       <c r="H299">
-        <v>24737</v>
+        <v>24736</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10718</v>
+        <v>10709</v>
       </c>
       <c r="E301">
         <v>69412</v>
       </c>
       <c r="F301">
-        <v>37358</v>
+        <v>37354</v>
       </c>
       <c r="G301">
-        <v>53796</v>
+        <v>53790</v>
       </c>
       <c r="H301">
-        <v>26640</v>
+        <v>26645</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24868</v>
+        <v>24884</v>
       </c>
       <c r="E302">
         <v>91337</v>
       </c>
       <c r="F302">
-        <v>51868</v>
+        <v>51884</v>
       </c>
       <c r="G302">
-        <v>74690</v>
+        <v>74713</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44189</v>
+        <v>44186</v>
       </c>
       <c r="E304">
         <v>109608</v>
       </c>
       <c r="F304">
-        <v>77004</v>
+        <v>77010</v>
       </c>
       <c r="G304">
-        <v>110886</v>
+        <v>110894</v>
       </c>
       <c r="H304">
-        <v>32815</v>
+        <v>32824</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45521</v>
+        <v>45535</v>
       </c>
       <c r="E305">
         <v>109608</v>
       </c>
       <c r="F305">
-        <v>66955</v>
+        <v>66961</v>
       </c>
       <c r="G305">
-        <v>96415</v>
+        <v>96424</v>
       </c>
       <c r="H305">
-        <v>21434</v>
+        <v>21426</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24241</v>
+        <v>24226</v>
       </c>
       <c r="E306">
         <v>109608</v>
       </c>
       <c r="F306">
-        <v>59241</v>
+        <v>59226</v>
       </c>
       <c r="G306">
-        <v>85307</v>
+        <v>85285</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33346</v>
+        <v>33351</v>
       </c>
       <c r="E307">
         <v>109608</v>
       </c>
       <c r="F307">
-        <v>60346</v>
+        <v>60351</v>
       </c>
       <c r="G307">
-        <v>86898</v>
+        <v>86905</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>189952</v>
+        <v>189775</v>
       </c>
       <c r="E308">
         <v>237505</v>
       </c>
       <c r="F308">
-        <v>205044</v>
+        <v>205056</v>
       </c>
       <c r="G308">
-        <v>295263</v>
+        <v>295281</v>
       </c>
       <c r="H308">
-        <v>15092</v>
+        <v>15281</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>141594</v>
+        <v>141606</v>
       </c>
       <c r="E309">
         <v>237505</v>
       </c>
       <c r="F309">
-        <v>156594</v>
+        <v>156606</v>
       </c>
       <c r="G309">
-        <v>225495</v>
+        <v>225513</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>71440</v>
+        <v>68741</v>
       </c>
       <c r="E310">
         <v>127879</v>
       </c>
       <c r="F310">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="G310">
-        <v>132778</v>
+        <v>132780</v>
       </c>
       <c r="H310">
-        <v>20767</v>
+        <v>23467</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53779</v>
+        <v>53782</v>
       </c>
       <c r="E311">
         <v>127879</v>
       </c>
       <c r="F311">
-        <v>77384</v>
+        <v>77385</v>
       </c>
       <c r="G311">
-        <v>111433</v>
+        <v>111434</v>
       </c>
       <c r="H311">
-        <v>23605</v>
+        <v>23603</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110505</v>
+        <v>110528</v>
       </c>
       <c r="E313">
         <v>182692</v>
       </c>
       <c r="F313">
-        <v>125505</v>
+        <v>125528</v>
       </c>
       <c r="G313">
-        <v>180727</v>
+        <v>180760</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>139040</v>
+        <v>130097</v>
       </c>
       <c r="E314">
         <v>237505</v>
       </c>
       <c r="F314">
-        <v>174040</v>
+        <v>165097</v>
       </c>
       <c r="G314">
-        <v>250618</v>
+        <v>237740</v>
       </c>
       <c r="H314">
         <v>35000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71440</v>
+        <v>71120</v>
       </c>
       <c r="E2">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F2">
-        <v>86472</v>
+        <v>86359</v>
       </c>
       <c r="G2">
-        <v>124520</v>
+        <v>124357</v>
       </c>
       <c r="H2">
-        <v>15032</v>
+        <v>15239</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46211</v>
+        <v>46098</v>
       </c>
       <c r="E3">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F3">
-        <v>61211</v>
+        <v>61098</v>
       </c>
       <c r="G3">
-        <v>88144</v>
+        <v>87981</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>84028</v>
+        <v>83194</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -617,16 +617,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>46334</v>
+        <v>46098</v>
       </c>
       <c r="E5">
-        <v>84028</v>
+        <v>83194</v>
       </c>
       <c r="F5">
-        <v>61334</v>
+        <v>61098</v>
       </c>
       <c r="G5">
-        <v>88321</v>
+        <v>87981</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4249</v>
+        <v>4243</v>
       </c>
       <c r="E7">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F7">
-        <v>29070</v>
+        <v>28855</v>
       </c>
       <c r="G7">
-        <v>41861</v>
+        <v>41551</v>
       </c>
       <c r="H7">
-        <v>24821</v>
+        <v>24612</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33979</v>
+        <v>33805</v>
       </c>
       <c r="E8">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F8">
-        <v>54400</v>
+        <v>53919</v>
       </c>
       <c r="G8">
-        <v>78336</v>
+        <v>77643</v>
       </c>
       <c r="H8">
-        <v>20421</v>
+        <v>20114</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>29761</v>
+        <v>29266</v>
       </c>
       <c r="E9">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F9">
-        <v>46400</v>
+        <v>45919</v>
       </c>
       <c r="G9">
-        <v>66816</v>
+        <v>66123</v>
       </c>
       <c r="H9">
-        <v>16639</v>
+        <v>16653</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41160</v>
+        <v>40950</v>
       </c>
       <c r="E11">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F11">
-        <v>65211</v>
+        <v>64702</v>
       </c>
       <c r="G11">
-        <v>93904</v>
+        <v>93171</v>
       </c>
       <c r="H11">
-        <v>24051</v>
+        <v>23752</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>75405</v>
+        <v>75020</v>
       </c>
       <c r="E12">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F12">
-        <v>92046</v>
+        <v>91987</v>
       </c>
       <c r="G12">
-        <v>132546</v>
+        <v>132461</v>
       </c>
       <c r="H12">
-        <v>16641</v>
+        <v>16967</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11697</v>
+        <v>11638</v>
       </c>
       <c r="E13">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F13">
-        <v>38697</v>
+        <v>38638</v>
       </c>
       <c r="G13">
-        <v>55724</v>
+        <v>55639</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>8953</v>
+        <v>20233</v>
       </c>
       <c r="E15">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F15">
-        <v>35953</v>
+        <v>42306</v>
       </c>
       <c r="G15">
-        <v>51772</v>
+        <v>60921</v>
       </c>
       <c r="H15">
-        <v>27000</v>
+        <v>22073</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>33022</v>
+        <v>32869</v>
       </c>
       <c r="E21">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F21">
-        <v>59105</v>
+        <v>58648</v>
       </c>
       <c r="G21">
-        <v>85111</v>
+        <v>84453</v>
       </c>
       <c r="H21">
-        <v>26083</v>
+        <v>25779</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52826</v>
+        <v>52556</v>
       </c>
       <c r="E23">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F23">
-        <v>78428</v>
+        <v>77811</v>
       </c>
       <c r="G23">
-        <v>112936</v>
+        <v>112048</v>
       </c>
       <c r="H23">
-        <v>25602</v>
+        <v>25255</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>160767</v>
+        <v>159170</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>160767</v>
+        <v>159170</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>19459</v>
+        <v>18065</v>
       </c>
       <c r="E27">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F27">
-        <v>38717</v>
+        <v>37911</v>
       </c>
       <c r="G27">
-        <v>55752</v>
+        <v>54592</v>
       </c>
       <c r="H27">
-        <v>19258</v>
+        <v>19846</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74308</v>
+        <v>74849</v>
       </c>
       <c r="E28">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F28">
-        <v>93290</v>
+        <v>93162</v>
       </c>
       <c r="G28">
-        <v>134338</v>
+        <v>134153</v>
       </c>
       <c r="H28">
-        <v>18982</v>
+        <v>18313</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25135</v>
+        <v>25007</v>
       </c>
       <c r="E29">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F29">
-        <v>52135</v>
+        <v>52007</v>
       </c>
       <c r="G29">
-        <v>75074</v>
+        <v>74890</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130661</v>
+        <v>129995</v>
       </c>
       <c r="E30">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F30">
-        <v>146477</v>
+        <v>146183</v>
       </c>
       <c r="G30">
-        <v>210927</v>
+        <v>210504</v>
       </c>
       <c r="H30">
-        <v>15816</v>
+        <v>16188</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57499</v>
+        <v>57205</v>
       </c>
       <c r="E31">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F31">
-        <v>84499</v>
+        <v>84205</v>
       </c>
       <c r="G31">
-        <v>121679</v>
+        <v>121255</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71485</v>
+        <v>71120</v>
       </c>
       <c r="E32">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F32">
-        <v>86548</v>
+        <v>86120</v>
       </c>
       <c r="G32">
-        <v>124629</v>
+        <v>124013</v>
       </c>
       <c r="H32">
-        <v>15063</v>
+        <v>15000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>41238</v>
+        <v>41028</v>
       </c>
       <c r="E33">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F33">
-        <v>65242</v>
+        <v>64733</v>
       </c>
       <c r="G33">
-        <v>93948</v>
+        <v>93216</v>
       </c>
       <c r="H33">
-        <v>24004</v>
+        <v>23705</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>57671</v>
+        <v>63118</v>
       </c>
       <c r="E35">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F35">
-        <v>78941</v>
+        <v>80624</v>
       </c>
       <c r="G35">
-        <v>113675</v>
+        <v>116099</v>
       </c>
       <c r="H35">
-        <v>21270</v>
+        <v>17506</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44672</v>
+        <v>44444</v>
       </c>
       <c r="E36">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F36">
-        <v>72673</v>
+        <v>72491</v>
       </c>
       <c r="G36">
-        <v>104649</v>
+        <v>104387</v>
       </c>
       <c r="H36">
-        <v>28001</v>
+        <v>28047</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,16 +2025,16 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35594</v>
+        <v>35412</v>
       </c>
       <c r="E37">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F37">
-        <v>62594</v>
+        <v>62412</v>
       </c>
       <c r="G37">
-        <v>90135</v>
+        <v>89873</v>
       </c>
       <c r="H37">
         <v>27000</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>83054</v>
       </c>
       <c r="E39">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>110054</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>158478</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>83054</v>
       </c>
       <c r="E41">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>110054</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>158478</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>39028</v>
+        <v>38875</v>
       </c>
       <c r="E43">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F43">
-        <v>66028</v>
+        <v>65875</v>
       </c>
       <c r="G43">
-        <v>95080</v>
+        <v>94860</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92873</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F45">
-        <v>114399</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>164735</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>21526</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>26734</v>
+        <v>25771</v>
       </c>
       <c r="E47">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F47">
-        <v>53734</v>
+        <v>52771</v>
       </c>
       <c r="G47">
-        <v>77377</v>
+        <v>75990</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35735</v>
+        <v>35552</v>
       </c>
       <c r="E50">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F50">
-        <v>56242</v>
+        <v>56103</v>
       </c>
       <c r="G50">
-        <v>80988</v>
+        <v>80788</v>
       </c>
       <c r="H50">
-        <v>20507</v>
+        <v>20551</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33242</v>
+        <v>33103</v>
       </c>
       <c r="E51">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F51">
-        <v>48242</v>
+        <v>48103</v>
       </c>
       <c r="G51">
-        <v>69468</v>
+        <v>69268</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>76720</v>
+        <v>75958</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2723,16 +2723,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>35625</v>
+        <v>35443</v>
       </c>
       <c r="E53">
-        <v>76720</v>
+        <v>75958</v>
       </c>
       <c r="F53">
-        <v>50625</v>
+        <v>50443</v>
       </c>
       <c r="G53">
-        <v>72900</v>
+        <v>72638</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48279</v>
+        <v>48032</v>
       </c>
       <c r="E54">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F54">
-        <v>83279</v>
+        <v>83032</v>
       </c>
       <c r="G54">
-        <v>119922</v>
+        <v>119566</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52026</v>
+        <v>51761</v>
       </c>
       <c r="E55">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F55">
-        <v>76683</v>
+        <v>76081</v>
       </c>
       <c r="G55">
-        <v>110424</v>
+        <v>109557</v>
       </c>
       <c r="H55">
-        <v>24657</v>
+        <v>24320</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62563</v>
+        <v>62244</v>
       </c>
       <c r="E57">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F57">
-        <v>88024</v>
+        <v>87330</v>
       </c>
       <c r="G57">
-        <v>126755</v>
+        <v>125755</v>
       </c>
       <c r="H57">
-        <v>25461</v>
+        <v>25086</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2950,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>36524</v>
+        <v>36161</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6209</v>
+        <v>6178</v>
       </c>
       <c r="E59">
-        <v>36524</v>
+        <v>36161</v>
       </c>
       <c r="F59">
-        <v>22728</v>
+        <v>22574</v>
       </c>
       <c r="G59">
-        <v>32728</v>
+        <v>32507</v>
       </c>
       <c r="H59">
-        <v>16519</v>
+        <v>16396</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26154</v>
+        <v>26021</v>
       </c>
       <c r="E60">
-        <v>49313</v>
+        <v>48824</v>
       </c>
       <c r="F60">
-        <v>47931</v>
+        <v>47804</v>
       </c>
       <c r="G60">
-        <v>69021</v>
+        <v>68838</v>
       </c>
       <c r="H60">
-        <v>21777</v>
+        <v>21783</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24931</v>
+        <v>24804</v>
       </c>
       <c r="E61">
-        <v>49313</v>
+        <v>48824</v>
       </c>
       <c r="F61">
-        <v>39931</v>
+        <v>39804</v>
       </c>
       <c r="G61">
-        <v>57501</v>
+        <v>57318</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12826</v>
+        <v>12776</v>
       </c>
       <c r="E63">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F63">
-        <v>39826</v>
+        <v>39776</v>
       </c>
       <c r="G63">
-        <v>57349</v>
+        <v>57277</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>123293</v>
+        <v>122068</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28977</v>
+        <v>28657</v>
       </c>
       <c r="E65">
-        <v>123293</v>
+        <v>122068</v>
       </c>
       <c r="F65">
-        <v>55977</v>
+        <v>55657</v>
       </c>
       <c r="G65">
-        <v>80607</v>
+        <v>80146</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24712</v>
+        <v>24554</v>
       </c>
       <c r="E66">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F66">
-        <v>52279</v>
+        <v>53486</v>
       </c>
       <c r="G66">
-        <v>75282</v>
+        <v>77020</v>
       </c>
       <c r="H66">
-        <v>27567</v>
+        <v>28932</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>17279</v>
+        <v>18486</v>
       </c>
       <c r="E67">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F67">
-        <v>44279</v>
+        <v>45486</v>
       </c>
       <c r="G67">
-        <v>63762</v>
+        <v>65500</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34339</v>
+        <v>34226</v>
       </c>
       <c r="E68">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F68">
-        <v>62722</v>
+        <v>62582</v>
       </c>
       <c r="G68">
-        <v>90320</v>
+        <v>90118</v>
       </c>
       <c r="H68">
-        <v>28383</v>
+        <v>28356</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27534</v>
+        <v>27394</v>
       </c>
       <c r="E69">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F69">
-        <v>54534</v>
+        <v>54394</v>
       </c>
       <c r="G69">
-        <v>78529</v>
+        <v>78327</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45143</v>
+        <v>44912</v>
       </c>
       <c r="E70">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F70">
-        <v>80143</v>
+        <v>79912</v>
       </c>
       <c r="G70">
-        <v>115406</v>
+        <v>115073</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50709</v>
+        <v>50450</v>
       </c>
       <c r="E71">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F71">
-        <v>76156</v>
+        <v>75557</v>
       </c>
       <c r="G71">
-        <v>109665</v>
+        <v>108802</v>
       </c>
       <c r="H71">
-        <v>25447</v>
+        <v>25107</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5519</v>
+        <v>5491</v>
       </c>
       <c r="E73">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F73">
-        <v>20519</v>
+        <v>20491</v>
       </c>
       <c r="G73">
-        <v>29547</v>
+        <v>29507</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>95904</v>
+        <v>94952</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70403</v>
+        <v>70044</v>
       </c>
       <c r="E75">
-        <v>95904</v>
+        <v>94952</v>
       </c>
       <c r="F75">
-        <v>85403</v>
+        <v>85044</v>
       </c>
       <c r="G75">
-        <v>122980</v>
+        <v>122463</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80564</v>
+        <v>80153</v>
       </c>
       <c r="E76">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F76">
-        <v>95771</v>
+        <v>95153</v>
       </c>
       <c r="G76">
-        <v>137910</v>
+        <v>137020</v>
       </c>
       <c r="H76">
-        <v>15207</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>48373</v>
+        <v>47284</v>
       </c>
       <c r="E77">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F77">
-        <v>75222</v>
+        <v>74284</v>
       </c>
       <c r="G77">
-        <v>108320</v>
+        <v>106969</v>
       </c>
       <c r="H77">
-        <v>26849</v>
+        <v>27000</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36911</v>
+        <v>36785</v>
       </c>
       <c r="E81">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F81">
-        <v>56386</v>
+        <v>55981</v>
       </c>
       <c r="G81">
-        <v>81196</v>
+        <v>80613</v>
       </c>
       <c r="H81">
-        <v>19475</v>
+        <v>19196</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84358</v>
+        <v>83928</v>
       </c>
       <c r="E83">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F83">
-        <v>99358</v>
+        <v>98928</v>
       </c>
       <c r="G83">
-        <v>143076</v>
+        <v>142456</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47934</v>
+        <v>47596</v>
       </c>
       <c r="E84">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F84">
-        <v>71235</v>
+        <v>70699</v>
       </c>
       <c r="G84">
-        <v>102578</v>
+        <v>101807</v>
       </c>
       <c r="H84">
-        <v>23301</v>
+        <v>23103</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32269</v>
+        <v>31918</v>
       </c>
       <c r="E85">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F85">
-        <v>58804</v>
+        <v>58268</v>
       </c>
       <c r="G85">
-        <v>84678</v>
+        <v>83906</v>
       </c>
       <c r="H85">
-        <v>26535</v>
+        <v>26350</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4174,16 +4174,16 @@
         <v>149887</v>
       </c>
       <c r="E86">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F86">
-        <v>164896</v>
+        <v>164887</v>
       </c>
       <c r="G86">
-        <v>237450</v>
+        <v>237437</v>
       </c>
       <c r="H86">
-        <v>15009</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113758</v>
+        <v>113178</v>
       </c>
       <c r="E87">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F87">
-        <v>128758</v>
+        <v>128178</v>
       </c>
       <c r="G87">
-        <v>185412</v>
+        <v>184576</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>81285</v>
+        <v>158714</v>
       </c>
       <c r="E88">
-        <v>160767</v>
+        <v>159170</v>
       </c>
       <c r="F88">
-        <v>116285</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>167450</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>126271</v>
+        <v>125814</v>
       </c>
       <c r="E89">
-        <v>160767</v>
+        <v>159170</v>
       </c>
       <c r="F89">
-        <v>141271</v>
+        <v>140814</v>
       </c>
       <c r="G89">
-        <v>203430</v>
+        <v>202772</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4349,16 +4349,16 @@
         <v>7680</v>
       </c>
       <c r="E90">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F90">
-        <v>38495</v>
+        <v>38260</v>
       </c>
       <c r="G90">
-        <v>55433</v>
+        <v>55094</v>
       </c>
       <c r="H90">
-        <v>30815</v>
+        <v>30580</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4249</v>
+        <v>4228</v>
       </c>
       <c r="E91">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F91">
-        <v>30495</v>
+        <v>30260</v>
       </c>
       <c r="G91">
-        <v>43913</v>
+        <v>43574</v>
       </c>
       <c r="H91">
-        <v>26246</v>
+        <v>26032</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12121</v>
+        <v>12074</v>
       </c>
       <c r="E93">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F93">
-        <v>27121</v>
+        <v>27074</v>
       </c>
       <c r="G93">
-        <v>39054</v>
+        <v>38987</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>34697</v>
+        <v>34352</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>34697</v>
+        <v>34352</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61513</v>
+        <v>61168</v>
       </c>
       <c r="E96">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F96">
-        <v>76701</v>
+        <v>76298</v>
       </c>
       <c r="G96">
-        <v>110449</v>
+        <v>109869</v>
       </c>
       <c r="H96">
-        <v>15188</v>
+        <v>15130</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33487</v>
+        <v>33275</v>
       </c>
       <c r="E97">
-        <v>82201</v>
+        <v>81385</v>
       </c>
       <c r="F97">
-        <v>51453</v>
+        <v>51050</v>
       </c>
       <c r="G97">
-        <v>74092</v>
+        <v>73512</v>
       </c>
       <c r="H97">
-        <v>17966</v>
+        <v>17775</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>74621</v>
+        <v>74240</v>
       </c>
       <c r="E98">
-        <v>94991</v>
+        <v>94047</v>
       </c>
       <c r="F98">
-        <v>90953</v>
+        <v>89256</v>
       </c>
       <c r="G98">
-        <v>130972</v>
+        <v>128529</v>
       </c>
       <c r="H98">
-        <v>16332</v>
+        <v>15016</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>36644</v>
+        <v>33322</v>
       </c>
       <c r="E99">
-        <v>94991</v>
+        <v>94047</v>
       </c>
       <c r="F99">
-        <v>57704</v>
+        <v>56007</v>
       </c>
       <c r="G99">
-        <v>83094</v>
+        <v>80650</v>
       </c>
       <c r="H99">
-        <v>21060</v>
+        <v>22685</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61215</v>
+        <v>60902</v>
       </c>
       <c r="E100">
-        <v>106502</v>
+        <v>105444</v>
       </c>
       <c r="F100">
-        <v>79877</v>
+        <v>79083</v>
       </c>
       <c r="G100">
-        <v>115023</v>
+        <v>113880</v>
       </c>
       <c r="H100">
-        <v>18662</v>
+        <v>18181</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61356</v>
+        <v>61043</v>
       </c>
       <c r="E101">
-        <v>106502</v>
+        <v>105444</v>
       </c>
       <c r="F101">
-        <v>76356</v>
+        <v>76043</v>
       </c>
       <c r="G101">
-        <v>109953</v>
+        <v>109502</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>137014</v>
+        <v>135653</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>137014</v>
+        <v>135653</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68788</v>
+        <v>68437</v>
       </c>
       <c r="E105">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F105">
-        <v>83788</v>
+        <v>83437</v>
       </c>
       <c r="G105">
-        <v>120655</v>
+        <v>120149</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>100477</v>
+        <v>99965</v>
       </c>
       <c r="E107">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F107">
-        <v>117441</v>
+        <v>116528</v>
       </c>
       <c r="G107">
-        <v>169115</v>
+        <v>167800</v>
       </c>
       <c r="H107">
-        <v>16964</v>
+        <v>16563</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4092</v>
+        <v>4087</v>
       </c>
       <c r="E109">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F109">
-        <v>31092</v>
+        <v>31087</v>
       </c>
       <c r="G109">
-        <v>44772</v>
+        <v>44765</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>164421</v>
+        <v>162787</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13344</v>
+        <v>13276</v>
       </c>
       <c r="E111">
-        <v>164421</v>
+        <v>162787</v>
       </c>
       <c r="F111">
-        <v>40344</v>
+        <v>40276</v>
       </c>
       <c r="G111">
-        <v>58095</v>
+        <v>57997</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5310,7 +5310,7 @@
         <v>81703</v>
       </c>
       <c r="E112">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F112">
         <v>96703</v>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48561</v>
+        <v>48313</v>
       </c>
       <c r="E113">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F113">
-        <v>63561</v>
+        <v>63313</v>
       </c>
       <c r="G113">
-        <v>91528</v>
+        <v>91171</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>116916</v>
+        <v>115755</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85017</v>
+        <v>84583</v>
       </c>
       <c r="E115">
-        <v>116916</v>
+        <v>115755</v>
       </c>
       <c r="F115">
-        <v>100017</v>
+        <v>99583</v>
       </c>
       <c r="G115">
-        <v>144024</v>
+        <v>143400</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -5526,16 +5526,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>114668</v>
+        <v>111758</v>
       </c>
       <c r="E117">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F117">
-        <v>129668</v>
+        <v>126758</v>
       </c>
       <c r="G117">
-        <v>186722</v>
+        <v>182532</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5569,10 +5569,10 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43349</v>
+        <v>43321</v>
       </c>
       <c r="E118">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F118">
         <v>58349</v>
@@ -5581,7 +5581,7 @@
         <v>84023</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>15028</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5617,7 +5617,7 @@
         <v>31689</v>
       </c>
       <c r="E119">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F119">
         <v>46689</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60713</v>
+        <v>60528</v>
       </c>
       <c r="E120">
-        <v>80374</v>
+        <v>79576</v>
       </c>
       <c r="F120">
-        <v>79079</v>
+        <v>78805</v>
       </c>
       <c r="G120">
-        <v>113874</v>
+        <v>113479</v>
       </c>
       <c r="H120">
-        <v>18366</v>
+        <v>18277</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53751</v>
+        <v>53477</v>
       </c>
       <c r="E121">
-        <v>80374</v>
+        <v>79576</v>
       </c>
       <c r="F121">
-        <v>68751</v>
+        <v>68477</v>
       </c>
       <c r="G121">
-        <v>99001</v>
+        <v>98607</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>46538</v>
+        <v>53056</v>
       </c>
       <c r="E122">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F122">
-        <v>68339</v>
+        <v>69713</v>
       </c>
       <c r="G122">
-        <v>98408</v>
+        <v>100387</v>
       </c>
       <c r="H122">
-        <v>21801</v>
+        <v>16657</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>27707</v>
+        <v>32027</v>
       </c>
       <c r="E123">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F123">
-        <v>52704</v>
+        <v>54078</v>
       </c>
       <c r="G123">
-        <v>75894</v>
+        <v>77872</v>
       </c>
       <c r="H123">
-        <v>24997</v>
+        <v>22051</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5836,16 +5836,16 @@
         <v>13846</v>
       </c>
       <c r="E124">
-        <v>43832</v>
+        <v>43397</v>
       </c>
       <c r="F124">
-        <v>32874</v>
+        <v>32548</v>
       </c>
       <c r="G124">
-        <v>47339</v>
+        <v>46869</v>
       </c>
       <c r="H124">
-        <v>19028</v>
+        <v>18702</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7338</v>
+        <v>7301</v>
       </c>
       <c r="E125">
-        <v>43832</v>
+        <v>43397</v>
       </c>
       <c r="F125">
-        <v>26030</v>
+        <v>25845</v>
       </c>
       <c r="G125">
-        <v>37483</v>
+        <v>37217</v>
       </c>
       <c r="H125">
-        <v>18692</v>
+        <v>18544</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5926,7 +5926,7 @@
         <v>29642</v>
       </c>
       <c r="E126">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F126">
         <v>44642</v>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>59892</v>
+        <v>59297</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20117</v>
+        <v>20046</v>
       </c>
       <c r="E129">
-        <v>59892</v>
+        <v>59297</v>
       </c>
       <c r="F129">
-        <v>37405</v>
+        <v>37144</v>
       </c>
       <c r="G129">
-        <v>53863</v>
+        <v>53487</v>
       </c>
       <c r="H129">
-        <v>17288</v>
+        <v>17098</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>74619</v>
+        <v>73878</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20117</v>
+        <v>20046</v>
       </c>
       <c r="E131">
-        <v>74619</v>
+        <v>73878</v>
       </c>
       <c r="F131">
-        <v>43148</v>
+        <v>42831</v>
       </c>
       <c r="G131">
-        <v>62133</v>
+        <v>61677</v>
       </c>
       <c r="H131">
-        <v>23031</v>
+        <v>22785</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>93931</v>
+        <v>92998</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33210</v>
+        <v>33041</v>
       </c>
       <c r="E133">
-        <v>93931</v>
+        <v>92998</v>
       </c>
       <c r="F133">
-        <v>55917</v>
+        <v>55486</v>
       </c>
       <c r="G133">
-        <v>80520</v>
+        <v>79900</v>
       </c>
       <c r="H133">
-        <v>22707</v>
+        <v>22445</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>89510</v>
+        <v>88620</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53187</v>
+        <v>52915</v>
       </c>
       <c r="E135">
-        <v>89510</v>
+        <v>88620</v>
       </c>
       <c r="F135">
-        <v>68187</v>
+        <v>67915</v>
       </c>
       <c r="G135">
-        <v>98189</v>
+        <v>97798</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>73053</v>
+        <v>72680</v>
       </c>
       <c r="E137">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F137">
-        <v>88053</v>
+        <v>87680</v>
       </c>
       <c r="G137">
-        <v>126796</v>
+        <v>126259</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>153458</v>
+        <v>151934</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6486,16 +6486,16 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91164</v>
+        <v>90698</v>
       </c>
       <c r="E139">
-        <v>153458</v>
+        <v>151934</v>
       </c>
       <c r="F139">
-        <v>106164</v>
+        <v>105698</v>
       </c>
       <c r="G139">
-        <v>152876</v>
+        <v>152205</v>
       </c>
       <c r="H139">
         <v>15000</v>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37287</v>
+        <v>37144</v>
       </c>
       <c r="E140">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F140">
-        <v>62017</v>
+        <v>61551</v>
       </c>
       <c r="G140">
-        <v>89304</v>
+        <v>88633</v>
       </c>
       <c r="H140">
-        <v>24730</v>
+        <v>24407</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26687</v>
+        <v>26551</v>
       </c>
       <c r="E142">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F142">
-        <v>60541</v>
+        <v>60131</v>
       </c>
       <c r="G142">
-        <v>87179</v>
+        <v>86589</v>
       </c>
       <c r="H142">
-        <v>33854</v>
+        <v>33580</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27299</v>
+        <v>27160</v>
       </c>
       <c r="E143">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F143">
-        <v>52541</v>
+        <v>52131</v>
       </c>
       <c r="G143">
-        <v>75659</v>
+        <v>75069</v>
       </c>
       <c r="H143">
-        <v>25242</v>
+        <v>24971</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>42853</v>
+        <v>45817</v>
       </c>
       <c r="E144">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F144">
-        <v>68503</v>
+        <v>67822</v>
       </c>
       <c r="G144">
-        <v>98644</v>
+        <v>97664</v>
       </c>
       <c r="H144">
-        <v>25650</v>
+        <v>22005</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>79513</v>
+        <v>79108</v>
       </c>
       <c r="E145">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F145">
-        <v>94513</v>
+        <v>94108</v>
       </c>
       <c r="G145">
-        <v>136099</v>
+        <v>135516</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58251</v>
+        <v>57954</v>
       </c>
       <c r="E146">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F146">
-        <v>93251</v>
+        <v>92954</v>
       </c>
       <c r="G146">
-        <v>134281</v>
+        <v>133854</v>
       </c>
       <c r="H146">
         <v>35000</v>
@@ -6840,16 +6840,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>94096</v>
+        <v>93616</v>
       </c>
       <c r="E147">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F147">
-        <v>109096</v>
+        <v>108616</v>
       </c>
       <c r="G147">
-        <v>157098</v>
+        <v>156407</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36628</v>
+        <v>36504</v>
       </c>
       <c r="E148">
-        <v>62103</v>
+        <v>61486</v>
       </c>
       <c r="F148">
-        <v>64119</v>
+        <v>63911</v>
       </c>
       <c r="G148">
-        <v>92331</v>
+        <v>92032</v>
       </c>
       <c r="H148">
-        <v>27491</v>
+        <v>27407</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>40737</v>
+        <v>40529</v>
       </c>
       <c r="E149">
-        <v>62103</v>
+        <v>61486</v>
       </c>
       <c r="F149">
-        <v>55737</v>
+        <v>55529</v>
       </c>
       <c r="G149">
-        <v>80261</v>
+        <v>79962</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>82201</v>
+        <v>54250</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15602</v>
+        <v>15522</v>
       </c>
       <c r="E151">
-        <v>82201</v>
+        <v>54250</v>
       </c>
       <c r="F151">
-        <v>42602</v>
+        <v>33367</v>
       </c>
       <c r="G151">
-        <v>61347</v>
+        <v>48048</v>
       </c>
       <c r="H151">
-        <v>27000</v>
+        <v>17845</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37538</v>
+        <v>37362</v>
       </c>
       <c r="E152">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F152">
-        <v>54800</v>
+        <v>54255</v>
       </c>
       <c r="G152">
-        <v>78912</v>
+        <v>78127</v>
       </c>
       <c r="H152">
-        <v>17262</v>
+        <v>16893</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33445</v>
+        <v>33275</v>
       </c>
       <c r="E153">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F153">
-        <v>48445</v>
+        <v>48275</v>
       </c>
       <c r="G153">
-        <v>69761</v>
+        <v>69516</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56762</v>
+        <v>56472</v>
       </c>
       <c r="E154">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F154">
-        <v>84131</v>
+        <v>83819</v>
       </c>
       <c r="G154">
-        <v>121149</v>
+        <v>120699</v>
       </c>
       <c r="H154">
-        <v>27369</v>
+        <v>27347</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>58157</v>
+        <v>57845</v>
       </c>
       <c r="E155">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F155">
-        <v>73157</v>
+        <v>72845</v>
       </c>
       <c r="G155">
-        <v>105346</v>
+        <v>104897</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11948</v>
+        <v>11903</v>
       </c>
       <c r="E157">
-        <v>27388</v>
+        <v>27116</v>
       </c>
       <c r="F157">
-        <v>26948</v>
+        <v>26903</v>
       </c>
       <c r="G157">
-        <v>38805</v>
+        <v>38740</v>
       </c>
       <c r="H157">
         <v>15000</v>
@@ -7324,16 +7324,16 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>85080</v>
+        <v>84646</v>
       </c>
       <c r="E158">
-        <v>84028</v>
+        <v>83194</v>
       </c>
       <c r="F158">
-        <v>100080</v>
+        <v>99646</v>
       </c>
       <c r="G158">
-        <v>144115</v>
+        <v>143490</v>
       </c>
       <c r="H158">
         <v>15000</v>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>25668</v>
+        <v>5600</v>
       </c>
       <c r="E159">
-        <v>84028</v>
+        <v>83194</v>
       </c>
       <c r="F159">
-        <v>49038</v>
+        <v>32600</v>
       </c>
       <c r="G159">
-        <v>70615</v>
+        <v>46944</v>
       </c>
       <c r="H159">
-        <v>23370</v>
+        <v>27000</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7414,16 +7414,16 @@
         <v>7680</v>
       </c>
       <c r="E160">
-        <v>54813</v>
+        <v>54269</v>
       </c>
       <c r="F160">
-        <v>38801</v>
+        <v>38572</v>
       </c>
       <c r="G160">
-        <v>55873</v>
+        <v>55544</v>
       </c>
       <c r="H160">
-        <v>31121</v>
+        <v>30892</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8561</v>
+        <v>8518</v>
       </c>
       <c r="E161">
-        <v>54813</v>
+        <v>54269</v>
       </c>
       <c r="F161">
-        <v>30801</v>
+        <v>30572</v>
       </c>
       <c r="G161">
-        <v>44353</v>
+        <v>44024</v>
       </c>
       <c r="H161">
-        <v>22240</v>
+        <v>22054</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7504,16 +7504,16 @@
         <v>10147</v>
       </c>
       <c r="E162">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F162">
-        <v>44079</v>
+        <v>44048</v>
       </c>
       <c r="G162">
-        <v>63474</v>
+        <v>63429</v>
       </c>
       <c r="H162">
-        <v>33932</v>
+        <v>33901</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9079</v>
+        <v>9048</v>
       </c>
       <c r="E163">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F163">
-        <v>36079</v>
+        <v>36048</v>
       </c>
       <c r="G163">
-        <v>51954</v>
+        <v>51909</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>67252</v>
+        <v>66908</v>
       </c>
       <c r="E164">
-        <v>68516</v>
+        <v>67836</v>
       </c>
       <c r="F164">
-        <v>82308</v>
+        <v>82013</v>
       </c>
       <c r="G164">
-        <v>118524</v>
+        <v>118099</v>
       </c>
       <c r="H164">
-        <v>15056</v>
+        <v>15105</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20745</v>
+        <v>20670</v>
       </c>
       <c r="E165">
-        <v>68516</v>
+        <v>67836</v>
       </c>
       <c r="F165">
-        <v>41019</v>
+        <v>40724</v>
       </c>
       <c r="G165">
-        <v>59067</v>
+        <v>58643</v>
       </c>
       <c r="H165">
-        <v>20274</v>
+        <v>20054</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>90301</v>
+        <v>89840</v>
       </c>
       <c r="E166">
-        <v>103231</v>
+        <v>102206</v>
       </c>
       <c r="F166">
-        <v>105356</v>
+        <v>105245</v>
       </c>
       <c r="G166">
-        <v>151713</v>
+        <v>151553</v>
       </c>
       <c r="H166">
-        <v>15055</v>
+        <v>15405</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21842</v>
+        <v>21731</v>
       </c>
       <c r="E167">
-        <v>103231</v>
+        <v>102206</v>
       </c>
       <c r="F167">
-        <v>48842</v>
+        <v>48731</v>
       </c>
       <c r="G167">
-        <v>70332</v>
+        <v>70173</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7769,16 +7769,16 @@
         <v>88821</v>
       </c>
       <c r="E168">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F168">
-        <v>103857</v>
+        <v>103821</v>
       </c>
       <c r="G168">
-        <v>149554</v>
+        <v>149502</v>
       </c>
       <c r="H168">
-        <v>15036</v>
+        <v>15000</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8859</v>
+        <v>8814</v>
       </c>
       <c r="E169">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F169">
-        <v>35859</v>
+        <v>35814</v>
       </c>
       <c r="G169">
-        <v>51637</v>
+        <v>51572</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58784</v>
+        <v>58484</v>
       </c>
       <c r="E170">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F170">
-        <v>81223</v>
+        <v>80724</v>
       </c>
       <c r="G170">
-        <v>116961</v>
+        <v>116243</v>
       </c>
       <c r="H170">
-        <v>22439</v>
+        <v>22240</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>54692</v>
+        <v>54506</v>
       </c>
       <c r="E171">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F171">
-        <v>70624</v>
+        <v>70125</v>
       </c>
       <c r="G171">
-        <v>101699</v>
+        <v>100980</v>
       </c>
       <c r="H171">
-        <v>15932</v>
+        <v>15619</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77757</v>
+        <v>77360</v>
       </c>
       <c r="E172">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F172">
-        <v>108557</v>
+        <v>107831</v>
       </c>
       <c r="G172">
-        <v>156322</v>
+        <v>155277</v>
       </c>
       <c r="H172">
-        <v>30800</v>
+        <v>30471</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78478</v>
+        <v>78078</v>
       </c>
       <c r="E173">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F173">
-        <v>94390</v>
+        <v>93664</v>
       </c>
       <c r="G173">
-        <v>135922</v>
+        <v>134876</v>
       </c>
       <c r="H173">
-        <v>15912</v>
+        <v>15586</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8036,16 +8036,16 @@
         <v>48655</v>
       </c>
       <c r="E174">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F174">
-        <v>68503</v>
+        <v>67822</v>
       </c>
       <c r="G174">
-        <v>98644</v>
+        <v>97664</v>
       </c>
       <c r="H174">
-        <v>19848</v>
+        <v>19167</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>64037</v>
+        <v>63710</v>
       </c>
       <c r="E175">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F175">
-        <v>79037</v>
+        <v>78710</v>
       </c>
       <c r="G175">
-        <v>113813</v>
+        <v>113342</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65229</v>
+        <v>64896</v>
       </c>
       <c r="E176">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F176">
-        <v>80229</v>
+        <v>79896</v>
       </c>
       <c r="G176">
-        <v>115530</v>
+        <v>115050</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26609</v>
+        <v>26177</v>
       </c>
       <c r="E178">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F178">
-        <v>53609</v>
+        <v>53177</v>
       </c>
       <c r="G178">
-        <v>77197</v>
+        <v>76575</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25135</v>
+        <v>25038</v>
       </c>
       <c r="E180">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F180">
-        <v>52135</v>
+        <v>52038</v>
       </c>
       <c r="G180">
-        <v>75074</v>
+        <v>74935</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8347,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100336</v>
+        <v>99824</v>
       </c>
       <c r="E182">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F182">
-        <v>115419</v>
+        <v>114824</v>
       </c>
       <c r="G182">
-        <v>166203</v>
+        <v>165347</v>
       </c>
       <c r="H182">
-        <v>15083</v>
+        <v>15000</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64116</v>
+        <v>63804</v>
       </c>
       <c r="E183">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F183">
-        <v>81519</v>
+        <v>80899</v>
       </c>
       <c r="G183">
-        <v>117387</v>
+        <v>116495</v>
       </c>
       <c r="H183">
-        <v>17403</v>
+        <v>17095</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144240</v>
+        <v>143504</v>
       </c>
       <c r="E184">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F184">
-        <v>159240</v>
+        <v>159007</v>
       </c>
       <c r="G184">
-        <v>229306</v>
+        <v>228970</v>
       </c>
       <c r="H184">
-        <v>15000</v>
+        <v>15503</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64131</v>
+        <v>63898</v>
       </c>
       <c r="E185">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F185">
-        <v>91131</v>
+        <v>90898</v>
       </c>
       <c r="G185">
-        <v>131229</v>
+        <v>130893</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8561,16 +8561,16 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>188024</v>
+        <v>187184</v>
       </c>
       <c r="E186">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F186">
-        <v>203024</v>
+        <v>202184</v>
       </c>
       <c r="G186">
-        <v>292355</v>
+        <v>291145</v>
       </c>
       <c r="H186">
         <v>15000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64131</v>
+        <v>63898</v>
       </c>
       <c r="E187">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F187">
-        <v>91131</v>
+        <v>90898</v>
       </c>
       <c r="G187">
-        <v>131229</v>
+        <v>130893</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>290064</v>
+        <v>288584</v>
       </c>
       <c r="E188">
-        <v>365402</v>
+        <v>361772</v>
       </c>
       <c r="F188">
-        <v>325064</v>
+        <v>323584</v>
       </c>
       <c r="G188">
-        <v>468092</v>
+        <v>465961</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>305885</v>
+        <v>304325</v>
       </c>
       <c r="E189">
-        <v>365402</v>
+        <v>361772</v>
       </c>
       <c r="F189">
-        <v>320885</v>
+        <v>319325</v>
       </c>
       <c r="G189">
-        <v>462074</v>
+        <v>459828</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>30874</v>
+        <v>30623</v>
       </c>
       <c r="E190">
-        <v>95904</v>
+        <v>94952</v>
       </c>
       <c r="F190">
-        <v>65874</v>
+        <v>65623</v>
       </c>
       <c r="G190">
-        <v>94859</v>
+        <v>94497</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44390</v>
+        <v>44164</v>
       </c>
       <c r="E191">
-        <v>95904</v>
+        <v>94952</v>
       </c>
       <c r="F191">
-        <v>61159</v>
+        <v>60697</v>
       </c>
       <c r="G191">
-        <v>88069</v>
+        <v>87404</v>
       </c>
       <c r="H191">
-        <v>16769</v>
+        <v>16533</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>42948</v>
+        <v>80777</v>
       </c>
       <c r="E192">
-        <v>123311</v>
+        <v>122086</v>
       </c>
       <c r="F192">
-        <v>77948</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>112245</v>
+        <v>0</v>
       </c>
       <c r="H192">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>123311</v>
+        <v>122086</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50537</v>
+        <v>50060</v>
       </c>
       <c r="E194">
-        <v>150900</v>
+        <v>149401</v>
       </c>
       <c r="F194">
-        <v>77537</v>
+        <v>77060</v>
       </c>
       <c r="G194">
-        <v>111653</v>
+        <v>110966</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>123311</v>
+        <v>122086</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23755</v>
+        <v>23618</v>
       </c>
       <c r="E196">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F196">
-        <v>54800</v>
+        <v>54255</v>
       </c>
       <c r="G196">
-        <v>78912</v>
+        <v>78127</v>
       </c>
       <c r="H196">
-        <v>31045</v>
+        <v>30637</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32348</v>
+        <v>32183</v>
       </c>
       <c r="E197">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F197">
-        <v>47435</v>
+        <v>47183</v>
       </c>
       <c r="G197">
-        <v>68306</v>
+        <v>67944</v>
       </c>
       <c r="H197">
-        <v>15087</v>
+        <v>15000</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26170</v>
+        <v>26036</v>
       </c>
       <c r="E198">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F198">
-        <v>61170</v>
+        <v>61036</v>
       </c>
       <c r="G198">
-        <v>88085</v>
+        <v>87892</v>
       </c>
       <c r="H198">
         <v>35000</v>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37318</v>
+        <v>37128</v>
       </c>
       <c r="E199">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F199">
-        <v>63674</v>
+        <v>63173</v>
       </c>
       <c r="G199">
-        <v>91691</v>
+        <v>90969</v>
       </c>
       <c r="H199">
-        <v>26356</v>
+        <v>26045</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9179,16 +9179,16 @@
         <v>14065</v>
       </c>
       <c r="E200">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F200">
-        <v>46870</v>
+        <v>46825</v>
       </c>
       <c r="G200">
-        <v>67493</v>
+        <v>67428</v>
       </c>
       <c r="H200">
-        <v>32805</v>
+        <v>32760</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11870</v>
+        <v>11825</v>
       </c>
       <c r="E201">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F201">
-        <v>38870</v>
+        <v>38825</v>
       </c>
       <c r="G201">
-        <v>55973</v>
+        <v>55908</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9269,7 +9269,7 @@
         <v>22432</v>
       </c>
       <c r="E202">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F202">
         <v>57432</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22595</v>
+        <v>22480</v>
       </c>
       <c r="E203">
-        <v>146150</v>
+        <v>144698</v>
       </c>
       <c r="F203">
-        <v>49595</v>
+        <v>49480</v>
       </c>
       <c r="G203">
-        <v>71417</v>
+        <v>71251</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9359,16 +9359,16 @@
         <v>28738</v>
       </c>
       <c r="E204">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F204">
-        <v>61139</v>
+        <v>61005</v>
       </c>
       <c r="G204">
-        <v>88040</v>
+        <v>87847</v>
       </c>
       <c r="H204">
-        <v>32401</v>
+        <v>32267</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,16 +9402,16 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26139</v>
+        <v>26005</v>
       </c>
       <c r="E205">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F205">
-        <v>53139</v>
+        <v>53005</v>
       </c>
       <c r="G205">
-        <v>76520</v>
+        <v>76327</v>
       </c>
       <c r="H205">
         <v>27000</v>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24179</v>
+        <v>24086</v>
       </c>
       <c r="E206">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F206">
-        <v>42284</v>
+        <v>41931</v>
       </c>
       <c r="G206">
-        <v>60889</v>
+        <v>60381</v>
       </c>
       <c r="H206">
-        <v>18105</v>
+        <v>17845</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13014</v>
+        <v>12698</v>
       </c>
       <c r="E207">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F207">
-        <v>34001</v>
+        <v>33648</v>
       </c>
       <c r="G207">
-        <v>48961</v>
+        <v>48453</v>
       </c>
       <c r="H207">
-        <v>20987</v>
+        <v>20950</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="E208">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22908</v>
+        <v>22792</v>
       </c>
       <c r="E209">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F209">
-        <v>37908</v>
+        <v>37792</v>
       </c>
       <c r="G209">
-        <v>54588</v>
+        <v>54420</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="E210">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40235</v>
+        <v>40030</v>
       </c>
       <c r="E211">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F211">
-        <v>64841</v>
+        <v>64334</v>
       </c>
       <c r="G211">
-        <v>93371</v>
+        <v>92641</v>
       </c>
       <c r="H211">
-        <v>24606</v>
+        <v>24304</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83324</v>
+        <v>82898</v>
       </c>
       <c r="E213">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F213">
-        <v>110324</v>
+        <v>109701</v>
       </c>
       <c r="G213">
-        <v>158867</v>
+        <v>157969</v>
       </c>
       <c r="H213">
-        <v>27000</v>
+        <v>26803</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>29055</v>
+        <v>28439</v>
       </c>
       <c r="E214">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F214">
-        <v>60652</v>
+        <v>60250</v>
       </c>
       <c r="G214">
-        <v>87339</v>
+        <v>86760</v>
       </c>
       <c r="H214">
-        <v>31597</v>
+        <v>31811</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31140</v>
+        <v>30982</v>
       </c>
       <c r="E215">
-        <v>87683</v>
+        <v>86812</v>
       </c>
       <c r="F215">
-        <v>52652</v>
+        <v>52250</v>
       </c>
       <c r="G215">
-        <v>75819</v>
+        <v>75240</v>
       </c>
       <c r="H215">
-        <v>21512</v>
+        <v>21268</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,16 +9881,16 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>64272</v>
+        <v>63960</v>
       </c>
       <c r="E216">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F216">
-        <v>99272</v>
+        <v>98960</v>
       </c>
       <c r="G216">
-        <v>142952</v>
+        <v>142502</v>
       </c>
       <c r="H216">
         <v>35000</v>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88843</v>
+        <v>88390</v>
       </c>
       <c r="E217">
-        <v>102299</v>
+        <v>101283</v>
       </c>
       <c r="F217">
-        <v>103843</v>
+        <v>103390</v>
       </c>
       <c r="G217">
-        <v>149534</v>
+        <v>148882</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -9973,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="E218">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111046</v>
+        <v>110479</v>
       </c>
       <c r="E219">
-        <v>131533</v>
+        <v>130226</v>
       </c>
       <c r="F219">
-        <v>126046</v>
+        <v>125479</v>
       </c>
       <c r="G219">
-        <v>181506</v>
+        <v>180690</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10062,16 +10062,16 @@
         <v>59287</v>
       </c>
       <c r="E220">
-        <v>82220</v>
+        <v>81403</v>
       </c>
       <c r="F220">
-        <v>75686</v>
+        <v>75646</v>
       </c>
       <c r="G220">
-        <v>108988</v>
+        <v>108930</v>
       </c>
       <c r="H220">
-        <v>16399</v>
+        <v>16359</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>50646</v>
+        <v>50606</v>
       </c>
       <c r="E221">
-        <v>82220</v>
+        <v>81403</v>
       </c>
       <c r="F221">
-        <v>65646</v>
+        <v>65606</v>
       </c>
       <c r="G221">
-        <v>94530</v>
+        <v>94473</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>73524</v>
+        <v>73148</v>
       </c>
       <c r="E222">
-        <v>96836</v>
+        <v>95874</v>
       </c>
       <c r="F222">
-        <v>88609</v>
+        <v>88420</v>
       </c>
       <c r="G222">
-        <v>127597</v>
+        <v>127325</v>
       </c>
       <c r="H222">
-        <v>15085</v>
+        <v>15272</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>55413</v>
+        <v>55224</v>
       </c>
       <c r="E223">
-        <v>96836</v>
+        <v>95874</v>
       </c>
       <c r="F223">
-        <v>70413</v>
+        <v>70224</v>
       </c>
       <c r="G223">
-        <v>101395</v>
+        <v>101123</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10242,16 +10242,16 @@
         <v>16578</v>
       </c>
       <c r="E224">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F224">
-        <v>41572</v>
+        <v>41018</v>
       </c>
       <c r="G224">
-        <v>59864</v>
+        <v>59066</v>
       </c>
       <c r="H224">
-        <v>24994</v>
+        <v>24440</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10161</v>
+        <v>9360</v>
       </c>
       <c r="E225">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F225">
-        <v>33572</v>
+        <v>33018</v>
       </c>
       <c r="G225">
-        <v>48344</v>
+        <v>47546</v>
       </c>
       <c r="H225">
-        <v>23411</v>
+        <v>23658</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>38087</v>
+        <v>37892</v>
       </c>
       <c r="E226">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F226">
-        <v>54115</v>
+        <v>53778</v>
       </c>
       <c r="G226">
-        <v>77926</v>
+        <v>77440</v>
       </c>
       <c r="H226">
-        <v>16028</v>
+        <v>15886</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25935</v>
+        <v>25802</v>
       </c>
       <c r="E227">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F227">
-        <v>44870</v>
+        <v>44533</v>
       </c>
       <c r="G227">
-        <v>64613</v>
+        <v>64128</v>
       </c>
       <c r="H227">
-        <v>18935</v>
+        <v>18731</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83433</v>
+        <v>83008</v>
       </c>
       <c r="E228">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F228">
-        <v>98433</v>
+        <v>98331</v>
       </c>
       <c r="G228">
-        <v>141744</v>
+        <v>141597</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>15323</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13861</v>
+        <v>13759</v>
       </c>
       <c r="E229">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F229">
-        <v>40861</v>
+        <v>40759</v>
       </c>
       <c r="G229">
-        <v>58840</v>
+        <v>58693</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="E230">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19318</v>
+        <v>19141</v>
       </c>
       <c r="E231">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F231">
-        <v>46318</v>
+        <v>46141</v>
       </c>
       <c r="G231">
-        <v>66698</v>
+        <v>66443</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10592,16 +10592,16 @@
         <v>9335</v>
       </c>
       <c r="E232">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F232">
-        <v>38647</v>
+        <v>38422</v>
       </c>
       <c r="G232">
-        <v>55652</v>
+        <v>55328</v>
       </c>
       <c r="H232">
-        <v>29312</v>
+        <v>29087</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9957</v>
+        <v>9906</v>
       </c>
       <c r="E233">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F233">
-        <v>30647</v>
+        <v>30422</v>
       </c>
       <c r="G233">
-        <v>44132</v>
+        <v>43808</v>
       </c>
       <c r="H233">
-        <v>20690</v>
+        <v>20516</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="E234">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -10767,16 +10767,16 @@
         <v>8351</v>
       </c>
       <c r="E236">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F236">
-        <v>37481</v>
+        <v>37249</v>
       </c>
       <c r="G236">
-        <v>53973</v>
+        <v>53639</v>
       </c>
       <c r="H236">
-        <v>29130</v>
+        <v>28898</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>7040</v>
+        <v>6973</v>
       </c>
       <c r="E237">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F237">
-        <v>29481</v>
+        <v>29249</v>
       </c>
       <c r="G237">
-        <v>42453</v>
+        <v>42119</v>
       </c>
       <c r="H237">
-        <v>22441</v>
+        <v>22276</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10856,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="E238">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11415</v>
+        <v>11357</v>
       </c>
       <c r="E239">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F239">
-        <v>31231</v>
+        <v>31002</v>
       </c>
       <c r="G239">
-        <v>44973</v>
+        <v>44643</v>
       </c>
       <c r="H239">
-        <v>19816</v>
+        <v>19645</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24163</v>
+        <v>24040</v>
       </c>
       <c r="E240">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F240">
-        <v>53443</v>
+        <v>52912</v>
       </c>
       <c r="G240">
-        <v>76958</v>
+        <v>76193</v>
       </c>
       <c r="H240">
-        <v>29280</v>
+        <v>28872</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>71767</v>
+        <v>72290</v>
       </c>
       <c r="E241">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F241">
-        <v>86767</v>
+        <v>87290</v>
       </c>
       <c r="G241">
-        <v>124944</v>
+        <v>125698</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>32144</v>
+        <v>33821</v>
       </c>
       <c r="E242">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F242">
-        <v>50923</v>
+        <v>51276</v>
       </c>
       <c r="G242">
-        <v>73329</v>
+        <v>73837</v>
       </c>
       <c r="H242">
-        <v>18779</v>
+        <v>17455</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="E243">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -11119,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="E244">
-        <v>27407</v>
+        <v>27134</v>
       </c>
       <c r="F244">
         <v>0</v>
@@ -11164,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="E245">
-        <v>27407</v>
+        <v>27134</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92684</v>
+        <v>92212</v>
       </c>
       <c r="E246">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F246">
-        <v>107684</v>
+        <v>107212</v>
       </c>
       <c r="G246">
-        <v>155065</v>
+        <v>154385</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59490</v>
+        <v>59171</v>
       </c>
       <c r="E248">
-        <v>96836</v>
+        <v>95874</v>
       </c>
       <c r="F248">
-        <v>75054</v>
+        <v>74902</v>
       </c>
       <c r="G248">
-        <v>108078</v>
+        <v>107859</v>
       </c>
       <c r="H248">
-        <v>15564</v>
+        <v>15731</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48216</v>
+        <v>48064</v>
       </c>
       <c r="E249">
-        <v>96836</v>
+        <v>95874</v>
       </c>
       <c r="F249">
-        <v>63216</v>
+        <v>63064</v>
       </c>
       <c r="G249">
-        <v>91031</v>
+        <v>90812</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73571</v>
+        <v>73055</v>
       </c>
       <c r="E250">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F250">
-        <v>102057</v>
+        <v>103650</v>
       </c>
       <c r="G250">
-        <v>146962</v>
+        <v>149256</v>
       </c>
       <c r="H250">
-        <v>28486</v>
+        <v>30595</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>73602</v>
+        <v>75130</v>
       </c>
       <c r="E251">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F251">
-        <v>88602</v>
+        <v>90130</v>
       </c>
       <c r="G251">
-        <v>127587</v>
+        <v>129787</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11472,16 +11472,16 @@
         <v>11817</v>
       </c>
       <c r="E252">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F252">
-        <v>39740</v>
+        <v>39345</v>
       </c>
       <c r="G252">
-        <v>57226</v>
+        <v>56657</v>
       </c>
       <c r="H252">
-        <v>27923</v>
+        <v>27528</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38557</v>
+        <v>38360</v>
       </c>
       <c r="E253">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F253">
-        <v>53557</v>
+        <v>53360</v>
       </c>
       <c r="G253">
-        <v>77122</v>
+        <v>76838</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24288</v>
+        <v>24164</v>
       </c>
       <c r="E254">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F254">
-        <v>53443</v>
+        <v>52912</v>
       </c>
       <c r="G254">
-        <v>76958</v>
+        <v>76193</v>
       </c>
       <c r="H254">
-        <v>29155</v>
+        <v>28748</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69525</v>
+        <v>69170</v>
       </c>
       <c r="E255">
-        <v>71257</v>
+        <v>70549</v>
       </c>
       <c r="F255">
-        <v>84525</v>
+        <v>84170</v>
       </c>
       <c r="G255">
-        <v>121716</v>
+        <v>121205</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11650,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>52986</v>
+        <v>52460</v>
       </c>
       <c r="F257">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="E258">
-        <v>51141</v>
+        <v>50633</v>
       </c>
       <c r="F258">
         <v>0</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12481</v>
+        <v>12402</v>
       </c>
       <c r="E259">
-        <v>51141</v>
+        <v>50633</v>
       </c>
       <c r="F259">
-        <v>30938</v>
+        <v>30707</v>
       </c>
       <c r="G259">
-        <v>44551</v>
+        <v>44218</v>
       </c>
       <c r="H259">
-        <v>18457</v>
+        <v>18305</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="E260">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12481</v>
+        <v>12402</v>
       </c>
       <c r="E261">
-        <v>63930</v>
+        <v>63295</v>
       </c>
       <c r="F261">
-        <v>35925</v>
+        <v>35646</v>
       </c>
       <c r="G261">
-        <v>51732</v>
+        <v>51330</v>
       </c>
       <c r="H261">
-        <v>23444</v>
+        <v>23244</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="E262">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F262">
         <v>0</v>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12481</v>
+        <v>12402</v>
       </c>
       <c r="E263">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F263">
-        <v>39481</v>
+        <v>39173</v>
       </c>
       <c r="G263">
-        <v>56853</v>
+        <v>56409</v>
       </c>
       <c r="H263">
-        <v>27000</v>
+        <v>26771</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39561</v>
+        <v>39764</v>
       </c>
       <c r="E264">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F264">
-        <v>66578</v>
+        <v>54764</v>
       </c>
       <c r="G264">
-        <v>95872</v>
+        <v>78860</v>
       </c>
       <c r="H264">
-        <v>27017</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>31125</v>
+        <v>16552</v>
       </c>
       <c r="E265">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>35895</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>51689</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>19343</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="E266">
-        <v>67584</v>
+        <v>66913</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -12131,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>67584</v>
+        <v>66913</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35954</v>
+        <v>35771</v>
       </c>
       <c r="E268">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F268">
-        <v>50954</v>
+        <v>50799</v>
       </c>
       <c r="G268">
-        <v>73374</v>
+        <v>73151</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>15028</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23943</v>
+        <v>23930</v>
       </c>
       <c r="E269">
-        <v>60276</v>
+        <v>59677</v>
       </c>
       <c r="F269">
-        <v>39085</v>
+        <v>38930</v>
       </c>
       <c r="G269">
-        <v>56282</v>
+        <v>56059</v>
       </c>
       <c r="H269">
-        <v>15142</v>
+        <v>15000</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>39106</v>
+        <v>38906</v>
       </c>
       <c r="E270">
-        <v>67584</v>
+        <v>66913</v>
       </c>
       <c r="F270">
-        <v>54119</v>
+        <v>53971</v>
       </c>
       <c r="G270">
-        <v>77931</v>
+        <v>77718</v>
       </c>
       <c r="H270">
-        <v>15013</v>
+        <v>15065</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29086</v>
+        <v>28938</v>
       </c>
       <c r="E271">
-        <v>67584</v>
+        <v>66913</v>
       </c>
       <c r="F271">
-        <v>44086</v>
+        <v>43938</v>
       </c>
       <c r="G271">
-        <v>63484</v>
+        <v>63271</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71093</v>
+        <v>70855</v>
       </c>
       <c r="E272">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F272">
-        <v>86235</v>
+        <v>85855</v>
       </c>
       <c r="G272">
-        <v>124178</v>
+        <v>123631</v>
       </c>
       <c r="H272">
-        <v>15142</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21466</v>
+        <v>20998</v>
       </c>
       <c r="E273">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F273">
-        <v>48466</v>
+        <v>47998</v>
       </c>
       <c r="G273">
-        <v>69791</v>
+        <v>69117</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12441,7 +12441,7 @@
         <v>21854</v>
       </c>
       <c r="E274">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F274">
         <v>48854</v>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10192</v>
+        <v>10140</v>
       </c>
       <c r="E275">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F275">
-        <v>37192</v>
+        <v>37140</v>
       </c>
       <c r="G275">
-        <v>53556</v>
+        <v>53482</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151845</v>
+        <v>151351</v>
       </c>
       <c r="E276">
-        <v>164421</v>
+        <v>162787</v>
       </c>
       <c r="F276">
-        <v>167179</v>
+        <v>186351</v>
       </c>
       <c r="G276">
-        <v>240738</v>
+        <v>268345</v>
       </c>
       <c r="H276">
-        <v>15334</v>
+        <v>35000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>38400</v>
+        <v>101119</v>
       </c>
       <c r="E277">
-        <v>164421</v>
+        <v>162787</v>
       </c>
       <c r="F277">
-        <v>65400</v>
+        <v>116119</v>
       </c>
       <c r="G277">
-        <v>94176</v>
+        <v>167211</v>
       </c>
       <c r="H277">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>51854</v>
+        <v>51589</v>
       </c>
       <c r="E278">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F278">
-        <v>78544</v>
+        <v>78019</v>
       </c>
       <c r="G278">
-        <v>113103</v>
+        <v>112347</v>
       </c>
       <c r="H278">
-        <v>26690</v>
+        <v>26430</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48859</v>
+        <v>48610</v>
       </c>
       <c r="E279">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F279">
-        <v>68291</v>
+        <v>67766</v>
       </c>
       <c r="G279">
-        <v>98339</v>
+        <v>97583</v>
       </c>
       <c r="H279">
-        <v>19432</v>
+        <v>19156</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>69635</v>
+        <v>67439</v>
       </c>
       <c r="E280">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F280">
-        <v>91428</v>
+        <v>90864</v>
       </c>
       <c r="G280">
-        <v>131656</v>
+        <v>130844</v>
       </c>
       <c r="H280">
-        <v>21793</v>
+        <v>23425</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48859</v>
+        <v>48688</v>
       </c>
       <c r="E281">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F281">
-        <v>75416</v>
+        <v>74852</v>
       </c>
       <c r="G281">
-        <v>108599</v>
+        <v>107787</v>
       </c>
       <c r="H281">
-        <v>26557</v>
+        <v>26164</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24084</v>
+        <v>24008</v>
       </c>
       <c r="E282">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F282">
-        <v>41096</v>
+        <v>40688</v>
       </c>
       <c r="G282">
-        <v>59178</v>
+        <v>58591</v>
       </c>
       <c r="H282">
-        <v>17012</v>
+        <v>16680</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24492</v>
+        <v>24508</v>
       </c>
       <c r="E283">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F283">
-        <v>39492</v>
+        <v>39508</v>
       </c>
       <c r="G283">
-        <v>56868</v>
+        <v>56892</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65689</v>
+        <v>65380</v>
       </c>
       <c r="E284">
-        <v>82220</v>
+        <v>81403</v>
       </c>
       <c r="F284">
-        <v>80689</v>
+        <v>80380</v>
       </c>
       <c r="G284">
-        <v>116192</v>
+        <v>115747</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="E285">
-        <v>82220</v>
+        <v>81403</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>38351</v>
+        <v>37970</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20794</v>
+        <v>18938</v>
       </c>
       <c r="E287">
-        <v>38351</v>
+        <v>37970</v>
       </c>
       <c r="F287">
-        <v>35794</v>
+        <v>33938</v>
       </c>
       <c r="G287">
-        <v>51543</v>
+        <v>48871</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31501</v>
+        <v>31340</v>
       </c>
       <c r="E288">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F288">
-        <v>48700</v>
+        <v>48506</v>
       </c>
       <c r="G288">
-        <v>70128</v>
+        <v>69849</v>
       </c>
       <c r="H288">
-        <v>17199</v>
+        <v>17166</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25700</v>
+        <v>25506</v>
       </c>
       <c r="E289">
-        <v>58449</v>
+        <v>57868</v>
       </c>
       <c r="F289">
-        <v>40700</v>
+        <v>40506</v>
       </c>
       <c r="G289">
-        <v>58608</v>
+        <v>58329</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13146,16 +13146,16 @@
         <v>10662</v>
       </c>
       <c r="E290">
-        <v>43832</v>
+        <v>43397</v>
       </c>
       <c r="F290">
-        <v>32874</v>
+        <v>32548</v>
       </c>
       <c r="G290">
-        <v>47339</v>
+        <v>46869</v>
       </c>
       <c r="H290">
-        <v>22212</v>
+        <v>21886</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34073</v>
+        <v>33899</v>
       </c>
       <c r="E291">
-        <v>43832</v>
+        <v>43397</v>
       </c>
       <c r="F291">
-        <v>49073</v>
+        <v>48899</v>
       </c>
       <c r="G291">
-        <v>70665</v>
+        <v>70415</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43026</v>
+        <v>42619</v>
       </c>
       <c r="E292">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F292">
-        <v>73511</v>
+        <v>73009</v>
       </c>
       <c r="G292">
-        <v>105856</v>
+        <v>105133</v>
       </c>
       <c r="H292">
-        <v>30485</v>
+        <v>30390</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37930</v>
+        <v>37736</v>
       </c>
       <c r="E293">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F293">
-        <v>63919</v>
+        <v>63417</v>
       </c>
       <c r="G293">
-        <v>92043</v>
+        <v>91320</v>
       </c>
       <c r="H293">
-        <v>25989</v>
+        <v>25681</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="E295">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54911</v>
+        <v>54304</v>
       </c>
       <c r="E296">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F296">
-        <v>89911</v>
+        <v>89304</v>
       </c>
       <c r="G296">
-        <v>129472</v>
+        <v>128598</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64319</v>
+        <v>63991</v>
       </c>
       <c r="E297">
-        <v>73066</v>
+        <v>72340</v>
       </c>
       <c r="F297">
-        <v>79319</v>
+        <v>78991</v>
       </c>
       <c r="G297">
-        <v>114219</v>
+        <v>113747</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13501,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4390</v>
+        <v>4368</v>
       </c>
       <c r="E299">
-        <v>54795</v>
+        <v>54250</v>
       </c>
       <c r="F299">
-        <v>29126</v>
+        <v>28905</v>
       </c>
       <c r="G299">
-        <v>41941</v>
+        <v>41623</v>
       </c>
       <c r="H299">
-        <v>24736</v>
+        <v>24537</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>69412</v>
+        <v>68722</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10709</v>
+        <v>10655</v>
       </c>
       <c r="E301">
-        <v>69412</v>
+        <v>68722</v>
       </c>
       <c r="F301">
-        <v>37354</v>
+        <v>37063</v>
       </c>
       <c r="G301">
-        <v>53790</v>
+        <v>53371</v>
       </c>
       <c r="H301">
-        <v>26645</v>
+        <v>26408</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24884</v>
+        <v>24773</v>
       </c>
       <c r="E302">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F302">
-        <v>51884</v>
+        <v>51773</v>
       </c>
       <c r="G302">
-        <v>74713</v>
+        <v>74553</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13717,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="E303">
-        <v>91337</v>
+        <v>90429</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44186</v>
+        <v>44039</v>
       </c>
       <c r="E304">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F304">
-        <v>77010</v>
+        <v>76492</v>
       </c>
       <c r="G304">
-        <v>110894</v>
+        <v>110148</v>
       </c>
       <c r="H304">
-        <v>32824</v>
+        <v>32453</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45535</v>
+        <v>45302</v>
       </c>
       <c r="E305">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F305">
-        <v>66961</v>
+        <v>66443</v>
       </c>
       <c r="G305">
-        <v>96424</v>
+        <v>95678</v>
       </c>
       <c r="H305">
-        <v>21426</v>
+        <v>21141</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24226</v>
+        <v>24149</v>
       </c>
       <c r="E306">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F306">
-        <v>59226</v>
+        <v>59149</v>
       </c>
       <c r="G306">
-        <v>85285</v>
+        <v>85175</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33351</v>
+        <v>33181</v>
       </c>
       <c r="E307">
-        <v>109608</v>
+        <v>108519</v>
       </c>
       <c r="F307">
-        <v>60351</v>
+        <v>60181</v>
       </c>
       <c r="G307">
-        <v>86905</v>
+        <v>86661</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>189775</v>
+        <v>188807</v>
       </c>
       <c r="E308">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F308">
-        <v>205056</v>
+        <v>204334</v>
       </c>
       <c r="G308">
-        <v>295281</v>
+        <v>294241</v>
       </c>
       <c r="H308">
-        <v>15281</v>
+        <v>15527</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>141606</v>
+        <v>140884</v>
       </c>
       <c r="E309">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F309">
-        <v>156606</v>
+        <v>155884</v>
       </c>
       <c r="G309">
-        <v>225513</v>
+        <v>224473</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>68741</v>
+        <v>68203</v>
       </c>
       <c r="E310">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F310">
-        <v>92208</v>
+        <v>90255</v>
       </c>
       <c r="G310">
-        <v>132780</v>
+        <v>129967</v>
       </c>
       <c r="H310">
-        <v>23467</v>
+        <v>22052</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53782</v>
+        <v>0</v>
       </c>
       <c r="E311">
-        <v>127879</v>
+        <v>126608</v>
       </c>
       <c r="F311">
-        <v>77385</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>111434</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>23603</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14110,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="E312">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F312">
         <v>0</v>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110528</v>
+        <v>109964</v>
       </c>
       <c r="E313">
-        <v>182692</v>
+        <v>180877</v>
       </c>
       <c r="F313">
-        <v>125528</v>
+        <v>124964</v>
       </c>
       <c r="G313">
-        <v>180760</v>
+        <v>179948</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>130097</v>
+        <v>129433</v>
       </c>
       <c r="E314">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F314">
-        <v>165097</v>
+        <v>164433</v>
       </c>
       <c r="G314">
-        <v>237740</v>
+        <v>236784</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>147690</v>
+        <v>146936</v>
       </c>
       <c r="E315">
-        <v>237505</v>
+        <v>235145</v>
       </c>
       <c r="F315">
-        <v>162690</v>
+        <v>161936</v>
       </c>
       <c r="G315">
-        <v>234274</v>
+        <v>233188</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,7 +481,7 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71120</v>
+        <v>71153</v>
       </c>
       <c r="E2">
         <v>72340</v>
@@ -493,7 +493,7 @@
         <v>124357</v>
       </c>
       <c r="H2">
-        <v>15239</v>
+        <v>15206</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4243</v>
+        <v>4240</v>
       </c>
       <c r="E7">
         <v>54250</v>
       </c>
       <c r="F7">
-        <v>28855</v>
+        <v>28854</v>
       </c>
       <c r="G7">
-        <v>41551</v>
+        <v>41550</v>
       </c>
       <c r="H7">
-        <v>24612</v>
+        <v>24614</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33805</v>
+        <v>33815</v>
       </c>
       <c r="E8">
         <v>72340</v>
       </c>
       <c r="F8">
-        <v>53919</v>
+        <v>52079</v>
       </c>
       <c r="G8">
-        <v>77643</v>
+        <v>74994</v>
       </c>
       <c r="H8">
-        <v>20114</v>
+        <v>18264</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>29266</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>72340</v>
       </c>
       <c r="F9">
-        <v>45919</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>66123</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>16653</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>40950</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>108519</v>
       </c>
       <c r="F11">
-        <v>64702</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>93171</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>23752</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>75020</v>
+        <v>75019</v>
       </c>
       <c r="E12">
         <v>81385</v>
       </c>
       <c r="F12">
-        <v>91987</v>
+        <v>91979</v>
       </c>
       <c r="G12">
-        <v>132461</v>
+        <v>132450</v>
       </c>
       <c r="H12">
-        <v>16967</v>
+        <v>16960</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11638</v>
+        <v>11630</v>
       </c>
       <c r="E13">
         <v>81385</v>
       </c>
       <c r="F13">
-        <v>38638</v>
+        <v>38630</v>
       </c>
       <c r="G13">
-        <v>55639</v>
+        <v>55627</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>32869</v>
+        <v>35062</v>
       </c>
       <c r="E21">
         <v>101283</v>
       </c>
       <c r="F21">
-        <v>58648</v>
+        <v>59525</v>
       </c>
       <c r="G21">
-        <v>84453</v>
+        <v>85716</v>
       </c>
       <c r="H21">
-        <v>25779</v>
+        <v>24463</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52556</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>130226</v>
       </c>
       <c r="F23">
-        <v>77811</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>112048</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>25255</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>18065</v>
+        <v>18038</v>
       </c>
       <c r="E27">
         <v>63295</v>
       </c>
       <c r="F27">
-        <v>37911</v>
+        <v>37900</v>
       </c>
       <c r="G27">
-        <v>54592</v>
+        <v>54576</v>
       </c>
       <c r="H27">
-        <v>19846</v>
+        <v>19862</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74849</v>
+        <v>74271</v>
       </c>
       <c r="E28">
         <v>126608</v>
       </c>
       <c r="F28">
-        <v>93162</v>
+        <v>93161</v>
       </c>
       <c r="G28">
-        <v>134153</v>
+        <v>134152</v>
       </c>
       <c r="H28">
-        <v>18313</v>
+        <v>18890</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25007</v>
+        <v>25006</v>
       </c>
       <c r="E29">
         <v>126608</v>
       </c>
       <c r="F29">
-        <v>52007</v>
+        <v>52006</v>
       </c>
       <c r="G29">
-        <v>74890</v>
+        <v>74889</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>129995</v>
+        <v>129989</v>
       </c>
       <c r="E30">
         <v>180877</v>
       </c>
       <c r="F30">
-        <v>146183</v>
+        <v>164989</v>
       </c>
       <c r="G30">
-        <v>210504</v>
+        <v>237584</v>
       </c>
       <c r="H30">
-        <v>16188</v>
+        <v>35000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57205</v>
+        <v>77233</v>
       </c>
       <c r="E31">
         <v>180877</v>
       </c>
       <c r="F31">
-        <v>84205</v>
+        <v>104233</v>
       </c>
       <c r="G31">
-        <v>121255</v>
+        <v>150096</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71120</v>
+        <v>71075</v>
       </c>
       <c r="E32">
         <v>108519</v>
       </c>
       <c r="F32">
-        <v>86120</v>
+        <v>89652</v>
       </c>
       <c r="G32">
-        <v>124013</v>
+        <v>129099</v>
       </c>
       <c r="H32">
-        <v>15000</v>
+        <v>18577</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>41028</v>
+        <v>49857</v>
       </c>
       <c r="E33">
         <v>108519</v>
       </c>
       <c r="F33">
-        <v>64733</v>
+        <v>68265</v>
       </c>
       <c r="G33">
-        <v>93216</v>
+        <v>98302</v>
       </c>
       <c r="H33">
-        <v>23705</v>
+        <v>18408</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>63118</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>126608</v>
       </c>
       <c r="F35">
-        <v>80624</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>116099</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>17506</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44444</v>
+        <v>44416</v>
       </c>
       <c r="E36">
         <v>126608</v>
       </c>
       <c r="F36">
-        <v>72491</v>
+        <v>71416</v>
       </c>
       <c r="G36">
-        <v>104387</v>
+        <v>102839</v>
       </c>
       <c r="H36">
-        <v>28047</v>
+        <v>27000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35412</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>126608</v>
       </c>
       <c r="F37">
-        <v>62412</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89873</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>83054</v>
+        <v>81972</v>
       </c>
       <c r="E39">
         <v>235145</v>
       </c>
       <c r="F39">
-        <v>110054</v>
+        <v>108972</v>
       </c>
       <c r="G39">
-        <v>158478</v>
+        <v>156920</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>83054</v>
+        <v>81972</v>
       </c>
       <c r="E41">
         <v>235145</v>
       </c>
       <c r="F41">
-        <v>110054</v>
+        <v>108972</v>
       </c>
       <c r="G41">
-        <v>158478</v>
+        <v>156920</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38875</v>
+        <v>38835</v>
       </c>
       <c r="E43">
         <v>126608</v>
       </c>
       <c r="F43">
-        <v>65875</v>
+        <v>65835</v>
       </c>
       <c r="G43">
-        <v>94860</v>
+        <v>94802</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>92184</v>
       </c>
       <c r="E45">
         <v>180877</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>113416</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>163319</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>21232</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25771</v>
+        <v>27298</v>
       </c>
       <c r="E47">
         <v>108519</v>
       </c>
       <c r="F47">
-        <v>52771</v>
+        <v>54298</v>
       </c>
       <c r="G47">
-        <v>75990</v>
+        <v>78189</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35552</v>
+        <v>35530</v>
       </c>
       <c r="E50">
         <v>63295</v>
       </c>
       <c r="F50">
-        <v>56103</v>
+        <v>58452</v>
       </c>
       <c r="G50">
-        <v>80788</v>
+        <v>84171</v>
       </c>
       <c r="H50">
-        <v>20551</v>
+        <v>22922</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33103</v>
+        <v>35452</v>
       </c>
       <c r="E51">
         <v>63295</v>
       </c>
       <c r="F51">
-        <v>48103</v>
+        <v>50452</v>
       </c>
       <c r="G51">
-        <v>69268</v>
+        <v>72651</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48032</v>
+        <v>48002</v>
       </c>
       <c r="E54">
         <v>126608</v>
       </c>
       <c r="F54">
-        <v>83032</v>
+        <v>83002</v>
       </c>
       <c r="G54">
-        <v>119566</v>
+        <v>119523</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,7 +2813,7 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>51761</v>
+        <v>51759</v>
       </c>
       <c r="E55">
         <v>126608</v>
@@ -2825,7 +2825,7 @@
         <v>109557</v>
       </c>
       <c r="H55">
-        <v>24320</v>
+        <v>24322</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62244</v>
+        <v>62251</v>
       </c>
       <c r="E57">
         <v>144698</v>
       </c>
       <c r="F57">
-        <v>87330</v>
+        <v>87333</v>
       </c>
       <c r="G57">
-        <v>125755</v>
+        <v>125760</v>
       </c>
       <c r="H57">
-        <v>25086</v>
+        <v>25082</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>24523</v>
       </c>
       <c r="E58">
         <v>36161</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>39523</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>56913</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6178</v>
+        <v>6174</v>
       </c>
       <c r="E59">
         <v>36161</v>
       </c>
       <c r="F59">
-        <v>22574</v>
+        <v>22573</v>
       </c>
       <c r="G59">
-        <v>32507</v>
+        <v>32505</v>
       </c>
       <c r="H59">
-        <v>16396</v>
+        <v>16399</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26021</v>
+        <v>26020</v>
       </c>
       <c r="E60">
         <v>48824</v>
       </c>
       <c r="F60">
-        <v>47804</v>
+        <v>47757</v>
       </c>
       <c r="G60">
-        <v>68838</v>
+        <v>68770</v>
       </c>
       <c r="H60">
-        <v>21783</v>
+        <v>21737</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24804</v>
+        <v>24757</v>
       </c>
       <c r="E61">
         <v>48824</v>
       </c>
       <c r="F61">
-        <v>39804</v>
+        <v>39757</v>
       </c>
       <c r="G61">
-        <v>57318</v>
+        <v>57250</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12776</v>
+        <v>12753</v>
       </c>
       <c r="E63">
         <v>81385</v>
       </c>
       <c r="F63">
-        <v>39776</v>
+        <v>39753</v>
       </c>
       <c r="G63">
-        <v>57277</v>
+        <v>57244</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28657</v>
+        <v>28452</v>
       </c>
       <c r="E65">
         <v>122068</v>
       </c>
       <c r="F65">
-        <v>55657</v>
+        <v>55452</v>
       </c>
       <c r="G65">
-        <v>80146</v>
+        <v>79851</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24554</v>
+        <v>24414</v>
       </c>
       <c r="E66">
         <v>90429</v>
       </c>
       <c r="F66">
-        <v>53486</v>
+        <v>53459</v>
       </c>
       <c r="G66">
-        <v>77020</v>
+        <v>76981</v>
       </c>
       <c r="H66">
-        <v>28932</v>
+        <v>29045</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18486</v>
+        <v>18459</v>
       </c>
       <c r="E67">
         <v>90429</v>
       </c>
       <c r="F67">
-        <v>45486</v>
+        <v>45459</v>
       </c>
       <c r="G67">
-        <v>65500</v>
+        <v>65461</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34226</v>
+        <v>34251</v>
       </c>
       <c r="E68">
         <v>108519</v>
       </c>
       <c r="F68">
-        <v>62582</v>
+        <v>62517</v>
       </c>
       <c r="G68">
-        <v>90118</v>
+        <v>90024</v>
       </c>
       <c r="H68">
-        <v>28356</v>
+        <v>28266</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27394</v>
+        <v>27329</v>
       </c>
       <c r="E69">
         <v>108519</v>
       </c>
       <c r="F69">
-        <v>54394</v>
+        <v>54329</v>
       </c>
       <c r="G69">
-        <v>78327</v>
+        <v>78234</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>44912</v>
+        <v>44915</v>
       </c>
       <c r="E70">
         <v>126608</v>
       </c>
       <c r="F70">
-        <v>79912</v>
+        <v>79915</v>
       </c>
       <c r="G70">
-        <v>115073</v>
+        <v>115078</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50450</v>
+        <v>50325</v>
       </c>
       <c r="E71">
         <v>126608</v>
       </c>
       <c r="F71">
-        <v>75557</v>
+        <v>75507</v>
       </c>
       <c r="G71">
-        <v>108802</v>
+        <v>108730</v>
       </c>
       <c r="H71">
-        <v>25107</v>
+        <v>25182</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5491</v>
+        <v>5784</v>
       </c>
       <c r="E73">
         <v>27116</v>
       </c>
       <c r="F73">
-        <v>20491</v>
+        <v>20784</v>
       </c>
       <c r="G73">
-        <v>29507</v>
+        <v>29929</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70044</v>
+        <v>69874</v>
       </c>
       <c r="E75">
         <v>94952</v>
       </c>
       <c r="F75">
-        <v>85044</v>
+        <v>84874</v>
       </c>
       <c r="G75">
-        <v>122463</v>
+        <v>122219</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80153</v>
+        <v>79119</v>
       </c>
       <c r="E76">
         <v>126608</v>
       </c>
       <c r="F76">
-        <v>95153</v>
+        <v>94621</v>
       </c>
       <c r="G76">
-        <v>137020</v>
+        <v>136254</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>15502</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47284</v>
+        <v>46599</v>
       </c>
       <c r="E77">
         <v>126608</v>
       </c>
       <c r="F77">
-        <v>74284</v>
+        <v>73599</v>
       </c>
       <c r="G77">
-        <v>106969</v>
+        <v>105983</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36785</v>
+        <v>36730</v>
       </c>
       <c r="E81">
         <v>90429</v>
       </c>
       <c r="F81">
-        <v>55981</v>
+        <v>55959</v>
       </c>
       <c r="G81">
-        <v>80613</v>
+        <v>80581</v>
       </c>
       <c r="H81">
-        <v>19196</v>
+        <v>19229</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>47596</v>
+        <v>48002</v>
       </c>
       <c r="E84">
         <v>101283</v>
       </c>
       <c r="F84">
-        <v>70699</v>
+        <v>70778</v>
       </c>
       <c r="G84">
-        <v>101807</v>
+        <v>101920</v>
       </c>
       <c r="H84">
-        <v>23103</v>
+        <v>22776</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31918</v>
+        <v>31757</v>
       </c>
       <c r="E85">
         <v>101283</v>
       </c>
       <c r="F85">
-        <v>58268</v>
+        <v>58203</v>
       </c>
       <c r="G85">
-        <v>83906</v>
+        <v>83812</v>
       </c>
       <c r="H85">
-        <v>26350</v>
+        <v>26446</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113178</v>
+        <v>112918</v>
       </c>
       <c r="E87">
         <v>144698</v>
       </c>
       <c r="F87">
-        <v>128178</v>
+        <v>127918</v>
       </c>
       <c r="G87">
-        <v>184576</v>
+        <v>184202</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>158714</v>
+        <v>158472</v>
       </c>
       <c r="E88">
         <v>159170</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>173472</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>249800</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>125814</v>
+        <v>125624</v>
       </c>
       <c r="E89">
         <v>159170</v>
       </c>
       <c r="F89">
-        <v>140814</v>
+        <v>140624</v>
       </c>
       <c r="G89">
-        <v>202772</v>
+        <v>202499</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4352,13 +4352,13 @@
         <v>57868</v>
       </c>
       <c r="F90">
-        <v>38260</v>
+        <v>38264</v>
       </c>
       <c r="G90">
-        <v>55094</v>
+        <v>55100</v>
       </c>
       <c r="H90">
-        <v>30580</v>
+        <v>30584</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4228</v>
+        <v>4240</v>
       </c>
       <c r="E91">
         <v>57868</v>
       </c>
       <c r="F91">
-        <v>30260</v>
+        <v>30264</v>
       </c>
       <c r="G91">
-        <v>43574</v>
+        <v>43580</v>
       </c>
       <c r="H91">
-        <v>26032</v>
+        <v>26024</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12074</v>
+        <v>12067</v>
       </c>
       <c r="E93">
         <v>27116</v>
       </c>
       <c r="F93">
-        <v>27074</v>
+        <v>27067</v>
       </c>
       <c r="G93">
-        <v>38987</v>
+        <v>38976</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61168</v>
+        <v>61175</v>
       </c>
       <c r="E96">
         <v>81385</v>
       </c>
       <c r="F96">
-        <v>76298</v>
+        <v>76296</v>
       </c>
       <c r="G96">
-        <v>109869</v>
+        <v>109866</v>
       </c>
       <c r="H96">
-        <v>15130</v>
+        <v>15121</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33275</v>
+        <v>33269</v>
       </c>
       <c r="E97">
         <v>81385</v>
       </c>
       <c r="F97">
-        <v>51050</v>
+        <v>51048</v>
       </c>
       <c r="G97">
-        <v>73512</v>
+        <v>73509</v>
       </c>
       <c r="H97">
-        <v>17775</v>
+        <v>17779</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>74240</v>
+        <v>74193</v>
       </c>
       <c r="E98">
         <v>94047</v>
       </c>
       <c r="F98">
-        <v>89256</v>
+        <v>89235</v>
       </c>
       <c r="G98">
-        <v>128529</v>
+        <v>128498</v>
       </c>
       <c r="H98">
-        <v>15016</v>
+        <v>15042</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33322</v>
+        <v>33269</v>
       </c>
       <c r="E99">
         <v>94047</v>
       </c>
       <c r="F99">
-        <v>56007</v>
+        <v>55986</v>
       </c>
       <c r="G99">
-        <v>80650</v>
+        <v>80620</v>
       </c>
       <c r="H99">
-        <v>22685</v>
+        <v>22717</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60902</v>
+        <v>60910</v>
       </c>
       <c r="E100">
         <v>105444</v>
@@ -4800,7 +4800,7 @@
         <v>113880</v>
       </c>
       <c r="H100">
-        <v>18181</v>
+        <v>18173</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61043</v>
+        <v>60863</v>
       </c>
       <c r="E101">
         <v>105444</v>
       </c>
       <c r="F101">
-        <v>76043</v>
+        <v>75863</v>
       </c>
       <c r="G101">
-        <v>109502</v>
+        <v>109243</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68437</v>
+        <v>68269</v>
       </c>
       <c r="E105">
         <v>126608</v>
       </c>
       <c r="F105">
-        <v>83437</v>
+        <v>83269</v>
       </c>
       <c r="G105">
-        <v>120149</v>
+        <v>119907</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>99965</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>180877</v>
       </c>
       <c r="F107">
-        <v>116528</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>167800</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>16563</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4087</v>
+        <v>4069</v>
       </c>
       <c r="E109">
         <v>126608</v>
       </c>
       <c r="F109">
-        <v>31087</v>
+        <v>31069</v>
       </c>
       <c r="G109">
-        <v>44765</v>
+        <v>44739</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13276</v>
+        <v>13267</v>
       </c>
       <c r="E111">
         <v>162787</v>
       </c>
       <c r="F111">
-        <v>40276</v>
+        <v>40267</v>
       </c>
       <c r="G111">
-        <v>57997</v>
+        <v>57984</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>84583</v>
+        <v>98747</v>
       </c>
       <c r="E115">
         <v>115755</v>
       </c>
       <c r="F115">
-        <v>99583</v>
+        <v>113747</v>
       </c>
       <c r="G115">
-        <v>143400</v>
+        <v>163796</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>111758</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>144698</v>
       </c>
       <c r="F117">
-        <v>126758</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>182532</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,7 +5569,7 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43321</v>
+        <v>43340</v>
       </c>
       <c r="E118">
         <v>57868</v>
@@ -5581,7 +5581,7 @@
         <v>84023</v>
       </c>
       <c r="H118">
-        <v>15028</v>
+        <v>15009</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60528</v>
+        <v>60552</v>
       </c>
       <c r="E120">
         <v>79576</v>
       </c>
       <c r="F120">
-        <v>78805</v>
+        <v>75552</v>
       </c>
       <c r="G120">
-        <v>113479</v>
+        <v>108795</v>
       </c>
       <c r="H120">
-        <v>18277</v>
+        <v>15000</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53477</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>79576</v>
       </c>
       <c r="F121">
-        <v>68477</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>98607</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>53056</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>90429</v>
       </c>
       <c r="F122">
-        <v>69713</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>100387</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>16657</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>32027</v>
+        <v>34906</v>
       </c>
       <c r="E123">
         <v>90429</v>
       </c>
       <c r="F123">
-        <v>54078</v>
+        <v>55230</v>
       </c>
       <c r="G123">
-        <v>77872</v>
+        <v>79531</v>
       </c>
       <c r="H123">
-        <v>22051</v>
+        <v>20324</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7301</v>
+        <v>8029</v>
       </c>
       <c r="E125">
         <v>43397</v>
       </c>
       <c r="F125">
-        <v>25845</v>
+        <v>26136</v>
       </c>
       <c r="G125">
-        <v>37217</v>
+        <v>37636</v>
       </c>
       <c r="H125">
-        <v>18544</v>
+        <v>18107</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20046</v>
+        <v>20018</v>
       </c>
       <c r="E129">
         <v>59297</v>
       </c>
       <c r="F129">
-        <v>37144</v>
+        <v>37133</v>
       </c>
       <c r="G129">
-        <v>53487</v>
+        <v>53472</v>
       </c>
       <c r="H129">
-        <v>17098</v>
+        <v>17115</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20046</v>
+        <v>20018</v>
       </c>
       <c r="E131">
         <v>73878</v>
       </c>
       <c r="F131">
-        <v>42831</v>
+        <v>42820</v>
       </c>
       <c r="G131">
-        <v>61677</v>
+        <v>61661</v>
       </c>
       <c r="H131">
-        <v>22785</v>
+        <v>22802</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33041</v>
+        <v>37354</v>
       </c>
       <c r="E133">
         <v>92998</v>
       </c>
       <c r="F133">
-        <v>55486</v>
+        <v>57211</v>
       </c>
       <c r="G133">
-        <v>79900</v>
+        <v>82384</v>
       </c>
       <c r="H133">
-        <v>22445</v>
+        <v>19857</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37144</v>
+        <v>37089</v>
       </c>
       <c r="E140">
         <v>90429</v>
       </c>
       <c r="F140">
-        <v>61551</v>
+        <v>61529</v>
       </c>
       <c r="G140">
-        <v>88633</v>
+        <v>88602</v>
       </c>
       <c r="H140">
-        <v>24407</v>
+        <v>24440</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,7 +6618,7 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26551</v>
+        <v>26550</v>
       </c>
       <c r="E142">
         <v>90429</v>
@@ -6630,7 +6630,7 @@
         <v>86589</v>
       </c>
       <c r="H142">
-        <v>33580</v>
+        <v>33581</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,7 +6662,7 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27160</v>
+        <v>27158</v>
       </c>
       <c r="E143">
         <v>90429</v>
@@ -6674,7 +6674,7 @@
         <v>75069</v>
       </c>
       <c r="H143">
-        <v>24971</v>
+        <v>24973</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45817</v>
+        <v>45164</v>
       </c>
       <c r="E144">
         <v>90429</v>
       </c>
       <c r="F144">
-        <v>67822</v>
+        <v>64759</v>
       </c>
       <c r="G144">
-        <v>97664</v>
+        <v>93253</v>
       </c>
       <c r="H144">
-        <v>22005</v>
+        <v>19595</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>79108</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>90429</v>
       </c>
       <c r="F145">
-        <v>94108</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>135516</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>57954</v>
+        <v>0</v>
       </c>
       <c r="E146">
         <v>90429</v>
       </c>
       <c r="F146">
-        <v>92954</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>133854</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>93616</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>90429</v>
       </c>
       <c r="F147">
-        <v>108616</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>156407</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36504</v>
+        <v>36527</v>
       </c>
       <c r="E148">
         <v>61486</v>
@@ -6895,7 +6895,7 @@
         <v>92032</v>
       </c>
       <c r="H148">
-        <v>27407</v>
+        <v>27384</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15522</v>
+        <v>15512</v>
       </c>
       <c r="E151">
         <v>54250</v>
       </c>
       <c r="F151">
-        <v>33367</v>
+        <v>33363</v>
       </c>
       <c r="G151">
-        <v>48048</v>
+        <v>48043</v>
       </c>
       <c r="H151">
-        <v>17845</v>
+        <v>17851</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37362</v>
+        <v>37151</v>
       </c>
       <c r="E152">
         <v>72340</v>
@@ -7070,7 +7070,7 @@
         <v>78127</v>
       </c>
       <c r="H152">
-        <v>16893</v>
+        <v>17104</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33275</v>
+        <v>34984</v>
       </c>
       <c r="E153">
         <v>72340</v>
       </c>
       <c r="F153">
-        <v>48275</v>
+        <v>49984</v>
       </c>
       <c r="G153">
-        <v>69516</v>
+        <v>71977</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56472</v>
+        <v>56405</v>
       </c>
       <c r="E154">
         <v>72340</v>
       </c>
       <c r="F154">
-        <v>83819</v>
+        <v>83704</v>
       </c>
       <c r="G154">
-        <v>120699</v>
+        <v>120534</v>
       </c>
       <c r="H154">
-        <v>27347</v>
+        <v>27299</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>57845</v>
+        <v>57730</v>
       </c>
       <c r="E155">
         <v>72340</v>
       </c>
       <c r="F155">
-        <v>72845</v>
+        <v>72730</v>
       </c>
       <c r="G155">
-        <v>104897</v>
+        <v>104731</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7281,16 +7281,16 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11903</v>
+        <v>11880</v>
       </c>
       <c r="E157">
         <v>27116</v>
       </c>
       <c r="F157">
-        <v>26903</v>
+        <v>26880</v>
       </c>
       <c r="G157">
-        <v>38740</v>
+        <v>38707</v>
       </c>
       <c r="H157">
         <v>15000</v>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>84646</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>83194</v>
       </c>
       <c r="F158">
-        <v>99646</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>143490</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54269</v>
       </c>
       <c r="F160">
-        <v>38572</v>
+        <v>38545</v>
       </c>
       <c r="G160">
-        <v>55544</v>
+        <v>55505</v>
       </c>
       <c r="H160">
-        <v>30892</v>
+        <v>30865</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8518</v>
+        <v>8450</v>
       </c>
       <c r="E161">
         <v>54269</v>
       </c>
       <c r="F161">
-        <v>30572</v>
+        <v>30545</v>
       </c>
       <c r="G161">
-        <v>44024</v>
+        <v>43985</v>
       </c>
       <c r="H161">
-        <v>22054</v>
+        <v>22095</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>72340</v>
       </c>
       <c r="F162">
-        <v>44048</v>
+        <v>44011</v>
       </c>
       <c r="G162">
-        <v>63429</v>
+        <v>63376</v>
       </c>
       <c r="H162">
-        <v>33901</v>
+        <v>33864</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9048</v>
+        <v>9011</v>
       </c>
       <c r="E163">
         <v>72340</v>
       </c>
       <c r="F163">
-        <v>36048</v>
+        <v>36011</v>
       </c>
       <c r="G163">
-        <v>51909</v>
+        <v>51856</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>66908</v>
+        <v>66866</v>
       </c>
       <c r="E164">
         <v>67836</v>
       </c>
       <c r="F164">
-        <v>82013</v>
+        <v>82001</v>
       </c>
       <c r="G164">
-        <v>118099</v>
+        <v>118081</v>
       </c>
       <c r="H164">
-        <v>15105</v>
+        <v>15135</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20670</v>
+        <v>20641</v>
       </c>
       <c r="E165">
         <v>67836</v>
       </c>
       <c r="F165">
-        <v>40724</v>
+        <v>40712</v>
       </c>
       <c r="G165">
-        <v>58643</v>
+        <v>58625</v>
       </c>
       <c r="H165">
-        <v>20054</v>
+        <v>20071</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>89840</v>
+        <v>89783</v>
       </c>
       <c r="E166">
         <v>102206</v>
       </c>
       <c r="F166">
-        <v>105245</v>
+        <v>105246</v>
       </c>
       <c r="G166">
-        <v>151553</v>
+        <v>151554</v>
       </c>
       <c r="H166">
-        <v>15405</v>
+        <v>15463</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21731</v>
+        <v>21732</v>
       </c>
       <c r="E167">
         <v>102206</v>
       </c>
       <c r="F167">
-        <v>48731</v>
+        <v>48732</v>
       </c>
       <c r="G167">
-        <v>70173</v>
+        <v>70174</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8814</v>
+        <v>8793</v>
       </c>
       <c r="E169">
         <v>72340</v>
       </c>
       <c r="F169">
-        <v>35814</v>
+        <v>35793</v>
       </c>
       <c r="G169">
-        <v>51572</v>
+        <v>51542</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58484</v>
+        <v>58447</v>
       </c>
       <c r="E170">
         <v>108519</v>
       </c>
       <c r="F170">
-        <v>80724</v>
+        <v>78212</v>
       </c>
       <c r="G170">
-        <v>116243</v>
+        <v>112625</v>
       </c>
       <c r="H170">
-        <v>22240</v>
+        <v>19765</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>54506</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>108519</v>
       </c>
       <c r="F171">
-        <v>70125</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>100980</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>15619</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77360</v>
+        <v>77311</v>
       </c>
       <c r="E172">
         <v>144698</v>
       </c>
       <c r="F172">
-        <v>107831</v>
+        <v>102039</v>
       </c>
       <c r="G172">
-        <v>155277</v>
+        <v>146936</v>
       </c>
       <c r="H172">
-        <v>30471</v>
+        <v>24728</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78078</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>144698</v>
       </c>
       <c r="F173">
-        <v>93664</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>134876</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>15586</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48655</v>
+        <v>48516</v>
       </c>
       <c r="E174">
         <v>90429</v>
@@ -8045,7 +8045,7 @@
         <v>97664</v>
       </c>
       <c r="H174">
-        <v>19167</v>
+        <v>19306</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26177</v>
+        <v>25630</v>
       </c>
       <c r="E178">
         <v>108519</v>
       </c>
       <c r="F178">
-        <v>53177</v>
+        <v>52630</v>
       </c>
       <c r="G178">
-        <v>76575</v>
+        <v>75787</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>99824</v>
+        <v>99760</v>
       </c>
       <c r="E182">
         <v>126608</v>
       </c>
       <c r="F182">
-        <v>114824</v>
+        <v>114826</v>
       </c>
       <c r="G182">
-        <v>165347</v>
+        <v>165349</v>
       </c>
       <c r="H182">
-        <v>15000</v>
+        <v>15066</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>63804</v>
+        <v>63810</v>
       </c>
       <c r="E183">
         <v>126608</v>
       </c>
       <c r="F183">
-        <v>80899</v>
+        <v>80901</v>
       </c>
       <c r="G183">
-        <v>116495</v>
+        <v>116497</v>
       </c>
       <c r="H183">
-        <v>17095</v>
+        <v>17091</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>143504</v>
+        <v>143412</v>
       </c>
       <c r="E184">
         <v>180877</v>
       </c>
       <c r="F184">
-        <v>159007</v>
+        <v>158919</v>
       </c>
       <c r="G184">
-        <v>228970</v>
+        <v>228843</v>
       </c>
       <c r="H184">
-        <v>15503</v>
+        <v>15507</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>63898</v>
+        <v>63810</v>
       </c>
       <c r="E185">
         <v>180877</v>
       </c>
       <c r="F185">
-        <v>90898</v>
+        <v>90810</v>
       </c>
       <c r="G185">
-        <v>130893</v>
+        <v>130766</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8561,16 +8561,16 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>187184</v>
+        <v>187064</v>
       </c>
       <c r="E186">
         <v>235145</v>
       </c>
       <c r="F186">
-        <v>202184</v>
+        <v>202064</v>
       </c>
       <c r="G186">
-        <v>291145</v>
+        <v>290972</v>
       </c>
       <c r="H186">
         <v>15000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>63898</v>
+        <v>63810</v>
       </c>
       <c r="E187">
         <v>180877</v>
       </c>
       <c r="F187">
-        <v>90898</v>
+        <v>90810</v>
       </c>
       <c r="G187">
-        <v>130893</v>
+        <v>130766</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>288584</v>
+        <v>288399</v>
       </c>
       <c r="E188">
         <v>361772</v>
       </c>
       <c r="F188">
-        <v>323584</v>
+        <v>323399</v>
       </c>
       <c r="G188">
-        <v>465961</v>
+        <v>465695</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>304325</v>
+        <v>303631</v>
       </c>
       <c r="E189">
         <v>361772</v>
       </c>
       <c r="F189">
-        <v>319325</v>
+        <v>318631</v>
       </c>
       <c r="G189">
-        <v>459828</v>
+        <v>458829</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>30623</v>
+        <v>30369</v>
       </c>
       <c r="E190">
         <v>94952</v>
       </c>
       <c r="F190">
-        <v>65623</v>
+        <v>65369</v>
       </c>
       <c r="G190">
-        <v>94497</v>
+        <v>94131</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44164</v>
+        <v>44057</v>
       </c>
       <c r="E191">
         <v>94952</v>
       </c>
       <c r="F191">
-        <v>60697</v>
+        <v>60654</v>
       </c>
       <c r="G191">
-        <v>87404</v>
+        <v>87342</v>
       </c>
       <c r="H191">
-        <v>16533</v>
+        <v>16597</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>80777</v>
+        <v>42873</v>
       </c>
       <c r="E192">
         <v>122086</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>77873</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>112137</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>50060</v>
+        <v>49826</v>
       </c>
       <c r="E194">
         <v>149401</v>
       </c>
       <c r="F194">
-        <v>77060</v>
+        <v>76826</v>
       </c>
       <c r="G194">
-        <v>110966</v>
+        <v>110629</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -9004,13 +9004,13 @@
         <v>72340</v>
       </c>
       <c r="F196">
-        <v>54255</v>
+        <v>48000</v>
       </c>
       <c r="G196">
-        <v>78127</v>
+        <v>69120</v>
       </c>
       <c r="H196">
-        <v>30637</v>
+        <v>24382</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32183</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>72340</v>
       </c>
       <c r="F197">
-        <v>47183</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>67944</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26036</v>
+        <v>26020</v>
       </c>
       <c r="E198">
         <v>108519</v>
       </c>
       <c r="F198">
-        <v>61036</v>
+        <v>53020</v>
       </c>
       <c r="G198">
-        <v>87892</v>
+        <v>76349</v>
       </c>
       <c r="H198">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37128</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>108519</v>
       </c>
       <c r="F199">
-        <v>63173</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>90969</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>26045</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>126608</v>
       </c>
       <c r="F200">
-        <v>46825</v>
+        <v>46817</v>
       </c>
       <c r="G200">
-        <v>67428</v>
+        <v>67416</v>
       </c>
       <c r="H200">
-        <v>32760</v>
+        <v>32752</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11825</v>
+        <v>11817</v>
       </c>
       <c r="E201">
         <v>126608</v>
       </c>
       <c r="F201">
-        <v>38825</v>
+        <v>38817</v>
       </c>
       <c r="G201">
-        <v>55908</v>
+        <v>55896</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22480</v>
+        <v>22434</v>
       </c>
       <c r="E203">
         <v>144698</v>
       </c>
       <c r="F203">
-        <v>49480</v>
+        <v>49434</v>
       </c>
       <c r="G203">
-        <v>71251</v>
+        <v>71185</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>180877</v>
       </c>
       <c r="F204">
-        <v>61005</v>
+        <v>55738</v>
       </c>
       <c r="G204">
-        <v>87847</v>
+        <v>80263</v>
       </c>
       <c r="H204">
-        <v>32267</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26005</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>180877</v>
       </c>
       <c r="F205">
-        <v>53005</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>76327</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24086</v>
+        <v>24055</v>
       </c>
       <c r="E206">
         <v>57868</v>
       </c>
       <c r="F206">
-        <v>41931</v>
+        <v>41927</v>
       </c>
       <c r="G206">
-        <v>60381</v>
+        <v>60375</v>
       </c>
       <c r="H206">
-        <v>17845</v>
+        <v>17872</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12698</v>
+        <v>12690</v>
       </c>
       <c r="E207">
         <v>57868</v>
       </c>
       <c r="F207">
-        <v>33648</v>
+        <v>33644</v>
       </c>
       <c r="G207">
-        <v>48453</v>
+        <v>48447</v>
       </c>
       <c r="H207">
-        <v>20950</v>
+        <v>20954</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22792</v>
+        <v>22746</v>
       </c>
       <c r="E209">
         <v>54250</v>
       </c>
       <c r="F209">
-        <v>37792</v>
+        <v>37746</v>
       </c>
       <c r="G209">
-        <v>54420</v>
+        <v>54354</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40030</v>
+        <v>0</v>
       </c>
       <c r="E211">
         <v>108519</v>
       </c>
       <c r="F211">
-        <v>64334</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>92641</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>24304</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>82898</v>
+        <v>82689</v>
       </c>
       <c r="E213">
         <v>180877</v>
       </c>
       <c r="F213">
-        <v>109701</v>
+        <v>109618</v>
       </c>
       <c r="G213">
-        <v>157969</v>
+        <v>157850</v>
       </c>
       <c r="H213">
-        <v>26803</v>
+        <v>26929</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28439</v>
+        <v>28452</v>
       </c>
       <c r="E214">
         <v>86812</v>
       </c>
       <c r="F214">
-        <v>60250</v>
+        <v>55452</v>
       </c>
       <c r="G214">
-        <v>86760</v>
+        <v>79851</v>
       </c>
       <c r="H214">
-        <v>31811</v>
+        <v>27000</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>30982</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>86812</v>
       </c>
       <c r="F215">
-        <v>52250</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>75240</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>21268</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>63960</v>
+        <v>45305</v>
       </c>
       <c r="E216">
         <v>101283</v>
       </c>
       <c r="F216">
-        <v>98960</v>
+        <v>75962</v>
       </c>
       <c r="G216">
-        <v>142502</v>
+        <v>109385</v>
       </c>
       <c r="H216">
-        <v>35000</v>
+        <v>30657</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88390</v>
+        <v>88193</v>
       </c>
       <c r="E217">
         <v>101283</v>
       </c>
       <c r="F217">
-        <v>103390</v>
+        <v>103193</v>
       </c>
       <c r="G217">
-        <v>148882</v>
+        <v>148598</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>110479</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>130226</v>
       </c>
       <c r="F219">
-        <v>125479</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>180690</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10065,13 +10065,13 @@
         <v>81403</v>
       </c>
       <c r="F220">
-        <v>75646</v>
+        <v>74287</v>
       </c>
       <c r="G220">
-        <v>108930</v>
+        <v>106973</v>
       </c>
       <c r="H220">
-        <v>16359</v>
+        <v>15000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>50606</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>81403</v>
       </c>
       <c r="F221">
-        <v>65606</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>94473</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>73148</v>
+        <v>73102</v>
       </c>
       <c r="E222">
         <v>95874</v>
       </c>
       <c r="F222">
-        <v>88420</v>
+        <v>88151</v>
       </c>
       <c r="G222">
-        <v>127325</v>
+        <v>126937</v>
       </c>
       <c r="H222">
-        <v>15272</v>
+        <v>15049</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>55224</v>
+        <v>54955</v>
       </c>
       <c r="E223">
         <v>95874</v>
       </c>
       <c r="F223">
-        <v>70224</v>
+        <v>69955</v>
       </c>
       <c r="G223">
-        <v>101123</v>
+        <v>100735</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>59677</v>
       </c>
       <c r="F224">
-        <v>41018</v>
+        <v>41016</v>
       </c>
       <c r="G224">
-        <v>59066</v>
+        <v>59063</v>
       </c>
       <c r="H224">
-        <v>24440</v>
+        <v>24438</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>9360</v>
+        <v>9354</v>
       </c>
       <c r="E225">
         <v>59677</v>
       </c>
       <c r="F225">
-        <v>33018</v>
+        <v>33016</v>
       </c>
       <c r="G225">
-        <v>47546</v>
+        <v>47543</v>
       </c>
       <c r="H225">
-        <v>23658</v>
+        <v>23662</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37892</v>
+        <v>37806</v>
       </c>
       <c r="E226">
         <v>72340</v>
       </c>
       <c r="F226">
-        <v>53778</v>
+        <v>53675</v>
       </c>
       <c r="G226">
-        <v>77440</v>
+        <v>77292</v>
       </c>
       <c r="H226">
-        <v>15886</v>
+        <v>15869</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25802</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>72340</v>
       </c>
       <c r="F227">
-        <v>44533</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>64128</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>18731</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83008</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>108519</v>
       </c>
       <c r="F228">
-        <v>98331</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>141597</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>15323</v>
+        <v>0</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13759</v>
+        <v>13158</v>
       </c>
       <c r="E229">
         <v>108519</v>
       </c>
       <c r="F229">
-        <v>40759</v>
+        <v>40158</v>
       </c>
       <c r="G229">
-        <v>58693</v>
+        <v>57828</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19141</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>180877</v>
       </c>
       <c r="F231">
-        <v>46141</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>66443</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10595,13 +10595,13 @@
         <v>52460</v>
       </c>
       <c r="F232">
-        <v>38422</v>
+        <v>34459</v>
       </c>
       <c r="G232">
-        <v>55328</v>
+        <v>49621</v>
       </c>
       <c r="H232">
-        <v>29087</v>
+        <v>25124</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9906</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>52460</v>
       </c>
       <c r="F233">
-        <v>30422</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>43808</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>20516</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52460</v>
       </c>
       <c r="F236">
-        <v>37249</v>
+        <v>37247</v>
       </c>
       <c r="G236">
-        <v>53639</v>
+        <v>53636</v>
       </c>
       <c r="H236">
-        <v>28898</v>
+        <v>28896</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6973</v>
+        <v>6969</v>
       </c>
       <c r="E237">
         <v>52460</v>
       </c>
       <c r="F237">
-        <v>29249</v>
+        <v>29247</v>
       </c>
       <c r="G237">
-        <v>42119</v>
+        <v>42116</v>
       </c>
       <c r="H237">
-        <v>22276</v>
+        <v>22278</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11357</v>
+        <v>11303</v>
       </c>
       <c r="E239">
         <v>52460</v>
       </c>
       <c r="F239">
-        <v>31002</v>
+        <v>30981</v>
       </c>
       <c r="G239">
-        <v>44643</v>
+        <v>44613</v>
       </c>
       <c r="H239">
-        <v>19645</v>
+        <v>19678</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24040</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>70549</v>
       </c>
       <c r="F240">
-        <v>52912</v>
+        <v>0</v>
       </c>
       <c r="G240">
-        <v>76193</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>28872</v>
+        <v>0</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>72290</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>70549</v>
       </c>
       <c r="F241">
-        <v>87290</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>125698</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>33821</v>
+        <v>33830</v>
       </c>
       <c r="E242">
         <v>70549</v>
       </c>
       <c r="F242">
-        <v>51276</v>
+        <v>51279</v>
       </c>
       <c r="G242">
-        <v>73837</v>
+        <v>73842</v>
       </c>
       <c r="H242">
-        <v>17455</v>
+        <v>17449</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92212</v>
+        <v>0</v>
       </c>
       <c r="E246">
         <v>108519</v>
       </c>
       <c r="F246">
-        <v>107212</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>154385</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59171</v>
+        <v>58993</v>
       </c>
       <c r="E248">
         <v>95874</v>
       </c>
       <c r="F248">
-        <v>74902</v>
+        <v>73993</v>
       </c>
       <c r="G248">
-        <v>107859</v>
+        <v>106550</v>
       </c>
       <c r="H248">
-        <v>15731</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48064</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>95874</v>
       </c>
       <c r="F249">
-        <v>63064</v>
+        <v>0</v>
       </c>
       <c r="G249">
-        <v>90812</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73055</v>
+        <v>72899</v>
       </c>
       <c r="E250">
         <v>108519</v>
       </c>
       <c r="F250">
-        <v>103650</v>
+        <v>87899</v>
       </c>
       <c r="G250">
-        <v>149256</v>
+        <v>126575</v>
       </c>
       <c r="H250">
-        <v>30595</v>
+        <v>15000</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>75130</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>108519</v>
       </c>
       <c r="F251">
-        <v>90130</v>
+        <v>0</v>
       </c>
       <c r="G251">
-        <v>129787</v>
+        <v>0</v>
       </c>
       <c r="H251">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11475,13 +11475,13 @@
         <v>52460</v>
       </c>
       <c r="F252">
-        <v>39345</v>
+        <v>34459</v>
       </c>
       <c r="G252">
-        <v>56657</v>
+        <v>49621</v>
       </c>
       <c r="H252">
-        <v>27528</v>
+        <v>22642</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38360</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>52460</v>
       </c>
       <c r="F253">
-        <v>53360</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>76838</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24164</v>
+        <v>24757</v>
       </c>
       <c r="E254">
         <v>70549</v>
       </c>
       <c r="F254">
-        <v>52912</v>
+        <v>47650</v>
       </c>
       <c r="G254">
-        <v>76193</v>
+        <v>68616</v>
       </c>
       <c r="H254">
-        <v>28748</v>
+        <v>22893</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69170</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>70549</v>
       </c>
       <c r="F255">
-        <v>84170</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>121205</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12402</v>
+        <v>12410</v>
       </c>
       <c r="E259">
         <v>50633</v>
       </c>
       <c r="F259">
-        <v>30707</v>
+        <v>30711</v>
       </c>
       <c r="G259">
-        <v>44218</v>
+        <v>44224</v>
       </c>
       <c r="H259">
-        <v>18305</v>
+        <v>18301</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12402</v>
+        <v>12410</v>
       </c>
       <c r="E261">
         <v>63295</v>
       </c>
       <c r="F261">
-        <v>35646</v>
+        <v>35649</v>
       </c>
       <c r="G261">
-        <v>51330</v>
+        <v>51335</v>
       </c>
       <c r="H261">
-        <v>23244</v>
+        <v>23239</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12402</v>
+        <v>12410</v>
       </c>
       <c r="E263">
         <v>72340</v>
       </c>
       <c r="F263">
-        <v>39173</v>
+        <v>39177</v>
       </c>
       <c r="G263">
-        <v>56409</v>
+        <v>56415</v>
       </c>
       <c r="H263">
-        <v>26771</v>
+        <v>26767</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39764</v>
+        <v>39739</v>
       </c>
       <c r="E264">
         <v>59677</v>
       </c>
       <c r="F264">
-        <v>54764</v>
+        <v>58751</v>
       </c>
       <c r="G264">
-        <v>78860</v>
+        <v>84601</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>19012</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>16552</v>
+        <v>24882</v>
       </c>
       <c r="E265">
         <v>59677</v>
       </c>
       <c r="F265">
-        <v>35895</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>51689</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>19343</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35771</v>
+        <v>35498</v>
       </c>
       <c r="E268">
         <v>59677</v>
       </c>
       <c r="F268">
-        <v>50799</v>
+        <v>50615</v>
       </c>
       <c r="G268">
-        <v>73151</v>
+        <v>72886</v>
       </c>
       <c r="H268">
-        <v>15028</v>
+        <v>15117</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23930</v>
+        <v>23681</v>
       </c>
       <c r="E269">
         <v>59677</v>
       </c>
       <c r="F269">
-        <v>38930</v>
+        <v>38746</v>
       </c>
       <c r="G269">
-        <v>56059</v>
+        <v>55794</v>
       </c>
       <c r="H269">
-        <v>15000</v>
+        <v>15065</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>38906</v>
+        <v>38819</v>
       </c>
       <c r="E270">
         <v>66913</v>
       </c>
       <c r="F270">
-        <v>53971</v>
+        <v>53906</v>
       </c>
       <c r="G270">
-        <v>77718</v>
+        <v>77625</v>
       </c>
       <c r="H270">
-        <v>15065</v>
+        <v>15087</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>28938</v>
+        <v>28873</v>
       </c>
       <c r="E271">
         <v>66913</v>
       </c>
       <c r="F271">
-        <v>43938</v>
+        <v>43873</v>
       </c>
       <c r="G271">
-        <v>63271</v>
+        <v>63177</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,16 +12349,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>70855</v>
+        <v>70529</v>
       </c>
       <c r="E272">
         <v>90429</v>
       </c>
       <c r="F272">
-        <v>85855</v>
+        <v>85529</v>
       </c>
       <c r="G272">
-        <v>123631</v>
+        <v>123162</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>20998</v>
+        <v>19846</v>
       </c>
       <c r="E273">
         <v>90429</v>
       </c>
       <c r="F273">
-        <v>47998</v>
+        <v>46846</v>
       </c>
       <c r="G273">
-        <v>69117</v>
+        <v>67458</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10140</v>
+        <v>10118</v>
       </c>
       <c r="E275">
         <v>126608</v>
       </c>
       <c r="F275">
-        <v>37140</v>
+        <v>37118</v>
       </c>
       <c r="G275">
-        <v>53482</v>
+        <v>53450</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,16 +12525,16 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151351</v>
+        <v>151239</v>
       </c>
       <c r="E276">
         <v>162787</v>
       </c>
       <c r="F276">
-        <v>186351</v>
+        <v>186239</v>
       </c>
       <c r="G276">
-        <v>268345</v>
+        <v>268184</v>
       </c>
       <c r="H276">
         <v>35000</v>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101119</v>
+        <v>101023</v>
       </c>
       <c r="E277">
         <v>162787</v>
       </c>
       <c r="F277">
-        <v>116119</v>
+        <v>116023</v>
       </c>
       <c r="G277">
-        <v>167211</v>
+        <v>167073</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,7 +12612,7 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>51589</v>
+        <v>49966</v>
       </c>
       <c r="E278">
         <v>108519</v>
@@ -12624,7 +12624,7 @@
         <v>112347</v>
       </c>
       <c r="H278">
-        <v>26430</v>
+        <v>28053</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>67439</v>
+        <v>67442</v>
       </c>
       <c r="E280">
         <v>126608</v>
       </c>
       <c r="F280">
-        <v>90864</v>
+        <v>90833</v>
       </c>
       <c r="G280">
-        <v>130844</v>
+        <v>130800</v>
       </c>
       <c r="H280">
-        <v>23425</v>
+        <v>23391</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48688</v>
+        <v>48610</v>
       </c>
       <c r="E281">
         <v>126608</v>
       </c>
       <c r="F281">
-        <v>74852</v>
+        <v>74821</v>
       </c>
       <c r="G281">
-        <v>107787</v>
+        <v>107742</v>
       </c>
       <c r="H281">
-        <v>26164</v>
+        <v>26211</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24008</v>
+        <v>24009</v>
       </c>
       <c r="E282">
         <v>54250</v>
@@ -12803,7 +12803,7 @@
         <v>58591</v>
       </c>
       <c r="H282">
-        <v>16680</v>
+        <v>16679</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24508</v>
+        <v>24305</v>
       </c>
       <c r="E283">
         <v>54250</v>
       </c>
       <c r="F283">
-        <v>39508</v>
+        <v>39305</v>
       </c>
       <c r="G283">
-        <v>56892</v>
+        <v>56599</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>18938</v>
+        <v>18926</v>
       </c>
       <c r="E287">
         <v>37970</v>
       </c>
       <c r="F287">
-        <v>33938</v>
+        <v>33926</v>
       </c>
       <c r="G287">
-        <v>48871</v>
+        <v>48853</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31340</v>
+        <v>31320</v>
       </c>
       <c r="E288">
         <v>57868</v>
       </c>
       <c r="F288">
-        <v>48506</v>
+        <v>48427</v>
       </c>
       <c r="G288">
-        <v>69849</v>
+        <v>69735</v>
       </c>
       <c r="H288">
-        <v>17166</v>
+        <v>17107</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25506</v>
+        <v>25427</v>
       </c>
       <c r="E289">
         <v>57868</v>
       </c>
       <c r="F289">
-        <v>40506</v>
+        <v>40427</v>
       </c>
       <c r="G289">
-        <v>58329</v>
+        <v>58215</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>33899</v>
+        <v>33830</v>
       </c>
       <c r="E291">
         <v>43397</v>
       </c>
       <c r="F291">
-        <v>48899</v>
+        <v>48830</v>
       </c>
       <c r="G291">
-        <v>70415</v>
+        <v>70315</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>42619</v>
+        <v>42717</v>
       </c>
       <c r="E292">
         <v>108519</v>
       </c>
       <c r="F292">
-        <v>73009</v>
+        <v>69717</v>
       </c>
       <c r="G292">
-        <v>105133</v>
+        <v>100392</v>
       </c>
       <c r="H292">
-        <v>30390</v>
+        <v>27000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37736</v>
+        <v>0</v>
       </c>
       <c r="E293">
         <v>108519</v>
       </c>
       <c r="F293">
-        <v>63417</v>
+        <v>0</v>
       </c>
       <c r="G293">
-        <v>91320</v>
+        <v>0</v>
       </c>
       <c r="H293">
-        <v>25681</v>
+        <v>0</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54304</v>
+        <v>53287</v>
       </c>
       <c r="E296">
         <v>72340</v>
       </c>
       <c r="F296">
-        <v>89304</v>
+        <v>88287</v>
       </c>
       <c r="G296">
-        <v>128598</v>
+        <v>127133</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>63991</v>
+        <v>63841</v>
       </c>
       <c r="E297">
         <v>72340</v>
       </c>
       <c r="F297">
-        <v>78991</v>
+        <v>78841</v>
       </c>
       <c r="G297">
-        <v>113747</v>
+        <v>113531</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4368</v>
+        <v>0</v>
       </c>
       <c r="E299">
         <v>54250</v>
       </c>
       <c r="F299">
-        <v>28905</v>
+        <v>0</v>
       </c>
       <c r="G299">
-        <v>41623</v>
+        <v>0</v>
       </c>
       <c r="H299">
-        <v>24537</v>
+        <v>0</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10655</v>
+        <v>10632</v>
       </c>
       <c r="E301">
         <v>68722</v>
       </c>
       <c r="F301">
-        <v>37063</v>
+        <v>37054</v>
       </c>
       <c r="G301">
-        <v>53371</v>
+        <v>53358</v>
       </c>
       <c r="H301">
-        <v>26408</v>
+        <v>26422</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44039</v>
+        <v>44057</v>
       </c>
       <c r="E304">
         <v>108519</v>
       </c>
       <c r="F304">
-        <v>76492</v>
+        <v>76449</v>
       </c>
       <c r="G304">
-        <v>110148</v>
+        <v>110087</v>
       </c>
       <c r="H304">
-        <v>32453</v>
+        <v>32392</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45302</v>
+        <v>45195</v>
       </c>
       <c r="E305">
         <v>108519</v>
       </c>
       <c r="F305">
-        <v>66443</v>
+        <v>66400</v>
       </c>
       <c r="G305">
-        <v>95678</v>
+        <v>95616</v>
       </c>
       <c r="H305">
-        <v>21141</v>
+        <v>21205</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24149</v>
+        <v>24165</v>
       </c>
       <c r="E306">
         <v>108519</v>
       </c>
       <c r="F306">
-        <v>59149</v>
+        <v>59165</v>
       </c>
       <c r="G306">
-        <v>85175</v>
+        <v>85198</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33181</v>
+        <v>33113</v>
       </c>
       <c r="E307">
         <v>108519</v>
       </c>
       <c r="F307">
-        <v>60181</v>
+        <v>60113</v>
       </c>
       <c r="G307">
-        <v>86661</v>
+        <v>86563</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>188807</v>
+        <v>188904</v>
       </c>
       <c r="E308">
         <v>235145</v>
       </c>
       <c r="F308">
-        <v>204334</v>
+        <v>204009</v>
       </c>
       <c r="G308">
-        <v>294241</v>
+        <v>293773</v>
       </c>
       <c r="H308">
-        <v>15527</v>
+        <v>15105</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>140884</v>
+        <v>140559</v>
       </c>
       <c r="E309">
         <v>235145</v>
       </c>
       <c r="F309">
-        <v>155884</v>
+        <v>155559</v>
       </c>
       <c r="G309">
-        <v>224473</v>
+        <v>224005</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>68203</v>
+        <v>67863</v>
       </c>
       <c r="E310">
         <v>126608</v>
       </c>
       <c r="F310">
-        <v>90255</v>
+        <v>90119</v>
       </c>
       <c r="G310">
-        <v>129967</v>
+        <v>129771</v>
       </c>
       <c r="H310">
-        <v>22052</v>
+        <v>22256</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>53380</v>
       </c>
       <c r="E311">
         <v>126608</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>76729</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>110490</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>23349</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>109964</v>
+        <v>109707</v>
       </c>
       <c r="E313">
         <v>180877</v>
       </c>
       <c r="F313">
-        <v>124964</v>
+        <v>124707</v>
       </c>
       <c r="G313">
-        <v>179948</v>
+        <v>179578</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>129433</v>
+        <v>124408</v>
       </c>
       <c r="E314">
         <v>235145</v>
       </c>
       <c r="F314">
-        <v>164433</v>
+        <v>159408</v>
       </c>
       <c r="G314">
-        <v>236784</v>
+        <v>229548</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>146936</v>
+        <v>146608</v>
       </c>
       <c r="E315">
         <v>235145</v>
       </c>
       <c r="F315">
-        <v>161936</v>
+        <v>161608</v>
       </c>
       <c r="G315">
-        <v>233188</v>
+        <v>232716</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,7 +481,7 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71153</v>
+        <v>71257</v>
       </c>
       <c r="E2">
         <v>72340</v>
@@ -493,7 +493,7 @@
         <v>124357</v>
       </c>
       <c r="H2">
-        <v>15206</v>
+        <v>15102</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4240</v>
+        <v>4251</v>
       </c>
       <c r="E7">
         <v>54250</v>
       </c>
       <c r="F7">
-        <v>28854</v>
+        <v>28858</v>
       </c>
       <c r="G7">
-        <v>41550</v>
+        <v>41556</v>
       </c>
       <c r="H7">
-        <v>24614</v>
+        <v>24607</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33815</v>
+        <v>33901</v>
       </c>
       <c r="E8">
         <v>72340</v>
       </c>
       <c r="F8">
-        <v>52079</v>
+        <v>54010</v>
       </c>
       <c r="G8">
-        <v>74994</v>
+        <v>77774</v>
       </c>
       <c r="H8">
-        <v>18264</v>
+        <v>20109</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>29494</v>
       </c>
       <c r="E9">
         <v>72340</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>46010</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>66254</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>16516</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>40966</v>
       </c>
       <c r="E11">
         <v>108519</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>64709</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>93181</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>23743</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>75019</v>
+        <v>75212</v>
       </c>
       <c r="E12">
         <v>81385</v>
       </c>
       <c r="F12">
-        <v>91979</v>
+        <v>92009</v>
       </c>
       <c r="G12">
-        <v>132450</v>
+        <v>132493</v>
       </c>
       <c r="H12">
-        <v>16960</v>
+        <v>16797</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11630</v>
+        <v>11660</v>
       </c>
       <c r="E13">
         <v>81385</v>
       </c>
       <c r="F13">
-        <v>38630</v>
+        <v>38660</v>
       </c>
       <c r="G13">
-        <v>55627</v>
+        <v>55670</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>35062</v>
+        <v>34964</v>
       </c>
       <c r="E21">
         <v>101283</v>
       </c>
       <c r="F21">
-        <v>59525</v>
+        <v>59486</v>
       </c>
       <c r="G21">
-        <v>85716</v>
+        <v>85660</v>
       </c>
       <c r="H21">
-        <v>24463</v>
+        <v>24522</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>52564</v>
       </c>
       <c r="E23">
         <v>130226</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>77814</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>112052</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>25250</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>18038</v>
+        <v>17646</v>
       </c>
       <c r="E27">
         <v>63295</v>
       </c>
       <c r="F27">
-        <v>37900</v>
+        <v>37744</v>
       </c>
       <c r="G27">
-        <v>54576</v>
+        <v>54351</v>
       </c>
       <c r="H27">
-        <v>19862</v>
+        <v>20098</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74271</v>
+        <v>74321</v>
       </c>
       <c r="E28">
         <v>126608</v>
       </c>
       <c r="F28">
-        <v>93161</v>
+        <v>93226</v>
       </c>
       <c r="G28">
-        <v>134152</v>
+        <v>134245</v>
       </c>
       <c r="H28">
-        <v>18890</v>
+        <v>18905</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25006</v>
+        <v>25071</v>
       </c>
       <c r="E29">
         <v>126608</v>
       </c>
       <c r="F29">
-        <v>52006</v>
+        <v>52071</v>
       </c>
       <c r="G29">
-        <v>74889</v>
+        <v>74982</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,16 +1709,16 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>129989</v>
+        <v>130120</v>
       </c>
       <c r="E30">
         <v>180877</v>
       </c>
       <c r="F30">
-        <v>164989</v>
+        <v>165120</v>
       </c>
       <c r="G30">
-        <v>237584</v>
+        <v>237773</v>
       </c>
       <c r="H30">
         <v>35000</v>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>77233</v>
+        <v>77431</v>
       </c>
       <c r="E31">
         <v>180877</v>
       </c>
       <c r="F31">
-        <v>104233</v>
+        <v>104431</v>
       </c>
       <c r="G31">
-        <v>150096</v>
+        <v>150381</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71075</v>
+        <v>71257</v>
       </c>
       <c r="E32">
         <v>108519</v>
       </c>
       <c r="F32">
-        <v>89652</v>
+        <v>89540</v>
       </c>
       <c r="G32">
-        <v>129099</v>
+        <v>128938</v>
       </c>
       <c r="H32">
-        <v>18577</v>
+        <v>18283</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>49857</v>
+        <v>49578</v>
       </c>
       <c r="E33">
         <v>108519</v>
       </c>
       <c r="F33">
-        <v>68265</v>
+        <v>68153</v>
       </c>
       <c r="G33">
-        <v>98302</v>
+        <v>98140</v>
       </c>
       <c r="H33">
-        <v>18408</v>
+        <v>18575</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>75634</v>
       </c>
       <c r="E35">
         <v>126608</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>90634</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>130513</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44416</v>
+        <v>44530</v>
       </c>
       <c r="E36">
         <v>126608</v>
       </c>
       <c r="F36">
-        <v>71416</v>
+        <v>71781</v>
       </c>
       <c r="G36">
-        <v>102839</v>
+        <v>103365</v>
       </c>
       <c r="H36">
-        <v>27000</v>
+        <v>27251</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35418</v>
       </c>
       <c r="E37">
         <v>126608</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62418</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89882</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>81972</v>
+        <v>82183</v>
       </c>
       <c r="E39">
         <v>235145</v>
       </c>
       <c r="F39">
-        <v>108972</v>
+        <v>109183</v>
       </c>
       <c r="G39">
-        <v>156920</v>
+        <v>157224</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>81972</v>
+        <v>82183</v>
       </c>
       <c r="E41">
         <v>235145</v>
       </c>
       <c r="F41">
-        <v>108972</v>
+        <v>109183</v>
       </c>
       <c r="G41">
-        <v>156920</v>
+        <v>157224</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38835</v>
+        <v>38934</v>
       </c>
       <c r="E43">
         <v>126608</v>
       </c>
       <c r="F43">
-        <v>65835</v>
+        <v>65934</v>
       </c>
       <c r="G43">
-        <v>94802</v>
+        <v>94945</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92184</v>
+        <v>92420</v>
       </c>
       <c r="E45">
         <v>180877</v>
       </c>
       <c r="F45">
-        <v>113416</v>
+        <v>113510</v>
       </c>
       <c r="G45">
-        <v>163319</v>
+        <v>163454</v>
       </c>
       <c r="H45">
-        <v>21232</v>
+        <v>21090</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27298</v>
+        <v>25743</v>
       </c>
       <c r="E47">
         <v>108519</v>
       </c>
       <c r="F47">
-        <v>54298</v>
+        <v>52743</v>
       </c>
       <c r="G47">
-        <v>78189</v>
+        <v>75950</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35530</v>
+        <v>35621</v>
       </c>
       <c r="E50">
         <v>63295</v>
       </c>
       <c r="F50">
-        <v>58452</v>
+        <v>56714</v>
       </c>
       <c r="G50">
-        <v>84171</v>
+        <v>81668</v>
       </c>
       <c r="H50">
-        <v>22922</v>
+        <v>21093</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>35452</v>
+        <v>33714</v>
       </c>
       <c r="E51">
         <v>63295</v>
       </c>
       <c r="F51">
-        <v>50452</v>
+        <v>48714</v>
       </c>
       <c r="G51">
-        <v>72651</v>
+        <v>70148</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48002</v>
+        <v>48125</v>
       </c>
       <c r="E54">
         <v>126608</v>
       </c>
       <c r="F54">
-        <v>83002</v>
+        <v>83125</v>
       </c>
       <c r="G54">
-        <v>119523</v>
+        <v>119700</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>51759</v>
+        <v>51892</v>
       </c>
       <c r="E55">
         <v>126608</v>
       </c>
       <c r="F55">
-        <v>76081</v>
+        <v>76134</v>
       </c>
       <c r="G55">
-        <v>109557</v>
+        <v>109633</v>
       </c>
       <c r="H55">
-        <v>24322</v>
+        <v>24242</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62251</v>
+        <v>62411</v>
       </c>
       <c r="E57">
         <v>144698</v>
       </c>
       <c r="F57">
-        <v>87333</v>
+        <v>87397</v>
       </c>
       <c r="G57">
-        <v>125760</v>
+        <v>125852</v>
       </c>
       <c r="H57">
-        <v>25082</v>
+        <v>24986</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>24523</v>
+        <v>24430</v>
       </c>
       <c r="E58">
         <v>36161</v>
       </c>
       <c r="F58">
-        <v>39523</v>
+        <v>39529</v>
       </c>
       <c r="G58">
-        <v>56913</v>
+        <v>56922</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>15099</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6174</v>
+        <v>6189</v>
       </c>
       <c r="E59">
         <v>36161</v>
       </c>
       <c r="F59">
-        <v>22573</v>
+        <v>22579</v>
       </c>
       <c r="G59">
-        <v>32505</v>
+        <v>32514</v>
       </c>
       <c r="H59">
-        <v>16399</v>
+        <v>16390</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26020</v>
+        <v>26086</v>
       </c>
       <c r="E60">
         <v>48824</v>
       </c>
       <c r="F60">
-        <v>47757</v>
+        <v>47820</v>
       </c>
       <c r="G60">
-        <v>68770</v>
+        <v>68861</v>
       </c>
       <c r="H60">
-        <v>21737</v>
+        <v>21734</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24757</v>
+        <v>24820</v>
       </c>
       <c r="E61">
         <v>48824</v>
       </c>
       <c r="F61">
-        <v>39757</v>
+        <v>39820</v>
       </c>
       <c r="G61">
-        <v>57250</v>
+        <v>57341</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12753</v>
+        <v>12785</v>
       </c>
       <c r="E63">
         <v>81385</v>
       </c>
       <c r="F63">
-        <v>39753</v>
+        <v>39785</v>
       </c>
       <c r="G63">
-        <v>57244</v>
+        <v>57290</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28452</v>
+        <v>28400</v>
       </c>
       <c r="E65">
         <v>122068</v>
       </c>
       <c r="F65">
-        <v>55452</v>
+        <v>55400</v>
       </c>
       <c r="G65">
-        <v>79851</v>
+        <v>79776</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24414</v>
+        <v>24430</v>
       </c>
       <c r="E66">
         <v>90429</v>
       </c>
       <c r="F66">
-        <v>53459</v>
+        <v>53537</v>
       </c>
       <c r="G66">
-        <v>76981</v>
+        <v>77093</v>
       </c>
       <c r="H66">
-        <v>29045</v>
+        <v>29107</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18459</v>
+        <v>18537</v>
       </c>
       <c r="E67">
         <v>90429</v>
       </c>
       <c r="F67">
-        <v>45459</v>
+        <v>45537</v>
       </c>
       <c r="G67">
-        <v>65461</v>
+        <v>65573</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34251</v>
+        <v>34386</v>
       </c>
       <c r="E68">
         <v>108519</v>
       </c>
       <c r="F68">
-        <v>62517</v>
+        <v>62587</v>
       </c>
       <c r="G68">
-        <v>90024</v>
+        <v>90125</v>
       </c>
       <c r="H68">
-        <v>28266</v>
+        <v>28201</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27329</v>
+        <v>27399</v>
       </c>
       <c r="E69">
         <v>108519</v>
       </c>
       <c r="F69">
-        <v>54329</v>
+        <v>54399</v>
       </c>
       <c r="G69">
-        <v>78234</v>
+        <v>78335</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>44915</v>
+        <v>45030</v>
       </c>
       <c r="E70">
         <v>126608</v>
       </c>
       <c r="F70">
-        <v>79915</v>
+        <v>80030</v>
       </c>
       <c r="G70">
-        <v>115078</v>
+        <v>115243</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50325</v>
+        <v>50454</v>
       </c>
       <c r="E71">
         <v>126608</v>
       </c>
       <c r="F71">
-        <v>75507</v>
+        <v>75559</v>
       </c>
       <c r="G71">
-        <v>108730</v>
+        <v>108805</v>
       </c>
       <c r="H71">
-        <v>25182</v>
+        <v>25105</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5784</v>
+        <v>5689</v>
       </c>
       <c r="E73">
         <v>27116</v>
       </c>
       <c r="F73">
-        <v>20784</v>
+        <v>20689</v>
       </c>
       <c r="G73">
-        <v>29929</v>
+        <v>29792</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>69874</v>
+        <v>70054</v>
       </c>
       <c r="E75">
         <v>94952</v>
       </c>
       <c r="F75">
-        <v>84874</v>
+        <v>85054</v>
       </c>
       <c r="G75">
-        <v>122219</v>
+        <v>122478</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>79119</v>
+        <v>79322</v>
       </c>
       <c r="E76">
         <v>126608</v>
       </c>
       <c r="F76">
-        <v>94621</v>
+        <v>94740</v>
       </c>
       <c r="G76">
-        <v>136254</v>
+        <v>136426</v>
       </c>
       <c r="H76">
-        <v>15502</v>
+        <v>15418</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>46599</v>
+        <v>46718</v>
       </c>
       <c r="E77">
         <v>126608</v>
       </c>
       <c r="F77">
-        <v>73599</v>
+        <v>73718</v>
       </c>
       <c r="G77">
-        <v>105983</v>
+        <v>106154</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36730</v>
+        <v>36824</v>
       </c>
       <c r="E81">
         <v>90429</v>
       </c>
       <c r="F81">
-        <v>55959</v>
+        <v>55997</v>
       </c>
       <c r="G81">
-        <v>80581</v>
+        <v>80636</v>
       </c>
       <c r="H81">
-        <v>19229</v>
+        <v>19173</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48002</v>
+        <v>48187</v>
       </c>
       <c r="E84">
         <v>101283</v>
       </c>
       <c r="F84">
-        <v>70778</v>
+        <v>70852</v>
       </c>
       <c r="G84">
-        <v>101920</v>
+        <v>102027</v>
       </c>
       <c r="H84">
-        <v>22776</v>
+        <v>22665</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31757</v>
+        <v>31776</v>
       </c>
       <c r="E85">
         <v>101283</v>
       </c>
       <c r="F85">
-        <v>58203</v>
+        <v>58211</v>
       </c>
       <c r="G85">
-        <v>83812</v>
+        <v>83824</v>
       </c>
       <c r="H85">
-        <v>26446</v>
+        <v>26435</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4177,13 +4177,13 @@
         <v>144698</v>
       </c>
       <c r="F86">
-        <v>164887</v>
+        <v>165177</v>
       </c>
       <c r="G86">
-        <v>237437</v>
+        <v>237855</v>
       </c>
       <c r="H86">
-        <v>15000</v>
+        <v>15290</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>112918</v>
+        <v>113208</v>
       </c>
       <c r="E87">
         <v>144698</v>
       </c>
       <c r="F87">
-        <v>127918</v>
+        <v>128208</v>
       </c>
       <c r="G87">
-        <v>184202</v>
+        <v>184620</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,16 +4258,16 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>158472</v>
+        <v>158879</v>
       </c>
       <c r="E88">
         <v>159170</v>
       </c>
       <c r="F88">
-        <v>173472</v>
+        <v>173879</v>
       </c>
       <c r="G88">
-        <v>249800</v>
+        <v>250386</v>
       </c>
       <c r="H88">
         <v>15000</v>
@@ -4352,13 +4352,13 @@
         <v>57868</v>
       </c>
       <c r="F90">
-        <v>38264</v>
+        <v>38269</v>
       </c>
       <c r="G90">
-        <v>55100</v>
+        <v>55107</v>
       </c>
       <c r="H90">
-        <v>30584</v>
+        <v>30589</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4240</v>
+        <v>4251</v>
       </c>
       <c r="E91">
         <v>57868</v>
       </c>
       <c r="F91">
-        <v>30264</v>
+        <v>30269</v>
       </c>
       <c r="G91">
-        <v>43580</v>
+        <v>43587</v>
       </c>
       <c r="H91">
-        <v>26024</v>
+        <v>26018</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4614,13 +4614,13 @@
         <v>81385</v>
       </c>
       <c r="F96">
-        <v>76296</v>
+        <v>76330</v>
       </c>
       <c r="G96">
-        <v>109866</v>
+        <v>109915</v>
       </c>
       <c r="H96">
-        <v>15121</v>
+        <v>15155</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33269</v>
+        <v>33354</v>
       </c>
       <c r="E97">
         <v>81385</v>
       </c>
       <c r="F97">
-        <v>51048</v>
+        <v>51082</v>
       </c>
       <c r="G97">
-        <v>73509</v>
+        <v>73558</v>
       </c>
       <c r="H97">
-        <v>17779</v>
+        <v>17728</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4704,13 +4704,13 @@
         <v>94047</v>
       </c>
       <c r="F98">
-        <v>89235</v>
+        <v>89269</v>
       </c>
       <c r="G98">
-        <v>128498</v>
+        <v>128547</v>
       </c>
       <c r="H98">
-        <v>15042</v>
+        <v>15076</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33269</v>
+        <v>33354</v>
       </c>
       <c r="E99">
         <v>94047</v>
       </c>
       <c r="F99">
-        <v>55986</v>
+        <v>56020</v>
       </c>
       <c r="G99">
-        <v>80620</v>
+        <v>80669</v>
       </c>
       <c r="H99">
-        <v>22717</v>
+        <v>22666</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>60910</v>
+        <v>61066</v>
       </c>
       <c r="E100">
         <v>105444</v>
@@ -4800,7 +4800,7 @@
         <v>113880</v>
       </c>
       <c r="H100">
-        <v>18173</v>
+        <v>18017</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>60863</v>
+        <v>61020</v>
       </c>
       <c r="E101">
         <v>105444</v>
       </c>
       <c r="F101">
-        <v>75863</v>
+        <v>76020</v>
       </c>
       <c r="G101">
-        <v>109243</v>
+        <v>109469</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68269</v>
+        <v>68444</v>
       </c>
       <c r="E105">
         <v>126608</v>
       </c>
       <c r="F105">
-        <v>83269</v>
+        <v>83444</v>
       </c>
       <c r="G105">
-        <v>119907</v>
+        <v>120159</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>99985</v>
       </c>
       <c r="E107">
         <v>180877</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>116536</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>167812</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>16551</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4069</v>
+        <v>3954</v>
       </c>
       <c r="E109">
         <v>126608</v>
       </c>
       <c r="F109">
-        <v>31069</v>
+        <v>30954</v>
       </c>
       <c r="G109">
-        <v>44739</v>
+        <v>44574</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13267</v>
+        <v>13301</v>
       </c>
       <c r="E111">
         <v>162787</v>
       </c>
       <c r="F111">
-        <v>40267</v>
+        <v>40301</v>
       </c>
       <c r="G111">
-        <v>57984</v>
+        <v>58033</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>98747</v>
+        <v>84605</v>
       </c>
       <c r="E115">
         <v>115755</v>
       </c>
       <c r="F115">
-        <v>113747</v>
+        <v>99605</v>
       </c>
       <c r="G115">
-        <v>163796</v>
+        <v>143431</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>115162</v>
       </c>
       <c r="E117">
         <v>144698</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>130162</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>187433</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5575,13 +5575,13 @@
         <v>57868</v>
       </c>
       <c r="F118">
-        <v>58349</v>
+        <v>58340</v>
       </c>
       <c r="G118">
-        <v>84023</v>
+        <v>84010</v>
       </c>
       <c r="H118">
-        <v>15009</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>31689</v>
+        <v>31666</v>
       </c>
       <c r="E119">
         <v>57868</v>
       </c>
       <c r="F119">
-        <v>46689</v>
+        <v>46666</v>
       </c>
       <c r="G119">
-        <v>67232</v>
+        <v>67199</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5664,13 +5664,13 @@
         <v>79576</v>
       </c>
       <c r="F120">
-        <v>75552</v>
+        <v>78759</v>
       </c>
       <c r="G120">
-        <v>108795</v>
+        <v>113413</v>
       </c>
       <c r="H120">
-        <v>15000</v>
+        <v>18207</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>53486</v>
       </c>
       <c r="E121">
         <v>79576</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>68486</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>98620</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>53079</v>
       </c>
       <c r="E122">
         <v>90429</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>68079</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>98034</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>34906</v>
+        <v>34230</v>
       </c>
       <c r="E123">
         <v>90429</v>
       </c>
       <c r="F123">
-        <v>55230</v>
+        <v>54959</v>
       </c>
       <c r="G123">
-        <v>79531</v>
+        <v>79141</v>
       </c>
       <c r="H123">
-        <v>20324</v>
+        <v>20729</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>8029</v>
+        <v>7299</v>
       </c>
       <c r="E125">
         <v>43397</v>
       </c>
       <c r="F125">
-        <v>26136</v>
+        <v>25844</v>
       </c>
       <c r="G125">
-        <v>37636</v>
+        <v>37215</v>
       </c>
       <c r="H125">
-        <v>18107</v>
+        <v>18545</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20018</v>
+        <v>20069</v>
       </c>
       <c r="E129">
         <v>59297</v>
       </c>
       <c r="F129">
-        <v>37133</v>
+        <v>37153</v>
       </c>
       <c r="G129">
-        <v>53472</v>
+        <v>53500</v>
       </c>
       <c r="H129">
-        <v>17115</v>
+        <v>17084</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20018</v>
+        <v>20069</v>
       </c>
       <c r="E131">
         <v>73878</v>
       </c>
       <c r="F131">
-        <v>42820</v>
+        <v>42840</v>
       </c>
       <c r="G131">
-        <v>61661</v>
+        <v>61690</v>
       </c>
       <c r="H131">
-        <v>22802</v>
+        <v>22771</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37354</v>
+        <v>33042</v>
       </c>
       <c r="E133">
         <v>92998</v>
       </c>
       <c r="F133">
-        <v>57211</v>
+        <v>55486</v>
       </c>
       <c r="G133">
-        <v>82384</v>
+        <v>79900</v>
       </c>
       <c r="H133">
-        <v>19857</v>
+        <v>22444</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37089</v>
+        <v>37184</v>
       </c>
       <c r="E140">
         <v>90429</v>
       </c>
       <c r="F140">
-        <v>61529</v>
+        <v>61567</v>
       </c>
       <c r="G140">
-        <v>88602</v>
+        <v>88656</v>
       </c>
       <c r="H140">
-        <v>24440</v>
+        <v>24383</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26550</v>
+        <v>26618</v>
       </c>
       <c r="E142">
         <v>90429</v>
       </c>
       <c r="F142">
-        <v>60131</v>
+        <v>60158</v>
       </c>
       <c r="G142">
-        <v>86589</v>
+        <v>86628</v>
       </c>
       <c r="H142">
-        <v>33581</v>
+        <v>33540</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27158</v>
+        <v>27227</v>
       </c>
       <c r="E143">
         <v>90429</v>
       </c>
       <c r="F143">
-        <v>52131</v>
+        <v>52158</v>
       </c>
       <c r="G143">
-        <v>75069</v>
+        <v>75108</v>
       </c>
       <c r="H143">
-        <v>24973</v>
+        <v>24931</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45164</v>
+        <v>44624</v>
       </c>
       <c r="E144">
         <v>90429</v>
       </c>
       <c r="F144">
-        <v>64759</v>
+        <v>67822</v>
       </c>
       <c r="G144">
-        <v>93253</v>
+        <v>97664</v>
       </c>
       <c r="H144">
-        <v>19595</v>
+        <v>23198</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>79901</v>
       </c>
       <c r="E145">
         <v>90429</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>94901</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>136657</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>57972</v>
       </c>
       <c r="E146">
         <v>90429</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>92972</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>133880</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>93639</v>
       </c>
       <c r="E147">
         <v>90429</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>108639</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>156440</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36527</v>
+        <v>36684</v>
       </c>
       <c r="E148">
         <v>61486</v>
@@ -6895,7 +6895,7 @@
         <v>92032</v>
       </c>
       <c r="H148">
-        <v>27384</v>
+        <v>27227</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15512</v>
+        <v>15239</v>
       </c>
       <c r="E151">
         <v>54250</v>
       </c>
       <c r="F151">
-        <v>33363</v>
+        <v>33253</v>
       </c>
       <c r="G151">
-        <v>48043</v>
+        <v>47884</v>
       </c>
       <c r="H151">
-        <v>17851</v>
+        <v>18014</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37151</v>
+        <v>37246</v>
       </c>
       <c r="E152">
         <v>72340</v>
@@ -7070,7 +7070,7 @@
         <v>78127</v>
       </c>
       <c r="H152">
-        <v>17104</v>
+        <v>17009</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>34984</v>
+        <v>33198</v>
       </c>
       <c r="E153">
         <v>72340</v>
       </c>
       <c r="F153">
-        <v>49984</v>
+        <v>48198</v>
       </c>
       <c r="G153">
-        <v>71977</v>
+        <v>69405</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56405</v>
+        <v>56502</v>
       </c>
       <c r="E154">
         <v>72340</v>
       </c>
       <c r="F154">
-        <v>83704</v>
+        <v>83836</v>
       </c>
       <c r="G154">
-        <v>120534</v>
+        <v>120724</v>
       </c>
       <c r="H154">
-        <v>27299</v>
+        <v>27334</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>57730</v>
+        <v>57862</v>
       </c>
       <c r="E155">
         <v>72340</v>
       </c>
       <c r="F155">
-        <v>72730</v>
+        <v>72862</v>
       </c>
       <c r="G155">
-        <v>104731</v>
+        <v>104921</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="E156">
-        <v>27116</v>
+        <v>59677</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11880</v>
+        <v>11879</v>
       </c>
       <c r="E157">
-        <v>27116</v>
+        <v>59677</v>
       </c>
       <c r="F157">
-        <v>26880</v>
+        <v>34026</v>
       </c>
       <c r="G157">
-        <v>38707</v>
+        <v>48997</v>
       </c>
       <c r="H157">
-        <v>15000</v>
+        <v>22147</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>84668</v>
       </c>
       <c r="E158">
         <v>83194</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>99668</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>143522</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54269</v>
       </c>
       <c r="F160">
-        <v>38545</v>
+        <v>38553</v>
       </c>
       <c r="G160">
-        <v>55505</v>
+        <v>55516</v>
       </c>
       <c r="H160">
-        <v>30865</v>
+        <v>30873</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8450</v>
+        <v>8471</v>
       </c>
       <c r="E161">
         <v>54269</v>
       </c>
       <c r="F161">
-        <v>30545</v>
+        <v>30553</v>
       </c>
       <c r="G161">
-        <v>43985</v>
+        <v>43996</v>
       </c>
       <c r="H161">
-        <v>22095</v>
+        <v>22082</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>72340</v>
       </c>
       <c r="F162">
-        <v>44011</v>
+        <v>44034</v>
       </c>
       <c r="G162">
-        <v>63376</v>
+        <v>63409</v>
       </c>
       <c r="H162">
-        <v>33864</v>
+        <v>33887</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9011</v>
+        <v>9034</v>
       </c>
       <c r="E163">
         <v>72340</v>
       </c>
       <c r="F163">
-        <v>36011</v>
+        <v>36034</v>
       </c>
       <c r="G163">
-        <v>51856</v>
+        <v>51889</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7597,13 +7597,13 @@
         <v>67836</v>
       </c>
       <c r="F164">
-        <v>82001</v>
+        <v>82022</v>
       </c>
       <c r="G164">
-        <v>118081</v>
+        <v>118112</v>
       </c>
       <c r="H164">
-        <v>15135</v>
+        <v>15156</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20641</v>
+        <v>20694</v>
       </c>
       <c r="E165">
         <v>67836</v>
       </c>
       <c r="F165">
-        <v>40712</v>
+        <v>40733</v>
       </c>
       <c r="G165">
-        <v>58625</v>
+        <v>58656</v>
       </c>
       <c r="H165">
-        <v>20071</v>
+        <v>20039</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>89783</v>
+        <v>90013</v>
       </c>
       <c r="E166">
         <v>102206</v>
       </c>
       <c r="F166">
-        <v>105246</v>
+        <v>105302</v>
       </c>
       <c r="G166">
-        <v>151554</v>
+        <v>151635</v>
       </c>
       <c r="H166">
-        <v>15463</v>
+        <v>15289</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21732</v>
+        <v>21788</v>
       </c>
       <c r="E167">
         <v>102206</v>
       </c>
       <c r="F167">
-        <v>48732</v>
+        <v>48788</v>
       </c>
       <c r="G167">
-        <v>70174</v>
+        <v>70255</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>72340</v>
       </c>
       <c r="F168">
-        <v>103821</v>
+        <v>103843</v>
       </c>
       <c r="G168">
-        <v>149502</v>
+        <v>149534</v>
       </c>
       <c r="H168">
-        <v>15000</v>
+        <v>15022</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8793</v>
+        <v>8815</v>
       </c>
       <c r="E169">
         <v>72340</v>
       </c>
       <c r="F169">
-        <v>35793</v>
+        <v>35815</v>
       </c>
       <c r="G169">
-        <v>51542</v>
+        <v>51574</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58447</v>
+        <v>58597</v>
       </c>
       <c r="E170">
         <v>108519</v>
       </c>
       <c r="F170">
-        <v>78212</v>
+        <v>80498</v>
       </c>
       <c r="G170">
-        <v>112625</v>
+        <v>115917</v>
       </c>
       <c r="H170">
-        <v>19765</v>
+        <v>21901</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>54189</v>
       </c>
       <c r="E171">
         <v>108519</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>69998</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>100797</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>15809</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77311</v>
+        <v>77509</v>
       </c>
       <c r="E172">
         <v>144698</v>
       </c>
       <c r="F172">
-        <v>102039</v>
+        <v>107725</v>
       </c>
       <c r="G172">
-        <v>146936</v>
+        <v>155124</v>
       </c>
       <c r="H172">
-        <v>24728</v>
+        <v>30216</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>78103</v>
       </c>
       <c r="E173">
         <v>144698</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>93674</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>134891</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>15571</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48516</v>
+        <v>47734</v>
       </c>
       <c r="E174">
         <v>90429</v>
@@ -8045,7 +8045,7 @@
         <v>97664</v>
       </c>
       <c r="H174">
-        <v>19306</v>
+        <v>20088</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>25630</v>
+        <v>27946</v>
       </c>
       <c r="E178">
         <v>108519</v>
       </c>
       <c r="F178">
-        <v>52630</v>
+        <v>54946</v>
       </c>
       <c r="G178">
-        <v>75787</v>
+        <v>79122</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>25038</v>
+        <v>24570</v>
       </c>
       <c r="E180">
         <v>90429</v>
       </c>
       <c r="F180">
-        <v>52038</v>
+        <v>51570</v>
       </c>
       <c r="G180">
-        <v>74935</v>
+        <v>74261</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8393,13 +8393,13 @@
         <v>126608</v>
       </c>
       <c r="F182">
-        <v>114826</v>
+        <v>114892</v>
       </c>
       <c r="G182">
-        <v>165349</v>
+        <v>165444</v>
       </c>
       <c r="H182">
-        <v>15066</v>
+        <v>15132</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>63810</v>
+        <v>63974</v>
       </c>
       <c r="E183">
         <v>126608</v>
       </c>
       <c r="F183">
-        <v>80901</v>
+        <v>80967</v>
       </c>
       <c r="G183">
-        <v>116497</v>
+        <v>116592</v>
       </c>
       <c r="H183">
-        <v>17091</v>
+        <v>16993</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>143412</v>
+        <v>143780</v>
       </c>
       <c r="E184">
         <v>180877</v>
       </c>
       <c r="F184">
-        <v>158919</v>
+        <v>159083</v>
       </c>
       <c r="G184">
-        <v>228843</v>
+        <v>229080</v>
       </c>
       <c r="H184">
-        <v>15507</v>
+        <v>15303</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>63810</v>
+        <v>63974</v>
       </c>
       <c r="E185">
         <v>180877</v>
       </c>
       <c r="F185">
-        <v>90810</v>
+        <v>90974</v>
       </c>
       <c r="G185">
-        <v>130766</v>
+        <v>131003</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>63810</v>
+        <v>63974</v>
       </c>
       <c r="E187">
         <v>180877</v>
       </c>
       <c r="F187">
-        <v>90810</v>
+        <v>90974</v>
       </c>
       <c r="G187">
-        <v>130766</v>
+        <v>131003</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>288399</v>
+        <v>289139</v>
       </c>
       <c r="E188">
         <v>361772</v>
       </c>
       <c r="F188">
-        <v>323399</v>
+        <v>324139</v>
       </c>
       <c r="G188">
-        <v>465695</v>
+        <v>466760</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>303631</v>
+        <v>304410</v>
       </c>
       <c r="E189">
         <v>361772</v>
       </c>
       <c r="F189">
-        <v>318631</v>
+        <v>319410</v>
       </c>
       <c r="G189">
-        <v>458829</v>
+        <v>459950</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>30369</v>
+        <v>29947</v>
       </c>
       <c r="E190">
         <v>94952</v>
       </c>
       <c r="F190">
-        <v>65369</v>
+        <v>64947</v>
       </c>
       <c r="G190">
-        <v>94131</v>
+        <v>93524</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44057</v>
+        <v>44170</v>
       </c>
       <c r="E191">
         <v>94952</v>
       </c>
       <c r="F191">
-        <v>60654</v>
+        <v>60699</v>
       </c>
       <c r="G191">
-        <v>87342</v>
+        <v>87407</v>
       </c>
       <c r="H191">
-        <v>16597</v>
+        <v>16529</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>42873</v>
+        <v>43389</v>
       </c>
       <c r="E192">
         <v>122086</v>
       </c>
       <c r="F192">
-        <v>77873</v>
+        <v>78389</v>
       </c>
       <c r="G192">
-        <v>112137</v>
+        <v>112880</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>49826</v>
+        <v>49907</v>
       </c>
       <c r="E194">
         <v>149401</v>
       </c>
       <c r="F194">
-        <v>76826</v>
+        <v>76907</v>
       </c>
       <c r="G194">
-        <v>110629</v>
+        <v>110746</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -9004,13 +9004,13 @@
         <v>72340</v>
       </c>
       <c r="F196">
-        <v>48000</v>
+        <v>54255</v>
       </c>
       <c r="G196">
-        <v>69120</v>
+        <v>78127</v>
       </c>
       <c r="H196">
-        <v>24382</v>
+        <v>30637</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>32198</v>
       </c>
       <c r="E197">
         <v>72340</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>47198</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>67965</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26020</v>
+        <v>26086</v>
       </c>
       <c r="E198">
         <v>108519</v>
       </c>
       <c r="F198">
-        <v>53020</v>
+        <v>61086</v>
       </c>
       <c r="G198">
-        <v>76349</v>
+        <v>87964</v>
       </c>
       <c r="H198">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>0</v>
+        <v>37137</v>
       </c>
       <c r="E199">
         <v>108519</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>63177</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>90975</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>26040</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>126608</v>
       </c>
       <c r="F200">
-        <v>46817</v>
+        <v>46848</v>
       </c>
       <c r="G200">
-        <v>67416</v>
+        <v>67461</v>
       </c>
       <c r="H200">
-        <v>32752</v>
+        <v>32783</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11817</v>
+        <v>11848</v>
       </c>
       <c r="E201">
         <v>126608</v>
       </c>
       <c r="F201">
-        <v>38817</v>
+        <v>38848</v>
       </c>
       <c r="G201">
-        <v>55896</v>
+        <v>55941</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22434</v>
+        <v>22492</v>
       </c>
       <c r="E203">
         <v>144698</v>
       </c>
       <c r="F203">
-        <v>49434</v>
+        <v>49492</v>
       </c>
       <c r="G203">
-        <v>71185</v>
+        <v>71268</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>180877</v>
       </c>
       <c r="F204">
-        <v>55738</v>
+        <v>61008</v>
       </c>
       <c r="G204">
-        <v>80263</v>
+        <v>87852</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>32270</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>26008</v>
       </c>
       <c r="E205">
         <v>180877</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>53008</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>76332</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24055</v>
+        <v>24242</v>
       </c>
       <c r="E206">
         <v>57868</v>
       </c>
       <c r="F206">
-        <v>41927</v>
+        <v>42015</v>
       </c>
       <c r="G206">
-        <v>60375</v>
+        <v>60502</v>
       </c>
       <c r="H206">
-        <v>17872</v>
+        <v>17773</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12690</v>
+        <v>12910</v>
       </c>
       <c r="E207">
         <v>57868</v>
       </c>
       <c r="F207">
-        <v>33644</v>
+        <v>33732</v>
       </c>
       <c r="G207">
-        <v>48447</v>
+        <v>48574</v>
       </c>
       <c r="H207">
-        <v>20954</v>
+        <v>20822</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22746</v>
+        <v>22804</v>
       </c>
       <c r="E209">
         <v>54250</v>
       </c>
       <c r="F209">
-        <v>37746</v>
+        <v>37804</v>
       </c>
       <c r="G209">
-        <v>54354</v>
+        <v>54438</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>40044</v>
       </c>
       <c r="E211">
         <v>108519</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>64340</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>92650</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>24296</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>82689</v>
+        <v>82870</v>
       </c>
       <c r="E213">
         <v>180877</v>
       </c>
       <c r="F213">
-        <v>109618</v>
+        <v>109690</v>
       </c>
       <c r="G213">
-        <v>157850</v>
+        <v>157954</v>
       </c>
       <c r="H213">
-        <v>26929</v>
+        <v>26820</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28452</v>
+        <v>28103</v>
       </c>
       <c r="E214">
         <v>86812</v>
       </c>
       <c r="F214">
-        <v>55452</v>
+        <v>60254</v>
       </c>
       <c r="G214">
-        <v>79851</v>
+        <v>86766</v>
       </c>
       <c r="H214">
-        <v>27000</v>
+        <v>32151</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>30994</v>
       </c>
       <c r="E215">
         <v>86812</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>52254</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>75246</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>21260</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45305</v>
+        <v>45421</v>
       </c>
       <c r="E216">
         <v>101283</v>
@@ -9893,7 +9893,7 @@
         <v>109385</v>
       </c>
       <c r="H216">
-        <v>30657</v>
+        <v>30541</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88193</v>
+        <v>88419</v>
       </c>
       <c r="E217">
         <v>101283</v>
       </c>
       <c r="F217">
-        <v>103193</v>
+        <v>103419</v>
       </c>
       <c r="G217">
-        <v>148598</v>
+        <v>148923</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>110176</v>
       </c>
       <c r="E219">
         <v>130226</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>125176</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>180253</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10065,13 +10065,13 @@
         <v>81403</v>
       </c>
       <c r="F220">
-        <v>74287</v>
+        <v>75343</v>
       </c>
       <c r="G220">
-        <v>106973</v>
+        <v>108494</v>
       </c>
       <c r="H220">
-        <v>15000</v>
+        <v>16056</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>50516</v>
       </c>
       <c r="E221">
         <v>81403</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>65516</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>94343</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10155,13 +10155,13 @@
         <v>95874</v>
       </c>
       <c r="F222">
-        <v>88151</v>
+        <v>108102</v>
       </c>
       <c r="G222">
-        <v>126937</v>
+        <v>155667</v>
       </c>
       <c r="H222">
-        <v>15049</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>54955</v>
+        <v>83480</v>
       </c>
       <c r="E223">
         <v>95874</v>
       </c>
       <c r="F223">
-        <v>69955</v>
+        <v>98480</v>
       </c>
       <c r="G223">
-        <v>100735</v>
+        <v>141811</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>59677</v>
       </c>
       <c r="F224">
-        <v>41016</v>
+        <v>41400</v>
       </c>
       <c r="G224">
-        <v>59063</v>
+        <v>59616</v>
       </c>
       <c r="H224">
-        <v>24438</v>
+        <v>24822</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>9354</v>
+        <v>10316</v>
       </c>
       <c r="E225">
         <v>59677</v>
       </c>
       <c r="F225">
-        <v>33016</v>
+        <v>33400</v>
       </c>
       <c r="G225">
-        <v>47543</v>
+        <v>48096</v>
       </c>
       <c r="H225">
-        <v>23662</v>
+        <v>23084</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37806</v>
+        <v>37621</v>
       </c>
       <c r="E226">
         <v>72340</v>
       </c>
       <c r="F226">
-        <v>53675</v>
+        <v>53601</v>
       </c>
       <c r="G226">
-        <v>77292</v>
+        <v>77185</v>
       </c>
       <c r="H226">
-        <v>15869</v>
+        <v>15980</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>25805</v>
       </c>
       <c r="E227">
         <v>72340</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>44535</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>64130</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>18730</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>83027</v>
       </c>
       <c r="E228">
         <v>108519</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>98027</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>141159</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13158</v>
+        <v>13223</v>
       </c>
       <c r="E229">
         <v>108519</v>
       </c>
       <c r="F229">
-        <v>40158</v>
+        <v>40223</v>
       </c>
       <c r="G229">
-        <v>57828</v>
+        <v>57921</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>19100</v>
       </c>
       <c r="E231">
         <v>180877</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>66384</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10595,13 +10595,13 @@
         <v>52460</v>
       </c>
       <c r="F232">
-        <v>34459</v>
+        <v>38423</v>
       </c>
       <c r="G232">
-        <v>49621</v>
+        <v>55329</v>
       </c>
       <c r="H232">
-        <v>25124</v>
+        <v>29088</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>9909</v>
       </c>
       <c r="E233">
         <v>52460</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>30423</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>43809</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>20514</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52460</v>
       </c>
       <c r="F236">
-        <v>37247</v>
+        <v>37235</v>
       </c>
       <c r="G236">
-        <v>53636</v>
+        <v>53618</v>
       </c>
       <c r="H236">
-        <v>28896</v>
+        <v>28884</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6969</v>
+        <v>6940</v>
       </c>
       <c r="E237">
         <v>52460</v>
       </c>
       <c r="F237">
-        <v>29247</v>
+        <v>29235</v>
       </c>
       <c r="G237">
-        <v>42116</v>
+        <v>42098</v>
       </c>
       <c r="H237">
-        <v>22278</v>
+        <v>22295</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11303</v>
+        <v>11332</v>
       </c>
       <c r="E239">
         <v>52460</v>
       </c>
       <c r="F239">
-        <v>30981</v>
+        <v>30992</v>
       </c>
       <c r="G239">
-        <v>44613</v>
+        <v>44628</v>
       </c>
       <c r="H239">
-        <v>19678</v>
+        <v>19660</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>24039</v>
       </c>
       <c r="E240">
         <v>70549</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>52912</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>76193</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>28873</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>70272</v>
       </c>
       <c r="E241">
         <v>70549</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>85272</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>122792</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>33830</v>
+        <v>33964</v>
       </c>
       <c r="E242">
         <v>70549</v>
       </c>
       <c r="F242">
-        <v>51279</v>
+        <v>51333</v>
       </c>
       <c r="G242">
-        <v>73842</v>
+        <v>73920</v>
       </c>
       <c r="H242">
-        <v>17449</v>
+        <v>17369</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>92233</v>
       </c>
       <c r="E246">
         <v>108519</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>107233</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>154416</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>47750</v>
       </c>
       <c r="E249">
         <v>95874</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>62750</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>90360</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72899</v>
+        <v>72945</v>
       </c>
       <c r="E250">
         <v>108519</v>
       </c>
       <c r="F250">
-        <v>87899</v>
+        <v>103815</v>
       </c>
       <c r="G250">
-        <v>126575</v>
+        <v>149494</v>
       </c>
       <c r="H250">
-        <v>15000</v>
+        <v>30870</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>75274</v>
       </c>
       <c r="E251">
         <v>108519</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>90274</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>129995</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11475,13 +11475,13 @@
         <v>52460</v>
       </c>
       <c r="F252">
-        <v>34459</v>
+        <v>39345</v>
       </c>
       <c r="G252">
-        <v>49621</v>
+        <v>56657</v>
       </c>
       <c r="H252">
-        <v>22642</v>
+        <v>27528</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>38372</v>
       </c>
       <c r="E253">
         <v>52460</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>53372</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>76856</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24757</v>
+        <v>24164</v>
       </c>
       <c r="E254">
         <v>70549</v>
       </c>
       <c r="F254">
-        <v>47650</v>
+        <v>52912</v>
       </c>
       <c r="G254">
-        <v>68616</v>
+        <v>76193</v>
       </c>
       <c r="H254">
-        <v>22893</v>
+        <v>28748</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>69194</v>
       </c>
       <c r="E255">
         <v>70549</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>84194</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>121239</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12410</v>
+        <v>12441</v>
       </c>
       <c r="E259">
         <v>50633</v>
       </c>
       <c r="F259">
-        <v>30711</v>
+        <v>30723</v>
       </c>
       <c r="G259">
-        <v>44224</v>
+        <v>44241</v>
       </c>
       <c r="H259">
-        <v>18301</v>
+        <v>18282</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12410</v>
+        <v>12441</v>
       </c>
       <c r="E261">
         <v>63295</v>
       </c>
       <c r="F261">
-        <v>35649</v>
+        <v>35662</v>
       </c>
       <c r="G261">
-        <v>51335</v>
+        <v>51353</v>
       </c>
       <c r="H261">
-        <v>23239</v>
+        <v>23221</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12410</v>
+        <v>12441</v>
       </c>
       <c r="E263">
         <v>72340</v>
       </c>
       <c r="F263">
-        <v>39177</v>
+        <v>39189</v>
       </c>
       <c r="G263">
-        <v>56415</v>
+        <v>56432</v>
       </c>
       <c r="H263">
-        <v>26767</v>
+        <v>26748</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39739</v>
+        <v>39841</v>
       </c>
       <c r="E264">
         <v>59677</v>
       </c>
       <c r="F264">
-        <v>58751</v>
+        <v>54841</v>
       </c>
       <c r="G264">
-        <v>84601</v>
+        <v>78971</v>
       </c>
       <c r="H264">
-        <v>19012</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>24882</v>
+        <v>23914</v>
       </c>
       <c r="E265">
         <v>59677</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>38914</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>56036</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35498</v>
+        <v>35480</v>
       </c>
       <c r="E268">
         <v>59677</v>
       </c>
       <c r="F268">
-        <v>50615</v>
+        <v>50583</v>
       </c>
       <c r="G268">
-        <v>72886</v>
+        <v>72840</v>
       </c>
       <c r="H268">
-        <v>15117</v>
+        <v>15103</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23681</v>
+        <v>23601</v>
       </c>
       <c r="E269">
         <v>59677</v>
       </c>
       <c r="F269">
-        <v>38746</v>
+        <v>38714</v>
       </c>
       <c r="G269">
-        <v>55794</v>
+        <v>55748</v>
       </c>
       <c r="H269">
-        <v>15065</v>
+        <v>15113</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>38819</v>
+        <v>38919</v>
       </c>
       <c r="E270">
         <v>66913</v>
       </c>
       <c r="F270">
-        <v>53906</v>
+        <v>53980</v>
       </c>
       <c r="G270">
-        <v>77625</v>
+        <v>77731</v>
       </c>
       <c r="H270">
-        <v>15087</v>
+        <v>15061</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>28873</v>
+        <v>28947</v>
       </c>
       <c r="E271">
         <v>66913</v>
       </c>
       <c r="F271">
-        <v>43873</v>
+        <v>43947</v>
       </c>
       <c r="G271">
-        <v>63177</v>
+        <v>63284</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12355,13 +12355,13 @@
         <v>90429</v>
       </c>
       <c r="F272">
-        <v>85529</v>
+        <v>85580</v>
       </c>
       <c r="G272">
-        <v>123162</v>
+        <v>123235</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>15051</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>19846</v>
+        <v>19897</v>
       </c>
       <c r="E273">
         <v>90429</v>
       </c>
       <c r="F273">
-        <v>46846</v>
+        <v>46897</v>
       </c>
       <c r="G273">
-        <v>67458</v>
+        <v>67532</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12444,13 +12444,13 @@
         <v>126608</v>
       </c>
       <c r="F274">
-        <v>48854</v>
+        <v>48880</v>
       </c>
       <c r="G274">
-        <v>70350</v>
+        <v>70387</v>
       </c>
       <c r="H274">
-        <v>27000</v>
+        <v>27026</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10118</v>
+        <v>10144</v>
       </c>
       <c r="E275">
         <v>126608</v>
       </c>
       <c r="F275">
-        <v>37118</v>
+        <v>37144</v>
       </c>
       <c r="G275">
-        <v>53450</v>
+        <v>53487</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151239</v>
+        <v>151861</v>
       </c>
       <c r="E276">
         <v>162787</v>
       </c>
       <c r="F276">
-        <v>186239</v>
+        <v>186498</v>
       </c>
       <c r="G276">
-        <v>268184</v>
+        <v>268557</v>
       </c>
       <c r="H276">
-        <v>35000</v>
+        <v>34637</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101023</v>
+        <v>101282</v>
       </c>
       <c r="E277">
         <v>162787</v>
       </c>
       <c r="F277">
-        <v>116023</v>
+        <v>116282</v>
       </c>
       <c r="G277">
-        <v>167073</v>
+        <v>167446</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>49966</v>
+        <v>50094</v>
       </c>
       <c r="E278">
         <v>108519</v>
       </c>
       <c r="F278">
-        <v>78019</v>
+        <v>78069</v>
       </c>
       <c r="G278">
-        <v>112347</v>
+        <v>112419</v>
       </c>
       <c r="H278">
-        <v>28053</v>
+        <v>27975</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48610</v>
+        <v>48734</v>
       </c>
       <c r="E279">
         <v>108519</v>
       </c>
       <c r="F279">
-        <v>67766</v>
+        <v>67816</v>
       </c>
       <c r="G279">
-        <v>97583</v>
+        <v>97655</v>
       </c>
       <c r="H279">
-        <v>19156</v>
+        <v>19082</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>67442</v>
+        <v>67615</v>
       </c>
       <c r="E280">
         <v>126608</v>
       </c>
       <c r="F280">
-        <v>90833</v>
+        <v>90883</v>
       </c>
       <c r="G280">
-        <v>130800</v>
+        <v>130872</v>
       </c>
       <c r="H280">
-        <v>23391</v>
+        <v>23268</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48610</v>
+        <v>48734</v>
       </c>
       <c r="E281">
         <v>126608</v>
       </c>
       <c r="F281">
-        <v>74821</v>
+        <v>74871</v>
       </c>
       <c r="G281">
-        <v>107742</v>
+        <v>107814</v>
       </c>
       <c r="H281">
-        <v>26211</v>
+        <v>26137</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24009</v>
+        <v>23508</v>
       </c>
       <c r="E282">
         <v>54250</v>
@@ -12803,7 +12803,7 @@
         <v>58591</v>
       </c>
       <c r="H282">
-        <v>16679</v>
+        <v>17180</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24305</v>
+        <v>24148</v>
       </c>
       <c r="E283">
         <v>54250</v>
       </c>
       <c r="F283">
-        <v>39305</v>
+        <v>39148</v>
       </c>
       <c r="G283">
-        <v>56599</v>
+        <v>56373</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65380</v>
+        <v>64521</v>
       </c>
       <c r="E284">
         <v>81403</v>
       </c>
       <c r="F284">
-        <v>80380</v>
+        <v>79521</v>
       </c>
       <c r="G284">
-        <v>115747</v>
+        <v>114510</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31320</v>
+        <v>31401</v>
       </c>
       <c r="E288">
         <v>57868</v>
       </c>
       <c r="F288">
-        <v>48427</v>
+        <v>48399</v>
       </c>
       <c r="G288">
-        <v>69735</v>
+        <v>69695</v>
       </c>
       <c r="H288">
-        <v>17107</v>
+        <v>16998</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25427</v>
+        <v>25399</v>
       </c>
       <c r="E289">
         <v>57868</v>
       </c>
       <c r="F289">
-        <v>40427</v>
+        <v>40399</v>
       </c>
       <c r="G289">
-        <v>58215</v>
+        <v>58175</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>33830</v>
+        <v>33917</v>
       </c>
       <c r="E291">
         <v>43397</v>
       </c>
       <c r="F291">
-        <v>48830</v>
+        <v>48917</v>
       </c>
       <c r="G291">
-        <v>70315</v>
+        <v>70440</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>42717</v>
+        <v>42623</v>
       </c>
       <c r="E292">
         <v>108519</v>
       </c>
       <c r="F292">
-        <v>69717</v>
+        <v>72934</v>
       </c>
       <c r="G292">
-        <v>100392</v>
+        <v>105025</v>
       </c>
       <c r="H292">
-        <v>27000</v>
+        <v>30311</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>37746</v>
       </c>
       <c r="E293">
         <v>108519</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>63421</v>
       </c>
       <c r="G293">
-        <v>0</v>
+        <v>91326</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>25675</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>53287</v>
+        <v>54220</v>
       </c>
       <c r="E296">
         <v>72340</v>
       </c>
       <c r="F296">
-        <v>88287</v>
+        <v>89220</v>
       </c>
       <c r="G296">
-        <v>127133</v>
+        <v>128477</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>63841</v>
+        <v>64005</v>
       </c>
       <c r="E297">
         <v>72340</v>
       </c>
       <c r="F297">
-        <v>78841</v>
+        <v>79005</v>
       </c>
       <c r="G297">
-        <v>113531</v>
+        <v>113767</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10632</v>
+        <v>10660</v>
       </c>
       <c r="E301">
         <v>68722</v>
       </c>
       <c r="F301">
-        <v>37054</v>
+        <v>37065</v>
       </c>
       <c r="G301">
-        <v>53358</v>
+        <v>53374</v>
       </c>
       <c r="H301">
-        <v>26422</v>
+        <v>26405</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>44057</v>
+        <v>42701</v>
       </c>
       <c r="E304">
         <v>108519</v>
       </c>
       <c r="F304">
-        <v>76449</v>
+        <v>76496</v>
       </c>
       <c r="G304">
-        <v>110087</v>
+        <v>110154</v>
       </c>
       <c r="H304">
-        <v>32392</v>
+        <v>33795</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45195</v>
+        <v>45311</v>
       </c>
       <c r="E305">
         <v>108519</v>
       </c>
       <c r="F305">
-        <v>66400</v>
+        <v>66447</v>
       </c>
       <c r="G305">
-        <v>95616</v>
+        <v>95684</v>
       </c>
       <c r="H305">
-        <v>21205</v>
+        <v>21136</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24165</v>
+        <v>24148</v>
       </c>
       <c r="E306">
         <v>108519</v>
       </c>
       <c r="F306">
-        <v>59165</v>
+        <v>59148</v>
       </c>
       <c r="G306">
-        <v>85198</v>
+        <v>85173</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33113</v>
+        <v>33198</v>
       </c>
       <c r="E307">
         <v>108519</v>
       </c>
       <c r="F307">
-        <v>60113</v>
+        <v>60198</v>
       </c>
       <c r="G307">
-        <v>86563</v>
+        <v>86685</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13938,13 +13938,13 @@
         <v>235145</v>
       </c>
       <c r="F308">
-        <v>204009</v>
+        <v>204370</v>
       </c>
       <c r="G308">
-        <v>293773</v>
+        <v>294293</v>
       </c>
       <c r="H308">
-        <v>15105</v>
+        <v>15466</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>140559</v>
+        <v>140920</v>
       </c>
       <c r="E309">
         <v>235145</v>
       </c>
       <c r="F309">
-        <v>155559</v>
+        <v>155920</v>
       </c>
       <c r="G309">
-        <v>224005</v>
+        <v>224525</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>67863</v>
+        <v>67819</v>
       </c>
       <c r="E310">
         <v>126608</v>
       </c>
       <c r="F310">
-        <v>90119</v>
+        <v>90174</v>
       </c>
       <c r="G310">
-        <v>129771</v>
+        <v>129851</v>
       </c>
       <c r="H310">
-        <v>22256</v>
+        <v>22355</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53380</v>
+        <v>53517</v>
       </c>
       <c r="E311">
         <v>126608</v>
       </c>
       <c r="F311">
-        <v>76729</v>
+        <v>76784</v>
       </c>
       <c r="G311">
-        <v>110490</v>
+        <v>110569</v>
       </c>
       <c r="H311">
-        <v>23349</v>
+        <v>23267</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>109707</v>
+        <v>109988</v>
       </c>
       <c r="E313">
         <v>180877</v>
       </c>
       <c r="F313">
-        <v>124707</v>
+        <v>124988</v>
       </c>
       <c r="G313">
-        <v>179578</v>
+        <v>179983</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>124408</v>
+        <v>124727</v>
       </c>
       <c r="E314">
         <v>235145</v>
       </c>
       <c r="F314">
-        <v>159408</v>
+        <v>159727</v>
       </c>
       <c r="G314">
-        <v>229548</v>
+        <v>230007</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>146608</v>
+        <v>146985</v>
       </c>
       <c r="E315">
         <v>235145</v>
       </c>
       <c r="F315">
-        <v>161608</v>
+        <v>161985</v>
       </c>
       <c r="G315">
-        <v>232716</v>
+        <v>233258</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4251</v>
+        <v>4270</v>
       </c>
       <c r="E7">
         <v>54250</v>
       </c>
       <c r="F7">
-        <v>28858</v>
+        <v>28866</v>
       </c>
       <c r="G7">
-        <v>41556</v>
+        <v>41567</v>
       </c>
       <c r="H7">
-        <v>24607</v>
+        <v>24596</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33901</v>
+        <v>34064</v>
       </c>
       <c r="E8">
         <v>72340</v>
       </c>
       <c r="F8">
-        <v>54010</v>
+        <v>54024</v>
       </c>
       <c r="G8">
-        <v>77774</v>
+        <v>77795</v>
       </c>
       <c r="H8">
-        <v>20109</v>
+        <v>19960</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>29494</v>
+        <v>29528</v>
       </c>
       <c r="E9">
         <v>72340</v>
       </c>
       <c r="F9">
-        <v>46010</v>
+        <v>46024</v>
       </c>
       <c r="G9">
-        <v>66254</v>
+        <v>66275</v>
       </c>
       <c r="H9">
-        <v>16516</v>
+        <v>16496</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>40966</v>
+        <v>40992</v>
       </c>
       <c r="E11">
         <v>108519</v>
       </c>
       <c r="F11">
-        <v>64709</v>
+        <v>64719</v>
       </c>
       <c r="G11">
-        <v>93181</v>
+        <v>93195</v>
       </c>
       <c r="H11">
-        <v>23743</v>
+        <v>23727</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>75212</v>
+        <v>34955</v>
       </c>
       <c r="E12">
         <v>81385</v>
       </c>
       <c r="F12">
-        <v>92009</v>
+        <v>61039</v>
       </c>
       <c r="G12">
-        <v>132493</v>
+        <v>87896</v>
       </c>
       <c r="H12">
-        <v>16797</v>
+        <v>26084</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11660</v>
+        <v>11730</v>
       </c>
       <c r="E13">
         <v>81385</v>
       </c>
       <c r="F13">
-        <v>38660</v>
+        <v>38730</v>
       </c>
       <c r="G13">
-        <v>55670</v>
+        <v>55771</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>34964</v>
+        <v>32891</v>
       </c>
       <c r="E21">
         <v>101283</v>
       </c>
       <c r="F21">
-        <v>59486</v>
+        <v>58657</v>
       </c>
       <c r="G21">
-        <v>85660</v>
+        <v>84466</v>
       </c>
       <c r="H21">
-        <v>24522</v>
+        <v>25766</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52564</v>
+        <v>52597</v>
       </c>
       <c r="E23">
         <v>130226</v>
       </c>
       <c r="F23">
-        <v>77814</v>
+        <v>77827</v>
       </c>
       <c r="G23">
-        <v>112052</v>
+        <v>112071</v>
       </c>
       <c r="H23">
-        <v>25250</v>
+        <v>25230</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>17646</v>
+        <v>17532</v>
       </c>
       <c r="E27">
         <v>63295</v>
       </c>
       <c r="F27">
-        <v>37744</v>
+        <v>37698</v>
       </c>
       <c r="G27">
-        <v>54351</v>
+        <v>54285</v>
       </c>
       <c r="H27">
-        <v>20098</v>
+        <v>20166</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74321</v>
+        <v>75291</v>
       </c>
       <c r="E28">
         <v>126608</v>
       </c>
       <c r="F28">
-        <v>93226</v>
+        <v>93335</v>
       </c>
       <c r="G28">
-        <v>134245</v>
+        <v>134402</v>
       </c>
       <c r="H28">
-        <v>18905</v>
+        <v>18044</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25071</v>
+        <v>25180</v>
       </c>
       <c r="E29">
         <v>126608</v>
       </c>
       <c r="F29">
-        <v>52071</v>
+        <v>52180</v>
       </c>
       <c r="G29">
-        <v>74982</v>
+        <v>75139</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130120</v>
+        <v>130578</v>
       </c>
       <c r="E30">
         <v>180877</v>
       </c>
       <c r="F30">
-        <v>165120</v>
+        <v>145578</v>
       </c>
       <c r="G30">
-        <v>237773</v>
+        <v>209632</v>
       </c>
       <c r="H30">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>77431</v>
+        <v>57258</v>
       </c>
       <c r="E31">
         <v>180877</v>
       </c>
       <c r="F31">
-        <v>104431</v>
+        <v>84258</v>
       </c>
       <c r="G31">
-        <v>150381</v>
+        <v>121332</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>71257</v>
+        <v>72085</v>
       </c>
       <c r="E32">
         <v>108519</v>
       </c>
       <c r="F32">
-        <v>89540</v>
+        <v>89447</v>
       </c>
       <c r="G32">
-        <v>128938</v>
+        <v>128804</v>
       </c>
       <c r="H32">
-        <v>18283</v>
+        <v>17362</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>49578</v>
+        <v>49344</v>
       </c>
       <c r="E33">
         <v>108519</v>
       </c>
       <c r="F33">
-        <v>68153</v>
+        <v>68060</v>
       </c>
       <c r="G33">
-        <v>98140</v>
+        <v>98006</v>
       </c>
       <c r="H33">
-        <v>18575</v>
+        <v>18716</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,16 +1935,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>75634</v>
+        <v>79076</v>
       </c>
       <c r="E35">
         <v>126608</v>
       </c>
       <c r="F35">
-        <v>90634</v>
+        <v>94076</v>
       </c>
       <c r="G35">
-        <v>130513</v>
+        <v>135469</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -1979,19 +1979,19 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44530</v>
+        <v>45184</v>
       </c>
       <c r="E36">
         <v>126608</v>
       </c>
       <c r="F36">
-        <v>71781</v>
+        <v>72184</v>
       </c>
       <c r="G36">
-        <v>103365</v>
+        <v>103945</v>
       </c>
       <c r="H36">
-        <v>27251</v>
+        <v>27000</v>
       </c>
       <c r="I36" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35418</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>126608</v>
       </c>
       <c r="F37">
-        <v>62418</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89882</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>82183</v>
+        <v>81344</v>
       </c>
       <c r="E39">
         <v>235145</v>
       </c>
       <c r="F39">
-        <v>109183</v>
+        <v>108344</v>
       </c>
       <c r="G39">
-        <v>157224</v>
+        <v>156015</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>82183</v>
+        <v>81344</v>
       </c>
       <c r="E41">
         <v>235145</v>
       </c>
       <c r="F41">
-        <v>109183</v>
+        <v>108344</v>
       </c>
       <c r="G41">
-        <v>157224</v>
+        <v>156015</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38934</v>
+        <v>38584</v>
       </c>
       <c r="E43">
         <v>126608</v>
       </c>
       <c r="F43">
-        <v>65934</v>
+        <v>65584</v>
       </c>
       <c r="G43">
-        <v>94945</v>
+        <v>94441</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92420</v>
+        <v>92479</v>
       </c>
       <c r="E45">
         <v>180877</v>
       </c>
       <c r="F45">
-        <v>113510</v>
+        <v>113534</v>
       </c>
       <c r="G45">
-        <v>163454</v>
+        <v>163489</v>
       </c>
       <c r="H45">
-        <v>21090</v>
+        <v>21055</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25743</v>
+        <v>25712</v>
       </c>
       <c r="E47">
         <v>108519</v>
       </c>
       <c r="F47">
-        <v>52743</v>
+        <v>52712</v>
       </c>
       <c r="G47">
-        <v>75950</v>
+        <v>75905</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35621</v>
+        <v>35956</v>
       </c>
       <c r="E50">
         <v>63295</v>
       </c>
       <c r="F50">
-        <v>56714</v>
+        <v>56251</v>
       </c>
       <c r="G50">
-        <v>81668</v>
+        <v>81001</v>
       </c>
       <c r="H50">
-        <v>21093</v>
+        <v>20295</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33714</v>
+        <v>33251</v>
       </c>
       <c r="E51">
         <v>63295</v>
       </c>
       <c r="F51">
-        <v>48714</v>
+        <v>48251</v>
       </c>
       <c r="G51">
-        <v>70148</v>
+        <v>69481</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48125</v>
+        <v>48781</v>
       </c>
       <c r="E54">
         <v>126608</v>
       </c>
       <c r="F54">
-        <v>83125</v>
+        <v>83781</v>
       </c>
       <c r="G54">
-        <v>119700</v>
+        <v>120645</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>51892</v>
+        <v>52144</v>
       </c>
       <c r="E55">
         <v>126608</v>
       </c>
       <c r="F55">
-        <v>76134</v>
+        <v>76235</v>
       </c>
       <c r="G55">
-        <v>109633</v>
+        <v>109778</v>
       </c>
       <c r="H55">
-        <v>24242</v>
+        <v>24091</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62411</v>
+        <v>62701</v>
       </c>
       <c r="E57">
         <v>144698</v>
       </c>
       <c r="F57">
-        <v>87397</v>
+        <v>87513</v>
       </c>
       <c r="G57">
-        <v>125852</v>
+        <v>126019</v>
       </c>
       <c r="H57">
-        <v>24986</v>
+        <v>24812</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>24430</v>
+        <v>24477</v>
       </c>
       <c r="E58">
         <v>36161</v>
       </c>
       <c r="F58">
-        <v>39529</v>
+        <v>39543</v>
       </c>
       <c r="G58">
-        <v>56922</v>
+        <v>56942</v>
       </c>
       <c r="H58">
-        <v>15099</v>
+        <v>15066</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6189</v>
+        <v>6225</v>
       </c>
       <c r="E59">
         <v>36161</v>
       </c>
       <c r="F59">
-        <v>22579</v>
+        <v>22593</v>
       </c>
       <c r="G59">
-        <v>32514</v>
+        <v>32534</v>
       </c>
       <c r="H59">
-        <v>16390</v>
+        <v>16368</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26086</v>
+        <v>26213</v>
       </c>
       <c r="E60">
         <v>48824</v>
       </c>
       <c r="F60">
-        <v>47820</v>
+        <v>47836</v>
       </c>
       <c r="G60">
-        <v>68861</v>
+        <v>68884</v>
       </c>
       <c r="H60">
-        <v>21734</v>
+        <v>21623</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24820</v>
+        <v>24836</v>
       </c>
       <c r="E61">
         <v>48824</v>
       </c>
       <c r="F61">
-        <v>39820</v>
+        <v>39836</v>
       </c>
       <c r="G61">
-        <v>57341</v>
+        <v>57364</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12785</v>
+        <v>12856</v>
       </c>
       <c r="E63">
         <v>81385</v>
       </c>
       <c r="F63">
-        <v>39785</v>
+        <v>39856</v>
       </c>
       <c r="G63">
-        <v>57290</v>
+        <v>57393</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28400</v>
+        <v>28371</v>
       </c>
       <c r="E65">
         <v>122068</v>
       </c>
       <c r="F65">
-        <v>55400</v>
+        <v>55371</v>
       </c>
       <c r="G65">
-        <v>79776</v>
+        <v>79734</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24430</v>
+        <v>24383</v>
       </c>
       <c r="E66">
         <v>90429</v>
       </c>
       <c r="F66">
-        <v>53537</v>
+        <v>53533</v>
       </c>
       <c r="G66">
-        <v>77093</v>
+        <v>77088</v>
       </c>
       <c r="H66">
-        <v>29107</v>
+        <v>29150</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18537</v>
+        <v>18533</v>
       </c>
       <c r="E67">
         <v>90429</v>
       </c>
       <c r="F67">
-        <v>45537</v>
+        <v>45533</v>
       </c>
       <c r="G67">
-        <v>65573</v>
+        <v>65568</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34386</v>
+        <v>34455</v>
       </c>
       <c r="E68">
         <v>108519</v>
       </c>
       <c r="F68">
-        <v>62587</v>
+        <v>62605</v>
       </c>
       <c r="G68">
-        <v>90125</v>
+        <v>90151</v>
       </c>
       <c r="H68">
-        <v>28201</v>
+        <v>28150</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27399</v>
+        <v>27417</v>
       </c>
       <c r="E69">
         <v>108519</v>
       </c>
       <c r="F69">
-        <v>54399</v>
+        <v>54417</v>
       </c>
       <c r="G69">
-        <v>78335</v>
+        <v>78360</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45030</v>
+        <v>45247</v>
       </c>
       <c r="E70">
         <v>126608</v>
       </c>
       <c r="F70">
-        <v>80030</v>
+        <v>80247</v>
       </c>
       <c r="G70">
-        <v>115243</v>
+        <v>115556</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50454</v>
+        <v>50502</v>
       </c>
       <c r="E71">
         <v>126608</v>
       </c>
       <c r="F71">
-        <v>75559</v>
+        <v>75578</v>
       </c>
       <c r="G71">
-        <v>108805</v>
+        <v>108832</v>
       </c>
       <c r="H71">
-        <v>25105</v>
+        <v>25076</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5689</v>
+        <v>5693</v>
       </c>
       <c r="E73">
         <v>27116</v>
       </c>
       <c r="F73">
-        <v>20689</v>
+        <v>20693</v>
       </c>
       <c r="G73">
-        <v>29792</v>
+        <v>29798</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70054</v>
+        <v>70098</v>
       </c>
       <c r="E75">
         <v>94952</v>
       </c>
       <c r="F75">
-        <v>85054</v>
+        <v>85098</v>
       </c>
       <c r="G75">
-        <v>122478</v>
+        <v>122541</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>79322</v>
+        <v>80124</v>
       </c>
       <c r="E76">
         <v>126608</v>
       </c>
       <c r="F76">
-        <v>94740</v>
+        <v>95124</v>
       </c>
       <c r="G76">
-        <v>136426</v>
+        <v>136979</v>
       </c>
       <c r="H76">
-        <v>15418</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>46718</v>
+        <v>46951</v>
       </c>
       <c r="E77">
         <v>126608</v>
       </c>
       <c r="F77">
-        <v>73718</v>
+        <v>73951</v>
       </c>
       <c r="G77">
-        <v>106154</v>
+        <v>106489</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36824</v>
+        <v>37004</v>
       </c>
       <c r="E81">
         <v>90429</v>
       </c>
       <c r="F81">
-        <v>55997</v>
+        <v>56069</v>
       </c>
       <c r="G81">
-        <v>80636</v>
+        <v>80739</v>
       </c>
       <c r="H81">
-        <v>19173</v>
+        <v>19065</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48187</v>
+        <v>48296</v>
       </c>
       <c r="E84">
         <v>101283</v>
       </c>
       <c r="F84">
-        <v>70852</v>
+        <v>70910</v>
       </c>
       <c r="G84">
-        <v>102027</v>
+        <v>102110</v>
       </c>
       <c r="H84">
-        <v>22665</v>
+        <v>22614</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31776</v>
+        <v>31921</v>
       </c>
       <c r="E85">
         <v>101283</v>
       </c>
       <c r="F85">
-        <v>58211</v>
+        <v>58269</v>
       </c>
       <c r="G85">
-        <v>83824</v>
+        <v>83907</v>
       </c>
       <c r="H85">
-        <v>26435</v>
+        <v>26348</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4177,13 +4177,13 @@
         <v>144698</v>
       </c>
       <c r="F86">
-        <v>165177</v>
+        <v>165077</v>
       </c>
       <c r="G86">
-        <v>237855</v>
+        <v>237711</v>
       </c>
       <c r="H86">
-        <v>15290</v>
+        <v>15190</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113208</v>
+        <v>113108</v>
       </c>
       <c r="E87">
         <v>144698</v>
       </c>
       <c r="F87">
-        <v>128208</v>
+        <v>128108</v>
       </c>
       <c r="G87">
-        <v>184620</v>
+        <v>184476</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,7 +4258,7 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>158879</v>
+        <v>158699</v>
       </c>
       <c r="E88">
         <v>159170</v>
@@ -4270,7 +4270,7 @@
         <v>250386</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>15180</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4352,13 +4352,13 @@
         <v>57868</v>
       </c>
       <c r="F90">
-        <v>38269</v>
+        <v>38276</v>
       </c>
       <c r="G90">
-        <v>55107</v>
+        <v>55117</v>
       </c>
       <c r="H90">
-        <v>30589</v>
+        <v>30596</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4251</v>
+        <v>4270</v>
       </c>
       <c r="E91">
         <v>57868</v>
       </c>
       <c r="F91">
-        <v>30269</v>
+        <v>30276</v>
       </c>
       <c r="G91">
-        <v>43587</v>
+        <v>43597</v>
       </c>
       <c r="H91">
-        <v>26018</v>
+        <v>26006</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4614,13 +4614,13 @@
         <v>81385</v>
       </c>
       <c r="F96">
-        <v>76330</v>
+        <v>76395</v>
       </c>
       <c r="G96">
-        <v>109915</v>
+        <v>110009</v>
       </c>
       <c r="H96">
-        <v>15155</v>
+        <v>15220</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33354</v>
+        <v>33517</v>
       </c>
       <c r="E97">
         <v>81385</v>
       </c>
       <c r="F97">
-        <v>51082</v>
+        <v>51147</v>
       </c>
       <c r="G97">
-        <v>73558</v>
+        <v>73652</v>
       </c>
       <c r="H97">
-        <v>17728</v>
+        <v>17630</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4704,13 +4704,13 @@
         <v>94047</v>
       </c>
       <c r="F98">
-        <v>89269</v>
+        <v>89334</v>
       </c>
       <c r="G98">
-        <v>128547</v>
+        <v>128641</v>
       </c>
       <c r="H98">
-        <v>15076</v>
+        <v>15141</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33354</v>
+        <v>33517</v>
       </c>
       <c r="E99">
         <v>94047</v>
       </c>
       <c r="F99">
-        <v>56020</v>
+        <v>56085</v>
       </c>
       <c r="G99">
-        <v>80669</v>
+        <v>80762</v>
       </c>
       <c r="H99">
-        <v>22666</v>
+        <v>22568</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61066</v>
+        <v>61356</v>
       </c>
       <c r="E100">
         <v>105444</v>
@@ -4800,7 +4800,7 @@
         <v>113880</v>
       </c>
       <c r="H100">
-        <v>18017</v>
+        <v>17727</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61020</v>
+        <v>61059</v>
       </c>
       <c r="E101">
         <v>105444</v>
       </c>
       <c r="F101">
-        <v>76020</v>
+        <v>76059</v>
       </c>
       <c r="G101">
-        <v>109469</v>
+        <v>109525</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>68444</v>
+        <v>72007</v>
       </c>
       <c r="E105">
         <v>126608</v>
       </c>
       <c r="F105">
-        <v>83444</v>
+        <v>87007</v>
       </c>
       <c r="G105">
-        <v>120159</v>
+        <v>125290</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>99985</v>
+        <v>100065</v>
       </c>
       <c r="E107">
         <v>180877</v>
       </c>
       <c r="F107">
-        <v>116536</v>
+        <v>116568</v>
       </c>
       <c r="G107">
-        <v>167812</v>
+        <v>167858</v>
       </c>
       <c r="H107">
-        <v>16551</v>
+        <v>16503</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3954</v>
+        <v>3973</v>
       </c>
       <c r="E109">
         <v>126608</v>
       </c>
       <c r="F109">
-        <v>30954</v>
+        <v>30973</v>
       </c>
       <c r="G109">
-        <v>44574</v>
+        <v>44601</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13301</v>
+        <v>13372</v>
       </c>
       <c r="E111">
         <v>162787</v>
       </c>
       <c r="F111">
-        <v>40301</v>
+        <v>40372</v>
       </c>
       <c r="G111">
-        <v>58033</v>
+        <v>58136</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>84605</v>
+        <v>84675</v>
       </c>
       <c r="E115">
         <v>115755</v>
       </c>
       <c r="F115">
-        <v>99605</v>
+        <v>99675</v>
       </c>
       <c r="G115">
-        <v>143431</v>
+        <v>143532</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>115162</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>144698</v>
       </c>
       <c r="F117">
-        <v>130162</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>187433</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5664,13 +5664,13 @@
         <v>79576</v>
       </c>
       <c r="F120">
-        <v>78759</v>
+        <v>78798</v>
       </c>
       <c r="G120">
-        <v>113413</v>
+        <v>113469</v>
       </c>
       <c r="H120">
-        <v>18207</v>
+        <v>18246</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53486</v>
+        <v>53520</v>
       </c>
       <c r="E121">
         <v>79576</v>
       </c>
       <c r="F121">
-        <v>68486</v>
+        <v>68520</v>
       </c>
       <c r="G121">
-        <v>98620</v>
+        <v>98669</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,16 +5746,16 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>53079</v>
+        <v>53113</v>
       </c>
       <c r="E122">
         <v>90429</v>
       </c>
       <c r="F122">
-        <v>68079</v>
+        <v>68113</v>
       </c>
       <c r="G122">
-        <v>98034</v>
+        <v>98083</v>
       </c>
       <c r="H122">
         <v>15000</v>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>34230</v>
+        <v>34173</v>
       </c>
       <c r="E123">
         <v>90429</v>
       </c>
       <c r="F123">
-        <v>54959</v>
+        <v>54937</v>
       </c>
       <c r="G123">
-        <v>79141</v>
+        <v>79109</v>
       </c>
       <c r="H123">
-        <v>20729</v>
+        <v>20764</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7299</v>
+        <v>7304</v>
       </c>
       <c r="E125">
         <v>43397</v>
       </c>
       <c r="F125">
-        <v>25844</v>
+        <v>25846</v>
       </c>
       <c r="G125">
-        <v>37215</v>
+        <v>37218</v>
       </c>
       <c r="H125">
-        <v>18545</v>
+        <v>18542</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20069</v>
+        <v>20160</v>
       </c>
       <c r="E129">
         <v>59297</v>
       </c>
       <c r="F129">
-        <v>37153</v>
+        <v>37190</v>
       </c>
       <c r="G129">
-        <v>53500</v>
+        <v>53554</v>
       </c>
       <c r="H129">
-        <v>17084</v>
+        <v>17030</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20069</v>
+        <v>20160</v>
       </c>
       <c r="E131">
         <v>73878</v>
       </c>
       <c r="F131">
-        <v>42840</v>
+        <v>42877</v>
       </c>
       <c r="G131">
-        <v>61690</v>
+        <v>61743</v>
       </c>
       <c r="H131">
-        <v>22771</v>
+        <v>22717</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33042</v>
+        <v>33063</v>
       </c>
       <c r="E133">
         <v>92998</v>
       </c>
       <c r="F133">
-        <v>55486</v>
+        <v>55495</v>
       </c>
       <c r="G133">
-        <v>79900</v>
+        <v>79913</v>
       </c>
       <c r="H133">
-        <v>22444</v>
+        <v>22432</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37184</v>
+        <v>37364</v>
       </c>
       <c r="E140">
         <v>90429</v>
       </c>
       <c r="F140">
-        <v>61567</v>
+        <v>61639</v>
       </c>
       <c r="G140">
-        <v>88656</v>
+        <v>88760</v>
       </c>
       <c r="H140">
-        <v>24383</v>
+        <v>24275</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26618</v>
+        <v>26744</v>
       </c>
       <c r="E142">
         <v>90429</v>
       </c>
       <c r="F142">
-        <v>60158</v>
+        <v>60209</v>
       </c>
       <c r="G142">
-        <v>86628</v>
+        <v>86701</v>
       </c>
       <c r="H142">
-        <v>33540</v>
+        <v>33465</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27227</v>
+        <v>27354</v>
       </c>
       <c r="E143">
         <v>90429</v>
       </c>
       <c r="F143">
-        <v>52158</v>
+        <v>52209</v>
       </c>
       <c r="G143">
-        <v>75108</v>
+        <v>75181</v>
       </c>
       <c r="H143">
-        <v>24931</v>
+        <v>24855</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>44624</v>
+        <v>60120</v>
       </c>
       <c r="E144">
         <v>90429</v>
       </c>
       <c r="F144">
-        <v>67822</v>
+        <v>0</v>
       </c>
       <c r="G144">
-        <v>97664</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>23198</v>
+        <v>0</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>79901</v>
+        <v>79967</v>
       </c>
       <c r="E145">
         <v>90429</v>
       </c>
       <c r="F145">
-        <v>94901</v>
+        <v>94967</v>
       </c>
       <c r="G145">
-        <v>136657</v>
+        <v>136752</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>57972</v>
+        <v>58009</v>
       </c>
       <c r="E146">
         <v>90429</v>
       </c>
       <c r="F146">
-        <v>92972</v>
+        <v>93009</v>
       </c>
       <c r="G146">
-        <v>133880</v>
+        <v>133933</v>
       </c>
       <c r="H146">
         <v>35000</v>
@@ -6840,16 +6840,16 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>93639</v>
+        <v>93699</v>
       </c>
       <c r="E147">
         <v>90429</v>
       </c>
       <c r="F147">
-        <v>108639</v>
+        <v>108699</v>
       </c>
       <c r="G147">
-        <v>156440</v>
+        <v>156527</v>
       </c>
       <c r="H147">
         <v>15000</v>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36684</v>
+        <v>36754</v>
       </c>
       <c r="E148">
         <v>61486</v>
@@ -6895,7 +6895,7 @@
         <v>92032</v>
       </c>
       <c r="H148">
-        <v>27227</v>
+        <v>27157</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15239</v>
+        <v>15233</v>
       </c>
       <c r="E151">
         <v>54250</v>
       </c>
       <c r="F151">
-        <v>33253</v>
+        <v>33251</v>
       </c>
       <c r="G151">
-        <v>47884</v>
+        <v>47881</v>
       </c>
       <c r="H151">
-        <v>18014</v>
+        <v>18018</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37246</v>
+        <v>37395</v>
       </c>
       <c r="E152">
         <v>72340</v>
@@ -7070,7 +7070,7 @@
         <v>78127</v>
       </c>
       <c r="H152">
-        <v>17009</v>
+        <v>16860</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33198</v>
+        <v>33219</v>
       </c>
       <c r="E153">
         <v>72340</v>
       </c>
       <c r="F153">
-        <v>48198</v>
+        <v>48219</v>
       </c>
       <c r="G153">
-        <v>69405</v>
+        <v>69435</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56502</v>
+        <v>56632</v>
       </c>
       <c r="E154">
         <v>72340</v>
       </c>
       <c r="F154">
-        <v>83836</v>
+        <v>83889</v>
       </c>
       <c r="G154">
-        <v>120724</v>
+        <v>120800</v>
       </c>
       <c r="H154">
-        <v>27334</v>
+        <v>27257</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>57862</v>
+        <v>57915</v>
       </c>
       <c r="E155">
         <v>72340</v>
       </c>
       <c r="F155">
-        <v>72862</v>
+        <v>72915</v>
       </c>
       <c r="G155">
-        <v>104921</v>
+        <v>104998</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>34690</v>
       </c>
       <c r="E156">
         <v>59677</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>49690</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>71554</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11879</v>
+        <v>11871</v>
       </c>
       <c r="E157">
         <v>59677</v>
       </c>
       <c r="F157">
-        <v>34026</v>
+        <v>34022</v>
       </c>
       <c r="G157">
-        <v>48997</v>
+        <v>48992</v>
       </c>
       <c r="H157">
-        <v>22147</v>
+        <v>22151</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7324,16 +7324,16 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>84668</v>
+        <v>84722</v>
       </c>
       <c r="E158">
         <v>83194</v>
       </c>
       <c r="F158">
-        <v>99668</v>
+        <v>99722</v>
       </c>
       <c r="G158">
-        <v>143522</v>
+        <v>143600</v>
       </c>
       <c r="H158">
         <v>15000</v>
@@ -7417,13 +7417,13 @@
         <v>54269</v>
       </c>
       <c r="F160">
-        <v>38553</v>
+        <v>38537</v>
       </c>
       <c r="G160">
-        <v>55516</v>
+        <v>55493</v>
       </c>
       <c r="H160">
-        <v>30873</v>
+        <v>30857</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8471</v>
+        <v>8430</v>
       </c>
       <c r="E161">
         <v>54269</v>
       </c>
       <c r="F161">
-        <v>30553</v>
+        <v>30537</v>
       </c>
       <c r="G161">
-        <v>43996</v>
+        <v>43973</v>
       </c>
       <c r="H161">
-        <v>22082</v>
+        <v>22107</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>72340</v>
       </c>
       <c r="F162">
-        <v>44034</v>
+        <v>44040</v>
       </c>
       <c r="G162">
-        <v>63409</v>
+        <v>63418</v>
       </c>
       <c r="H162">
-        <v>33887</v>
+        <v>33893</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9034</v>
+        <v>9040</v>
       </c>
       <c r="E163">
         <v>72340</v>
       </c>
       <c r="F163">
-        <v>36034</v>
+        <v>36040</v>
       </c>
       <c r="G163">
-        <v>51889</v>
+        <v>51898</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7597,13 +7597,13 @@
         <v>67836</v>
       </c>
       <c r="F164">
-        <v>82022</v>
+        <v>82065</v>
       </c>
       <c r="G164">
-        <v>118112</v>
+        <v>118174</v>
       </c>
       <c r="H164">
-        <v>15156</v>
+        <v>15199</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20694</v>
+        <v>20801</v>
       </c>
       <c r="E165">
         <v>67836</v>
       </c>
       <c r="F165">
-        <v>40733</v>
+        <v>40776</v>
       </c>
       <c r="G165">
-        <v>58656</v>
+        <v>58717</v>
       </c>
       <c r="H165">
-        <v>20039</v>
+        <v>19975</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7685,13 +7685,13 @@
         <v>102206</v>
       </c>
       <c r="F166">
-        <v>105302</v>
+        <v>105410</v>
       </c>
       <c r="G166">
-        <v>151635</v>
+        <v>151790</v>
       </c>
       <c r="H166">
-        <v>15289</v>
+        <v>15397</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21788</v>
+        <v>21896</v>
       </c>
       <c r="E167">
         <v>102206</v>
       </c>
       <c r="F167">
-        <v>48788</v>
+        <v>48896</v>
       </c>
       <c r="G167">
-        <v>70255</v>
+        <v>70410</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>72340</v>
       </c>
       <c r="F168">
-        <v>103843</v>
+        <v>103833</v>
       </c>
       <c r="G168">
-        <v>149534</v>
+        <v>149520</v>
       </c>
       <c r="H168">
-        <v>15022</v>
+        <v>15012</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8815</v>
+        <v>8805</v>
       </c>
       <c r="E169">
         <v>72340</v>
       </c>
       <c r="F169">
-        <v>35815</v>
+        <v>35805</v>
       </c>
       <c r="G169">
-        <v>51574</v>
+        <v>51559</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>58597</v>
+        <v>59260</v>
       </c>
       <c r="E170">
         <v>108519</v>
       </c>
       <c r="F170">
-        <v>80498</v>
+        <v>80055</v>
       </c>
       <c r="G170">
-        <v>115917</v>
+        <v>115279</v>
       </c>
       <c r="H170">
-        <v>21901</v>
+        <v>20795</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>54189</v>
+        <v>53082</v>
       </c>
       <c r="E171">
         <v>108519</v>
       </c>
       <c r="F171">
-        <v>69998</v>
+        <v>69555</v>
       </c>
       <c r="G171">
-        <v>100797</v>
+        <v>100159</v>
       </c>
       <c r="H171">
-        <v>15809</v>
+        <v>16473</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>77509</v>
+        <v>78341</v>
       </c>
       <c r="E172">
         <v>144698</v>
       </c>
       <c r="F172">
-        <v>107725</v>
+        <v>107748</v>
       </c>
       <c r="G172">
-        <v>155124</v>
+        <v>155157</v>
       </c>
       <c r="H172">
-        <v>30216</v>
+        <v>29407</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78103</v>
+        <v>78153</v>
       </c>
       <c r="E173">
         <v>144698</v>
       </c>
       <c r="F173">
-        <v>93674</v>
+        <v>93694</v>
       </c>
       <c r="G173">
-        <v>134891</v>
+        <v>134919</v>
       </c>
       <c r="H173">
-        <v>15571</v>
+        <v>15541</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>47734</v>
+        <v>47217</v>
       </c>
       <c r="E174">
         <v>90429</v>
@@ -8045,7 +8045,7 @@
         <v>97664</v>
       </c>
       <c r="H174">
-        <v>20088</v>
+        <v>20605</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>27946</v>
+        <v>27354</v>
       </c>
       <c r="E178">
         <v>108519</v>
       </c>
       <c r="F178">
-        <v>54946</v>
+        <v>54354</v>
       </c>
       <c r="G178">
-        <v>79122</v>
+        <v>78270</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>24570</v>
+        <v>23992</v>
       </c>
       <c r="E180">
         <v>90429</v>
       </c>
       <c r="F180">
-        <v>51570</v>
+        <v>50992</v>
       </c>
       <c r="G180">
-        <v>74261</v>
+        <v>73428</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8393,13 +8393,13 @@
         <v>126608</v>
       </c>
       <c r="F182">
-        <v>114892</v>
+        <v>115014</v>
       </c>
       <c r="G182">
-        <v>165444</v>
+        <v>165620</v>
       </c>
       <c r="H182">
-        <v>15132</v>
+        <v>15254</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>63974</v>
+        <v>64280</v>
       </c>
       <c r="E183">
         <v>126608</v>
       </c>
       <c r="F183">
-        <v>80967</v>
+        <v>81089</v>
       </c>
       <c r="G183">
-        <v>116592</v>
+        <v>116768</v>
       </c>
       <c r="H183">
-        <v>16993</v>
+        <v>16809</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>143780</v>
+        <v>143872</v>
       </c>
       <c r="E184">
         <v>180877</v>
       </c>
       <c r="F184">
-        <v>159083</v>
+        <v>159389</v>
       </c>
       <c r="G184">
-        <v>229080</v>
+        <v>229520</v>
       </c>
       <c r="H184">
-        <v>15303</v>
+        <v>15517</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>63974</v>
+        <v>64280</v>
       </c>
       <c r="E185">
         <v>180877</v>
       </c>
       <c r="F185">
-        <v>90974</v>
+        <v>91280</v>
       </c>
       <c r="G185">
-        <v>131003</v>
+        <v>131443</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>63974</v>
+        <v>64280</v>
       </c>
       <c r="E187">
         <v>180877</v>
       </c>
       <c r="F187">
-        <v>90974</v>
+        <v>91280</v>
       </c>
       <c r="G187">
-        <v>131003</v>
+        <v>131443</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>289139</v>
+        <v>289324</v>
       </c>
       <c r="E188">
         <v>361772</v>
       </c>
       <c r="F188">
-        <v>324139</v>
+        <v>324324</v>
       </c>
       <c r="G188">
-        <v>466760</v>
+        <v>467027</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>304410</v>
+        <v>304620</v>
       </c>
       <c r="E189">
         <v>361772</v>
       </c>
       <c r="F189">
-        <v>319410</v>
+        <v>319620</v>
       </c>
       <c r="G189">
-        <v>459950</v>
+        <v>460253</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29947</v>
+        <v>29857</v>
       </c>
       <c r="E190">
         <v>94952</v>
       </c>
       <c r="F190">
-        <v>64947</v>
+        <v>64857</v>
       </c>
       <c r="G190">
-        <v>93524</v>
+        <v>93394</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44170</v>
+        <v>44199</v>
       </c>
       <c r="E191">
         <v>94952</v>
       </c>
       <c r="F191">
-        <v>60699</v>
+        <v>60711</v>
       </c>
       <c r="G191">
-        <v>87407</v>
+        <v>87424</v>
       </c>
       <c r="H191">
-        <v>16529</v>
+        <v>16512</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>43389</v>
+        <v>43495</v>
       </c>
       <c r="E192">
         <v>122086</v>
       </c>
       <c r="F192">
-        <v>78389</v>
+        <v>78495</v>
       </c>
       <c r="G192">
-        <v>112880</v>
+        <v>113033</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>49907</v>
+        <v>49766</v>
       </c>
       <c r="E194">
         <v>149401</v>
       </c>
       <c r="F194">
-        <v>76907</v>
+        <v>76766</v>
       </c>
       <c r="G194">
-        <v>110746</v>
+        <v>110543</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -9044,16 +9044,16 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32198</v>
+        <v>32218</v>
       </c>
       <c r="E197">
         <v>72340</v>
       </c>
       <c r="F197">
-        <v>47198</v>
+        <v>47218</v>
       </c>
       <c r="G197">
-        <v>67965</v>
+        <v>67994</v>
       </c>
       <c r="H197">
         <v>15000</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26086</v>
+        <v>26400</v>
       </c>
       <c r="E198">
         <v>108519</v>
       </c>
       <c r="F198">
-        <v>61086</v>
+        <v>61400</v>
       </c>
       <c r="G198">
-        <v>87964</v>
+        <v>88416</v>
       </c>
       <c r="H198">
         <v>35000</v>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37137</v>
+        <v>37161</v>
       </c>
       <c r="E199">
         <v>108519</v>
       </c>
       <c r="F199">
-        <v>63177</v>
+        <v>63187</v>
       </c>
       <c r="G199">
-        <v>90975</v>
+        <v>90989</v>
       </c>
       <c r="H199">
-        <v>26040</v>
+        <v>26026</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>126608</v>
       </c>
       <c r="F200">
-        <v>46848</v>
+        <v>46902</v>
       </c>
       <c r="G200">
-        <v>67461</v>
+        <v>67539</v>
       </c>
       <c r="H200">
-        <v>32783</v>
+        <v>32837</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11848</v>
+        <v>11902</v>
       </c>
       <c r="E201">
         <v>126608</v>
       </c>
       <c r="F201">
-        <v>38848</v>
+        <v>38902</v>
       </c>
       <c r="G201">
-        <v>55941</v>
+        <v>56019</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22492</v>
+        <v>22506</v>
       </c>
       <c r="E203">
         <v>144698</v>
       </c>
       <c r="F203">
-        <v>49492</v>
+        <v>49506</v>
       </c>
       <c r="G203">
-        <v>71268</v>
+        <v>71289</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>180877</v>
       </c>
       <c r="F204">
-        <v>61008</v>
+        <v>61166</v>
       </c>
       <c r="G204">
-        <v>87852</v>
+        <v>88079</v>
       </c>
       <c r="H204">
-        <v>32270</v>
+        <v>32428</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,16 +9402,16 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26008</v>
+        <v>26166</v>
       </c>
       <c r="E205">
         <v>180877</v>
       </c>
       <c r="F205">
-        <v>53008</v>
+        <v>53166</v>
       </c>
       <c r="G205">
-        <v>76332</v>
+        <v>76559</v>
       </c>
       <c r="H205">
         <v>27000</v>
@@ -9451,13 +9451,13 @@
         <v>57868</v>
       </c>
       <c r="F206">
-        <v>42015</v>
+        <v>42044</v>
       </c>
       <c r="G206">
-        <v>60502</v>
+        <v>60543</v>
       </c>
       <c r="H206">
-        <v>17773</v>
+        <v>17802</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12910</v>
+        <v>12981</v>
       </c>
       <c r="E207">
         <v>57868</v>
       </c>
       <c r="F207">
-        <v>33732</v>
+        <v>33761</v>
       </c>
       <c r="G207">
-        <v>48574</v>
+        <v>48616</v>
       </c>
       <c r="H207">
-        <v>20822</v>
+        <v>20780</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22804</v>
+        <v>22819</v>
       </c>
       <c r="E209">
         <v>54250</v>
       </c>
       <c r="F209">
-        <v>37804</v>
+        <v>37819</v>
       </c>
       <c r="G209">
-        <v>54438</v>
+        <v>54459</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40044</v>
+        <v>40070</v>
       </c>
       <c r="E211">
         <v>108519</v>
       </c>
       <c r="F211">
-        <v>64340</v>
+        <v>64350</v>
       </c>
       <c r="G211">
-        <v>92650</v>
+        <v>92664</v>
       </c>
       <c r="H211">
-        <v>24296</v>
+        <v>24280</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>82870</v>
+        <v>82939</v>
       </c>
       <c r="E213">
         <v>180877</v>
       </c>
       <c r="F213">
-        <v>109690</v>
+        <v>109718</v>
       </c>
       <c r="G213">
-        <v>157954</v>
+        <v>157994</v>
       </c>
       <c r="H213">
-        <v>26820</v>
+        <v>26779</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28103</v>
+        <v>28168</v>
       </c>
       <c r="E214">
         <v>86812</v>
       </c>
       <c r="F214">
-        <v>60254</v>
+        <v>60262</v>
       </c>
       <c r="G214">
-        <v>86766</v>
+        <v>86777</v>
       </c>
       <c r="H214">
-        <v>32151</v>
+        <v>32094</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>30994</v>
+        <v>31014</v>
       </c>
       <c r="E215">
         <v>86812</v>
       </c>
       <c r="F215">
-        <v>52254</v>
+        <v>52262</v>
       </c>
       <c r="G215">
-        <v>75246</v>
+        <v>75257</v>
       </c>
       <c r="H215">
-        <v>21260</v>
+        <v>21248</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45421</v>
+        <v>45638</v>
       </c>
       <c r="E216">
         <v>101283</v>
@@ -9893,7 +9893,7 @@
         <v>109385</v>
       </c>
       <c r="H216">
-        <v>30541</v>
+        <v>30324</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88419</v>
+        <v>88475</v>
       </c>
       <c r="E217">
         <v>101283</v>
       </c>
       <c r="F217">
-        <v>103419</v>
+        <v>103475</v>
       </c>
       <c r="G217">
-        <v>148923</v>
+        <v>149004</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>110176</v>
+        <v>110262</v>
       </c>
       <c r="E219">
         <v>130226</v>
       </c>
       <c r="F219">
-        <v>125176</v>
+        <v>125262</v>
       </c>
       <c r="G219">
-        <v>180253</v>
+        <v>180377</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10065,13 +10065,13 @@
         <v>81403</v>
       </c>
       <c r="F220">
-        <v>75343</v>
+        <v>75938</v>
       </c>
       <c r="G220">
-        <v>108494</v>
+        <v>109351</v>
       </c>
       <c r="H220">
-        <v>16056</v>
+        <v>16651</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>50516</v>
+        <v>51033</v>
       </c>
       <c r="E221">
         <v>81403</v>
       </c>
       <c r="F221">
-        <v>65516</v>
+        <v>66033</v>
       </c>
       <c r="G221">
-        <v>94343</v>
+        <v>95088</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10149,16 +10149,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>73102</v>
+        <v>74118</v>
       </c>
       <c r="E222">
         <v>95874</v>
       </c>
       <c r="F222">
-        <v>108102</v>
+        <v>109118</v>
       </c>
       <c r="G222">
-        <v>155667</v>
+        <v>157130</v>
       </c>
       <c r="H222">
         <v>35000</v>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>83480</v>
+        <v>93105</v>
       </c>
       <c r="E223">
         <v>95874</v>
       </c>
       <c r="F223">
-        <v>98480</v>
+        <v>108105</v>
       </c>
       <c r="G223">
-        <v>141811</v>
+        <v>155671</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>59677</v>
       </c>
       <c r="F224">
-        <v>41400</v>
+        <v>41422</v>
       </c>
       <c r="G224">
-        <v>59616</v>
+        <v>59648</v>
       </c>
       <c r="H224">
-        <v>24822</v>
+        <v>24844</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10316</v>
+        <v>10369</v>
       </c>
       <c r="E225">
         <v>59677</v>
       </c>
       <c r="F225">
-        <v>33400</v>
+        <v>33422</v>
       </c>
       <c r="G225">
-        <v>48096</v>
+        <v>48128</v>
       </c>
       <c r="H225">
-        <v>23084</v>
+        <v>23053</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37621</v>
+        <v>37630</v>
       </c>
       <c r="E226">
         <v>72340</v>
       </c>
       <c r="F226">
-        <v>53601</v>
+        <v>53613</v>
       </c>
       <c r="G226">
-        <v>77185</v>
+        <v>77203</v>
       </c>
       <c r="H226">
-        <v>15980</v>
+        <v>15983</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25805</v>
+        <v>25837</v>
       </c>
       <c r="E227">
         <v>72340</v>
       </c>
       <c r="F227">
-        <v>44535</v>
+        <v>44547</v>
       </c>
       <c r="G227">
-        <v>64130</v>
+        <v>64148</v>
       </c>
       <c r="H227">
-        <v>18730</v>
+        <v>18710</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,16 +10418,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83027</v>
+        <v>83095</v>
       </c>
       <c r="E228">
         <v>108519</v>
       </c>
       <c r="F228">
-        <v>98027</v>
+        <v>98095</v>
       </c>
       <c r="G228">
-        <v>141159</v>
+        <v>141257</v>
       </c>
       <c r="H228">
         <v>15000</v>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13223</v>
+        <v>13231</v>
       </c>
       <c r="E229">
         <v>108519</v>
       </c>
       <c r="F229">
-        <v>40223</v>
+        <v>40231</v>
       </c>
       <c r="G229">
-        <v>57921</v>
+        <v>57933</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19100</v>
+        <v>19065</v>
       </c>
       <c r="E231">
         <v>180877</v>
       </c>
       <c r="F231">
-        <v>46100</v>
+        <v>46065</v>
       </c>
       <c r="G231">
-        <v>66384</v>
+        <v>66334</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10595,13 +10595,13 @@
         <v>52460</v>
       </c>
       <c r="F232">
-        <v>38423</v>
+        <v>38426</v>
       </c>
       <c r="G232">
-        <v>55329</v>
+        <v>55333</v>
       </c>
       <c r="H232">
-        <v>29088</v>
+        <v>29091</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9909</v>
+        <v>9916</v>
       </c>
       <c r="E233">
         <v>52460</v>
       </c>
       <c r="F233">
-        <v>30423</v>
+        <v>30426</v>
       </c>
       <c r="G233">
-        <v>43809</v>
+        <v>43813</v>
       </c>
       <c r="H233">
-        <v>20514</v>
+        <v>20510</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52460</v>
       </c>
       <c r="F236">
-        <v>37235</v>
+        <v>37225</v>
       </c>
       <c r="G236">
-        <v>53618</v>
+        <v>53604</v>
       </c>
       <c r="H236">
-        <v>28884</v>
+        <v>28874</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6940</v>
+        <v>6913</v>
       </c>
       <c r="E237">
         <v>52460</v>
       </c>
       <c r="F237">
-        <v>29235</v>
+        <v>29225</v>
       </c>
       <c r="G237">
-        <v>42098</v>
+        <v>42084</v>
       </c>
       <c r="H237">
-        <v>22295</v>
+        <v>22312</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11332</v>
+        <v>11292</v>
       </c>
       <c r="E239">
         <v>52460</v>
       </c>
       <c r="F239">
-        <v>30992</v>
+        <v>30976</v>
       </c>
       <c r="G239">
-        <v>44628</v>
+        <v>44605</v>
       </c>
       <c r="H239">
-        <v>19660</v>
+        <v>19684</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,7 +10941,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24039</v>
+        <v>24054</v>
       </c>
       <c r="E240">
         <v>70549</v>
@@ -10953,7 +10953,7 @@
         <v>76193</v>
       </c>
       <c r="H240">
-        <v>28873</v>
+        <v>28858</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70272</v>
+        <v>71271</v>
       </c>
       <c r="E241">
         <v>70549</v>
       </c>
       <c r="F241">
-        <v>85272</v>
+        <v>86271</v>
       </c>
       <c r="G241">
-        <v>122792</v>
+        <v>124230</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>33964</v>
+        <v>34048</v>
       </c>
       <c r="E242">
         <v>70549</v>
       </c>
       <c r="F242">
-        <v>51333</v>
+        <v>51366</v>
       </c>
       <c r="G242">
-        <v>73920</v>
+        <v>73967</v>
       </c>
       <c r="H242">
-        <v>17369</v>
+        <v>17318</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92233</v>
+        <v>92292</v>
       </c>
       <c r="E246">
         <v>108519</v>
       </c>
       <c r="F246">
-        <v>107233</v>
+        <v>107292</v>
       </c>
       <c r="G246">
-        <v>154416</v>
+        <v>154500</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11297,13 +11297,13 @@
         <v>95874</v>
       </c>
       <c r="F248">
-        <v>73993</v>
+        <v>74242</v>
       </c>
       <c r="G248">
-        <v>106550</v>
+        <v>106908</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>15249</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>47750</v>
+        <v>47999</v>
       </c>
       <c r="E249">
         <v>95874</v>
       </c>
       <c r="F249">
-        <v>62750</v>
+        <v>62999</v>
       </c>
       <c r="G249">
-        <v>90360</v>
+        <v>90719</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72945</v>
+        <v>73008</v>
       </c>
       <c r="E250">
         <v>108519</v>
       </c>
       <c r="F250">
-        <v>103815</v>
+        <v>103707</v>
       </c>
       <c r="G250">
-        <v>149494</v>
+        <v>149338</v>
       </c>
       <c r="H250">
-        <v>30870</v>
+        <v>30699</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>75274</v>
+        <v>75166</v>
       </c>
       <c r="E251">
         <v>108519</v>
       </c>
       <c r="F251">
-        <v>90274</v>
+        <v>90166</v>
       </c>
       <c r="G251">
-        <v>129995</v>
+        <v>129839</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38372</v>
+        <v>38396</v>
       </c>
       <c r="E253">
         <v>52460</v>
       </c>
       <c r="F253">
-        <v>53372</v>
+        <v>53396</v>
       </c>
       <c r="G253">
-        <v>76856</v>
+        <v>76890</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11558,7 +11558,7 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24164</v>
+        <v>24179</v>
       </c>
       <c r="E254">
         <v>70549</v>
@@ -11570,7 +11570,7 @@
         <v>76193</v>
       </c>
       <c r="H254">
-        <v>28748</v>
+        <v>28733</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69194</v>
+        <v>69238</v>
       </c>
       <c r="E255">
         <v>70549</v>
       </c>
       <c r="F255">
-        <v>84194</v>
+        <v>84238</v>
       </c>
       <c r="G255">
-        <v>121239</v>
+        <v>121303</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12441</v>
+        <v>12496</v>
       </c>
       <c r="E259">
         <v>50633</v>
       </c>
       <c r="F259">
-        <v>30723</v>
+        <v>30745</v>
       </c>
       <c r="G259">
-        <v>44241</v>
+        <v>44273</v>
       </c>
       <c r="H259">
-        <v>18282</v>
+        <v>18249</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12441</v>
+        <v>12496</v>
       </c>
       <c r="E261">
         <v>63295</v>
       </c>
       <c r="F261">
-        <v>35662</v>
+        <v>35684</v>
       </c>
       <c r="G261">
-        <v>51353</v>
+        <v>51385</v>
       </c>
       <c r="H261">
-        <v>23221</v>
+        <v>23188</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12441</v>
+        <v>12496</v>
       </c>
       <c r="E263">
         <v>72340</v>
       </c>
       <c r="F263">
-        <v>39189</v>
+        <v>39211</v>
       </c>
       <c r="G263">
-        <v>56432</v>
+        <v>56464</v>
       </c>
       <c r="H263">
-        <v>26748</v>
+        <v>26715</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39841</v>
+        <v>39397</v>
       </c>
       <c r="E264">
         <v>59677</v>
       </c>
       <c r="F264">
-        <v>54841</v>
+        <v>54856</v>
       </c>
       <c r="G264">
-        <v>78971</v>
+        <v>78993</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>15459</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,16 +12038,16 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23914</v>
+        <v>23929</v>
       </c>
       <c r="E265">
         <v>59677</v>
       </c>
       <c r="F265">
-        <v>38914</v>
+        <v>38929</v>
       </c>
       <c r="G265">
-        <v>56036</v>
+        <v>56058</v>
       </c>
       <c r="H265">
         <v>15000</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35480</v>
+        <v>35550</v>
       </c>
       <c r="E268">
         <v>59677</v>
       </c>
       <c r="F268">
-        <v>50583</v>
+        <v>50596</v>
       </c>
       <c r="G268">
-        <v>72840</v>
+        <v>72858</v>
       </c>
       <c r="H268">
-        <v>15103</v>
+        <v>15046</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23601</v>
+        <v>23632</v>
       </c>
       <c r="E269">
         <v>59677</v>
       </c>
       <c r="F269">
-        <v>38714</v>
+        <v>38727</v>
       </c>
       <c r="G269">
-        <v>55748</v>
+        <v>55767</v>
       </c>
       <c r="H269">
-        <v>15113</v>
+        <v>15095</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>38919</v>
+        <v>38944</v>
       </c>
       <c r="E270">
         <v>66913</v>
       </c>
       <c r="F270">
-        <v>53980</v>
+        <v>53998</v>
       </c>
       <c r="G270">
-        <v>77731</v>
+        <v>77757</v>
       </c>
       <c r="H270">
-        <v>15061</v>
+        <v>15054</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>28947</v>
+        <v>28965</v>
       </c>
       <c r="E271">
         <v>66913</v>
       </c>
       <c r="F271">
-        <v>43947</v>
+        <v>43965</v>
       </c>
       <c r="G271">
-        <v>63284</v>
+        <v>63310</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12355,13 +12355,13 @@
         <v>90429</v>
       </c>
       <c r="F272">
-        <v>85580</v>
+        <v>86860</v>
       </c>
       <c r="G272">
-        <v>123235</v>
+        <v>125078</v>
       </c>
       <c r="H272">
-        <v>15051</v>
+        <v>16331</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>19897</v>
+        <v>21177</v>
       </c>
       <c r="E273">
         <v>90429</v>
       </c>
       <c r="F273">
-        <v>46897</v>
+        <v>48177</v>
       </c>
       <c r="G273">
-        <v>67532</v>
+        <v>69375</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12444,13 +12444,13 @@
         <v>126608</v>
       </c>
       <c r="F274">
-        <v>48880</v>
+        <v>48886</v>
       </c>
       <c r="G274">
-        <v>70387</v>
+        <v>70396</v>
       </c>
       <c r="H274">
-        <v>27026</v>
+        <v>27032</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10144</v>
+        <v>10150</v>
       </c>
       <c r="E275">
         <v>126608</v>
       </c>
       <c r="F275">
-        <v>37144</v>
+        <v>37150</v>
       </c>
       <c r="G275">
-        <v>53487</v>
+        <v>53496</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151861</v>
+        <v>160685</v>
       </c>
       <c r="E276">
         <v>162787</v>
       </c>
       <c r="F276">
-        <v>186498</v>
+        <v>186579</v>
       </c>
       <c r="G276">
-        <v>268557</v>
+        <v>268674</v>
       </c>
       <c r="H276">
-        <v>34637</v>
+        <v>25894</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101282</v>
+        <v>101363</v>
       </c>
       <c r="E277">
         <v>162787</v>
       </c>
       <c r="F277">
-        <v>116282</v>
+        <v>116363</v>
       </c>
       <c r="G277">
-        <v>167446</v>
+        <v>167563</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>50094</v>
+        <v>50345</v>
       </c>
       <c r="E278">
         <v>108519</v>
       </c>
       <c r="F278">
-        <v>78069</v>
+        <v>78163</v>
       </c>
       <c r="G278">
-        <v>112419</v>
+        <v>112555</v>
       </c>
       <c r="H278">
-        <v>27975</v>
+        <v>27818</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48734</v>
+        <v>48969</v>
       </c>
       <c r="E279">
         <v>108519</v>
       </c>
       <c r="F279">
-        <v>67816</v>
+        <v>67910</v>
       </c>
       <c r="G279">
-        <v>97655</v>
+        <v>97790</v>
       </c>
       <c r="H279">
-        <v>19082</v>
+        <v>18941</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>67615</v>
+        <v>67612</v>
       </c>
       <c r="E280">
         <v>126608</v>
       </c>
       <c r="F280">
-        <v>90883</v>
+        <v>90977</v>
       </c>
       <c r="G280">
-        <v>130872</v>
+        <v>131007</v>
       </c>
       <c r="H280">
-        <v>23268</v>
+        <v>23365</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48734</v>
+        <v>48969</v>
       </c>
       <c r="E281">
         <v>126608</v>
       </c>
       <c r="F281">
-        <v>74871</v>
+        <v>74965</v>
       </c>
       <c r="G281">
-        <v>107814</v>
+        <v>107950</v>
       </c>
       <c r="H281">
-        <v>26137</v>
+        <v>25996</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24148</v>
+        <v>24383</v>
       </c>
       <c r="E283">
         <v>54250</v>
       </c>
       <c r="F283">
-        <v>39148</v>
+        <v>39383</v>
       </c>
       <c r="G283">
-        <v>56373</v>
+        <v>56712</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>64521</v>
+        <v>64578</v>
       </c>
       <c r="E284">
         <v>81403</v>
       </c>
       <c r="F284">
-        <v>79521</v>
+        <v>79578</v>
       </c>
       <c r="G284">
-        <v>114510</v>
+        <v>114592</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -13053,7 +13053,7 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31401</v>
+        <v>31734</v>
       </c>
       <c r="E288">
         <v>57868</v>
@@ -13065,7 +13065,7 @@
         <v>69695</v>
       </c>
       <c r="H288">
-        <v>16998</v>
+        <v>16665</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>33917</v>
+        <v>33939</v>
       </c>
       <c r="E291">
         <v>43397</v>
       </c>
       <c r="F291">
-        <v>48917</v>
+        <v>48939</v>
       </c>
       <c r="G291">
-        <v>70440</v>
+        <v>70472</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>42623</v>
+        <v>42854</v>
       </c>
       <c r="E292">
         <v>108519</v>
       </c>
       <c r="F292">
-        <v>72934</v>
+        <v>72946</v>
       </c>
       <c r="G292">
-        <v>105025</v>
+        <v>105042</v>
       </c>
       <c r="H292">
-        <v>30311</v>
+        <v>30092</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37746</v>
+        <v>37771</v>
       </c>
       <c r="E293">
         <v>108519</v>
       </c>
       <c r="F293">
-        <v>63421</v>
+        <v>63431</v>
       </c>
       <c r="G293">
-        <v>91326</v>
+        <v>91341</v>
       </c>
       <c r="H293">
-        <v>25675</v>
+        <v>25660</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54220</v>
+        <v>54240</v>
       </c>
       <c r="E296">
         <v>72340</v>
       </c>
       <c r="F296">
-        <v>89220</v>
+        <v>89240</v>
       </c>
       <c r="G296">
-        <v>128477</v>
+        <v>128506</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64005</v>
+        <v>64046</v>
       </c>
       <c r="E297">
         <v>72340</v>
       </c>
       <c r="F297">
-        <v>79005</v>
+        <v>79046</v>
       </c>
       <c r="G297">
-        <v>113767</v>
+        <v>113826</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>4848</v>
       </c>
       <c r="E299">
         <v>54250</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>29097</v>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>41900</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>24249</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10660</v>
+        <v>10666</v>
       </c>
       <c r="E301">
         <v>68722</v>
       </c>
       <c r="F301">
-        <v>37065</v>
+        <v>37068</v>
       </c>
       <c r="G301">
-        <v>53374</v>
+        <v>53378</v>
       </c>
       <c r="H301">
-        <v>26405</v>
+        <v>26402</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>42701</v>
+        <v>42150</v>
       </c>
       <c r="E304">
         <v>108519</v>
       </c>
       <c r="F304">
-        <v>76496</v>
+        <v>76507</v>
       </c>
       <c r="G304">
-        <v>110154</v>
+        <v>110170</v>
       </c>
       <c r="H304">
-        <v>33795</v>
+        <v>34357</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45311</v>
+        <v>45340</v>
       </c>
       <c r="E305">
         <v>108519</v>
       </c>
       <c r="F305">
-        <v>66447</v>
+        <v>66458</v>
       </c>
       <c r="G305">
-        <v>95684</v>
+        <v>95700</v>
       </c>
       <c r="H305">
-        <v>21136</v>
+        <v>21118</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24148</v>
+        <v>24117</v>
       </c>
       <c r="E306">
         <v>108519</v>
       </c>
       <c r="F306">
-        <v>59148</v>
+        <v>59117</v>
       </c>
       <c r="G306">
-        <v>85173</v>
+        <v>85128</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33198</v>
+        <v>33219</v>
       </c>
       <c r="E307">
         <v>108519</v>
       </c>
       <c r="F307">
-        <v>60198</v>
+        <v>60219</v>
       </c>
       <c r="G307">
-        <v>86685</v>
+        <v>86715</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13938,13 +13938,13 @@
         <v>235145</v>
       </c>
       <c r="F308">
-        <v>204370</v>
+        <v>204476</v>
       </c>
       <c r="G308">
-        <v>294293</v>
+        <v>294445</v>
       </c>
       <c r="H308">
-        <v>15466</v>
+        <v>15572</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>140920</v>
+        <v>141026</v>
       </c>
       <c r="E309">
         <v>235145</v>
       </c>
       <c r="F309">
-        <v>155920</v>
+        <v>156026</v>
       </c>
       <c r="G309">
-        <v>224525</v>
+        <v>224677</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>67819</v>
+        <v>67424</v>
       </c>
       <c r="E310">
         <v>126608</v>
       </c>
       <c r="F310">
-        <v>90174</v>
+        <v>90194</v>
       </c>
       <c r="G310">
-        <v>129851</v>
+        <v>129879</v>
       </c>
       <c r="H310">
-        <v>22355</v>
+        <v>22770</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53517</v>
+        <v>53567</v>
       </c>
       <c r="E311">
         <v>126608</v>
       </c>
       <c r="F311">
-        <v>76784</v>
+        <v>76804</v>
       </c>
       <c r="G311">
-        <v>110569</v>
+        <v>110598</v>
       </c>
       <c r="H311">
-        <v>23267</v>
+        <v>23237</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>109988</v>
+        <v>110074</v>
       </c>
       <c r="E313">
         <v>180877</v>
       </c>
       <c r="F313">
-        <v>124988</v>
+        <v>125074</v>
       </c>
       <c r="G313">
-        <v>179983</v>
+        <v>180107</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>124727</v>
+        <v>123728</v>
       </c>
       <c r="E314">
         <v>235145</v>
       </c>
       <c r="F314">
-        <v>159727</v>
+        <v>158728</v>
       </c>
       <c r="G314">
-        <v>230007</v>
+        <v>228568</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>146985</v>
+        <v>147094</v>
       </c>
       <c r="E315">
         <v>235145</v>
       </c>
       <c r="F315">
-        <v>161985</v>
+        <v>162094</v>
       </c>
       <c r="G315">
-        <v>233258</v>
+        <v>233415</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4270</v>
+        <v>4272</v>
       </c>
       <c r="E7">
         <v>54250</v>
       </c>
       <c r="F7">
-        <v>28866</v>
+        <v>28867</v>
       </c>
       <c r="G7">
-        <v>41567</v>
+        <v>41568</v>
       </c>
       <c r="H7">
-        <v>24596</v>
+        <v>24595</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>34064</v>
+        <v>35839</v>
       </c>
       <c r="E8">
         <v>72340</v>
       </c>
       <c r="F8">
-        <v>54024</v>
+        <v>54031</v>
       </c>
       <c r="G8">
-        <v>77795</v>
+        <v>77805</v>
       </c>
       <c r="H8">
-        <v>19960</v>
+        <v>18192</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>29528</v>
+        <v>29547</v>
       </c>
       <c r="E9">
         <v>72340</v>
       </c>
       <c r="F9">
-        <v>46024</v>
+        <v>46031</v>
       </c>
       <c r="G9">
-        <v>66275</v>
+        <v>66285</v>
       </c>
       <c r="H9">
-        <v>16496</v>
+        <v>16484</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>40992</v>
+        <v>41019</v>
       </c>
       <c r="E11">
         <v>108519</v>
       </c>
       <c r="F11">
-        <v>64719</v>
+        <v>64730</v>
       </c>
       <c r="G11">
-        <v>93195</v>
+        <v>93211</v>
       </c>
       <c r="H11">
-        <v>23727</v>
+        <v>23711</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11730</v>
+        <v>11738</v>
       </c>
       <c r="E13">
         <v>81385</v>
       </c>
       <c r="F13">
-        <v>38730</v>
+        <v>38738</v>
       </c>
       <c r="G13">
-        <v>55771</v>
+        <v>55783</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>32891</v>
+        <v>32912</v>
       </c>
       <c r="E21">
         <v>101283</v>
       </c>
       <c r="F21">
-        <v>58657</v>
+        <v>58665</v>
       </c>
       <c r="G21">
-        <v>84466</v>
+        <v>84478</v>
       </c>
       <c r="H21">
-        <v>25766</v>
+        <v>25753</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52597</v>
+        <v>52631</v>
       </c>
       <c r="E23">
         <v>130226</v>
       </c>
       <c r="F23">
-        <v>77827</v>
+        <v>77841</v>
       </c>
       <c r="G23">
-        <v>112071</v>
+        <v>112091</v>
       </c>
       <c r="H23">
-        <v>25230</v>
+        <v>25210</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>17532</v>
+        <v>20110</v>
       </c>
       <c r="E27">
         <v>63295</v>
       </c>
       <c r="F27">
-        <v>37698</v>
+        <v>38729</v>
       </c>
       <c r="G27">
-        <v>54285</v>
+        <v>55770</v>
       </c>
       <c r="H27">
-        <v>20166</v>
+        <v>18619</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75291</v>
+        <v>74791</v>
       </c>
       <c r="E28">
         <v>126608</v>
       </c>
       <c r="F28">
-        <v>93335</v>
+        <v>93352</v>
       </c>
       <c r="G28">
-        <v>134402</v>
+        <v>134427</v>
       </c>
       <c r="H28">
-        <v>18044</v>
+        <v>18561</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25180</v>
+        <v>25197</v>
       </c>
       <c r="E29">
         <v>126608</v>
       </c>
       <c r="F29">
-        <v>52180</v>
+        <v>52197</v>
       </c>
       <c r="G29">
-        <v>75139</v>
+        <v>75164</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130578</v>
+        <v>130568</v>
       </c>
       <c r="E30">
         <v>180877</v>
       </c>
       <c r="F30">
-        <v>145578</v>
+        <v>165568</v>
       </c>
       <c r="G30">
-        <v>209632</v>
+        <v>238418</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57258</v>
+        <v>77859</v>
       </c>
       <c r="E31">
         <v>180877</v>
       </c>
       <c r="F31">
-        <v>84258</v>
+        <v>104859</v>
       </c>
       <c r="G31">
-        <v>121332</v>
+        <v>150997</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72085</v>
+        <v>72131</v>
       </c>
       <c r="E32">
         <v>108519</v>
       </c>
       <c r="F32">
-        <v>89447</v>
+        <v>89297</v>
       </c>
       <c r="G32">
-        <v>128804</v>
+        <v>128588</v>
       </c>
       <c r="H32">
-        <v>17362</v>
+        <v>17166</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>49344</v>
+        <v>48969</v>
       </c>
       <c r="E33">
         <v>108519</v>
       </c>
       <c r="F33">
-        <v>68060</v>
+        <v>67910</v>
       </c>
       <c r="G33">
-        <v>98006</v>
+        <v>97790</v>
       </c>
       <c r="H33">
-        <v>18716</v>
+        <v>18941</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,16 +1935,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>79076</v>
+        <v>80206</v>
       </c>
       <c r="E35">
         <v>126608</v>
       </c>
       <c r="F35">
-        <v>94076</v>
+        <v>95206</v>
       </c>
       <c r="G35">
-        <v>135469</v>
+        <v>137097</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45184</v>
+        <v>45213</v>
       </c>
       <c r="E36">
         <v>126608</v>
       </c>
       <c r="F36">
-        <v>72184</v>
+        <v>72213</v>
       </c>
       <c r="G36">
-        <v>103945</v>
+        <v>103987</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35479</v>
       </c>
       <c r="E37">
         <v>126608</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62479</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>89970</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,16 +2113,16 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>81344</v>
+        <v>81396</v>
       </c>
       <c r="E39">
         <v>235145</v>
       </c>
       <c r="F39">
-        <v>108344</v>
+        <v>108396</v>
       </c>
       <c r="G39">
-        <v>156015</v>
+        <v>156090</v>
       </c>
       <c r="H39">
         <v>27000</v>
@@ -2201,16 +2201,16 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>81344</v>
+        <v>81396</v>
       </c>
       <c r="E41">
         <v>235145</v>
       </c>
       <c r="F41">
-        <v>108344</v>
+        <v>108396</v>
       </c>
       <c r="G41">
-        <v>156015</v>
+        <v>156090</v>
       </c>
       <c r="H41">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38584</v>
+        <v>39141</v>
       </c>
       <c r="E43">
         <v>126608</v>
       </c>
       <c r="F43">
-        <v>65584</v>
+        <v>66141</v>
       </c>
       <c r="G43">
-        <v>94441</v>
+        <v>95243</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92479</v>
+        <v>92538</v>
       </c>
       <c r="E45">
         <v>180877</v>
       </c>
       <c r="F45">
-        <v>113534</v>
+        <v>113557</v>
       </c>
       <c r="G45">
-        <v>163489</v>
+        <v>163522</v>
       </c>
       <c r="H45">
-        <v>21055</v>
+        <v>21019</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25712</v>
+        <v>25650</v>
       </c>
       <c r="E47">
         <v>108519</v>
       </c>
       <c r="F47">
-        <v>52712</v>
+        <v>52650</v>
       </c>
       <c r="G47">
-        <v>75905</v>
+        <v>75816</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35956</v>
+        <v>35979</v>
       </c>
       <c r="E50">
         <v>63295</v>
       </c>
       <c r="F50">
-        <v>56251</v>
+        <v>56272</v>
       </c>
       <c r="G50">
-        <v>81001</v>
+        <v>81032</v>
       </c>
       <c r="H50">
-        <v>20295</v>
+        <v>20293</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33251</v>
+        <v>33272</v>
       </c>
       <c r="E51">
         <v>63295</v>
       </c>
       <c r="F51">
-        <v>48251</v>
+        <v>48272</v>
       </c>
       <c r="G51">
-        <v>69481</v>
+        <v>69512</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48781</v>
+        <v>48812</v>
       </c>
       <c r="E54">
         <v>126608</v>
       </c>
       <c r="F54">
-        <v>83781</v>
+        <v>83812</v>
       </c>
       <c r="G54">
-        <v>120645</v>
+        <v>120689</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52144</v>
+        <v>52177</v>
       </c>
       <c r="E55">
         <v>126608</v>
       </c>
       <c r="F55">
-        <v>76235</v>
+        <v>76248</v>
       </c>
       <c r="G55">
-        <v>109778</v>
+        <v>109797</v>
       </c>
       <c r="H55">
-        <v>24091</v>
+        <v>24071</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62701</v>
+        <v>62741</v>
       </c>
       <c r="E57">
         <v>144698</v>
       </c>
       <c r="F57">
-        <v>87513</v>
+        <v>87529</v>
       </c>
       <c r="G57">
-        <v>126019</v>
+        <v>126042</v>
       </c>
       <c r="H57">
-        <v>24812</v>
+        <v>24788</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>24477</v>
+        <v>23553</v>
       </c>
       <c r="E58">
         <v>36161</v>
       </c>
       <c r="F58">
-        <v>39543</v>
+        <v>39545</v>
       </c>
       <c r="G58">
-        <v>56942</v>
+        <v>56945</v>
       </c>
       <c r="H58">
-        <v>15066</v>
+        <v>15992</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6225</v>
+        <v>6229</v>
       </c>
       <c r="E59">
         <v>36161</v>
       </c>
       <c r="F59">
-        <v>22593</v>
+        <v>22595</v>
       </c>
       <c r="G59">
-        <v>32534</v>
+        <v>32537</v>
       </c>
       <c r="H59">
-        <v>16368</v>
+        <v>16366</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,16 +3036,16 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26213</v>
+        <v>26229</v>
       </c>
       <c r="E60">
         <v>48824</v>
       </c>
       <c r="F60">
-        <v>47836</v>
+        <v>47852</v>
       </c>
       <c r="G60">
-        <v>68884</v>
+        <v>68907</v>
       </c>
       <c r="H60">
         <v>21623</v>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24836</v>
+        <v>24852</v>
       </c>
       <c r="E61">
         <v>48824</v>
       </c>
       <c r="F61">
-        <v>39836</v>
+        <v>39852</v>
       </c>
       <c r="G61">
-        <v>57364</v>
+        <v>57387</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12856</v>
+        <v>12864</v>
       </c>
       <c r="E63">
         <v>81385</v>
       </c>
       <c r="F63">
-        <v>39856</v>
+        <v>39864</v>
       </c>
       <c r="G63">
-        <v>57393</v>
+        <v>57404</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28371</v>
+        <v>28248</v>
       </c>
       <c r="E65">
         <v>122068</v>
       </c>
       <c r="F65">
-        <v>55371</v>
+        <v>55248</v>
       </c>
       <c r="G65">
-        <v>79734</v>
+        <v>79557</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24383</v>
+        <v>24289</v>
       </c>
       <c r="E66">
         <v>90429</v>
       </c>
       <c r="F66">
-        <v>53533</v>
+        <v>53545</v>
       </c>
       <c r="G66">
-        <v>77088</v>
+        <v>77105</v>
       </c>
       <c r="H66">
-        <v>29150</v>
+        <v>29256</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18533</v>
+        <v>18545</v>
       </c>
       <c r="E67">
         <v>90429</v>
       </c>
       <c r="F67">
-        <v>45533</v>
+        <v>45545</v>
       </c>
       <c r="G67">
-        <v>65568</v>
+        <v>65585</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34455</v>
+        <v>34446</v>
       </c>
       <c r="E68">
         <v>108519</v>
       </c>
       <c r="F68">
-        <v>62605</v>
+        <v>62622</v>
       </c>
       <c r="G68">
-        <v>90151</v>
+        <v>90176</v>
       </c>
       <c r="H68">
-        <v>28150</v>
+        <v>28176</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27417</v>
+        <v>27434</v>
       </c>
       <c r="E69">
         <v>108519</v>
       </c>
       <c r="F69">
-        <v>54417</v>
+        <v>54434</v>
       </c>
       <c r="G69">
-        <v>78360</v>
+        <v>78385</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45247</v>
+        <v>45275</v>
       </c>
       <c r="E70">
         <v>126608</v>
       </c>
       <c r="F70">
-        <v>80247</v>
+        <v>80275</v>
       </c>
       <c r="G70">
-        <v>115556</v>
+        <v>115596</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50502</v>
+        <v>50534</v>
       </c>
       <c r="E71">
         <v>126608</v>
       </c>
       <c r="F71">
-        <v>75578</v>
+        <v>75591</v>
       </c>
       <c r="G71">
-        <v>108832</v>
+        <v>108851</v>
       </c>
       <c r="H71">
-        <v>25076</v>
+        <v>25057</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5693</v>
+        <v>5697</v>
       </c>
       <c r="E73">
         <v>27116</v>
       </c>
       <c r="F73">
-        <v>20693</v>
+        <v>20697</v>
       </c>
       <c r="G73">
-        <v>29798</v>
+        <v>29804</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70098</v>
+        <v>70143</v>
       </c>
       <c r="E75">
         <v>94952</v>
       </c>
       <c r="F75">
-        <v>85098</v>
+        <v>85143</v>
       </c>
       <c r="G75">
-        <v>122541</v>
+        <v>122606</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,16 +3734,16 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80124</v>
+        <v>80175</v>
       </c>
       <c r="E76">
         <v>126608</v>
       </c>
       <c r="F76">
-        <v>95124</v>
+        <v>95175</v>
       </c>
       <c r="G76">
-        <v>136979</v>
+        <v>137052</v>
       </c>
       <c r="H76">
         <v>15000</v>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>46951</v>
+        <v>46981</v>
       </c>
       <c r="E77">
         <v>126608</v>
       </c>
       <c r="F77">
-        <v>73951</v>
+        <v>73981</v>
       </c>
       <c r="G77">
-        <v>106489</v>
+        <v>106533</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37004</v>
+        <v>37028</v>
       </c>
       <c r="E81">
         <v>90429</v>
       </c>
       <c r="F81">
-        <v>56069</v>
+        <v>56079</v>
       </c>
       <c r="G81">
-        <v>80739</v>
+        <v>80754</v>
       </c>
       <c r="H81">
-        <v>19065</v>
+        <v>19051</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48296</v>
+        <v>48280</v>
       </c>
       <c r="E84">
         <v>101283</v>
       </c>
       <c r="F84">
-        <v>70910</v>
+        <v>70918</v>
       </c>
       <c r="G84">
-        <v>102110</v>
+        <v>102122</v>
       </c>
       <c r="H84">
-        <v>22614</v>
+        <v>22638</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31921</v>
+        <v>31942</v>
       </c>
       <c r="E85">
         <v>101283</v>
       </c>
       <c r="F85">
-        <v>58269</v>
+        <v>58277</v>
       </c>
       <c r="G85">
-        <v>83907</v>
+        <v>83919</v>
       </c>
       <c r="H85">
-        <v>26348</v>
+        <v>26335</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4177,13 +4177,13 @@
         <v>144698</v>
       </c>
       <c r="F86">
-        <v>165077</v>
+        <v>165150</v>
       </c>
       <c r="G86">
-        <v>237711</v>
+        <v>237816</v>
       </c>
       <c r="H86">
-        <v>15190</v>
+        <v>15263</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,16 +4215,16 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113108</v>
+        <v>113181</v>
       </c>
       <c r="E87">
         <v>144698</v>
       </c>
       <c r="F87">
-        <v>128108</v>
+        <v>128181</v>
       </c>
       <c r="G87">
-        <v>184476</v>
+        <v>184581</v>
       </c>
       <c r="H87">
         <v>15000</v>
@@ -4258,7 +4258,7 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>158699</v>
+        <v>158801</v>
       </c>
       <c r="E88">
         <v>159170</v>
@@ -4270,7 +4270,7 @@
         <v>250386</v>
       </c>
       <c r="H88">
-        <v>15180</v>
+        <v>15078</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4352,13 +4352,13 @@
         <v>57868</v>
       </c>
       <c r="F90">
-        <v>38276</v>
+        <v>38277</v>
       </c>
       <c r="G90">
-        <v>55117</v>
+        <v>55119</v>
       </c>
       <c r="H90">
-        <v>30596</v>
+        <v>30597</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4270</v>
+        <v>4272</v>
       </c>
       <c r="E91">
         <v>57868</v>
       </c>
       <c r="F91">
-        <v>30276</v>
+        <v>30277</v>
       </c>
       <c r="G91">
-        <v>43597</v>
+        <v>43599</v>
       </c>
       <c r="H91">
-        <v>26006</v>
+        <v>26005</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4614,13 +4614,13 @@
         <v>81385</v>
       </c>
       <c r="F96">
-        <v>76395</v>
+        <v>76403</v>
       </c>
       <c r="G96">
-        <v>110009</v>
+        <v>110020</v>
       </c>
       <c r="H96">
-        <v>15220</v>
+        <v>15228</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33517</v>
+        <v>33538</v>
       </c>
       <c r="E97">
         <v>81385</v>
       </c>
       <c r="F97">
-        <v>51147</v>
+        <v>51155</v>
       </c>
       <c r="G97">
-        <v>73652</v>
+        <v>73663</v>
       </c>
       <c r="H97">
-        <v>17630</v>
+        <v>17617</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4704,13 +4704,13 @@
         <v>94047</v>
       </c>
       <c r="F98">
-        <v>89334</v>
+        <v>89343</v>
       </c>
       <c r="G98">
-        <v>128641</v>
+        <v>128654</v>
       </c>
       <c r="H98">
-        <v>15141</v>
+        <v>15150</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33517</v>
+        <v>33538</v>
       </c>
       <c r="E99">
         <v>94047</v>
       </c>
       <c r="F99">
-        <v>56085</v>
+        <v>56094</v>
       </c>
       <c r="G99">
-        <v>80762</v>
+        <v>80775</v>
       </c>
       <c r="H99">
-        <v>22568</v>
+        <v>22556</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61356</v>
+        <v>61395</v>
       </c>
       <c r="E100">
         <v>105444</v>
@@ -4800,7 +4800,7 @@
         <v>113880</v>
       </c>
       <c r="H100">
-        <v>17727</v>
+        <v>17688</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61059</v>
+        <v>61098</v>
       </c>
       <c r="E101">
         <v>105444</v>
       </c>
       <c r="F101">
-        <v>76059</v>
+        <v>76098</v>
       </c>
       <c r="G101">
-        <v>109525</v>
+        <v>109581</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>72007</v>
+        <v>72053</v>
       </c>
       <c r="E105">
         <v>126608</v>
       </c>
       <c r="F105">
-        <v>87007</v>
+        <v>87053</v>
       </c>
       <c r="G105">
-        <v>125290</v>
+        <v>125356</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>100065</v>
+        <v>100129</v>
       </c>
       <c r="E107">
         <v>180877</v>
       </c>
       <c r="F107">
-        <v>116568</v>
+        <v>116594</v>
       </c>
       <c r="G107">
-        <v>167858</v>
+        <v>167895</v>
       </c>
       <c r="H107">
-        <v>16503</v>
+        <v>16465</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3973</v>
+        <v>3975</v>
       </c>
       <c r="E109">
         <v>126608</v>
       </c>
       <c r="F109">
-        <v>30973</v>
+        <v>30975</v>
       </c>
       <c r="G109">
-        <v>44601</v>
+        <v>44604</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13372</v>
+        <v>13381</v>
       </c>
       <c r="E111">
         <v>162787</v>
       </c>
       <c r="F111">
-        <v>40372</v>
+        <v>40381</v>
       </c>
       <c r="G111">
-        <v>58136</v>
+        <v>58149</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>84675</v>
+        <v>84729</v>
       </c>
       <c r="E115">
         <v>115755</v>
       </c>
       <c r="F115">
-        <v>99675</v>
+        <v>99729</v>
       </c>
       <c r="G115">
-        <v>143532</v>
+        <v>143610</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>110317</v>
       </c>
       <c r="E117">
         <v>144698</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>125317</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>180456</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60552</v>
+        <v>60925</v>
       </c>
       <c r="E120">
         <v>79576</v>
       </c>
       <c r="F120">
-        <v>78798</v>
+        <v>78837</v>
       </c>
       <c r="G120">
-        <v>113469</v>
+        <v>113525</v>
       </c>
       <c r="H120">
-        <v>18246</v>
+        <v>17912</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53520</v>
+        <v>53554</v>
       </c>
       <c r="E121">
         <v>79576</v>
       </c>
       <c r="F121">
-        <v>68520</v>
+        <v>68554</v>
       </c>
       <c r="G121">
-        <v>98669</v>
+        <v>98718</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>53113</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>90429</v>
       </c>
       <c r="F122">
-        <v>68113</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>98083</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>34173</v>
+        <v>33945</v>
       </c>
       <c r="E123">
         <v>90429</v>
       </c>
       <c r="F123">
-        <v>54937</v>
+        <v>54845</v>
       </c>
       <c r="G123">
-        <v>79109</v>
+        <v>78977</v>
       </c>
       <c r="H123">
-        <v>20764</v>
+        <v>20900</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7304</v>
+        <v>7309</v>
       </c>
       <c r="E125">
         <v>43397</v>
       </c>
       <c r="F125">
-        <v>25846</v>
+        <v>25848</v>
       </c>
       <c r="G125">
-        <v>37218</v>
+        <v>37221</v>
       </c>
       <c r="H125">
-        <v>18542</v>
+        <v>18539</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20160</v>
+        <v>20173</v>
       </c>
       <c r="E129">
         <v>59297</v>
       </c>
       <c r="F129">
-        <v>37190</v>
+        <v>37195</v>
       </c>
       <c r="G129">
-        <v>53554</v>
+        <v>53561</v>
       </c>
       <c r="H129">
-        <v>17030</v>
+        <v>17022</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20160</v>
+        <v>20173</v>
       </c>
       <c r="E131">
         <v>73878</v>
       </c>
       <c r="F131">
-        <v>42877</v>
+        <v>42882</v>
       </c>
       <c r="G131">
-        <v>61743</v>
+        <v>61750</v>
       </c>
       <c r="H131">
-        <v>22717</v>
+        <v>22709</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33063</v>
+        <v>33084</v>
       </c>
       <c r="E133">
         <v>92998</v>
       </c>
       <c r="F133">
-        <v>55495</v>
+        <v>55503</v>
       </c>
       <c r="G133">
-        <v>79913</v>
+        <v>79924</v>
       </c>
       <c r="H133">
-        <v>22432</v>
+        <v>22419</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37364</v>
+        <v>37388</v>
       </c>
       <c r="E140">
         <v>90429</v>
       </c>
       <c r="F140">
-        <v>61639</v>
+        <v>61648</v>
       </c>
       <c r="G140">
-        <v>88760</v>
+        <v>88773</v>
       </c>
       <c r="H140">
-        <v>24275</v>
+        <v>24260</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26744</v>
+        <v>26762</v>
       </c>
       <c r="E142">
         <v>90429</v>
       </c>
       <c r="F142">
-        <v>60209</v>
+        <v>60216</v>
       </c>
       <c r="G142">
-        <v>86701</v>
+        <v>86711</v>
       </c>
       <c r="H142">
-        <v>33465</v>
+        <v>33454</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27354</v>
+        <v>27372</v>
       </c>
       <c r="E143">
         <v>90429</v>
       </c>
       <c r="F143">
-        <v>52209</v>
+        <v>52216</v>
       </c>
       <c r="G143">
-        <v>75181</v>
+        <v>75191</v>
       </c>
       <c r="H143">
-        <v>24855</v>
+        <v>24844</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>60120</v>
+        <v>46089</v>
       </c>
       <c r="E144">
         <v>90429</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>67822</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>97664</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>21733</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>79967</v>
+        <v>80018</v>
       </c>
       <c r="E145">
         <v>90429</v>
       </c>
       <c r="F145">
-        <v>94967</v>
+        <v>95018</v>
       </c>
       <c r="G145">
-        <v>136752</v>
+        <v>136826</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58009</v>
+        <v>58046</v>
       </c>
       <c r="E146">
         <v>90429</v>
       </c>
       <c r="F146">
-        <v>93009</v>
+        <v>73046</v>
       </c>
       <c r="G146">
-        <v>133933</v>
+        <v>105186</v>
       </c>
       <c r="H146">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>93699</v>
+        <v>0</v>
       </c>
       <c r="E147">
         <v>90429</v>
       </c>
       <c r="F147">
-        <v>108699</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>156527</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36754</v>
+        <v>36746</v>
       </c>
       <c r="E148">
         <v>61486</v>
@@ -6895,7 +6895,7 @@
         <v>92032</v>
       </c>
       <c r="H148">
-        <v>27157</v>
+        <v>27165</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15233</v>
+        <v>15634</v>
       </c>
       <c r="E151">
         <v>54250</v>
       </c>
       <c r="F151">
-        <v>33251</v>
+        <v>33411</v>
       </c>
       <c r="G151">
-        <v>47881</v>
+        <v>48112</v>
       </c>
       <c r="H151">
-        <v>18018</v>
+        <v>17777</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37395</v>
+        <v>37450</v>
       </c>
       <c r="E152">
         <v>72340</v>
@@ -7070,7 +7070,7 @@
         <v>78127</v>
       </c>
       <c r="H152">
-        <v>16860</v>
+        <v>16805</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33219</v>
+        <v>33241</v>
       </c>
       <c r="E153">
         <v>72340</v>
       </c>
       <c r="F153">
-        <v>48219</v>
+        <v>48241</v>
       </c>
       <c r="G153">
-        <v>69435</v>
+        <v>69467</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56632</v>
+        <v>56622</v>
       </c>
       <c r="E154">
         <v>72340</v>
       </c>
       <c r="F154">
-        <v>83889</v>
+        <v>91622</v>
       </c>
       <c r="G154">
-        <v>120800</v>
+        <v>131936</v>
       </c>
       <c r="H154">
-        <v>27257</v>
+        <v>35000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>57915</v>
+        <v>72600</v>
       </c>
       <c r="E155">
         <v>72340</v>
       </c>
       <c r="F155">
-        <v>72915</v>
+        <v>87600</v>
       </c>
       <c r="G155">
-        <v>104998</v>
+        <v>126144</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>34690</v>
+        <v>34461</v>
       </c>
       <c r="E156">
         <v>59677</v>
       </c>
       <c r="F156">
-        <v>49690</v>
+        <v>49693</v>
       </c>
       <c r="G156">
-        <v>71554</v>
+        <v>71558</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>15232</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11871</v>
+        <v>11878</v>
       </c>
       <c r="E157">
         <v>59677</v>
       </c>
       <c r="F157">
-        <v>34022</v>
+        <v>34025</v>
       </c>
       <c r="G157">
-        <v>48992</v>
+        <v>48996</v>
       </c>
       <c r="H157">
-        <v>22151</v>
+        <v>22147</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7324,19 +7324,19 @@
         <v>15</v>
       </c>
       <c r="D158">
-        <v>84722</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>83194</v>
       </c>
       <c r="F158">
-        <v>99722</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>143600</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I158" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54269</v>
       </c>
       <c r="F160">
-        <v>38537</v>
+        <v>38602</v>
       </c>
       <c r="G160">
-        <v>55493</v>
+        <v>55587</v>
       </c>
       <c r="H160">
-        <v>30857</v>
+        <v>30922</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8430</v>
+        <v>8592</v>
       </c>
       <c r="E161">
         <v>54269</v>
       </c>
       <c r="F161">
-        <v>30537</v>
+        <v>30602</v>
       </c>
       <c r="G161">
-        <v>43973</v>
+        <v>44067</v>
       </c>
       <c r="H161">
-        <v>22107</v>
+        <v>22010</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>72340</v>
       </c>
       <c r="F162">
-        <v>44040</v>
+        <v>44046</v>
       </c>
       <c r="G162">
-        <v>63418</v>
+        <v>63426</v>
       </c>
       <c r="H162">
-        <v>33893</v>
+        <v>33899</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9040</v>
+        <v>9046</v>
       </c>
       <c r="E163">
         <v>72340</v>
       </c>
       <c r="F163">
-        <v>36040</v>
+        <v>36046</v>
       </c>
       <c r="G163">
-        <v>51898</v>
+        <v>51906</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7597,13 +7597,13 @@
         <v>67836</v>
       </c>
       <c r="F164">
-        <v>82065</v>
+        <v>82071</v>
       </c>
       <c r="G164">
-        <v>118174</v>
+        <v>118182</v>
       </c>
       <c r="H164">
-        <v>15199</v>
+        <v>15205</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20801</v>
+        <v>20815</v>
       </c>
       <c r="E165">
         <v>67836</v>
       </c>
       <c r="F165">
-        <v>40776</v>
+        <v>40782</v>
       </c>
       <c r="G165">
-        <v>58717</v>
+        <v>58726</v>
       </c>
       <c r="H165">
-        <v>19975</v>
+        <v>19967</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7685,13 +7685,13 @@
         <v>102206</v>
       </c>
       <c r="F166">
-        <v>105410</v>
+        <v>105424</v>
       </c>
       <c r="G166">
-        <v>151790</v>
+        <v>151811</v>
       </c>
       <c r="H166">
-        <v>15397</v>
+        <v>15411</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21896</v>
+        <v>21910</v>
       </c>
       <c r="E167">
         <v>102206</v>
       </c>
       <c r="F167">
-        <v>48896</v>
+        <v>48910</v>
       </c>
       <c r="G167">
-        <v>70410</v>
+        <v>70430</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>72340</v>
       </c>
       <c r="F168">
-        <v>103833</v>
+        <v>103839</v>
       </c>
       <c r="G168">
-        <v>149520</v>
+        <v>149528</v>
       </c>
       <c r="H168">
-        <v>15012</v>
+        <v>15018</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8805</v>
+        <v>8811</v>
       </c>
       <c r="E169">
         <v>72340</v>
       </c>
       <c r="F169">
-        <v>35805</v>
+        <v>35811</v>
       </c>
       <c r="G169">
-        <v>51559</v>
+        <v>51568</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59260</v>
+        <v>59298</v>
       </c>
       <c r="E170">
         <v>108519</v>
       </c>
       <c r="F170">
-        <v>80055</v>
+        <v>80081</v>
       </c>
       <c r="G170">
-        <v>115279</v>
+        <v>115317</v>
       </c>
       <c r="H170">
-        <v>20795</v>
+        <v>20783</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>53082</v>
+        <v>53147</v>
       </c>
       <c r="E171">
         <v>108519</v>
       </c>
       <c r="F171">
-        <v>69555</v>
+        <v>69581</v>
       </c>
       <c r="G171">
-        <v>100159</v>
+        <v>100197</v>
       </c>
       <c r="H171">
-        <v>16473</v>
+        <v>16434</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78341</v>
+        <v>78391</v>
       </c>
       <c r="E172">
         <v>144698</v>
       </c>
       <c r="F172">
-        <v>107748</v>
+        <v>107771</v>
       </c>
       <c r="G172">
-        <v>155157</v>
+        <v>155190</v>
       </c>
       <c r="H172">
-        <v>29407</v>
+        <v>29380</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78153</v>
+        <v>78203</v>
       </c>
       <c r="E173">
         <v>144698</v>
       </c>
       <c r="F173">
-        <v>93694</v>
+        <v>93714</v>
       </c>
       <c r="G173">
-        <v>134919</v>
+        <v>134948</v>
       </c>
       <c r="H173">
-        <v>15541</v>
+        <v>15511</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>47217</v>
+        <v>46762</v>
       </c>
       <c r="E174">
         <v>90429</v>
@@ -8045,7 +8045,7 @@
         <v>97664</v>
       </c>
       <c r="H174">
-        <v>20605</v>
+        <v>21060</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>27354</v>
+        <v>26902</v>
       </c>
       <c r="E178">
         <v>108519</v>
       </c>
       <c r="F178">
-        <v>54354</v>
+        <v>53902</v>
       </c>
       <c r="G178">
-        <v>78270</v>
+        <v>77619</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>23992</v>
+        <v>23553</v>
       </c>
       <c r="E180">
         <v>90429</v>
       </c>
       <c r="F180">
-        <v>50992</v>
+        <v>50553</v>
       </c>
       <c r="G180">
-        <v>73428</v>
+        <v>72796</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8393,13 +8393,13 @@
         <v>126608</v>
       </c>
       <c r="F182">
-        <v>115014</v>
+        <v>115031</v>
       </c>
       <c r="G182">
-        <v>165620</v>
+        <v>165645</v>
       </c>
       <c r="H182">
-        <v>15254</v>
+        <v>15271</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64280</v>
+        <v>64322</v>
       </c>
       <c r="E183">
         <v>126608</v>
       </c>
       <c r="F183">
-        <v>81089</v>
+        <v>81106</v>
       </c>
       <c r="G183">
-        <v>116768</v>
+        <v>116793</v>
       </c>
       <c r="H183">
-        <v>16809</v>
+        <v>16784</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>143872</v>
+        <v>143964</v>
       </c>
       <c r="E184">
         <v>180877</v>
       </c>
       <c r="F184">
-        <v>159389</v>
+        <v>159431</v>
       </c>
       <c r="G184">
-        <v>229520</v>
+        <v>229581</v>
       </c>
       <c r="H184">
-        <v>15517</v>
+        <v>15467</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64280</v>
+        <v>64322</v>
       </c>
       <c r="E185">
         <v>180877</v>
       </c>
       <c r="F185">
-        <v>91280</v>
+        <v>91322</v>
       </c>
       <c r="G185">
-        <v>131443</v>
+        <v>131504</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64280</v>
+        <v>64322</v>
       </c>
       <c r="E187">
         <v>180877</v>
       </c>
       <c r="F187">
-        <v>91280</v>
+        <v>91322</v>
       </c>
       <c r="G187">
-        <v>131443</v>
+        <v>131504</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8648,16 +8648,16 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>289324</v>
+        <v>289509</v>
       </c>
       <c r="E188">
         <v>361772</v>
       </c>
       <c r="F188">
-        <v>324324</v>
+        <v>324509</v>
       </c>
       <c r="G188">
-        <v>467027</v>
+        <v>467293</v>
       </c>
       <c r="H188">
         <v>35000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>304620</v>
+        <v>304815</v>
       </c>
       <c r="E189">
         <v>361772</v>
       </c>
       <c r="F189">
-        <v>319620</v>
+        <v>319815</v>
       </c>
       <c r="G189">
-        <v>460253</v>
+        <v>460534</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29857</v>
+        <v>29751</v>
       </c>
       <c r="E190">
         <v>94952</v>
       </c>
       <c r="F190">
-        <v>64857</v>
+        <v>64751</v>
       </c>
       <c r="G190">
-        <v>93394</v>
+        <v>93241</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44199</v>
+        <v>44227</v>
       </c>
       <c r="E191">
         <v>94952</v>
       </c>
       <c r="F191">
-        <v>60711</v>
+        <v>60722</v>
       </c>
       <c r="G191">
-        <v>87424</v>
+        <v>87440</v>
       </c>
       <c r="H191">
-        <v>16512</v>
+        <v>16495</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>43495</v>
+        <v>43476</v>
       </c>
       <c r="E192">
         <v>122086</v>
       </c>
       <c r="F192">
-        <v>78495</v>
+        <v>78476</v>
       </c>
       <c r="G192">
-        <v>113033</v>
+        <v>113005</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>49766</v>
+        <v>49673</v>
       </c>
       <c r="E194">
         <v>149401</v>
       </c>
       <c r="F194">
-        <v>76766</v>
+        <v>76673</v>
       </c>
       <c r="G194">
-        <v>110543</v>
+        <v>110409</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -9044,16 +9044,16 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32218</v>
+        <v>32239</v>
       </c>
       <c r="E197">
         <v>72340</v>
       </c>
       <c r="F197">
-        <v>47218</v>
+        <v>47239</v>
       </c>
       <c r="G197">
-        <v>67994</v>
+        <v>68024</v>
       </c>
       <c r="H197">
         <v>15000</v>
@@ -9087,19 +9087,19 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26400</v>
+        <v>26417</v>
       </c>
       <c r="E198">
         <v>108519</v>
       </c>
       <c r="F198">
-        <v>61400</v>
+        <v>53417</v>
       </c>
       <c r="G198">
-        <v>88416</v>
+        <v>76920</v>
       </c>
       <c r="H198">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I198" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9133,19 +9133,19 @@
         <v>17</v>
       </c>
       <c r="D199">
-        <v>37161</v>
+        <v>0</v>
       </c>
       <c r="E199">
         <v>108519</v>
       </c>
       <c r="F199">
-        <v>63187</v>
+        <v>0</v>
       </c>
       <c r="G199">
-        <v>90989</v>
+        <v>0</v>
       </c>
       <c r="H199">
-        <v>26026</v>
+        <v>0</v>
       </c>
       <c r="I199" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9182,13 +9182,13 @@
         <v>126608</v>
       </c>
       <c r="F200">
-        <v>46902</v>
+        <v>46910</v>
       </c>
       <c r="G200">
-        <v>67539</v>
+        <v>67550</v>
       </c>
       <c r="H200">
-        <v>32837</v>
+        <v>32845</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11902</v>
+        <v>11910</v>
       </c>
       <c r="E201">
         <v>126608</v>
       </c>
       <c r="F201">
-        <v>38902</v>
+        <v>38910</v>
       </c>
       <c r="G201">
-        <v>56019</v>
+        <v>56030</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22506</v>
+        <v>22520</v>
       </c>
       <c r="E203">
         <v>144698</v>
       </c>
       <c r="F203">
-        <v>49506</v>
+        <v>49520</v>
       </c>
       <c r="G203">
-        <v>71289</v>
+        <v>71309</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>180877</v>
       </c>
       <c r="F204">
-        <v>61166</v>
+        <v>61057</v>
       </c>
       <c r="G204">
-        <v>88079</v>
+        <v>87922</v>
       </c>
       <c r="H204">
-        <v>32428</v>
+        <v>32319</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,16 +9402,16 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26166</v>
+        <v>26057</v>
       </c>
       <c r="E205">
         <v>180877</v>
       </c>
       <c r="F205">
-        <v>53166</v>
+        <v>53057</v>
       </c>
       <c r="G205">
-        <v>76559</v>
+        <v>76402</v>
       </c>
       <c r="H205">
         <v>27000</v>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24242</v>
+        <v>24258</v>
       </c>
       <c r="E206">
         <v>57868</v>
       </c>
       <c r="F206">
-        <v>42044</v>
+        <v>42047</v>
       </c>
       <c r="G206">
-        <v>60543</v>
+        <v>60548</v>
       </c>
       <c r="H206">
-        <v>17802</v>
+        <v>17789</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12981</v>
+        <v>12990</v>
       </c>
       <c r="E207">
         <v>57868</v>
       </c>
       <c r="F207">
-        <v>33761</v>
+        <v>33764</v>
       </c>
       <c r="G207">
-        <v>48616</v>
+        <v>48620</v>
       </c>
       <c r="H207">
-        <v>20780</v>
+        <v>20774</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22819</v>
+        <v>22833</v>
       </c>
       <c r="E209">
         <v>54250</v>
       </c>
       <c r="F209">
-        <v>37819</v>
+        <v>37833</v>
       </c>
       <c r="G209">
-        <v>54459</v>
+        <v>54480</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40070</v>
+        <v>40095</v>
       </c>
       <c r="E211">
         <v>108519</v>
       </c>
       <c r="F211">
-        <v>64350</v>
+        <v>64360</v>
       </c>
       <c r="G211">
-        <v>92664</v>
+        <v>92678</v>
       </c>
       <c r="H211">
-        <v>24280</v>
+        <v>24265</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>82939</v>
+        <v>82992</v>
       </c>
       <c r="E213">
         <v>180877</v>
       </c>
       <c r="F213">
-        <v>109718</v>
+        <v>109739</v>
       </c>
       <c r="G213">
-        <v>157994</v>
+        <v>158024</v>
       </c>
       <c r="H213">
-        <v>26779</v>
+        <v>26747</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28168</v>
+        <v>28154</v>
       </c>
       <c r="E214">
         <v>86812</v>
       </c>
       <c r="F214">
-        <v>60262</v>
+        <v>60270</v>
       </c>
       <c r="G214">
-        <v>86777</v>
+        <v>86789</v>
       </c>
       <c r="H214">
-        <v>32094</v>
+        <v>32116</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31014</v>
+        <v>31034</v>
       </c>
       <c r="E215">
         <v>86812</v>
       </c>
       <c r="F215">
-        <v>52262</v>
+        <v>52270</v>
       </c>
       <c r="G215">
-        <v>75257</v>
+        <v>75269</v>
       </c>
       <c r="H215">
-        <v>21248</v>
+        <v>21236</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45638</v>
+        <v>45667</v>
       </c>
       <c r="E216">
         <v>101283</v>
@@ -9893,7 +9893,7 @@
         <v>109385</v>
       </c>
       <c r="H216">
-        <v>30324</v>
+        <v>30295</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88475</v>
+        <v>88532</v>
       </c>
       <c r="E217">
         <v>101283</v>
       </c>
       <c r="F217">
-        <v>103475</v>
+        <v>103532</v>
       </c>
       <c r="G217">
-        <v>149004</v>
+        <v>149086</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>110262</v>
+        <v>110333</v>
       </c>
       <c r="E219">
         <v>130226</v>
       </c>
       <c r="F219">
-        <v>125262</v>
+        <v>125333</v>
       </c>
       <c r="G219">
-        <v>180377</v>
+        <v>180480</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10065,13 +10065,13 @@
         <v>81403</v>
       </c>
       <c r="F220">
-        <v>75938</v>
+        <v>75783</v>
       </c>
       <c r="G220">
-        <v>109351</v>
+        <v>109128</v>
       </c>
       <c r="H220">
-        <v>16651</v>
+        <v>16496</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>51033</v>
+        <v>50878</v>
       </c>
       <c r="E221">
         <v>81403</v>
       </c>
       <c r="F221">
-        <v>66033</v>
+        <v>65878</v>
       </c>
       <c r="G221">
-        <v>95088</v>
+        <v>94864</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10149,16 +10149,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74118</v>
+        <v>74165</v>
       </c>
       <c r="E222">
         <v>95874</v>
       </c>
       <c r="F222">
-        <v>109118</v>
+        <v>109165</v>
       </c>
       <c r="G222">
-        <v>157130</v>
+        <v>157198</v>
       </c>
       <c r="H222">
         <v>35000</v>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>93105</v>
+        <v>90535</v>
       </c>
       <c r="E223">
         <v>95874</v>
       </c>
       <c r="F223">
-        <v>108105</v>
+        <v>105535</v>
       </c>
       <c r="G223">
-        <v>155671</v>
+        <v>151970</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>59677</v>
       </c>
       <c r="F224">
-        <v>41422</v>
+        <v>41424</v>
       </c>
       <c r="G224">
-        <v>59648</v>
+        <v>59651</v>
       </c>
       <c r="H224">
-        <v>24844</v>
+        <v>24846</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10369</v>
+        <v>10376</v>
       </c>
       <c r="E225">
         <v>59677</v>
       </c>
       <c r="F225">
-        <v>33422</v>
+        <v>33424</v>
       </c>
       <c r="G225">
-        <v>48128</v>
+        <v>48131</v>
       </c>
       <c r="H225">
-        <v>23053</v>
+        <v>23048</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37630</v>
+        <v>37654</v>
       </c>
       <c r="E226">
         <v>72340</v>
       </c>
       <c r="F226">
-        <v>53613</v>
+        <v>53620</v>
       </c>
       <c r="G226">
-        <v>77203</v>
+        <v>77213</v>
       </c>
       <c r="H226">
-        <v>15983</v>
+        <v>15966</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25837</v>
+        <v>25854</v>
       </c>
       <c r="E227">
         <v>72340</v>
       </c>
       <c r="F227">
-        <v>44547</v>
+        <v>44554</v>
       </c>
       <c r="G227">
-        <v>64148</v>
+        <v>64158</v>
       </c>
       <c r="H227">
-        <v>18710</v>
+        <v>18700</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,16 +10418,16 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83095</v>
+        <v>83148</v>
       </c>
       <c r="E228">
         <v>108519</v>
       </c>
       <c r="F228">
-        <v>98095</v>
+        <v>98148</v>
       </c>
       <c r="G228">
-        <v>141257</v>
+        <v>141333</v>
       </c>
       <c r="H228">
         <v>15000</v>
@@ -10461,16 +10461,16 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13231</v>
+        <v>13240</v>
       </c>
       <c r="E229">
         <v>108519</v>
       </c>
       <c r="F229">
-        <v>40231</v>
+        <v>40240</v>
       </c>
       <c r="G229">
-        <v>57933</v>
+        <v>57946</v>
       </c>
       <c r="H229">
         <v>27000</v>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19065</v>
+        <v>19077</v>
       </c>
       <c r="E231">
         <v>180877</v>
       </c>
       <c r="F231">
-        <v>46065</v>
+        <v>46077</v>
       </c>
       <c r="G231">
-        <v>66334</v>
+        <v>66351</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10595,13 +10595,13 @@
         <v>52460</v>
       </c>
       <c r="F232">
-        <v>38426</v>
+        <v>38428</v>
       </c>
       <c r="G232">
-        <v>55333</v>
+        <v>55336</v>
       </c>
       <c r="H232">
-        <v>29091</v>
+        <v>29093</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9916</v>
+        <v>9922</v>
       </c>
       <c r="E233">
         <v>52460</v>
       </c>
       <c r="F233">
-        <v>30426</v>
+        <v>30428</v>
       </c>
       <c r="G233">
-        <v>43813</v>
+        <v>43816</v>
       </c>
       <c r="H233">
-        <v>20510</v>
+        <v>20506</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52460</v>
       </c>
       <c r="F236">
-        <v>37225</v>
+        <v>37226</v>
       </c>
       <c r="G236">
-        <v>53604</v>
+        <v>53605</v>
       </c>
       <c r="H236">
-        <v>28874</v>
+        <v>28875</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6913</v>
+        <v>6917</v>
       </c>
       <c r="E237">
         <v>52460</v>
       </c>
       <c r="F237">
-        <v>29225</v>
+        <v>29226</v>
       </c>
       <c r="G237">
-        <v>42084</v>
+        <v>42085</v>
       </c>
       <c r="H237">
-        <v>22312</v>
+        <v>22309</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11292</v>
+        <v>11299</v>
       </c>
       <c r="E239">
         <v>52460</v>
       </c>
       <c r="F239">
-        <v>30976</v>
+        <v>30979</v>
       </c>
       <c r="G239">
-        <v>44605</v>
+        <v>44610</v>
       </c>
       <c r="H239">
-        <v>19684</v>
+        <v>19680</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,7 +10941,7 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24054</v>
+        <v>24070</v>
       </c>
       <c r="E240">
         <v>70549</v>
@@ -10953,7 +10953,7 @@
         <v>76193</v>
       </c>
       <c r="H240">
-        <v>28858</v>
+        <v>28842</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>71271</v>
+        <v>71880</v>
       </c>
       <c r="E241">
         <v>70549</v>
       </c>
       <c r="F241">
-        <v>86271</v>
+        <v>86880</v>
       </c>
       <c r="G241">
-        <v>124230</v>
+        <v>125107</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34048</v>
+        <v>34039</v>
       </c>
       <c r="E242">
         <v>70549</v>
       </c>
       <c r="F242">
-        <v>51366</v>
+        <v>51363</v>
       </c>
       <c r="G242">
-        <v>73967</v>
+        <v>73963</v>
       </c>
       <c r="H242">
-        <v>17318</v>
+        <v>17324</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92292</v>
+        <v>92351</v>
       </c>
       <c r="E246">
         <v>108519</v>
       </c>
       <c r="F246">
-        <v>107292</v>
+        <v>107351</v>
       </c>
       <c r="G246">
-        <v>154500</v>
+        <v>154585</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>58993</v>
+        <v>67139</v>
       </c>
       <c r="E248">
         <v>95874</v>
       </c>
       <c r="F248">
-        <v>74242</v>
+        <v>0</v>
       </c>
       <c r="G248">
-        <v>106908</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>15249</v>
+        <v>0</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>47999</v>
+        <v>48139</v>
       </c>
       <c r="E249">
         <v>95874</v>
       </c>
       <c r="F249">
-        <v>62999</v>
+        <v>63139</v>
       </c>
       <c r="G249">
-        <v>90719</v>
+        <v>90920</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73008</v>
+        <v>72945</v>
       </c>
       <c r="E250">
         <v>108519</v>
       </c>
       <c r="F250">
-        <v>103707</v>
+        <v>103176</v>
       </c>
       <c r="G250">
-        <v>149338</v>
+        <v>148573</v>
       </c>
       <c r="H250">
-        <v>30699</v>
+        <v>30231</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>75166</v>
+        <v>74635</v>
       </c>
       <c r="E251">
         <v>108519</v>
       </c>
       <c r="F251">
-        <v>90166</v>
+        <v>89635</v>
       </c>
       <c r="G251">
-        <v>129839</v>
+        <v>129074</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11515,16 +11515,16 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38396</v>
+        <v>38421</v>
       </c>
       <c r="E253">
         <v>52460</v>
       </c>
       <c r="F253">
-        <v>53396</v>
+        <v>53421</v>
       </c>
       <c r="G253">
-        <v>76890</v>
+        <v>76926</v>
       </c>
       <c r="H253">
         <v>15000</v>
@@ -11558,7 +11558,7 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24179</v>
+        <v>24195</v>
       </c>
       <c r="E254">
         <v>70549</v>
@@ -11570,7 +11570,7 @@
         <v>76193</v>
       </c>
       <c r="H254">
-        <v>28733</v>
+        <v>28717</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69238</v>
+        <v>69283</v>
       </c>
       <c r="E255">
         <v>70549</v>
       </c>
       <c r="F255">
-        <v>84238</v>
+        <v>84283</v>
       </c>
       <c r="G255">
-        <v>121303</v>
+        <v>121368</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12496</v>
+        <v>12504</v>
       </c>
       <c r="E259">
         <v>50633</v>
       </c>
       <c r="F259">
-        <v>30745</v>
+        <v>30748</v>
       </c>
       <c r="G259">
-        <v>44273</v>
+        <v>44277</v>
       </c>
       <c r="H259">
-        <v>18249</v>
+        <v>18244</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12496</v>
+        <v>12504</v>
       </c>
       <c r="E261">
         <v>63295</v>
       </c>
       <c r="F261">
-        <v>35684</v>
+        <v>35687</v>
       </c>
       <c r="G261">
-        <v>51385</v>
+        <v>51389</v>
       </c>
       <c r="H261">
-        <v>23188</v>
+        <v>23183</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12496</v>
+        <v>12504</v>
       </c>
       <c r="E263">
         <v>72340</v>
       </c>
       <c r="F263">
-        <v>39211</v>
+        <v>39214</v>
       </c>
       <c r="G263">
-        <v>56464</v>
+        <v>56468</v>
       </c>
       <c r="H263">
-        <v>26715</v>
+        <v>26710</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39397</v>
+        <v>39422</v>
       </c>
       <c r="E264">
         <v>59677</v>
       </c>
       <c r="F264">
-        <v>54856</v>
+        <v>54566</v>
       </c>
       <c r="G264">
-        <v>78993</v>
+        <v>78575</v>
       </c>
       <c r="H264">
-        <v>15459</v>
+        <v>15144</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23929</v>
+        <v>23412</v>
       </c>
       <c r="E265">
         <v>59677</v>
       </c>
       <c r="F265">
-        <v>38929</v>
+        <v>38639</v>
       </c>
       <c r="G265">
-        <v>56058</v>
+        <v>55640</v>
       </c>
       <c r="H265">
-        <v>15000</v>
+        <v>15227</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35550</v>
+        <v>34790</v>
       </c>
       <c r="E268">
         <v>59677</v>
       </c>
       <c r="F268">
-        <v>50596</v>
+        <v>50527</v>
       </c>
       <c r="G268">
-        <v>72858</v>
+        <v>72759</v>
       </c>
       <c r="H268">
-        <v>15046</v>
+        <v>15737</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23632</v>
+        <v>23459</v>
       </c>
       <c r="E269">
         <v>59677</v>
       </c>
       <c r="F269">
-        <v>38727</v>
+        <v>38658</v>
       </c>
       <c r="G269">
-        <v>55767</v>
+        <v>55668</v>
       </c>
       <c r="H269">
-        <v>15095</v>
+        <v>15199</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12260,19 +12260,19 @@
         <v>15</v>
       </c>
       <c r="D270">
-        <v>38944</v>
+        <v>0</v>
       </c>
       <c r="E270">
         <v>66913</v>
       </c>
       <c r="F270">
-        <v>53998</v>
+        <v>0</v>
       </c>
       <c r="G270">
-        <v>77757</v>
+        <v>0</v>
       </c>
       <c r="H270">
-        <v>15054</v>
+        <v>0</v>
       </c>
       <c r="I270" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>28965</v>
+        <v>28984</v>
       </c>
       <c r="E271">
         <v>66913</v>
       </c>
       <c r="F271">
-        <v>43965</v>
+        <v>43984</v>
       </c>
       <c r="G271">
-        <v>63310</v>
+        <v>63337</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>70529</v>
+        <v>71082</v>
       </c>
       <c r="E272">
         <v>90429</v>
       </c>
       <c r="F272">
-        <v>86860</v>
+        <v>86826</v>
       </c>
       <c r="G272">
-        <v>125078</v>
+        <v>125029</v>
       </c>
       <c r="H272">
-        <v>16331</v>
+        <v>15744</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21177</v>
+        <v>21143</v>
       </c>
       <c r="E273">
         <v>90429</v>
       </c>
       <c r="F273">
-        <v>48177</v>
+        <v>48143</v>
       </c>
       <c r="G273">
-        <v>69375</v>
+        <v>69326</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12444,13 +12444,13 @@
         <v>126608</v>
       </c>
       <c r="F274">
-        <v>48886</v>
+        <v>50818</v>
       </c>
       <c r="G274">
-        <v>70396</v>
+        <v>73178</v>
       </c>
       <c r="H274">
-        <v>27032</v>
+        <v>28964</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10150</v>
+        <v>12082</v>
       </c>
       <c r="E275">
         <v>126608</v>
       </c>
       <c r="F275">
-        <v>37150</v>
+        <v>39082</v>
       </c>
       <c r="G275">
-        <v>53496</v>
+        <v>56278</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>160685</v>
+        <v>160632</v>
       </c>
       <c r="E276">
         <v>162787</v>
       </c>
       <c r="F276">
-        <v>186579</v>
+        <v>186644</v>
       </c>
       <c r="G276">
-        <v>268674</v>
+        <v>268767</v>
       </c>
       <c r="H276">
-        <v>25894</v>
+        <v>26012</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101363</v>
+        <v>101428</v>
       </c>
       <c r="E277">
         <v>162787</v>
       </c>
       <c r="F277">
-        <v>116363</v>
+        <v>116428</v>
       </c>
       <c r="G277">
-        <v>167563</v>
+        <v>167656</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>50345</v>
+        <v>50049</v>
       </c>
       <c r="E278">
         <v>108519</v>
       </c>
       <c r="F278">
-        <v>78163</v>
+        <v>78175</v>
       </c>
       <c r="G278">
-        <v>112555</v>
+        <v>112572</v>
       </c>
       <c r="H278">
-        <v>27818</v>
+        <v>28126</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48969</v>
+        <v>49000</v>
       </c>
       <c r="E279">
         <v>108519</v>
       </c>
       <c r="F279">
-        <v>67910</v>
+        <v>67922</v>
       </c>
       <c r="G279">
-        <v>97790</v>
+        <v>97808</v>
       </c>
       <c r="H279">
-        <v>18941</v>
+        <v>18922</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>67612</v>
+        <v>67123</v>
       </c>
       <c r="E280">
         <v>126608</v>
       </c>
       <c r="F280">
-        <v>90977</v>
+        <v>90989</v>
       </c>
       <c r="G280">
-        <v>131007</v>
+        <v>131024</v>
       </c>
       <c r="H280">
-        <v>23365</v>
+        <v>23866</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48969</v>
+        <v>49000</v>
       </c>
       <c r="E281">
         <v>126608</v>
       </c>
       <c r="F281">
-        <v>74965</v>
+        <v>74977</v>
       </c>
       <c r="G281">
-        <v>107950</v>
+        <v>107967</v>
       </c>
       <c r="H281">
-        <v>25996</v>
+        <v>25977</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24383</v>
+        <v>24555</v>
       </c>
       <c r="E283">
         <v>54250</v>
       </c>
       <c r="F283">
-        <v>39383</v>
+        <v>39555</v>
       </c>
       <c r="G283">
-        <v>56712</v>
+        <v>56959</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>64578</v>
+        <v>64619</v>
       </c>
       <c r="E284">
         <v>81403</v>
       </c>
       <c r="F284">
-        <v>79578</v>
+        <v>79619</v>
       </c>
       <c r="G284">
-        <v>114592</v>
+        <v>114651</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31734</v>
+        <v>31754</v>
       </c>
       <c r="E288">
         <v>57868</v>
       </c>
       <c r="F288">
-        <v>48399</v>
+        <v>48416</v>
       </c>
       <c r="G288">
-        <v>69695</v>
+        <v>69719</v>
       </c>
       <c r="H288">
-        <v>16665</v>
+        <v>16662</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25399</v>
+        <v>25416</v>
       </c>
       <c r="E289">
         <v>57868</v>
       </c>
       <c r="F289">
-        <v>40399</v>
+        <v>40416</v>
       </c>
       <c r="G289">
-        <v>58175</v>
+        <v>58199</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>33939</v>
+        <v>33961</v>
       </c>
       <c r="E291">
         <v>43397</v>
       </c>
       <c r="F291">
-        <v>48939</v>
+        <v>48961</v>
       </c>
       <c r="G291">
-        <v>70472</v>
+        <v>70504</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>42854</v>
+        <v>43006</v>
       </c>
       <c r="E292">
         <v>108519</v>
       </c>
       <c r="F292">
-        <v>72946</v>
+        <v>72956</v>
       </c>
       <c r="G292">
-        <v>105042</v>
+        <v>105057</v>
       </c>
       <c r="H292">
-        <v>30092</v>
+        <v>29950</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37771</v>
+        <v>37795</v>
       </c>
       <c r="E293">
         <v>108519</v>
       </c>
       <c r="F293">
-        <v>63431</v>
+        <v>63440</v>
       </c>
       <c r="G293">
-        <v>91341</v>
+        <v>91354</v>
       </c>
       <c r="H293">
-        <v>25660</v>
+        <v>25645</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54240</v>
+        <v>54165</v>
       </c>
       <c r="E296">
         <v>72340</v>
       </c>
       <c r="F296">
-        <v>89240</v>
+        <v>89165</v>
       </c>
       <c r="G296">
-        <v>128506</v>
+        <v>128398</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64046</v>
+        <v>64087</v>
       </c>
       <c r="E297">
         <v>72340</v>
       </c>
       <c r="F297">
-        <v>79046</v>
+        <v>79087</v>
       </c>
       <c r="G297">
-        <v>113826</v>
+        <v>113885</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4848</v>
+        <v>4805</v>
       </c>
       <c r="E299">
         <v>54250</v>
       </c>
       <c r="F299">
-        <v>29097</v>
+        <v>29080</v>
       </c>
       <c r="G299">
-        <v>41900</v>
+        <v>41875</v>
       </c>
       <c r="H299">
-        <v>24249</v>
+        <v>24275</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10666</v>
+        <v>10705</v>
       </c>
       <c r="E301">
         <v>68722</v>
       </c>
       <c r="F301">
-        <v>37068</v>
+        <v>37083</v>
       </c>
       <c r="G301">
-        <v>53378</v>
+        <v>53400</v>
       </c>
       <c r="H301">
-        <v>26402</v>
+        <v>26378</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>42150</v>
+        <v>41692</v>
       </c>
       <c r="E304">
         <v>108519</v>
       </c>
       <c r="F304">
-        <v>76507</v>
+        <v>76519</v>
       </c>
       <c r="G304">
-        <v>110170</v>
+        <v>110187</v>
       </c>
       <c r="H304">
-        <v>34357</v>
+        <v>34827</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45340</v>
+        <v>45369</v>
       </c>
       <c r="E305">
         <v>108519</v>
       </c>
       <c r="F305">
-        <v>66458</v>
+        <v>66470</v>
       </c>
       <c r="G305">
-        <v>95700</v>
+        <v>95717</v>
       </c>
       <c r="H305">
-        <v>21118</v>
+        <v>21101</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24117</v>
+        <v>24445</v>
       </c>
       <c r="E306">
         <v>108519</v>
       </c>
       <c r="F306">
-        <v>59117</v>
+        <v>59445</v>
       </c>
       <c r="G306">
-        <v>85128</v>
+        <v>85601</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33219</v>
+        <v>33241</v>
       </c>
       <c r="E307">
         <v>108519</v>
       </c>
       <c r="F307">
-        <v>60219</v>
+        <v>60241</v>
       </c>
       <c r="G307">
-        <v>86715</v>
+        <v>86747</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13938,13 +13938,13 @@
         <v>235145</v>
       </c>
       <c r="F308">
-        <v>204476</v>
+        <v>204566</v>
       </c>
       <c r="G308">
-        <v>294445</v>
+        <v>294575</v>
       </c>
       <c r="H308">
-        <v>15572</v>
+        <v>15662</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>141026</v>
+        <v>141116</v>
       </c>
       <c r="E309">
         <v>235145</v>
       </c>
       <c r="F309">
-        <v>156026</v>
+        <v>156116</v>
       </c>
       <c r="G309">
-        <v>224677</v>
+        <v>224807</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>67424</v>
+        <v>67045</v>
       </c>
       <c r="E310">
         <v>126608</v>
       </c>
       <c r="F310">
-        <v>90194</v>
+        <v>90207</v>
       </c>
       <c r="G310">
-        <v>129879</v>
+        <v>129898</v>
       </c>
       <c r="H310">
-        <v>22770</v>
+        <v>23162</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53567</v>
+        <v>53601</v>
       </c>
       <c r="E311">
         <v>126608</v>
       </c>
       <c r="F311">
-        <v>76804</v>
+        <v>76817</v>
       </c>
       <c r="G311">
-        <v>110598</v>
+        <v>110616</v>
       </c>
       <c r="H311">
-        <v>23237</v>
+        <v>23216</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110074</v>
+        <v>110145</v>
       </c>
       <c r="E313">
         <v>180877</v>
       </c>
       <c r="F313">
-        <v>125074</v>
+        <v>125145</v>
       </c>
       <c r="G313">
-        <v>180107</v>
+        <v>180209</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>123728</v>
+        <v>123807</v>
       </c>
       <c r="E314">
         <v>235145</v>
       </c>
       <c r="F314">
-        <v>158728</v>
+        <v>158807</v>
       </c>
       <c r="G314">
-        <v>228568</v>
+        <v>228682</v>
       </c>
       <c r="H314">
         <v>35000</v>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>147094</v>
+        <v>147188</v>
       </c>
       <c r="E315">
         <v>235145</v>
       </c>
       <c r="F315">
-        <v>162094</v>
+        <v>162188</v>
       </c>
       <c r="G315">
-        <v>233415</v>
+        <v>233551</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4272</v>
+        <v>4241</v>
       </c>
       <c r="E7">
         <v>54250</v>
       </c>
       <c r="F7">
-        <v>28867</v>
+        <v>28854</v>
       </c>
       <c r="G7">
-        <v>41568</v>
+        <v>41550</v>
       </c>
       <c r="H7">
-        <v>24595</v>
+        <v>24613</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35839</v>
+        <v>35745</v>
       </c>
       <c r="E8">
         <v>72340</v>
       </c>
       <c r="F8">
-        <v>54031</v>
+        <v>52851</v>
       </c>
       <c r="G8">
-        <v>77805</v>
+        <v>76105</v>
       </c>
       <c r="H8">
-        <v>18192</v>
+        <v>17106</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>29547</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>72340</v>
       </c>
       <c r="F9">
-        <v>46031</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>66285</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>16484</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41019</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>108519</v>
       </c>
       <c r="F11">
-        <v>64730</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>93211</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>23711</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>34955</v>
+        <v>26464</v>
       </c>
       <c r="E12">
         <v>81385</v>
       </c>
       <c r="F12">
-        <v>61039</v>
+        <v>61007</v>
       </c>
       <c r="G12">
-        <v>87896</v>
+        <v>87850</v>
       </c>
       <c r="H12">
-        <v>26084</v>
+        <v>34543</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11738</v>
+        <v>11706</v>
       </c>
       <c r="E13">
         <v>81385</v>
       </c>
       <c r="F13">
-        <v>38738</v>
+        <v>38706</v>
       </c>
       <c r="G13">
-        <v>55783</v>
+        <v>55737</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>32912</v>
+        <v>34493</v>
       </c>
       <c r="E21">
         <v>101283</v>
       </c>
       <c r="F21">
-        <v>58665</v>
+        <v>59298</v>
       </c>
       <c r="G21">
-        <v>84478</v>
+        <v>85389</v>
       </c>
       <c r="H21">
-        <v>25753</v>
+        <v>24805</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>52631</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>130226</v>
       </c>
       <c r="F23">
-        <v>77841</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>112091</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>25210</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20110</v>
+        <v>21049</v>
       </c>
       <c r="E27">
         <v>63295</v>
       </c>
       <c r="F27">
-        <v>38729</v>
+        <v>39105</v>
       </c>
       <c r="G27">
-        <v>55770</v>
+        <v>56311</v>
       </c>
       <c r="H27">
-        <v>18619</v>
+        <v>18056</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74791</v>
+        <v>74494</v>
       </c>
       <c r="E28">
         <v>126608</v>
       </c>
       <c r="F28">
-        <v>93352</v>
+        <v>94956</v>
       </c>
       <c r="G28">
-        <v>134427</v>
+        <v>136737</v>
       </c>
       <c r="H28">
-        <v>18561</v>
+        <v>20462</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>25197</v>
+        <v>29140</v>
       </c>
       <c r="E29">
         <v>126608</v>
       </c>
       <c r="F29">
-        <v>52197</v>
+        <v>56140</v>
       </c>
       <c r="G29">
-        <v>75164</v>
+        <v>80842</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,16 +1709,16 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130568</v>
+        <v>130224</v>
       </c>
       <c r="E30">
         <v>180877</v>
       </c>
       <c r="F30">
-        <v>165568</v>
+        <v>165224</v>
       </c>
       <c r="G30">
-        <v>238418</v>
+        <v>237923</v>
       </c>
       <c r="H30">
         <v>35000</v>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>77859</v>
+        <v>77640</v>
       </c>
       <c r="E31">
         <v>180877</v>
       </c>
       <c r="F31">
-        <v>104859</v>
+        <v>104640</v>
       </c>
       <c r="G31">
-        <v>150997</v>
+        <v>150682</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1805,13 +1805,13 @@
         <v>108519</v>
       </c>
       <c r="F32">
-        <v>89297</v>
+        <v>89065</v>
       </c>
       <c r="G32">
-        <v>128588</v>
+        <v>128254</v>
       </c>
       <c r="H32">
-        <v>17166</v>
+        <v>16934</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>48969</v>
+        <v>48390</v>
       </c>
       <c r="E33">
         <v>108519</v>
       </c>
       <c r="F33">
-        <v>67910</v>
+        <v>67678</v>
       </c>
       <c r="G33">
-        <v>97790</v>
+        <v>97456</v>
       </c>
       <c r="H33">
-        <v>18941</v>
+        <v>19288</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80206</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>126608</v>
       </c>
       <c r="F35">
-        <v>95206</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>137097</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35479</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>126608</v>
       </c>
       <c r="F37">
-        <v>62479</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>89970</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>81396</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>235145</v>
       </c>
       <c r="F39">
-        <v>108396</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>156090</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>81396</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>235145</v>
       </c>
       <c r="F41">
-        <v>108396</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>156090</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>39141</v>
+        <v>38671</v>
       </c>
       <c r="E43">
         <v>126608</v>
       </c>
       <c r="F43">
-        <v>66141</v>
+        <v>65671</v>
       </c>
       <c r="G43">
-        <v>95243</v>
+        <v>94566</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>92538</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>180877</v>
       </c>
       <c r="F45">
-        <v>113557</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>163522</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>21019</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25650</v>
+        <v>27450</v>
       </c>
       <c r="E47">
         <v>108519</v>
       </c>
       <c r="F47">
-        <v>52650</v>
+        <v>54450</v>
       </c>
       <c r="G47">
-        <v>75816</v>
+        <v>78408</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2593,13 +2593,13 @@
         <v>63295</v>
       </c>
       <c r="F50">
-        <v>56272</v>
+        <v>58635</v>
       </c>
       <c r="G50">
-        <v>81032</v>
+        <v>84434</v>
       </c>
       <c r="H50">
-        <v>20293</v>
+        <v>22656</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33272</v>
+        <v>35635</v>
       </c>
       <c r="E51">
         <v>63295</v>
       </c>
       <c r="F51">
-        <v>48272</v>
+        <v>50635</v>
       </c>
       <c r="G51">
-        <v>69512</v>
+        <v>72914</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52177</v>
+        <v>52036</v>
       </c>
       <c r="E55">
         <v>126608</v>
       </c>
       <c r="F55">
-        <v>76248</v>
+        <v>76191</v>
       </c>
       <c r="G55">
-        <v>109797</v>
+        <v>109715</v>
       </c>
       <c r="H55">
-        <v>24071</v>
+        <v>24155</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62741</v>
+        <v>62584</v>
       </c>
       <c r="E57">
         <v>144698</v>
       </c>
       <c r="F57">
-        <v>87529</v>
+        <v>87466</v>
       </c>
       <c r="G57">
-        <v>126042</v>
+        <v>125951</v>
       </c>
       <c r="H57">
-        <v>24788</v>
+        <v>24882</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23553</v>
+        <v>23491</v>
       </c>
       <c r="E58">
         <v>36161</v>
       </c>
       <c r="F58">
-        <v>39545</v>
+        <v>39538</v>
       </c>
       <c r="G58">
-        <v>56945</v>
+        <v>56935</v>
       </c>
       <c r="H58">
-        <v>15992</v>
+        <v>16047</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6229</v>
+        <v>6213</v>
       </c>
       <c r="E59">
         <v>36161</v>
       </c>
       <c r="F59">
-        <v>22595</v>
+        <v>22588</v>
       </c>
       <c r="G59">
-        <v>32537</v>
+        <v>32527</v>
       </c>
       <c r="H59">
-        <v>16366</v>
+        <v>16375</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26229</v>
+        <v>26151</v>
       </c>
       <c r="E60">
         <v>48824</v>
       </c>
       <c r="F60">
-        <v>47852</v>
+        <v>47977</v>
       </c>
       <c r="G60">
-        <v>68907</v>
+        <v>69087</v>
       </c>
       <c r="H60">
-        <v>21623</v>
+        <v>21826</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24852</v>
+        <v>24977</v>
       </c>
       <c r="E61">
         <v>48824</v>
       </c>
       <c r="F61">
-        <v>39852</v>
+        <v>39977</v>
       </c>
       <c r="G61">
-        <v>57387</v>
+        <v>57567</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12864</v>
+        <v>12833</v>
       </c>
       <c r="E63">
         <v>81385</v>
       </c>
       <c r="F63">
-        <v>39864</v>
+        <v>39833</v>
       </c>
       <c r="G63">
-        <v>57404</v>
+        <v>57360</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28248</v>
+        <v>28013</v>
       </c>
       <c r="E65">
         <v>122068</v>
       </c>
       <c r="F65">
-        <v>55248</v>
+        <v>55013</v>
       </c>
       <c r="G65">
-        <v>79557</v>
+        <v>79219</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24289</v>
+        <v>24226</v>
       </c>
       <c r="E66">
         <v>90429</v>
       </c>
       <c r="F66">
-        <v>53545</v>
+        <v>53498</v>
       </c>
       <c r="G66">
-        <v>77105</v>
+        <v>77037</v>
       </c>
       <c r="H66">
-        <v>29256</v>
+        <v>29272</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18545</v>
+        <v>18498</v>
       </c>
       <c r="E67">
         <v>90429</v>
       </c>
       <c r="F67">
-        <v>45545</v>
+        <v>45498</v>
       </c>
       <c r="G67">
-        <v>65585</v>
+        <v>65517</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34446</v>
+        <v>34414</v>
       </c>
       <c r="E68">
         <v>108519</v>
       </c>
       <c r="F68">
-        <v>62622</v>
+        <v>62763</v>
       </c>
       <c r="G68">
-        <v>90176</v>
+        <v>90379</v>
       </c>
       <c r="H68">
-        <v>28176</v>
+        <v>28349</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27434</v>
+        <v>27575</v>
       </c>
       <c r="E69">
         <v>108519</v>
       </c>
       <c r="F69">
-        <v>54434</v>
+        <v>54575</v>
       </c>
       <c r="G69">
-        <v>78385</v>
+        <v>78588</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45275</v>
+        <v>45150</v>
       </c>
       <c r="E70">
         <v>126608</v>
       </c>
       <c r="F70">
-        <v>80275</v>
+        <v>80150</v>
       </c>
       <c r="G70">
-        <v>115596</v>
+        <v>115416</v>
       </c>
       <c r="H70">
         <v>35000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50534</v>
+        <v>50800</v>
       </c>
       <c r="E71">
         <v>126608</v>
       </c>
       <c r="F71">
-        <v>75591</v>
+        <v>75697</v>
       </c>
       <c r="G71">
-        <v>108851</v>
+        <v>109004</v>
       </c>
       <c r="H71">
-        <v>25057</v>
+        <v>24897</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5697</v>
+        <v>5822</v>
       </c>
       <c r="E73">
         <v>27116</v>
       </c>
       <c r="F73">
-        <v>20697</v>
+        <v>20822</v>
       </c>
       <c r="G73">
-        <v>29804</v>
+        <v>29984</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3691,16 +3691,16 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70143</v>
+        <v>70519</v>
       </c>
       <c r="E75">
         <v>94952</v>
       </c>
       <c r="F75">
-        <v>85143</v>
+        <v>85519</v>
       </c>
       <c r="G75">
-        <v>122606</v>
+        <v>123147</v>
       </c>
       <c r="H75">
         <v>15000</v>
@@ -3734,16 +3734,16 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80175</v>
+        <v>85527</v>
       </c>
       <c r="E76">
         <v>126608</v>
       </c>
       <c r="F76">
-        <v>95175</v>
+        <v>100527</v>
       </c>
       <c r="G76">
-        <v>137052</v>
+        <v>144759</v>
       </c>
       <c r="H76">
         <v>15000</v>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>46981</v>
+        <v>46856</v>
       </c>
       <c r="E77">
         <v>126608</v>
       </c>
       <c r="F77">
-        <v>73981</v>
+        <v>73856</v>
       </c>
       <c r="G77">
-        <v>106533</v>
+        <v>106353</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37028</v>
+        <v>36918</v>
       </c>
       <c r="E81">
         <v>90429</v>
       </c>
       <c r="F81">
-        <v>56079</v>
+        <v>56035</v>
       </c>
       <c r="G81">
-        <v>80754</v>
+        <v>80690</v>
       </c>
       <c r="H81">
-        <v>19051</v>
+        <v>19117</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48280</v>
+        <v>75187</v>
       </c>
       <c r="E84">
         <v>101283</v>
       </c>
       <c r="F84">
-        <v>70918</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>102122</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>22638</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31942</v>
+        <v>31863</v>
       </c>
       <c r="E85">
         <v>101283</v>
       </c>
       <c r="F85">
-        <v>58277</v>
+        <v>58246</v>
       </c>
       <c r="G85">
-        <v>83919</v>
+        <v>83874</v>
       </c>
       <c r="H85">
-        <v>26335</v>
+        <v>26383</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4177,13 +4177,13 @@
         <v>144698</v>
       </c>
       <c r="F86">
-        <v>165150</v>
+        <v>164887</v>
       </c>
       <c r="G86">
-        <v>237816</v>
+        <v>237437</v>
       </c>
       <c r="H86">
-        <v>15263</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,19 +4215,19 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>113181</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>144698</v>
       </c>
       <c r="F87">
-        <v>128181</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>184581</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I87" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>158801</v>
+        <v>159223</v>
       </c>
       <c r="E88">
         <v>159170</v>
       </c>
       <c r="F88">
-        <v>173879</v>
+        <v>174223</v>
       </c>
       <c r="G88">
-        <v>250386</v>
+        <v>250881</v>
       </c>
       <c r="H88">
-        <v>15078</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4352,13 +4352,13 @@
         <v>57868</v>
       </c>
       <c r="F90">
-        <v>38277</v>
+        <v>38271</v>
       </c>
       <c r="G90">
-        <v>55119</v>
+        <v>55110</v>
       </c>
       <c r="H90">
-        <v>30597</v>
+        <v>30591</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4272</v>
+        <v>4257</v>
       </c>
       <c r="E91">
         <v>57868</v>
       </c>
       <c r="F91">
-        <v>30277</v>
+        <v>30271</v>
       </c>
       <c r="G91">
-        <v>43599</v>
+        <v>43590</v>
       </c>
       <c r="H91">
-        <v>26005</v>
+        <v>26014</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4614,13 +4614,13 @@
         <v>81385</v>
       </c>
       <c r="F96">
-        <v>76403</v>
+        <v>76372</v>
       </c>
       <c r="G96">
-        <v>110020</v>
+        <v>109976</v>
       </c>
       <c r="H96">
-        <v>15228</v>
+        <v>15197</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33538</v>
+        <v>33460</v>
       </c>
       <c r="E97">
         <v>81385</v>
       </c>
       <c r="F97">
-        <v>51155</v>
+        <v>51124</v>
       </c>
       <c r="G97">
-        <v>73663</v>
+        <v>73619</v>
       </c>
       <c r="H97">
-        <v>17617</v>
+        <v>17664</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4704,13 +4704,13 @@
         <v>94047</v>
       </c>
       <c r="F98">
-        <v>89343</v>
+        <v>89312</v>
       </c>
       <c r="G98">
-        <v>128654</v>
+        <v>128609</v>
       </c>
       <c r="H98">
-        <v>15150</v>
+        <v>15119</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33538</v>
+        <v>33460</v>
       </c>
       <c r="E99">
         <v>94047</v>
       </c>
       <c r="F99">
-        <v>56094</v>
+        <v>56063</v>
       </c>
       <c r="G99">
-        <v>80775</v>
+        <v>80731</v>
       </c>
       <c r="H99">
-        <v>22556</v>
+        <v>22603</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,7 +4788,7 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61395</v>
+        <v>61238</v>
       </c>
       <c r="E100">
         <v>105444</v>
@@ -4800,7 +4800,7 @@
         <v>113880</v>
       </c>
       <c r="H100">
-        <v>17688</v>
+        <v>17845</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,16 +4834,16 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61098</v>
+        <v>61426</v>
       </c>
       <c r="E101">
         <v>105444</v>
       </c>
       <c r="F101">
-        <v>76098</v>
+        <v>76426</v>
       </c>
       <c r="G101">
-        <v>109581</v>
+        <v>110053</v>
       </c>
       <c r="H101">
         <v>15000</v>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>72053</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>126608</v>
       </c>
       <c r="F105">
-        <v>87053</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>125356</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>100129</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>180877</v>
       </c>
       <c r="F107">
-        <v>116594</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>167895</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>16465</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13381</v>
+        <v>13349</v>
       </c>
       <c r="E111">
         <v>162787</v>
       </c>
       <c r="F111">
-        <v>40381</v>
+        <v>40349</v>
       </c>
       <c r="G111">
-        <v>58149</v>
+        <v>58103</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>84729</v>
+        <v>85183</v>
       </c>
       <c r="E115">
         <v>115755</v>
       </c>
       <c r="F115">
-        <v>99729</v>
+        <v>100183</v>
       </c>
       <c r="G115">
-        <v>143610</v>
+        <v>144264</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5526,16 +5526,16 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>110317</v>
+        <v>116702</v>
       </c>
       <c r="E117">
         <v>144698</v>
       </c>
       <c r="F117">
-        <v>125317</v>
+        <v>131702</v>
       </c>
       <c r="G117">
-        <v>180456</v>
+        <v>189651</v>
       </c>
       <c r="H117">
         <v>15000</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60925</v>
+        <v>60847</v>
       </c>
       <c r="E120">
         <v>79576</v>
       </c>
       <c r="F120">
-        <v>78837</v>
+        <v>79180</v>
       </c>
       <c r="G120">
-        <v>113525</v>
+        <v>114019</v>
       </c>
       <c r="H120">
-        <v>17912</v>
+        <v>18333</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53554</v>
+        <v>53852</v>
       </c>
       <c r="E121">
         <v>79576</v>
       </c>
       <c r="F121">
-        <v>68554</v>
+        <v>68852</v>
       </c>
       <c r="G121">
-        <v>98718</v>
+        <v>99147</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>46512</v>
       </c>
       <c r="E122">
         <v>90429</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>65298</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>94029</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>18786</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>33945</v>
+        <v>33616</v>
       </c>
       <c r="E123">
         <v>90429</v>
       </c>
       <c r="F123">
-        <v>54845</v>
+        <v>54714</v>
       </c>
       <c r="G123">
-        <v>78977</v>
+        <v>78788</v>
       </c>
       <c r="H123">
-        <v>20900</v>
+        <v>21098</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7309</v>
+        <v>9406</v>
       </c>
       <c r="E125">
         <v>43397</v>
       </c>
       <c r="F125">
-        <v>25848</v>
+        <v>26687</v>
       </c>
       <c r="G125">
-        <v>37221</v>
+        <v>38429</v>
       </c>
       <c r="H125">
-        <v>18539</v>
+        <v>17281</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20173</v>
+        <v>20126</v>
       </c>
       <c r="E129">
         <v>59297</v>
       </c>
       <c r="F129">
-        <v>37195</v>
+        <v>37176</v>
       </c>
       <c r="G129">
-        <v>53561</v>
+        <v>53533</v>
       </c>
       <c r="H129">
-        <v>17022</v>
+        <v>17050</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20173</v>
+        <v>20126</v>
       </c>
       <c r="E131">
         <v>73878</v>
       </c>
       <c r="F131">
-        <v>42882</v>
+        <v>42863</v>
       </c>
       <c r="G131">
-        <v>61750</v>
+        <v>61723</v>
       </c>
       <c r="H131">
-        <v>22709</v>
+        <v>22737</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33084</v>
+        <v>37544</v>
       </c>
       <c r="E133">
         <v>92998</v>
       </c>
       <c r="F133">
-        <v>55503</v>
+        <v>57287</v>
       </c>
       <c r="G133">
-        <v>79924</v>
+        <v>82493</v>
       </c>
       <c r="H133">
-        <v>22419</v>
+        <v>19743</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37388</v>
+        <v>37247</v>
       </c>
       <c r="E140">
         <v>90429</v>
       </c>
       <c r="F140">
-        <v>61648</v>
+        <v>61592</v>
       </c>
       <c r="G140">
-        <v>88773</v>
+        <v>88692</v>
       </c>
       <c r="H140">
-        <v>24260</v>
+        <v>24345</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26762</v>
+        <v>26699</v>
       </c>
       <c r="E142">
         <v>90429</v>
       </c>
       <c r="F142">
-        <v>60216</v>
+        <v>60185</v>
       </c>
       <c r="G142">
-        <v>86711</v>
+        <v>86666</v>
       </c>
       <c r="H142">
-        <v>33454</v>
+        <v>33486</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27372</v>
+        <v>27294</v>
       </c>
       <c r="E143">
         <v>90429</v>
       </c>
       <c r="F143">
-        <v>52216</v>
+        <v>52185</v>
       </c>
       <c r="G143">
-        <v>75191</v>
+        <v>75146</v>
       </c>
       <c r="H143">
-        <v>24844</v>
+        <v>24891</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>46089</v>
+        <v>45667</v>
       </c>
       <c r="E144">
         <v>90429</v>
       </c>
       <c r="F144">
-        <v>67822</v>
+        <v>64960</v>
       </c>
       <c r="G144">
-        <v>97664</v>
+        <v>93542</v>
       </c>
       <c r="H144">
-        <v>21733</v>
+        <v>19293</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>80018</v>
+        <v>0</v>
       </c>
       <c r="E145">
         <v>90429</v>
       </c>
       <c r="F145">
-        <v>95018</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>136826</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58046</v>
+        <v>58359</v>
       </c>
       <c r="E146">
         <v>90429</v>
       </c>
       <c r="F146">
-        <v>73046</v>
+        <v>73359</v>
       </c>
       <c r="G146">
-        <v>105186</v>
+        <v>105637</v>
       </c>
       <c r="H146">
         <v>15000</v>
@@ -6883,7 +6883,7 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36746</v>
+        <v>36699</v>
       </c>
       <c r="E148">
         <v>61486</v>
@@ -6895,7 +6895,7 @@
         <v>92032</v>
       </c>
       <c r="H148">
-        <v>27165</v>
+        <v>27212</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15634</v>
+        <v>15337</v>
       </c>
       <c r="E151">
         <v>54250</v>
       </c>
       <c r="F151">
-        <v>33411</v>
+        <v>33293</v>
       </c>
       <c r="G151">
-        <v>48112</v>
+        <v>47942</v>
       </c>
       <c r="H151">
-        <v>17777</v>
+        <v>17956</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37450</v>
+        <v>37357</v>
       </c>
       <c r="E152">
         <v>72340</v>
@@ -7070,7 +7070,7 @@
         <v>78127</v>
       </c>
       <c r="H152">
-        <v>16805</v>
+        <v>16898</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,16 +7104,16 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33241</v>
+        <v>33413</v>
       </c>
       <c r="E153">
         <v>72340</v>
       </c>
       <c r="F153">
-        <v>48241</v>
+        <v>48413</v>
       </c>
       <c r="G153">
-        <v>69467</v>
+        <v>69715</v>
       </c>
       <c r="H153">
         <v>15000</v>
@@ -7148,16 +7148,16 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56622</v>
+        <v>56559</v>
       </c>
       <c r="E154">
         <v>72340</v>
       </c>
       <c r="F154">
-        <v>91622</v>
+        <v>91559</v>
       </c>
       <c r="G154">
-        <v>131936</v>
+        <v>131845</v>
       </c>
       <c r="H154">
         <v>35000</v>
@@ -7194,16 +7194,16 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>72600</v>
+        <v>72992</v>
       </c>
       <c r="E155">
         <v>72340</v>
       </c>
       <c r="F155">
-        <v>87600</v>
+        <v>87992</v>
       </c>
       <c r="G155">
-        <v>126144</v>
+        <v>126708</v>
       </c>
       <c r="H155">
         <v>15000</v>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>34461</v>
+        <v>34117</v>
       </c>
       <c r="E156">
         <v>59677</v>
       </c>
       <c r="F156">
-        <v>49693</v>
+        <v>49662</v>
       </c>
       <c r="G156">
-        <v>71558</v>
+        <v>71513</v>
       </c>
       <c r="H156">
-        <v>15232</v>
+        <v>15545</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11878</v>
+        <v>11800</v>
       </c>
       <c r="E157">
         <v>59677</v>
       </c>
       <c r="F157">
-        <v>34025</v>
+        <v>33994</v>
       </c>
       <c r="G157">
-        <v>48996</v>
+        <v>48951</v>
       </c>
       <c r="H157">
-        <v>22147</v>
+        <v>22194</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54269</v>
       </c>
       <c r="F160">
-        <v>38602</v>
+        <v>38558</v>
       </c>
       <c r="G160">
-        <v>55587</v>
+        <v>55524</v>
       </c>
       <c r="H160">
-        <v>30922</v>
+        <v>30878</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8592</v>
+        <v>8482</v>
       </c>
       <c r="E161">
         <v>54269</v>
       </c>
       <c r="F161">
-        <v>30602</v>
+        <v>30558</v>
       </c>
       <c r="G161">
-        <v>44067</v>
+        <v>44004</v>
       </c>
       <c r="H161">
-        <v>22010</v>
+        <v>22076</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7507,13 +7507,13 @@
         <v>72340</v>
       </c>
       <c r="F162">
-        <v>44046</v>
+        <v>44014</v>
       </c>
       <c r="G162">
-        <v>63426</v>
+        <v>63380</v>
       </c>
       <c r="H162">
-        <v>33899</v>
+        <v>33867</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9046</v>
+        <v>9014</v>
       </c>
       <c r="E163">
         <v>72340</v>
       </c>
       <c r="F163">
-        <v>36046</v>
+        <v>36014</v>
       </c>
       <c r="G163">
-        <v>51906</v>
+        <v>51860</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7597,13 +7597,13 @@
         <v>67836</v>
       </c>
       <c r="F164">
-        <v>82071</v>
+        <v>82046</v>
       </c>
       <c r="G164">
-        <v>118182</v>
+        <v>118146</v>
       </c>
       <c r="H164">
-        <v>15205</v>
+        <v>15180</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20815</v>
+        <v>20752</v>
       </c>
       <c r="E165">
         <v>67836</v>
       </c>
       <c r="F165">
-        <v>40782</v>
+        <v>40757</v>
       </c>
       <c r="G165">
-        <v>58726</v>
+        <v>58690</v>
       </c>
       <c r="H165">
-        <v>19967</v>
+        <v>20005</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7685,13 +7685,13 @@
         <v>102206</v>
       </c>
       <c r="F166">
-        <v>105424</v>
+        <v>105361</v>
       </c>
       <c r="G166">
-        <v>151811</v>
+        <v>151720</v>
       </c>
       <c r="H166">
-        <v>15411</v>
+        <v>15348</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21910</v>
+        <v>21847</v>
       </c>
       <c r="E167">
         <v>102206</v>
       </c>
       <c r="F167">
-        <v>48910</v>
+        <v>48847</v>
       </c>
       <c r="G167">
-        <v>70430</v>
+        <v>70340</v>
       </c>
       <c r="H167">
         <v>27000</v>
@@ -7772,13 +7772,13 @@
         <v>72340</v>
       </c>
       <c r="F168">
-        <v>103839</v>
+        <v>103902</v>
       </c>
       <c r="G168">
-        <v>149528</v>
+        <v>149619</v>
       </c>
       <c r="H168">
-        <v>15018</v>
+        <v>15081</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8811</v>
+        <v>8874</v>
       </c>
       <c r="E169">
         <v>72340</v>
       </c>
       <c r="F169">
-        <v>35811</v>
+        <v>35874</v>
       </c>
       <c r="G169">
-        <v>51568</v>
+        <v>51659</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7861,13 +7861,13 @@
         <v>108519</v>
       </c>
       <c r="F170">
-        <v>80081</v>
+        <v>78553</v>
       </c>
       <c r="G170">
-        <v>115317</v>
+        <v>113116</v>
       </c>
       <c r="H170">
-        <v>20783</v>
+        <v>19255</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>53147</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>108519</v>
       </c>
       <c r="F171">
-        <v>69581</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>100197</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>16434</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7950,13 +7950,13 @@
         <v>144698</v>
       </c>
       <c r="F172">
-        <v>107771</v>
+        <v>107965</v>
       </c>
       <c r="G172">
-        <v>155190</v>
+        <v>155470</v>
       </c>
       <c r="H172">
-        <v>29380</v>
+        <v>29574</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78203</v>
+        <v>78626</v>
       </c>
       <c r="E173">
         <v>144698</v>
       </c>
       <c r="F173">
-        <v>93714</v>
+        <v>93883</v>
       </c>
       <c r="G173">
-        <v>134948</v>
+        <v>135192</v>
       </c>
       <c r="H173">
-        <v>15511</v>
+        <v>15257</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>46762</v>
+        <v>48046</v>
       </c>
       <c r="E174">
         <v>90429</v>
@@ -8045,7 +8045,7 @@
         <v>97664</v>
       </c>
       <c r="H174">
-        <v>21060</v>
+        <v>19776</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26902</v>
+        <v>26542</v>
       </c>
       <c r="E178">
         <v>108519</v>
       </c>
       <c r="F178">
-        <v>53902</v>
+        <v>53542</v>
       </c>
       <c r="G178">
-        <v>77619</v>
+        <v>77100</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>23553</v>
+        <v>26104</v>
       </c>
       <c r="E180">
         <v>90429</v>
       </c>
       <c r="F180">
-        <v>50553</v>
+        <v>53104</v>
       </c>
       <c r="G180">
-        <v>72796</v>
+        <v>76470</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8393,13 +8393,13 @@
         <v>126608</v>
       </c>
       <c r="F182">
-        <v>115031</v>
+        <v>114962</v>
       </c>
       <c r="G182">
-        <v>165645</v>
+        <v>165545</v>
       </c>
       <c r="H182">
-        <v>15271</v>
+        <v>15202</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64322</v>
+        <v>64149</v>
       </c>
       <c r="E183">
         <v>126608</v>
       </c>
       <c r="F183">
-        <v>81106</v>
+        <v>81037</v>
       </c>
       <c r="G183">
-        <v>116793</v>
+        <v>116693</v>
       </c>
       <c r="H183">
-        <v>16784</v>
+        <v>16888</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8480,13 +8480,13 @@
         <v>180877</v>
       </c>
       <c r="F184">
-        <v>159431</v>
+        <v>159258</v>
       </c>
       <c r="G184">
-        <v>229581</v>
+        <v>229332</v>
       </c>
       <c r="H184">
-        <v>15467</v>
+        <v>15294</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64322</v>
+        <v>64149</v>
       </c>
       <c r="E185">
         <v>180877</v>
       </c>
       <c r="F185">
-        <v>91322</v>
+        <v>91149</v>
       </c>
       <c r="G185">
-        <v>131504</v>
+        <v>131255</v>
       </c>
       <c r="H185">
         <v>27000</v>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64322</v>
+        <v>64149</v>
       </c>
       <c r="E187">
         <v>180877</v>
       </c>
       <c r="F187">
-        <v>91322</v>
+        <v>91149</v>
       </c>
       <c r="G187">
-        <v>131504</v>
+        <v>131255</v>
       </c>
       <c r="H187">
         <v>27000</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>304815</v>
+        <v>306458</v>
       </c>
       <c r="E189">
         <v>361772</v>
       </c>
       <c r="F189">
-        <v>319815</v>
+        <v>321458</v>
       </c>
       <c r="G189">
-        <v>460534</v>
+        <v>462900</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29751</v>
+        <v>29610</v>
       </c>
       <c r="E190">
         <v>94952</v>
       </c>
       <c r="F190">
-        <v>64751</v>
+        <v>64610</v>
       </c>
       <c r="G190">
-        <v>93241</v>
+        <v>93038</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44227</v>
+        <v>44462</v>
       </c>
       <c r="E191">
         <v>94952</v>
       </c>
       <c r="F191">
-        <v>60722</v>
+        <v>60816</v>
       </c>
       <c r="G191">
-        <v>87440</v>
+        <v>87575</v>
       </c>
       <c r="H191">
-        <v>16495</v>
+        <v>16354</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>43476</v>
+        <v>43397</v>
       </c>
       <c r="E192">
         <v>122086</v>
       </c>
       <c r="F192">
-        <v>78476</v>
+        <v>70397</v>
       </c>
       <c r="G192">
-        <v>113005</v>
+        <v>101372</v>
       </c>
       <c r="H192">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>49673</v>
+        <v>53601</v>
       </c>
       <c r="E194">
         <v>149401</v>
       </c>
       <c r="F194">
-        <v>76673</v>
+        <v>80601</v>
       </c>
       <c r="G194">
-        <v>110409</v>
+        <v>116065</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -9044,16 +9044,16 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32239</v>
+        <v>32411</v>
       </c>
       <c r="E197">
         <v>72340</v>
       </c>
       <c r="F197">
-        <v>47239</v>
+        <v>47411</v>
       </c>
       <c r="G197">
-        <v>68024</v>
+        <v>68272</v>
       </c>
       <c r="H197">
         <v>15000</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26417</v>
+        <v>26433</v>
       </c>
       <c r="E198">
         <v>108519</v>
       </c>
       <c r="F198">
-        <v>53417</v>
+        <v>53433</v>
       </c>
       <c r="G198">
-        <v>76920</v>
+        <v>76944</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9182,13 +9182,13 @@
         <v>126608</v>
       </c>
       <c r="F200">
-        <v>46910</v>
+        <v>46878</v>
       </c>
       <c r="G200">
-        <v>67550</v>
+        <v>67504</v>
       </c>
       <c r="H200">
-        <v>32845</v>
+        <v>32813</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11910</v>
+        <v>11878</v>
       </c>
       <c r="E201">
         <v>126608</v>
       </c>
       <c r="F201">
-        <v>38910</v>
+        <v>38878</v>
       </c>
       <c r="G201">
-        <v>56030</v>
+        <v>55984</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22520</v>
+        <v>22646</v>
       </c>
       <c r="E203">
         <v>144698</v>
       </c>
       <c r="F203">
-        <v>49520</v>
+        <v>49646</v>
       </c>
       <c r="G203">
-        <v>71309</v>
+        <v>71490</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9362,13 +9362,13 @@
         <v>180877</v>
       </c>
       <c r="F204">
-        <v>61057</v>
+        <v>55738</v>
       </c>
       <c r="G204">
-        <v>87922</v>
+        <v>80263</v>
       </c>
       <c r="H204">
-        <v>32319</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26057</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>180877</v>
       </c>
       <c r="F205">
-        <v>53057</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>76402</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24258</v>
+        <v>24179</v>
       </c>
       <c r="E206">
         <v>57868</v>
       </c>
       <c r="F206">
-        <v>42047</v>
+        <v>42122</v>
       </c>
       <c r="G206">
-        <v>60548</v>
+        <v>60656</v>
       </c>
       <c r="H206">
-        <v>17789</v>
+        <v>17943</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12990</v>
+        <v>13177</v>
       </c>
       <c r="E207">
         <v>57868</v>
       </c>
       <c r="F207">
-        <v>33764</v>
+        <v>33839</v>
       </c>
       <c r="G207">
-        <v>48620</v>
+        <v>48728</v>
       </c>
       <c r="H207">
-        <v>20774</v>
+        <v>20662</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,19 +9578,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>22833</v>
+        <v>0</v>
       </c>
       <c r="E209">
         <v>54250</v>
       </c>
       <c r="F209">
-        <v>37833</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>54480</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40095</v>
+        <v>40299</v>
       </c>
       <c r="E211">
         <v>108519</v>
       </c>
       <c r="F211">
-        <v>64360</v>
+        <v>64442</v>
       </c>
       <c r="G211">
-        <v>92678</v>
+        <v>92796</v>
       </c>
       <c r="H211">
-        <v>24265</v>
+        <v>24143</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>82992</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>180877</v>
       </c>
       <c r="F213">
-        <v>109739</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>158024</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>26747</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28154</v>
+        <v>28953</v>
       </c>
       <c r="E214">
         <v>86812</v>
       </c>
       <c r="F214">
-        <v>60270</v>
+        <v>55953</v>
       </c>
       <c r="G214">
-        <v>86789</v>
+        <v>80572</v>
       </c>
       <c r="H214">
-        <v>32116</v>
+        <v>27000</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31034</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>86812</v>
       </c>
       <c r="F215">
-        <v>52270</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>75269</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>21236</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45667</v>
+        <v>45542</v>
       </c>
       <c r="E216">
         <v>101283</v>
       </c>
       <c r="F216">
-        <v>75962</v>
+        <v>69794</v>
       </c>
       <c r="G216">
-        <v>109385</v>
+        <v>100503</v>
       </c>
       <c r="H216">
-        <v>30295</v>
+        <v>24252</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>88532</v>
+        <v>0</v>
       </c>
       <c r="E217">
         <v>101283</v>
       </c>
       <c r="F217">
-        <v>103532</v>
+        <v>0</v>
       </c>
       <c r="G217">
-        <v>149086</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>110333</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>130226</v>
       </c>
       <c r="F219">
-        <v>125333</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>180480</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10065,13 +10065,13 @@
         <v>81403</v>
       </c>
       <c r="F220">
-        <v>75783</v>
+        <v>74287</v>
       </c>
       <c r="G220">
-        <v>109128</v>
+        <v>106973</v>
       </c>
       <c r="H220">
-        <v>16496</v>
+        <v>15000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>50878</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>81403</v>
       </c>
       <c r="F221">
-        <v>65878</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>94864</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,16 +10195,16 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>90535</v>
+        <v>88047</v>
       </c>
       <c r="E223">
         <v>95874</v>
       </c>
       <c r="F223">
-        <v>105535</v>
+        <v>103047</v>
       </c>
       <c r="G223">
-        <v>151970</v>
+        <v>148388</v>
       </c>
       <c r="H223">
         <v>15000</v>
@@ -10245,13 +10245,13 @@
         <v>59677</v>
       </c>
       <c r="F224">
-        <v>41424</v>
+        <v>41412</v>
       </c>
       <c r="G224">
-        <v>59651</v>
+        <v>59633</v>
       </c>
       <c r="H224">
-        <v>24846</v>
+        <v>24834</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10376</v>
+        <v>10345</v>
       </c>
       <c r="E225">
         <v>59677</v>
       </c>
       <c r="F225">
-        <v>33424</v>
+        <v>33412</v>
       </c>
       <c r="G225">
-        <v>48131</v>
+        <v>48113</v>
       </c>
       <c r="H225">
-        <v>23048</v>
+        <v>23067</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37654</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>72340</v>
       </c>
       <c r="F226">
-        <v>53620</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>77213</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>15966</v>
+        <v>0</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>25854</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>72340</v>
       </c>
       <c r="F227">
-        <v>44554</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>64158</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>18700</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83148</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>108519</v>
       </c>
       <c r="F228">
-        <v>98148</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>141333</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13240</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>108519</v>
       </c>
       <c r="F229">
-        <v>40240</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>57946</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19077</v>
+        <v>19187</v>
       </c>
       <c r="E231">
         <v>180877</v>
       </c>
       <c r="F231">
-        <v>46077</v>
+        <v>46187</v>
       </c>
       <c r="G231">
-        <v>66351</v>
+        <v>66509</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10595,13 +10595,13 @@
         <v>52460</v>
       </c>
       <c r="F232">
-        <v>38428</v>
+        <v>34459</v>
       </c>
       <c r="G232">
-        <v>55336</v>
+        <v>49621</v>
       </c>
       <c r="H232">
-        <v>29093</v>
+        <v>25124</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>9922</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>52460</v>
       </c>
       <c r="F233">
-        <v>30428</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>43816</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>20506</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10770,13 +10770,13 @@
         <v>52460</v>
       </c>
       <c r="F236">
-        <v>37226</v>
+        <v>37207</v>
       </c>
       <c r="G236">
-        <v>53605</v>
+        <v>53578</v>
       </c>
       <c r="H236">
-        <v>28875</v>
+        <v>28856</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6917</v>
+        <v>6870</v>
       </c>
       <c r="E237">
         <v>52460</v>
       </c>
       <c r="F237">
-        <v>29226</v>
+        <v>29207</v>
       </c>
       <c r="G237">
-        <v>42085</v>
+        <v>42058</v>
       </c>
       <c r="H237">
-        <v>22309</v>
+        <v>22337</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11299</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>52460</v>
       </c>
       <c r="F239">
-        <v>30979</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>44610</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>19680</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24070</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>70549</v>
       </c>
       <c r="F240">
-        <v>52912</v>
+        <v>0</v>
       </c>
       <c r="G240">
-        <v>76193</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>28842</v>
+        <v>0</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>71880</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>70549</v>
       </c>
       <c r="F241">
-        <v>86880</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>125107</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34039</v>
+        <v>33992</v>
       </c>
       <c r="E242">
         <v>70549</v>
       </c>
       <c r="F242">
-        <v>51363</v>
+        <v>51344</v>
       </c>
       <c r="G242">
-        <v>73963</v>
+        <v>73935</v>
       </c>
       <c r="H242">
-        <v>17324</v>
+        <v>17352</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92351</v>
+        <v>92851</v>
       </c>
       <c r="E246">
         <v>108519</v>
       </c>
       <c r="F246">
-        <v>107351</v>
+        <v>107851</v>
       </c>
       <c r="G246">
-        <v>154585</v>
+        <v>155305</v>
       </c>
       <c r="H246">
         <v>15000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>67139</v>
+        <v>58703</v>
       </c>
       <c r="E248">
         <v>95874</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>73703</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>106132</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48139</v>
+        <v>48296</v>
       </c>
       <c r="E249">
         <v>95874</v>
       </c>
       <c r="F249">
-        <v>63139</v>
+        <v>63296</v>
       </c>
       <c r="G249">
-        <v>90920</v>
+        <v>91146</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72945</v>
+        <v>73023</v>
       </c>
       <c r="E250">
         <v>108519</v>
       </c>
       <c r="F250">
-        <v>103176</v>
+        <v>102738</v>
       </c>
       <c r="G250">
-        <v>148573</v>
+        <v>147943</v>
       </c>
       <c r="H250">
-        <v>30231</v>
+        <v>29715</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>74635</v>
+        <v>74197</v>
       </c>
       <c r="E251">
         <v>108519</v>
       </c>
       <c r="F251">
-        <v>89635</v>
+        <v>89197</v>
       </c>
       <c r="G251">
-        <v>129074</v>
+        <v>128444</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11475,13 +11475,13 @@
         <v>52460</v>
       </c>
       <c r="F252">
-        <v>39345</v>
+        <v>34459</v>
       </c>
       <c r="G252">
-        <v>56657</v>
+        <v>49621</v>
       </c>
       <c r="H252">
-        <v>27528</v>
+        <v>22642</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38421</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>52460</v>
       </c>
       <c r="F253">
-        <v>53421</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>76926</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,7 +11558,7 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24195</v>
+        <v>24336</v>
       </c>
       <c r="E254">
         <v>70549</v>
@@ -11570,7 +11570,7 @@
         <v>76193</v>
       </c>
       <c r="H254">
-        <v>28717</v>
+        <v>28576</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,16 +11604,16 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69283</v>
+        <v>69658</v>
       </c>
       <c r="E255">
         <v>70549</v>
       </c>
       <c r="F255">
-        <v>84283</v>
+        <v>84658</v>
       </c>
       <c r="G255">
-        <v>121368</v>
+        <v>121908</v>
       </c>
       <c r="H255">
         <v>15000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12504</v>
+        <v>12473</v>
       </c>
       <c r="E259">
         <v>50633</v>
       </c>
       <c r="F259">
-        <v>30748</v>
+        <v>30736</v>
       </c>
       <c r="G259">
-        <v>44277</v>
+        <v>44260</v>
       </c>
       <c r="H259">
-        <v>18244</v>
+        <v>18263</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12504</v>
+        <v>12473</v>
       </c>
       <c r="E261">
         <v>63295</v>
       </c>
       <c r="F261">
-        <v>35687</v>
+        <v>35674</v>
       </c>
       <c r="G261">
-        <v>51389</v>
+        <v>51371</v>
       </c>
       <c r="H261">
-        <v>23183</v>
+        <v>23201</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12504</v>
+        <v>12473</v>
       </c>
       <c r="E263">
         <v>72340</v>
       </c>
       <c r="F263">
-        <v>39214</v>
+        <v>39202</v>
       </c>
       <c r="G263">
-        <v>56468</v>
+        <v>56451</v>
       </c>
       <c r="H263">
-        <v>26710</v>
+        <v>26729</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39422</v>
+        <v>39641</v>
       </c>
       <c r="E264">
         <v>59677</v>
       </c>
       <c r="F264">
-        <v>54566</v>
+        <v>54641</v>
       </c>
       <c r="G264">
-        <v>78575</v>
+        <v>78683</v>
       </c>
       <c r="H264">
-        <v>15144</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23412</v>
+        <v>23538</v>
       </c>
       <c r="E265">
         <v>59677</v>
       </c>
       <c r="F265">
-        <v>38639</v>
+        <v>38689</v>
       </c>
       <c r="G265">
-        <v>55640</v>
+        <v>55712</v>
       </c>
       <c r="H265">
-        <v>15227</v>
+        <v>15151</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34790</v>
+        <v>34743</v>
       </c>
       <c r="E268">
         <v>59677</v>
       </c>
       <c r="F268">
-        <v>50527</v>
+        <v>50452</v>
       </c>
       <c r="G268">
-        <v>72759</v>
+        <v>72651</v>
       </c>
       <c r="H268">
-        <v>15737</v>
+        <v>15709</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23459</v>
+        <v>23272</v>
       </c>
       <c r="E269">
         <v>59677</v>
       </c>
       <c r="F269">
-        <v>38658</v>
+        <v>38583</v>
       </c>
       <c r="G269">
-        <v>55668</v>
+        <v>55560</v>
       </c>
       <c r="H269">
-        <v>15199</v>
+        <v>15311</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>28984</v>
+        <v>29140</v>
       </c>
       <c r="E271">
         <v>66913</v>
       </c>
       <c r="F271">
-        <v>43984</v>
+        <v>44140</v>
       </c>
       <c r="G271">
-        <v>63337</v>
+        <v>63562</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71082</v>
+        <v>70973</v>
       </c>
       <c r="E272">
         <v>90429</v>
       </c>
       <c r="F272">
-        <v>86826</v>
+        <v>85973</v>
       </c>
       <c r="G272">
-        <v>125029</v>
+        <v>123801</v>
       </c>
       <c r="H272">
-        <v>15744</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21143</v>
+        <v>19625</v>
       </c>
       <c r="E273">
         <v>90429</v>
       </c>
       <c r="F273">
-        <v>48143</v>
+        <v>46625</v>
       </c>
       <c r="G273">
-        <v>69326</v>
+        <v>67140</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12444,13 +12444,13 @@
         <v>126608</v>
       </c>
       <c r="F274">
-        <v>50818</v>
+        <v>50896</v>
       </c>
       <c r="G274">
-        <v>73178</v>
+        <v>73290</v>
       </c>
       <c r="H274">
-        <v>28964</v>
+        <v>29042</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12082</v>
+        <v>12160</v>
       </c>
       <c r="E275">
         <v>126608</v>
       </c>
       <c r="F275">
-        <v>39082</v>
+        <v>39160</v>
       </c>
       <c r="G275">
-        <v>56278</v>
+        <v>56390</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>160632</v>
+        <v>151962</v>
       </c>
       <c r="E276">
         <v>162787</v>
       </c>
       <c r="F276">
-        <v>186644</v>
+        <v>186962</v>
       </c>
       <c r="G276">
-        <v>268767</v>
+        <v>269225</v>
       </c>
       <c r="H276">
-        <v>26012</v>
+        <v>35000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101428</v>
+        <v>101975</v>
       </c>
       <c r="E277">
         <v>162787</v>
       </c>
       <c r="F277">
-        <v>116428</v>
+        <v>116975</v>
       </c>
       <c r="G277">
-        <v>167656</v>
+        <v>168444</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>50049</v>
+        <v>49689</v>
       </c>
       <c r="E278">
         <v>108519</v>
       </c>
       <c r="F278">
-        <v>78175</v>
+        <v>78125</v>
       </c>
       <c r="G278">
-        <v>112572</v>
+        <v>112500</v>
       </c>
       <c r="H278">
-        <v>28126</v>
+        <v>28436</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49000</v>
+        <v>48875</v>
       </c>
       <c r="E279">
         <v>108519</v>
       </c>
       <c r="F279">
-        <v>67922</v>
+        <v>67872</v>
       </c>
       <c r="G279">
-        <v>97808</v>
+        <v>97736</v>
       </c>
       <c r="H279">
-        <v>18922</v>
+        <v>18997</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>67123</v>
+        <v>66732</v>
       </c>
       <c r="E280">
         <v>126608</v>
       </c>
       <c r="F280">
-        <v>90989</v>
+        <v>90939</v>
       </c>
       <c r="G280">
-        <v>131024</v>
+        <v>130952</v>
       </c>
       <c r="H280">
-        <v>23866</v>
+        <v>24207</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>49000</v>
+        <v>48875</v>
       </c>
       <c r="E281">
         <v>126608</v>
       </c>
       <c r="F281">
-        <v>74977</v>
+        <v>74927</v>
       </c>
       <c r="G281">
-        <v>107967</v>
+        <v>107895</v>
       </c>
       <c r="H281">
-        <v>25977</v>
+        <v>26052</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,7 +12791,7 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23508</v>
+        <v>24132</v>
       </c>
       <c r="E282">
         <v>54250</v>
@@ -12803,7 +12803,7 @@
         <v>58591</v>
       </c>
       <c r="H282">
-        <v>17180</v>
+        <v>16556</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,16 +12835,16 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24555</v>
+        <v>24539</v>
       </c>
       <c r="E283">
         <v>54250</v>
       </c>
       <c r="F283">
-        <v>39555</v>
+        <v>39539</v>
       </c>
       <c r="G283">
-        <v>56959</v>
+        <v>56936</v>
       </c>
       <c r="H283">
         <v>15000</v>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>64619</v>
+        <v>65480</v>
       </c>
       <c r="E284">
         <v>81403</v>
       </c>
       <c r="F284">
-        <v>79619</v>
+        <v>80480</v>
       </c>
       <c r="G284">
-        <v>114651</v>
+        <v>115891</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -13059,13 +13059,13 @@
         <v>57868</v>
       </c>
       <c r="F288">
-        <v>48416</v>
+        <v>48556</v>
       </c>
       <c r="G288">
-        <v>69719</v>
+        <v>69921</v>
       </c>
       <c r="H288">
-        <v>16662</v>
+        <v>16802</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25416</v>
+        <v>25556</v>
       </c>
       <c r="E289">
         <v>57868</v>
       </c>
       <c r="F289">
-        <v>40416</v>
+        <v>40556</v>
       </c>
       <c r="G289">
-        <v>58199</v>
+        <v>58401</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>33961</v>
+        <v>34133</v>
       </c>
       <c r="E291">
         <v>43397</v>
       </c>
       <c r="F291">
-        <v>48961</v>
+        <v>49133</v>
       </c>
       <c r="G291">
-        <v>70504</v>
+        <v>70752</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43006</v>
+        <v>43304</v>
       </c>
       <c r="E292">
         <v>108519</v>
       </c>
       <c r="F292">
-        <v>72956</v>
+        <v>73049</v>
       </c>
       <c r="G292">
-        <v>105057</v>
+        <v>105191</v>
       </c>
       <c r="H292">
-        <v>29950</v>
+        <v>29745</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37795</v>
+        <v>37998</v>
       </c>
       <c r="E293">
         <v>108519</v>
       </c>
       <c r="F293">
-        <v>63440</v>
+        <v>63521</v>
       </c>
       <c r="G293">
-        <v>91354</v>
+        <v>91470</v>
       </c>
       <c r="H293">
-        <v>25645</v>
+        <v>25523</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54165</v>
+        <v>54462</v>
       </c>
       <c r="E296">
         <v>72340</v>
       </c>
       <c r="F296">
-        <v>89165</v>
+        <v>69462</v>
       </c>
       <c r="G296">
-        <v>128398</v>
+        <v>100025</v>
       </c>
       <c r="H296">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64087</v>
+        <v>0</v>
       </c>
       <c r="E297">
         <v>72340</v>
       </c>
       <c r="F297">
-        <v>79087</v>
+        <v>0</v>
       </c>
       <c r="G297">
-        <v>113885</v>
+        <v>0</v>
       </c>
       <c r="H297">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4805</v>
+        <v>4836</v>
       </c>
       <c r="E299">
         <v>54250</v>
       </c>
       <c r="F299">
-        <v>29080</v>
+        <v>29092</v>
       </c>
       <c r="G299">
-        <v>41875</v>
+        <v>41892</v>
       </c>
       <c r="H299">
-        <v>24275</v>
+        <v>24256</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10705</v>
+        <v>10752</v>
       </c>
       <c r="E301">
         <v>68722</v>
       </c>
       <c r="F301">
-        <v>37083</v>
+        <v>37102</v>
       </c>
       <c r="G301">
-        <v>53400</v>
+        <v>53427</v>
       </c>
       <c r="H301">
-        <v>26378</v>
+        <v>26350</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>41692</v>
+        <v>41347</v>
       </c>
       <c r="E304">
         <v>108519</v>
       </c>
       <c r="F304">
-        <v>76519</v>
+        <v>76347</v>
       </c>
       <c r="G304">
-        <v>110187</v>
+        <v>109940</v>
       </c>
       <c r="H304">
-        <v>34827</v>
+        <v>35000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45369</v>
+        <v>45620</v>
       </c>
       <c r="E305">
         <v>108519</v>
       </c>
       <c r="F305">
-        <v>66470</v>
+        <v>66570</v>
       </c>
       <c r="G305">
-        <v>95717</v>
+        <v>95861</v>
       </c>
       <c r="H305">
-        <v>21101</v>
+        <v>20950</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24445</v>
+        <v>24273</v>
       </c>
       <c r="E306">
         <v>108519</v>
       </c>
       <c r="F306">
-        <v>59445</v>
+        <v>59273</v>
       </c>
       <c r="G306">
-        <v>85601</v>
+        <v>85353</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33241</v>
+        <v>33413</v>
       </c>
       <c r="E307">
         <v>108519</v>
       </c>
       <c r="F307">
-        <v>60241</v>
+        <v>60413</v>
       </c>
       <c r="G307">
-        <v>86747</v>
+        <v>86995</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13938,13 +13938,13 @@
         <v>235145</v>
       </c>
       <c r="F308">
-        <v>204566</v>
+        <v>221087</v>
       </c>
       <c r="G308">
-        <v>294575</v>
+        <v>318365</v>
       </c>
       <c r="H308">
-        <v>15662</v>
+        <v>32183</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>141116</v>
+        <v>157637</v>
       </c>
       <c r="E309">
         <v>235145</v>
       </c>
       <c r="F309">
-        <v>156116</v>
+        <v>172637</v>
       </c>
       <c r="G309">
-        <v>224807</v>
+        <v>248597</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>67045</v>
+        <v>66184</v>
       </c>
       <c r="E310">
         <v>126608</v>
       </c>
       <c r="F310">
-        <v>90207</v>
+        <v>89447</v>
       </c>
       <c r="G310">
-        <v>129898</v>
+        <v>128804</v>
       </c>
       <c r="H310">
-        <v>23162</v>
+        <v>23263</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53601</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>126608</v>
       </c>
       <c r="F311">
-        <v>76817</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>110616</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>23216</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,16 +14149,16 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110145</v>
+        <v>110739</v>
       </c>
       <c r="E313">
         <v>180877</v>
       </c>
       <c r="F313">
-        <v>125145</v>
+        <v>125739</v>
       </c>
       <c r="G313">
-        <v>180209</v>
+        <v>181064</v>
       </c>
       <c r="H313">
         <v>15000</v>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>123807</v>
+        <v>0</v>
       </c>
       <c r="E314">
         <v>235145</v>
       </c>
       <c r="F314">
-        <v>158807</v>
+        <v>0</v>
       </c>
       <c r="G314">
-        <v>228682</v>
+        <v>0</v>
       </c>
       <c r="H314">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>147188</v>
+        <v>147971</v>
       </c>
       <c r="E315">
         <v>235145</v>
       </c>
       <c r="F315">
-        <v>162188</v>
+        <v>162971</v>
       </c>
       <c r="G315">
-        <v>233551</v>
+        <v>234678</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71257</v>
+        <v>62720</v>
       </c>
       <c r="E2">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F2">
-        <v>86359</v>
+        <v>81029</v>
       </c>
       <c r="G2">
-        <v>124357</v>
+        <v>116682</v>
       </c>
       <c r="H2">
-        <v>15102</v>
+        <v>18309</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46098</v>
+        <v>40768</v>
       </c>
       <c r="E3">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F3">
-        <v>61098</v>
+        <v>55768</v>
       </c>
       <c r="G3">
-        <v>87981</v>
+        <v>80306</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>83194</v>
+        <v>83472</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>46098</v>
+        <v>73696</v>
       </c>
       <c r="E5">
-        <v>83194</v>
+        <v>83472</v>
       </c>
       <c r="F5">
-        <v>61098</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>87981</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4241</v>
+        <v>4704</v>
       </c>
       <c r="E7">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F7">
-        <v>28854</v>
+        <v>29110</v>
       </c>
       <c r="G7">
-        <v>41550</v>
+        <v>41918</v>
       </c>
       <c r="H7">
-        <v>24613</v>
+        <v>24406</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35745</v>
+        <v>31360</v>
       </c>
       <c r="E8">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F8">
-        <v>52851</v>
+        <v>51206</v>
       </c>
       <c r="G8">
-        <v>76105</v>
+        <v>73737</v>
       </c>
       <c r="H8">
-        <v>17106</v>
+        <v>19846</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>41313</v>
       </c>
       <c r="E11">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>64989</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>93584</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>23676</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>26464</v>
+        <v>70560</v>
       </c>
       <c r="E12">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F12">
-        <v>61007</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>87850</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>34543</v>
+        <v>0</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11706</v>
+        <v>10976</v>
       </c>
       <c r="E13">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F13">
-        <v>38706</v>
+        <v>37976</v>
       </c>
       <c r="G13">
-        <v>55737</v>
+        <v>54685</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>20233</v>
+        <v>39200</v>
       </c>
       <c r="E15">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F15">
-        <v>42306</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>60921</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>22073</v>
+        <v>0</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>34493</v>
+        <v>29792</v>
       </c>
       <c r="E21">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F21">
-        <v>59298</v>
+        <v>56792</v>
       </c>
       <c r="G21">
-        <v>85389</v>
+        <v>81780</v>
       </c>
       <c r="H21">
-        <v>24805</v>
+        <v>27000</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>159170</v>
+        <v>159702</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>159170</v>
+        <v>159702</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>21049</v>
+        <v>18816</v>
       </c>
       <c r="E27">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F27">
-        <v>39105</v>
+        <v>38294</v>
       </c>
       <c r="G27">
-        <v>56311</v>
+        <v>55143</v>
       </c>
       <c r="H27">
-        <v>18056</v>
+        <v>19478</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74494</v>
+        <v>65856</v>
       </c>
       <c r="E28">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F28">
-        <v>94956</v>
+        <v>94040</v>
       </c>
       <c r="G28">
-        <v>136737</v>
+        <v>135418</v>
       </c>
       <c r="H28">
-        <v>20462</v>
+        <v>28184</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>29140</v>
+        <v>28224</v>
       </c>
       <c r="E29">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F29">
-        <v>56140</v>
+        <v>55224</v>
       </c>
       <c r="G29">
-        <v>80842</v>
+        <v>79523</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>130224</v>
+        <v>114464</v>
       </c>
       <c r="E30">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F30">
-        <v>165224</v>
+        <v>136112</v>
       </c>
       <c r="G30">
-        <v>237923</v>
+        <v>196001</v>
       </c>
       <c r="H30">
-        <v>35000</v>
+        <v>21648</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>77640</v>
+        <v>57702</v>
       </c>
       <c r="E31">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F31">
-        <v>104640</v>
+        <v>84702</v>
       </c>
       <c r="G31">
-        <v>150682</v>
+        <v>121971</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72131</v>
+        <v>72269</v>
       </c>
       <c r="E32">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F32">
-        <v>89065</v>
+        <v>87269</v>
       </c>
       <c r="G32">
-        <v>128254</v>
+        <v>125667</v>
       </c>
       <c r="H32">
-        <v>16934</v>
+        <v>15000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>48390</v>
+        <v>42336</v>
       </c>
       <c r="E33">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F33">
-        <v>67678</v>
+        <v>65398</v>
       </c>
       <c r="G33">
-        <v>97456</v>
+        <v>94173</v>
       </c>
       <c r="H33">
-        <v>19288</v>
+        <v>23062</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>79742</v>
       </c>
       <c r="E35">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>94742</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>136428</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45213</v>
+        <v>42336</v>
       </c>
       <c r="E36">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F36">
-        <v>72213</v>
+        <v>69336</v>
       </c>
       <c r="G36">
-        <v>103987</v>
+        <v>99844</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38671</v>
+        <v>34496</v>
       </c>
       <c r="E43">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F43">
-        <v>65671</v>
+        <v>61496</v>
       </c>
       <c r="G43">
-        <v>94566</v>
+        <v>88554</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27450</v>
+        <v>23520</v>
       </c>
       <c r="E47">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F47">
-        <v>54450</v>
+        <v>50520</v>
       </c>
       <c r="G47">
-        <v>78408</v>
+        <v>72749</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>35979</v>
+        <v>36048</v>
       </c>
       <c r="E50">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F50">
-        <v>58635</v>
+        <v>54360</v>
       </c>
       <c r="G50">
-        <v>84434</v>
+        <v>78278</v>
       </c>
       <c r="H50">
-        <v>22656</v>
+        <v>18312</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>35635</v>
+        <v>31360</v>
       </c>
       <c r="E51">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F51">
-        <v>50635</v>
+        <v>46360</v>
       </c>
       <c r="G51">
-        <v>72914</v>
+        <v>66758</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>75958</v>
+        <v>76212</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>35443</v>
+        <v>61152</v>
       </c>
       <c r="E53">
-        <v>75958</v>
+        <v>76212</v>
       </c>
       <c r="F53">
-        <v>50443</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>72638</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48812</v>
+        <v>48608</v>
       </c>
       <c r="E54">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F54">
-        <v>83812</v>
+        <v>83343</v>
       </c>
       <c r="G54">
-        <v>120689</v>
+        <v>120014</v>
       </c>
       <c r="H54">
-        <v>35000</v>
+        <v>34735</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52036</v>
+        <v>45472</v>
       </c>
       <c r="E55">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F55">
-        <v>76191</v>
+        <v>72472</v>
       </c>
       <c r="G55">
-        <v>109715</v>
+        <v>104360</v>
       </c>
       <c r="H55">
-        <v>24155</v>
+        <v>27000</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62584</v>
+        <v>54880</v>
       </c>
       <c r="E57">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F57">
-        <v>87466</v>
+        <v>81880</v>
       </c>
       <c r="G57">
-        <v>125951</v>
+        <v>117907</v>
       </c>
       <c r="H57">
-        <v>24882</v>
+        <v>27000</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23491</v>
+        <v>24257</v>
       </c>
       <c r="E58">
-        <v>36161</v>
+        <v>36282</v>
       </c>
       <c r="F58">
-        <v>39538</v>
+        <v>39257</v>
       </c>
       <c r="G58">
-        <v>56935</v>
+        <v>56530</v>
       </c>
       <c r="H58">
-        <v>16047</v>
+        <v>15000</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6213</v>
+        <v>4704</v>
       </c>
       <c r="E59">
-        <v>36161</v>
+        <v>36282</v>
       </c>
       <c r="F59">
-        <v>22588</v>
+        <v>22031</v>
       </c>
       <c r="G59">
-        <v>32527</v>
+        <v>31725</v>
       </c>
       <c r="H59">
-        <v>16375</v>
+        <v>17327</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26151</v>
+        <v>23520</v>
       </c>
       <c r="E60">
-        <v>48824</v>
+        <v>48987</v>
       </c>
       <c r="F60">
-        <v>47977</v>
+        <v>48025</v>
       </c>
       <c r="G60">
-        <v>69087</v>
+        <v>69156</v>
       </c>
       <c r="H60">
-        <v>21826</v>
+        <v>24505</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>24977</v>
+        <v>25025</v>
       </c>
       <c r="E61">
-        <v>48824</v>
+        <v>48987</v>
       </c>
       <c r="F61">
-        <v>39977</v>
+        <v>40025</v>
       </c>
       <c r="G61">
-        <v>57567</v>
+        <v>57636</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12833</v>
+        <v>10976</v>
       </c>
       <c r="E63">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F63">
-        <v>39833</v>
+        <v>37976</v>
       </c>
       <c r="G63">
-        <v>57360</v>
+        <v>54685</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>122068</v>
+        <v>122476</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28013</v>
+        <v>25088</v>
       </c>
       <c r="E65">
-        <v>122068</v>
+        <v>122476</v>
       </c>
       <c r="F65">
-        <v>55013</v>
+        <v>52088</v>
       </c>
       <c r="G65">
-        <v>79219</v>
+        <v>75007</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24226</v>
+        <v>23520</v>
       </c>
       <c r="E66">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F66">
-        <v>53498</v>
+        <v>50680</v>
       </c>
       <c r="G66">
-        <v>77037</v>
+        <v>72979</v>
       </c>
       <c r="H66">
-        <v>29272</v>
+        <v>27160</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18498</v>
+        <v>15680</v>
       </c>
       <c r="E67">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F67">
-        <v>45498</v>
+        <v>42680</v>
       </c>
       <c r="G67">
-        <v>65517</v>
+        <v>61459</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34414</v>
+        <v>34480</v>
       </c>
       <c r="E68">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F68">
-        <v>62763</v>
+        <v>61480</v>
       </c>
       <c r="G68">
-        <v>90379</v>
+        <v>88531</v>
       </c>
       <c r="H68">
-        <v>28349</v>
+        <v>27000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27575</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F69">
-        <v>54575</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78588</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>45150</v>
+        <v>100352</v>
       </c>
       <c r="E70">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F70">
-        <v>80150</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>115416</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>50800</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F71">
-        <v>75697</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>109004</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>24897</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27116</v>
+        <v>27207</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5822</v>
+        <v>4704</v>
       </c>
       <c r="E73">
-        <v>27116</v>
+        <v>27207</v>
       </c>
       <c r="F73">
-        <v>20822</v>
+        <v>19704</v>
       </c>
       <c r="G73">
-        <v>29984</v>
+        <v>28374</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>94952</v>
+        <v>95269</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3691,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70519</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>94952</v>
+        <v>95269</v>
       </c>
       <c r="F75">
-        <v>85519</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>123147</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>85527</v>
+        <v>85676</v>
       </c>
       <c r="E76">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F76">
-        <v>100527</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>144759</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>46856</v>
+        <v>40768</v>
       </c>
       <c r="E77">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F77">
-        <v>73856</v>
+        <v>67768</v>
       </c>
       <c r="G77">
-        <v>106353</v>
+        <v>97586</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>36918</v>
+        <v>32928</v>
       </c>
       <c r="E81">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F81">
-        <v>56035</v>
+        <v>54557</v>
       </c>
       <c r="G81">
-        <v>80690</v>
+        <v>78562</v>
       </c>
       <c r="H81">
-        <v>19117</v>
+        <v>21629</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>83928</v>
+        <v>73696</v>
       </c>
       <c r="E83">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F83">
-        <v>98928</v>
+        <v>88696</v>
       </c>
       <c r="G83">
-        <v>142456</v>
+        <v>127722</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>75187</v>
+        <v>48326</v>
       </c>
       <c r="E84">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>71061</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>102328</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>22735</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>31863</v>
+        <v>28224</v>
       </c>
       <c r="E85">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F85">
-        <v>58246</v>
+        <v>55224</v>
       </c>
       <c r="G85">
-        <v>83874</v>
+        <v>79523</v>
       </c>
       <c r="H85">
-        <v>26383</v>
+        <v>27000</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>149887</v>
+        <v>150450</v>
       </c>
       <c r="E86">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F86">
-        <v>164887</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>237437</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>159223</v>
+        <v>0</v>
       </c>
       <c r="E88">
-        <v>159170</v>
+        <v>159702</v>
       </c>
       <c r="F88">
-        <v>174223</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>250881</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>125624</v>
+        <v>111328</v>
       </c>
       <c r="E89">
-        <v>159170</v>
+        <v>159702</v>
       </c>
       <c r="F89">
-        <v>140624</v>
+        <v>126328</v>
       </c>
       <c r="G89">
-        <v>202499</v>
+        <v>181912</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>7680</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F90">
-        <v>38271</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>55110</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>30591</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4257</v>
+        <v>5173</v>
       </c>
       <c r="E91">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F91">
-        <v>30271</v>
+        <v>30713</v>
       </c>
       <c r="G91">
-        <v>43590</v>
+        <v>44227</v>
       </c>
       <c r="H91">
-        <v>26014</v>
+        <v>25540</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27116</v>
+        <v>27207</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12067</v>
+        <v>10976</v>
       </c>
       <c r="E93">
-        <v>27116</v>
+        <v>27207</v>
       </c>
       <c r="F93">
-        <v>27067</v>
+        <v>25976</v>
       </c>
       <c r="G93">
-        <v>38976</v>
+        <v>37405</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>34352</v>
+        <v>34467</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>34352</v>
+        <v>34467</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61175</v>
+        <v>53312</v>
       </c>
       <c r="E96">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F96">
-        <v>76372</v>
+        <v>75011</v>
       </c>
       <c r="G96">
-        <v>109976</v>
+        <v>108016</v>
       </c>
       <c r="H96">
-        <v>15197</v>
+        <v>21699</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33460</v>
+        <v>29792</v>
       </c>
       <c r="E97">
-        <v>81385</v>
+        <v>81657</v>
       </c>
       <c r="F97">
-        <v>51124</v>
+        <v>49763</v>
       </c>
       <c r="G97">
-        <v>73619</v>
+        <v>71659</v>
       </c>
       <c r="H97">
-        <v>17664</v>
+        <v>19971</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>74193</v>
+        <v>72128</v>
       </c>
       <c r="E98">
-        <v>94047</v>
+        <v>94362</v>
       </c>
       <c r="F98">
-        <v>89312</v>
+        <v>107128</v>
       </c>
       <c r="G98">
-        <v>128609</v>
+        <v>154264</v>
       </c>
       <c r="H98">
-        <v>15119</v>
+        <v>35000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>33460</v>
+        <v>59584</v>
       </c>
       <c r="E99">
-        <v>94047</v>
+        <v>94362</v>
       </c>
       <c r="F99">
-        <v>56063</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>80731</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>22603</v>
+        <v>0</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61238</v>
+        <v>53312</v>
       </c>
       <c r="E100">
-        <v>105444</v>
+        <v>105796</v>
       </c>
       <c r="F100">
-        <v>79083</v>
+        <v>74933</v>
       </c>
       <c r="G100">
-        <v>113880</v>
+        <v>107904</v>
       </c>
       <c r="H100">
-        <v>17845</v>
+        <v>21621</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,19 +4834,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61426</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>105444</v>
+        <v>105796</v>
       </c>
       <c r="F101">
-        <v>76426</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>110053</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>135653</v>
+        <v>136107</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>135653</v>
+        <v>136107</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>72577</v>
       </c>
       <c r="E105">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>87577</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>126111</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3975</v>
+        <v>3983</v>
       </c>
       <c r="E109">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F109">
-        <v>30975</v>
+        <v>30983</v>
       </c>
       <c r="G109">
-        <v>44604</v>
+        <v>44616</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>162787</v>
+        <v>163332</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13349</v>
+        <v>12544</v>
       </c>
       <c r="E111">
-        <v>162787</v>
+        <v>163332</v>
       </c>
       <c r="F111">
-        <v>40349</v>
+        <v>39544</v>
       </c>
       <c r="G111">
-        <v>58103</v>
+        <v>56943</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>81703</v>
+        <v>86240</v>
       </c>
       <c r="E112">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F112">
-        <v>96703</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>139252</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>48313</v>
+        <v>47040</v>
       </c>
       <c r="E113">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F113">
-        <v>63313</v>
+        <v>62040</v>
       </c>
       <c r="G113">
-        <v>91171</v>
+        <v>89338</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5399,7 +5399,7 @@
         <v>0</v>
       </c>
       <c r="E114">
-        <v>115755</v>
+        <v>116142</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85183</v>
+        <v>87808</v>
       </c>
       <c r="E115">
-        <v>115755</v>
+        <v>116142</v>
       </c>
       <c r="F115">
-        <v>100183</v>
+        <v>102808</v>
       </c>
       <c r="G115">
-        <v>144264</v>
+        <v>148044</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>116702</v>
+        <v>0</v>
       </c>
       <c r="E117">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F117">
-        <v>131702</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>189651</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43340</v>
+        <v>43904</v>
       </c>
       <c r="E118">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F118">
-        <v>58340</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>84010</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>31666</v>
+        <v>28224</v>
       </c>
       <c r="E119">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F119">
-        <v>46666</v>
+        <v>43224</v>
       </c>
       <c r="G119">
-        <v>67199</v>
+        <v>62243</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60847</v>
+        <v>60964</v>
       </c>
       <c r="E120">
-        <v>79576</v>
+        <v>79842</v>
       </c>
       <c r="F120">
-        <v>79180</v>
+        <v>79291</v>
       </c>
       <c r="G120">
-        <v>114019</v>
+        <v>114179</v>
       </c>
       <c r="H120">
-        <v>18333</v>
+        <v>18327</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53852</v>
+        <v>53949</v>
       </c>
       <c r="E121">
-        <v>79576</v>
+        <v>79842</v>
       </c>
       <c r="F121">
-        <v>68852</v>
+        <v>68949</v>
       </c>
       <c r="G121">
-        <v>99147</v>
+        <v>99287</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>46512</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F122">
-        <v>65298</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>94029</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>18786</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>33616</v>
+        <v>39200</v>
       </c>
       <c r="E123">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F123">
-        <v>54714</v>
+        <v>57066</v>
       </c>
       <c r="G123">
-        <v>78788</v>
+        <v>82175</v>
       </c>
       <c r="H123">
-        <v>21098</v>
+        <v>17866</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,19 +5833,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13846</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>43397</v>
+        <v>43542</v>
       </c>
       <c r="F124">
-        <v>32548</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>46869</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>18702</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>9406</v>
+        <v>7840</v>
       </c>
       <c r="E125">
-        <v>43397</v>
+        <v>43542</v>
       </c>
       <c r="F125">
-        <v>26687</v>
+        <v>26117</v>
       </c>
       <c r="G125">
-        <v>38429</v>
+        <v>37608</v>
       </c>
       <c r="H125">
-        <v>17281</v>
+        <v>18277</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,19 +5923,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>29642</v>
+        <v>28224</v>
       </c>
       <c r="E126">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F126">
-        <v>44642</v>
+        <v>43418</v>
       </c>
       <c r="G126">
-        <v>64284</v>
+        <v>62522</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>15194</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>59297</v>
+        <v>59496</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20126</v>
+        <v>17248</v>
       </c>
       <c r="E129">
-        <v>59297</v>
+        <v>59496</v>
       </c>
       <c r="F129">
-        <v>37176</v>
+        <v>36102</v>
       </c>
       <c r="G129">
-        <v>53533</v>
+        <v>51987</v>
       </c>
       <c r="H129">
-        <v>17050</v>
+        <v>18854</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>73878</v>
+        <v>74125</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>20126</v>
+        <v>31360</v>
       </c>
       <c r="E131">
-        <v>73878</v>
+        <v>74125</v>
       </c>
       <c r="F131">
-        <v>42863</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>61723</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>22737</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>92998</v>
+        <v>93309</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37544</v>
+        <v>32928</v>
       </c>
       <c r="E133">
-        <v>92998</v>
+        <v>93309</v>
       </c>
       <c r="F133">
-        <v>57287</v>
+        <v>55562</v>
       </c>
       <c r="G133">
-        <v>82493</v>
+        <v>80009</v>
       </c>
       <c r="H133">
-        <v>19743</v>
+        <v>22634</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>88620</v>
+        <v>88917</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>52915</v>
+        <v>47040</v>
       </c>
       <c r="E135">
-        <v>88620</v>
+        <v>88917</v>
       </c>
       <c r="F135">
-        <v>67915</v>
+        <v>62040</v>
       </c>
       <c r="G135">
-        <v>97798</v>
+        <v>89338</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>72680</v>
+        <v>64288</v>
       </c>
       <c r="E137">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F137">
-        <v>87680</v>
+        <v>81258</v>
       </c>
       <c r="G137">
-        <v>126259</v>
+        <v>117012</v>
       </c>
       <c r="H137">
-        <v>15000</v>
+        <v>16970</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>151934</v>
+        <v>152442</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>90698</v>
+        <v>79968</v>
       </c>
       <c r="E139">
-        <v>151934</v>
+        <v>152442</v>
       </c>
       <c r="F139">
-        <v>105698</v>
+        <v>97439</v>
       </c>
       <c r="G139">
-        <v>152205</v>
+        <v>140312</v>
       </c>
       <c r="H139">
-        <v>15000</v>
+        <v>17471</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37247</v>
+        <v>32928</v>
       </c>
       <c r="E140">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F140">
-        <v>61592</v>
+        <v>59928</v>
       </c>
       <c r="G140">
-        <v>88692</v>
+        <v>86296</v>
       </c>
       <c r="H140">
-        <v>24345</v>
+        <v>27000</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>26699</v>
+        <v>23520</v>
       </c>
       <c r="E142">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F142">
-        <v>60185</v>
+        <v>58520</v>
       </c>
       <c r="G142">
-        <v>86666</v>
+        <v>84269</v>
       </c>
       <c r="H142">
-        <v>33486</v>
+        <v>35000</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27294</v>
+        <v>25088</v>
       </c>
       <c r="E143">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F143">
-        <v>52185</v>
+        <v>51421</v>
       </c>
       <c r="G143">
-        <v>75146</v>
+        <v>74046</v>
       </c>
       <c r="H143">
-        <v>24891</v>
+        <v>26333</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45667</v>
+        <v>45754</v>
       </c>
       <c r="E144">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F144">
-        <v>64960</v>
+        <v>65131</v>
       </c>
       <c r="G144">
-        <v>93542</v>
+        <v>93789</v>
       </c>
       <c r="H144">
-        <v>19293</v>
+        <v>19377</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6754,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>58359</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F146">
-        <v>73359</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>105637</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>94441</v>
       </c>
       <c r="E147">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>109441</v>
       </c>
       <c r="G147">
-        <v>0</v>
+        <v>157595</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36699</v>
+        <v>36770</v>
       </c>
       <c r="E148">
-        <v>61486</v>
+        <v>61692</v>
       </c>
       <c r="F148">
-        <v>63911</v>
+        <v>59446</v>
       </c>
       <c r="G148">
-        <v>92032</v>
+        <v>85602</v>
       </c>
       <c r="H148">
-        <v>27212</v>
+        <v>22676</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>40529</v>
+        <v>36064</v>
       </c>
       <c r="E149">
-        <v>61486</v>
+        <v>61692</v>
       </c>
       <c r="F149">
-        <v>55529</v>
+        <v>51064</v>
       </c>
       <c r="G149">
-        <v>79962</v>
+        <v>73532</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15337</v>
+        <v>14112</v>
       </c>
       <c r="E151">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F151">
-        <v>33293</v>
+        <v>32873</v>
       </c>
       <c r="G151">
-        <v>47942</v>
+        <v>47337</v>
       </c>
       <c r="H151">
-        <v>17956</v>
+        <v>18761</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37357</v>
+        <v>32928</v>
       </c>
       <c r="E152">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F152">
-        <v>54255</v>
+        <v>54437</v>
       </c>
       <c r="G152">
-        <v>78127</v>
+        <v>78389</v>
       </c>
       <c r="H152">
-        <v>16898</v>
+        <v>21509</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33413</v>
+        <v>31360</v>
       </c>
       <c r="E153">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F153">
-        <v>48413</v>
+        <v>46851</v>
       </c>
       <c r="G153">
-        <v>69715</v>
+        <v>67465</v>
       </c>
       <c r="H153">
-        <v>15000</v>
+        <v>15491</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56559</v>
+        <v>50176</v>
       </c>
       <c r="E154">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F154">
-        <v>91559</v>
+        <v>65176</v>
       </c>
       <c r="G154">
-        <v>131845</v>
+        <v>93853</v>
       </c>
       <c r="H154">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>72992</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F155">
-        <v>87992</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>126708</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>34117</v>
+        <v>29792</v>
       </c>
       <c r="E156">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F156">
-        <v>49662</v>
+        <v>44908</v>
       </c>
       <c r="G156">
-        <v>71513</v>
+        <v>64668</v>
       </c>
       <c r="H156">
-        <v>15545</v>
+        <v>15116</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11800</v>
+        <v>10976</v>
       </c>
       <c r="E157">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F157">
-        <v>33994</v>
+        <v>33742</v>
       </c>
       <c r="G157">
-        <v>48951</v>
+        <v>48588</v>
       </c>
       <c r="H157">
-        <v>22194</v>
+        <v>22766</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>83194</v>
+        <v>83472</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>5600</v>
+        <v>31360</v>
       </c>
       <c r="E159">
-        <v>83194</v>
+        <v>83472</v>
       </c>
       <c r="F159">
-        <v>32600</v>
+        <v>0</v>
       </c>
       <c r="G159">
-        <v>46944</v>
+        <v>0</v>
       </c>
       <c r="H159">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>7680</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>54269</v>
+        <v>54450</v>
       </c>
       <c r="F160">
-        <v>38558</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>55524</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>30878</v>
+        <v>0</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8482</v>
+        <v>7840</v>
       </c>
       <c r="E161">
-        <v>54269</v>
+        <v>54450</v>
       </c>
       <c r="F161">
-        <v>30558</v>
+        <v>30372</v>
       </c>
       <c r="G161">
-        <v>44004</v>
+        <v>43736</v>
       </c>
       <c r="H161">
-        <v>22076</v>
+        <v>22532</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>10147</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F162">
-        <v>44014</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>63380</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>33867</v>
+        <v>0</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9014</v>
+        <v>9408</v>
       </c>
       <c r="E163">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F163">
-        <v>36014</v>
+        <v>36408</v>
       </c>
       <c r="G163">
-        <v>51860</v>
+        <v>52428</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>66866</v>
+        <v>68036</v>
       </c>
       <c r="E164">
-        <v>67836</v>
+        <v>68063</v>
       </c>
       <c r="F164">
-        <v>82046</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>118146</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>15180</v>
+        <v>0</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20752</v>
+        <v>18816</v>
       </c>
       <c r="E165">
-        <v>67836</v>
+        <v>68063</v>
       </c>
       <c r="F165">
-        <v>40757</v>
+        <v>40071</v>
       </c>
       <c r="G165">
-        <v>58690</v>
+        <v>57702</v>
       </c>
       <c r="H165">
-        <v>20005</v>
+        <v>21255</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>90013</v>
+        <v>91399</v>
       </c>
       <c r="E166">
-        <v>102206</v>
+        <v>102548</v>
       </c>
       <c r="F166">
-        <v>105361</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>151720</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15348</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>21847</v>
+        <v>40580</v>
       </c>
       <c r="E167">
-        <v>102206</v>
+        <v>102548</v>
       </c>
       <c r="F167">
-        <v>48847</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>70340</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7766,19 +7766,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>88821</v>
+        <v>73696</v>
       </c>
       <c r="E168">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F168">
-        <v>103902</v>
+        <v>102868</v>
       </c>
       <c r="G168">
-        <v>149619</v>
+        <v>148130</v>
       </c>
       <c r="H168">
-        <v>15081</v>
+        <v>29172</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8874</v>
+        <v>7840</v>
       </c>
       <c r="E169">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F169">
-        <v>35874</v>
+        <v>34840</v>
       </c>
       <c r="G169">
-        <v>51659</v>
+        <v>50170</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59298</v>
+        <v>59412</v>
       </c>
       <c r="E170">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F170">
-        <v>78553</v>
+        <v>78762</v>
       </c>
       <c r="G170">
-        <v>113116</v>
+        <v>113417</v>
       </c>
       <c r="H170">
-        <v>19255</v>
+        <v>19350</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78391</v>
+        <v>78541</v>
       </c>
       <c r="E172">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F172">
-        <v>107965</v>
+        <v>108250</v>
       </c>
       <c r="G172">
-        <v>155470</v>
+        <v>155880</v>
       </c>
       <c r="H172">
-        <v>29574</v>
+        <v>29709</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78626</v>
+        <v>78774</v>
       </c>
       <c r="E173">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F173">
-        <v>93883</v>
+        <v>94130</v>
       </c>
       <c r="G173">
-        <v>135192</v>
+        <v>135547</v>
       </c>
       <c r="H173">
-        <v>15257</v>
+        <v>15356</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>48046</v>
+        <v>47040</v>
       </c>
       <c r="E174">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F174">
-        <v>67822</v>
+        <v>68049</v>
       </c>
       <c r="G174">
-        <v>97664</v>
+        <v>97991</v>
       </c>
       <c r="H174">
-        <v>19776</v>
+        <v>21009</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>63710</v>
+        <v>59584</v>
       </c>
       <c r="E175">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F175">
-        <v>78710</v>
+        <v>74584</v>
       </c>
       <c r="G175">
-        <v>113342</v>
+        <v>107401</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>64896</v>
+        <v>56448</v>
       </c>
       <c r="E176">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F176">
-        <v>79896</v>
+        <v>71448</v>
       </c>
       <c r="G176">
-        <v>115050</v>
+        <v>102885</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26542</v>
+        <v>26593</v>
       </c>
       <c r="E178">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F178">
-        <v>53542</v>
+        <v>53593</v>
       </c>
       <c r="G178">
-        <v>77100</v>
+        <v>77174</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>26104</v>
+        <v>23520</v>
       </c>
       <c r="E180">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F180">
-        <v>53104</v>
+        <v>50520</v>
       </c>
       <c r="G180">
-        <v>76470</v>
+        <v>72749</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8347,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>99760</v>
+        <v>100336</v>
       </c>
       <c r="E182">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F182">
-        <v>114962</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>165545</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>15202</v>
+        <v>0</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64149</v>
+        <v>56448</v>
       </c>
       <c r="E183">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F183">
-        <v>81037</v>
+        <v>78122</v>
       </c>
       <c r="G183">
-        <v>116693</v>
+        <v>112496</v>
       </c>
       <c r="H183">
-        <v>16888</v>
+        <v>21674</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>143964</v>
+        <v>144240</v>
       </c>
       <c r="E184">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F184">
-        <v>159258</v>
+        <v>179240</v>
       </c>
       <c r="G184">
-        <v>229332</v>
+        <v>258106</v>
       </c>
       <c r="H184">
-        <v>15294</v>
+        <v>35000</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,19 +8517,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>64149</v>
+        <v>0</v>
       </c>
       <c r="E185">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F185">
-        <v>91149</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>131255</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>187064</v>
+        <v>188144</v>
       </c>
       <c r="E186">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F186">
-        <v>202064</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>290972</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,19 +8604,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>64149</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F187">
-        <v>91149</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>131255</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>289509</v>
+        <v>290064</v>
       </c>
       <c r="E188">
-        <v>361772</v>
+        <v>362982</v>
       </c>
       <c r="F188">
-        <v>324509</v>
+        <v>305064</v>
       </c>
       <c r="G188">
-        <v>467293</v>
+        <v>439292</v>
       </c>
       <c r="H188">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8691,19 +8691,19 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>306458</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>361772</v>
+        <v>362982</v>
       </c>
       <c r="F189">
-        <v>321458</v>
+        <v>0</v>
       </c>
       <c r="G189">
-        <v>462900</v>
+        <v>0</v>
       </c>
       <c r="H189">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I189" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29610</v>
+        <v>29588</v>
       </c>
       <c r="E190">
-        <v>94952</v>
+        <v>95269</v>
       </c>
       <c r="F190">
-        <v>64610</v>
+        <v>64588</v>
       </c>
       <c r="G190">
-        <v>93038</v>
+        <v>93007</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44462</v>
+        <v>65856</v>
       </c>
       <c r="E191">
-        <v>94952</v>
+        <v>95269</v>
       </c>
       <c r="F191">
-        <v>60816</v>
+        <v>80856</v>
       </c>
       <c r="G191">
-        <v>87575</v>
+        <v>116433</v>
       </c>
       <c r="H191">
-        <v>16354</v>
+        <v>15000</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>43397</v>
+        <v>43340</v>
       </c>
       <c r="E192">
-        <v>122086</v>
+        <v>122494</v>
       </c>
       <c r="F192">
-        <v>70397</v>
+        <v>70340</v>
       </c>
       <c r="G192">
-        <v>101372</v>
+        <v>101290</v>
       </c>
       <c r="H192">
         <v>27000</v>
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>122086</v>
+        <v>122494</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>53601</v>
+        <v>53610</v>
       </c>
       <c r="E194">
-        <v>149401</v>
+        <v>149901</v>
       </c>
       <c r="F194">
-        <v>80601</v>
+        <v>80610</v>
       </c>
       <c r="G194">
-        <v>116065</v>
+        <v>116078</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>122086</v>
+        <v>122494</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23618</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F196">
-        <v>54255</v>
+        <v>0</v>
       </c>
       <c r="G196">
-        <v>78127</v>
+        <v>0</v>
       </c>
       <c r="H196">
-        <v>30637</v>
+        <v>0</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32411</v>
+        <v>0</v>
       </c>
       <c r="E197">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F197">
-        <v>47411</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>68272</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26433</v>
+        <v>26484</v>
       </c>
       <c r="E198">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F198">
-        <v>53433</v>
+        <v>53484</v>
       </c>
       <c r="G198">
-        <v>76944</v>
+        <v>77017</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9136,7 +9136,7 @@
         <v>0</v>
       </c>
       <c r="E199">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>14065</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F200">
-        <v>46878</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>67504</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>32813</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11878</v>
+        <v>10976</v>
       </c>
       <c r="E201">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F201">
-        <v>38878</v>
+        <v>37976</v>
       </c>
       <c r="G201">
-        <v>55984</v>
+        <v>54685</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9266,19 +9266,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>22432</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F202">
-        <v>57432</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>82702</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22646</v>
+        <v>72128</v>
       </c>
       <c r="E203">
-        <v>144698</v>
+        <v>145182</v>
       </c>
       <c r="F203">
-        <v>49646</v>
+        <v>91472</v>
       </c>
       <c r="G203">
-        <v>71490</v>
+        <v>131720</v>
       </c>
       <c r="H203">
-        <v>27000</v>
+        <v>19344</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>28738</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F204">
-        <v>55738</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>80263</v>
+        <v>0</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>26233</v>
       </c>
       <c r="E205">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>53233</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>76656</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24179</v>
+        <v>27581</v>
       </c>
       <c r="E206">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F206">
-        <v>42122</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>60656</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>17943</v>
+        <v>0</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13177</v>
+        <v>12544</v>
       </c>
       <c r="E207">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F207">
-        <v>33839</v>
+        <v>33662</v>
       </c>
       <c r="G207">
-        <v>48728</v>
+        <v>48473</v>
       </c>
       <c r="H207">
-        <v>20662</v>
+        <v>21118</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="E208">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="E209">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="E210">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40299</v>
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F211">
-        <v>64442</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>92796</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>24143</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="E213">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -9792,16 +9792,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28953</v>
+        <v>25088</v>
       </c>
       <c r="E214">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F214">
-        <v>55953</v>
+        <v>52088</v>
       </c>
       <c r="G214">
-        <v>80572</v>
+        <v>75007</v>
       </c>
       <c r="H214">
         <v>27000</v>
@@ -9841,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="E215">
-        <v>86812</v>
+        <v>87102</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45542</v>
+        <v>39200</v>
       </c>
       <c r="E216">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F216">
-        <v>69794</v>
+        <v>66200</v>
       </c>
       <c r="G216">
-        <v>100503</v>
+        <v>95328</v>
       </c>
       <c r="H216">
-        <v>24252</v>
+        <v>27000</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9930,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>101283</v>
+        <v>101622</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -9973,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="E218">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>111136</v>
       </c>
       <c r="E219">
-        <v>130226</v>
+        <v>130662</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>126136</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>181636</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>59287</v>
+        <v>59584</v>
       </c>
       <c r="E220">
-        <v>81403</v>
+        <v>81675</v>
       </c>
       <c r="F220">
-        <v>74287</v>
+        <v>0</v>
       </c>
       <c r="G220">
-        <v>106973</v>
+        <v>0</v>
       </c>
       <c r="H220">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10108,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="E221">
-        <v>81403</v>
+        <v>81675</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74165</v>
+        <v>68992</v>
       </c>
       <c r="E222">
-        <v>95874</v>
+        <v>96195</v>
       </c>
       <c r="F222">
-        <v>109165</v>
+        <v>83992</v>
       </c>
       <c r="G222">
-        <v>157198</v>
+        <v>120948</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>88047</v>
+        <v>0</v>
       </c>
       <c r="E223">
-        <v>95874</v>
+        <v>96195</v>
       </c>
       <c r="F223">
-        <v>103047</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>148388</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16578</v>
+        <v>0</v>
       </c>
       <c r="E224">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F224">
-        <v>41412</v>
+        <v>0</v>
       </c>
       <c r="G224">
-        <v>59633</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>24834</v>
+        <v>0</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10345</v>
+        <v>9408</v>
       </c>
       <c r="E225">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F225">
-        <v>33412</v>
+        <v>33115</v>
       </c>
       <c r="G225">
-        <v>48113</v>
+        <v>47686</v>
       </c>
       <c r="H225">
-        <v>23067</v>
+        <v>23707</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>37926</v>
       </c>
       <c r="E226">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>53833</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>77520</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>15907</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="E227">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>83747</v>
       </c>
       <c r="E228">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>98747</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>142196</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>13343</v>
       </c>
       <c r="E229">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>40343</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>58094</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="E230">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19187</v>
+        <v>0</v>
       </c>
       <c r="E231">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F231">
-        <v>46187</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>66509</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9335</v>
+        <v>0</v>
       </c>
       <c r="E232">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F232">
-        <v>34459</v>
+        <v>0</v>
       </c>
       <c r="G232">
-        <v>49621</v>
+        <v>0</v>
       </c>
       <c r="H232">
-        <v>25124</v>
+        <v>0</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="E233">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -10680,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="E234">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>8351</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F236">
-        <v>37207</v>
+        <v>0</v>
       </c>
       <c r="G236">
-        <v>53578</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>28856</v>
+        <v>0</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6870</v>
+        <v>6272</v>
       </c>
       <c r="E237">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F237">
-        <v>29207</v>
+        <v>29037</v>
       </c>
       <c r="G237">
-        <v>42058</v>
+        <v>41813</v>
       </c>
       <c r="H237">
-        <v>22337</v>
+        <v>22765</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10856,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="E238">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -10901,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="E239">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F239">
         <v>0</v>
@@ -10944,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="E240">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="E241">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>33992</v>
+        <v>34057</v>
       </c>
       <c r="E242">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F242">
-        <v>51344</v>
+        <v>51476</v>
       </c>
       <c r="G242">
-        <v>73935</v>
+        <v>74125</v>
       </c>
       <c r="H242">
-        <v>17352</v>
+        <v>17419</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="E243">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -11119,7 +11119,7 @@
         <v>0</v>
       </c>
       <c r="E244">
-        <v>27134</v>
+        <v>27225</v>
       </c>
       <c r="F244">
         <v>0</v>
@@ -11164,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="E245">
-        <v>27134</v>
+        <v>27225</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>92851</v>
+        <v>0</v>
       </c>
       <c r="E246">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F246">
-        <v>107851</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>155305</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>58703</v>
+        <v>59364</v>
       </c>
       <c r="E248">
-        <v>95874</v>
+        <v>96195</v>
       </c>
       <c r="F248">
-        <v>73703</v>
+        <v>0</v>
       </c>
       <c r="G248">
-        <v>106132</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48296</v>
+        <v>0</v>
       </c>
       <c r="E249">
-        <v>95874</v>
+        <v>96195</v>
       </c>
       <c r="F249">
-        <v>63296</v>
+        <v>0</v>
       </c>
       <c r="G249">
-        <v>91146</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>73023</v>
+        <v>72128</v>
       </c>
       <c r="E250">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F250">
-        <v>102738</v>
+        <v>103724</v>
       </c>
       <c r="G250">
-        <v>147943</v>
+        <v>149363</v>
       </c>
       <c r="H250">
-        <v>29715</v>
+        <v>31596</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,16 +11426,16 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>74197</v>
+        <v>75183</v>
       </c>
       <c r="E251">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F251">
-        <v>89197</v>
+        <v>90183</v>
       </c>
       <c r="G251">
-        <v>128444</v>
+        <v>129864</v>
       </c>
       <c r="H251">
         <v>15000</v>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>11817</v>
+        <v>0</v>
       </c>
       <c r="E252">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F252">
-        <v>34459</v>
+        <v>0</v>
       </c>
       <c r="G252">
-        <v>49621</v>
+        <v>0</v>
       </c>
       <c r="H252">
-        <v>22642</v>
+        <v>0</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="E253">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>24336</v>
+        <v>23520</v>
       </c>
       <c r="E254">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F254">
-        <v>52912</v>
+        <v>47261</v>
       </c>
       <c r="G254">
-        <v>76193</v>
+        <v>68056</v>
       </c>
       <c r="H254">
-        <v>28576</v>
+        <v>23741</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>69658</v>
+        <v>0</v>
       </c>
       <c r="E255">
-        <v>70549</v>
+        <v>70785</v>
       </c>
       <c r="F255">
-        <v>84658</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>121908</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11650,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>52460</v>
+        <v>52635</v>
       </c>
       <c r="F257">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="E258">
-        <v>50633</v>
+        <v>50802</v>
       </c>
       <c r="F258">
         <v>0</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12473</v>
+        <v>10976</v>
       </c>
       <c r="E259">
-        <v>50633</v>
+        <v>50802</v>
       </c>
       <c r="F259">
-        <v>30736</v>
+        <v>30203</v>
       </c>
       <c r="G259">
-        <v>44260</v>
+        <v>43492</v>
       </c>
       <c r="H259">
-        <v>18263</v>
+        <v>19227</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="E260">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>12473</v>
+        <v>54880</v>
       </c>
       <c r="E261">
-        <v>63295</v>
+        <v>63507</v>
       </c>
       <c r="F261">
-        <v>35674</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>51371</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>23201</v>
+        <v>0</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="E262">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F262">
         <v>0</v>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>12473</v>
+        <v>65856</v>
       </c>
       <c r="E263">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F263">
-        <v>39202</v>
+        <v>0</v>
       </c>
       <c r="G263">
-        <v>56451</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>26729</v>
+        <v>0</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39641</v>
+        <v>39200</v>
       </c>
       <c r="E264">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F264">
-        <v>54641</v>
+        <v>54712</v>
       </c>
       <c r="G264">
-        <v>78683</v>
+        <v>78785</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>15512</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23538</v>
+        <v>23520</v>
       </c>
       <c r="E265">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F265">
-        <v>38689</v>
+        <v>38760</v>
       </c>
       <c r="G265">
-        <v>55712</v>
+        <v>55814</v>
       </c>
       <c r="H265">
-        <v>15151</v>
+        <v>15240</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="E266">
-        <v>66913</v>
+        <v>67137</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -12131,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>66913</v>
+        <v>67137</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34743</v>
+        <v>31360</v>
       </c>
       <c r="E268">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F268">
-        <v>50452</v>
+        <v>49375</v>
       </c>
       <c r="G268">
-        <v>72651</v>
+        <v>71100</v>
       </c>
       <c r="H268">
-        <v>15709</v>
+        <v>18015</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23272</v>
+        <v>20384</v>
       </c>
       <c r="E269">
-        <v>59677</v>
+        <v>59877</v>
       </c>
       <c r="F269">
-        <v>38583</v>
+        <v>37506</v>
       </c>
       <c r="G269">
-        <v>55560</v>
+        <v>54009</v>
       </c>
       <c r="H269">
-        <v>15311</v>
+        <v>17122</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12263,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="E270">
-        <v>66913</v>
+        <v>67137</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29140</v>
+        <v>0</v>
       </c>
       <c r="E271">
-        <v>66913</v>
+        <v>67137</v>
       </c>
       <c r="F271">
-        <v>44140</v>
+        <v>0</v>
       </c>
       <c r="G271">
-        <v>63562</v>
+        <v>0</v>
       </c>
       <c r="H271">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>70973</v>
+        <v>62720</v>
       </c>
       <c r="E272">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F272">
-        <v>85973</v>
+        <v>85164</v>
       </c>
       <c r="G272">
-        <v>123801</v>
+        <v>122636</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>22444</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>19625</v>
+        <v>18816</v>
       </c>
       <c r="E273">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F273">
-        <v>46625</v>
+        <v>45816</v>
       </c>
       <c r="G273">
-        <v>67140</v>
+        <v>65975</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>21854</v>
+        <v>57702</v>
       </c>
       <c r="E274">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F274">
-        <v>50896</v>
+        <v>0</v>
       </c>
       <c r="G274">
-        <v>73290</v>
+        <v>0</v>
       </c>
       <c r="H274">
-        <v>29042</v>
+        <v>0</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12160</v>
+        <v>10976</v>
       </c>
       <c r="E275">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F275">
-        <v>39160</v>
+        <v>37976</v>
       </c>
       <c r="G275">
-        <v>56390</v>
+        <v>54685</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>151962</v>
+        <v>152268</v>
       </c>
       <c r="E276">
-        <v>162787</v>
+        <v>163332</v>
       </c>
       <c r="F276">
-        <v>186962</v>
+        <v>167268</v>
       </c>
       <c r="G276">
-        <v>269225</v>
+        <v>240866</v>
       </c>
       <c r="H276">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>101975</v>
+        <v>0</v>
       </c>
       <c r="E277">
-        <v>162787</v>
+        <v>163332</v>
       </c>
       <c r="F277">
-        <v>116975</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>168444</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>49689</v>
+        <v>43904</v>
       </c>
       <c r="E278">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F278">
-        <v>78125</v>
+        <v>75651</v>
       </c>
       <c r="G278">
-        <v>112500</v>
+        <v>108937</v>
       </c>
       <c r="H278">
-        <v>28436</v>
+        <v>31747</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>48875</v>
+        <v>42336</v>
       </c>
       <c r="E279">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F279">
-        <v>67872</v>
+        <v>65398</v>
       </c>
       <c r="G279">
-        <v>97736</v>
+        <v>94173</v>
       </c>
       <c r="H279">
-        <v>18997</v>
+        <v>23062</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>66732</v>
+        <v>59584</v>
       </c>
       <c r="E280">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F280">
-        <v>90939</v>
+        <v>94584</v>
       </c>
       <c r="G280">
-        <v>130952</v>
+        <v>136201</v>
       </c>
       <c r="H280">
-        <v>24207</v>
+        <v>35000</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>48875</v>
+        <v>92512</v>
       </c>
       <c r="E281">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F281">
-        <v>74927</v>
+        <v>0</v>
       </c>
       <c r="G281">
-        <v>107895</v>
+        <v>0</v>
       </c>
       <c r="H281">
-        <v>26052</v>
+        <v>0</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24132</v>
+        <v>23755</v>
       </c>
       <c r="E282">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F282">
-        <v>40688</v>
+        <v>39996</v>
       </c>
       <c r="G282">
-        <v>58591</v>
+        <v>57594</v>
       </c>
       <c r="H282">
-        <v>16556</v>
+        <v>16241</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24539</v>
+        <v>0</v>
       </c>
       <c r="E283">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F283">
-        <v>39539</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>56936</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,16 +12878,16 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65480</v>
+        <v>58016</v>
       </c>
       <c r="E284">
-        <v>81403</v>
+        <v>81675</v>
       </c>
       <c r="F284">
-        <v>80480</v>
+        <v>73016</v>
       </c>
       <c r="G284">
-        <v>115891</v>
+        <v>105143</v>
       </c>
       <c r="H284">
         <v>15000</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="E285">
-        <v>81403</v>
+        <v>81675</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>37970</v>
+        <v>38097</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>18926</v>
+        <v>17248</v>
       </c>
       <c r="E287">
-        <v>37970</v>
+        <v>38097</v>
       </c>
       <c r="F287">
-        <v>33926</v>
+        <v>32248</v>
       </c>
       <c r="G287">
-        <v>48853</v>
+        <v>46437</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31754</v>
+        <v>29792</v>
       </c>
       <c r="E288">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F288">
-        <v>48556</v>
+        <v>48605</v>
       </c>
       <c r="G288">
-        <v>69921</v>
+        <v>69991</v>
       </c>
       <c r="H288">
-        <v>16802</v>
+        <v>18813</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25556</v>
+        <v>25605</v>
       </c>
       <c r="E289">
-        <v>57868</v>
+        <v>58062</v>
       </c>
       <c r="F289">
-        <v>40556</v>
+        <v>40605</v>
       </c>
       <c r="G289">
-        <v>58401</v>
+        <v>58471</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13143,19 +13143,19 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>10662</v>
+        <v>0</v>
       </c>
       <c r="E290">
-        <v>43397</v>
+        <v>43542</v>
       </c>
       <c r="F290">
-        <v>32548</v>
+        <v>0</v>
       </c>
       <c r="G290">
-        <v>46869</v>
+        <v>0</v>
       </c>
       <c r="H290">
-        <v>21886</v>
+        <v>0</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34133</v>
+        <v>39200</v>
       </c>
       <c r="E291">
-        <v>43397</v>
+        <v>43542</v>
       </c>
       <c r="F291">
-        <v>49133</v>
+        <v>54200</v>
       </c>
       <c r="G291">
-        <v>70752</v>
+        <v>78048</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43304</v>
+        <v>43340</v>
       </c>
       <c r="E292">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F292">
-        <v>73049</v>
+        <v>70340</v>
       </c>
       <c r="G292">
-        <v>105191</v>
+        <v>101290</v>
       </c>
       <c r="H292">
-        <v>29745</v>
+        <v>27000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>37998</v>
+        <v>0</v>
       </c>
       <c r="E293">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F293">
-        <v>63521</v>
+        <v>0</v>
       </c>
       <c r="G293">
-        <v>91470</v>
+        <v>0</v>
       </c>
       <c r="H293">
-        <v>25523</v>
+        <v>0</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="E295">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54462</v>
+        <v>54452</v>
       </c>
       <c r="E296">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F296">
-        <v>69462</v>
+        <v>89452</v>
       </c>
       <c r="G296">
-        <v>100025</v>
+        <v>128811</v>
       </c>
       <c r="H296">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>63291</v>
       </c>
       <c r="E297">
-        <v>72340</v>
+        <v>72582</v>
       </c>
       <c r="F297">
-        <v>0</v>
+        <v>78291</v>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>112739</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13501,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4836</v>
+        <v>4782</v>
       </c>
       <c r="E299">
-        <v>54250</v>
+        <v>54432</v>
       </c>
       <c r="F299">
-        <v>29092</v>
+        <v>29141</v>
       </c>
       <c r="G299">
-        <v>41892</v>
+        <v>41963</v>
       </c>
       <c r="H299">
-        <v>24256</v>
+        <v>24359</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>68722</v>
+        <v>68952</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10752</v>
+        <v>0</v>
       </c>
       <c r="E301">
-        <v>68722</v>
+        <v>68952</v>
       </c>
       <c r="F301">
-        <v>37102</v>
+        <v>0</v>
       </c>
       <c r="G301">
-        <v>53427</v>
+        <v>0</v>
       </c>
       <c r="H301">
-        <v>26350</v>
+        <v>0</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,19 +13668,19 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24773</v>
+        <v>0</v>
       </c>
       <c r="E302">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F302">
-        <v>51773</v>
+        <v>0</v>
       </c>
       <c r="G302">
-        <v>74553</v>
+        <v>0</v>
       </c>
       <c r="H302">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I302" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13717,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="E303">
-        <v>90429</v>
+        <v>90732</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>41347</v>
+        <v>41427</v>
       </c>
       <c r="E304">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F304">
-        <v>76347</v>
+        <v>68427</v>
       </c>
       <c r="G304">
-        <v>109940</v>
+        <v>98535</v>
       </c>
       <c r="H304">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45620</v>
+        <v>0</v>
       </c>
       <c r="E305">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F305">
-        <v>66570</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>95861</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>20950</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24273</v>
+        <v>24320</v>
       </c>
       <c r="E306">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F306">
-        <v>59273</v>
+        <v>51320</v>
       </c>
       <c r="G306">
-        <v>85353</v>
+        <v>73901</v>
       </c>
       <c r="H306">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33413</v>
+        <v>0</v>
       </c>
       <c r="E307">
-        <v>108519</v>
+        <v>108882</v>
       </c>
       <c r="F307">
-        <v>60413</v>
+        <v>0</v>
       </c>
       <c r="G307">
-        <v>86995</v>
+        <v>0</v>
       </c>
       <c r="H307">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>188904</v>
+        <v>166208</v>
       </c>
       <c r="E308">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F308">
-        <v>221087</v>
+        <v>201208</v>
       </c>
       <c r="G308">
-        <v>318365</v>
+        <v>289740</v>
       </c>
       <c r="H308">
-        <v>32183</v>
+        <v>35000</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,16 +13976,16 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>157637</v>
+        <v>142155</v>
       </c>
       <c r="E309">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F309">
-        <v>172637</v>
+        <v>157155</v>
       </c>
       <c r="G309">
-        <v>248597</v>
+        <v>226303</v>
       </c>
       <c r="H309">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>66184</v>
+        <v>66154</v>
       </c>
       <c r="E310">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F310">
-        <v>89447</v>
+        <v>89626</v>
       </c>
       <c r="G310">
-        <v>128804</v>
+        <v>129061</v>
       </c>
       <c r="H310">
-        <v>23263</v>
+        <v>23472</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>53986</v>
       </c>
       <c r="E311">
-        <v>126608</v>
+        <v>127032</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>77137</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>111077</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>23151</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14110,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="E312">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F312">
         <v>0</v>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>110739</v>
+        <v>0</v>
       </c>
       <c r="E313">
-        <v>180877</v>
+        <v>181482</v>
       </c>
       <c r="F313">
-        <v>125739</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>181064</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>124703</v>
       </c>
       <c r="E314">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F314">
-        <v>0</v>
+        <v>159703</v>
       </c>
       <c r="G314">
-        <v>0</v>
+        <v>229972</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>147971</v>
+        <v>148254</v>
       </c>
       <c r="E315">
-        <v>235145</v>
+        <v>235932</v>
       </c>
       <c r="F315">
-        <v>162971</v>
+        <v>163254</v>
       </c>
       <c r="G315">
-        <v>234678</v>
+        <v>235086</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>62720</v>
+        <v>67989</v>
       </c>
       <c r="E2">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F2">
-        <v>81029</v>
+        <v>82989</v>
       </c>
       <c r="G2">
-        <v>116682</v>
+        <v>119504</v>
       </c>
       <c r="H2">
-        <v>18309</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>40768</v>
+        <v>44051</v>
       </c>
       <c r="E3">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F3">
-        <v>55768</v>
+        <v>59051</v>
       </c>
       <c r="G3">
-        <v>80306</v>
+        <v>85033</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -574,7 +574,7 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>83472</v>
+        <v>84028</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -617,10 +617,10 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>73696</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>83472</v>
+        <v>84028</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4704</v>
+        <v>3570</v>
       </c>
       <c r="E7">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F7">
-        <v>29110</v>
+        <v>28798</v>
       </c>
       <c r="G7">
-        <v>41918</v>
+        <v>41469</v>
       </c>
       <c r="H7">
-        <v>24406</v>
+        <v>25228</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>31360</v>
+        <v>33509</v>
       </c>
       <c r="E8">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F8">
-        <v>51206</v>
+        <v>52284</v>
       </c>
       <c r="G8">
-        <v>73737</v>
+        <v>75289</v>
       </c>
       <c r="H8">
-        <v>19846</v>
+        <v>18775</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -796,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41313</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F11">
-        <v>64989</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>93584</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>23676</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>70560</v>
+        <v>81335</v>
       </c>
       <c r="E12">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>96335</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>138722</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>10976</v>
+        <v>11017</v>
       </c>
       <c r="E13">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F13">
-        <v>37976</v>
+        <v>38017</v>
       </c>
       <c r="G13">
-        <v>54685</v>
+        <v>54744</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>39200</v>
+        <v>29651</v>
       </c>
       <c r="E15">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>46356</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>66753</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>16705</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>29792</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F21">
-        <v>56792</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>81780</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1407,7 +1407,7 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>159702</v>
+        <v>160767</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>159702</v>
+        <v>160767</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>18816</v>
+        <v>20436</v>
       </c>
       <c r="E27">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F27">
-        <v>38294</v>
+        <v>39107</v>
       </c>
       <c r="G27">
-        <v>55143</v>
+        <v>56314</v>
       </c>
       <c r="H27">
-        <v>19478</v>
+        <v>18671</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>65856</v>
+        <v>65966</v>
       </c>
       <c r="E28">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F28">
-        <v>94040</v>
+        <v>89932</v>
       </c>
       <c r="G28">
-        <v>135418</v>
+        <v>129502</v>
       </c>
       <c r="H28">
-        <v>28184</v>
+        <v>23966</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>28224</v>
+        <v>23887</v>
       </c>
       <c r="E29">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F29">
-        <v>55224</v>
+        <v>50887</v>
       </c>
       <c r="G29">
-        <v>79523</v>
+        <v>73277</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>114464</v>
+        <v>131643</v>
       </c>
       <c r="E30">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F30">
-        <v>136112</v>
+        <v>146643</v>
       </c>
       <c r="G30">
-        <v>196001</v>
+        <v>211166</v>
       </c>
       <c r="H30">
-        <v>21648</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57702</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F31">
-        <v>84702</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>121971</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72269</v>
+        <v>62975</v>
       </c>
       <c r="E32">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F32">
-        <v>87269</v>
+        <v>80514</v>
       </c>
       <c r="G32">
-        <v>125667</v>
+        <v>115940</v>
       </c>
       <c r="H32">
-        <v>15000</v>
+        <v>17539</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>42336</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F33">
-        <v>65398</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>94173</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>23062</v>
+        <v>0</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>79742</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F35">
-        <v>94742</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>136428</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>42336</v>
+        <v>45275</v>
       </c>
       <c r="E36">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F36">
-        <v>69336</v>
+        <v>72275</v>
       </c>
       <c r="G36">
-        <v>99844</v>
+        <v>104076</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F37">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F38">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -2159,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="E41">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2286,19 +2286,19 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>34496</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F43">
-        <v>61496</v>
+        <v>0</v>
       </c>
       <c r="G43">
-        <v>88554</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I43" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="E45">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2457,19 +2457,19 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>23520</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F47">
-        <v>50520</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>72749</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I47" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/311210/Call_of_Duty_Black_Ops_III/","Abrir Steam")</f>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36048</v>
+        <v>34525</v>
       </c>
       <c r="E50">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F50">
-        <v>54360</v>
+        <v>49525</v>
       </c>
       <c r="G50">
-        <v>78278</v>
+        <v>71316</v>
       </c>
       <c r="H50">
-        <v>18312</v>
+        <v>15000</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>31360</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F51">
-        <v>46360</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>66758</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>76212</v>
+        <v>76720</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>61152</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>76212</v>
+        <v>76720</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>48608</v>
+        <v>46718</v>
       </c>
       <c r="E54">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F54">
-        <v>83343</v>
+        <v>81718</v>
       </c>
       <c r="G54">
-        <v>120014</v>
+        <v>117674</v>
       </c>
       <c r="H54">
-        <v>34735</v>
+        <v>35000</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>45472</v>
+        <v>49457</v>
       </c>
       <c r="E55">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F55">
-        <v>72472</v>
+        <v>75655</v>
       </c>
       <c r="G55">
-        <v>104360</v>
+        <v>108943</v>
       </c>
       <c r="H55">
-        <v>27000</v>
+        <v>26198</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2860,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>54880</v>
+        <v>59471</v>
       </c>
       <c r="E57">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F57">
-        <v>81880</v>
+        <v>86471</v>
       </c>
       <c r="G57">
-        <v>117907</v>
+        <v>124518</v>
       </c>
       <c r="H57">
         <v>27000</v>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>24257</v>
+        <v>20351</v>
       </c>
       <c r="E58">
-        <v>36282</v>
+        <v>36524</v>
       </c>
       <c r="F58">
-        <v>39257</v>
+        <v>37056</v>
       </c>
       <c r="G58">
-        <v>56530</v>
+        <v>53361</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>16705</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>4704</v>
+        <v>5900</v>
       </c>
       <c r="E59">
-        <v>36282</v>
+        <v>36524</v>
       </c>
       <c r="F59">
-        <v>22031</v>
+        <v>22605</v>
       </c>
       <c r="G59">
-        <v>31725</v>
+        <v>32551</v>
       </c>
       <c r="H59">
-        <v>17327</v>
+        <v>16705</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>23520</v>
+        <v>24499</v>
       </c>
       <c r="E60">
-        <v>48987</v>
+        <v>49313</v>
       </c>
       <c r="F60">
-        <v>48025</v>
+        <v>39499</v>
       </c>
       <c r="G60">
-        <v>69156</v>
+        <v>56879</v>
       </c>
       <c r="H60">
-        <v>24505</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25025</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>48987</v>
+        <v>49313</v>
       </c>
       <c r="F61">
-        <v>40025</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>57636</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>10976</v>
+        <v>12190</v>
       </c>
       <c r="E63">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F63">
-        <v>37976</v>
+        <v>39190</v>
       </c>
       <c r="G63">
-        <v>54685</v>
+        <v>56434</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>122476</v>
+        <v>123293</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>25088</v>
+        <v>29124</v>
       </c>
       <c r="E65">
-        <v>122476</v>
+        <v>123293</v>
       </c>
       <c r="F65">
-        <v>52088</v>
+        <v>56124</v>
       </c>
       <c r="G65">
-        <v>75007</v>
+        <v>80819</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>23520</v>
+        <v>25241</v>
       </c>
       <c r="E66">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F66">
-        <v>50680</v>
+        <v>53124</v>
       </c>
       <c r="G66">
-        <v>72979</v>
+        <v>76499</v>
       </c>
       <c r="H66">
-        <v>27160</v>
+        <v>27883</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>15680</v>
+        <v>18124</v>
       </c>
       <c r="E67">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F67">
-        <v>42680</v>
+        <v>45124</v>
       </c>
       <c r="G67">
-        <v>61459</v>
+        <v>64979</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34480</v>
+        <v>56879</v>
       </c>
       <c r="E68">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F68">
-        <v>61480</v>
+        <v>78075</v>
       </c>
       <c r="G68">
-        <v>88531</v>
+        <v>112428</v>
       </c>
       <c r="H68">
-        <v>27000</v>
+        <v>21196</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3434,7 +3434,7 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>100352</v>
+        <v>109592</v>
       </c>
       <c r="E70">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>124592</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>179412</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27207</v>
+        <v>27388</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>4704</v>
+        <v>5253</v>
       </c>
       <c r="E73">
-        <v>27207</v>
+        <v>27388</v>
       </c>
       <c r="F73">
-        <v>19704</v>
+        <v>20253</v>
       </c>
       <c r="G73">
-        <v>28374</v>
+        <v>29164</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>95269</v>
+        <v>95904</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>95269</v>
+        <v>95904</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -3734,10 +3734,10 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>85676</v>
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>40768</v>
+        <v>53657</v>
       </c>
       <c r="E77">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F77">
-        <v>67768</v>
+        <v>77335</v>
       </c>
       <c r="G77">
-        <v>97586</v>
+        <v>111362</v>
       </c>
       <c r="H77">
-        <v>27000</v>
+        <v>23678</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>32928</v>
+        <v>0</v>
       </c>
       <c r="E81">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F81">
-        <v>54557</v>
+        <v>0</v>
       </c>
       <c r="G81">
-        <v>78562</v>
+        <v>0</v>
       </c>
       <c r="H81">
-        <v>21629</v>
+        <v>0</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>73696</v>
+        <v>84158</v>
       </c>
       <c r="E83">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F83">
-        <v>88696</v>
+        <v>99158</v>
       </c>
       <c r="G83">
-        <v>127722</v>
+        <v>142788</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48326</v>
+        <v>48157</v>
       </c>
       <c r="E84">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F84">
-        <v>71061</v>
+        <v>71297</v>
       </c>
       <c r="G84">
-        <v>102328</v>
+        <v>102668</v>
       </c>
       <c r="H84">
-        <v>22735</v>
+        <v>23140</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>28224</v>
+        <v>32388</v>
       </c>
       <c r="E85">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F85">
-        <v>55224</v>
+        <v>58852</v>
       </c>
       <c r="G85">
-        <v>79523</v>
+        <v>84747</v>
       </c>
       <c r="H85">
-        <v>27000</v>
+        <v>26464</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>150450</v>
+        <v>67763</v>
       </c>
       <c r="E86">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>94763</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>136459</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -4261,7 +4261,7 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>159702</v>
+        <v>160767</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>111328</v>
+        <v>85552</v>
       </c>
       <c r="E89">
-        <v>159702</v>
+        <v>160767</v>
       </c>
       <c r="F89">
-        <v>126328</v>
+        <v>102920</v>
       </c>
       <c r="G89">
-        <v>181912</v>
+        <v>148205</v>
       </c>
       <c r="H89">
-        <v>15000</v>
+        <v>17368</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>7711</v>
       </c>
       <c r="E90">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>38060</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>54806</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>30349</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>5173</v>
+        <v>3162</v>
       </c>
       <c r="E91">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F91">
-        <v>30713</v>
+        <v>30060</v>
       </c>
       <c r="G91">
-        <v>44227</v>
+        <v>43286</v>
       </c>
       <c r="H91">
-        <v>25540</v>
+        <v>26898</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27207</v>
+        <v>27388</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>10976</v>
+        <v>11544</v>
       </c>
       <c r="E93">
-        <v>27207</v>
+        <v>27388</v>
       </c>
       <c r="F93">
-        <v>25976</v>
+        <v>26544</v>
       </c>
       <c r="G93">
-        <v>37405</v>
+        <v>38223</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>34467</v>
+        <v>34697</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>34467</v>
+        <v>34697</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>53312</v>
+        <v>56879</v>
       </c>
       <c r="E96">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F96">
-        <v>75011</v>
+        <v>72197</v>
       </c>
       <c r="G96">
-        <v>108016</v>
+        <v>103964</v>
       </c>
       <c r="H96">
-        <v>21699</v>
+        <v>15318</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>29792</v>
+        <v>31793</v>
       </c>
       <c r="E97">
-        <v>81657</v>
+        <v>82201</v>
       </c>
       <c r="F97">
-        <v>49763</v>
+        <v>50776</v>
       </c>
       <c r="G97">
-        <v>71659</v>
+        <v>73117</v>
       </c>
       <c r="H97">
-        <v>19971</v>
+        <v>18983</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>72128</v>
+        <v>72119</v>
       </c>
       <c r="E98">
-        <v>94362</v>
+        <v>94991</v>
       </c>
       <c r="F98">
-        <v>107128</v>
+        <v>87119</v>
       </c>
       <c r="G98">
-        <v>154264</v>
+        <v>125451</v>
       </c>
       <c r="H98">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>59584</v>
+        <v>58859</v>
       </c>
       <c r="E99">
-        <v>94362</v>
+        <v>94991</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>73859</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>106357</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>53312</v>
+        <v>57533</v>
       </c>
       <c r="E100">
-        <v>105796</v>
+        <v>106502</v>
       </c>
       <c r="F100">
-        <v>74933</v>
+        <v>76939</v>
       </c>
       <c r="G100">
-        <v>107904</v>
+        <v>110792</v>
       </c>
       <c r="H100">
-        <v>21621</v>
+        <v>19406</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4837,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="E101">
-        <v>105796</v>
+        <v>106502</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>136107</v>
+        <v>137014</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>136107</v>
+        <v>137014</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>72577</v>
+        <v>0</v>
       </c>
       <c r="E105">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F105">
-        <v>87577</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>126111</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5094,7 +5094,7 @@
         <v>0</v>
       </c>
       <c r="E107">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3983</v>
+        <v>3060</v>
       </c>
       <c r="E109">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F109">
-        <v>30983</v>
+        <v>30060</v>
       </c>
       <c r="G109">
-        <v>44616</v>
+        <v>43286</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>163332</v>
+        <v>164421</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>12544</v>
+        <v>13329</v>
       </c>
       <c r="E111">
-        <v>163332</v>
+        <v>164421</v>
       </c>
       <c r="F111">
-        <v>39544</v>
+        <v>40329</v>
       </c>
       <c r="G111">
-        <v>56943</v>
+        <v>58074</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>86240</v>
+        <v>82936</v>
       </c>
       <c r="E112">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>97936</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>141028</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>47040</v>
+        <v>46125</v>
       </c>
       <c r="E113">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F113">
-        <v>62040</v>
+        <v>61125</v>
       </c>
       <c r="G113">
-        <v>89338</v>
+        <v>88020</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5396,19 +5396,19 @@
         <v>15</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>132685</v>
       </c>
       <c r="E114">
-        <v>116142</v>
+        <v>116916</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>147685</v>
       </c>
       <c r="G114">
-        <v>0</v>
+        <v>212666</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I114" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>87808</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>116142</v>
+        <v>116916</v>
       </c>
       <c r="F115">
-        <v>102808</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>148044</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5486,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="E116">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="E117">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F117">
         <v>0</v>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43904</v>
+        <v>43521</v>
       </c>
       <c r="E118">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>58521</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>84270</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,16 +5614,16 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>28224</v>
+        <v>31011</v>
       </c>
       <c r="E119">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F119">
-        <v>43224</v>
+        <v>46011</v>
       </c>
       <c r="G119">
-        <v>62243</v>
+        <v>66256</v>
       </c>
       <c r="H119">
         <v>15000</v>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>60964</v>
+        <v>65813</v>
       </c>
       <c r="E120">
-        <v>79842</v>
+        <v>80374</v>
       </c>
       <c r="F120">
-        <v>79291</v>
+        <v>80813</v>
       </c>
       <c r="G120">
-        <v>114179</v>
+        <v>116371</v>
       </c>
       <c r="H120">
-        <v>18327</v>
+        <v>15000</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>53949</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>79842</v>
+        <v>80374</v>
       </c>
       <c r="F121">
-        <v>68949</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>99287</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="E122">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>39200</v>
+        <v>50988</v>
       </c>
       <c r="E123">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F123">
-        <v>57066</v>
+        <v>65988</v>
       </c>
       <c r="G123">
-        <v>82175</v>
+        <v>95023</v>
       </c>
       <c r="H123">
-        <v>17866</v>
+        <v>15000</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,19 +5833,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>13142</v>
       </c>
       <c r="E124">
-        <v>43542</v>
+        <v>43832</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>31095</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>44777</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>17953</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7840</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>43542</v>
+        <v>43832</v>
       </c>
       <c r="F125">
-        <v>26117</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>37608</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>18277</v>
+        <v>0</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,19 +5923,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>28224</v>
+        <v>30722</v>
       </c>
       <c r="E126">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F126">
-        <v>43418</v>
+        <v>45722</v>
       </c>
       <c r="G126">
-        <v>62522</v>
+        <v>65840</v>
       </c>
       <c r="H126">
-        <v>15194</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>59496</v>
+        <v>59892</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>17248</v>
+        <v>19943</v>
       </c>
       <c r="E129">
-        <v>59496</v>
+        <v>59892</v>
       </c>
       <c r="F129">
-        <v>36102</v>
+        <v>37335</v>
       </c>
       <c r="G129">
-        <v>51987</v>
+        <v>53762</v>
       </c>
       <c r="H129">
-        <v>18854</v>
+        <v>17392</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>74125</v>
+        <v>74619</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -6141,10 +6141,10 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>31360</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>74125</v>
+        <v>74619</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>93309</v>
+        <v>93931</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>32928</v>
+        <v>35805</v>
       </c>
       <c r="E133">
-        <v>93309</v>
+        <v>93931</v>
       </c>
       <c r="F133">
-        <v>55562</v>
+        <v>56955</v>
       </c>
       <c r="G133">
-        <v>80009</v>
+        <v>82015</v>
       </c>
       <c r="H133">
-        <v>22634</v>
+        <v>21150</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>88917</v>
+        <v>89510</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>47040</v>
+        <v>50954</v>
       </c>
       <c r="E135">
-        <v>88917</v>
+        <v>89510</v>
       </c>
       <c r="F135">
-        <v>62040</v>
+        <v>65954</v>
       </c>
       <c r="G135">
-        <v>89338</v>
+        <v>94974</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>64288</v>
+        <v>69451</v>
       </c>
       <c r="E137">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F137">
-        <v>81258</v>
+        <v>84451</v>
       </c>
       <c r="G137">
-        <v>117012</v>
+        <v>121609</v>
       </c>
       <c r="H137">
-        <v>16970</v>
+        <v>15000</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>152442</v>
+        <v>153458</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>79968</v>
+        <v>86657</v>
       </c>
       <c r="E139">
-        <v>152442</v>
+        <v>153458</v>
       </c>
       <c r="F139">
-        <v>97439</v>
+        <v>101657</v>
       </c>
       <c r="G139">
-        <v>140312</v>
+        <v>146386</v>
       </c>
       <c r="H139">
-        <v>17471</v>
+        <v>15000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>32928</v>
+        <v>36009</v>
       </c>
       <c r="E140">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F140">
-        <v>59928</v>
+        <v>61505</v>
       </c>
       <c r="G140">
-        <v>86296</v>
+        <v>88567</v>
       </c>
       <c r="H140">
-        <v>27000</v>
+        <v>25496</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>23520</v>
+        <v>23509</v>
       </c>
       <c r="E142">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F142">
-        <v>58520</v>
+        <v>50509</v>
       </c>
       <c r="G142">
-        <v>84269</v>
+        <v>72733</v>
       </c>
       <c r="H142">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>25088</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F143">
-        <v>51421</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>74046</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>26333</v>
+        <v>0</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45754</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F144">
-        <v>65131</v>
+        <v>0</v>
       </c>
       <c r="G144">
-        <v>93789</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>19377</v>
+        <v>0</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6754,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -6798,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="E146">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F146">
         <v>0</v>
@@ -6840,19 +6840,19 @@
         <v>17</v>
       </c>
       <c r="D147">
-        <v>94441</v>
+        <v>0</v>
       </c>
       <c r="E147">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F147">
-        <v>109441</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>157595</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I147" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36770</v>
+        <v>36558</v>
       </c>
       <c r="E148">
-        <v>61692</v>
+        <v>62103</v>
       </c>
       <c r="F148">
-        <v>59446</v>
+        <v>62297</v>
       </c>
       <c r="G148">
-        <v>85602</v>
+        <v>89708</v>
       </c>
       <c r="H148">
-        <v>22676</v>
+        <v>25739</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>36064</v>
+        <v>38730</v>
       </c>
       <c r="E149">
-        <v>61692</v>
+        <v>62103</v>
       </c>
       <c r="F149">
-        <v>51064</v>
+        <v>53730</v>
       </c>
       <c r="G149">
-        <v>73532</v>
+        <v>77371</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>54432</v>
+        <v>82201</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>14112</v>
+        <v>14842</v>
       </c>
       <c r="E151">
-        <v>54432</v>
+        <v>82201</v>
       </c>
       <c r="F151">
-        <v>32873</v>
+        <v>41842</v>
       </c>
       <c r="G151">
-        <v>47337</v>
+        <v>60252</v>
       </c>
       <c r="H151">
-        <v>18761</v>
+        <v>27000</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>32928</v>
+        <v>35652</v>
       </c>
       <c r="E152">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F152">
-        <v>54437</v>
+        <v>54800</v>
       </c>
       <c r="G152">
-        <v>78389</v>
+        <v>78912</v>
       </c>
       <c r="H152">
-        <v>21509</v>
+        <v>19148</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>31360</v>
+        <v>33425</v>
       </c>
       <c r="E153">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F153">
-        <v>46851</v>
+        <v>48425</v>
       </c>
       <c r="G153">
-        <v>67465</v>
+        <v>69732</v>
       </c>
       <c r="H153">
-        <v>15491</v>
+        <v>15000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,16 +7148,16 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>50176</v>
+        <v>54728</v>
       </c>
       <c r="E154">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F154">
-        <v>65176</v>
+        <v>69728</v>
       </c>
       <c r="G154">
-        <v>93853</v>
+        <v>100408</v>
       </c>
       <c r="H154">
         <v>15000</v>
@@ -7197,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="E155">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>29792</v>
+        <v>32116</v>
       </c>
       <c r="E156">
-        <v>59877</v>
+        <v>27388</v>
       </c>
       <c r="F156">
-        <v>44908</v>
+        <v>47116</v>
       </c>
       <c r="G156">
-        <v>64668</v>
+        <v>67847</v>
       </c>
       <c r="H156">
-        <v>15116</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>10976</v>
+        <v>13244</v>
       </c>
       <c r="E157">
-        <v>59877</v>
+        <v>27388</v>
       </c>
       <c r="F157">
-        <v>33742</v>
+        <v>28244</v>
       </c>
       <c r="G157">
-        <v>48588</v>
+        <v>40671</v>
       </c>
       <c r="H157">
-        <v>22766</v>
+        <v>15000</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>83472</v>
+        <v>84028</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -7367,10 +7367,10 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>31360</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>83472</v>
+        <v>84028</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>7836</v>
       </c>
       <c r="E160">
-        <v>54450</v>
+        <v>54813</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>50400</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>27164</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>7840</v>
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>54450</v>
+        <v>54813</v>
       </c>
       <c r="F161">
-        <v>30372</v>
+        <v>0</v>
       </c>
       <c r="G161">
-        <v>43736</v>
+        <v>0</v>
       </c>
       <c r="H161">
-        <v>22532</v>
+        <v>0</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>10147</v>
       </c>
       <c r="E162">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>37147</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>53492</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,19 +7547,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9408</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F163">
-        <v>36408</v>
+        <v>0</v>
       </c>
       <c r="G163">
-        <v>52428</v>
+        <v>0</v>
       </c>
       <c r="H163">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>68036</v>
+        <v>65007</v>
       </c>
       <c r="E164">
-        <v>68063</v>
+        <v>68516</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>80271</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>115590</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>15264</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>18816</v>
+        <v>20759</v>
       </c>
       <c r="E165">
-        <v>68063</v>
+        <v>68516</v>
       </c>
       <c r="F165">
-        <v>40071</v>
+        <v>41025</v>
       </c>
       <c r="G165">
-        <v>57702</v>
+        <v>59076</v>
       </c>
       <c r="H165">
-        <v>21255</v>
+        <v>20266</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>91399</v>
+        <v>87360</v>
       </c>
       <c r="E166">
-        <v>102548</v>
+        <v>103231</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>102360</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>147398</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,10 +7722,10 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>40580</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>102548</v>
+        <v>103231</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -7766,19 +7766,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>73696</v>
+        <v>75504</v>
       </c>
       <c r="E168">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F168">
-        <v>102868</v>
+        <v>94034</v>
       </c>
       <c r="G168">
-        <v>148130</v>
+        <v>135409</v>
       </c>
       <c r="H168">
-        <v>29172</v>
+        <v>18530</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,19 +7811,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>7840</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F169">
-        <v>34840</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>50170</v>
+        <v>0</v>
       </c>
       <c r="H169">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59412</v>
+        <v>56879</v>
       </c>
       <c r="E170">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F170">
-        <v>78762</v>
+        <v>78075</v>
       </c>
       <c r="G170">
-        <v>113417</v>
+        <v>112428</v>
       </c>
       <c r="H170">
-        <v>19350</v>
+        <v>21196</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="E171">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78541</v>
+        <v>75168</v>
       </c>
       <c r="E172">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F172">
-        <v>108250</v>
+        <v>101835</v>
       </c>
       <c r="G172">
-        <v>155880</v>
+        <v>146642</v>
       </c>
       <c r="H172">
-        <v>29709</v>
+        <v>26667</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78774</v>
+        <v>0</v>
       </c>
       <c r="E173">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F173">
-        <v>94130</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>135547</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>15356</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>47040</v>
+        <v>46720</v>
       </c>
       <c r="E174">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F174">
-        <v>68049</v>
+        <v>68503</v>
       </c>
       <c r="G174">
-        <v>97991</v>
+        <v>98644</v>
       </c>
       <c r="H174">
-        <v>21009</v>
+        <v>21783</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>59584</v>
+        <v>75640</v>
       </c>
       <c r="E175">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F175">
-        <v>74584</v>
+        <v>90640</v>
       </c>
       <c r="G175">
-        <v>107401</v>
+        <v>130522</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>56448</v>
+        <v>56241</v>
       </c>
       <c r="E176">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F176">
-        <v>71448</v>
+        <v>71241</v>
       </c>
       <c r="G176">
-        <v>102885</v>
+        <v>102587</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26593</v>
+        <v>28444</v>
       </c>
       <c r="E178">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F178">
-        <v>53593</v>
+        <v>55444</v>
       </c>
       <c r="G178">
-        <v>77174</v>
+        <v>79839</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>23520</v>
+        <v>24907</v>
       </c>
       <c r="E180">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F180">
-        <v>50520</v>
+        <v>51907</v>
       </c>
       <c r="G180">
-        <v>72749</v>
+        <v>74746</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8347,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100336</v>
+        <v>82280</v>
       </c>
       <c r="E182">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>97622</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>140576</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>15342</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>56448</v>
+        <v>61682</v>
       </c>
       <c r="E183">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F183">
-        <v>78122</v>
+        <v>80545</v>
       </c>
       <c r="G183">
-        <v>112496</v>
+        <v>115985</v>
       </c>
       <c r="H183">
-        <v>21674</v>
+        <v>18863</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144240</v>
+        <v>111745</v>
       </c>
       <c r="E184">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F184">
-        <v>179240</v>
+        <v>137019</v>
       </c>
       <c r="G184">
-        <v>258106</v>
+        <v>197307</v>
       </c>
       <c r="H184">
-        <v>35000</v>
+        <v>25274</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,19 +8517,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>0</v>
+        <v>176867</v>
       </c>
       <c r="E185">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F185">
-        <v>0</v>
+        <v>191867</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>276288</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>188144</v>
+        <v>140195</v>
       </c>
       <c r="E186">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>167195</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>240761</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,19 +8604,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>176867</v>
       </c>
       <c r="E187">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F187">
-        <v>0</v>
+        <v>191867</v>
       </c>
       <c r="G187">
-        <v>0</v>
+        <v>276288</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>290064</v>
+        <v>218431</v>
       </c>
       <c r="E188">
-        <v>362982</v>
+        <v>365402</v>
       </c>
       <c r="F188">
-        <v>305064</v>
+        <v>245431</v>
       </c>
       <c r="G188">
-        <v>439292</v>
+        <v>353421</v>
       </c>
       <c r="H188">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8694,7 +8694,7 @@
         <v>0</v>
       </c>
       <c r="E189">
-        <v>362982</v>
+        <v>365402</v>
       </c>
       <c r="F189">
         <v>0</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29588</v>
+        <v>30627</v>
       </c>
       <c r="E190">
-        <v>95269</v>
+        <v>95904</v>
       </c>
       <c r="F190">
-        <v>64588</v>
+        <v>65627</v>
       </c>
       <c r="G190">
-        <v>93007</v>
+        <v>94503</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>65856</v>
+        <v>37760</v>
       </c>
       <c r="E191">
-        <v>95269</v>
+        <v>95904</v>
       </c>
       <c r="F191">
-        <v>80856</v>
+        <v>58507</v>
       </c>
       <c r="G191">
-        <v>116433</v>
+        <v>84250</v>
       </c>
       <c r="H191">
-        <v>15000</v>
+        <v>20747</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>43340</v>
+        <v>41897</v>
       </c>
       <c r="E192">
-        <v>122494</v>
+        <v>123311</v>
       </c>
       <c r="F192">
-        <v>70340</v>
+        <v>68897</v>
       </c>
       <c r="G192">
-        <v>101290</v>
+        <v>99212</v>
       </c>
       <c r="H192">
         <v>27000</v>
@@ -8871,7 +8871,7 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>122494</v>
+        <v>123311</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>53610</v>
+        <v>52091</v>
       </c>
       <c r="E194">
-        <v>149901</v>
+        <v>150900</v>
       </c>
       <c r="F194">
-        <v>80610</v>
+        <v>79091</v>
       </c>
       <c r="G194">
-        <v>116078</v>
+        <v>113891</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8958,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="E195">
-        <v>122494</v>
+        <v>123311</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>12597</v>
       </c>
       <c r="E196">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F196">
-        <v>0</v>
+        <v>39597</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>57020</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9047,7 +9047,7 @@
         <v>0</v>
       </c>
       <c r="E197">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26484</v>
+        <v>21230</v>
       </c>
       <c r="E198">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F198">
-        <v>53484</v>
+        <v>48230</v>
       </c>
       <c r="G198">
-        <v>77017</v>
+        <v>69451</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9136,7 +9136,7 @@
         <v>0</v>
       </c>
       <c r="E199">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>13176</v>
       </c>
       <c r="E200">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>40176</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>57853</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,19 +9222,19 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>10976</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F201">
-        <v>37976</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>54685</v>
+        <v>0</v>
       </c>
       <c r="H201">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I201" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9266,19 +9266,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>21317</v>
       </c>
       <c r="E202">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>56317</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>81096</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>72128</v>
+        <v>27883</v>
       </c>
       <c r="E203">
-        <v>145182</v>
+        <v>146150</v>
       </c>
       <c r="F203">
-        <v>91472</v>
+        <v>54883</v>
       </c>
       <c r="G203">
-        <v>131720</v>
+        <v>79032</v>
       </c>
       <c r="H203">
-        <v>19344</v>
+        <v>27000</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>26397</v>
       </c>
       <c r="E204">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>53397</v>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>76892</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26233</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F205">
-        <v>53233</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>76656</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>27581</v>
+        <v>15766</v>
       </c>
       <c r="E206">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F206">
-        <v>0</v>
+        <v>38609</v>
       </c>
       <c r="G206">
-        <v>0</v>
+        <v>55597</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>22843</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>12544</v>
+        <v>0</v>
       </c>
       <c r="E207">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F207">
-        <v>33662</v>
+        <v>0</v>
       </c>
       <c r="G207">
-        <v>48473</v>
+        <v>0</v>
       </c>
       <c r="H207">
-        <v>21118</v>
+        <v>0</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="E208">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -9581,7 +9581,7 @@
         <v>0</v>
       </c>
       <c r="E209">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="E210">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="E211">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F211">
         <v>0</v>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9752,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="E213">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F213">
         <v>0</v>
@@ -9792,16 +9792,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>25088</v>
+        <v>26284</v>
       </c>
       <c r="E214">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F214">
-        <v>52088</v>
+        <v>53284</v>
       </c>
       <c r="G214">
-        <v>75007</v>
+        <v>76729</v>
       </c>
       <c r="H214">
         <v>27000</v>
@@ -9841,7 +9841,7 @@
         <v>0</v>
       </c>
       <c r="E215">
-        <v>87102</v>
+        <v>87683</v>
       </c>
       <c r="F215">
         <v>0</v>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>39200</v>
+        <v>0</v>
       </c>
       <c r="E216">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F216">
-        <v>66200</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>95328</v>
+        <v>0</v>
       </c>
       <c r="H216">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9930,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>101622</v>
+        <v>102299</v>
       </c>
       <c r="F217">
         <v>0</v>
@@ -9973,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="E218">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111136</v>
+        <v>0</v>
       </c>
       <c r="E219">
-        <v>130662</v>
+        <v>131533</v>
       </c>
       <c r="F219">
-        <v>126136</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>181636</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>59584</v>
+        <v>59365</v>
       </c>
       <c r="E220">
-        <v>81675</v>
+        <v>82220</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>74365</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>107086</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10108,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="E221">
-        <v>81675</v>
+        <v>82220</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -10149,16 +10149,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>68992</v>
+        <v>71103</v>
       </c>
       <c r="E222">
-        <v>96195</v>
+        <v>96836</v>
       </c>
       <c r="F222">
-        <v>83992</v>
+        <v>86103</v>
       </c>
       <c r="G222">
-        <v>120948</v>
+        <v>123988</v>
       </c>
       <c r="H222">
         <v>15000</v>
@@ -10198,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="E223">
-        <v>96195</v>
+        <v>96836</v>
       </c>
       <c r="F223">
         <v>0</v>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>16406</v>
       </c>
       <c r="E224">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F224">
-        <v>0</v>
+        <v>41445</v>
       </c>
       <c r="G224">
-        <v>0</v>
+        <v>59681</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>25039</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>9408</v>
+        <v>9844</v>
       </c>
       <c r="E225">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F225">
-        <v>33115</v>
+        <v>33445</v>
       </c>
       <c r="G225">
-        <v>47686</v>
+        <v>48161</v>
       </c>
       <c r="H225">
-        <v>23707</v>
+        <v>23601</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>37926</v>
+        <v>0</v>
       </c>
       <c r="E226">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F226">
-        <v>53833</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>77520</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>15907</v>
+        <v>0</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10378,7 +10378,7 @@
         <v>0</v>
       </c>
       <c r="E227">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>83747</v>
+        <v>0</v>
       </c>
       <c r="E228">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F228">
-        <v>98747</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>142196</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13343</v>
+        <v>0</v>
       </c>
       <c r="E229">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F229">
-        <v>40343</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>58094</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="E230">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         <v>0</v>
       </c>
       <c r="E231">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F231">
         <v>0</v>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>9335</v>
       </c>
       <c r="E232">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F232">
-        <v>0</v>
+        <v>34665</v>
       </c>
       <c r="G232">
-        <v>0</v>
+        <v>49918</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>25330</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10637,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="E233">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -10677,19 +10677,19 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>11864</v>
       </c>
       <c r="E234">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F234">
-        <v>0</v>
+        <v>38864</v>
       </c>
       <c r="G234">
-        <v>0</v>
+        <v>55964</v>
       </c>
       <c r="H234">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I234" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>15216</v>
       </c>
       <c r="E236">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F236">
-        <v>0</v>
+        <v>35930</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>51739</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>20714</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6272</v>
+        <v>0</v>
       </c>
       <c r="E237">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F237">
-        <v>29037</v>
+        <v>0</v>
       </c>
       <c r="G237">
-        <v>41813</v>
+        <v>0</v>
       </c>
       <c r="H237">
-        <v>22765</v>
+        <v>0</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10856,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="E238">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -10901,7 +10901,7 @@
         <v>0</v>
       </c>
       <c r="E239">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F239">
         <v>0</v>
@@ -10944,7 +10944,7 @@
         <v>0</v>
       </c>
       <c r="E240">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -10988,7 +10988,7 @@
         <v>0</v>
       </c>
       <c r="E241">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34057</v>
+        <v>28441</v>
       </c>
       <c r="E242">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F242">
-        <v>51476</v>
+        <v>49442</v>
       </c>
       <c r="G242">
-        <v>74125</v>
+        <v>71196</v>
       </c>
       <c r="H242">
-        <v>17419</v>
+        <v>21001</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="E243">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>9506</v>
       </c>
       <c r="E244">
-        <v>27225</v>
+        <v>27407</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>24689</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>35552</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15183</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11164,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="E245">
-        <v>27225</v>
+        <v>27407</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>11817</v>
       </c>
       <c r="E246">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>38817</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>55896</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59364</v>
+        <v>58876</v>
       </c>
       <c r="E248">
-        <v>96195</v>
+        <v>96836</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>73876</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>106381</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11340,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>96195</v>
+        <v>96836</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72128</v>
+        <v>68890</v>
       </c>
       <c r="E250">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F250">
-        <v>103724</v>
+        <v>83890</v>
       </c>
       <c r="G250">
-        <v>149363</v>
+        <v>120802</v>
       </c>
       <c r="H250">
-        <v>31596</v>
+        <v>15000</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>75183</v>
+        <v>0</v>
       </c>
       <c r="E251">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F251">
-        <v>90183</v>
+        <v>0</v>
       </c>
       <c r="G251">
-        <v>129864</v>
+        <v>0</v>
       </c>
       <c r="H251">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11472,7 +11472,7 @@
         <v>0</v>
       </c>
       <c r="E252">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F252">
         <v>0</v>
@@ -11518,7 +11518,7 @@
         <v>0</v>
       </c>
       <c r="E253">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F253">
         <v>0</v>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>23520</v>
+        <v>17577</v>
       </c>
       <c r="E254">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F254">
-        <v>47261</v>
+        <v>44577</v>
       </c>
       <c r="G254">
-        <v>68056</v>
+        <v>64191</v>
       </c>
       <c r="H254">
-        <v>23741</v>
+        <v>27000</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11607,7 +11607,7 @@
         <v>0</v>
       </c>
       <c r="E255">
-        <v>70785</v>
+        <v>71257</v>
       </c>
       <c r="F255">
         <v>0</v>
@@ -11650,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>52635</v>
+        <v>52986</v>
       </c>
       <c r="F257">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="E258">
-        <v>50802</v>
+        <v>51141</v>
       </c>
       <c r="F258">
         <v>0</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>10976</v>
+        <v>0</v>
       </c>
       <c r="E259">
-        <v>50802</v>
+        <v>51141</v>
       </c>
       <c r="F259">
-        <v>30203</v>
+        <v>0</v>
       </c>
       <c r="G259">
-        <v>43492</v>
+        <v>0</v>
       </c>
       <c r="H259">
-        <v>19227</v>
+        <v>0</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="E260">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>54880</v>
+        <v>62889</v>
       </c>
       <c r="E261">
-        <v>63507</v>
+        <v>63930</v>
       </c>
       <c r="F261">
-        <v>0</v>
+        <v>77889</v>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>112160</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="E262">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F262">
         <v>0</v>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>65856</v>
+        <v>75640</v>
       </c>
       <c r="E263">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>90640</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>130522</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39200</v>
+        <v>0</v>
       </c>
       <c r="E264">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F264">
-        <v>54712</v>
+        <v>0</v>
       </c>
       <c r="G264">
-        <v>78785</v>
+        <v>0</v>
       </c>
       <c r="H264">
-        <v>15512</v>
+        <v>0</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23520</v>
+        <v>0</v>
       </c>
       <c r="E265">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F265">
-        <v>38760</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>55814</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>15240</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="E266">
-        <v>67137</v>
+        <v>67584</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -12131,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>67137</v>
+        <v>67584</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>31360</v>
+        <v>34173</v>
       </c>
       <c r="E268">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F268">
-        <v>49375</v>
+        <v>49173</v>
       </c>
       <c r="G268">
-        <v>71100</v>
+        <v>70809</v>
       </c>
       <c r="H268">
-        <v>18015</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>20384</v>
+        <v>0</v>
       </c>
       <c r="E269">
-        <v>59877</v>
+        <v>60276</v>
       </c>
       <c r="F269">
-        <v>37506</v>
+        <v>0</v>
       </c>
       <c r="G269">
-        <v>54009</v>
+        <v>0</v>
       </c>
       <c r="H269">
-        <v>17122</v>
+        <v>0</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12263,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="E270">
-        <v>67137</v>
+        <v>67584</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -12308,7 +12308,7 @@
         <v>0</v>
       </c>
       <c r="E271">
-        <v>67137</v>
+        <v>67584</v>
       </c>
       <c r="F271">
         <v>0</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>62720</v>
+        <v>68839</v>
       </c>
       <c r="E272">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F272">
-        <v>85164</v>
+        <v>93929</v>
       </c>
       <c r="G272">
-        <v>122636</v>
+        <v>135258</v>
       </c>
       <c r="H272">
-        <v>22444</v>
+        <v>25090</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>18816</v>
+        <v>20402</v>
       </c>
       <c r="E273">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F273">
-        <v>45816</v>
+        <v>47402</v>
       </c>
       <c r="G273">
-        <v>65975</v>
+        <v>68259</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,10 +12438,10 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>57702</v>
+        <v>0</v>
       </c>
       <c r="E274">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F274">
         <v>0</v>
@@ -12481,19 +12481,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>10976</v>
+        <v>0</v>
       </c>
       <c r="E275">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F275">
-        <v>37976</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>54685</v>
+        <v>0</v>
       </c>
       <c r="H275">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12525,16 +12525,16 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152268</v>
+        <v>152244</v>
       </c>
       <c r="E276">
-        <v>163332</v>
+        <v>164421</v>
       </c>
       <c r="F276">
-        <v>167268</v>
+        <v>167244</v>
       </c>
       <c r="G276">
-        <v>240866</v>
+        <v>240831</v>
       </c>
       <c r="H276">
         <v>15000</v>
@@ -12572,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="E277">
-        <v>163332</v>
+        <v>164421</v>
       </c>
       <c r="F277">
         <v>0</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>43904</v>
+        <v>55527</v>
       </c>
       <c r="E278">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F278">
-        <v>75651</v>
+        <v>77534</v>
       </c>
       <c r="G278">
-        <v>108937</v>
+        <v>111649</v>
       </c>
       <c r="H278">
-        <v>31747</v>
+        <v>22007</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>42336</v>
+        <v>46448</v>
       </c>
       <c r="E279">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F279">
-        <v>65398</v>
+        <v>67326</v>
       </c>
       <c r="G279">
-        <v>94173</v>
+        <v>96949</v>
       </c>
       <c r="H279">
-        <v>23062</v>
+        <v>20878</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>59584</v>
+        <v>74348</v>
       </c>
       <c r="E280">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F280">
-        <v>94584</v>
+        <v>93285</v>
       </c>
       <c r="G280">
-        <v>136201</v>
+        <v>134330</v>
       </c>
       <c r="H280">
-        <v>35000</v>
+        <v>18937</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,10 +12747,10 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>92512</v>
+        <v>0</v>
       </c>
       <c r="E281">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F281">
         <v>0</v>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23755</v>
+        <v>23509</v>
       </c>
       <c r="E282">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F282">
-        <v>39996</v>
+        <v>40061</v>
       </c>
       <c r="G282">
-        <v>57594</v>
+        <v>57688</v>
       </c>
       <c r="H282">
-        <v>16241</v>
+        <v>16552</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="E283">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F283">
         <v>0</v>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>58016</v>
+        <v>43201</v>
       </c>
       <c r="E284">
-        <v>81675</v>
+        <v>82220</v>
       </c>
       <c r="F284">
-        <v>73016</v>
+        <v>60279</v>
       </c>
       <c r="G284">
-        <v>105143</v>
+        <v>86802</v>
       </c>
       <c r="H284">
-        <v>15000</v>
+        <v>17078</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="E285">
-        <v>81675</v>
+        <v>82220</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>38097</v>
+        <v>38351</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>17248</v>
+        <v>19977</v>
       </c>
       <c r="E287">
-        <v>38097</v>
+        <v>38351</v>
       </c>
       <c r="F287">
-        <v>32248</v>
+        <v>34977</v>
       </c>
       <c r="G287">
-        <v>46437</v>
+        <v>50367</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>29792</v>
+        <v>30461</v>
       </c>
       <c r="E288">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F288">
-        <v>48605</v>
+        <v>45461</v>
       </c>
       <c r="G288">
-        <v>69991</v>
+        <v>65464</v>
       </c>
       <c r="H288">
-        <v>18813</v>
+        <v>15000</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25605</v>
+        <v>0</v>
       </c>
       <c r="E289">
-        <v>58062</v>
+        <v>58449</v>
       </c>
       <c r="F289">
-        <v>40605</v>
+        <v>0</v>
       </c>
       <c r="G289">
-        <v>58471</v>
+        <v>0</v>
       </c>
       <c r="H289">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13143,19 +13143,19 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>10422</v>
       </c>
       <c r="E290">
-        <v>43542</v>
+        <v>43832</v>
       </c>
       <c r="F290">
-        <v>0</v>
+        <v>31095</v>
       </c>
       <c r="G290">
-        <v>0</v>
+        <v>44777</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>20673</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>39200</v>
+        <v>0</v>
       </c>
       <c r="E291">
-        <v>43542</v>
+        <v>43832</v>
       </c>
       <c r="F291">
-        <v>54200</v>
+        <v>0</v>
       </c>
       <c r="G291">
-        <v>78048</v>
+        <v>0</v>
       </c>
       <c r="H291">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43340</v>
+        <v>0</v>
       </c>
       <c r="E292">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F292">
-        <v>70340</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>101290</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13282,7 +13282,7 @@
         <v>0</v>
       </c>
       <c r="E293">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="E295">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54452</v>
+        <v>0</v>
       </c>
       <c r="E296">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F296">
-        <v>89452</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>128811</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>63291</v>
+        <v>0</v>
       </c>
       <c r="E297">
-        <v>72582</v>
+        <v>73066</v>
       </c>
       <c r="F297">
-        <v>78291</v>
+        <v>0</v>
       </c>
       <c r="G297">
-        <v>112739</v>
+        <v>0</v>
       </c>
       <c r="H297">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13501,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4782</v>
+        <v>0</v>
       </c>
       <c r="E299">
-        <v>54432</v>
+        <v>54795</v>
       </c>
       <c r="F299">
-        <v>29141</v>
+        <v>0</v>
       </c>
       <c r="G299">
-        <v>41963</v>
+        <v>0</v>
       </c>
       <c r="H299">
-        <v>24359</v>
+        <v>0</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>68952</v>
+        <v>69412</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -13628,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="E301">
-        <v>68952</v>
+        <v>69412</v>
       </c>
       <c r="F301">
         <v>0</v>
@@ -13668,19 +13668,19 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="E302">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F302">
-        <v>0</v>
+        <v>46200</v>
       </c>
       <c r="G302">
-        <v>0</v>
+        <v>66528</v>
       </c>
       <c r="H302">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I302" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659420/UNCHARTED_Coleccin_Legado_de_los_Ladrones/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13717,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="E303">
-        <v>90732</v>
+        <v>91337</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -13756,16 +13756,16 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>41427</v>
+        <v>45409</v>
       </c>
       <c r="E304">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F304">
-        <v>68427</v>
+        <v>72409</v>
       </c>
       <c r="G304">
-        <v>98535</v>
+        <v>104269</v>
       </c>
       <c r="H304">
         <v>27000</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="E305">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24320</v>
+        <v>23530</v>
       </c>
       <c r="E306">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F306">
-        <v>51320</v>
+        <v>50530</v>
       </c>
       <c r="G306">
-        <v>73901</v>
+        <v>72763</v>
       </c>
       <c r="H306">
         <v>27000</v>
@@ -13892,7 +13892,7 @@
         <v>0</v>
       </c>
       <c r="E307">
-        <v>108882</v>
+        <v>109608</v>
       </c>
       <c r="F307">
         <v>0</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>166208</v>
+        <v>179978</v>
       </c>
       <c r="E308">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F308">
-        <v>201208</v>
+        <v>194978</v>
       </c>
       <c r="G308">
-        <v>289740</v>
+        <v>280768</v>
       </c>
       <c r="H308">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>142155</v>
+        <v>0</v>
       </c>
       <c r="E309">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F309">
-        <v>157155</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>226303</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>66154</v>
+        <v>0</v>
       </c>
       <c r="E310">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F310">
-        <v>89626</v>
+        <v>0</v>
       </c>
       <c r="G310">
-        <v>129061</v>
+        <v>0</v>
       </c>
       <c r="H310">
-        <v>23472</v>
+        <v>0</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>53986</v>
+        <v>0</v>
       </c>
       <c r="E311">
-        <v>127032</v>
+        <v>127879</v>
       </c>
       <c r="F311">
-        <v>77137</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>111077</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>23151</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14110,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="E312">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F312">
         <v>0</v>
@@ -14152,7 +14152,7 @@
         <v>0</v>
       </c>
       <c r="E313">
-        <v>181482</v>
+        <v>182692</v>
       </c>
       <c r="F313">
         <v>0</v>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>124703</v>
+        <v>0</v>
       </c>
       <c r="E314">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F314">
-        <v>159703</v>
+        <v>0</v>
       </c>
       <c r="G314">
-        <v>229972</v>
+        <v>0</v>
       </c>
       <c r="H314">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,19 +14235,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>148254</v>
+        <v>0</v>
       </c>
       <c r="E315">
-        <v>235932</v>
+        <v>237505</v>
       </c>
       <c r="F315">
-        <v>163254</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>235086</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>67989</v>
+        <v>71993</v>
       </c>
       <c r="E2">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F2">
-        <v>82989</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>119504</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>44051</v>
+        <v>46652</v>
       </c>
       <c r="E3">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F3">
-        <v>59051</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>85033</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -571,19 +571,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>82325</v>
       </c>
       <c r="E4">
-        <v>84028</v>
+        <v>83472</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>97325</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>140148</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>62890</v>
       </c>
       <c r="E5">
-        <v>84028</v>
+        <v>83472</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>77890</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>112162</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -664,7 +664,7 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>3570</v>
+        <v>4268</v>
       </c>
       <c r="E7">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F7">
-        <v>28798</v>
+        <v>28936</v>
       </c>
       <c r="G7">
-        <v>41469</v>
+        <v>41668</v>
       </c>
       <c r="H7">
-        <v>25228</v>
+        <v>24668</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>33509</v>
+        <v>35973</v>
       </c>
       <c r="E8">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F8">
-        <v>52284</v>
+        <v>54437</v>
       </c>
       <c r="G8">
-        <v>75289</v>
+        <v>78389</v>
       </c>
       <c r="H8">
-        <v>18775</v>
+        <v>18464</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>30996</v>
       </c>
       <c r="E9">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>46705</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>67255</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15709</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -836,19 +836,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>53377</v>
       </c>
       <c r="E10">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>76348</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>109941</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>22971</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>41501</v>
       </c>
       <c r="E11">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>65064</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>93692</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>23563</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>81335</v>
+        <v>80750</v>
       </c>
       <c r="E12">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F12">
-        <v>96335</v>
+        <v>97099</v>
       </c>
       <c r="G12">
-        <v>138722</v>
+        <v>139823</v>
       </c>
       <c r="H12">
-        <v>15000</v>
+        <v>16349</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11017</v>
+        <v>11781</v>
       </c>
       <c r="E13">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F13">
-        <v>38017</v>
+        <v>38781</v>
       </c>
       <c r="G13">
-        <v>54744</v>
+        <v>55845</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>29651</v>
+        <v>44888</v>
       </c>
       <c r="E15">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F15">
-        <v>46356</v>
+        <v>59888</v>
       </c>
       <c r="G15">
-        <v>66753</v>
+        <v>86239</v>
       </c>
       <c r="H15">
-        <v>16705</v>
+        <v>15000</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -1145,7 +1145,7 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -1188,7 +1188,7 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -1230,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>33296</v>
       </c>
       <c r="E21">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>58951</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>84889</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>25655</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1362,7 +1362,7 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>53251</v>
       </c>
       <c r="E23">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>78258</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>112692</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>25007</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1450,7 +1450,7 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>160767</v>
+        <v>159702</v>
       </c>
       <c r="F24">
         <v>0</v>
@@ -1494,7 +1494,7 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>160767</v>
+        <v>159702</v>
       </c>
       <c r="F25">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="E26">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20436</v>
+        <v>20176</v>
       </c>
       <c r="E27">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F27">
-        <v>39107</v>
+        <v>38838</v>
       </c>
       <c r="G27">
-        <v>56314</v>
+        <v>55927</v>
       </c>
       <c r="H27">
-        <v>18671</v>
+        <v>18662</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>65966</v>
+        <v>74907</v>
       </c>
       <c r="E28">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F28">
-        <v>89932</v>
+        <v>94994</v>
       </c>
       <c r="G28">
-        <v>129502</v>
+        <v>136791</v>
       </c>
       <c r="H28">
-        <v>23966</v>
+        <v>20087</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>23887</v>
+        <v>28949</v>
       </c>
       <c r="E29">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F29">
-        <v>50887</v>
+        <v>55949</v>
       </c>
       <c r="G29">
-        <v>73277</v>
+        <v>80567</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131643</v>
+        <v>131056</v>
       </c>
       <c r="E30">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F30">
-        <v>146643</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>211166</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>57960</v>
       </c>
       <c r="E31">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>84960</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>122342</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>62975</v>
+        <v>72592</v>
       </c>
       <c r="E32">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F32">
-        <v>80514</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>115940</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>17539</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>48274</v>
       </c>
       <c r="E33">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>67773</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>97593</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>19499</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="E34">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>80199</v>
       </c>
       <c r="E35">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>95199</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>137087</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45275</v>
+        <v>45502</v>
       </c>
       <c r="E36">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F36">
-        <v>72275</v>
+        <v>72502</v>
       </c>
       <c r="G36">
-        <v>104076</v>
+        <v>104403</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>35894</v>
       </c>
       <c r="E37">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>62894</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>90567</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2068,19 +2068,19 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>64969</v>
       </c>
       <c r="E38">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>91969</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>132435</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I38" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>82136</v>
       </c>
       <c r="E39">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>109136</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>157156</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2156,19 +2156,19 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>84578</v>
       </c>
       <c r="E40">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>111578</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>160672</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I40" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>82136</v>
       </c>
       <c r="E41">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>109136</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>157156</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -2286,19 +2286,19 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>38918</v>
       </c>
       <c r="E43">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>65918</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>94922</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I43" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="E44">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>93634</v>
       </c>
       <c r="E45">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>114231</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>164493</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>20597</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="E46">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2457,19 +2457,19 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>25909</v>
       </c>
       <c r="E47">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>52909</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>76189</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I47" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/311210/Call_of_Duty_Black_Ops_III/","Abrir Steam")</f>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="E48">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F48">
         <v>0</v>
@@ -2546,7 +2546,7 @@
         <v>0</v>
       </c>
       <c r="E49">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F49">
         <v>0</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>34525</v>
+        <v>36209</v>
       </c>
       <c r="E50">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F50">
-        <v>49525</v>
+        <v>56217</v>
       </c>
       <c r="G50">
-        <v>71316</v>
+        <v>80952</v>
       </c>
       <c r="H50">
-        <v>15000</v>
+        <v>20008</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,10 +2633,10 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>33217</v>
       </c>
       <c r="E51">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -2677,19 +2677,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>49802</v>
       </c>
       <c r="E52">
-        <v>76720</v>
+        <v>76212</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>64802</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>93315</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>57346</v>
       </c>
       <c r="E53">
-        <v>76720</v>
+        <v>76212</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>72346</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>104178</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>46718</v>
+        <v>49124</v>
       </c>
       <c r="E54">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F54">
-        <v>81718</v>
+        <v>84124</v>
       </c>
       <c r="G54">
-        <v>117674</v>
+        <v>121139</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>49457</v>
+        <v>52369</v>
       </c>
       <c r="E55">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F55">
-        <v>75655</v>
+        <v>76490</v>
       </c>
       <c r="G55">
-        <v>108943</v>
+        <v>110146</v>
       </c>
       <c r="H55">
-        <v>26198</v>
+        <v>24121</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,19 +2857,19 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>53377</v>
       </c>
       <c r="E56">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>80377</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>115743</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I56" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>59471</v>
+        <v>62984</v>
       </c>
       <c r="E57">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F57">
-        <v>86471</v>
+        <v>87814</v>
       </c>
       <c r="G57">
-        <v>124518</v>
+        <v>126452</v>
       </c>
       <c r="H57">
-        <v>27000</v>
+        <v>24830</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>20351</v>
+        <v>23909</v>
       </c>
       <c r="E58">
-        <v>36524</v>
+        <v>36282</v>
       </c>
       <c r="F58">
-        <v>37056</v>
+        <v>38909</v>
       </c>
       <c r="G58">
-        <v>53361</v>
+        <v>56029</v>
       </c>
       <c r="H58">
-        <v>16705</v>
+        <v>15000</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>5900</v>
+        <v>6253</v>
       </c>
       <c r="E59">
-        <v>36524</v>
+        <v>36282</v>
       </c>
       <c r="F59">
-        <v>22605</v>
+        <v>22651</v>
       </c>
       <c r="G59">
-        <v>32551</v>
+        <v>32617</v>
       </c>
       <c r="H59">
-        <v>16705</v>
+        <v>16398</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>24499</v>
+        <v>26318</v>
       </c>
       <c r="E60">
-        <v>49313</v>
+        <v>48987</v>
       </c>
       <c r="F60">
-        <v>39499</v>
+        <v>48137</v>
       </c>
       <c r="G60">
-        <v>56879</v>
+        <v>69317</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>21819</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>25137</v>
       </c>
       <c r="E61">
-        <v>49313</v>
+        <v>48987</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40137</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>57797</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12190</v>
+        <v>12915</v>
       </c>
       <c r="E63">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F63">
-        <v>39190</v>
+        <v>39915</v>
       </c>
       <c r="G63">
-        <v>56434</v>
+        <v>57478</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="E64">
-        <v>123293</v>
+        <v>122476</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>29124</v>
+        <v>28019</v>
       </c>
       <c r="E65">
-        <v>123293</v>
+        <v>122476</v>
       </c>
       <c r="F65">
-        <v>56124</v>
+        <v>55019</v>
       </c>
       <c r="G65">
-        <v>80819</v>
+        <v>79227</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>25241</v>
+        <v>24255</v>
       </c>
       <c r="E66">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F66">
-        <v>53124</v>
+        <v>53601</v>
       </c>
       <c r="G66">
-        <v>76499</v>
+        <v>77185</v>
       </c>
       <c r="H66">
-        <v>27883</v>
+        <v>29346</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18124</v>
+        <v>18601</v>
       </c>
       <c r="E67">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F67">
-        <v>45124</v>
+        <v>45601</v>
       </c>
       <c r="G67">
-        <v>64979</v>
+        <v>65665</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>56879</v>
+        <v>34619</v>
       </c>
       <c r="E68">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F68">
-        <v>78075</v>
+        <v>62965</v>
       </c>
       <c r="G68">
-        <v>112428</v>
+        <v>90670</v>
       </c>
       <c r="H68">
-        <v>21196</v>
+        <v>28346</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>27752</v>
       </c>
       <c r="E69">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>54752</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>78843</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>109592</v>
+        <v>107809</v>
       </c>
       <c r="E70">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F70">
-        <v>124592</v>
+        <v>122809</v>
       </c>
       <c r="G70">
-        <v>179412</v>
+        <v>176845</v>
       </c>
       <c r="H70">
         <v>15000</v>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>51125</v>
       </c>
       <c r="E71">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>75993</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>109430</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>24868</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="E72">
-        <v>27388</v>
+        <v>27207</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5253</v>
+        <v>5576</v>
       </c>
       <c r="E73">
-        <v>27388</v>
+        <v>27207</v>
       </c>
       <c r="F73">
-        <v>20253</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>29164</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3652,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>95904</v>
+        <v>95269</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -3691,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>70970</v>
       </c>
       <c r="E75">
-        <v>95904</v>
+        <v>95269</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>85970</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>123797</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>80372</v>
       </c>
       <c r="E76">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>95372</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>137336</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,19 +3779,19 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>53657</v>
+        <v>47156</v>
       </c>
       <c r="E77">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F77">
-        <v>77335</v>
+        <v>74156</v>
       </c>
       <c r="G77">
-        <v>111362</v>
+        <v>106785</v>
       </c>
       <c r="H77">
-        <v>23678</v>
+        <v>27000</v>
       </c>
       <c r="I77" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3825,7 +3825,7 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -3870,7 +3870,7 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>37154</v>
       </c>
       <c r="E81">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F81">
-        <v>0</v>
+        <v>56247</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>80996</v>
       </c>
       <c r="H81">
-        <v>0</v>
+        <v>19093</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84158</v>
+        <v>84924</v>
       </c>
       <c r="E83">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F83">
-        <v>99158</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>142788</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48157</v>
+        <v>48526</v>
       </c>
       <c r="E84">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F84">
-        <v>71297</v>
+        <v>71141</v>
       </c>
       <c r="G84">
-        <v>102668</v>
+        <v>102443</v>
       </c>
       <c r="H84">
-        <v>23140</v>
+        <v>22615</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32388</v>
+        <v>32067</v>
       </c>
       <c r="E85">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F85">
-        <v>58852</v>
+        <v>58459</v>
       </c>
       <c r="G85">
-        <v>84747</v>
+        <v>84181</v>
       </c>
       <c r="H85">
-        <v>26464</v>
+        <v>26392</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>67763</v>
+        <v>151106</v>
       </c>
       <c r="E86">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F86">
-        <v>94763</v>
+        <v>166106</v>
       </c>
       <c r="G86">
-        <v>136459</v>
+        <v>239193</v>
       </c>
       <c r="H86">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,19 +4215,19 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>114518</v>
       </c>
       <c r="E87">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>129518</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>186506</v>
       </c>
       <c r="H87">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I87" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>160241</v>
       </c>
       <c r="E88">
-        <v>160767</v>
+        <v>159702</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>175241</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>252347</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>85552</v>
+        <v>127103</v>
       </c>
       <c r="E89">
-        <v>160767</v>
+        <v>159702</v>
       </c>
       <c r="F89">
-        <v>102920</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>148205</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>17368</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>7711</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F90">
-        <v>38060</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>54806</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>30349</v>
+        <v>0</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>3162</v>
+        <v>4284</v>
       </c>
       <c r="E91">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F91">
-        <v>30060</v>
+        <v>30358</v>
       </c>
       <c r="G91">
-        <v>43286</v>
+        <v>43716</v>
       </c>
       <c r="H91">
-        <v>26898</v>
+        <v>26074</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>27388</v>
+        <v>27207</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>11544</v>
+        <v>12206</v>
       </c>
       <c r="E93">
-        <v>27388</v>
+        <v>27207</v>
       </c>
       <c r="F93">
-        <v>26544</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>38223</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>34697</v>
+        <v>34467</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>34697</v>
+        <v>34467</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>56879</v>
+        <v>61897</v>
       </c>
       <c r="E96">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F96">
-        <v>72197</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>103964</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15318</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>31793</v>
+        <v>33674</v>
       </c>
       <c r="E97">
-        <v>82201</v>
+        <v>81657</v>
       </c>
       <c r="F97">
-        <v>50776</v>
+        <v>51316</v>
       </c>
       <c r="G97">
-        <v>73117</v>
+        <v>73895</v>
       </c>
       <c r="H97">
-        <v>18983</v>
+        <v>17642</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>72119</v>
+        <v>77380</v>
       </c>
       <c r="E98">
-        <v>94991</v>
+        <v>94362</v>
       </c>
       <c r="F98">
-        <v>87119</v>
+        <v>94111</v>
       </c>
       <c r="G98">
-        <v>125451</v>
+        <v>135520</v>
       </c>
       <c r="H98">
-        <v>15000</v>
+        <v>16731</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,16 +4744,16 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>58859</v>
+        <v>65851</v>
       </c>
       <c r="E99">
-        <v>94991</v>
+        <v>94362</v>
       </c>
       <c r="F99">
-        <v>73859</v>
+        <v>80851</v>
       </c>
       <c r="G99">
-        <v>106357</v>
+        <v>116425</v>
       </c>
       <c r="H99">
         <v>15000</v>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>57533</v>
+        <v>61630</v>
       </c>
       <c r="E100">
-        <v>106502</v>
+        <v>105796</v>
       </c>
       <c r="F100">
-        <v>76939</v>
+        <v>0</v>
       </c>
       <c r="G100">
-        <v>110792</v>
+        <v>0</v>
       </c>
       <c r="H100">
-        <v>19406</v>
+        <v>0</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,19 +4834,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>61819</v>
       </c>
       <c r="E101">
-        <v>106502</v>
+        <v>105796</v>
       </c>
       <c r="F101">
-        <v>0</v>
+        <v>76819</v>
       </c>
       <c r="G101">
-        <v>0</v>
+        <v>110619</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="E102">
-        <v>137014</v>
+        <v>136107</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -4924,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="E103">
-        <v>137014</v>
+        <v>136107</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -4967,7 +4967,7 @@
         <v>0</v>
       </c>
       <c r="E104">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>72907</v>
       </c>
       <c r="E105">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>87907</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>126586</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5052,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="E106">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>101304</v>
       </c>
       <c r="E107">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>117299</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>168911</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>15995</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3060</v>
+        <v>4001</v>
       </c>
       <c r="E109">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F109">
-        <v>30060</v>
+        <v>31001</v>
       </c>
       <c r="G109">
-        <v>43286</v>
+        <v>44641</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5223,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="E110">
-        <v>164421</v>
+        <v>163332</v>
       </c>
       <c r="F110">
         <v>0</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>13329</v>
+        <v>14128</v>
       </c>
       <c r="E111">
-        <v>164421</v>
+        <v>163332</v>
       </c>
       <c r="F111">
-        <v>40329</v>
+        <v>41128</v>
       </c>
       <c r="G111">
-        <v>58074</v>
+        <v>59224</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,16 +5307,16 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>82936</v>
+        <v>90925</v>
       </c>
       <c r="E112">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F112">
-        <v>97936</v>
+        <v>105925</v>
       </c>
       <c r="G112">
-        <v>141028</v>
+        <v>152532</v>
       </c>
       <c r="H112">
         <v>15000</v>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>46125</v>
+        <v>52857</v>
       </c>
       <c r="E113">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F113">
-        <v>61125</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>88020</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5396,19 +5396,19 @@
         <v>15</v>
       </c>
       <c r="D114">
-        <v>132685</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>116916</v>
+        <v>116142</v>
       </c>
       <c r="F114">
-        <v>147685</v>
+        <v>0</v>
       </c>
       <c r="G114">
-        <v>212666</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I114" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>85727</v>
       </c>
       <c r="E115">
-        <v>116916</v>
+        <v>116142</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>100727</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>145047</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>169061</v>
       </c>
       <c r="E116">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>184061</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>265048</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>114770</v>
       </c>
       <c r="E117">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>129770</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>186869</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>43521</v>
+        <v>44667</v>
       </c>
       <c r="E118">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F118">
-        <v>58521</v>
+        <v>60223</v>
       </c>
       <c r="G118">
-        <v>84270</v>
+        <v>86721</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>15556</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>31011</v>
+        <v>32713</v>
       </c>
       <c r="E119">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F119">
-        <v>46011</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>66256</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>65813</v>
+        <v>61236</v>
       </c>
       <c r="E120">
-        <v>80374</v>
+        <v>79842</v>
       </c>
       <c r="F120">
-        <v>80813</v>
+        <v>79575</v>
       </c>
       <c r="G120">
-        <v>116371</v>
+        <v>114588</v>
       </c>
       <c r="H120">
-        <v>15000</v>
+        <v>18339</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>54196</v>
       </c>
       <c r="E121">
-        <v>80374</v>
+        <v>79842</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>69196</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>99642</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>46809</v>
       </c>
       <c r="E122">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>67068</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>96578</v>
       </c>
       <c r="H122">
-        <v>0</v>
+        <v>20259</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>50988</v>
+        <v>42336</v>
       </c>
       <c r="E123">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F123">
-        <v>65988</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>95023</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,19 +5833,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13142</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>43832</v>
+        <v>43542</v>
       </c>
       <c r="F124">
-        <v>31095</v>
+        <v>0</v>
       </c>
       <c r="G124">
-        <v>44777</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>17953</v>
+        <v>0</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>7403</v>
       </c>
       <c r="E125">
-        <v>43832</v>
+        <v>43542</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>25942</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>37356</v>
       </c>
       <c r="H125">
-        <v>0</v>
+        <v>18539</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,19 +5923,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>30722</v>
+        <v>29894</v>
       </c>
       <c r="E126">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F126">
-        <v>45722</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>65840</v>
+        <v>0</v>
       </c>
       <c r="H126">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5972,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="E127">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -6015,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="E128">
-        <v>59892</v>
+        <v>59496</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>19943</v>
+        <v>20255</v>
       </c>
       <c r="E129">
-        <v>59892</v>
+        <v>59496</v>
       </c>
       <c r="F129">
-        <v>37335</v>
+        <v>37305</v>
       </c>
       <c r="G129">
-        <v>53762</v>
+        <v>53719</v>
       </c>
       <c r="H129">
-        <v>17392</v>
+        <v>17050</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6102,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="E130">
-        <v>74619</v>
+        <v>74125</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>30004</v>
       </c>
       <c r="E131">
-        <v>74619</v>
+        <v>74125</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>46910</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>67550</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>16906</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6188,7 +6188,7 @@
         <v>0</v>
       </c>
       <c r="E132">
-        <v>93931</v>
+        <v>93309</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>35805</v>
+        <v>33485</v>
       </c>
       <c r="E133">
-        <v>93931</v>
+        <v>93309</v>
       </c>
       <c r="F133">
-        <v>56955</v>
+        <v>55785</v>
       </c>
       <c r="G133">
-        <v>82015</v>
+        <v>80330</v>
       </c>
       <c r="H133">
-        <v>21150</v>
+        <v>22300</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6275,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="E134">
-        <v>89510</v>
+        <v>88917</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>50954</v>
+        <v>53550</v>
       </c>
       <c r="E135">
-        <v>89510</v>
+        <v>88917</v>
       </c>
       <c r="F135">
-        <v>65954</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>94974</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>69451</v>
+        <v>73490</v>
       </c>
       <c r="E137">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F137">
-        <v>84451</v>
+        <v>0</v>
       </c>
       <c r="G137">
-        <v>121609</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="E138">
-        <v>153458</v>
+        <v>152442</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>86657</v>
+        <v>91760</v>
       </c>
       <c r="E139">
-        <v>153458</v>
+        <v>152442</v>
       </c>
       <c r="F139">
-        <v>101657</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>146386</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>36009</v>
+        <v>37485</v>
       </c>
       <c r="E140">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F140">
-        <v>61505</v>
+        <v>61823</v>
       </c>
       <c r="G140">
-        <v>88567</v>
+        <v>89025</v>
       </c>
       <c r="H140">
-        <v>25496</v>
+        <v>24338</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="E141">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>23509</v>
+        <v>24948</v>
       </c>
       <c r="E142">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F142">
-        <v>50509</v>
+        <v>59948</v>
       </c>
       <c r="G142">
-        <v>72733</v>
+        <v>86325</v>
       </c>
       <c r="H142">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>27988</v>
       </c>
       <c r="E143">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>52581</v>
       </c>
       <c r="G143">
-        <v>0</v>
+        <v>75717</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>24593</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,19 +6706,19 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>43691</v>
       </c>
       <c r="E144">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>68049</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>97991</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>24358</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>65189</v>
       </c>
       <c r="E145">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>80189</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>115472</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>60512</v>
       </c>
       <c r="E146">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>75512</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>108737</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="E147">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F147">
         <v>0</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36558</v>
+        <v>36934</v>
       </c>
       <c r="E148">
-        <v>62103</v>
+        <v>61692</v>
       </c>
       <c r="F148">
-        <v>62297</v>
+        <v>64580</v>
       </c>
       <c r="G148">
-        <v>89708</v>
+        <v>92995</v>
       </c>
       <c r="H148">
-        <v>25739</v>
+        <v>27646</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>38730</v>
+        <v>41013</v>
       </c>
       <c r="E149">
-        <v>62103</v>
+        <v>61692</v>
       </c>
       <c r="F149">
-        <v>53730</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>77371</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6975,7 +6975,7 @@
         <v>0</v>
       </c>
       <c r="E150">
-        <v>82201</v>
+        <v>54432</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>14842</v>
+        <v>15435</v>
       </c>
       <c r="E151">
-        <v>82201</v>
+        <v>54432</v>
       </c>
       <c r="F151">
-        <v>41842</v>
+        <v>33403</v>
       </c>
       <c r="G151">
-        <v>60252</v>
+        <v>48100</v>
       </c>
       <c r="H151">
-        <v>27000</v>
+        <v>17968</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,19 +7058,19 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>35652</v>
+        <v>37595</v>
       </c>
       <c r="E152">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F152">
-        <v>54800</v>
+        <v>54437</v>
       </c>
       <c r="G152">
-        <v>78912</v>
+        <v>78389</v>
       </c>
       <c r="H152">
-        <v>19148</v>
+        <v>16842</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33425</v>
+        <v>33595</v>
       </c>
       <c r="E153">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F153">
-        <v>48425</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>69732</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>54728</v>
+        <v>56905</v>
       </c>
       <c r="E154">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F154">
-        <v>69728</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>100408</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>73458</v>
       </c>
       <c r="E155">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>88458</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>127380</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>32116</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>27388</v>
+        <v>59877</v>
       </c>
       <c r="F156">
-        <v>47116</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>67847</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>13244</v>
+        <v>11923</v>
       </c>
       <c r="E157">
-        <v>27388</v>
+        <v>59877</v>
       </c>
       <c r="F157">
-        <v>28244</v>
+        <v>34121</v>
       </c>
       <c r="G157">
-        <v>40671</v>
+        <v>49134</v>
       </c>
       <c r="H157">
-        <v>15000</v>
+        <v>22198</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="E158">
-        <v>84028</v>
+        <v>83472</v>
       </c>
       <c r="F158">
         <v>0</v>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>0</v>
+        <v>36131</v>
       </c>
       <c r="E159">
-        <v>84028</v>
+        <v>83472</v>
       </c>
       <c r="F159">
-        <v>0</v>
+        <v>53007</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>76330</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>16876</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>7836</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>54813</v>
+        <v>54450</v>
       </c>
       <c r="F160">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="H160">
-        <v>27164</v>
+        <v>0</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>8537</v>
       </c>
       <c r="E161">
-        <v>54813</v>
+        <v>54450</v>
       </c>
       <c r="F161">
-        <v>0</v>
+        <v>30651</v>
       </c>
       <c r="G161">
-        <v>0</v>
+        <v>44137</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>22114</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>10147</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F162">
-        <v>37147</v>
+        <v>0</v>
       </c>
       <c r="G162">
-        <v>53492</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,19 +7547,19 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>9639</v>
       </c>
       <c r="E163">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>36639</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>52760</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I163" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>65007</v>
+        <v>68339</v>
       </c>
       <c r="E164">
-        <v>68516</v>
+        <v>68063</v>
       </c>
       <c r="F164">
-        <v>80271</v>
+        <v>83339</v>
       </c>
       <c r="G164">
-        <v>115590</v>
+        <v>120008</v>
       </c>
       <c r="H164">
-        <v>15264</v>
+        <v>15000</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>20759</v>
+        <v>21987</v>
       </c>
       <c r="E165">
-        <v>68516</v>
+        <v>68063</v>
       </c>
       <c r="F165">
-        <v>41025</v>
+        <v>41339</v>
       </c>
       <c r="G165">
-        <v>59076</v>
+        <v>59528</v>
       </c>
       <c r="H165">
-        <v>20266</v>
+        <v>19352</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,16 +7679,16 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>87360</v>
+        <v>91807</v>
       </c>
       <c r="E166">
-        <v>103231</v>
+        <v>102548</v>
       </c>
       <c r="F166">
-        <v>102360</v>
+        <v>106807</v>
       </c>
       <c r="G166">
-        <v>147398</v>
+        <v>153802</v>
       </c>
       <c r="H166">
         <v>15000</v>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>38131</v>
       </c>
       <c r="E167">
-        <v>103231</v>
+        <v>102548</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>61246</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>88194</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>23115</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7766,19 +7766,19 @@
         <v>15</v>
       </c>
       <c r="D168">
-        <v>75504</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F168">
-        <v>94034</v>
+        <v>0</v>
       </c>
       <c r="G168">
-        <v>135409</v>
+        <v>0</v>
       </c>
       <c r="H168">
-        <v>18530</v>
+        <v>0</v>
       </c>
       <c r="I168" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7811,19 +7811,19 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>8930</v>
       </c>
       <c r="E169">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F169">
-        <v>0</v>
+        <v>35930</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>51739</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I169" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1426210/It_Takes_Two/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>56879</v>
+        <v>59677</v>
       </c>
       <c r="E170">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F170">
-        <v>78075</v>
+        <v>80475</v>
       </c>
       <c r="G170">
-        <v>112428</v>
+        <v>115884</v>
       </c>
       <c r="H170">
-        <v>21196</v>
+        <v>20798</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>53786</v>
       </c>
       <c r="E171">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>69978</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>100768</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>16192</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>75168</v>
+        <v>78892</v>
       </c>
       <c r="E172">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F172">
-        <v>101835</v>
+        <v>108413</v>
       </c>
       <c r="G172">
-        <v>146642</v>
+        <v>156115</v>
       </c>
       <c r="H172">
-        <v>26667</v>
+        <v>29521</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>79128</v>
       </c>
       <c r="E173">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>94272</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>135752</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>15144</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,19 +8033,19 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>46720</v>
+        <v>47691</v>
       </c>
       <c r="E174">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F174">
-        <v>68503</v>
+        <v>68049</v>
       </c>
       <c r="G174">
-        <v>98644</v>
+        <v>97991</v>
       </c>
       <c r="H174">
-        <v>21783</v>
+        <v>20358</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>75640</v>
+        <v>67851</v>
       </c>
       <c r="E175">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F175">
-        <v>90640</v>
+        <v>0</v>
       </c>
       <c r="G175">
-        <v>130522</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>56241</v>
+        <v>65662</v>
       </c>
       <c r="E176">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F176">
-        <v>71241</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>102587</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>28444</v>
+        <v>26476</v>
       </c>
       <c r="E178">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F178">
-        <v>55444</v>
+        <v>53476</v>
       </c>
       <c r="G178">
-        <v>79839</v>
+        <v>77005</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8258,7 +8258,7 @@
         <v>0</v>
       </c>
       <c r="E179">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>24907</v>
+        <v>26271</v>
       </c>
       <c r="E180">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F180">
-        <v>51907</v>
+        <v>53271</v>
       </c>
       <c r="G180">
-        <v>74746</v>
+        <v>76710</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8347,7 +8347,7 @@
         <v>0</v>
       </c>
       <c r="E181">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>82280</v>
+        <v>100784</v>
       </c>
       <c r="E182">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F182">
-        <v>97622</v>
+        <v>115784</v>
       </c>
       <c r="G182">
-        <v>140576</v>
+        <v>166729</v>
       </c>
       <c r="H182">
-        <v>15342</v>
+        <v>15000</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>61682</v>
+        <v>64559</v>
       </c>
       <c r="E183">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F183">
-        <v>80545</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>115985</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>18863</v>
+        <v>0</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>111745</v>
+        <v>144884</v>
       </c>
       <c r="E184">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F184">
-        <v>137019</v>
+        <v>179884</v>
       </c>
       <c r="G184">
-        <v>197307</v>
+        <v>259033</v>
       </c>
       <c r="H184">
-        <v>25274</v>
+        <v>35000</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8517,16 +8517,16 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>176867</v>
+        <v>196182</v>
       </c>
       <c r="E185">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F185">
-        <v>191867</v>
+        <v>211182</v>
       </c>
       <c r="G185">
-        <v>276288</v>
+        <v>304102</v>
       </c>
       <c r="H185">
         <v>15000</v>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>140195</v>
+        <v>188984</v>
       </c>
       <c r="E186">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F186">
-        <v>167195</v>
+        <v>203984</v>
       </c>
       <c r="G186">
-        <v>240761</v>
+        <v>293737</v>
       </c>
       <c r="H186">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,16 +8604,16 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>176867</v>
+        <v>196182</v>
       </c>
       <c r="E187">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F187">
-        <v>191867</v>
+        <v>211182</v>
       </c>
       <c r="G187">
-        <v>276288</v>
+        <v>304102</v>
       </c>
       <c r="H187">
         <v>15000</v>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>218431</v>
+        <v>291359</v>
       </c>
       <c r="E188">
-        <v>365402</v>
+        <v>362982</v>
       </c>
       <c r="F188">
-        <v>245431</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>353421</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8691,19 +8691,19 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>0</v>
+        <v>308417</v>
       </c>
       <c r="E189">
-        <v>365402</v>
+        <v>362982</v>
       </c>
       <c r="F189">
-        <v>0</v>
+        <v>323417</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>465720</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I189" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>30627</v>
+        <v>29705</v>
       </c>
       <c r="E190">
-        <v>95904</v>
+        <v>95269</v>
       </c>
       <c r="F190">
-        <v>65627</v>
+        <v>64705</v>
       </c>
       <c r="G190">
-        <v>94503</v>
+        <v>93175</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>37760</v>
+        <v>44746</v>
       </c>
       <c r="E191">
-        <v>95904</v>
+        <v>95269</v>
       </c>
       <c r="F191">
-        <v>58507</v>
+        <v>61053</v>
       </c>
       <c r="G191">
-        <v>84250</v>
+        <v>87916</v>
       </c>
       <c r="H191">
-        <v>20747</v>
+        <v>16307</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41897</v>
+        <v>42588</v>
       </c>
       <c r="E192">
-        <v>123311</v>
+        <v>122494</v>
       </c>
       <c r="F192">
-        <v>68897</v>
+        <v>77588</v>
       </c>
       <c r="G192">
-        <v>99212</v>
+        <v>111727</v>
       </c>
       <c r="H192">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8868,19 +8868,19 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>146680</v>
       </c>
       <c r="E193">
-        <v>123311</v>
+        <v>122494</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>161680</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>232819</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I193" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>52091</v>
+        <v>53771</v>
       </c>
       <c r="E194">
-        <v>150900</v>
+        <v>149901</v>
       </c>
       <c r="F194">
-        <v>79091</v>
+        <v>80771</v>
       </c>
       <c r="G194">
-        <v>113891</v>
+        <v>116310</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8955,19 +8955,19 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>146680</v>
       </c>
       <c r="E195">
-        <v>123311</v>
+        <v>122494</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>161680</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>232819</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I195" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>12597</v>
+        <v>23987</v>
       </c>
       <c r="E196">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F196">
-        <v>39597</v>
+        <v>54437</v>
       </c>
       <c r="G196">
-        <v>57020</v>
+        <v>78389</v>
       </c>
       <c r="H196">
-        <v>27000</v>
+        <v>30450</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>32618</v>
       </c>
       <c r="E197">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>47618</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>68570</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>21230</v>
+        <v>26602</v>
       </c>
       <c r="E198">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F198">
-        <v>48230</v>
+        <v>53602</v>
       </c>
       <c r="G198">
-        <v>69451</v>
+        <v>77187</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9136,7 +9136,7 @@
         <v>0</v>
       </c>
       <c r="E199">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>13176</v>
+        <v>126016</v>
       </c>
       <c r="E200">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F200">
-        <v>40176</v>
+        <v>141016</v>
       </c>
       <c r="G200">
-        <v>57853</v>
+        <v>203063</v>
       </c>
       <c r="H200">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,19 +9222,19 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>11954</v>
       </c>
       <c r="E201">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>38954</v>
       </c>
       <c r="G201">
-        <v>0</v>
+        <v>56094</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I201" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9266,19 +9266,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>21317</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F202">
-        <v>56317</v>
+        <v>0</v>
       </c>
       <c r="G202">
-        <v>81096</v>
+        <v>0</v>
       </c>
       <c r="H202">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>27883</v>
+        <v>22790</v>
       </c>
       <c r="E203">
-        <v>146150</v>
+        <v>145182</v>
       </c>
       <c r="F203">
-        <v>54883</v>
+        <v>49790</v>
       </c>
       <c r="G203">
-        <v>79032</v>
+        <v>71698</v>
       </c>
       <c r="H203">
         <v>27000</v>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>26397</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F204">
-        <v>53397</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>76892</v>
+        <v>0</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>26492</v>
       </c>
       <c r="E205">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>53492</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>77028</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>15766</v>
+        <v>24192</v>
       </c>
       <c r="E206">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F206">
-        <v>38609</v>
+        <v>42232</v>
       </c>
       <c r="G206">
-        <v>55597</v>
+        <v>60814</v>
       </c>
       <c r="H206">
-        <v>22843</v>
+        <v>18040</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>0</v>
+        <v>13970</v>
       </c>
       <c r="E207">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>34232</v>
       </c>
       <c r="G207">
-        <v>0</v>
+        <v>49294</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>20262</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9538,7 +9538,7 @@
         <v>0</v>
       </c>
       <c r="E208">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -9578,19 +9578,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>23105</v>
       </c>
       <c r="E209">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F209">
-        <v>0</v>
+        <v>38105</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>54871</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="E210">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>40556</v>
       </c>
       <c r="E211">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>64686</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>93148</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>24130</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9710,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="E212">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F212">
         <v>0</v>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>0</v>
+        <v>83963</v>
       </c>
       <c r="E213">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>110363</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>158923</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>26400</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>26284</v>
+        <v>28697</v>
       </c>
       <c r="E214">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F214">
-        <v>53284</v>
+        <v>60532</v>
       </c>
       <c r="G214">
-        <v>76729</v>
+        <v>87166</v>
       </c>
       <c r="H214">
-        <v>27000</v>
+        <v>31835</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>31406</v>
       </c>
       <c r="E215">
-        <v>87683</v>
+        <v>87102</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>52532</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>75646</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>21126</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>45833</v>
       </c>
       <c r="E216">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>76217</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>109752</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>30384</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>89570</v>
       </c>
       <c r="E217">
-        <v>102299</v>
+        <v>101622</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>104570</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>150581</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9973,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="E218">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>111636</v>
       </c>
       <c r="E219">
-        <v>131533</v>
+        <v>130662</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>126636</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>182356</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,16 +10059,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>59365</v>
+        <v>62669</v>
       </c>
       <c r="E220">
-        <v>82220</v>
+        <v>81675</v>
       </c>
       <c r="F220">
-        <v>74365</v>
+        <v>77669</v>
       </c>
       <c r="G220">
-        <v>107086</v>
+        <v>111843</v>
       </c>
       <c r="H220">
         <v>15000</v>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>52164</v>
       </c>
       <c r="E221">
-        <v>82220</v>
+        <v>81675</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>67164</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>96716</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>71103</v>
+        <v>74639</v>
       </c>
       <c r="E222">
-        <v>96836</v>
+        <v>96195</v>
       </c>
       <c r="F222">
-        <v>86103</v>
+        <v>0</v>
       </c>
       <c r="G222">
-        <v>123988</v>
+        <v>0</v>
       </c>
       <c r="H222">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>85601</v>
       </c>
       <c r="E223">
-        <v>96836</v>
+        <v>96195</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>100601</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>144865</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16406</v>
+        <v>0</v>
       </c>
       <c r="E224">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F224">
-        <v>41445</v>
+        <v>0</v>
       </c>
       <c r="G224">
-        <v>59681</v>
+        <v>0</v>
       </c>
       <c r="H224">
-        <v>25039</v>
+        <v>0</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>9844</v>
+        <v>10411</v>
       </c>
       <c r="E225">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F225">
-        <v>33445</v>
+        <v>33516</v>
       </c>
       <c r="G225">
-        <v>48161</v>
+        <v>48263</v>
       </c>
       <c r="H225">
-        <v>23601</v>
+        <v>23105</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>38099</v>
       </c>
       <c r="E226">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>53902</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>77619</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>15803</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>23531</v>
       </c>
       <c r="E227">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>43719</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>62955</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>20188</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>84121</v>
       </c>
       <c r="E228">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>99121</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>142734</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10464,7 +10464,7 @@
         <v>0</v>
       </c>
       <c r="E229">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F229">
         <v>0</v>
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="E230">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>19310</v>
       </c>
       <c r="E231">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>46310</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>66686</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9335</v>
+        <v>0</v>
       </c>
       <c r="E232">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F232">
-        <v>34665</v>
+        <v>0</v>
       </c>
       <c r="G232">
-        <v>49918</v>
+        <v>0</v>
       </c>
       <c r="H232">
-        <v>25330</v>
+        <v>0</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>10033</v>
       </c>
       <c r="E233">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>30541</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>43979</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>20508</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,19 +10677,19 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>11864</v>
+        <v>24617</v>
       </c>
       <c r="E234">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F234">
-        <v>38864</v>
+        <v>47700</v>
       </c>
       <c r="G234">
-        <v>55964</v>
+        <v>68688</v>
       </c>
       <c r="H234">
-        <v>27000</v>
+        <v>23083</v>
       </c>
       <c r="I234" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10725,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F235">
         <v>0</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>15216</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F236">
-        <v>35930</v>
+        <v>0</v>
       </c>
       <c r="G236">
-        <v>51739</v>
+        <v>0</v>
       </c>
       <c r="H236">
-        <v>20714</v>
+        <v>0</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>0</v>
+        <v>6883</v>
       </c>
       <c r="E237">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F237">
-        <v>0</v>
+        <v>29281</v>
       </c>
       <c r="G237">
-        <v>0</v>
+        <v>42165</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>22398</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10856,7 +10856,7 @@
         <v>0</v>
       </c>
       <c r="E238">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F238">
         <v>0</v>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>11435</v>
       </c>
       <c r="E239">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>31102</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>44787</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>19667</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>24350</v>
       </c>
       <c r="E240">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>53089</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>76448</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>28739</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>73253</v>
       </c>
       <c r="E241">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>88253</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>127084</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>28441</v>
+        <v>34209</v>
       </c>
       <c r="E242">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F242">
-        <v>49442</v>
+        <v>51537</v>
       </c>
       <c r="G242">
-        <v>71196</v>
+        <v>74213</v>
       </c>
       <c r="H242">
-        <v>21001</v>
+        <v>17328</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11076,7 +11076,7 @@
         <v>0</v>
       </c>
       <c r="E243">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9506</v>
+        <v>24082</v>
       </c>
       <c r="E244">
-        <v>27407</v>
+        <v>27225</v>
       </c>
       <c r="F244">
-        <v>24689</v>
+        <v>39082</v>
       </c>
       <c r="G244">
-        <v>35552</v>
+        <v>56278</v>
       </c>
       <c r="H244">
-        <v>15183</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11164,7 +11164,7 @@
         <v>0</v>
       </c>
       <c r="E245">
-        <v>27407</v>
+        <v>27225</v>
       </c>
       <c r="F245">
         <v>0</v>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11817</v>
+        <v>49518</v>
       </c>
       <c r="E246">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F246">
-        <v>38817</v>
+        <v>74804</v>
       </c>
       <c r="G246">
-        <v>55896</v>
+        <v>107718</v>
       </c>
       <c r="H246">
-        <v>27000</v>
+        <v>25286</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="E247">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F247">
         <v>0</v>
@@ -11291,16 +11291,16 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>58876</v>
+        <v>59078</v>
       </c>
       <c r="E248">
-        <v>96836</v>
+        <v>96195</v>
       </c>
       <c r="F248">
-        <v>73876</v>
+        <v>74078</v>
       </c>
       <c r="G248">
-        <v>106381</v>
+        <v>106672</v>
       </c>
       <c r="H248">
         <v>15000</v>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>48715</v>
       </c>
       <c r="E249">
-        <v>96836</v>
+        <v>96195</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>63715</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>91750</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>68890</v>
+        <v>72182</v>
       </c>
       <c r="E250">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F250">
-        <v>83890</v>
+        <v>104227</v>
       </c>
       <c r="G250">
-        <v>120802</v>
+        <v>150087</v>
       </c>
       <c r="H250">
-        <v>15000</v>
+        <v>32045</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>75632</v>
       </c>
       <c r="E251">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>90632</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>130510</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>36383</v>
       </c>
       <c r="E252">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>61970</v>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>89237</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>25587</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>38887</v>
       </c>
       <c r="E253">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>53887</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>77597</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>17577</v>
+        <v>27216</v>
       </c>
       <c r="E254">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F254">
-        <v>44577</v>
+        <v>53089</v>
       </c>
       <c r="G254">
-        <v>64191</v>
+        <v>76448</v>
       </c>
       <c r="H254">
-        <v>27000</v>
+        <v>25873</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>70103</v>
       </c>
       <c r="E255">
-        <v>71257</v>
+        <v>70785</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>85103</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>122548</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11650,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="E256">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -11695,7 +11695,7 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>52986</v>
+        <v>52635</v>
       </c>
       <c r="F257">
         <v>0</v>
@@ -11737,7 +11737,7 @@
         <v>0</v>
       </c>
       <c r="E258">
-        <v>51141</v>
+        <v>50802</v>
       </c>
       <c r="F258">
         <v>0</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>12553</v>
       </c>
       <c r="E259">
-        <v>51141</v>
+        <v>50802</v>
       </c>
       <c r="F259">
-        <v>0</v>
+        <v>30834</v>
       </c>
       <c r="G259">
-        <v>0</v>
+        <v>44401</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>18281</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11823,7 +11823,7 @@
         <v>0</v>
       </c>
       <c r="E260">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F260">
         <v>0</v>
@@ -11862,16 +11862,16 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62889</v>
+        <v>62638</v>
       </c>
       <c r="E261">
-        <v>63930</v>
+        <v>63507</v>
       </c>
       <c r="F261">
-        <v>77889</v>
+        <v>77638</v>
       </c>
       <c r="G261">
-        <v>112160</v>
+        <v>111799</v>
       </c>
       <c r="H261">
         <v>15000</v>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="E262">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F262">
         <v>0</v>
@@ -11948,16 +11948,16 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75640</v>
+        <v>75348</v>
       </c>
       <c r="E263">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F263">
-        <v>90640</v>
+        <v>90348</v>
       </c>
       <c r="G263">
-        <v>130522</v>
+        <v>130101</v>
       </c>
       <c r="H263">
         <v>15000</v>
@@ -11992,10 +11992,10 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>39895</v>
       </c>
       <c r="E264">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F264">
         <v>0</v>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>23625</v>
       </c>
       <c r="E265">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>38802</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>55875</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>15177</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="E266">
-        <v>67584</v>
+        <v>67137</v>
       </c>
       <c r="F266">
         <v>0</v>
@@ -12131,7 +12131,7 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>67584</v>
+        <v>67137</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34173</v>
+        <v>34965</v>
       </c>
       <c r="E268">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F268">
-        <v>49173</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>70809</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,10 +12216,10 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>23263</v>
       </c>
       <c r="E269">
-        <v>60276</v>
+        <v>59877</v>
       </c>
       <c r="F269">
         <v>0</v>
@@ -12263,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="E270">
-        <v>67584</v>
+        <v>67137</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>29327</v>
       </c>
       <c r="E271">
-        <v>67584</v>
+        <v>67137</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>44327</v>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>63831</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>68839</v>
+        <v>71395</v>
       </c>
       <c r="E272">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F272">
-        <v>93929</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>135258</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>25090</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>20402</v>
+        <v>21278</v>
       </c>
       <c r="E273">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F273">
-        <v>47402</v>
+        <v>48278</v>
       </c>
       <c r="G273">
-        <v>68259</v>
+        <v>69520</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>57960</v>
       </c>
       <c r="E274">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>84960</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>122342</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,19 +12481,19 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>12222</v>
       </c>
       <c r="E275">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F275">
-        <v>0</v>
+        <v>39222</v>
       </c>
       <c r="G275">
-        <v>0</v>
+        <v>56480</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I275" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152244</v>
+        <v>152917</v>
       </c>
       <c r="E276">
-        <v>164421</v>
+        <v>163332</v>
       </c>
       <c r="F276">
-        <v>167244</v>
+        <v>0</v>
       </c>
       <c r="G276">
-        <v>240831</v>
+        <v>0</v>
       </c>
       <c r="H276">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>102627</v>
       </c>
       <c r="E277">
-        <v>164421</v>
+        <v>163332</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>117627</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>169383</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>55527</v>
+        <v>49219</v>
       </c>
       <c r="E278">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F278">
-        <v>77534</v>
+        <v>78360</v>
       </c>
       <c r="G278">
-        <v>111649</v>
+        <v>112838</v>
       </c>
       <c r="H278">
-        <v>22007</v>
+        <v>29141</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>46448</v>
+        <v>49187</v>
       </c>
       <c r="E279">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F279">
-        <v>67326</v>
+        <v>68139</v>
       </c>
       <c r="G279">
-        <v>96949</v>
+        <v>98120</v>
       </c>
       <c r="H279">
-        <v>20878</v>
+        <v>18952</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,19 +12701,19 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>74348</v>
+        <v>63929</v>
       </c>
       <c r="E280">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F280">
-        <v>93285</v>
+        <v>95274</v>
       </c>
       <c r="G280">
-        <v>134330</v>
+        <v>137195</v>
       </c>
       <c r="H280">
-        <v>18937</v>
+        <v>31345</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>77506</v>
       </c>
       <c r="E281">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>92506</v>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>133209</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23509</v>
+        <v>24208</v>
       </c>
       <c r="E282">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F282">
-        <v>40061</v>
+        <v>40824</v>
       </c>
       <c r="G282">
-        <v>57688</v>
+        <v>58787</v>
       </c>
       <c r="H282">
-        <v>16552</v>
+        <v>16616</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>24838</v>
       </c>
       <c r="E283">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>39838</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>57367</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>43201</v>
+        <v>65174</v>
       </c>
       <c r="E284">
-        <v>82220</v>
+        <v>81675</v>
       </c>
       <c r="F284">
-        <v>60279</v>
+        <v>0</v>
       </c>
       <c r="G284">
-        <v>86802</v>
+        <v>0</v>
       </c>
       <c r="H284">
-        <v>17078</v>
+        <v>0</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="E285">
-        <v>82220</v>
+        <v>81675</v>
       </c>
       <c r="F285">
         <v>0</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
       <c r="E286">
-        <v>38351</v>
+        <v>38097</v>
       </c>
       <c r="F286">
         <v>0</v>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>19977</v>
+        <v>20412</v>
       </c>
       <c r="E287">
-        <v>38351</v>
+        <v>38097</v>
       </c>
       <c r="F287">
-        <v>34977</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>50367</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>30461</v>
+        <v>31957</v>
       </c>
       <c r="E288">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F288">
-        <v>45461</v>
+        <v>48720</v>
       </c>
       <c r="G288">
-        <v>65464</v>
+        <v>70157</v>
       </c>
       <c r="H288">
-        <v>15000</v>
+        <v>16763</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>25720</v>
       </c>
       <c r="E289">
-        <v>58449</v>
+        <v>58062</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>40720</v>
       </c>
       <c r="G289">
-        <v>0</v>
+        <v>58637</v>
       </c>
       <c r="H289">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13143,19 +13143,19 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>10422</v>
+        <v>0</v>
       </c>
       <c r="E290">
-        <v>43832</v>
+        <v>43542</v>
       </c>
       <c r="F290">
-        <v>31095</v>
+        <v>0</v>
       </c>
       <c r="G290">
-        <v>44777</v>
+        <v>0</v>
       </c>
       <c r="H290">
-        <v>20673</v>
+        <v>0</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>34351</v>
       </c>
       <c r="E291">
-        <v>43832</v>
+        <v>43542</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>49351</v>
       </c>
       <c r="G291">
-        <v>0</v>
+        <v>71065</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>0</v>
+        <v>43517</v>
       </c>
       <c r="E292">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>73324</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>105587</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>29807</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>38241</v>
       </c>
       <c r="E293">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>63760</v>
       </c>
       <c r="G293">
-        <v>0</v>
+        <v>91814</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>25519</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13325,7 +13325,7 @@
         <v>0</v>
       </c>
       <c r="E294">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -13370,7 +13370,7 @@
         <v>0</v>
       </c>
       <c r="E295">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>54133</v>
       </c>
       <c r="E296">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>89133</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>128352</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>64843</v>
       </c>
       <c r="E297">
-        <v>73066</v>
+        <v>72582</v>
       </c>
       <c r="F297">
-        <v>0</v>
+        <v>79843</v>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>114974</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13501,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="E298">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>4804</v>
       </c>
       <c r="E299">
-        <v>54795</v>
+        <v>54432</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>29150</v>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>41976</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>24346</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13586,7 +13586,7 @@
         <v>0</v>
       </c>
       <c r="E300">
-        <v>69412</v>
+        <v>68952</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>10820</v>
       </c>
       <c r="E301">
-        <v>69412</v>
+        <v>68952</v>
       </c>
       <c r="F301">
-        <v>0</v>
+        <v>37219</v>
       </c>
       <c r="G301">
-        <v>0</v>
+        <v>53595</v>
       </c>
       <c r="H301">
-        <v>0</v>
+        <v>26399</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>19200</v>
+        <v>23893</v>
       </c>
       <c r="E302">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F302">
-        <v>46200</v>
+        <v>50893</v>
       </c>
       <c r="G302">
-        <v>66528</v>
+        <v>73286</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13717,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="E303">
-        <v>91337</v>
+        <v>90732</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>45409</v>
+        <v>38997</v>
       </c>
       <c r="E304">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F304">
-        <v>72409</v>
+        <v>73997</v>
       </c>
       <c r="G304">
-        <v>104269</v>
+        <v>106556</v>
       </c>
       <c r="H304">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>45911</v>
       </c>
       <c r="E305">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>66828</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>96232</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>20917</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>23530</v>
+        <v>24428</v>
       </c>
       <c r="E306">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F306">
-        <v>50530</v>
+        <v>59428</v>
       </c>
       <c r="G306">
-        <v>72763</v>
+        <v>85576</v>
       </c>
       <c r="H306">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>33626</v>
       </c>
       <c r="E307">
-        <v>109608</v>
+        <v>108882</v>
       </c>
       <c r="F307">
-        <v>0</v>
+        <v>60626</v>
       </c>
       <c r="G307">
-        <v>0</v>
+        <v>87301</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,16 +13932,16 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>179978</v>
+        <v>185283</v>
       </c>
       <c r="E308">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F308">
-        <v>194978</v>
+        <v>200283</v>
       </c>
       <c r="G308">
-        <v>280768</v>
+        <v>288408</v>
       </c>
       <c r="H308">
         <v>15000</v>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>142790</v>
       </c>
       <c r="E309">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>157790</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>227218</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>66134</v>
       </c>
       <c r="E310">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F310">
-        <v>0</v>
+        <v>89618</v>
       </c>
       <c r="G310">
-        <v>0</v>
+        <v>129050</v>
       </c>
       <c r="H310">
-        <v>0</v>
+        <v>23484</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14067,7 +14067,7 @@
         <v>0</v>
       </c>
       <c r="E311">
-        <v>127879</v>
+        <v>127032</v>
       </c>
       <c r="F311">
         <v>0</v>
@@ -14110,7 +14110,7 @@
         <v>0</v>
       </c>
       <c r="E312">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F312">
         <v>0</v>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>111447</v>
       </c>
       <c r="E313">
-        <v>182692</v>
+        <v>181482</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>126447</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>182084</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14195,7 +14195,7 @@
         <v>0</v>
       </c>
       <c r="E314">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F314">
         <v>0</v>
@@ -14235,19 +14235,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>148916</v>
       </c>
       <c r="E315">
-        <v>237505</v>
+        <v>235932</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>163916</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>236039</v>
       </c>
       <c r="H315">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>71993</v>
+        <v>72102</v>
       </c>
       <c r="E2">
         <v>72582</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>87102</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125427</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46652</v>
+        <v>46713</v>
       </c>
       <c r="E3">
         <v>72582</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>61713</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88867</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -571,19 +571,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>82325</v>
+        <v>82378</v>
       </c>
       <c r="E4">
         <v>83472</v>
       </c>
       <c r="F4">
-        <v>97325</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>140148</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>62890</v>
+        <v>84773</v>
       </c>
       <c r="E5">
         <v>83472</v>
       </c>
       <c r="F5">
-        <v>77890</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>112162</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4268</v>
+        <v>4271</v>
       </c>
       <c r="E7">
         <v>54432</v>
       </c>
       <c r="F7">
-        <v>28936</v>
+        <v>28937</v>
       </c>
       <c r="G7">
-        <v>41668</v>
+        <v>41669</v>
       </c>
       <c r="H7">
-        <v>24668</v>
+        <v>24666</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>35973</v>
+        <v>36027</v>
       </c>
       <c r="E8">
         <v>72582</v>
       </c>
       <c r="F8">
-        <v>54437</v>
+        <v>53073</v>
       </c>
       <c r="G8">
-        <v>78389</v>
+        <v>76425</v>
       </c>
       <c r="H8">
-        <v>18464</v>
+        <v>17046</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>30996</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>72582</v>
       </c>
       <c r="F9">
-        <v>46705</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>67255</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>15709</v>
+        <v>0</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -836,19 +836,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>53377</v>
+        <v>53411</v>
       </c>
       <c r="E10">
         <v>108882</v>
       </c>
       <c r="F10">
-        <v>76348</v>
+        <v>76362</v>
       </c>
       <c r="G10">
-        <v>109941</v>
+        <v>109961</v>
       </c>
       <c r="H10">
-        <v>22971</v>
+        <v>22951</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -882,19 +882,19 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>41501</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>108882</v>
       </c>
       <c r="F11">
-        <v>65064</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>93692</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>23563</v>
+        <v>0</v>
       </c>
       <c r="I11" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>80750</v>
+        <v>79036</v>
       </c>
       <c r="E12">
         <v>81657</v>
       </c>
       <c r="F12">
-        <v>97099</v>
+        <v>97106</v>
       </c>
       <c r="G12">
-        <v>139823</v>
+        <v>139833</v>
       </c>
       <c r="H12">
-        <v>16349</v>
+        <v>18070</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11781</v>
+        <v>11788</v>
       </c>
       <c r="E13">
         <v>81657</v>
       </c>
       <c r="F13">
-        <v>38781</v>
+        <v>38788</v>
       </c>
       <c r="G13">
-        <v>55845</v>
+        <v>55855</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>44888</v>
+        <v>44948</v>
       </c>
       <c r="E15">
         <v>72582</v>
       </c>
       <c r="F15">
-        <v>59888</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>86239</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>33296</v>
+        <v>34341</v>
       </c>
       <c r="E21">
         <v>101622</v>
       </c>
       <c r="F21">
-        <v>58951</v>
+        <v>59369</v>
       </c>
       <c r="G21">
-        <v>84889</v>
+        <v>85491</v>
       </c>
       <c r="H21">
-        <v>25655</v>
+        <v>25028</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1404,19 +1404,19 @@
         <v>17</v>
       </c>
       <c r="D23">
-        <v>53251</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>130662</v>
       </c>
       <c r="F23">
-        <v>78258</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>112692</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>25007</v>
+        <v>0</v>
       </c>
       <c r="I23" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20176</v>
+        <v>20204</v>
       </c>
       <c r="E27">
         <v>63507</v>
       </c>
       <c r="F27">
-        <v>38838</v>
+        <v>38850</v>
       </c>
       <c r="G27">
-        <v>55927</v>
+        <v>55944</v>
       </c>
       <c r="H27">
-        <v>18662</v>
+        <v>18646</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74907</v>
+        <v>75018</v>
       </c>
       <c r="E28">
         <v>127032</v>
       </c>
       <c r="F28">
-        <v>94994</v>
+        <v>95043</v>
       </c>
       <c r="G28">
-        <v>136791</v>
+        <v>136862</v>
       </c>
       <c r="H28">
-        <v>20087</v>
+        <v>20025</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>28949</v>
+        <v>28998</v>
       </c>
       <c r="E29">
         <v>127032</v>
       </c>
       <c r="F29">
-        <v>55949</v>
+        <v>55998</v>
       </c>
       <c r="G29">
-        <v>80567</v>
+        <v>80637</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131056</v>
+        <v>131328</v>
       </c>
       <c r="E30">
         <v>181482</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>146328</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>210712</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>57960</v>
+        <v>70258</v>
       </c>
       <c r="E31">
         <v>181482</v>
       </c>
       <c r="F31">
-        <v>84960</v>
+        <v>0</v>
       </c>
       <c r="G31">
-        <v>122342</v>
+        <v>0</v>
       </c>
       <c r="H31">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72592</v>
+        <v>81353</v>
       </c>
       <c r="E32">
         <v>108882</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>96353</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>138748</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>48274</v>
+        <v>47910</v>
       </c>
       <c r="E33">
         <v>108882</v>
       </c>
       <c r="F33">
-        <v>67773</v>
+        <v>67628</v>
       </c>
       <c r="G33">
-        <v>97593</v>
+        <v>97384</v>
       </c>
       <c r="H33">
-        <v>19499</v>
+        <v>19718</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,16 +1935,16 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80199</v>
+        <v>80171</v>
       </c>
       <c r="E35">
         <v>127032</v>
       </c>
       <c r="F35">
-        <v>95199</v>
+        <v>95171</v>
       </c>
       <c r="G35">
-        <v>137087</v>
+        <v>137046</v>
       </c>
       <c r="H35">
         <v>15000</v>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45502</v>
+        <v>44112</v>
       </c>
       <c r="E36">
         <v>127032</v>
       </c>
       <c r="F36">
-        <v>72502</v>
+        <v>71112</v>
       </c>
       <c r="G36">
-        <v>104403</v>
+        <v>102401</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2025,19 +2025,19 @@
         <v>17</v>
       </c>
       <c r="D37">
-        <v>35894</v>
+        <v>0</v>
       </c>
       <c r="E37">
         <v>127032</v>
       </c>
       <c r="F37">
-        <v>62894</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>90567</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I37" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>64969</v>
+        <v>64837</v>
       </c>
       <c r="E38">
         <v>235932</v>
       </c>
       <c r="F38">
-        <v>91969</v>
+        <v>91837</v>
       </c>
       <c r="G38">
-        <v>132435</v>
+        <v>132245</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2113,19 +2113,19 @@
         <v>17</v>
       </c>
       <c r="D39">
-        <v>82136</v>
+        <v>0</v>
       </c>
       <c r="E39">
         <v>235932</v>
       </c>
       <c r="F39">
-        <v>109136</v>
+        <v>0</v>
       </c>
       <c r="G39">
-        <v>157156</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I39" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2156,16 +2156,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>84578</v>
+        <v>84284</v>
       </c>
       <c r="E40">
         <v>235932</v>
       </c>
       <c r="F40">
-        <v>111578</v>
+        <v>111284</v>
       </c>
       <c r="G40">
-        <v>160672</v>
+        <v>160249</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2201,19 +2201,19 @@
         <v>17</v>
       </c>
       <c r="D41">
-        <v>82136</v>
+        <v>0</v>
       </c>
       <c r="E41">
         <v>235932</v>
       </c>
       <c r="F41">
-        <v>109136</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>157156</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I41" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1285190/Borderlands_4/","Abrir Steam")</f>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38918</v>
+        <v>38974</v>
       </c>
       <c r="E43">
         <v>127032</v>
       </c>
       <c r="F43">
-        <v>65918</v>
+        <v>65974</v>
       </c>
       <c r="G43">
-        <v>94922</v>
+        <v>95003</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2372,19 +2372,19 @@
         <v>17</v>
       </c>
       <c r="D45">
-        <v>93634</v>
+        <v>0</v>
       </c>
       <c r="E45">
         <v>181482</v>
       </c>
       <c r="F45">
-        <v>114231</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>164493</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>20597</v>
+        <v>0</v>
       </c>
       <c r="I45" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3606480/Call_of_Duty_Black_Ops_7/","Abrir Steam")</f>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>25909</v>
+        <v>27627</v>
       </c>
       <c r="E47">
         <v>108882</v>
       </c>
       <c r="F47">
-        <v>52909</v>
+        <v>54627</v>
       </c>
       <c r="G47">
-        <v>76189</v>
+        <v>78663</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36209</v>
+        <v>36232</v>
       </c>
       <c r="E50">
         <v>63507</v>
       </c>
       <c r="F50">
-        <v>56217</v>
+        <v>55655</v>
       </c>
       <c r="G50">
-        <v>80952</v>
+        <v>80143</v>
       </c>
       <c r="H50">
-        <v>20008</v>
+        <v>19423</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>33217</v>
+        <v>32655</v>
       </c>
       <c r="E51">
         <v>63507</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>47655</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>68623</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2677,16 +2677,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>49802</v>
+        <v>49691</v>
       </c>
       <c r="E52">
         <v>76212</v>
       </c>
       <c r="F52">
-        <v>64802</v>
+        <v>64691</v>
       </c>
       <c r="G52">
-        <v>93315</v>
+        <v>93155</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2723,16 +2723,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>57346</v>
+        <v>57225</v>
       </c>
       <c r="E53">
         <v>76212</v>
       </c>
       <c r="F53">
-        <v>72346</v>
+        <v>72225</v>
       </c>
       <c r="G53">
-        <v>104178</v>
+        <v>104004</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2767,16 +2767,16 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49124</v>
+        <v>49155</v>
       </c>
       <c r="E54">
         <v>127032</v>
       </c>
       <c r="F54">
-        <v>84124</v>
+        <v>84155</v>
       </c>
       <c r="G54">
-        <v>121139</v>
+        <v>121183</v>
       </c>
       <c r="H54">
         <v>35000</v>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52369</v>
+        <v>52449</v>
       </c>
       <c r="E55">
         <v>127032</v>
       </c>
       <c r="F55">
-        <v>76490</v>
+        <v>76522</v>
       </c>
       <c r="G55">
-        <v>110146</v>
+        <v>110192</v>
       </c>
       <c r="H55">
-        <v>24121</v>
+        <v>24073</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,16 +2857,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53377</v>
+        <v>53411</v>
       </c>
       <c r="E56">
         <v>145182</v>
       </c>
       <c r="F56">
-        <v>80377</v>
+        <v>80411</v>
       </c>
       <c r="G56">
-        <v>115743</v>
+        <v>115792</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>62984</v>
+        <v>63072</v>
       </c>
       <c r="E57">
         <v>145182</v>
       </c>
       <c r="F57">
-        <v>87814</v>
+        <v>87850</v>
       </c>
       <c r="G57">
-        <v>126452</v>
+        <v>126504</v>
       </c>
       <c r="H57">
-        <v>24830</v>
+        <v>24778</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23909</v>
+        <v>24696</v>
       </c>
       <c r="E58">
         <v>36282</v>
       </c>
       <c r="F58">
-        <v>38909</v>
+        <v>0</v>
       </c>
       <c r="G58">
-        <v>56029</v>
+        <v>0</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6253</v>
+        <v>6257</v>
       </c>
       <c r="E59">
         <v>36282</v>
       </c>
       <c r="F59">
-        <v>22651</v>
+        <v>22653</v>
       </c>
       <c r="G59">
-        <v>32617</v>
+        <v>32620</v>
       </c>
       <c r="H59">
-        <v>16398</v>
+        <v>16396</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26318</v>
+        <v>26366</v>
       </c>
       <c r="E60">
         <v>48987</v>
       </c>
       <c r="F60">
-        <v>48137</v>
+        <v>48090</v>
       </c>
       <c r="G60">
-        <v>69317</v>
+        <v>69250</v>
       </c>
       <c r="H60">
-        <v>21819</v>
+        <v>21724</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,16 +3081,16 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25137</v>
+        <v>25090</v>
       </c>
       <c r="E61">
         <v>48987</v>
       </c>
       <c r="F61">
-        <v>40137</v>
+        <v>40090</v>
       </c>
       <c r="G61">
-        <v>57797</v>
+        <v>57730</v>
       </c>
       <c r="H61">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12915</v>
+        <v>13822</v>
       </c>
       <c r="E63">
         <v>81657</v>
       </c>
       <c r="F63">
-        <v>39915</v>
+        <v>40822</v>
       </c>
       <c r="G63">
-        <v>57478</v>
+        <v>58784</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>28019</v>
+        <v>27911</v>
       </c>
       <c r="E65">
         <v>122476</v>
       </c>
       <c r="F65">
-        <v>55019</v>
+        <v>54911</v>
       </c>
       <c r="G65">
-        <v>79227</v>
+        <v>79072</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24255</v>
+        <v>24144</v>
       </c>
       <c r="E66">
         <v>90732</v>
       </c>
       <c r="F66">
-        <v>53601</v>
+        <v>53534</v>
       </c>
       <c r="G66">
-        <v>77185</v>
+        <v>77089</v>
       </c>
       <c r="H66">
-        <v>29346</v>
+        <v>29390</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18601</v>
+        <v>18534</v>
       </c>
       <c r="E67">
         <v>90732</v>
       </c>
       <c r="F67">
-        <v>45601</v>
+        <v>45534</v>
       </c>
       <c r="G67">
-        <v>65665</v>
+        <v>65569</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34619</v>
+        <v>34640</v>
       </c>
       <c r="E68">
         <v>108882</v>
       </c>
       <c r="F68">
-        <v>62965</v>
+        <v>62919</v>
       </c>
       <c r="G68">
-        <v>90670</v>
+        <v>90603</v>
       </c>
       <c r="H68">
-        <v>28346</v>
+        <v>28279</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27752</v>
+        <v>27706</v>
       </c>
       <c r="E69">
         <v>108882</v>
       </c>
       <c r="F69">
-        <v>54752</v>
+        <v>54706</v>
       </c>
       <c r="G69">
-        <v>78843</v>
+        <v>78777</v>
       </c>
       <c r="H69">
         <v>27000</v>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>107809</v>
+        <v>107861</v>
       </c>
       <c r="E70">
         <v>127032</v>
       </c>
       <c r="F70">
-        <v>122809</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>176845</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3518,19 +3518,19 @@
         <v>17</v>
       </c>
       <c r="D71">
-        <v>51125</v>
+        <v>0</v>
       </c>
       <c r="E71">
         <v>127032</v>
       </c>
       <c r="F71">
-        <v>75993</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>109430</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>24868</v>
+        <v>0</v>
       </c>
       <c r="I71" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5576</v>
+        <v>5863</v>
       </c>
       <c r="E73">
         <v>27207</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>20863</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>30043</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3691,19 +3691,19 @@
         <v>17</v>
       </c>
       <c r="D75">
-        <v>70970</v>
+        <v>0</v>
       </c>
       <c r="E75">
         <v>95269</v>
       </c>
       <c r="F75">
-        <v>85970</v>
+        <v>0</v>
       </c>
       <c r="G75">
-        <v>123797</v>
+        <v>0</v>
       </c>
       <c r="H75">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I75" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>80372</v>
+        <v>86113</v>
       </c>
       <c r="E76">
         <v>127032</v>
       </c>
       <c r="F76">
-        <v>95372</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>137336</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47156</v>
+        <v>47217</v>
       </c>
       <c r="E77">
         <v>127032</v>
       </c>
       <c r="F77">
-        <v>74156</v>
+        <v>74217</v>
       </c>
       <c r="G77">
-        <v>106785</v>
+        <v>106872</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37154</v>
+        <v>37209</v>
       </c>
       <c r="E81">
         <v>90732</v>
       </c>
       <c r="F81">
-        <v>56247</v>
+        <v>56269</v>
       </c>
       <c r="G81">
-        <v>80996</v>
+        <v>81027</v>
       </c>
       <c r="H81">
-        <v>19093</v>
+        <v>19060</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>84924</v>
+        <v>85041</v>
       </c>
       <c r="E83">
         <v>127032</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>100041</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>144059</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48526</v>
+        <v>48557</v>
       </c>
       <c r="E84">
         <v>101622</v>
       </c>
       <c r="F84">
-        <v>71141</v>
+        <v>71156</v>
       </c>
       <c r="G84">
-        <v>102443</v>
+        <v>102465</v>
       </c>
       <c r="H84">
-        <v>22615</v>
+        <v>22599</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32067</v>
+        <v>32103</v>
       </c>
       <c r="E85">
         <v>101622</v>
       </c>
       <c r="F85">
-        <v>58459</v>
+        <v>58474</v>
       </c>
       <c r="G85">
-        <v>84181</v>
+        <v>84203</v>
       </c>
       <c r="H85">
-        <v>26392</v>
+        <v>26371</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>151106</v>
+        <v>151485</v>
       </c>
       <c r="E86">
         <v>145182</v>
       </c>
       <c r="F86">
-        <v>166106</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>239193</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4215,19 +4215,19 @@
         <v>17</v>
       </c>
       <c r="D87">
-        <v>114518</v>
+        <v>0</v>
       </c>
       <c r="E87">
         <v>145182</v>
       </c>
       <c r="F87">
-        <v>129518</v>
+        <v>0</v>
       </c>
       <c r="G87">
-        <v>186506</v>
+        <v>0</v>
       </c>
       <c r="H87">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I87" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>160241</v>
+        <v>171091</v>
       </c>
       <c r="E88">
         <v>159702</v>
       </c>
       <c r="F88">
-        <v>175241</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>252347</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127103</v>
+        <v>127294</v>
       </c>
       <c r="E89">
         <v>159702</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>142294</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>204903</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4284</v>
+        <v>4287</v>
       </c>
       <c r="E91">
         <v>58062</v>
       </c>
       <c r="F91">
-        <v>30358</v>
+        <v>30359</v>
       </c>
       <c r="G91">
-        <v>43716</v>
+        <v>43717</v>
       </c>
       <c r="H91">
-        <v>26074</v>
+        <v>26072</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12206</v>
+        <v>12230</v>
       </c>
       <c r="E93">
         <v>27207</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>39211</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61897</v>
+        <v>61984</v>
       </c>
       <c r="E96">
         <v>81657</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>76984</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>110857</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33674</v>
+        <v>33711</v>
       </c>
       <c r="E97">
         <v>81657</v>
       </c>
       <c r="F97">
-        <v>51316</v>
+        <v>51331</v>
       </c>
       <c r="G97">
-        <v>73895</v>
+        <v>73917</v>
       </c>
       <c r="H97">
-        <v>17642</v>
+        <v>17620</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>77380</v>
+        <v>77350</v>
       </c>
       <c r="E98">
         <v>94362</v>
       </c>
       <c r="F98">
-        <v>94111</v>
+        <v>96737</v>
       </c>
       <c r="G98">
-        <v>135520</v>
+        <v>139301</v>
       </c>
       <c r="H98">
-        <v>16731</v>
+        <v>19387</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>65851</v>
+        <v>68477</v>
       </c>
       <c r="E99">
         <v>94362</v>
       </c>
       <c r="F99">
-        <v>80851</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>116425</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61630</v>
+        <v>61716</v>
       </c>
       <c r="E100">
         <v>105796</v>
       </c>
       <c r="F100">
-        <v>0</v>
+        <v>78295</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>112745</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>16579</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -4834,19 +4834,19 @@
         <v>17</v>
       </c>
       <c r="D101">
-        <v>61819</v>
+        <v>0</v>
       </c>
       <c r="E101">
         <v>105796</v>
       </c>
       <c r="F101">
-        <v>76819</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>110619</v>
+        <v>0</v>
       </c>
       <c r="H101">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I101" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5006,16 +5006,16 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>72907</v>
+        <v>72748</v>
       </c>
       <c r="E105">
         <v>127032</v>
       </c>
       <c r="F105">
-        <v>87907</v>
+        <v>87748</v>
       </c>
       <c r="G105">
-        <v>126586</v>
+        <v>126357</v>
       </c>
       <c r="H105">
         <v>15000</v>
@@ -5091,19 +5091,19 @@
         <v>17</v>
       </c>
       <c r="D107">
-        <v>101304</v>
+        <v>0</v>
       </c>
       <c r="E107">
         <v>181482</v>
       </c>
       <c r="F107">
-        <v>117299</v>
+        <v>0</v>
       </c>
       <c r="G107">
-        <v>168911</v>
+        <v>0</v>
       </c>
       <c r="H107">
-        <v>15995</v>
+        <v>0</v>
       </c>
       <c r="I107" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4001</v>
+        <v>4003</v>
       </c>
       <c r="E109">
         <v>127032</v>
       </c>
       <c r="F109">
-        <v>31001</v>
+        <v>31003</v>
       </c>
       <c r="G109">
-        <v>44641</v>
+        <v>44644</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14128</v>
+        <v>14152</v>
       </c>
       <c r="E111">
         <v>163332</v>
       </c>
       <c r="F111">
-        <v>41128</v>
+        <v>41152</v>
       </c>
       <c r="G111">
-        <v>59224</v>
+        <v>59259</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>90925</v>
+        <v>91093</v>
       </c>
       <c r="E112">
         <v>87102</v>
       </c>
       <c r="F112">
-        <v>105925</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>152532</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>52857</v>
+        <v>53442</v>
       </c>
       <c r="E113">
         <v>87102</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>68442</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>98556</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,16 +5439,16 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85727</v>
+        <v>85545</v>
       </c>
       <c r="E115">
         <v>116142</v>
       </c>
       <c r="F115">
-        <v>100727</v>
+        <v>100545</v>
       </c>
       <c r="G115">
-        <v>145047</v>
+        <v>144785</v>
       </c>
       <c r="H115">
         <v>15000</v>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>169061</v>
+        <v>169152</v>
       </c>
       <c r="E116">
         <v>145182</v>
       </c>
       <c r="F116">
-        <v>184061</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>265048</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>114770</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>145182</v>
       </c>
       <c r="F117">
-        <v>129770</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>186869</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>44667</v>
+        <v>44475</v>
       </c>
       <c r="E118">
         <v>58062</v>
       </c>
       <c r="F118">
-        <v>60223</v>
+        <v>59475</v>
       </c>
       <c r="G118">
-        <v>86721</v>
+        <v>85644</v>
       </c>
       <c r="H118">
-        <v>15556</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>32713</v>
+        <v>32182</v>
       </c>
       <c r="E119">
         <v>58062</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>47182</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>67942</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>61236</v>
+        <v>61275</v>
       </c>
       <c r="E120">
         <v>79842</v>
       </c>
       <c r="F120">
-        <v>79575</v>
+        <v>79452</v>
       </c>
       <c r="G120">
-        <v>114588</v>
+        <v>114411</v>
       </c>
       <c r="H120">
-        <v>18339</v>
+        <v>18177</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,16 +5703,16 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>54196</v>
+        <v>54073</v>
       </c>
       <c r="E121">
         <v>79842</v>
       </c>
       <c r="F121">
-        <v>69196</v>
+        <v>69073</v>
       </c>
       <c r="G121">
-        <v>99642</v>
+        <v>99465</v>
       </c>
       <c r="H121">
         <v>15000</v>
@@ -5746,19 +5746,19 @@
         <v>15</v>
       </c>
       <c r="D122">
-        <v>46809</v>
+        <v>0</v>
       </c>
       <c r="E122">
         <v>90732</v>
       </c>
       <c r="F122">
-        <v>67068</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>96578</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>20259</v>
+        <v>0</v>
       </c>
       <c r="I122" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>42336</v>
+        <v>42253</v>
       </c>
       <c r="E123">
         <v>90732</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>58287</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>83933</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>16034</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7403</v>
+        <v>7391</v>
       </c>
       <c r="E125">
         <v>43542</v>
       </c>
       <c r="F125">
-        <v>25942</v>
+        <v>25938</v>
       </c>
       <c r="G125">
-        <v>37356</v>
+        <v>37351</v>
       </c>
       <c r="H125">
-        <v>18539</v>
+        <v>18547</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,19 +5923,19 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>29894</v>
+        <v>31646</v>
       </c>
       <c r="E126">
         <v>58062</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>46646</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>67170</v>
       </c>
       <c r="H126">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I126" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1462040/FINAL_FANTASY_VII_REMAKE_INTERGRADE/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20255</v>
+        <v>20283</v>
       </c>
       <c r="E129">
         <v>59496</v>
       </c>
       <c r="F129">
-        <v>37305</v>
+        <v>37316</v>
       </c>
       <c r="G129">
-        <v>53719</v>
+        <v>53735</v>
       </c>
       <c r="H129">
-        <v>17050</v>
+        <v>17033</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>30004</v>
+        <v>36358</v>
       </c>
       <c r="E131">
         <v>74125</v>
       </c>
       <c r="F131">
-        <v>46910</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>67550</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>16906</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>33485</v>
+        <v>37840</v>
       </c>
       <c r="E133">
         <v>93309</v>
       </c>
       <c r="F133">
-        <v>55785</v>
+        <v>57527</v>
       </c>
       <c r="G133">
-        <v>80330</v>
+        <v>82839</v>
       </c>
       <c r="H133">
-        <v>22300</v>
+        <v>19687</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53550</v>
+        <v>53616</v>
       </c>
       <c r="E135">
         <v>88917</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>68616</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>98807</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>73490</v>
+        <v>73599</v>
       </c>
       <c r="E137">
         <v>127032</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>88599</v>
       </c>
       <c r="G137">
-        <v>0</v>
+        <v>127583</v>
       </c>
       <c r="H137">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91760</v>
+        <v>91897</v>
       </c>
       <c r="E139">
         <v>152442</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>106897</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>153932</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37485</v>
+        <v>37540</v>
       </c>
       <c r="E140">
         <v>90732</v>
       </c>
       <c r="F140">
-        <v>61823</v>
+        <v>61845</v>
       </c>
       <c r="G140">
-        <v>89025</v>
+        <v>89057</v>
       </c>
       <c r="H140">
-        <v>24338</v>
+        <v>24305</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>24948</v>
+        <v>24995</v>
       </c>
       <c r="E142">
         <v>90732</v>
       </c>
       <c r="F142">
-        <v>59948</v>
+        <v>56749</v>
       </c>
       <c r="G142">
-        <v>86325</v>
+        <v>81719</v>
       </c>
       <c r="H142">
-        <v>35000</v>
+        <v>31754</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>27988</v>
+        <v>21749</v>
       </c>
       <c r="E143">
         <v>90732</v>
       </c>
       <c r="F143">
-        <v>52581</v>
+        <v>48749</v>
       </c>
       <c r="G143">
-        <v>75717</v>
+        <v>70199</v>
       </c>
       <c r="H143">
-        <v>24593</v>
+        <v>27000</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>43691</v>
+        <v>43750</v>
       </c>
       <c r="E144">
         <v>90732</v>
@@ -6718,7 +6718,7 @@
         <v>97991</v>
       </c>
       <c r="H144">
-        <v>24358</v>
+        <v>24299</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>65189</v>
+        <v>65278</v>
       </c>
       <c r="E145">
         <v>90732</v>
       </c>
       <c r="F145">
-        <v>80189</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>115472</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>60512</v>
+        <v>66759</v>
       </c>
       <c r="E146">
         <v>90732</v>
       </c>
       <c r="F146">
-        <v>75512</v>
+        <v>0</v>
       </c>
       <c r="G146">
-        <v>108737</v>
+        <v>0</v>
       </c>
       <c r="H146">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36934</v>
+        <v>36957</v>
       </c>
       <c r="E148">
         <v>61692</v>
       </c>
       <c r="F148">
-        <v>64580</v>
+        <v>64482</v>
       </c>
       <c r="G148">
-        <v>92995</v>
+        <v>92854</v>
       </c>
       <c r="H148">
-        <v>27646</v>
+        <v>27525</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>41013</v>
+        <v>41071</v>
       </c>
       <c r="E149">
         <v>61692</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>56071</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>80742</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15435</v>
+        <v>15413</v>
       </c>
       <c r="E151">
         <v>54432</v>
       </c>
       <c r="F151">
-        <v>33403</v>
+        <v>33394</v>
       </c>
       <c r="G151">
-        <v>48100</v>
+        <v>48087</v>
       </c>
       <c r="H151">
-        <v>17968</v>
+        <v>17981</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37595</v>
+        <v>37651</v>
       </c>
       <c r="E152">
         <v>72582</v>
@@ -7070,7 +7070,7 @@
         <v>78389</v>
       </c>
       <c r="H152">
-        <v>16842</v>
+        <v>16786</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33595</v>
+        <v>35444</v>
       </c>
       <c r="E153">
         <v>72582</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>50444</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>72639</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56905</v>
+        <v>56941</v>
       </c>
       <c r="E154">
         <v>72582</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>71941</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>103595</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>73458</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>72582</v>
       </c>
       <c r="F155">
-        <v>88458</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>127380</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>35428</v>
       </c>
       <c r="E156">
         <v>59877</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>50428</v>
       </c>
       <c r="G156">
-        <v>0</v>
+        <v>72616</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11923</v>
+        <v>11883</v>
       </c>
       <c r="E157">
         <v>59877</v>
       </c>
       <c r="F157">
-        <v>34121</v>
+        <v>34105</v>
       </c>
       <c r="G157">
-        <v>49134</v>
+        <v>49111</v>
       </c>
       <c r="H157">
-        <v>22198</v>
+        <v>22222</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36131</v>
+        <v>36185</v>
       </c>
       <c r="E159">
         <v>83472</v>
       </c>
       <c r="F159">
-        <v>53007</v>
+        <v>53028</v>
       </c>
       <c r="G159">
-        <v>76330</v>
+        <v>76360</v>
       </c>
       <c r="H159">
-        <v>16876</v>
+        <v>16843</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8537</v>
+        <v>8526</v>
       </c>
       <c r="E161">
         <v>54450</v>
       </c>
       <c r="F161">
-        <v>30651</v>
+        <v>30646</v>
       </c>
       <c r="G161">
-        <v>44137</v>
+        <v>44130</v>
       </c>
       <c r="H161">
-        <v>22114</v>
+        <v>22120</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9639</v>
+        <v>9629</v>
       </c>
       <c r="E163">
         <v>72582</v>
       </c>
       <c r="F163">
-        <v>36639</v>
+        <v>36629</v>
       </c>
       <c r="G163">
-        <v>52760</v>
+        <v>52746</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>68339</v>
+        <v>68383</v>
       </c>
       <c r="E164">
         <v>68063</v>
       </c>
       <c r="F164">
-        <v>83339</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>120008</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>21987</v>
+        <v>22017</v>
       </c>
       <c r="E165">
         <v>68063</v>
       </c>
       <c r="F165">
-        <v>41339</v>
+        <v>41351</v>
       </c>
       <c r="G165">
-        <v>59528</v>
+        <v>59545</v>
       </c>
       <c r="H165">
-        <v>19352</v>
+        <v>19334</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>91807</v>
+        <v>91865</v>
       </c>
       <c r="E166">
         <v>102548</v>
       </c>
       <c r="F166">
-        <v>106807</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>153802</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>38131</v>
+        <v>57351</v>
       </c>
       <c r="E167">
         <v>102548</v>
       </c>
       <c r="F167">
-        <v>61246</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>88194</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>23115</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>8930</v>
+        <v>9015</v>
       </c>
       <c r="E169">
         <v>72582</v>
       </c>
       <c r="F169">
-        <v>35930</v>
+        <v>36015</v>
       </c>
       <c r="G169">
-        <v>51739</v>
+        <v>51862</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59677</v>
+        <v>69060</v>
       </c>
       <c r="E170">
         <v>108882</v>
       </c>
       <c r="F170">
-        <v>80475</v>
+        <v>0</v>
       </c>
       <c r="G170">
-        <v>115884</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>20798</v>
+        <v>0</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7901,19 +7901,19 @@
         <v>17</v>
       </c>
       <c r="D171">
-        <v>53786</v>
+        <v>0</v>
       </c>
       <c r="E171">
         <v>108882</v>
       </c>
       <c r="F171">
-        <v>69978</v>
+        <v>0</v>
       </c>
       <c r="G171">
-        <v>100768</v>
+        <v>0</v>
       </c>
       <c r="H171">
-        <v>16192</v>
+        <v>0</v>
       </c>
       <c r="I171" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78892</v>
+        <v>78942</v>
       </c>
       <c r="E172">
         <v>145182</v>
       </c>
       <c r="F172">
-        <v>108413</v>
+        <v>108345</v>
       </c>
       <c r="G172">
-        <v>156115</v>
+        <v>156017</v>
       </c>
       <c r="H172">
-        <v>29521</v>
+        <v>29403</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>79128</v>
+        <v>78958</v>
       </c>
       <c r="E173">
         <v>145182</v>
       </c>
       <c r="F173">
-        <v>94272</v>
+        <v>94204</v>
       </c>
       <c r="G173">
-        <v>135752</v>
+        <v>135654</v>
       </c>
       <c r="H173">
-        <v>15144</v>
+        <v>15246</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>47691</v>
+        <v>46397</v>
       </c>
       <c r="E174">
         <v>90732</v>
@@ -8045,7 +8045,7 @@
         <v>97991</v>
       </c>
       <c r="H174">
-        <v>20358</v>
+        <v>21652</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>67851</v>
+        <v>67957</v>
       </c>
       <c r="E175">
         <v>90732</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>82957</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>119458</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65662</v>
+        <v>65751</v>
       </c>
       <c r="E176">
         <v>90732</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>80751</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>116281</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26476</v>
+        <v>26493</v>
       </c>
       <c r="E178">
         <v>108882</v>
       </c>
       <c r="F178">
-        <v>53476</v>
+        <v>53493</v>
       </c>
       <c r="G178">
-        <v>77005</v>
+        <v>77030</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>26271</v>
+        <v>24444</v>
       </c>
       <c r="E180">
         <v>90732</v>
       </c>
       <c r="F180">
-        <v>53271</v>
+        <v>51444</v>
       </c>
       <c r="G180">
-        <v>76710</v>
+        <v>74079</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100784</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>127032</v>
       </c>
       <c r="F182">
-        <v>115784</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>166729</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64559</v>
+        <v>64648</v>
       </c>
       <c r="E183">
         <v>127032</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>81402</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>117219</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>16754</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,16 +8474,16 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144884</v>
+        <v>144976</v>
       </c>
       <c r="E184">
         <v>181482</v>
       </c>
       <c r="F184">
-        <v>179884</v>
+        <v>179976</v>
       </c>
       <c r="G184">
-        <v>259033</v>
+        <v>259165</v>
       </c>
       <c r="H184">
         <v>35000</v>
@@ -8517,19 +8517,19 @@
         <v>17</v>
       </c>
       <c r="D185">
-        <v>196182</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>181482</v>
       </c>
       <c r="F185">
-        <v>211182</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>304102</v>
+        <v>0</v>
       </c>
       <c r="H185">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I185" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>188984</v>
+        <v>189104</v>
       </c>
       <c r="E186">
         <v>235932</v>
       </c>
       <c r="F186">
-        <v>203984</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>293737</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8604,19 +8604,19 @@
         <v>17</v>
       </c>
       <c r="D187">
-        <v>196182</v>
+        <v>0</v>
       </c>
       <c r="E187">
         <v>181482</v>
       </c>
       <c r="F187">
-        <v>211182</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>304102</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I187" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,7 +8648,7 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>291359</v>
+        <v>0</v>
       </c>
       <c r="E188">
         <v>362982</v>
@@ -8691,16 +8691,16 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>308417</v>
+        <v>307746</v>
       </c>
       <c r="E189">
         <v>362982</v>
       </c>
       <c r="F189">
-        <v>323417</v>
+        <v>322746</v>
       </c>
       <c r="G189">
-        <v>465720</v>
+        <v>464754</v>
       </c>
       <c r="H189">
         <v>15000</v>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29705</v>
+        <v>29723</v>
       </c>
       <c r="E190">
         <v>95269</v>
       </c>
       <c r="F190">
-        <v>64705</v>
+        <v>64723</v>
       </c>
       <c r="G190">
-        <v>93175</v>
+        <v>93201</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44746</v>
+        <v>44648</v>
       </c>
       <c r="E191">
         <v>95269</v>
       </c>
       <c r="F191">
-        <v>61053</v>
+        <v>61014</v>
       </c>
       <c r="G191">
-        <v>87916</v>
+        <v>87860</v>
       </c>
       <c r="H191">
-        <v>16307</v>
+        <v>16366</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>42588</v>
+        <v>41732</v>
       </c>
       <c r="E192">
         <v>122494</v>
       </c>
       <c r="F192">
-        <v>77588</v>
+        <v>76732</v>
       </c>
       <c r="G192">
-        <v>111727</v>
+        <v>110494</v>
       </c>
       <c r="H192">
         <v>35000</v>
@@ -8868,16 +8868,16 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>146680</v>
+        <v>145638</v>
       </c>
       <c r="E193">
         <v>122494</v>
       </c>
       <c r="F193">
-        <v>161680</v>
+        <v>160638</v>
       </c>
       <c r="G193">
-        <v>232819</v>
+        <v>231319</v>
       </c>
       <c r="H193">
         <v>15000</v>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>53771</v>
+        <v>53505</v>
       </c>
       <c r="E194">
         <v>149901</v>
       </c>
       <c r="F194">
-        <v>80771</v>
+        <v>80505</v>
       </c>
       <c r="G194">
-        <v>116310</v>
+        <v>115927</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8955,16 +8955,16 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>146680</v>
+        <v>145638</v>
       </c>
       <c r="E195">
         <v>122494</v>
       </c>
       <c r="F195">
-        <v>161680</v>
+        <v>160638</v>
       </c>
       <c r="G195">
-        <v>232819</v>
+        <v>231319</v>
       </c>
       <c r="H195">
         <v>15000</v>
@@ -8998,7 +8998,7 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>23987</v>
+        <v>24018</v>
       </c>
       <c r="E196">
         <v>72582</v>
@@ -9010,7 +9010,7 @@
         <v>78389</v>
       </c>
       <c r="H196">
-        <v>30450</v>
+        <v>30419</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,16 +9044,16 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32618</v>
+        <v>32544</v>
       </c>
       <c r="E197">
         <v>72582</v>
       </c>
       <c r="F197">
-        <v>47618</v>
+        <v>47544</v>
       </c>
       <c r="G197">
-        <v>68570</v>
+        <v>68463</v>
       </c>
       <c r="H197">
         <v>15000</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26602</v>
+        <v>26619</v>
       </c>
       <c r="E198">
         <v>108882</v>
       </c>
       <c r="F198">
-        <v>53602</v>
+        <v>53619</v>
       </c>
       <c r="G198">
-        <v>77187</v>
+        <v>77211</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>126016</v>
+        <v>126190</v>
       </c>
       <c r="E200">
         <v>127032</v>
       </c>
       <c r="F200">
-        <v>141016</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>203063</v>
+        <v>0</v>
       </c>
       <c r="H200">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11954</v>
+        <v>11946</v>
       </c>
       <c r="E201">
         <v>127032</v>
       </c>
       <c r="F201">
-        <v>38954</v>
+        <v>38946</v>
       </c>
       <c r="G201">
-        <v>56094</v>
+        <v>56082</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22790</v>
+        <v>82787</v>
       </c>
       <c r="E203">
         <v>145182</v>
       </c>
       <c r="F203">
-        <v>49790</v>
+        <v>0</v>
       </c>
       <c r="G203">
-        <v>71698</v>
+        <v>0</v>
       </c>
       <c r="H203">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26492</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>181482</v>
       </c>
       <c r="F205">
-        <v>53492</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>77028</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24192</v>
+        <v>24066</v>
       </c>
       <c r="E206">
         <v>58062</v>
       </c>
       <c r="F206">
-        <v>42232</v>
+        <v>42166</v>
       </c>
       <c r="G206">
-        <v>60814</v>
+        <v>60719</v>
       </c>
       <c r="H206">
-        <v>18040</v>
+        <v>18100</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13970</v>
+        <v>13806</v>
       </c>
       <c r="E207">
         <v>58062</v>
       </c>
       <c r="F207">
-        <v>34232</v>
+        <v>34166</v>
       </c>
       <c r="G207">
-        <v>49294</v>
+        <v>49199</v>
       </c>
       <c r="H207">
-        <v>20262</v>
+        <v>20360</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,16 +9578,16 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>23105</v>
+        <v>23057</v>
       </c>
       <c r="E209">
         <v>54432</v>
       </c>
       <c r="F209">
-        <v>38105</v>
+        <v>38057</v>
       </c>
       <c r="G209">
-        <v>54871</v>
+        <v>54802</v>
       </c>
       <c r="H209">
         <v>15000</v>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40556</v>
+        <v>40472</v>
       </c>
       <c r="E211">
         <v>108882</v>
       </c>
       <c r="F211">
-        <v>64686</v>
+        <v>64653</v>
       </c>
       <c r="G211">
-        <v>93148</v>
+        <v>93100</v>
       </c>
       <c r="H211">
-        <v>24130</v>
+        <v>24181</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83963</v>
+        <v>83780</v>
       </c>
       <c r="E213">
         <v>181482</v>
       </c>
       <c r="F213">
-        <v>110363</v>
+        <v>110290</v>
       </c>
       <c r="G213">
-        <v>158923</v>
+        <v>158818</v>
       </c>
       <c r="H213">
-        <v>26400</v>
+        <v>26510</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28697</v>
+        <v>28652</v>
       </c>
       <c r="E214">
         <v>87102</v>
       </c>
       <c r="F214">
-        <v>60532</v>
+        <v>55652</v>
       </c>
       <c r="G214">
-        <v>87166</v>
+        <v>80139</v>
       </c>
       <c r="H214">
-        <v>31835</v>
+        <v>27000</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31406</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>87102</v>
       </c>
       <c r="F215">
-        <v>52532</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>75646</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>21126</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45833</v>
+        <v>45909</v>
       </c>
       <c r="E216">
         <v>101622</v>
@@ -9893,7 +9893,7 @@
         <v>109752</v>
       </c>
       <c r="H216">
-        <v>30384</v>
+        <v>30308</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,16 +9927,16 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>89570</v>
+        <v>89375</v>
       </c>
       <c r="E217">
         <v>101622</v>
       </c>
       <c r="F217">
-        <v>104570</v>
+        <v>104375</v>
       </c>
       <c r="G217">
-        <v>150581</v>
+        <v>150300</v>
       </c>
       <c r="H217">
         <v>15000</v>
@@ -10016,16 +10016,16 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111636</v>
+        <v>111392</v>
       </c>
       <c r="E219">
         <v>130662</v>
       </c>
       <c r="F219">
-        <v>126636</v>
+        <v>126392</v>
       </c>
       <c r="G219">
-        <v>182356</v>
+        <v>182004</v>
       </c>
       <c r="H219">
         <v>15000</v>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>62669</v>
+        <v>62709</v>
       </c>
       <c r="E220">
         <v>81675</v>
       </c>
       <c r="F220">
-        <v>77669</v>
+        <v>0</v>
       </c>
       <c r="G220">
-        <v>111843</v>
+        <v>0</v>
       </c>
       <c r="H220">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,16 +10105,16 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>52164</v>
+        <v>51740</v>
       </c>
       <c r="E221">
         <v>81675</v>
       </c>
       <c r="F221">
-        <v>67164</v>
+        <v>66740</v>
       </c>
       <c r="G221">
-        <v>96716</v>
+        <v>96106</v>
       </c>
       <c r="H221">
         <v>15000</v>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74639</v>
+        <v>74687</v>
       </c>
       <c r="E222">
         <v>96195</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>109687</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>157949</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>85601</v>
+        <v>93268</v>
       </c>
       <c r="E223">
         <v>96195</v>
       </c>
       <c r="F223">
-        <v>100601</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>144865</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>30306</v>
       </c>
       <c r="E224">
         <v>59877</v>
       </c>
       <c r="F224">
-        <v>0</v>
+        <v>45306</v>
       </c>
       <c r="G224">
-        <v>0</v>
+        <v>65241</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10411</v>
+        <v>10417</v>
       </c>
       <c r="E225">
         <v>59877</v>
       </c>
       <c r="F225">
-        <v>33516</v>
+        <v>33519</v>
       </c>
       <c r="G225">
-        <v>48263</v>
+        <v>48267</v>
       </c>
       <c r="H225">
-        <v>23105</v>
+        <v>23102</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>38099</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>72582</v>
       </c>
       <c r="F226">
-        <v>53902</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>77619</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>15803</v>
+        <v>0</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>23531</v>
+        <v>0</v>
       </c>
       <c r="E227">
         <v>72582</v>
       </c>
       <c r="F227">
-        <v>43719</v>
+        <v>0</v>
       </c>
       <c r="G227">
-        <v>62955</v>
+        <v>0</v>
       </c>
       <c r="H227">
-        <v>20188</v>
+        <v>0</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>84121</v>
+        <v>0</v>
       </c>
       <c r="E228">
         <v>108882</v>
       </c>
       <c r="F228">
-        <v>99121</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>142734</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>13380</v>
       </c>
       <c r="E229">
         <v>108882</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>40380</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>58147</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19310</v>
+        <v>19274</v>
       </c>
       <c r="E231">
         <v>181482</v>
       </c>
       <c r="F231">
-        <v>46310</v>
+        <v>46274</v>
       </c>
       <c r="G231">
-        <v>66686</v>
+        <v>66635</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>10033</v>
+        <v>10023</v>
       </c>
       <c r="E233">
         <v>52635</v>
       </c>
       <c r="F233">
-        <v>30541</v>
+        <v>30537</v>
       </c>
       <c r="G233">
-        <v>43979</v>
+        <v>43973</v>
       </c>
       <c r="H233">
-        <v>20508</v>
+        <v>20514</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,19 +10677,19 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>24617</v>
+        <v>24649</v>
       </c>
       <c r="E234">
         <v>70785</v>
       </c>
       <c r="F234">
-        <v>47700</v>
+        <v>47713</v>
       </c>
       <c r="G234">
-        <v>68688</v>
+        <v>68707</v>
       </c>
       <c r="H234">
-        <v>23083</v>
+        <v>23064</v>
       </c>
       <c r="I234" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6883</v>
+        <v>6871</v>
       </c>
       <c r="E237">
         <v>52635</v>
       </c>
       <c r="F237">
-        <v>29281</v>
+        <v>29276</v>
       </c>
       <c r="G237">
-        <v>42165</v>
+        <v>42157</v>
       </c>
       <c r="H237">
-        <v>22398</v>
+        <v>22405</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11435</v>
+        <v>11410</v>
       </c>
       <c r="E239">
         <v>52635</v>
       </c>
       <c r="F239">
-        <v>31102</v>
+        <v>31092</v>
       </c>
       <c r="G239">
-        <v>44787</v>
+        <v>44772</v>
       </c>
       <c r="H239">
-        <v>19667</v>
+        <v>19682</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>24350</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>70785</v>
       </c>
       <c r="F240">
-        <v>53089</v>
+        <v>0</v>
       </c>
       <c r="G240">
-        <v>76448</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>28739</v>
+        <v>0</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>73253</v>
+        <v>70258</v>
       </c>
       <c r="E241">
         <v>70785</v>
       </c>
       <c r="F241">
-        <v>88253</v>
+        <v>85258</v>
       </c>
       <c r="G241">
-        <v>127084</v>
+        <v>122772</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34209</v>
+        <v>34231</v>
       </c>
       <c r="E242">
         <v>70785</v>
       </c>
       <c r="F242">
-        <v>51537</v>
+        <v>51546</v>
       </c>
       <c r="G242">
-        <v>74213</v>
+        <v>74226</v>
       </c>
       <c r="H242">
-        <v>17328</v>
+        <v>17315</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>24082</v>
+        <v>0</v>
       </c>
       <c r="E244">
         <v>27225</v>
       </c>
       <c r="F244">
-        <v>39082</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>56278</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>49518</v>
+        <v>108161</v>
       </c>
       <c r="E246">
         <v>108882</v>
       </c>
       <c r="F246">
-        <v>74804</v>
+        <v>0</v>
       </c>
       <c r="G246">
-        <v>107718</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>25286</v>
+        <v>0</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59078</v>
+        <v>67784</v>
       </c>
       <c r="E248">
         <v>96195</v>
       </c>
       <c r="F248">
-        <v>74078</v>
+        <v>0</v>
       </c>
       <c r="G248">
-        <v>106672</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48715</v>
+        <v>48462</v>
       </c>
       <c r="E249">
         <v>96195</v>
       </c>
       <c r="F249">
-        <v>63715</v>
+        <v>63462</v>
       </c>
       <c r="G249">
-        <v>91750</v>
+        <v>91385</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>72182</v>
+        <v>71566</v>
       </c>
       <c r="E250">
         <v>108882</v>
       </c>
       <c r="F250">
-        <v>104227</v>
+        <v>86566</v>
       </c>
       <c r="G250">
-        <v>150087</v>
+        <v>124655</v>
       </c>
       <c r="H250">
-        <v>32045</v>
+        <v>15000</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>75632</v>
+        <v>0</v>
       </c>
       <c r="E251">
         <v>108882</v>
       </c>
       <c r="F251">
-        <v>90632</v>
+        <v>0</v>
       </c>
       <c r="G251">
-        <v>130510</v>
+        <v>0</v>
       </c>
       <c r="H251">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>36383</v>
+        <v>34294</v>
       </c>
       <c r="E252">
         <v>52635</v>
       </c>
       <c r="F252">
-        <v>61970</v>
+        <v>49294</v>
       </c>
       <c r="G252">
-        <v>89237</v>
+        <v>70983</v>
       </c>
       <c r="H252">
-        <v>25587</v>
+        <v>15000</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>38887</v>
+        <v>0</v>
       </c>
       <c r="E253">
         <v>52635</v>
       </c>
       <c r="F253">
-        <v>53887</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>77597</v>
+        <v>0</v>
       </c>
       <c r="H253">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>27216</v>
+        <v>25248</v>
       </c>
       <c r="E254">
         <v>70785</v>
       </c>
       <c r="F254">
-        <v>53089</v>
+        <v>47953</v>
       </c>
       <c r="G254">
-        <v>76448</v>
+        <v>69052</v>
       </c>
       <c r="H254">
-        <v>25873</v>
+        <v>22705</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>70103</v>
+        <v>0</v>
       </c>
       <c r="E255">
         <v>70785</v>
       </c>
       <c r="F255">
-        <v>85103</v>
+        <v>0</v>
       </c>
       <c r="G255">
-        <v>122548</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12553</v>
+        <v>12561</v>
       </c>
       <c r="E259">
         <v>50802</v>
       </c>
       <c r="F259">
-        <v>30834</v>
+        <v>30837</v>
       </c>
       <c r="G259">
-        <v>44401</v>
+        <v>44405</v>
       </c>
       <c r="H259">
-        <v>18281</v>
+        <v>18276</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62638</v>
+        <v>62725</v>
       </c>
       <c r="E261">
         <v>63507</v>
       </c>
       <c r="F261">
-        <v>77638</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>111799</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75348</v>
+        <v>75459</v>
       </c>
       <c r="E263">
         <v>72582</v>
       </c>
       <c r="F263">
-        <v>90348</v>
+        <v>0</v>
       </c>
       <c r="G263">
-        <v>130101</v>
+        <v>0</v>
       </c>
       <c r="H263">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>39895</v>
+        <v>40314</v>
       </c>
       <c r="E264">
         <v>59877</v>
       </c>
       <c r="F264">
-        <v>0</v>
+        <v>55314</v>
       </c>
       <c r="G264">
-        <v>0</v>
+        <v>79652</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>23625</v>
+        <v>26540</v>
       </c>
       <c r="E265">
         <v>59877</v>
       </c>
       <c r="F265">
-        <v>38802</v>
+        <v>0</v>
       </c>
       <c r="G265">
-        <v>55875</v>
+        <v>0</v>
       </c>
       <c r="H265">
-        <v>15177</v>
+        <v>0</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34965</v>
+        <v>34987</v>
       </c>
       <c r="E268">
         <v>59877</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>49987</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>71981</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23263</v>
+        <v>23151</v>
       </c>
       <c r="E269">
         <v>59877</v>
       </c>
       <c r="F269">
-        <v>0</v>
+        <v>38612</v>
       </c>
       <c r="G269">
-        <v>0</v>
+        <v>55601</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>15461</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,16 +12305,16 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29327</v>
+        <v>29266</v>
       </c>
       <c r="E271">
         <v>67137</v>
       </c>
       <c r="F271">
-        <v>44327</v>
+        <v>44266</v>
       </c>
       <c r="G271">
-        <v>63831</v>
+        <v>63743</v>
       </c>
       <c r="H271">
         <v>15000</v>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71395</v>
+        <v>71440</v>
       </c>
       <c r="E272">
         <v>90732</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>86440</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>124474</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21278</v>
+        <v>21292</v>
       </c>
       <c r="E273">
         <v>90732</v>
       </c>
       <c r="F273">
-        <v>48278</v>
+        <v>48292</v>
       </c>
       <c r="G273">
-        <v>69520</v>
+        <v>69540</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>57960</v>
+        <v>57997</v>
       </c>
       <c r="E274">
         <v>127032</v>
       </c>
       <c r="F274">
-        <v>84960</v>
+        <v>85645</v>
       </c>
       <c r="G274">
-        <v>122342</v>
+        <v>123329</v>
       </c>
       <c r="H274">
-        <v>27000</v>
+        <v>27648</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12222</v>
+        <v>12907</v>
       </c>
       <c r="E275">
         <v>127032</v>
       </c>
       <c r="F275">
-        <v>39222</v>
+        <v>39907</v>
       </c>
       <c r="G275">
-        <v>56480</v>
+        <v>57466</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152917</v>
+        <v>152856</v>
       </c>
       <c r="E276">
         <v>163332</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>167856</v>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>241713</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,16 +12569,16 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>102627</v>
+        <v>102408</v>
       </c>
       <c r="E277">
         <v>163332</v>
       </c>
       <c r="F277">
-        <v>117627</v>
+        <v>117408</v>
       </c>
       <c r="G277">
-        <v>169383</v>
+        <v>169068</v>
       </c>
       <c r="H277">
         <v>15000</v>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>49219</v>
+        <v>48036</v>
       </c>
       <c r="E278">
         <v>108882</v>
       </c>
       <c r="F278">
-        <v>78360</v>
+        <v>78389</v>
       </c>
       <c r="G278">
-        <v>112838</v>
+        <v>112880</v>
       </c>
       <c r="H278">
-        <v>29141</v>
+        <v>30353</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49187</v>
+        <v>49250</v>
       </c>
       <c r="E279">
         <v>108882</v>
       </c>
       <c r="F279">
-        <v>68139</v>
+        <v>68164</v>
       </c>
       <c r="G279">
-        <v>98120</v>
+        <v>98156</v>
       </c>
       <c r="H279">
-        <v>18952</v>
+        <v>18914</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,7 +12701,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>63929</v>
+        <v>62678</v>
       </c>
       <c r="E280">
         <v>127032</v>
@@ -12713,7 +12713,7 @@
         <v>137195</v>
       </c>
       <c r="H280">
-        <v>31345</v>
+        <v>32596</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>77506</v>
+        <v>106081</v>
       </c>
       <c r="E281">
         <v>127032</v>
       </c>
       <c r="F281">
-        <v>92506</v>
+        <v>0</v>
       </c>
       <c r="G281">
-        <v>133209</v>
+        <v>0</v>
       </c>
       <c r="H281">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>24208</v>
+        <v>0</v>
       </c>
       <c r="E282">
         <v>54432</v>
       </c>
       <c r="F282">
-        <v>40824</v>
+        <v>0</v>
       </c>
       <c r="G282">
-        <v>58787</v>
+        <v>0</v>
       </c>
       <c r="H282">
-        <v>16616</v>
+        <v>0</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>24838</v>
+        <v>0</v>
       </c>
       <c r="E283">
         <v>54432</v>
       </c>
       <c r="F283">
-        <v>39838</v>
+        <v>0</v>
       </c>
       <c r="G283">
-        <v>57367</v>
+        <v>0</v>
       </c>
       <c r="H283">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65174</v>
+        <v>66097</v>
       </c>
       <c r="E284">
         <v>81675</v>
       </c>
       <c r="F284">
-        <v>0</v>
+        <v>81097</v>
       </c>
       <c r="G284">
-        <v>0</v>
+        <v>116780</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20412</v>
+        <v>20441</v>
       </c>
       <c r="E287">
         <v>38097</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>35441</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>51035</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31957</v>
+        <v>31977</v>
       </c>
       <c r="E288">
         <v>58062</v>
       </c>
       <c r="F288">
-        <v>48720</v>
+        <v>48689</v>
       </c>
       <c r="G288">
-        <v>70157</v>
+        <v>70112</v>
       </c>
       <c r="H288">
-        <v>16763</v>
+        <v>16712</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25720</v>
+        <v>25689</v>
       </c>
       <c r="E289">
         <v>58062</v>
       </c>
       <c r="F289">
-        <v>40720</v>
+        <v>40689</v>
       </c>
       <c r="G289">
-        <v>58637</v>
+        <v>58592</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34351</v>
+        <v>34278</v>
       </c>
       <c r="E291">
         <v>43542</v>
       </c>
       <c r="F291">
-        <v>49351</v>
+        <v>49278</v>
       </c>
       <c r="G291">
-        <v>71065</v>
+        <v>70960</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>43517</v>
+        <v>0</v>
       </c>
       <c r="E292">
         <v>108882</v>
       </c>
       <c r="F292">
-        <v>73324</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>105587</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>29807</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>38241</v>
+        <v>38155</v>
       </c>
       <c r="E293">
         <v>108882</v>
       </c>
       <c r="F293">
-        <v>63760</v>
+        <v>63726</v>
       </c>
       <c r="G293">
-        <v>91814</v>
+        <v>91765</v>
       </c>
       <c r="H293">
-        <v>25519</v>
+        <v>25571</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,16 +13409,16 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54133</v>
+        <v>54010</v>
       </c>
       <c r="E296">
         <v>72582</v>
       </c>
       <c r="F296">
-        <v>89133</v>
+        <v>89010</v>
       </c>
       <c r="G296">
-        <v>128352</v>
+        <v>128174</v>
       </c>
       <c r="H296">
         <v>35000</v>
@@ -13455,16 +13455,16 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64843</v>
+        <v>64711</v>
       </c>
       <c r="E297">
         <v>72582</v>
       </c>
       <c r="F297">
-        <v>79843</v>
+        <v>79711</v>
       </c>
       <c r="G297">
-        <v>114974</v>
+        <v>114784</v>
       </c>
       <c r="H297">
         <v>15000</v>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4804</v>
+        <v>0</v>
       </c>
       <c r="E299">
         <v>54432</v>
       </c>
       <c r="F299">
-        <v>29150</v>
+        <v>0</v>
       </c>
       <c r="G299">
-        <v>41976</v>
+        <v>0</v>
       </c>
       <c r="H299">
-        <v>24346</v>
+        <v>0</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13625,19 +13625,19 @@
         <v>17</v>
       </c>
       <c r="D301">
-        <v>10820</v>
+        <v>0</v>
       </c>
       <c r="E301">
         <v>68952</v>
       </c>
       <c r="F301">
-        <v>37219</v>
+        <v>0</v>
       </c>
       <c r="G301">
-        <v>53595</v>
+        <v>0</v>
       </c>
       <c r="H301">
-        <v>26399</v>
+        <v>0</v>
       </c>
       <c r="I301" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>23893</v>
+        <v>24192</v>
       </c>
       <c r="E302">
         <v>90732</v>
       </c>
       <c r="F302">
-        <v>50893</v>
+        <v>51192</v>
       </c>
       <c r="G302">
-        <v>73286</v>
+        <v>73716</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>38997</v>
+        <v>37698</v>
       </c>
       <c r="E304">
         <v>108882</v>
       </c>
       <c r="F304">
-        <v>73997</v>
+        <v>64698</v>
       </c>
       <c r="G304">
-        <v>106556</v>
+        <v>93165</v>
       </c>
       <c r="H304">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>45911</v>
+        <v>0</v>
       </c>
       <c r="E305">
         <v>108882</v>
       </c>
       <c r="F305">
-        <v>66828</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>96232</v>
+        <v>0</v>
       </c>
       <c r="H305">
-        <v>20917</v>
+        <v>0</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24428</v>
+        <v>24444</v>
       </c>
       <c r="E306">
         <v>108882</v>
       </c>
       <c r="F306">
-        <v>59428</v>
+        <v>59444</v>
       </c>
       <c r="G306">
-        <v>85576</v>
+        <v>85599</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33626</v>
+        <v>33553</v>
       </c>
       <c r="E307">
         <v>108882</v>
       </c>
       <c r="F307">
-        <v>60626</v>
+        <v>60553</v>
       </c>
       <c r="G307">
-        <v>87301</v>
+        <v>87196</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>185283</v>
+        <v>185653</v>
       </c>
       <c r="E308">
         <v>235932</v>
       </c>
       <c r="F308">
-        <v>200283</v>
+        <v>0</v>
       </c>
       <c r="G308">
-        <v>288408</v>
+        <v>0</v>
       </c>
       <c r="H308">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>142790</v>
+        <v>0</v>
       </c>
       <c r="E309">
         <v>235932</v>
       </c>
       <c r="F309">
-        <v>157790</v>
+        <v>0</v>
       </c>
       <c r="G309">
-        <v>227218</v>
+        <v>0</v>
       </c>
       <c r="H309">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>66134</v>
+        <v>65703</v>
       </c>
       <c r="E310">
         <v>127032</v>
       </c>
       <c r="F310">
-        <v>89618</v>
+        <v>89446</v>
       </c>
       <c r="G310">
-        <v>129050</v>
+        <v>128802</v>
       </c>
       <c r="H310">
-        <v>23484</v>
+        <v>23743</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>111447</v>
+        <v>0</v>
       </c>
       <c r="E313">
         <v>181482</v>
       </c>
       <c r="F313">
-        <v>126447</v>
+        <v>0</v>
       </c>
       <c r="G313">
-        <v>182084</v>
+        <v>0</v>
       </c>
       <c r="H313">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>124993</v>
       </c>
       <c r="E314">
         <v>235932</v>
       </c>
       <c r="F314">
-        <v>0</v>
+        <v>159993</v>
       </c>
       <c r="G314">
-        <v>0</v>
+        <v>230390</v>
       </c>
       <c r="H314">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,16 +14235,16 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>148916</v>
+        <v>148601</v>
       </c>
       <c r="E315">
         <v>235932</v>
       </c>
       <c r="F315">
-        <v>163916</v>
+        <v>163601</v>
       </c>
       <c r="G315">
-        <v>236039</v>
+        <v>235585</v>
       </c>
       <c r="H315">
         <v>15000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72102</v>
+        <v>72148</v>
       </c>
       <c r="E2">
         <v>72582</v>
       </c>
       <c r="F2">
-        <v>87102</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>125427</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46713</v>
+        <v>46742</v>
       </c>
       <c r="E3">
         <v>72582</v>
       </c>
       <c r="F3">
-        <v>61713</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>88867</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -571,19 +571,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>82378</v>
+        <v>82430</v>
       </c>
       <c r="E4">
         <v>83472</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>97430</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>140299</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>84773</v>
+        <v>84827</v>
       </c>
       <c r="E5">
         <v>83472</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>99827</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>143751</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>4271</v>
+        <v>3611</v>
       </c>
       <c r="E7">
         <v>54432</v>
       </c>
       <c r="F7">
-        <v>28937</v>
+        <v>28673</v>
       </c>
       <c r="G7">
-        <v>41669</v>
+        <v>41289</v>
       </c>
       <c r="H7">
-        <v>24666</v>
+        <v>25062</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>36027</v>
+        <v>36050</v>
       </c>
       <c r="E8">
         <v>72582</v>
       </c>
       <c r="F8">
-        <v>53073</v>
+        <v>53082</v>
       </c>
       <c r="G8">
-        <v>76425</v>
+        <v>76438</v>
       </c>
       <c r="H8">
-        <v>17046</v>
+        <v>17032</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -836,19 +836,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>53411</v>
+        <v>53445</v>
       </c>
       <c r="E10">
         <v>108882</v>
       </c>
       <c r="F10">
-        <v>76362</v>
+        <v>76375</v>
       </c>
       <c r="G10">
-        <v>109961</v>
+        <v>109980</v>
       </c>
       <c r="H10">
-        <v>22951</v>
+        <v>22930</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>79036</v>
+        <v>79087</v>
       </c>
       <c r="E12">
         <v>81657</v>
       </c>
       <c r="F12">
-        <v>97106</v>
+        <v>97114</v>
       </c>
       <c r="G12">
-        <v>139833</v>
+        <v>139844</v>
       </c>
       <c r="H12">
-        <v>18070</v>
+        <v>18027</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11788</v>
+        <v>11796</v>
       </c>
       <c r="E13">
         <v>81657</v>
       </c>
       <c r="F13">
-        <v>38788</v>
+        <v>38796</v>
       </c>
       <c r="G13">
-        <v>55855</v>
+        <v>55866</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>44948</v>
+        <v>44976</v>
       </c>
       <c r="E15">
         <v>72582</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>59976</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>86365</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>34341</v>
+        <v>34126</v>
       </c>
       <c r="E21">
         <v>101622</v>
       </c>
       <c r="F21">
-        <v>59369</v>
+        <v>59283</v>
       </c>
       <c r="G21">
-        <v>85491</v>
+        <v>85368</v>
       </c>
       <c r="H21">
-        <v>25028</v>
+        <v>25157</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20204</v>
+        <v>20217</v>
       </c>
       <c r="E27">
         <v>63507</v>
       </c>
       <c r="F27">
-        <v>38850</v>
+        <v>38855</v>
       </c>
       <c r="G27">
-        <v>55944</v>
+        <v>55951</v>
       </c>
       <c r="H27">
-        <v>18646</v>
+        <v>18638</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75018</v>
+        <v>75065</v>
       </c>
       <c r="E28">
         <v>127032</v>
       </c>
       <c r="F28">
-        <v>95043</v>
+        <v>95062</v>
       </c>
       <c r="G28">
-        <v>136862</v>
+        <v>136889</v>
       </c>
       <c r="H28">
-        <v>20025</v>
+        <v>19997</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>28998</v>
+        <v>29017</v>
       </c>
       <c r="E29">
         <v>127032</v>
       </c>
       <c r="F29">
-        <v>55998</v>
+        <v>56017</v>
       </c>
       <c r="G29">
-        <v>80637</v>
+        <v>80664</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,16 +1709,16 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>131328</v>
+        <v>126113</v>
       </c>
       <c r="E30">
         <v>181482</v>
       </c>
       <c r="F30">
-        <v>146328</v>
+        <v>141113</v>
       </c>
       <c r="G30">
-        <v>210712</v>
+        <v>203203</v>
       </c>
       <c r="H30">
         <v>15000</v>
@@ -1755,19 +1755,19 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>70258</v>
+        <v>78298</v>
       </c>
       <c r="E31">
         <v>181482</v>
       </c>
       <c r="F31">
-        <v>0</v>
+        <v>105298</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>151629</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I31" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>81353</v>
+        <v>72684</v>
       </c>
       <c r="E32">
         <v>108882</v>
       </c>
       <c r="F32">
-        <v>96353</v>
+        <v>96283</v>
       </c>
       <c r="G32">
-        <v>138748</v>
+        <v>138648</v>
       </c>
       <c r="H32">
-        <v>15000</v>
+        <v>23599</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>47910</v>
+        <v>47736</v>
       </c>
       <c r="E33">
         <v>108882</v>
       </c>
       <c r="F33">
-        <v>67628</v>
+        <v>67558</v>
       </c>
       <c r="G33">
-        <v>97384</v>
+        <v>97284</v>
       </c>
       <c r="H33">
-        <v>19718</v>
+        <v>19822</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>80171</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>127032</v>
       </c>
       <c r="F35">
-        <v>95171</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>137046</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>44112</v>
+        <v>43841</v>
       </c>
       <c r="E36">
         <v>127032</v>
       </c>
       <c r="F36">
-        <v>71112</v>
+        <v>70841</v>
       </c>
       <c r="G36">
-        <v>102401</v>
+        <v>102011</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>64837</v>
+        <v>65177</v>
       </c>
       <c r="E38">
         <v>235932</v>
       </c>
       <c r="F38">
-        <v>91837</v>
+        <v>92177</v>
       </c>
       <c r="G38">
-        <v>132245</v>
+        <v>132735</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2156,16 +2156,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>84284</v>
+        <v>84338</v>
       </c>
       <c r="E40">
         <v>235932</v>
       </c>
       <c r="F40">
-        <v>111284</v>
+        <v>111338</v>
       </c>
       <c r="G40">
-        <v>160249</v>
+        <v>160327</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38974</v>
+        <v>38999</v>
       </c>
       <c r="E43">
         <v>127032</v>
       </c>
       <c r="F43">
-        <v>65974</v>
+        <v>65999</v>
       </c>
       <c r="G43">
-        <v>95003</v>
+        <v>95039</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27627</v>
+        <v>27645</v>
       </c>
       <c r="E47">
         <v>108882</v>
       </c>
       <c r="F47">
-        <v>54627</v>
+        <v>54645</v>
       </c>
       <c r="G47">
-        <v>78663</v>
+        <v>78689</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36232</v>
+        <v>36255</v>
       </c>
       <c r="E50">
         <v>63507</v>
       </c>
       <c r="F50">
-        <v>55655</v>
+        <v>58940</v>
       </c>
       <c r="G50">
-        <v>80143</v>
+        <v>84874</v>
       </c>
       <c r="H50">
-        <v>19423</v>
+        <v>22685</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>32655</v>
+        <v>35940</v>
       </c>
       <c r="E51">
         <v>63507</v>
       </c>
       <c r="F51">
-        <v>47655</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>68623</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2677,19 +2677,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>49691</v>
+        <v>50133</v>
       </c>
       <c r="E52">
         <v>76212</v>
       </c>
       <c r="F52">
-        <v>64691</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>93155</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>57225</v>
+        <v>69987</v>
       </c>
       <c r="E53">
         <v>76212</v>
       </c>
       <c r="F53">
-        <v>72225</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>104004</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49155</v>
+        <v>54091</v>
       </c>
       <c r="E54">
         <v>127032</v>
       </c>
       <c r="F54">
-        <v>84155</v>
+        <v>88016</v>
       </c>
       <c r="G54">
-        <v>121183</v>
+        <v>126743</v>
       </c>
       <c r="H54">
-        <v>35000</v>
+        <v>33925</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52449</v>
+        <v>52483</v>
       </c>
       <c r="E55">
         <v>127032</v>
       </c>
       <c r="F55">
-        <v>76522</v>
+        <v>76536</v>
       </c>
       <c r="G55">
-        <v>110192</v>
+        <v>110212</v>
       </c>
       <c r="H55">
-        <v>24073</v>
+        <v>24053</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,16 +2857,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53411</v>
+        <v>53445</v>
       </c>
       <c r="E56">
         <v>145182</v>
       </c>
       <c r="F56">
-        <v>80411</v>
+        <v>80445</v>
       </c>
       <c r="G56">
-        <v>115792</v>
+        <v>115841</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>63072</v>
+        <v>63112</v>
       </c>
       <c r="E57">
         <v>145182</v>
       </c>
       <c r="F57">
-        <v>87850</v>
+        <v>87866</v>
       </c>
       <c r="G57">
-        <v>126504</v>
+        <v>126527</v>
       </c>
       <c r="H57">
-        <v>24778</v>
+        <v>24754</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>24696</v>
+        <v>23387</v>
       </c>
       <c r="E58">
         <v>36282</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>38387</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>55277</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6257</v>
+        <v>6261</v>
       </c>
       <c r="E59">
         <v>36282</v>
       </c>
       <c r="F59">
-        <v>22653</v>
+        <v>22654</v>
       </c>
       <c r="G59">
-        <v>32620</v>
+        <v>32622</v>
       </c>
       <c r="H59">
-        <v>16396</v>
+        <v>16393</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26366</v>
+        <v>26683</v>
       </c>
       <c r="E60">
         <v>48987</v>
       </c>
       <c r="F60">
-        <v>48090</v>
+        <v>41683</v>
       </c>
       <c r="G60">
-        <v>69250</v>
+        <v>60024</v>
       </c>
       <c r="H60">
-        <v>21724</v>
+        <v>15000</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>25090</v>
+        <v>0</v>
       </c>
       <c r="E61">
         <v>48987</v>
       </c>
       <c r="F61">
-        <v>40090</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>57730</v>
+        <v>0</v>
       </c>
       <c r="H61">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13822</v>
+        <v>13878</v>
       </c>
       <c r="E63">
         <v>81657</v>
       </c>
       <c r="F63">
-        <v>40822</v>
+        <v>40878</v>
       </c>
       <c r="G63">
-        <v>58784</v>
+        <v>58864</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>27911</v>
+        <v>27708</v>
       </c>
       <c r="E65">
         <v>122476</v>
       </c>
       <c r="F65">
-        <v>54911</v>
+        <v>54708</v>
       </c>
       <c r="G65">
-        <v>79072</v>
+        <v>78780</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24144</v>
+        <v>24002</v>
       </c>
       <c r="E66">
         <v>90732</v>
       </c>
       <c r="F66">
-        <v>53534</v>
+        <v>53624</v>
       </c>
       <c r="G66">
-        <v>77089</v>
+        <v>77219</v>
       </c>
       <c r="H66">
-        <v>29390</v>
+        <v>29622</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18534</v>
+        <v>18624</v>
       </c>
       <c r="E67">
         <v>90732</v>
       </c>
       <c r="F67">
-        <v>45534</v>
+        <v>45624</v>
       </c>
       <c r="G67">
-        <v>65569</v>
+        <v>65699</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34640</v>
+        <v>34662</v>
       </c>
       <c r="E68">
         <v>108882</v>
       </c>
       <c r="F68">
-        <v>62919</v>
+        <v>61662</v>
       </c>
       <c r="G68">
-        <v>90603</v>
+        <v>88793</v>
       </c>
       <c r="H68">
-        <v>28279</v>
+        <v>27000</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3431,19 +3431,19 @@
         <v>17</v>
       </c>
       <c r="D69">
-        <v>27706</v>
+        <v>0</v>
       </c>
       <c r="E69">
         <v>108882</v>
       </c>
       <c r="F69">
-        <v>54706</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>78777</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I69" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>107861</v>
+        <v>107930</v>
       </c>
       <c r="E70">
         <v>127032</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>122930</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>177019</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5863</v>
+        <v>5866</v>
       </c>
       <c r="E73">
         <v>27207</v>
       </c>
       <c r="F73">
-        <v>20863</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>30043</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86113</v>
+        <v>86167</v>
       </c>
       <c r="E76">
         <v>127032</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>101167</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>145680</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47217</v>
+        <v>47247</v>
       </c>
       <c r="E77">
         <v>127032</v>
       </c>
       <c r="F77">
-        <v>74217</v>
+        <v>74247</v>
       </c>
       <c r="G77">
-        <v>106872</v>
+        <v>106916</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37209</v>
+        <v>37233</v>
       </c>
       <c r="E81">
         <v>90732</v>
       </c>
       <c r="F81">
-        <v>56269</v>
+        <v>56279</v>
       </c>
       <c r="G81">
-        <v>81027</v>
+        <v>81042</v>
       </c>
       <c r="H81">
-        <v>19060</v>
+        <v>19046</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>85041</v>
+        <v>85095</v>
       </c>
       <c r="E83">
         <v>127032</v>
       </c>
       <c r="F83">
-        <v>100041</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>144059</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48557</v>
+        <v>48603</v>
       </c>
       <c r="E84">
         <v>101622</v>
       </c>
       <c r="F84">
-        <v>71156</v>
+        <v>71171</v>
       </c>
       <c r="G84">
-        <v>102465</v>
+        <v>102486</v>
       </c>
       <c r="H84">
-        <v>22599</v>
+        <v>22568</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32103</v>
+        <v>32123</v>
       </c>
       <c r="E85">
         <v>101622</v>
       </c>
       <c r="F85">
-        <v>58474</v>
+        <v>58482</v>
       </c>
       <c r="G85">
-        <v>84203</v>
+        <v>84214</v>
       </c>
       <c r="H85">
-        <v>26371</v>
+        <v>26359</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>151485</v>
+        <v>151581</v>
       </c>
       <c r="E86">
         <v>145182</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>166581</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>239877</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>171091</v>
+        <v>171183</v>
       </c>
       <c r="E88">
         <v>159702</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>186183</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>268104</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127294</v>
+        <v>127374</v>
       </c>
       <c r="E89">
         <v>159702</v>
       </c>
       <c r="F89">
-        <v>142294</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>204903</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>7790</v>
       </c>
       <c r="E90">
         <v>58062</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>38360</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>55238</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>30570</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="E91">
         <v>58062</v>
       </c>
       <c r="F91">
-        <v>30359</v>
+        <v>30360</v>
       </c>
       <c r="G91">
-        <v>43717</v>
+        <v>43718</v>
       </c>
       <c r="H91">
-        <v>26072</v>
+        <v>26071</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12230</v>
+        <v>12238</v>
       </c>
       <c r="E93">
         <v>27207</v>
       </c>
       <c r="F93">
-        <v>27230</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>39211</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61984</v>
+        <v>62023</v>
       </c>
       <c r="E96">
         <v>81657</v>
       </c>
       <c r="F96">
-        <v>76984</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>110857</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33711</v>
+        <v>33732</v>
       </c>
       <c r="E97">
         <v>81657</v>
       </c>
       <c r="F97">
-        <v>51331</v>
+        <v>51339</v>
       </c>
       <c r="G97">
-        <v>73917</v>
+        <v>73928</v>
       </c>
       <c r="H97">
-        <v>17620</v>
+        <v>17607</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>77350</v>
+        <v>77383</v>
       </c>
       <c r="E98">
         <v>94362</v>
       </c>
       <c r="F98">
-        <v>96737</v>
+        <v>96049</v>
       </c>
       <c r="G98">
-        <v>139301</v>
+        <v>138311</v>
       </c>
       <c r="H98">
-        <v>19387</v>
+        <v>18666</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>68477</v>
+        <v>68521</v>
       </c>
       <c r="E99">
         <v>94362</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>83521</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>120270</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61716</v>
+        <v>61755</v>
       </c>
       <c r="E100">
         <v>105796</v>
       </c>
       <c r="F100">
-        <v>78295</v>
+        <v>78310</v>
       </c>
       <c r="G100">
-        <v>112745</v>
+        <v>112766</v>
       </c>
       <c r="H100">
-        <v>16579</v>
+        <v>16555</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5006,19 +5006,19 @@
         <v>17</v>
       </c>
       <c r="D105">
-        <v>72748</v>
+        <v>0</v>
       </c>
       <c r="E105">
         <v>127032</v>
       </c>
       <c r="F105">
-        <v>87748</v>
+        <v>0</v>
       </c>
       <c r="G105">
-        <v>126357</v>
+        <v>0</v>
       </c>
       <c r="H105">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I105" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/4032350/EA_SPORTS_College_Football_27/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="E108">
-        <v>127032</v>
+        <v>163332</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>4003</v>
+        <v>3249</v>
       </c>
       <c r="E109">
-        <v>127032</v>
+        <v>163332</v>
       </c>
       <c r="F109">
-        <v>31003</v>
+        <v>30249</v>
       </c>
       <c r="G109">
-        <v>44644</v>
+        <v>43559</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14152</v>
+        <v>14161</v>
       </c>
       <c r="E111">
         <v>163332</v>
       </c>
       <c r="F111">
-        <v>41152</v>
+        <v>41161</v>
       </c>
       <c r="G111">
-        <v>59259</v>
+        <v>59272</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>91093</v>
+        <v>91135</v>
       </c>
       <c r="E112">
         <v>87102</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>106135</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>152834</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>53442</v>
+        <v>53918</v>
       </c>
       <c r="E113">
         <v>87102</v>
       </c>
       <c r="F113">
-        <v>68442</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>98556</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85545</v>
+        <v>99698</v>
       </c>
       <c r="E115">
         <v>116142</v>
       </c>
       <c r="F115">
-        <v>100545</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>144785</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>169152</v>
+        <v>169259</v>
       </c>
       <c r="E116">
         <v>145182</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>184259</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>265333</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>44475</v>
+        <v>44345</v>
       </c>
       <c r="E118">
         <v>58062</v>
       </c>
       <c r="F118">
-        <v>59475</v>
+        <v>60394</v>
       </c>
       <c r="G118">
-        <v>85644</v>
+        <v>86967</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>16049</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>32182</v>
+        <v>33101</v>
       </c>
       <c r="E119">
         <v>58062</v>
       </c>
       <c r="F119">
-        <v>47182</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>67942</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>61275</v>
+        <v>61314</v>
       </c>
       <c r="E120">
         <v>79842</v>
       </c>
       <c r="F120">
-        <v>79452</v>
+        <v>76314</v>
       </c>
       <c r="G120">
-        <v>114411</v>
+        <v>109892</v>
       </c>
       <c r="H120">
-        <v>18177</v>
+        <v>15000</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>54073</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>79842</v>
       </c>
       <c r="F121">
-        <v>69073</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>99465</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>42253</v>
+        <v>44960</v>
       </c>
       <c r="E123">
         <v>90732</v>
       </c>
       <c r="F123">
-        <v>58287</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>83933</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>16034</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,19 +5833,19 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>13310</v>
       </c>
       <c r="E124">
         <v>43542</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>32657</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>47026</v>
       </c>
       <c r="H124">
-        <v>0</v>
+        <v>19347</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7391</v>
+        <v>8989</v>
       </c>
       <c r="E125">
         <v>43542</v>
       </c>
       <c r="F125">
-        <v>25938</v>
+        <v>26577</v>
       </c>
       <c r="G125">
-        <v>37351</v>
+        <v>38271</v>
       </c>
       <c r="H125">
-        <v>18547</v>
+        <v>17588</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>31646</v>
+        <v>31146</v>
       </c>
       <c r="E126">
         <v>58062</v>
       </c>
       <c r="F126">
-        <v>46646</v>
+        <v>46146</v>
       </c>
       <c r="G126">
-        <v>67170</v>
+        <v>66450</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20283</v>
+        <v>20296</v>
       </c>
       <c r="E129">
         <v>59496</v>
       </c>
       <c r="F129">
-        <v>37316</v>
+        <v>37322</v>
       </c>
       <c r="G129">
-        <v>53735</v>
+        <v>53744</v>
       </c>
       <c r="H129">
-        <v>17033</v>
+        <v>17026</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>36358</v>
+        <v>29963</v>
       </c>
       <c r="E131">
         <v>74125</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>46894</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>67527</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>16931</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37840</v>
+        <v>37864</v>
       </c>
       <c r="E133">
         <v>93309</v>
       </c>
       <c r="F133">
-        <v>57527</v>
+        <v>57536</v>
       </c>
       <c r="G133">
-        <v>82839</v>
+        <v>82852</v>
       </c>
       <c r="H133">
-        <v>19687</v>
+        <v>19672</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53616</v>
+        <v>53650</v>
       </c>
       <c r="E135">
         <v>88917</v>
       </c>
       <c r="F135">
-        <v>68616</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>98807</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>73599</v>
+        <v>72905</v>
       </c>
       <c r="E137">
         <v>127032</v>
       </c>
       <c r="F137">
-        <v>88599</v>
+        <v>87905</v>
       </c>
       <c r="G137">
-        <v>127583</v>
+        <v>126583</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91897</v>
+        <v>91955</v>
       </c>
       <c r="E139">
         <v>152442</v>
       </c>
       <c r="F139">
-        <v>106897</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>153932</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37540</v>
+        <v>37438</v>
       </c>
       <c r="E140">
         <v>90732</v>
       </c>
       <c r="F140">
-        <v>61845</v>
+        <v>61805</v>
       </c>
       <c r="G140">
-        <v>89057</v>
+        <v>88999</v>
       </c>
       <c r="H140">
-        <v>24305</v>
+        <v>24367</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>24995</v>
+        <v>23371</v>
       </c>
       <c r="E142">
         <v>90732</v>
       </c>
       <c r="F142">
-        <v>56749</v>
+        <v>52678</v>
       </c>
       <c r="G142">
-        <v>81719</v>
+        <v>75856</v>
       </c>
       <c r="H142">
-        <v>31754</v>
+        <v>29307</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,16 +6662,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>21749</v>
+        <v>17678</v>
       </c>
       <c r="E143">
         <v>90732</v>
       </c>
       <c r="F143">
-        <v>48749</v>
+        <v>44678</v>
       </c>
       <c r="G143">
-        <v>70199</v>
+        <v>64336</v>
       </c>
       <c r="H143">
         <v>27000</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>43750</v>
+        <v>45055</v>
       </c>
       <c r="E144">
         <v>90732</v>
@@ -6718,7 +6718,7 @@
         <v>97991</v>
       </c>
       <c r="H144">
-        <v>24299</v>
+        <v>22994</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>65278</v>
+        <v>65319</v>
       </c>
       <c r="E145">
         <v>90732</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>80319</v>
       </c>
       <c r="G145">
-        <v>0</v>
+        <v>115659</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,19 +6795,19 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>66759</v>
+        <v>66234</v>
       </c>
       <c r="E146">
         <v>90732</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>81234</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>116977</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I146" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36957</v>
+        <v>36981</v>
       </c>
       <c r="E148">
         <v>61692</v>
       </c>
       <c r="F148">
-        <v>64482</v>
+        <v>64512</v>
       </c>
       <c r="G148">
-        <v>92854</v>
+        <v>92897</v>
       </c>
       <c r="H148">
-        <v>27525</v>
+        <v>27531</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>41071</v>
+        <v>41097</v>
       </c>
       <c r="E149">
         <v>61692</v>
       </c>
       <c r="F149">
-        <v>56071</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>80742</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15413</v>
+        <v>15738</v>
       </c>
       <c r="E151">
         <v>54432</v>
       </c>
       <c r="F151">
-        <v>33394</v>
+        <v>33524</v>
       </c>
       <c r="G151">
-        <v>48087</v>
+        <v>48275</v>
       </c>
       <c r="H151">
-        <v>17981</v>
+        <v>17786</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37651</v>
+        <v>37675</v>
       </c>
       <c r="E152">
         <v>72582</v>
@@ -7070,7 +7070,7 @@
         <v>78389</v>
       </c>
       <c r="H152">
-        <v>16786</v>
+        <v>16762</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>35444</v>
+        <v>35467</v>
       </c>
       <c r="E153">
         <v>72582</v>
       </c>
       <c r="F153">
-        <v>50444</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>72639</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,16 +7148,16 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56941</v>
+        <v>56583</v>
       </c>
       <c r="E154">
         <v>72582</v>
       </c>
       <c r="F154">
-        <v>71941</v>
+        <v>71583</v>
       </c>
       <c r="G154">
-        <v>103595</v>
+        <v>103080</v>
       </c>
       <c r="H154">
         <v>15000</v>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>35428</v>
+        <v>34852</v>
       </c>
       <c r="E156">
         <v>59877</v>
       </c>
       <c r="F156">
-        <v>50428</v>
+        <v>50355</v>
       </c>
       <c r="G156">
-        <v>72616</v>
+        <v>72511</v>
       </c>
       <c r="H156">
-        <v>15000</v>
+        <v>15503</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11883</v>
+        <v>11701</v>
       </c>
       <c r="E157">
         <v>59877</v>
       </c>
       <c r="F157">
-        <v>34105</v>
+        <v>34032</v>
       </c>
       <c r="G157">
-        <v>49111</v>
+        <v>49006</v>
       </c>
       <c r="H157">
-        <v>22222</v>
+        <v>22331</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36185</v>
+        <v>36208</v>
       </c>
       <c r="E159">
         <v>83472</v>
       </c>
       <c r="F159">
-        <v>53028</v>
+        <v>53037</v>
       </c>
       <c r="G159">
-        <v>76360</v>
+        <v>76373</v>
       </c>
       <c r="H159">
-        <v>16843</v>
+        <v>16829</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>7775</v>
       </c>
       <c r="E160">
         <v>54450</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>38875</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>55980</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>8526</v>
+        <v>9099</v>
       </c>
       <c r="E161">
         <v>54450</v>
       </c>
       <c r="F161">
-        <v>30646</v>
+        <v>30875</v>
       </c>
       <c r="G161">
-        <v>44130</v>
+        <v>44460</v>
       </c>
       <c r="H161">
-        <v>22120</v>
+        <v>21776</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>9967</v>
       </c>
       <c r="E162">
         <v>72582</v>
       </c>
       <c r="F162">
-        <v>0</v>
+        <v>44967</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>64752</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9629</v>
+        <v>10629</v>
       </c>
       <c r="E163">
         <v>72582</v>
       </c>
       <c r="F163">
-        <v>36629</v>
+        <v>37629</v>
       </c>
       <c r="G163">
-        <v>52746</v>
+        <v>54186</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,7 +7591,7 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>68383</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>68063</v>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>22017</v>
+        <v>22031</v>
       </c>
       <c r="E165">
         <v>68063</v>
       </c>
       <c r="F165">
-        <v>41351</v>
+        <v>41357</v>
       </c>
       <c r="G165">
-        <v>59545</v>
+        <v>59554</v>
       </c>
       <c r="H165">
-        <v>19334</v>
+        <v>19326</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,7 +7679,7 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>91865</v>
+        <v>0</v>
       </c>
       <c r="E166">
         <v>102548</v>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>57351</v>
+        <v>57387</v>
       </c>
       <c r="E167">
         <v>102548</v>
       </c>
       <c r="F167">
-        <v>0</v>
+        <v>72387</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>104237</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>9015</v>
+        <v>9020</v>
       </c>
       <c r="E169">
         <v>72582</v>
       </c>
       <c r="F169">
-        <v>36015</v>
+        <v>36020</v>
       </c>
       <c r="G169">
-        <v>51862</v>
+        <v>51869</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>69060</v>
+        <v>59753</v>
       </c>
       <c r="E170">
         <v>108882</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>78898</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>113613</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>19145</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78942</v>
+        <v>78992</v>
       </c>
       <c r="E172">
         <v>145182</v>
       </c>
       <c r="F172">
-        <v>108345</v>
+        <v>102929</v>
       </c>
       <c r="G172">
-        <v>156017</v>
+        <v>148218</v>
       </c>
       <c r="H172">
-        <v>29403</v>
+        <v>23937</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>78958</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>145182</v>
       </c>
       <c r="F173">
-        <v>94204</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>135654</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>15246</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>46397</v>
+        <v>45386</v>
       </c>
       <c r="E174">
         <v>90732</v>
@@ -8045,7 +8045,7 @@
         <v>97991</v>
       </c>
       <c r="H174">
-        <v>21652</v>
+        <v>22663</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>67957</v>
+        <v>68000</v>
       </c>
       <c r="E175">
         <v>90732</v>
       </c>
       <c r="F175">
-        <v>82957</v>
+        <v>0</v>
       </c>
       <c r="G175">
-        <v>119458</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65751</v>
+        <v>65792</v>
       </c>
       <c r="E176">
         <v>90732</v>
       </c>
       <c r="F176">
-        <v>80751</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>116281</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26493</v>
+        <v>26509</v>
       </c>
       <c r="E178">
         <v>108882</v>
       </c>
       <c r="F178">
-        <v>53493</v>
+        <v>53509</v>
       </c>
       <c r="G178">
-        <v>77030</v>
+        <v>77053</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>24444</v>
+        <v>23450</v>
       </c>
       <c r="E180">
         <v>90732</v>
       </c>
       <c r="F180">
-        <v>51444</v>
+        <v>50450</v>
       </c>
       <c r="G180">
-        <v>74079</v>
+        <v>72648</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>100912</v>
       </c>
       <c r="E182">
         <v>127032</v>
       </c>
       <c r="F182">
-        <v>0</v>
+        <v>115912</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>166913</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64648</v>
+        <v>64689</v>
       </c>
       <c r="E183">
         <v>127032</v>
       </c>
       <c r="F183">
-        <v>81402</v>
+        <v>81418</v>
       </c>
       <c r="G183">
-        <v>117219</v>
+        <v>117242</v>
       </c>
       <c r="H183">
-        <v>16754</v>
+        <v>16729</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144976</v>
+        <v>0</v>
       </c>
       <c r="E184">
         <v>181482</v>
       </c>
       <c r="F184">
-        <v>179976</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>259165</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,7 +8561,7 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>189104</v>
+        <v>0</v>
       </c>
       <c r="E186">
         <v>235932</v>
@@ -8691,19 +8691,19 @@
         <v>17</v>
       </c>
       <c r="D189">
-        <v>307746</v>
+        <v>0</v>
       </c>
       <c r="E189">
         <v>362982</v>
       </c>
       <c r="F189">
-        <v>322746</v>
+        <v>0</v>
       </c>
       <c r="G189">
-        <v>464754</v>
+        <v>0</v>
       </c>
       <c r="H189">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I189" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29723</v>
+        <v>29742</v>
       </c>
       <c r="E190">
         <v>95269</v>
       </c>
       <c r="F190">
-        <v>64723</v>
+        <v>64742</v>
       </c>
       <c r="G190">
-        <v>93201</v>
+        <v>93228</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44648</v>
+        <v>74214</v>
       </c>
       <c r="E191">
         <v>95269</v>
       </c>
       <c r="F191">
-        <v>61014</v>
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>87860</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>16366</v>
+        <v>0</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41732</v>
+        <v>41507</v>
       </c>
       <c r="E192">
         <v>122494</v>
       </c>
       <c r="F192">
-        <v>76732</v>
+        <v>68507</v>
       </c>
       <c r="G192">
-        <v>110494</v>
+        <v>98650</v>
       </c>
       <c r="H192">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8868,19 +8868,19 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>145638</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>122494</v>
       </c>
       <c r="F193">
-        <v>160638</v>
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>231319</v>
+        <v>0</v>
       </c>
       <c r="H193">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I193" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,16 +8911,16 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>53505</v>
+        <v>24428</v>
       </c>
       <c r="E194">
         <v>149901</v>
       </c>
       <c r="F194">
-        <v>80505</v>
+        <v>51428</v>
       </c>
       <c r="G194">
-        <v>115927</v>
+        <v>74056</v>
       </c>
       <c r="H194">
         <v>27000</v>
@@ -8955,19 +8955,19 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>145638</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>122494</v>
       </c>
       <c r="F195">
-        <v>160638</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>231319</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I195" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>24018</v>
+        <v>13641</v>
       </c>
       <c r="E196">
         <v>72582</v>
       </c>
       <c r="F196">
-        <v>54437</v>
+        <v>40641</v>
       </c>
       <c r="G196">
-        <v>78389</v>
+        <v>58523</v>
       </c>
       <c r="H196">
-        <v>30419</v>
+        <v>27000</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32544</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>72582</v>
       </c>
       <c r="F197">
-        <v>47544</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>68463</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>26619</v>
+        <v>22141</v>
       </c>
       <c r="E198">
         <v>108882</v>
       </c>
       <c r="F198">
-        <v>53619</v>
+        <v>49141</v>
       </c>
       <c r="G198">
-        <v>77211</v>
+        <v>70763</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>126190</v>
+        <v>13389</v>
       </c>
       <c r="E200">
         <v>127032</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>46922</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>67568</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>33533</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11946</v>
+        <v>11922</v>
       </c>
       <c r="E201">
         <v>127032</v>
       </c>
       <c r="F201">
-        <v>38946</v>
+        <v>38922</v>
       </c>
       <c r="G201">
-        <v>56082</v>
+        <v>56048</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9266,19 +9266,19 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>22677</v>
       </c>
       <c r="E202">
         <v>145182</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>57677</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>83055</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I202" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>82787</v>
+        <v>82840</v>
       </c>
       <c r="E203">
         <v>145182</v>
       </c>
       <c r="F203">
-        <v>0</v>
+        <v>97840</v>
       </c>
       <c r="G203">
-        <v>0</v>
+        <v>140890</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>26998</v>
       </c>
       <c r="E204">
         <v>181482</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>53998</v>
       </c>
       <c r="G204">
-        <v>0</v>
+        <v>77757</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24066</v>
+        <v>19066</v>
       </c>
       <c r="E206">
         <v>58062</v>
       </c>
       <c r="F206">
-        <v>42166</v>
+        <v>42170</v>
       </c>
       <c r="G206">
-        <v>60719</v>
+        <v>60725</v>
       </c>
       <c r="H206">
-        <v>18100</v>
+        <v>23104</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13806</v>
+        <v>13815</v>
       </c>
       <c r="E207">
         <v>58062</v>
       </c>
       <c r="F207">
-        <v>34166</v>
+        <v>34170</v>
       </c>
       <c r="G207">
-        <v>49199</v>
+        <v>49205</v>
       </c>
       <c r="H207">
-        <v>20360</v>
+        <v>20355</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9578,19 +9578,19 @@
         <v>17</v>
       </c>
       <c r="D209">
-        <v>23057</v>
+        <v>0</v>
       </c>
       <c r="E209">
         <v>54432</v>
       </c>
       <c r="F209">
-        <v>38057</v>
+        <v>0</v>
       </c>
       <c r="G209">
-        <v>54802</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I209" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40472</v>
+        <v>0</v>
       </c>
       <c r="E211">
         <v>108882</v>
       </c>
       <c r="F211">
-        <v>64653</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>93100</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>24181</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83780</v>
+        <v>83833</v>
       </c>
       <c r="E213">
         <v>181482</v>
       </c>
       <c r="F213">
-        <v>110290</v>
+        <v>110311</v>
       </c>
       <c r="G213">
-        <v>158818</v>
+        <v>158848</v>
       </c>
       <c r="H213">
-        <v>26510</v>
+        <v>26478</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,16 +9792,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28652</v>
+        <v>28654</v>
       </c>
       <c r="E214">
         <v>87102</v>
       </c>
       <c r="F214">
-        <v>55652</v>
+        <v>55654</v>
       </c>
       <c r="G214">
-        <v>80139</v>
+        <v>80142</v>
       </c>
       <c r="H214">
         <v>27000</v>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45909</v>
+        <v>45938</v>
       </c>
       <c r="E216">
         <v>101622</v>
       </c>
       <c r="F216">
-        <v>76217</v>
+        <v>70105</v>
       </c>
       <c r="G216">
-        <v>109752</v>
+        <v>100951</v>
       </c>
       <c r="H216">
-        <v>30308</v>
+        <v>24167</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>89375</v>
+        <v>0</v>
       </c>
       <c r="E217">
         <v>101622</v>
       </c>
       <c r="F217">
-        <v>104375</v>
+        <v>0</v>
       </c>
       <c r="G217">
-        <v>150300</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>111392</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>130662</v>
       </c>
       <c r="F219">
-        <v>126392</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>182004</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>62709</v>
+        <v>62749</v>
       </c>
       <c r="E220">
         <v>81675</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>77749</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>111959</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>51740</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>81675</v>
       </c>
       <c r="F221">
-        <v>66740</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>96106</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74687</v>
+        <v>75381</v>
       </c>
       <c r="E222">
         <v>96195</v>
       </c>
       <c r="F222">
-        <v>109687</v>
+        <v>90381</v>
       </c>
       <c r="G222">
-        <v>157949</v>
+        <v>130149</v>
       </c>
       <c r="H222">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,7 +10195,7 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>93268</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>96195</v>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>30306</v>
+        <v>16606</v>
       </c>
       <c r="E224">
         <v>59877</v>
       </c>
       <c r="F224">
-        <v>45306</v>
+        <v>44908</v>
       </c>
       <c r="G224">
-        <v>65241</v>
+        <v>64668</v>
       </c>
       <c r="H224">
-        <v>15000</v>
+        <v>28302</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10417</v>
+        <v>10424</v>
       </c>
       <c r="E225">
         <v>59877</v>
       </c>
       <c r="F225">
-        <v>33519</v>
+        <v>33522</v>
       </c>
       <c r="G225">
-        <v>48267</v>
+        <v>48272</v>
       </c>
       <c r="H225">
-        <v>23102</v>
+        <v>23098</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10461,19 +10461,19 @@
         <v>17</v>
       </c>
       <c r="D229">
-        <v>13380</v>
+        <v>0</v>
       </c>
       <c r="E229">
         <v>108882</v>
       </c>
       <c r="F229">
-        <v>40380</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>58147</v>
+        <v>0</v>
       </c>
       <c r="H229">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I229" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,16 +10546,16 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19274</v>
+        <v>19287</v>
       </c>
       <c r="E231">
         <v>181482</v>
       </c>
       <c r="F231">
-        <v>46274</v>
+        <v>46287</v>
       </c>
       <c r="G231">
-        <v>66635</v>
+        <v>66653</v>
       </c>
       <c r="H231">
         <v>27000</v>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>9415</v>
       </c>
       <c r="E232">
         <v>52635</v>
       </c>
       <c r="F232">
-        <v>0</v>
+        <v>34528</v>
       </c>
       <c r="G232">
-        <v>0</v>
+        <v>49720</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>25113</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>10023</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>52635</v>
       </c>
       <c r="F233">
-        <v>30537</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>43973</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>20514</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,19 +10677,19 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>24649</v>
+        <v>11954</v>
       </c>
       <c r="E234">
         <v>70785</v>
       </c>
       <c r="F234">
-        <v>47713</v>
+        <v>38954</v>
       </c>
       <c r="G234">
-        <v>68707</v>
+        <v>56094</v>
       </c>
       <c r="H234">
-        <v>23064</v>
+        <v>27000</v>
       </c>
       <c r="I234" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>8484</v>
       </c>
       <c r="E236">
         <v>52635</v>
       </c>
       <c r="F236">
-        <v>0</v>
+        <v>37253</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>53644</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>28769</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6871</v>
+        <v>6813</v>
       </c>
       <c r="E237">
         <v>52635</v>
       </c>
       <c r="F237">
-        <v>29276</v>
+        <v>29253</v>
       </c>
       <c r="G237">
-        <v>42157</v>
+        <v>42124</v>
       </c>
       <c r="H237">
-        <v>22405</v>
+        <v>22440</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11410</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>52635</v>
       </c>
       <c r="F239">
-        <v>31092</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>44772</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>19682</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,16 +10985,16 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70258</v>
+        <v>70145</v>
       </c>
       <c r="E241">
         <v>70785</v>
       </c>
       <c r="F241">
-        <v>85258</v>
+        <v>85145</v>
       </c>
       <c r="G241">
-        <v>122772</v>
+        <v>122609</v>
       </c>
       <c r="H241">
         <v>15000</v>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34231</v>
+        <v>34252</v>
       </c>
       <c r="E242">
         <v>70785</v>
       </c>
       <c r="F242">
-        <v>51546</v>
+        <v>51554</v>
       </c>
       <c r="G242">
-        <v>74226</v>
+        <v>74238</v>
       </c>
       <c r="H242">
-        <v>17315</v>
+        <v>17302</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>9904</v>
       </c>
       <c r="E244">
         <v>27225</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>24904</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>35862</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11204,19 +11204,19 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>108161</v>
+        <v>11922</v>
       </c>
       <c r="E246">
         <v>108882</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>38922</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>56048</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I246" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>67784</v>
+        <v>59090</v>
       </c>
       <c r="E248">
         <v>96195</v>
       </c>
       <c r="F248">
-        <v>0</v>
+        <v>74090</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>106690</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,16 +11337,16 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48462</v>
+        <v>48177</v>
       </c>
       <c r="E249">
         <v>96195</v>
       </c>
       <c r="F249">
-        <v>63462</v>
+        <v>63177</v>
       </c>
       <c r="G249">
-        <v>91385</v>
+        <v>90975</v>
       </c>
       <c r="H249">
         <v>15000</v>
@@ -11380,16 +11380,16 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>71566</v>
+        <v>71375</v>
       </c>
       <c r="E250">
         <v>108882</v>
       </c>
       <c r="F250">
-        <v>86566</v>
+        <v>86375</v>
       </c>
       <c r="G250">
-        <v>124655</v>
+        <v>124380</v>
       </c>
       <c r="H250">
         <v>15000</v>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>34294</v>
+        <v>11938</v>
       </c>
       <c r="E252">
         <v>52635</v>
       </c>
       <c r="F252">
-        <v>49294</v>
+        <v>34528</v>
       </c>
       <c r="G252">
-        <v>70983</v>
+        <v>49720</v>
       </c>
       <c r="H252">
-        <v>15000</v>
+        <v>22590</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>25248</v>
+        <v>16937</v>
       </c>
       <c r="E254">
         <v>70785</v>
       </c>
       <c r="F254">
-        <v>47953</v>
+        <v>43937</v>
       </c>
       <c r="G254">
-        <v>69052</v>
+        <v>63269</v>
       </c>
       <c r="H254">
-        <v>22705</v>
+        <v>27000</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12561</v>
+        <v>12569</v>
       </c>
       <c r="E259">
         <v>50802</v>
       </c>
       <c r="F259">
-        <v>30837</v>
+        <v>30840</v>
       </c>
       <c r="G259">
-        <v>44405</v>
+        <v>44410</v>
       </c>
       <c r="H259">
-        <v>18276</v>
+        <v>18271</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,19 +11862,19 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62725</v>
+        <v>62765</v>
       </c>
       <c r="E261">
         <v>63507</v>
       </c>
       <c r="F261">
-        <v>0</v>
+        <v>77765</v>
       </c>
       <c r="G261">
-        <v>0</v>
+        <v>111982</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I261" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11948,19 +11948,19 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75459</v>
+        <v>75507</v>
       </c>
       <c r="E263">
         <v>72582</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>90507</v>
       </c>
       <c r="G263">
-        <v>0</v>
+        <v>130330</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I263" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>40314</v>
+        <v>40560</v>
       </c>
       <c r="E264">
         <v>59877</v>
       </c>
       <c r="F264">
-        <v>55314</v>
+        <v>0</v>
       </c>
       <c r="G264">
-        <v>79652</v>
+        <v>0</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,19 +12038,19 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>26540</v>
+        <v>27361</v>
       </c>
       <c r="E265">
         <v>59877</v>
       </c>
       <c r="F265">
-        <v>0</v>
+        <v>42361</v>
       </c>
       <c r="G265">
-        <v>0</v>
+        <v>61000</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I265" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34987</v>
+        <v>35009</v>
       </c>
       <c r="E268">
         <v>59877</v>
       </c>
       <c r="F268">
-        <v>49987</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>71981</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23151</v>
+        <v>23072</v>
       </c>
       <c r="E269">
         <v>59877</v>
       </c>
       <c r="F269">
-        <v>38612</v>
+        <v>38581</v>
       </c>
       <c r="G269">
-        <v>55601</v>
+        <v>55557</v>
       </c>
       <c r="H269">
-        <v>15461</v>
+        <v>15509</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>29266</v>
+        <v>0</v>
       </c>
       <c r="E271">
         <v>67137</v>
       </c>
       <c r="F271">
-        <v>44266</v>
+        <v>0</v>
       </c>
       <c r="G271">
-        <v>63743</v>
+        <v>0</v>
       </c>
       <c r="H271">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71440</v>
+        <v>71470</v>
       </c>
       <c r="E272">
         <v>90732</v>
       </c>
       <c r="F272">
-        <v>86440</v>
+        <v>0</v>
       </c>
       <c r="G272">
-        <v>124474</v>
+        <v>0</v>
       </c>
       <c r="H272">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21292</v>
+        <v>21305</v>
       </c>
       <c r="E273">
         <v>90732</v>
       </c>
       <c r="F273">
-        <v>48292</v>
+        <v>48305</v>
       </c>
       <c r="G273">
-        <v>69540</v>
+        <v>69559</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>57997</v>
+        <v>17347</v>
       </c>
       <c r="E274">
         <v>127032</v>
       </c>
       <c r="F274">
-        <v>85645</v>
+        <v>52347</v>
       </c>
       <c r="G274">
-        <v>123329</v>
+        <v>75380</v>
       </c>
       <c r="H274">
-        <v>27648</v>
+        <v>35000</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12907</v>
+        <v>12916</v>
       </c>
       <c r="E275">
         <v>127032</v>
       </c>
       <c r="F275">
-        <v>39907</v>
+        <v>39916</v>
       </c>
       <c r="G275">
-        <v>57466</v>
+        <v>57479</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152856</v>
+        <v>153095</v>
       </c>
       <c r="E276">
         <v>163332</v>
       </c>
       <c r="F276">
-        <v>167856</v>
+        <v>0</v>
       </c>
       <c r="G276">
-        <v>241713</v>
+        <v>0</v>
       </c>
       <c r="H276">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>102408</v>
+        <v>0</v>
       </c>
       <c r="E277">
         <v>163332</v>
       </c>
       <c r="F277">
-        <v>117408</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>169068</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>48036</v>
+        <v>50653</v>
       </c>
       <c r="E278">
         <v>108882</v>
       </c>
       <c r="F278">
-        <v>78389</v>
+        <v>78402</v>
       </c>
       <c r="G278">
-        <v>112880</v>
+        <v>112899</v>
       </c>
       <c r="H278">
-        <v>30353</v>
+        <v>27749</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49250</v>
+        <v>49281</v>
       </c>
       <c r="E279">
         <v>108882</v>
       </c>
       <c r="F279">
-        <v>68164</v>
+        <v>68176</v>
       </c>
       <c r="G279">
-        <v>98156</v>
+        <v>98173</v>
       </c>
       <c r="H279">
-        <v>18914</v>
+        <v>18895</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,7 +12701,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>62678</v>
+        <v>63979</v>
       </c>
       <c r="E280">
         <v>127032</v>
@@ -12713,7 +12713,7 @@
         <v>137195</v>
       </c>
       <c r="H280">
-        <v>32596</v>
+        <v>31295</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,19 +12747,19 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>106081</v>
+        <v>106148</v>
       </c>
       <c r="E281">
         <v>127032</v>
       </c>
       <c r="F281">
-        <v>0</v>
+        <v>121148</v>
       </c>
       <c r="G281">
-        <v>0</v>
+        <v>174453</v>
       </c>
       <c r="H281">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I281" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>23371</v>
       </c>
       <c r="E282">
         <v>54432</v>
       </c>
       <c r="F282">
-        <v>0</v>
+        <v>39843</v>
       </c>
       <c r="G282">
-        <v>0</v>
+        <v>57374</v>
       </c>
       <c r="H282">
-        <v>0</v>
+        <v>16472</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>66097</v>
+        <v>66139</v>
       </c>
       <c r="E284">
         <v>81675</v>
       </c>
       <c r="F284">
-        <v>81097</v>
+        <v>0</v>
       </c>
       <c r="G284">
-        <v>116780</v>
+        <v>0</v>
       </c>
       <c r="H284">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20441</v>
+        <v>20454</v>
       </c>
       <c r="E287">
         <v>38097</v>
       </c>
       <c r="F287">
-        <v>35441</v>
+        <v>0</v>
       </c>
       <c r="G287">
-        <v>51035</v>
+        <v>0</v>
       </c>
       <c r="H287">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31977</v>
+        <v>32502</v>
       </c>
       <c r="E288">
         <v>58062</v>
       </c>
       <c r="F288">
-        <v>48689</v>
+        <v>62788</v>
       </c>
       <c r="G288">
-        <v>70112</v>
+        <v>90415</v>
       </c>
       <c r="H288">
-        <v>16712</v>
+        <v>30286</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>25689</v>
+        <v>39598</v>
       </c>
       <c r="E289">
         <v>58062</v>
       </c>
       <c r="F289">
-        <v>40689</v>
+        <v>0</v>
       </c>
       <c r="G289">
-        <v>58592</v>
+        <v>0</v>
       </c>
       <c r="H289">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13143,19 +13143,19 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>10629</v>
       </c>
       <c r="E290">
         <v>43542</v>
       </c>
       <c r="F290">
-        <v>0</v>
+        <v>32657</v>
       </c>
       <c r="G290">
-        <v>0</v>
+        <v>47026</v>
       </c>
       <c r="H290">
-        <v>0</v>
+        <v>22028</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>34278</v>
+        <v>45654</v>
       </c>
       <c r="E291">
         <v>43542</v>
       </c>
       <c r="F291">
-        <v>49278</v>
+        <v>0</v>
       </c>
       <c r="G291">
-        <v>70960</v>
+        <v>0</v>
       </c>
       <c r="H291">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>38155</v>
+        <v>38179</v>
       </c>
       <c r="E293">
         <v>108882</v>
       </c>
       <c r="F293">
-        <v>63726</v>
+        <v>63735</v>
       </c>
       <c r="G293">
-        <v>91765</v>
+        <v>91778</v>
       </c>
       <c r="H293">
-        <v>25571</v>
+        <v>25556</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>54010</v>
+        <v>0</v>
       </c>
       <c r="E296">
         <v>72582</v>
       </c>
       <c r="F296">
-        <v>89010</v>
+        <v>0</v>
       </c>
       <c r="G296">
-        <v>128174</v>
+        <v>0</v>
       </c>
       <c r="H296">
-        <v>35000</v>
+        <v>0</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>64711</v>
+        <v>0</v>
       </c>
       <c r="E297">
         <v>72582</v>
       </c>
       <c r="F297">
-        <v>79711</v>
+        <v>0</v>
       </c>
       <c r="G297">
-        <v>114784</v>
+        <v>0</v>
       </c>
       <c r="H297">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>4747</v>
       </c>
       <c r="E299">
         <v>54432</v>
       </c>
       <c r="F299">
-        <v>0</v>
+        <v>29127</v>
       </c>
       <c r="G299">
-        <v>0</v>
+        <v>41943</v>
       </c>
       <c r="H299">
-        <v>0</v>
+        <v>24380</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>24192</v>
+        <v>20895</v>
       </c>
       <c r="E302">
         <v>90732</v>
       </c>
       <c r="F302">
-        <v>51192</v>
+        <v>47895</v>
       </c>
       <c r="G302">
-        <v>73716</v>
+        <v>68969</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,16 +13756,16 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>37698</v>
+        <v>39551</v>
       </c>
       <c r="E304">
         <v>108882</v>
       </c>
       <c r="F304">
-        <v>64698</v>
+        <v>66551</v>
       </c>
       <c r="G304">
-        <v>93165</v>
+        <v>95833</v>
       </c>
       <c r="H304">
         <v>27000</v>
@@ -13844,16 +13844,16 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>24444</v>
+        <v>23876</v>
       </c>
       <c r="E306">
         <v>108882</v>
       </c>
       <c r="F306">
-        <v>59444</v>
+        <v>58876</v>
       </c>
       <c r="G306">
-        <v>85599</v>
+        <v>84781</v>
       </c>
       <c r="H306">
         <v>35000</v>
@@ -13889,16 +13889,16 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33553</v>
+        <v>33574</v>
       </c>
       <c r="E307">
         <v>108882</v>
       </c>
       <c r="F307">
-        <v>60553</v>
+        <v>60574</v>
       </c>
       <c r="G307">
-        <v>87196</v>
+        <v>87227</v>
       </c>
       <c r="H307">
         <v>27000</v>
@@ -13932,19 +13932,19 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>185653</v>
+        <v>185771</v>
       </c>
       <c r="E308">
         <v>235932</v>
       </c>
       <c r="F308">
-        <v>0</v>
+        <v>200771</v>
       </c>
       <c r="G308">
-        <v>0</v>
+        <v>289110</v>
       </c>
       <c r="H308">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I308" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>65703</v>
+        <v>65367</v>
       </c>
       <c r="E310">
         <v>127032</v>
       </c>
       <c r="F310">
-        <v>89446</v>
+        <v>89311</v>
       </c>
       <c r="G310">
-        <v>128802</v>
+        <v>128608</v>
       </c>
       <c r="H310">
-        <v>23743</v>
+        <v>23944</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>54138</v>
       </c>
       <c r="E311">
         <v>127032</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>77198</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>111165</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>23060</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,19 +14192,19 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>124993</v>
+        <v>125072</v>
       </c>
       <c r="E314">
         <v>235932</v>
       </c>
       <c r="F314">
-        <v>159993</v>
+        <v>152072</v>
       </c>
       <c r="G314">
-        <v>230390</v>
+        <v>218984</v>
       </c>
       <c r="H314">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I314" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14235,19 +14235,19 @@
         <v>17</v>
       </c>
       <c r="D315">
-        <v>148601</v>
+        <v>0</v>
       </c>
       <c r="E315">
         <v>235932</v>
       </c>
       <c r="F315">
-        <v>163601</v>
+        <v>0</v>
       </c>
       <c r="G315">
-        <v>235585</v>
+        <v>0</v>
       </c>
       <c r="H315">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I315" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72148</v>
+        <v>72102</v>
       </c>
       <c r="E2">
         <v>72582</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>87102</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>125427</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46742</v>
+        <v>46713</v>
       </c>
       <c r="E3">
         <v>72582</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>61713</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>88867</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -571,16 +571,16 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>82430</v>
+        <v>82378</v>
       </c>
       <c r="E4">
         <v>83472</v>
       </c>
       <c r="F4">
-        <v>97430</v>
+        <v>97378</v>
       </c>
       <c r="G4">
-        <v>140299</v>
+        <v>140224</v>
       </c>
       <c r="H4">
         <v>15000</v>
@@ -617,16 +617,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>84827</v>
+        <v>84773</v>
       </c>
       <c r="E5">
         <v>83472</v>
       </c>
       <c r="F5">
-        <v>99827</v>
+        <v>99773</v>
       </c>
       <c r="G5">
-        <v>143751</v>
+        <v>143673</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>3611</v>
+        <v>3609</v>
       </c>
       <c r="E7">
         <v>54432</v>
       </c>
       <c r="F7">
-        <v>28673</v>
+        <v>28672</v>
       </c>
       <c r="G7">
-        <v>41289</v>
+        <v>41288</v>
       </c>
       <c r="H7">
-        <v>25062</v>
+        <v>25063</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>36050</v>
+        <v>34451</v>
       </c>
       <c r="E8">
         <v>72582</v>
       </c>
       <c r="F8">
-        <v>53082</v>
+        <v>52443</v>
       </c>
       <c r="G8">
-        <v>76438</v>
+        <v>75518</v>
       </c>
       <c r="H8">
-        <v>17032</v>
+        <v>17992</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -836,19 +836,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>53445</v>
+        <v>53442</v>
       </c>
       <c r="E10">
         <v>108882</v>
       </c>
       <c r="F10">
-        <v>76375</v>
+        <v>76374</v>
       </c>
       <c r="G10">
-        <v>109980</v>
+        <v>109979</v>
       </c>
       <c r="H10">
-        <v>22930</v>
+        <v>22932</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>79087</v>
+        <v>79036</v>
       </c>
       <c r="E12">
         <v>81657</v>
       </c>
       <c r="F12">
-        <v>97114</v>
+        <v>97106</v>
       </c>
       <c r="G12">
-        <v>139844</v>
+        <v>139833</v>
       </c>
       <c r="H12">
-        <v>18027</v>
+        <v>18070</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11796</v>
+        <v>11788</v>
       </c>
       <c r="E13">
         <v>81657</v>
       </c>
       <c r="F13">
-        <v>38796</v>
+        <v>38788</v>
       </c>
       <c r="G13">
-        <v>55866</v>
+        <v>55855</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,16 +1056,16 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>44976</v>
+        <v>44948</v>
       </c>
       <c r="E15">
         <v>72582</v>
       </c>
       <c r="F15">
-        <v>59976</v>
+        <v>59948</v>
       </c>
       <c r="G15">
-        <v>86365</v>
+        <v>86325</v>
       </c>
       <c r="H15">
         <v>15000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>34126</v>
+        <v>33963</v>
       </c>
       <c r="E21">
         <v>101622</v>
       </c>
       <c r="F21">
-        <v>59283</v>
+        <v>59218</v>
       </c>
       <c r="G21">
-        <v>85368</v>
+        <v>85274</v>
       </c>
       <c r="H21">
-        <v>25157</v>
+        <v>25255</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20217</v>
+        <v>20204</v>
       </c>
       <c r="E27">
         <v>63507</v>
       </c>
       <c r="F27">
-        <v>38855</v>
+        <v>38850</v>
       </c>
       <c r="G27">
-        <v>55951</v>
+        <v>55944</v>
       </c>
       <c r="H27">
-        <v>18638</v>
+        <v>18646</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75065</v>
+        <v>75018</v>
       </c>
       <c r="E28">
         <v>127032</v>
       </c>
       <c r="F28">
-        <v>95062</v>
+        <v>95043</v>
       </c>
       <c r="G28">
-        <v>136889</v>
+        <v>136862</v>
       </c>
       <c r="H28">
-        <v>19997</v>
+        <v>20025</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>29017</v>
+        <v>28998</v>
       </c>
       <c r="E29">
         <v>127032</v>
       </c>
       <c r="F29">
-        <v>56017</v>
+        <v>55998</v>
       </c>
       <c r="G29">
-        <v>80664</v>
+        <v>80637</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,16 +1709,16 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>126113</v>
+        <v>126080</v>
       </c>
       <c r="E30">
         <v>181482</v>
       </c>
       <c r="F30">
-        <v>141113</v>
+        <v>141080</v>
       </c>
       <c r="G30">
-        <v>203203</v>
+        <v>203155</v>
       </c>
       <c r="H30">
         <v>15000</v>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>78298</v>
+        <v>78248</v>
       </c>
       <c r="E31">
         <v>181482</v>
       </c>
       <c r="F31">
-        <v>105298</v>
+        <v>105248</v>
       </c>
       <c r="G31">
-        <v>151629</v>
+        <v>151557</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72684</v>
+        <v>72638</v>
       </c>
       <c r="E32">
         <v>108882</v>
       </c>
       <c r="F32">
-        <v>96283</v>
+        <v>96271</v>
       </c>
       <c r="G32">
-        <v>138648</v>
+        <v>138630</v>
       </c>
       <c r="H32">
-        <v>23599</v>
+        <v>23633</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>47736</v>
+        <v>47706</v>
       </c>
       <c r="E33">
         <v>108882</v>
       </c>
       <c r="F33">
-        <v>67558</v>
+        <v>67546</v>
       </c>
       <c r="G33">
-        <v>97284</v>
+        <v>97266</v>
       </c>
       <c r="H33">
-        <v>19822</v>
+        <v>19840</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>43841</v>
+        <v>45531</v>
       </c>
       <c r="E36">
         <v>127032</v>
       </c>
       <c r="F36">
-        <v>70841</v>
+        <v>72531</v>
       </c>
       <c r="G36">
-        <v>102011</v>
+        <v>104445</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>65177</v>
+        <v>64963</v>
       </c>
       <c r="E38">
         <v>235932</v>
       </c>
       <c r="F38">
-        <v>92177</v>
+        <v>91963</v>
       </c>
       <c r="G38">
-        <v>132735</v>
+        <v>132427</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2156,16 +2156,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>84338</v>
+        <v>84348</v>
       </c>
       <c r="E40">
         <v>235932</v>
       </c>
       <c r="F40">
-        <v>111338</v>
+        <v>111348</v>
       </c>
       <c r="G40">
-        <v>160327</v>
+        <v>160341</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38999</v>
+        <v>38974</v>
       </c>
       <c r="E43">
         <v>127032</v>
       </c>
       <c r="F43">
-        <v>65999</v>
+        <v>65974</v>
       </c>
       <c r="G43">
-        <v>95039</v>
+        <v>95003</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27645</v>
+        <v>27659</v>
       </c>
       <c r="E47">
         <v>108882</v>
       </c>
       <c r="F47">
-        <v>54645</v>
+        <v>54659</v>
       </c>
       <c r="G47">
-        <v>78689</v>
+        <v>78709</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>36255</v>
+        <v>37682</v>
       </c>
       <c r="E50">
         <v>63507</v>
       </c>
       <c r="F50">
-        <v>58940</v>
+        <v>58917</v>
       </c>
       <c r="G50">
-        <v>84874</v>
+        <v>84840</v>
       </c>
       <c r="H50">
-        <v>22685</v>
+        <v>21235</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>35940</v>
+        <v>35917</v>
       </c>
       <c r="E51">
         <v>63507</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>50917</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>73320</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2677,19 +2677,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>50133</v>
+        <v>61685</v>
       </c>
       <c r="E52">
         <v>76212</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>76685</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>110426</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>69987</v>
+        <v>69943</v>
       </c>
       <c r="E53">
         <v>76212</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>84943</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>122318</v>
       </c>
       <c r="H53">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>54091</v>
+        <v>49155</v>
       </c>
       <c r="E54">
         <v>127032</v>
       </c>
       <c r="F54">
-        <v>88016</v>
+        <v>84155</v>
       </c>
       <c r="G54">
-        <v>126743</v>
+        <v>121183</v>
       </c>
       <c r="H54">
-        <v>33925</v>
+        <v>35000</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52483</v>
+        <v>52449</v>
       </c>
       <c r="E55">
         <v>127032</v>
       </c>
       <c r="F55">
-        <v>76536</v>
+        <v>76522</v>
       </c>
       <c r="G55">
-        <v>110212</v>
+        <v>110192</v>
       </c>
       <c r="H55">
-        <v>24053</v>
+        <v>24073</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,16 +2857,16 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53445</v>
+        <v>53411</v>
       </c>
       <c r="E56">
         <v>145182</v>
       </c>
       <c r="F56">
-        <v>80445</v>
+        <v>80411</v>
       </c>
       <c r="G56">
-        <v>115841</v>
+        <v>115792</v>
       </c>
       <c r="H56">
         <v>27000</v>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>63112</v>
+        <v>63072</v>
       </c>
       <c r="E57">
         <v>145182</v>
       </c>
       <c r="F57">
-        <v>87866</v>
+        <v>87850</v>
       </c>
       <c r="G57">
-        <v>126527</v>
+        <v>126504</v>
       </c>
       <c r="H57">
-        <v>24754</v>
+        <v>24778</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23387</v>
+        <v>23278</v>
       </c>
       <c r="E58">
         <v>36282</v>
       </c>
       <c r="F58">
-        <v>38387</v>
+        <v>38386</v>
       </c>
       <c r="G58">
-        <v>55277</v>
+        <v>55276</v>
       </c>
       <c r="H58">
-        <v>15000</v>
+        <v>15108</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6261</v>
+        <v>6257</v>
       </c>
       <c r="E59">
         <v>36282</v>
       </c>
       <c r="F59">
-        <v>22654</v>
+        <v>22653</v>
       </c>
       <c r="G59">
-        <v>32622</v>
+        <v>32620</v>
       </c>
       <c r="H59">
-        <v>16393</v>
+        <v>16396</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,16 +3036,16 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26683</v>
+        <v>26666</v>
       </c>
       <c r="E60">
         <v>48987</v>
       </c>
       <c r="F60">
-        <v>41683</v>
+        <v>41666</v>
       </c>
       <c r="G60">
-        <v>60024</v>
+        <v>59999</v>
       </c>
       <c r="H60">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>13878</v>
+        <v>12923</v>
       </c>
       <c r="E63">
         <v>81657</v>
       </c>
       <c r="F63">
-        <v>40878</v>
+        <v>39923</v>
       </c>
       <c r="G63">
-        <v>58864</v>
+        <v>57489</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>27708</v>
+        <v>27564</v>
       </c>
       <c r="E65">
         <v>122476</v>
       </c>
       <c r="F65">
-        <v>54708</v>
+        <v>54564</v>
       </c>
       <c r="G65">
-        <v>78780</v>
+        <v>78572</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>24002</v>
+        <v>23908</v>
       </c>
       <c r="E66">
         <v>90732</v>
       </c>
       <c r="F66">
-        <v>53624</v>
+        <v>53613</v>
       </c>
       <c r="G66">
-        <v>77219</v>
+        <v>77203</v>
       </c>
       <c r="H66">
-        <v>29622</v>
+        <v>29705</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18624</v>
+        <v>18613</v>
       </c>
       <c r="E67">
         <v>90732</v>
       </c>
       <c r="F67">
-        <v>45624</v>
+        <v>45613</v>
       </c>
       <c r="G67">
-        <v>65699</v>
+        <v>65683</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,16 +3385,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34662</v>
+        <v>34640</v>
       </c>
       <c r="E68">
         <v>108882</v>
       </c>
       <c r="F68">
-        <v>61662</v>
+        <v>61640</v>
       </c>
       <c r="G68">
-        <v>88793</v>
+        <v>88762</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3474,16 +3474,16 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>107930</v>
+        <v>107861</v>
       </c>
       <c r="E70">
         <v>127032</v>
       </c>
       <c r="F70">
-        <v>122930</v>
+        <v>122861</v>
       </c>
       <c r="G70">
-        <v>177019</v>
+        <v>176920</v>
       </c>
       <c r="H70">
         <v>15000</v>
@@ -3605,19 +3605,19 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>5866</v>
+        <v>6083</v>
       </c>
       <c r="E73">
         <v>27207</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>21083</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>30360</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I73" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/381210/Dead_by_Daylight/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86167</v>
+        <v>86097</v>
       </c>
       <c r="E76">
         <v>127032</v>
       </c>
       <c r="F76">
-        <v>101167</v>
+        <v>101137</v>
       </c>
       <c r="G76">
-        <v>145680</v>
+        <v>145637</v>
       </c>
       <c r="H76">
-        <v>15000</v>
+        <v>15040</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47247</v>
+        <v>47217</v>
       </c>
       <c r="E77">
         <v>127032</v>
       </c>
       <c r="F77">
-        <v>74247</v>
+        <v>74217</v>
       </c>
       <c r="G77">
-        <v>106916</v>
+        <v>106872</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37233</v>
+        <v>37209</v>
       </c>
       <c r="E81">
         <v>90732</v>
       </c>
       <c r="F81">
-        <v>56279</v>
+        <v>56269</v>
       </c>
       <c r="G81">
-        <v>81042</v>
+        <v>81027</v>
       </c>
       <c r="H81">
-        <v>19046</v>
+        <v>19060</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>85095</v>
+        <v>85041</v>
       </c>
       <c r="E83">
         <v>127032</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>100041</v>
       </c>
       <c r="G83">
-        <v>0</v>
+        <v>144059</v>
       </c>
       <c r="H83">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48603</v>
+        <v>48572</v>
       </c>
       <c r="E84">
         <v>101622</v>
       </c>
       <c r="F84">
-        <v>71171</v>
+        <v>71163</v>
       </c>
       <c r="G84">
-        <v>102486</v>
+        <v>102475</v>
       </c>
       <c r="H84">
-        <v>22568</v>
+        <v>22591</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32123</v>
+        <v>32103</v>
       </c>
       <c r="E85">
         <v>101622</v>
       </c>
       <c r="F85">
-        <v>58482</v>
+        <v>58474</v>
       </c>
       <c r="G85">
-        <v>84214</v>
+        <v>84203</v>
       </c>
       <c r="H85">
-        <v>26359</v>
+        <v>26371</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,16 +4171,16 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>151581</v>
+        <v>151485</v>
       </c>
       <c r="E86">
         <v>145182</v>
       </c>
       <c r="F86">
-        <v>166581</v>
+        <v>166485</v>
       </c>
       <c r="G86">
-        <v>239877</v>
+        <v>239738</v>
       </c>
       <c r="H86">
         <v>15000</v>
@@ -4258,16 +4258,16 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>171183</v>
+        <v>171075</v>
       </c>
       <c r="E88">
         <v>159702</v>
       </c>
       <c r="F88">
-        <v>186183</v>
+        <v>186075</v>
       </c>
       <c r="G88">
-        <v>268104</v>
+        <v>267948</v>
       </c>
       <c r="H88">
         <v>15000</v>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127374</v>
+        <v>127294</v>
       </c>
       <c r="E89">
         <v>159702</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>142294</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>204903</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>7790</v>
+        <v>7770</v>
       </c>
       <c r="E90">
         <v>58062</v>
       </c>
       <c r="F90">
-        <v>38360</v>
+        <v>38359</v>
       </c>
       <c r="G90">
-        <v>55238</v>
+        <v>55237</v>
       </c>
       <c r="H90">
-        <v>30570</v>
+        <v>30589</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4289</v>
+        <v>4287</v>
       </c>
       <c r="E91">
         <v>58062</v>
       </c>
       <c r="F91">
-        <v>30360</v>
+        <v>30359</v>
       </c>
       <c r="G91">
-        <v>43718</v>
+        <v>43717</v>
       </c>
       <c r="H91">
-        <v>26071</v>
+        <v>26072</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,19 +4478,19 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12238</v>
+        <v>12230</v>
       </c>
       <c r="E93">
         <v>27207</v>
       </c>
       <c r="F93">
-        <v>0</v>
+        <v>27230</v>
       </c>
       <c r="G93">
-        <v>0</v>
+        <v>39211</v>
       </c>
       <c r="H93">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I93" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2592160/Dispatch/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>62023</v>
+        <v>61984</v>
       </c>
       <c r="E96">
         <v>81657</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>76984</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>110857</v>
       </c>
       <c r="H96">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33732</v>
+        <v>33711</v>
       </c>
       <c r="E97">
         <v>81657</v>
       </c>
       <c r="F97">
-        <v>51339</v>
+        <v>51331</v>
       </c>
       <c r="G97">
-        <v>73928</v>
+        <v>73917</v>
       </c>
       <c r="H97">
-        <v>17607</v>
+        <v>17620</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>77383</v>
+        <v>79635</v>
       </c>
       <c r="E98">
         <v>94362</v>
       </c>
       <c r="F98">
-        <v>96049</v>
+        <v>96005</v>
       </c>
       <c r="G98">
-        <v>138311</v>
+        <v>138247</v>
       </c>
       <c r="H98">
-        <v>18666</v>
+        <v>16370</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,16 +4744,16 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>68521</v>
+        <v>68477</v>
       </c>
       <c r="E99">
         <v>94362</v>
       </c>
       <c r="F99">
-        <v>83521</v>
+        <v>83477</v>
       </c>
       <c r="G99">
-        <v>120270</v>
+        <v>120207</v>
       </c>
       <c r="H99">
         <v>15000</v>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61755</v>
+        <v>61716</v>
       </c>
       <c r="E100">
         <v>105796</v>
       </c>
       <c r="F100">
-        <v>78310</v>
+        <v>78295</v>
       </c>
       <c r="G100">
-        <v>112766</v>
+        <v>112745</v>
       </c>
       <c r="H100">
-        <v>16555</v>
+        <v>16579</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3249</v>
+        <v>3247</v>
       </c>
       <c r="E109">
         <v>163332</v>
       </c>
       <c r="F109">
-        <v>30249</v>
+        <v>30247</v>
       </c>
       <c r="G109">
-        <v>43559</v>
+        <v>43556</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14161</v>
+        <v>14152</v>
       </c>
       <c r="E111">
         <v>163332</v>
       </c>
       <c r="F111">
-        <v>41161</v>
+        <v>41152</v>
       </c>
       <c r="G111">
-        <v>59272</v>
+        <v>59259</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,16 +5307,16 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>91135</v>
+        <v>91077</v>
       </c>
       <c r="E112">
         <v>87102</v>
       </c>
       <c r="F112">
-        <v>106135</v>
+        <v>106077</v>
       </c>
       <c r="G112">
-        <v>152834</v>
+        <v>152751</v>
       </c>
       <c r="H112">
         <v>15000</v>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>53918</v>
+        <v>53237</v>
       </c>
       <c r="E113">
         <v>87102</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>68237</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>98261</v>
       </c>
       <c r="H113">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>99698</v>
+        <v>85545</v>
       </c>
       <c r="E115">
         <v>116142</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>100545</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>144785</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5483,16 +5483,16 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>169259</v>
+        <v>169136</v>
       </c>
       <c r="E116">
         <v>145182</v>
       </c>
       <c r="F116">
-        <v>184259</v>
+        <v>184136</v>
       </c>
       <c r="G116">
-        <v>265333</v>
+        <v>265156</v>
       </c>
       <c r="H116">
         <v>15000</v>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>114938</v>
       </c>
       <c r="E117">
         <v>145182</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>129938</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>187111</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>44345</v>
+        <v>44207</v>
       </c>
       <c r="E118">
         <v>58062</v>
       </c>
       <c r="F118">
-        <v>60394</v>
+        <v>59207</v>
       </c>
       <c r="G118">
-        <v>86967</v>
+        <v>85258</v>
       </c>
       <c r="H118">
-        <v>16049</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>33101</v>
+        <v>32765</v>
       </c>
       <c r="E119">
         <v>58062</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>47765</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>68782</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>61314</v>
+        <v>61259</v>
       </c>
       <c r="E120">
         <v>79842</v>
       </c>
       <c r="F120">
-        <v>76314</v>
+        <v>79434</v>
       </c>
       <c r="G120">
-        <v>109892</v>
+        <v>114385</v>
       </c>
       <c r="H120">
-        <v>15000</v>
+        <v>18175</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>54073</v>
       </c>
       <c r="E121">
         <v>79842</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>69073</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>99465</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>44960</v>
+        <v>42253</v>
       </c>
       <c r="E123">
         <v>90732</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>58287</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>83933</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>16034</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13310</v>
+        <v>13301</v>
       </c>
       <c r="E124">
         <v>43542</v>
@@ -5845,7 +5845,7 @@
         <v>47026</v>
       </c>
       <c r="H124">
-        <v>19347</v>
+        <v>19356</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>8989</v>
+        <v>7391</v>
       </c>
       <c r="E125">
         <v>43542</v>
       </c>
       <c r="F125">
-        <v>26577</v>
+        <v>25938</v>
       </c>
       <c r="G125">
-        <v>38271</v>
+        <v>37351</v>
       </c>
       <c r="H125">
-        <v>17588</v>
+        <v>18547</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>31146</v>
+        <v>30653</v>
       </c>
       <c r="E126">
         <v>58062</v>
       </c>
       <c r="F126">
-        <v>46146</v>
+        <v>45653</v>
       </c>
       <c r="G126">
-        <v>66450</v>
+        <v>65740</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20296</v>
+        <v>20283</v>
       </c>
       <c r="E129">
         <v>59496</v>
       </c>
       <c r="F129">
-        <v>37322</v>
+        <v>37316</v>
       </c>
       <c r="G129">
-        <v>53744</v>
+        <v>53735</v>
       </c>
       <c r="H129">
-        <v>17026</v>
+        <v>17033</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>29963</v>
+        <v>36358</v>
       </c>
       <c r="E131">
         <v>74125</v>
       </c>
       <c r="F131">
-        <v>46894</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>67527</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>16931</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37864</v>
+        <v>37840</v>
       </c>
       <c r="E133">
         <v>93309</v>
       </c>
       <c r="F133">
-        <v>57536</v>
+        <v>57527</v>
       </c>
       <c r="G133">
-        <v>82852</v>
+        <v>82839</v>
       </c>
       <c r="H133">
-        <v>19672</v>
+        <v>19687</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53650</v>
+        <v>53616</v>
       </c>
       <c r="E135">
         <v>88917</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>68616</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>98807</v>
       </c>
       <c r="H135">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>72905</v>
+        <v>72197</v>
       </c>
       <c r="E137">
         <v>127032</v>
       </c>
       <c r="F137">
-        <v>87905</v>
+        <v>87197</v>
       </c>
       <c r="G137">
-        <v>126583</v>
+        <v>125564</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91955</v>
+        <v>91897</v>
       </c>
       <c r="E139">
         <v>152442</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>106897</v>
       </c>
       <c r="G139">
-        <v>0</v>
+        <v>153932</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37438</v>
+        <v>37414</v>
       </c>
       <c r="E140">
         <v>90732</v>
       </c>
       <c r="F140">
-        <v>61805</v>
+        <v>61795</v>
       </c>
       <c r="G140">
-        <v>88999</v>
+        <v>88985</v>
       </c>
       <c r="H140">
-        <v>24367</v>
+        <v>24381</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>23371</v>
+        <v>22994</v>
       </c>
       <c r="E142">
         <v>90732</v>
       </c>
       <c r="F142">
-        <v>52678</v>
+        <v>52667</v>
       </c>
       <c r="G142">
-        <v>75856</v>
+        <v>75840</v>
       </c>
       <c r="H142">
-        <v>29307</v>
+        <v>29673</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,16 +6662,16 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>17678</v>
+        <v>17667</v>
       </c>
       <c r="E143">
         <v>90732</v>
       </c>
       <c r="F143">
-        <v>44678</v>
+        <v>44667</v>
       </c>
       <c r="G143">
-        <v>64336</v>
+        <v>64320</v>
       </c>
       <c r="H143">
         <v>27000</v>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45055</v>
+        <v>45594</v>
       </c>
       <c r="E144">
         <v>90732</v>
@@ -6718,7 +6718,7 @@
         <v>97991</v>
       </c>
       <c r="H144">
-        <v>22994</v>
+        <v>22455</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>65319</v>
+        <v>65278</v>
       </c>
       <c r="E145">
         <v>90732</v>
       </c>
       <c r="F145">
-        <v>80319</v>
+        <v>80278</v>
       </c>
       <c r="G145">
-        <v>115659</v>
+        <v>115600</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>66234</v>
+        <v>65845</v>
       </c>
       <c r="E146">
         <v>90732</v>
       </c>
       <c r="F146">
-        <v>81234</v>
+        <v>80845</v>
       </c>
       <c r="G146">
-        <v>116977</v>
+        <v>116417</v>
       </c>
       <c r="H146">
         <v>15000</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36981</v>
+        <v>36957</v>
       </c>
       <c r="E148">
         <v>61692</v>
       </c>
       <c r="F148">
-        <v>64512</v>
+        <v>64482</v>
       </c>
       <c r="G148">
-        <v>92897</v>
+        <v>92854</v>
       </c>
       <c r="H148">
-        <v>27531</v>
+        <v>27525</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>41097</v>
+        <v>41071</v>
       </c>
       <c r="E149">
         <v>61692</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>56071</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>80742</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15738</v>
+        <v>15728</v>
       </c>
       <c r="E151">
         <v>54432</v>
       </c>
       <c r="F151">
-        <v>33524</v>
+        <v>33520</v>
       </c>
       <c r="G151">
-        <v>48275</v>
+        <v>48269</v>
       </c>
       <c r="H151">
-        <v>17786</v>
+        <v>17792</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37675</v>
+        <v>37651</v>
       </c>
       <c r="E152">
         <v>72582</v>
@@ -7070,7 +7070,7 @@
         <v>78389</v>
       </c>
       <c r="H152">
-        <v>16762</v>
+        <v>16786</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>35467</v>
+        <v>33458</v>
       </c>
       <c r="E153">
         <v>72582</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>48458</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>69780</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56583</v>
+        <v>56547</v>
       </c>
       <c r="E154">
         <v>72582</v>
       </c>
       <c r="F154">
-        <v>71583</v>
+        <v>91547</v>
       </c>
       <c r="G154">
-        <v>103080</v>
+        <v>131828</v>
       </c>
       <c r="H154">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>73300</v>
       </c>
       <c r="E155">
         <v>72582</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>88300</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>127152</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>34852</v>
+        <v>34577</v>
       </c>
       <c r="E156">
         <v>59877</v>
       </c>
       <c r="F156">
-        <v>50355</v>
+        <v>50346</v>
       </c>
       <c r="G156">
-        <v>72511</v>
+        <v>72498</v>
       </c>
       <c r="H156">
-        <v>15503</v>
+        <v>15769</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11701</v>
+        <v>11678</v>
       </c>
       <c r="E157">
         <v>59877</v>
       </c>
       <c r="F157">
-        <v>34032</v>
+        <v>34023</v>
       </c>
       <c r="G157">
-        <v>49006</v>
+        <v>48993</v>
       </c>
       <c r="H157">
-        <v>22331</v>
+        <v>22345</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36208</v>
+        <v>36185</v>
       </c>
       <c r="E159">
         <v>83472</v>
       </c>
       <c r="F159">
-        <v>53037</v>
+        <v>53028</v>
       </c>
       <c r="G159">
-        <v>76373</v>
+        <v>76360</v>
       </c>
       <c r="H159">
-        <v>16829</v>
+        <v>16843</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>7775</v>
+        <v>7770</v>
       </c>
       <c r="E160">
         <v>54450</v>
       </c>
       <c r="F160">
-        <v>38875</v>
+        <v>38873</v>
       </c>
       <c r="G160">
-        <v>55980</v>
+        <v>55977</v>
       </c>
       <c r="H160">
-        <v>31100</v>
+        <v>31103</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>9099</v>
+        <v>9094</v>
       </c>
       <c r="E161">
         <v>54450</v>
       </c>
       <c r="F161">
-        <v>30875</v>
+        <v>30873</v>
       </c>
       <c r="G161">
-        <v>44460</v>
+        <v>44457</v>
       </c>
       <c r="H161">
-        <v>21776</v>
+        <v>21779</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>9967</v>
+        <v>9960</v>
       </c>
       <c r="E162">
         <v>72582</v>
       </c>
       <c r="F162">
-        <v>44967</v>
+        <v>44629</v>
       </c>
       <c r="G162">
-        <v>64752</v>
+        <v>64266</v>
       </c>
       <c r="H162">
-        <v>35000</v>
+        <v>34669</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>10629</v>
+        <v>9629</v>
       </c>
       <c r="E163">
         <v>72582</v>
       </c>
       <c r="F163">
-        <v>37629</v>
+        <v>36629</v>
       </c>
       <c r="G163">
-        <v>54186</v>
+        <v>52746</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>68383</v>
       </c>
       <c r="E164">
         <v>68063</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>83383</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>120072</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>22031</v>
+        <v>22017</v>
       </c>
       <c r="E165">
         <v>68063</v>
       </c>
       <c r="F165">
-        <v>41357</v>
+        <v>41351</v>
       </c>
       <c r="G165">
-        <v>59554</v>
+        <v>59545</v>
       </c>
       <c r="H165">
-        <v>19326</v>
+        <v>19334</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>91865</v>
       </c>
       <c r="E166">
         <v>102548</v>
       </c>
       <c r="F166">
-        <v>0</v>
+        <v>106865</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>153886</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>57387</v>
+        <v>57193</v>
       </c>
       <c r="E167">
         <v>102548</v>
       </c>
       <c r="F167">
-        <v>72387</v>
+        <v>72193</v>
       </c>
       <c r="G167">
-        <v>104237</v>
+        <v>103958</v>
       </c>
       <c r="H167">
         <v>15000</v>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>9020</v>
+        <v>9015</v>
       </c>
       <c r="E169">
         <v>72582</v>
       </c>
       <c r="F169">
-        <v>36020</v>
+        <v>36015</v>
       </c>
       <c r="G169">
-        <v>51869</v>
+        <v>51862</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59753</v>
+        <v>59715</v>
       </c>
       <c r="E170">
         <v>108882</v>
       </c>
       <c r="F170">
-        <v>78898</v>
+        <v>78883</v>
       </c>
       <c r="G170">
-        <v>113613</v>
+        <v>113592</v>
       </c>
       <c r="H170">
-        <v>19145</v>
+        <v>19168</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78992</v>
+        <v>78942</v>
       </c>
       <c r="E172">
         <v>145182</v>
       </c>
       <c r="F172">
-        <v>102929</v>
+        <v>102909</v>
       </c>
       <c r="G172">
-        <v>148218</v>
+        <v>148189</v>
       </c>
       <c r="H172">
-        <v>23937</v>
+        <v>23967</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>45386</v>
+        <v>45420</v>
       </c>
       <c r="E174">
         <v>90732</v>
@@ -8045,7 +8045,7 @@
         <v>97991</v>
       </c>
       <c r="H174">
-        <v>22663</v>
+        <v>22629</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>68000</v>
+        <v>67957</v>
       </c>
       <c r="E175">
         <v>90732</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>82957</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>119458</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65792</v>
+        <v>65751</v>
       </c>
       <c r="E176">
         <v>90732</v>
       </c>
       <c r="F176">
-        <v>0</v>
+        <v>80751</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>116281</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26509</v>
+        <v>26493</v>
       </c>
       <c r="E178">
         <v>108882</v>
       </c>
       <c r="F178">
-        <v>53509</v>
+        <v>53493</v>
       </c>
       <c r="G178">
-        <v>77053</v>
+        <v>77030</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>23450</v>
+        <v>22584</v>
       </c>
       <c r="E180">
         <v>90732</v>
       </c>
       <c r="F180">
-        <v>50450</v>
+        <v>49584</v>
       </c>
       <c r="G180">
-        <v>72648</v>
+        <v>71401</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100912</v>
+        <v>100848</v>
       </c>
       <c r="E182">
         <v>127032</v>
       </c>
       <c r="F182">
-        <v>115912</v>
+        <v>115896</v>
       </c>
       <c r="G182">
-        <v>166913</v>
+        <v>166890</v>
       </c>
       <c r="H182">
-        <v>15000</v>
+        <v>15048</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64689</v>
+        <v>64648</v>
       </c>
       <c r="E183">
         <v>127032</v>
       </c>
       <c r="F183">
-        <v>81418</v>
+        <v>81402</v>
       </c>
       <c r="G183">
-        <v>117242</v>
+        <v>117219</v>
       </c>
       <c r="H183">
-        <v>16729</v>
+        <v>16754</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>144976</v>
       </c>
       <c r="E184">
         <v>181482</v>
       </c>
       <c r="F184">
-        <v>0</v>
+        <v>159976</v>
       </c>
       <c r="G184">
-        <v>0</v>
+        <v>230365</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>189104</v>
       </c>
       <c r="E186">
         <v>235932</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>204104</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>293910</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>291544</v>
       </c>
       <c r="E188">
         <v>362982</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>306544</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>441423</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29742</v>
+        <v>29723</v>
       </c>
       <c r="E190">
         <v>95269</v>
       </c>
       <c r="F190">
-        <v>64742</v>
+        <v>64723</v>
       </c>
       <c r="G190">
-        <v>93228</v>
+        <v>93201</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>74214</v>
+        <v>74151</v>
       </c>
       <c r="E191">
         <v>95269</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>89151</v>
       </c>
       <c r="G191">
-        <v>0</v>
+        <v>128377</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,16 +8823,16 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>41507</v>
+        <v>40976</v>
       </c>
       <c r="E192">
         <v>122494</v>
       </c>
       <c r="F192">
-        <v>68507</v>
+        <v>67976</v>
       </c>
       <c r="G192">
-        <v>98650</v>
+        <v>97885</v>
       </c>
       <c r="H192">
         <v>27000</v>
@@ -8911,19 +8911,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>24428</v>
+        <v>53474</v>
       </c>
       <c r="E194">
         <v>149901</v>
       </c>
       <c r="F194">
-        <v>51428</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>74056</v>
+        <v>0</v>
       </c>
       <c r="H194">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,16 +8998,16 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>13641</v>
+        <v>13632</v>
       </c>
       <c r="E196">
         <v>72582</v>
       </c>
       <c r="F196">
-        <v>40641</v>
+        <v>40632</v>
       </c>
       <c r="G196">
-        <v>58523</v>
+        <v>58510</v>
       </c>
       <c r="H196">
         <v>27000</v>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>22141</v>
+        <v>22127</v>
       </c>
       <c r="E198">
         <v>108882</v>
       </c>
       <c r="F198">
-        <v>49141</v>
+        <v>49127</v>
       </c>
       <c r="G198">
-        <v>70763</v>
+        <v>70743</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>13389</v>
+        <v>13175</v>
       </c>
       <c r="E200">
         <v>127032</v>
       </c>
       <c r="F200">
-        <v>46922</v>
+        <v>46852</v>
       </c>
       <c r="G200">
-        <v>67568</v>
+        <v>67467</v>
       </c>
       <c r="H200">
-        <v>33533</v>
+        <v>33677</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11922</v>
+        <v>11852</v>
       </c>
       <c r="E201">
         <v>127032</v>
       </c>
       <c r="F201">
-        <v>38922</v>
+        <v>38852</v>
       </c>
       <c r="G201">
-        <v>56048</v>
+        <v>55947</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9266,16 +9266,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>22677</v>
+        <v>22363</v>
       </c>
       <c r="E202">
         <v>145182</v>
       </c>
       <c r="F202">
-        <v>57677</v>
+        <v>57363</v>
       </c>
       <c r="G202">
-        <v>83055</v>
+        <v>82603</v>
       </c>
       <c r="H202">
         <v>35000</v>
@@ -9312,16 +9312,16 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>82840</v>
+        <v>82787</v>
       </c>
       <c r="E203">
         <v>145182</v>
       </c>
       <c r="F203">
-        <v>97840</v>
+        <v>97787</v>
       </c>
       <c r="G203">
-        <v>140890</v>
+        <v>140813</v>
       </c>
       <c r="H203">
         <v>15000</v>
@@ -9356,16 +9356,16 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>26998</v>
+        <v>25137</v>
       </c>
       <c r="E204">
         <v>181482</v>
       </c>
       <c r="F204">
-        <v>53998</v>
+        <v>52137</v>
       </c>
       <c r="G204">
-        <v>77757</v>
+        <v>75077</v>
       </c>
       <c r="H204">
         <v>27000</v>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>19066</v>
+        <v>24066</v>
       </c>
       <c r="E206">
         <v>58062</v>
       </c>
       <c r="F206">
-        <v>42170</v>
+        <v>41920</v>
       </c>
       <c r="G206">
-        <v>60725</v>
+        <v>60365</v>
       </c>
       <c r="H206">
-        <v>23104</v>
+        <v>17854</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13815</v>
+        <v>13191</v>
       </c>
       <c r="E207">
         <v>58062</v>
       </c>
       <c r="F207">
-        <v>34170</v>
+        <v>33920</v>
       </c>
       <c r="G207">
-        <v>49205</v>
+        <v>48845</v>
       </c>
       <c r="H207">
-        <v>20355</v>
+        <v>20729</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83833</v>
+        <v>83780</v>
       </c>
       <c r="E213">
         <v>181482</v>
       </c>
       <c r="F213">
-        <v>110311</v>
+        <v>110290</v>
       </c>
       <c r="G213">
-        <v>158848</v>
+        <v>158818</v>
       </c>
       <c r="H213">
-        <v>26478</v>
+        <v>26510</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,16 +9792,16 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>28654</v>
+        <v>27879</v>
       </c>
       <c r="E214">
         <v>87102</v>
       </c>
       <c r="F214">
-        <v>55654</v>
+        <v>54879</v>
       </c>
       <c r="G214">
-        <v>80142</v>
+        <v>79026</v>
       </c>
       <c r="H214">
         <v>27000</v>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45938</v>
+        <v>45909</v>
       </c>
       <c r="E216">
         <v>101622</v>
       </c>
       <c r="F216">
-        <v>70105</v>
+        <v>76217</v>
       </c>
       <c r="G216">
-        <v>100951</v>
+        <v>109752</v>
       </c>
       <c r="H216">
-        <v>24167</v>
+        <v>30308</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>89375</v>
       </c>
       <c r="E217">
         <v>101622</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>104375</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>150300</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,16 +10059,16 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>62749</v>
+        <v>62709</v>
       </c>
       <c r="E220">
         <v>81675</v>
       </c>
       <c r="F220">
-        <v>77749</v>
+        <v>77709</v>
       </c>
       <c r="G220">
-        <v>111959</v>
+        <v>111901</v>
       </c>
       <c r="H220">
         <v>15000</v>
@@ -10149,16 +10149,16 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>75381</v>
+        <v>74687</v>
       </c>
       <c r="E222">
         <v>96195</v>
       </c>
       <c r="F222">
-        <v>90381</v>
+        <v>89687</v>
       </c>
       <c r="G222">
-        <v>130149</v>
+        <v>129149</v>
       </c>
       <c r="H222">
         <v>15000</v>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16606</v>
+        <v>16422</v>
       </c>
       <c r="E224">
         <v>59877</v>
       </c>
       <c r="F224">
-        <v>44908</v>
+        <v>44905</v>
       </c>
       <c r="G224">
-        <v>64668</v>
+        <v>64663</v>
       </c>
       <c r="H224">
-        <v>28302</v>
+        <v>28483</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10424</v>
+        <v>10417</v>
       </c>
       <c r="E225">
         <v>59877</v>
       </c>
       <c r="F225">
-        <v>33522</v>
+        <v>33519</v>
       </c>
       <c r="G225">
-        <v>48272</v>
+        <v>48267</v>
       </c>
       <c r="H225">
-        <v>23098</v>
+        <v>23102</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>38013</v>
       </c>
       <c r="E226">
         <v>72582</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>53867</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>77568</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>15854</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19287</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>181482</v>
       </c>
       <c r="F231">
-        <v>46287</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>66653</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10589,7 +10589,7 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9415</v>
+        <v>9440</v>
       </c>
       <c r="E232">
         <v>52635</v>
@@ -10601,7 +10601,7 @@
         <v>49720</v>
       </c>
       <c r="H232">
-        <v>25113</v>
+        <v>25088</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,16 +10677,16 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>11954</v>
+        <v>11946</v>
       </c>
       <c r="E234">
         <v>70785</v>
       </c>
       <c r="F234">
-        <v>38954</v>
+        <v>38946</v>
       </c>
       <c r="G234">
-        <v>56094</v>
+        <v>56082</v>
       </c>
       <c r="H234">
         <v>27000</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>8484</v>
+        <v>8479</v>
       </c>
       <c r="E236">
         <v>52635</v>
       </c>
       <c r="F236">
-        <v>37253</v>
+        <v>37251</v>
       </c>
       <c r="G236">
-        <v>53644</v>
+        <v>53641</v>
       </c>
       <c r="H236">
-        <v>28769</v>
+        <v>28772</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6813</v>
+        <v>6808</v>
       </c>
       <c r="E237">
         <v>52635</v>
       </c>
       <c r="F237">
-        <v>29253</v>
+        <v>29251</v>
       </c>
       <c r="G237">
-        <v>42124</v>
+        <v>42121</v>
       </c>
       <c r="H237">
-        <v>22440</v>
+        <v>22443</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70145</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>70785</v>
       </c>
       <c r="F241">
-        <v>85145</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>122609</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34252</v>
+        <v>34231</v>
       </c>
       <c r="E242">
         <v>70785</v>
       </c>
       <c r="F242">
-        <v>51554</v>
+        <v>51546</v>
       </c>
       <c r="G242">
-        <v>74238</v>
+        <v>74226</v>
       </c>
       <c r="H242">
-        <v>17302</v>
+        <v>17315</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,16 +11116,16 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9904</v>
+        <v>9803</v>
       </c>
       <c r="E244">
         <v>27225</v>
       </c>
       <c r="F244">
-        <v>24904</v>
+        <v>24803</v>
       </c>
       <c r="G244">
-        <v>35862</v>
+        <v>35716</v>
       </c>
       <c r="H244">
         <v>15000</v>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11922</v>
+        <v>11915</v>
       </c>
       <c r="E246">
         <v>108882</v>
       </c>
       <c r="F246">
-        <v>38922</v>
+        <v>38915</v>
       </c>
       <c r="G246">
-        <v>56048</v>
+        <v>56038</v>
       </c>
       <c r="H246">
         <v>27000</v>
@@ -11291,16 +11291,16 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59090</v>
+        <v>58974</v>
       </c>
       <c r="E248">
         <v>96195</v>
       </c>
       <c r="F248">
-        <v>74090</v>
+        <v>73974</v>
       </c>
       <c r="G248">
-        <v>106690</v>
+        <v>106523</v>
       </c>
       <c r="H248">
         <v>15000</v>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>48177</v>
+        <v>0</v>
       </c>
       <c r="E249">
         <v>96195</v>
       </c>
       <c r="F249">
-        <v>63177</v>
+        <v>0</v>
       </c>
       <c r="G249">
-        <v>90975</v>
+        <v>0</v>
       </c>
       <c r="H249">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,16 +11380,16 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>71375</v>
+        <v>70731</v>
       </c>
       <c r="E250">
         <v>108882</v>
       </c>
       <c r="F250">
-        <v>86375</v>
+        <v>85731</v>
       </c>
       <c r="G250">
-        <v>124380</v>
+        <v>123453</v>
       </c>
       <c r="H250">
         <v>15000</v>
@@ -11469,7 +11469,7 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>11938</v>
+        <v>11930</v>
       </c>
       <c r="E252">
         <v>52635</v>
@@ -11481,7 +11481,7 @@
         <v>49720</v>
       </c>
       <c r="H252">
-        <v>22590</v>
+        <v>22598</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,16 +11558,16 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>16937</v>
+        <v>17226</v>
       </c>
       <c r="E254">
         <v>70785</v>
       </c>
       <c r="F254">
-        <v>43937</v>
+        <v>44226</v>
       </c>
       <c r="G254">
-        <v>63269</v>
+        <v>63685</v>
       </c>
       <c r="H254">
         <v>27000</v>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12569</v>
+        <v>12561</v>
       </c>
       <c r="E259">
         <v>50802</v>
       </c>
       <c r="F259">
-        <v>30840</v>
+        <v>30837</v>
       </c>
       <c r="G259">
-        <v>44410</v>
+        <v>44405</v>
       </c>
       <c r="H259">
-        <v>18271</v>
+        <v>18276</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,16 +11862,16 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62765</v>
+        <v>62725</v>
       </c>
       <c r="E261">
         <v>63507</v>
       </c>
       <c r="F261">
-        <v>77765</v>
+        <v>77725</v>
       </c>
       <c r="G261">
-        <v>111982</v>
+        <v>111924</v>
       </c>
       <c r="H261">
         <v>15000</v>
@@ -11948,16 +11948,16 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75507</v>
+        <v>75459</v>
       </c>
       <c r="E263">
         <v>72582</v>
       </c>
       <c r="F263">
-        <v>90507</v>
+        <v>90459</v>
       </c>
       <c r="G263">
-        <v>130330</v>
+        <v>130261</v>
       </c>
       <c r="H263">
         <v>15000</v>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>40560</v>
+        <v>40298</v>
       </c>
       <c r="E264">
         <v>59877</v>
       </c>
       <c r="F264">
-        <v>0</v>
+        <v>55298</v>
       </c>
       <c r="G264">
-        <v>0</v>
+        <v>79629</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,16 +12038,16 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>27361</v>
+        <v>25531</v>
       </c>
       <c r="E265">
         <v>59877</v>
       </c>
       <c r="F265">
-        <v>42361</v>
+        <v>40531</v>
       </c>
       <c r="G265">
-        <v>61000</v>
+        <v>58365</v>
       </c>
       <c r="H265">
         <v>15000</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>35009</v>
+        <v>34987</v>
       </c>
       <c r="E268">
         <v>59877</v>
       </c>
       <c r="F268">
-        <v>0</v>
+        <v>49987</v>
       </c>
       <c r="G268">
-        <v>0</v>
+        <v>71981</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23072</v>
+        <v>23041</v>
       </c>
       <c r="E269">
         <v>59877</v>
       </c>
       <c r="F269">
-        <v>38581</v>
+        <v>38568</v>
       </c>
       <c r="G269">
-        <v>55557</v>
+        <v>55538</v>
       </c>
       <c r="H269">
-        <v>15509</v>
+        <v>15527</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,19 +12349,19 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71470</v>
+        <v>71393</v>
       </c>
       <c r="E272">
         <v>90732</v>
       </c>
       <c r="F272">
-        <v>0</v>
+        <v>86393</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>124406</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I272" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2001120/Split_Fiction/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21305</v>
+        <v>21292</v>
       </c>
       <c r="E273">
         <v>90732</v>
       </c>
       <c r="F273">
-        <v>48305</v>
+        <v>48292</v>
       </c>
       <c r="G273">
-        <v>69559</v>
+        <v>69540</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,16 +12438,16 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>17347</v>
+        <v>17336</v>
       </c>
       <c r="E274">
         <v>127032</v>
       </c>
       <c r="F274">
-        <v>52347</v>
+        <v>52336</v>
       </c>
       <c r="G274">
-        <v>75380</v>
+        <v>75364</v>
       </c>
       <c r="H274">
         <v>35000</v>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12916</v>
+        <v>12907</v>
       </c>
       <c r="E275">
         <v>127032</v>
       </c>
       <c r="F275">
-        <v>39916</v>
+        <v>39907</v>
       </c>
       <c r="G275">
-        <v>57479</v>
+        <v>57466</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>153095</v>
+        <v>152809</v>
       </c>
       <c r="E276">
         <v>163332</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>167809</v>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>241645</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>50653</v>
+        <v>46571</v>
       </c>
       <c r="E278">
         <v>108882</v>
       </c>
       <c r="F278">
-        <v>78402</v>
+        <v>78390</v>
       </c>
       <c r="G278">
-        <v>112899</v>
+        <v>112882</v>
       </c>
       <c r="H278">
-        <v>27749</v>
+        <v>31819</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49281</v>
+        <v>49250</v>
       </c>
       <c r="E279">
         <v>108882</v>
       </c>
       <c r="F279">
-        <v>68176</v>
+        <v>68164</v>
       </c>
       <c r="G279">
-        <v>98173</v>
+        <v>98156</v>
       </c>
       <c r="H279">
-        <v>18895</v>
+        <v>18914</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,7 +12701,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>63979</v>
+        <v>63576</v>
       </c>
       <c r="E280">
         <v>127032</v>
@@ -12713,7 +12713,7 @@
         <v>137195</v>
       </c>
       <c r="H280">
-        <v>31295</v>
+        <v>31698</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,16 +12747,16 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>106148</v>
+        <v>106081</v>
       </c>
       <c r="E281">
         <v>127032</v>
       </c>
       <c r="F281">
-        <v>121148</v>
+        <v>121081</v>
       </c>
       <c r="G281">
-        <v>174453</v>
+        <v>174357</v>
       </c>
       <c r="H281">
         <v>15000</v>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23371</v>
+        <v>23214</v>
       </c>
       <c r="E282">
         <v>54432</v>
       </c>
       <c r="F282">
-        <v>39843</v>
+        <v>39780</v>
       </c>
       <c r="G282">
-        <v>57374</v>
+        <v>57283</v>
       </c>
       <c r="H282">
-        <v>16472</v>
+        <v>16566</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>66139</v>
+        <v>65152</v>
       </c>
       <c r="E284">
         <v>81675</v>
       </c>
       <c r="F284">
-        <v>0</v>
+        <v>80152</v>
       </c>
       <c r="G284">
-        <v>0</v>
+        <v>115419</v>
       </c>
       <c r="H284">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,19 +13009,19 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20454</v>
+        <v>20441</v>
       </c>
       <c r="E287">
         <v>38097</v>
       </c>
       <c r="F287">
-        <v>0</v>
+        <v>35441</v>
       </c>
       <c r="G287">
-        <v>0</v>
+        <v>51035</v>
       </c>
       <c r="H287">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I287" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1962700/Subnautica_2/","Abrir Steam")</f>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>32502</v>
+        <v>31977</v>
       </c>
       <c r="E288">
         <v>58062</v>
       </c>
       <c r="F288">
-        <v>62788</v>
+        <v>62759</v>
       </c>
       <c r="G288">
-        <v>90415</v>
+        <v>90373</v>
       </c>
       <c r="H288">
-        <v>30286</v>
+        <v>30782</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,19 +13099,19 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>39598</v>
+        <v>39573</v>
       </c>
       <c r="E289">
         <v>58062</v>
       </c>
       <c r="F289">
-        <v>0</v>
+        <v>54573</v>
       </c>
       <c r="G289">
-        <v>0</v>
+        <v>78585</v>
       </c>
       <c r="H289">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I289" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13143,7 +13143,7 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>10629</v>
+        <v>10780</v>
       </c>
       <c r="E290">
         <v>43542</v>
@@ -13155,7 +13155,7 @@
         <v>47026</v>
       </c>
       <c r="H290">
-        <v>22028</v>
+        <v>21877</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,19 +13189,19 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>45654</v>
+        <v>45625</v>
       </c>
       <c r="E291">
         <v>43542</v>
       </c>
       <c r="F291">
-        <v>0</v>
+        <v>60625</v>
       </c>
       <c r="G291">
-        <v>0</v>
+        <v>87300</v>
       </c>
       <c r="H291">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I291" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>0</v>
+        <v>41543</v>
       </c>
       <c r="E292">
         <v>108882</v>
       </c>
       <c r="F292">
-        <v>0</v>
+        <v>68543</v>
       </c>
       <c r="G292">
-        <v>0</v>
+        <v>98702</v>
       </c>
       <c r="H292">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>38179</v>
+        <v>0</v>
       </c>
       <c r="E293">
         <v>108882</v>
       </c>
       <c r="F293">
-        <v>63735</v>
+        <v>0</v>
       </c>
       <c r="G293">
-        <v>91778</v>
+        <v>0</v>
       </c>
       <c r="H293">
-        <v>25556</v>
+        <v>0</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4747</v>
+        <v>4744</v>
       </c>
       <c r="E299">
         <v>54432</v>
       </c>
       <c r="F299">
-        <v>29127</v>
+        <v>29126</v>
       </c>
       <c r="G299">
-        <v>41943</v>
+        <v>41941</v>
       </c>
       <c r="H299">
-        <v>24380</v>
+        <v>24382</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>20895</v>
+        <v>20472</v>
       </c>
       <c r="E302">
         <v>90732</v>
       </c>
       <c r="F302">
-        <v>47895</v>
+        <v>47472</v>
       </c>
       <c r="G302">
-        <v>68969</v>
+        <v>68360</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,16 +13756,16 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>39551</v>
+        <v>38722</v>
       </c>
       <c r="E304">
         <v>108882</v>
       </c>
       <c r="F304">
-        <v>66551</v>
+        <v>65722</v>
       </c>
       <c r="G304">
-        <v>95833</v>
+        <v>94640</v>
       </c>
       <c r="H304">
         <v>27000</v>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>23876</v>
+        <v>23861</v>
       </c>
       <c r="E306">
         <v>108882</v>
       </c>
       <c r="F306">
-        <v>58876</v>
+        <v>50861</v>
       </c>
       <c r="G306">
-        <v>84781</v>
+        <v>73240</v>
       </c>
       <c r="H306">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>33574</v>
+        <v>0</v>
       </c>
       <c r="E307">
         <v>108882</v>
       </c>
       <c r="F307">
-        <v>60574</v>
+        <v>0</v>
       </c>
       <c r="G307">
-        <v>87227</v>
+        <v>0</v>
       </c>
       <c r="H307">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,16 +13932,16 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>185771</v>
+        <v>185653</v>
       </c>
       <c r="E308">
         <v>235932</v>
       </c>
       <c r="F308">
-        <v>200771</v>
+        <v>200653</v>
       </c>
       <c r="G308">
-        <v>289110</v>
+        <v>288940</v>
       </c>
       <c r="H308">
         <v>15000</v>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>65367</v>
+        <v>65057</v>
       </c>
       <c r="E310">
         <v>127032</v>
       </c>
       <c r="F310">
-        <v>89311</v>
+        <v>89187</v>
       </c>
       <c r="G310">
-        <v>128608</v>
+        <v>128429</v>
       </c>
       <c r="H310">
-        <v>23944</v>
+        <v>24130</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>54138</v>
+        <v>0</v>
       </c>
       <c r="E311">
         <v>127032</v>
       </c>
       <c r="F311">
-        <v>77198</v>
+        <v>0</v>
       </c>
       <c r="G311">
-        <v>111165</v>
+        <v>0</v>
       </c>
       <c r="H311">
-        <v>23060</v>
+        <v>0</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>125072</v>
+        <v>124993</v>
       </c>
       <c r="E314">
         <v>235932</v>
       </c>
       <c r="F314">
-        <v>152072</v>
+        <v>151993</v>
       </c>
       <c r="G314">
-        <v>218984</v>
+        <v>218870</v>
       </c>
       <c r="H314">
         <v>27000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72102</v>
+        <v>72053</v>
       </c>
       <c r="E2">
         <v>72582</v>
       </c>
       <c r="F2">
-        <v>87102</v>
+        <v>87068</v>
       </c>
       <c r="G2">
-        <v>125427</v>
+        <v>125378</v>
       </c>
       <c r="H2">
-        <v>15000</v>
+        <v>15015</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,16 +527,16 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46713</v>
+        <v>46679</v>
       </c>
       <c r="E3">
         <v>72582</v>
       </c>
       <c r="F3">
-        <v>61713</v>
+        <v>61679</v>
       </c>
       <c r="G3">
-        <v>88867</v>
+        <v>88818</v>
       </c>
       <c r="H3">
         <v>15000</v>
@@ -571,19 +571,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>82378</v>
+        <v>82414</v>
       </c>
       <c r="E4">
         <v>83472</v>
       </c>
       <c r="F4">
-        <v>97378</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>140224</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,16 +617,16 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>84773</v>
+        <v>84732</v>
       </c>
       <c r="E5">
         <v>83472</v>
       </c>
       <c r="F5">
-        <v>99773</v>
+        <v>99732</v>
       </c>
       <c r="G5">
-        <v>143673</v>
+        <v>143614</v>
       </c>
       <c r="H5">
         <v>15000</v>
@@ -703,19 +703,19 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>3609</v>
+        <v>3611</v>
       </c>
       <c r="E7">
         <v>54432</v>
       </c>
       <c r="F7">
-        <v>28672</v>
+        <v>28673</v>
       </c>
       <c r="G7">
-        <v>41288</v>
+        <v>41289</v>
       </c>
       <c r="H7">
-        <v>25063</v>
+        <v>25062</v>
       </c>
       <c r="I7" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222700/A_Way_Out/?l=spanish","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>34451</v>
+        <v>34442</v>
       </c>
       <c r="E8">
         <v>72582</v>
       </c>
       <c r="F8">
-        <v>52443</v>
+        <v>52439</v>
       </c>
       <c r="G8">
-        <v>75518</v>
+        <v>75512</v>
       </c>
       <c r="H8">
-        <v>17992</v>
+        <v>17997</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -836,19 +836,19 @@
         <v>15</v>
       </c>
       <c r="D10">
-        <v>53442</v>
+        <v>53445</v>
       </c>
       <c r="E10">
         <v>108882</v>
       </c>
       <c r="F10">
-        <v>76374</v>
+        <v>76375</v>
       </c>
       <c r="G10">
-        <v>109979</v>
+        <v>109980</v>
       </c>
       <c r="H10">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="I10" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>79036</v>
+        <v>78992</v>
       </c>
       <c r="E12">
         <v>81657</v>
       </c>
       <c r="F12">
-        <v>97106</v>
+        <v>97098</v>
       </c>
       <c r="G12">
-        <v>139833</v>
+        <v>139821</v>
       </c>
       <c r="H12">
-        <v>18070</v>
+        <v>18106</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11788</v>
+        <v>11780</v>
       </c>
       <c r="E13">
         <v>81657</v>
       </c>
       <c r="F13">
-        <v>38788</v>
+        <v>38780</v>
       </c>
       <c r="G13">
-        <v>55855</v>
+        <v>55843</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,16 +1056,16 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>44948</v>
+        <v>44929</v>
       </c>
       <c r="E15">
         <v>72582</v>
       </c>
       <c r="F15">
-        <v>59948</v>
+        <v>59929</v>
       </c>
       <c r="G15">
-        <v>86325</v>
+        <v>86298</v>
       </c>
       <c r="H15">
         <v>15000</v>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>33963</v>
+        <v>35656</v>
       </c>
       <c r="E21">
         <v>101622</v>
       </c>
       <c r="F21">
-        <v>59218</v>
+        <v>59895</v>
       </c>
       <c r="G21">
-        <v>85274</v>
+        <v>86249</v>
       </c>
       <c r="H21">
-        <v>25255</v>
+        <v>24239</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="E27">
         <v>63507</v>
       </c>
       <c r="F27">
-        <v>38850</v>
+        <v>38848</v>
       </c>
       <c r="G27">
-        <v>55944</v>
+        <v>55941</v>
       </c>
       <c r="H27">
-        <v>18646</v>
+        <v>18647</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>75018</v>
+        <v>74971</v>
       </c>
       <c r="E28">
         <v>127032</v>
       </c>
       <c r="F28">
-        <v>95043</v>
+        <v>95014</v>
       </c>
       <c r="G28">
-        <v>136862</v>
+        <v>136820</v>
       </c>
       <c r="H28">
-        <v>20025</v>
+        <v>20043</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>28998</v>
+        <v>28969</v>
       </c>
       <c r="E29">
         <v>127032</v>
       </c>
       <c r="F29">
-        <v>55998</v>
+        <v>55969</v>
       </c>
       <c r="G29">
-        <v>80637</v>
+        <v>80595</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>126080</v>
+        <v>125908</v>
       </c>
       <c r="E30">
         <v>181482</v>
       </c>
       <c r="F30">
-        <v>141080</v>
+        <v>141035</v>
       </c>
       <c r="G30">
-        <v>203155</v>
+        <v>203090</v>
       </c>
       <c r="H30">
-        <v>15000</v>
+        <v>15127</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>78248</v>
+        <v>78203</v>
       </c>
       <c r="E31">
         <v>181482</v>
       </c>
       <c r="F31">
-        <v>105248</v>
+        <v>105203</v>
       </c>
       <c r="G31">
-        <v>151557</v>
+        <v>151492</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>72638</v>
+        <v>81515</v>
       </c>
       <c r="E32">
         <v>108882</v>
       </c>
       <c r="F32">
-        <v>96271</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>138630</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>23633</v>
+        <v>0</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>47706</v>
+        <v>47673</v>
       </c>
       <c r="E33">
         <v>108882</v>
       </c>
       <c r="F33">
-        <v>67546</v>
+        <v>67533</v>
       </c>
       <c r="G33">
-        <v>97266</v>
+        <v>97248</v>
       </c>
       <c r="H33">
-        <v>19840</v>
+        <v>19860</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>82114</v>
       </c>
       <c r="E35">
         <v>127032</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>97114</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>139844</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1979,16 +1979,16 @@
         <v>15</v>
       </c>
       <c r="D36">
-        <v>45531</v>
+        <v>45560</v>
       </c>
       <c r="E36">
         <v>127032</v>
       </c>
       <c r="F36">
-        <v>72531</v>
+        <v>72560</v>
       </c>
       <c r="G36">
-        <v>104445</v>
+        <v>104486</v>
       </c>
       <c r="H36">
         <v>27000</v>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>64963</v>
+        <v>64736</v>
       </c>
       <c r="E38">
         <v>235932</v>
       </c>
       <c r="F38">
-        <v>91963</v>
+        <v>91736</v>
       </c>
       <c r="G38">
-        <v>132427</v>
+        <v>132100</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2156,16 +2156,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>84348</v>
+        <v>84291</v>
       </c>
       <c r="E40">
         <v>235932</v>
       </c>
       <c r="F40">
-        <v>111348</v>
+        <v>111291</v>
       </c>
       <c r="G40">
-        <v>160341</v>
+        <v>160259</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38974</v>
+        <v>38952</v>
       </c>
       <c r="E43">
         <v>127032</v>
       </c>
       <c r="F43">
-        <v>65974</v>
+        <v>65952</v>
       </c>
       <c r="G43">
-        <v>95003</v>
+        <v>94971</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27659</v>
+        <v>27598</v>
       </c>
       <c r="E47">
         <v>108882</v>
       </c>
       <c r="F47">
-        <v>54659</v>
+        <v>54598</v>
       </c>
       <c r="G47">
-        <v>78709</v>
+        <v>78621</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="D50">
-        <v>37682</v>
+        <v>36255</v>
       </c>
       <c r="E50">
         <v>63507</v>
       </c>
       <c r="F50">
-        <v>58917</v>
+        <v>58893</v>
       </c>
       <c r="G50">
-        <v>84840</v>
+        <v>84806</v>
       </c>
       <c r="H50">
-        <v>21235</v>
+        <v>22638</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,16 +2633,16 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>35917</v>
+        <v>35893</v>
       </c>
       <c r="E51">
         <v>63507</v>
       </c>
       <c r="F51">
-        <v>50917</v>
+        <v>50893</v>
       </c>
       <c r="G51">
-        <v>73320</v>
+        <v>73286</v>
       </c>
       <c r="H51">
         <v>15000</v>
@@ -2677,16 +2677,16 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>61685</v>
+        <v>61645</v>
       </c>
       <c r="E52">
         <v>76212</v>
       </c>
       <c r="F52">
-        <v>76685</v>
+        <v>76645</v>
       </c>
       <c r="G52">
-        <v>110426</v>
+        <v>110369</v>
       </c>
       <c r="H52">
         <v>15000</v>
@@ -2723,16 +2723,16 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>69943</v>
+        <v>57261</v>
       </c>
       <c r="E53">
         <v>76212</v>
       </c>
       <c r="F53">
-        <v>84943</v>
+        <v>72261</v>
       </c>
       <c r="G53">
-        <v>122318</v>
+        <v>104056</v>
       </c>
       <c r="H53">
         <v>15000</v>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>49155</v>
+        <v>54075</v>
       </c>
       <c r="E54">
         <v>127032</v>
       </c>
       <c r="F54">
-        <v>84155</v>
+        <v>87987</v>
       </c>
       <c r="G54">
-        <v>121183</v>
+        <v>126701</v>
       </c>
       <c r="H54">
-        <v>35000</v>
+        <v>33912</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52449</v>
+        <v>52419</v>
       </c>
       <c r="E55">
         <v>127032</v>
       </c>
       <c r="F55">
-        <v>76522</v>
+        <v>76510</v>
       </c>
       <c r="G55">
-        <v>110192</v>
+        <v>110174</v>
       </c>
       <c r="H55">
-        <v>24073</v>
+        <v>24091</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,19 +2857,19 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>53411</v>
+        <v>70665</v>
       </c>
       <c r="E56">
         <v>145182</v>
       </c>
       <c r="F56">
-        <v>80411</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>115792</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I56" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>63072</v>
+        <v>63033</v>
       </c>
       <c r="E57">
         <v>145182</v>
       </c>
       <c r="F57">
-        <v>87850</v>
+        <v>87834</v>
       </c>
       <c r="G57">
-        <v>126504</v>
+        <v>126481</v>
       </c>
       <c r="H57">
-        <v>24778</v>
+        <v>24801</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23278</v>
+        <v>23261</v>
       </c>
       <c r="E58">
         <v>36282</v>
       </c>
       <c r="F58">
-        <v>38386</v>
+        <v>38381</v>
       </c>
       <c r="G58">
-        <v>55276</v>
+        <v>55269</v>
       </c>
       <c r="H58">
-        <v>15108</v>
+        <v>15120</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6257</v>
+        <v>6245</v>
       </c>
       <c r="E59">
         <v>36282</v>
       </c>
       <c r="F59">
-        <v>22653</v>
+        <v>22648</v>
       </c>
       <c r="G59">
-        <v>32620</v>
+        <v>32613</v>
       </c>
       <c r="H59">
-        <v>16396</v>
+        <v>16403</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,16 +3036,16 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26666</v>
+        <v>26651</v>
       </c>
       <c r="E60">
         <v>48987</v>
       </c>
       <c r="F60">
-        <v>41666</v>
+        <v>41651</v>
       </c>
       <c r="G60">
-        <v>59999</v>
+        <v>59977</v>
       </c>
       <c r="H60">
         <v>15000</v>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12923</v>
+        <v>12916</v>
       </c>
       <c r="E63">
         <v>81657</v>
       </c>
       <c r="F63">
-        <v>39923</v>
+        <v>39916</v>
       </c>
       <c r="G63">
-        <v>57489</v>
+        <v>57479</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>27564</v>
+        <v>27550</v>
       </c>
       <c r="E65">
         <v>122476</v>
       </c>
       <c r="F65">
-        <v>54564</v>
+        <v>54550</v>
       </c>
       <c r="G65">
-        <v>78572</v>
+        <v>78552</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3296,19 +3296,19 @@
         <v>15</v>
       </c>
       <c r="D66">
-        <v>23908</v>
+        <v>23860</v>
       </c>
       <c r="E66">
         <v>90732</v>
       </c>
       <c r="F66">
-        <v>53613</v>
+        <v>53624</v>
       </c>
       <c r="G66">
-        <v>77203</v>
+        <v>77219</v>
       </c>
       <c r="H66">
-        <v>29705</v>
+        <v>29764</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18613</v>
+        <v>18624</v>
       </c>
       <c r="E67">
         <v>90732</v>
       </c>
       <c r="F67">
-        <v>45613</v>
+        <v>45624</v>
       </c>
       <c r="G67">
-        <v>65683</v>
+        <v>65699</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,16 +3385,16 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34640</v>
+        <v>34662</v>
       </c>
       <c r="E68">
         <v>108882</v>
       </c>
       <c r="F68">
-        <v>61640</v>
+        <v>61662</v>
       </c>
       <c r="G68">
-        <v>88762</v>
+        <v>88793</v>
       </c>
       <c r="H68">
         <v>27000</v>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>107861</v>
+        <v>107914</v>
       </c>
       <c r="E70">
         <v>127032</v>
       </c>
       <c r="F70">
-        <v>122861</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>176920</v>
+        <v>0</v>
       </c>
       <c r="H70">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3605,16 +3605,16 @@
         <v>17</v>
       </c>
       <c r="D73">
-        <v>6083</v>
+        <v>6071</v>
       </c>
       <c r="E73">
         <v>27207</v>
       </c>
       <c r="F73">
-        <v>21083</v>
+        <v>21071</v>
       </c>
       <c r="G73">
-        <v>30360</v>
+        <v>30342</v>
       </c>
       <c r="H73">
         <v>15000</v>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86097</v>
+        <v>86152</v>
       </c>
       <c r="E76">
         <v>127032</v>
       </c>
       <c r="F76">
-        <v>101137</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>145637</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>15040</v>
+        <v>0</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47217</v>
+        <v>47184</v>
       </c>
       <c r="E77">
         <v>127032</v>
       </c>
       <c r="F77">
-        <v>74217</v>
+        <v>74184</v>
       </c>
       <c r="G77">
-        <v>106872</v>
+        <v>106825</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37209</v>
+        <v>37186</v>
       </c>
       <c r="E81">
         <v>90732</v>
       </c>
       <c r="F81">
-        <v>56269</v>
+        <v>56260</v>
       </c>
       <c r="G81">
-        <v>81027</v>
+        <v>81014</v>
       </c>
       <c r="H81">
-        <v>19060</v>
+        <v>19074</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,16 +4039,16 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>85041</v>
+        <v>85000</v>
       </c>
       <c r="E83">
         <v>127032</v>
       </c>
       <c r="F83">
-        <v>100041</v>
+        <v>100000</v>
       </c>
       <c r="G83">
-        <v>144059</v>
+        <v>144000</v>
       </c>
       <c r="H83">
         <v>15000</v>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>48572</v>
+        <v>94147</v>
       </c>
       <c r="E84">
         <v>101622</v>
       </c>
       <c r="F84">
-        <v>71163</v>
+        <v>0</v>
       </c>
       <c r="G84">
-        <v>102475</v>
+        <v>0</v>
       </c>
       <c r="H84">
-        <v>22591</v>
+        <v>0</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32103</v>
+        <v>32092</v>
       </c>
       <c r="E85">
         <v>101622</v>
       </c>
       <c r="F85">
-        <v>58474</v>
+        <v>58469</v>
       </c>
       <c r="G85">
-        <v>84203</v>
+        <v>84195</v>
       </c>
       <c r="H85">
-        <v>26371</v>
+        <v>26377</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>151485</v>
+        <v>151550</v>
       </c>
       <c r="E86">
         <v>145182</v>
       </c>
       <c r="F86">
-        <v>166485</v>
+        <v>0</v>
       </c>
       <c r="G86">
-        <v>239738</v>
+        <v>0</v>
       </c>
       <c r="H86">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>171075</v>
+        <v>171246</v>
       </c>
       <c r="E88">
         <v>159702</v>
       </c>
       <c r="F88">
-        <v>186075</v>
+        <v>0</v>
       </c>
       <c r="G88">
-        <v>267948</v>
+        <v>0</v>
       </c>
       <c r="H88">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,16 +4302,16 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127294</v>
+        <v>127217</v>
       </c>
       <c r="E89">
         <v>159702</v>
       </c>
       <c r="F89">
-        <v>142294</v>
+        <v>142217</v>
       </c>
       <c r="G89">
-        <v>204903</v>
+        <v>204792</v>
       </c>
       <c r="H89">
         <v>15000</v>
@@ -4346,19 +4346,19 @@
         <v>15</v>
       </c>
       <c r="D90">
-        <v>7770</v>
+        <v>7775</v>
       </c>
       <c r="E90">
         <v>58062</v>
       </c>
       <c r="F90">
-        <v>38359</v>
+        <v>38360</v>
       </c>
       <c r="G90">
-        <v>55237</v>
+        <v>55238</v>
       </c>
       <c r="H90">
-        <v>30589</v>
+        <v>30585</v>
       </c>
       <c r="I90" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4392,19 +4392,19 @@
         <v>17</v>
       </c>
       <c r="D91">
-        <v>4287</v>
+        <v>4289</v>
       </c>
       <c r="E91">
         <v>58062</v>
       </c>
       <c r="F91">
-        <v>30359</v>
+        <v>30360</v>
       </c>
       <c r="G91">
-        <v>43717</v>
+        <v>43718</v>
       </c>
       <c r="H91">
-        <v>26072</v>
+        <v>26071</v>
       </c>
       <c r="I91" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1222140/Detroit_Become_Human/?curator_clanid=4777282","Abrir Steam")</f>
@@ -4478,16 +4478,16 @@
         <v>17</v>
       </c>
       <c r="D93">
-        <v>12230</v>
+        <v>12222</v>
       </c>
       <c r="E93">
         <v>27207</v>
       </c>
       <c r="F93">
-        <v>27230</v>
+        <v>27222</v>
       </c>
       <c r="G93">
-        <v>39211</v>
+        <v>39200</v>
       </c>
       <c r="H93">
         <v>15000</v>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61984</v>
+        <v>61945</v>
       </c>
       <c r="E96">
         <v>81657</v>
       </c>
       <c r="F96">
-        <v>76984</v>
+        <v>76979</v>
       </c>
       <c r="G96">
-        <v>110857</v>
+        <v>110850</v>
       </c>
       <c r="H96">
-        <v>15000</v>
+        <v>15034</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33711</v>
+        <v>33700</v>
       </c>
       <c r="E97">
         <v>81657</v>
       </c>
       <c r="F97">
-        <v>51331</v>
+        <v>51326</v>
       </c>
       <c r="G97">
-        <v>73917</v>
+        <v>73909</v>
       </c>
       <c r="H97">
-        <v>17620</v>
+        <v>17626</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>79635</v>
+        <v>82130</v>
       </c>
       <c r="E98">
         <v>94362</v>
       </c>
       <c r="F98">
-        <v>96005</v>
+        <v>0</v>
       </c>
       <c r="G98">
-        <v>138247</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>16370</v>
+        <v>0</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,16 +4744,16 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>68477</v>
+        <v>68442</v>
       </c>
       <c r="E99">
         <v>94362</v>
       </c>
       <c r="F99">
-        <v>83477</v>
+        <v>83442</v>
       </c>
       <c r="G99">
-        <v>120207</v>
+        <v>120156</v>
       </c>
       <c r="H99">
         <v>15000</v>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61716</v>
+        <v>61676</v>
       </c>
       <c r="E100">
         <v>105796</v>
       </c>
       <c r="F100">
-        <v>78295</v>
+        <v>78279</v>
       </c>
       <c r="G100">
-        <v>112745</v>
+        <v>112722</v>
       </c>
       <c r="H100">
-        <v>16579</v>
+        <v>16603</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5176,16 +5176,16 @@
         <v>17</v>
       </c>
       <c r="D109">
-        <v>3247</v>
+        <v>3249</v>
       </c>
       <c r="E109">
         <v>163332</v>
       </c>
       <c r="F109">
-        <v>30247</v>
+        <v>30249</v>
       </c>
       <c r="G109">
-        <v>43556</v>
+        <v>43559</v>
       </c>
       <c r="H109">
         <v>27000</v>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14152</v>
+        <v>14146</v>
       </c>
       <c r="E111">
         <v>163332</v>
       </c>
       <c r="F111">
-        <v>41152</v>
+        <v>41146</v>
       </c>
       <c r="G111">
-        <v>59259</v>
+        <v>59250</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>91077</v>
+        <v>91119</v>
       </c>
       <c r="E112">
         <v>87102</v>
       </c>
       <c r="F112">
-        <v>106077</v>
+        <v>0</v>
       </c>
       <c r="G112">
-        <v>152751</v>
+        <v>0</v>
       </c>
       <c r="H112">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,16 +5352,16 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>53237</v>
+        <v>52830</v>
       </c>
       <c r="E113">
         <v>87102</v>
       </c>
       <c r="F113">
-        <v>68237</v>
+        <v>67830</v>
       </c>
       <c r="G113">
-        <v>98261</v>
+        <v>97675</v>
       </c>
       <c r="H113">
         <v>15000</v>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>85545</v>
+        <v>99572</v>
       </c>
       <c r="E115">
         <v>116142</v>
       </c>
       <c r="F115">
-        <v>100545</v>
+        <v>0</v>
       </c>
       <c r="G115">
-        <v>144785</v>
+        <v>0</v>
       </c>
       <c r="H115">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>169136</v>
+        <v>169228</v>
       </c>
       <c r="E116">
         <v>145182</v>
       </c>
       <c r="F116">
-        <v>184136</v>
+        <v>0</v>
       </c>
       <c r="G116">
-        <v>265156</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5526,19 +5526,19 @@
         <v>17</v>
       </c>
       <c r="D117">
-        <v>114938</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>145182</v>
       </c>
       <c r="F117">
-        <v>129938</v>
+        <v>0</v>
       </c>
       <c r="G117">
-        <v>187111</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I117" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>44207</v>
+        <v>44235</v>
       </c>
       <c r="E118">
         <v>58062</v>
       </c>
       <c r="F118">
-        <v>59207</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>85258</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>32765</v>
+        <v>33070</v>
       </c>
       <c r="E119">
         <v>58062</v>
       </c>
       <c r="F119">
-        <v>47765</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>68782</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,19 +5658,19 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>61259</v>
+        <v>61298</v>
       </c>
       <c r="E120">
         <v>79842</v>
       </c>
       <c r="F120">
-        <v>79434</v>
+        <v>76298</v>
       </c>
       <c r="G120">
-        <v>114385</v>
+        <v>109869</v>
       </c>
       <c r="H120">
-        <v>18175</v>
+        <v>15000</v>
       </c>
       <c r="I120" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5703,19 +5703,19 @@
         <v>17</v>
       </c>
       <c r="D121">
-        <v>54073</v>
+        <v>0</v>
       </c>
       <c r="E121">
         <v>79842</v>
       </c>
       <c r="F121">
-        <v>69073</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>99465</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I121" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>42253</v>
+        <v>44897</v>
       </c>
       <c r="E123">
         <v>90732</v>
       </c>
       <c r="F123">
-        <v>58287</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>83933</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>16034</v>
+        <v>0</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13301</v>
+        <v>13562</v>
       </c>
       <c r="E124">
         <v>43542</v>
@@ -5845,7 +5845,7 @@
         <v>47026</v>
       </c>
       <c r="H124">
-        <v>19356</v>
+        <v>19095</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>7391</v>
+        <v>8642</v>
       </c>
       <c r="E125">
         <v>43542</v>
       </c>
       <c r="F125">
-        <v>25938</v>
+        <v>26438</v>
       </c>
       <c r="G125">
-        <v>37351</v>
+        <v>38071</v>
       </c>
       <c r="H125">
-        <v>18547</v>
+        <v>17796</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>30653</v>
+        <v>30121</v>
       </c>
       <c r="E126">
         <v>58062</v>
       </c>
       <c r="F126">
-        <v>45653</v>
+        <v>45121</v>
       </c>
       <c r="G126">
-        <v>65740</v>
+        <v>64974</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20283</v>
+        <v>20264</v>
       </c>
       <c r="E129">
         <v>59496</v>
       </c>
       <c r="F129">
-        <v>37316</v>
+        <v>37309</v>
       </c>
       <c r="G129">
-        <v>53735</v>
+        <v>53725</v>
       </c>
       <c r="H129">
-        <v>17033</v>
+        <v>17045</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>36358</v>
+        <v>36350</v>
       </c>
       <c r="E131">
         <v>74125</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>51350</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>73944</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37840</v>
+        <v>37816</v>
       </c>
       <c r="E133">
         <v>93309</v>
       </c>
       <c r="F133">
-        <v>57527</v>
+        <v>57517</v>
       </c>
       <c r="G133">
-        <v>82839</v>
+        <v>82824</v>
       </c>
       <c r="H133">
-        <v>19687</v>
+        <v>19701</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,16 +6314,16 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53616</v>
+        <v>53586</v>
       </c>
       <c r="E135">
         <v>88917</v>
       </c>
       <c r="F135">
-        <v>68616</v>
+        <v>68586</v>
       </c>
       <c r="G135">
-        <v>98807</v>
+        <v>98764</v>
       </c>
       <c r="H135">
         <v>15000</v>
@@ -6400,16 +6400,16 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>72197</v>
+        <v>72148</v>
       </c>
       <c r="E137">
         <v>127032</v>
       </c>
       <c r="F137">
-        <v>87197</v>
+        <v>87148</v>
       </c>
       <c r="G137">
-        <v>125564</v>
+        <v>125493</v>
       </c>
       <c r="H137">
         <v>15000</v>
@@ -6486,16 +6486,16 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91897</v>
+        <v>91844</v>
       </c>
       <c r="E139">
         <v>152442</v>
       </c>
       <c r="F139">
-        <v>106897</v>
+        <v>106844</v>
       </c>
       <c r="G139">
-        <v>153932</v>
+        <v>153855</v>
       </c>
       <c r="H139">
         <v>15000</v>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37414</v>
+        <v>37375</v>
       </c>
       <c r="E140">
         <v>90732</v>
       </c>
       <c r="F140">
-        <v>61795</v>
+        <v>61779</v>
       </c>
       <c r="G140">
-        <v>88985</v>
+        <v>88962</v>
       </c>
       <c r="H140">
-        <v>24381</v>
+        <v>24404</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,19 +6618,19 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>22994</v>
+        <v>23229</v>
       </c>
       <c r="E142">
         <v>90732</v>
       </c>
       <c r="F142">
-        <v>52667</v>
+        <v>58229</v>
       </c>
       <c r="G142">
-        <v>75840</v>
+        <v>83850</v>
       </c>
       <c r="H142">
-        <v>29673</v>
+        <v>35000</v>
       </c>
       <c r="I142" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>17667</v>
+        <v>28938</v>
       </c>
       <c r="E143">
         <v>90732</v>
       </c>
       <c r="F143">
-        <v>44667</v>
+        <v>52961</v>
       </c>
       <c r="G143">
-        <v>64320</v>
+        <v>76264</v>
       </c>
       <c r="H143">
-        <v>27000</v>
+        <v>24023</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45594</v>
+        <v>45023</v>
       </c>
       <c r="E144">
         <v>90732</v>
@@ -6718,7 +6718,7 @@
         <v>97991</v>
       </c>
       <c r="H144">
-        <v>22455</v>
+        <v>23026</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,16 +6751,16 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>65278</v>
+        <v>65240</v>
       </c>
       <c r="E145">
         <v>90732</v>
       </c>
       <c r="F145">
-        <v>80278</v>
+        <v>80240</v>
       </c>
       <c r="G145">
-        <v>115600</v>
+        <v>115546</v>
       </c>
       <c r="H145">
         <v>15000</v>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>65845</v>
+        <v>65461</v>
       </c>
       <c r="E146">
         <v>90732</v>
       </c>
       <c r="F146">
-        <v>80845</v>
+        <v>80461</v>
       </c>
       <c r="G146">
-        <v>116417</v>
+        <v>115864</v>
       </c>
       <c r="H146">
         <v>15000</v>
@@ -6883,19 +6883,19 @@
         <v>15</v>
       </c>
       <c r="D148">
-        <v>36957</v>
+        <v>36965</v>
       </c>
       <c r="E148">
         <v>61692</v>
       </c>
       <c r="F148">
-        <v>64482</v>
+        <v>64460</v>
       </c>
       <c r="G148">
-        <v>92854</v>
+        <v>92822</v>
       </c>
       <c r="H148">
-        <v>27525</v>
+        <v>27495</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,16 +6929,16 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>41071</v>
+        <v>41049</v>
       </c>
       <c r="E149">
         <v>61692</v>
       </c>
       <c r="F149">
-        <v>56071</v>
+        <v>56049</v>
       </c>
       <c r="G149">
-        <v>80742</v>
+        <v>80711</v>
       </c>
       <c r="H149">
         <v>15000</v>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15728</v>
+        <v>15344</v>
       </c>
       <c r="E151">
         <v>54432</v>
       </c>
       <c r="F151">
-        <v>33520</v>
+        <v>33366</v>
       </c>
       <c r="G151">
-        <v>48269</v>
+        <v>48047</v>
       </c>
       <c r="H151">
-        <v>17792</v>
+        <v>18022</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37651</v>
+        <v>37485</v>
       </c>
       <c r="E152">
         <v>72582</v>
@@ -7070,7 +7070,7 @@
         <v>78389</v>
       </c>
       <c r="H152">
-        <v>16786</v>
+        <v>16952</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>33458</v>
+        <v>35419</v>
       </c>
       <c r="E153">
         <v>72582</v>
       </c>
       <c r="F153">
-        <v>48458</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>69780</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56547</v>
+        <v>56567</v>
       </c>
       <c r="E154">
         <v>72582</v>
       </c>
       <c r="F154">
-        <v>91547</v>
+        <v>71567</v>
       </c>
       <c r="G154">
-        <v>131828</v>
+        <v>103056</v>
       </c>
       <c r="H154">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>73300</v>
+        <v>0</v>
       </c>
       <c r="E155">
         <v>72582</v>
       </c>
       <c r="F155">
-        <v>88300</v>
+        <v>0</v>
       </c>
       <c r="G155">
-        <v>127152</v>
+        <v>0</v>
       </c>
       <c r="H155">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>34577</v>
+        <v>31572</v>
       </c>
       <c r="E156">
         <v>59877</v>
       </c>
       <c r="F156">
-        <v>50346</v>
+        <v>50343</v>
       </c>
       <c r="G156">
-        <v>72498</v>
+        <v>72494</v>
       </c>
       <c r="H156">
-        <v>15769</v>
+        <v>18771</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11678</v>
+        <v>11670</v>
       </c>
       <c r="E157">
         <v>59877</v>
       </c>
       <c r="F157">
-        <v>34023</v>
+        <v>34020</v>
       </c>
       <c r="G157">
-        <v>48993</v>
+        <v>48989</v>
       </c>
       <c r="H157">
-        <v>22345</v>
+        <v>22350</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36185</v>
+        <v>36161</v>
       </c>
       <c r="E159">
         <v>83472</v>
       </c>
       <c r="F159">
-        <v>53028</v>
+        <v>53019</v>
       </c>
       <c r="G159">
-        <v>76360</v>
+        <v>76347</v>
       </c>
       <c r="H159">
-        <v>16843</v>
+        <v>16858</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7411,19 +7411,19 @@
         <v>15</v>
       </c>
       <c r="D160">
-        <v>7770</v>
+        <v>7775</v>
       </c>
       <c r="E160">
         <v>54450</v>
       </c>
       <c r="F160">
-        <v>38873</v>
+        <v>38838</v>
       </c>
       <c r="G160">
-        <v>55977</v>
+        <v>55927</v>
       </c>
       <c r="H160">
-        <v>31103</v>
+        <v>31063</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>9094</v>
+        <v>9005</v>
       </c>
       <c r="E161">
         <v>54450</v>
       </c>
       <c r="F161">
-        <v>30873</v>
+        <v>30838</v>
       </c>
       <c r="G161">
-        <v>44457</v>
+        <v>44407</v>
       </c>
       <c r="H161">
-        <v>21779</v>
+        <v>21833</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,19 +7501,19 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>9960</v>
+        <v>9793</v>
       </c>
       <c r="E162">
         <v>72582</v>
       </c>
       <c r="F162">
-        <v>44629</v>
+        <v>44793</v>
       </c>
       <c r="G162">
-        <v>64266</v>
+        <v>64502</v>
       </c>
       <c r="H162">
-        <v>34669</v>
+        <v>35000</v>
       </c>
       <c r="I162" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>9629</v>
+        <v>10456</v>
       </c>
       <c r="E163">
         <v>72582</v>
       </c>
       <c r="F163">
-        <v>36629</v>
+        <v>37456</v>
       </c>
       <c r="G163">
-        <v>52746</v>
+        <v>53937</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,19 +7591,19 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>68383</v>
+        <v>68426</v>
       </c>
       <c r="E164">
         <v>68063</v>
       </c>
       <c r="F164">
-        <v>83383</v>
+        <v>0</v>
       </c>
       <c r="G164">
-        <v>120072</v>
+        <v>0</v>
       </c>
       <c r="H164">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I164" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>22017</v>
+        <v>21999</v>
       </c>
       <c r="E165">
         <v>68063</v>
       </c>
       <c r="F165">
-        <v>41351</v>
+        <v>41344</v>
       </c>
       <c r="G165">
-        <v>59545</v>
+        <v>59535</v>
       </c>
       <c r="H165">
-        <v>19334</v>
+        <v>19345</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,19 +7679,19 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>91865</v>
+        <v>91923</v>
       </c>
       <c r="E166">
         <v>102548</v>
       </c>
       <c r="F166">
-        <v>106865</v>
+        <v>0</v>
       </c>
       <c r="G166">
-        <v>153886</v>
+        <v>0</v>
       </c>
       <c r="H166">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I166" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7722,16 +7722,16 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>57193</v>
+        <v>57150</v>
       </c>
       <c r="E167">
         <v>102548</v>
       </c>
       <c r="F167">
-        <v>72193</v>
+        <v>72150</v>
       </c>
       <c r="G167">
-        <v>103958</v>
+        <v>103896</v>
       </c>
       <c r="H167">
         <v>15000</v>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>9015</v>
+        <v>9005</v>
       </c>
       <c r="E169">
         <v>72582</v>
       </c>
       <c r="F169">
-        <v>36015</v>
+        <v>36005</v>
       </c>
       <c r="G169">
-        <v>51862</v>
+        <v>51847</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59715</v>
+        <v>59753</v>
       </c>
       <c r="E170">
         <v>108882</v>
       </c>
       <c r="F170">
-        <v>78883</v>
+        <v>78898</v>
       </c>
       <c r="G170">
-        <v>113592</v>
+        <v>113613</v>
       </c>
       <c r="H170">
-        <v>19168</v>
+        <v>19145</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>78942</v>
+        <v>91766</v>
       </c>
       <c r="E172">
         <v>145182</v>
       </c>
       <c r="F172">
-        <v>102909</v>
+        <v>0</v>
       </c>
       <c r="G172">
-        <v>148189</v>
+        <v>0</v>
       </c>
       <c r="H172">
-        <v>23967</v>
+        <v>0</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>79008</v>
       </c>
       <c r="E173">
         <v>145182</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>94224</v>
       </c>
       <c r="G173">
-        <v>0</v>
+        <v>135683</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>15216</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>45420</v>
+        <v>45386</v>
       </c>
       <c r="E174">
         <v>90732</v>
@@ -8045,7 +8045,7 @@
         <v>97991</v>
       </c>
       <c r="H174">
-        <v>22629</v>
+        <v>22663</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,16 +8078,16 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>67957</v>
+        <v>67906</v>
       </c>
       <c r="E175">
         <v>90732</v>
       </c>
       <c r="F175">
-        <v>82957</v>
+        <v>82906</v>
       </c>
       <c r="G175">
-        <v>119458</v>
+        <v>119385</v>
       </c>
       <c r="H175">
         <v>15000</v>
@@ -8122,16 +8122,16 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>65751</v>
+        <v>61771</v>
       </c>
       <c r="E176">
         <v>90732</v>
       </c>
       <c r="F176">
-        <v>80751</v>
+        <v>76771</v>
       </c>
       <c r="G176">
-        <v>116281</v>
+        <v>110550</v>
       </c>
       <c r="H176">
         <v>15000</v>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26493</v>
+        <v>26509</v>
       </c>
       <c r="E178">
         <v>108882</v>
       </c>
       <c r="F178">
-        <v>53493</v>
+        <v>53509</v>
       </c>
       <c r="G178">
-        <v>77030</v>
+        <v>77053</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>22584</v>
+        <v>24664</v>
       </c>
       <c r="E180">
         <v>90732</v>
       </c>
       <c r="F180">
-        <v>49584</v>
+        <v>51664</v>
       </c>
       <c r="G180">
-        <v>71401</v>
+        <v>74396</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8387,19 +8387,19 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>100848</v>
+        <v>0</v>
       </c>
       <c r="E182">
         <v>127032</v>
       </c>
       <c r="F182">
-        <v>115896</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>166890</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>15048</v>
+        <v>0</v>
       </c>
       <c r="I182" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64648</v>
+        <v>64610</v>
       </c>
       <c r="E183">
         <v>127032</v>
       </c>
       <c r="F183">
-        <v>81402</v>
+        <v>81387</v>
       </c>
       <c r="G183">
-        <v>117219</v>
+        <v>117197</v>
       </c>
       <c r="H183">
-        <v>16754</v>
+        <v>16777</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8474,19 +8474,19 @@
         <v>15</v>
       </c>
       <c r="D184">
-        <v>144976</v>
+        <v>0</v>
       </c>
       <c r="E184">
         <v>181482</v>
       </c>
       <c r="F184">
-        <v>159976</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>230365</v>
+        <v>0</v>
       </c>
       <c r="H184">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I184" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8561,19 +8561,19 @@
         <v>15</v>
       </c>
       <c r="D186">
-        <v>189104</v>
+        <v>0</v>
       </c>
       <c r="E186">
         <v>235932</v>
       </c>
       <c r="F186">
-        <v>204104</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>293910</v>
+        <v>0</v>
       </c>
       <c r="H186">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I186" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8648,19 +8648,19 @@
         <v>15</v>
       </c>
       <c r="D188">
-        <v>291544</v>
+        <v>291729</v>
       </c>
       <c r="E188">
         <v>362982</v>
       </c>
       <c r="F188">
-        <v>306544</v>
+        <v>0</v>
       </c>
       <c r="G188">
-        <v>441423</v>
+        <v>0</v>
       </c>
       <c r="H188">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29723</v>
+        <v>29758</v>
       </c>
       <c r="E190">
         <v>95269</v>
       </c>
       <c r="F190">
-        <v>64723</v>
+        <v>64758</v>
       </c>
       <c r="G190">
-        <v>93201</v>
+        <v>93252</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>74151</v>
+        <v>44676</v>
       </c>
       <c r="E191">
         <v>95269</v>
       </c>
       <c r="F191">
-        <v>89151</v>
+        <v>61025</v>
       </c>
       <c r="G191">
-        <v>128377</v>
+        <v>87876</v>
       </c>
       <c r="H191">
-        <v>15000</v>
+        <v>16349</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>40976</v>
+        <v>40939</v>
       </c>
       <c r="E192">
         <v>122494</v>
       </c>
       <c r="F192">
-        <v>67976</v>
+        <v>75939</v>
       </c>
       <c r="G192">
-        <v>97885</v>
+        <v>109352</v>
       </c>
       <c r="H192">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8868,19 +8868,19 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>146377</v>
       </c>
       <c r="E193">
         <v>122494</v>
       </c>
       <c r="F193">
-        <v>0</v>
+        <v>161377</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>232383</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I193" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,19 +8911,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>53474</v>
+        <v>24428</v>
       </c>
       <c r="E194">
         <v>149901</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>51428</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>74056</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8955,19 +8955,19 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>146377</v>
       </c>
       <c r="E195">
         <v>122494</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>161377</v>
       </c>
       <c r="G195">
-        <v>0</v>
+        <v>232383</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I195" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>13632</v>
+        <v>14225</v>
       </c>
       <c r="E196">
         <v>72582</v>
       </c>
       <c r="F196">
-        <v>40632</v>
+        <v>49225</v>
       </c>
       <c r="G196">
-        <v>58510</v>
+        <v>70884</v>
       </c>
       <c r="H196">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>32565</v>
       </c>
       <c r="E197">
         <v>72582</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>47565</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>68494</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>22127</v>
+        <v>20517</v>
       </c>
       <c r="E198">
         <v>108882</v>
       </c>
       <c r="F198">
-        <v>49127</v>
+        <v>47517</v>
       </c>
       <c r="G198">
-        <v>70743</v>
+        <v>68424</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>13175</v>
+        <v>13058</v>
       </c>
       <c r="E200">
         <v>127032</v>
       </c>
       <c r="F200">
-        <v>46852</v>
+        <v>46638</v>
       </c>
       <c r="G200">
-        <v>67467</v>
+        <v>67159</v>
       </c>
       <c r="H200">
-        <v>33677</v>
+        <v>33580</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11852</v>
+        <v>11638</v>
       </c>
       <c r="E201">
         <v>127032</v>
       </c>
       <c r="F201">
-        <v>38852</v>
+        <v>38638</v>
       </c>
       <c r="G201">
-        <v>55947</v>
+        <v>55639</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9266,16 +9266,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>22363</v>
+        <v>22378</v>
       </c>
       <c r="E202">
         <v>145182</v>
       </c>
       <c r="F202">
-        <v>57363</v>
+        <v>57378</v>
       </c>
       <c r="G202">
-        <v>82603</v>
+        <v>82624</v>
       </c>
       <c r="H202">
         <v>35000</v>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>82787</v>
+        <v>22756</v>
       </c>
       <c r="E203">
         <v>145182</v>
       </c>
       <c r="F203">
-        <v>97787</v>
+        <v>49756</v>
       </c>
       <c r="G203">
-        <v>140813</v>
+        <v>71649</v>
       </c>
       <c r="H203">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>25137</v>
+        <v>25043</v>
       </c>
       <c r="E204">
         <v>181482</v>
       </c>
       <c r="F204">
-        <v>52137</v>
+        <v>60043</v>
       </c>
       <c r="G204">
-        <v>75077</v>
+        <v>86462</v>
       </c>
       <c r="H204">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>26446</v>
       </c>
       <c r="E205">
         <v>181482</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>53446</v>
       </c>
       <c r="G205">
-        <v>0</v>
+        <v>76962</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9445,19 +9445,19 @@
         <v>15</v>
       </c>
       <c r="D206">
-        <v>24066</v>
+        <v>18467</v>
       </c>
       <c r="E206">
         <v>58062</v>
       </c>
       <c r="F206">
-        <v>41920</v>
+        <v>41690</v>
       </c>
       <c r="G206">
-        <v>60365</v>
+        <v>60034</v>
       </c>
       <c r="H206">
-        <v>17854</v>
+        <v>23223</v>
       </c>
       <c r="I206" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9491,19 +9491,19 @@
         <v>17</v>
       </c>
       <c r="D207">
-        <v>13191</v>
+        <v>12616</v>
       </c>
       <c r="E207">
         <v>58062</v>
       </c>
       <c r="F207">
-        <v>33920</v>
+        <v>33690</v>
       </c>
       <c r="G207">
-        <v>48845</v>
+        <v>48514</v>
       </c>
       <c r="H207">
-        <v>20729</v>
+        <v>21074</v>
       </c>
       <c r="I207" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/524220/NieRAutomata/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>0</v>
+        <v>40497</v>
       </c>
       <c r="E211">
         <v>108882</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>64663</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>93115</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>24166</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9749,19 +9749,19 @@
         <v>17</v>
       </c>
       <c r="D213">
-        <v>83780</v>
+        <v>0</v>
       </c>
       <c r="E213">
         <v>181482</v>
       </c>
       <c r="F213">
-        <v>110290</v>
+        <v>0</v>
       </c>
       <c r="G213">
-        <v>158818</v>
+        <v>0</v>
       </c>
       <c r="H213">
-        <v>26510</v>
+        <v>0</v>
       </c>
       <c r="I213" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>27879</v>
+        <v>27897</v>
       </c>
       <c r="E214">
         <v>87102</v>
       </c>
       <c r="F214">
-        <v>54879</v>
+        <v>60510</v>
       </c>
       <c r="G214">
-        <v>79026</v>
+        <v>87134</v>
       </c>
       <c r="H214">
-        <v>27000</v>
+        <v>32613</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>31351</v>
       </c>
       <c r="E215">
         <v>87102</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>52510</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>75614</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>21159</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45909</v>
+        <v>45875</v>
       </c>
       <c r="E216">
         <v>101622</v>
@@ -9893,7 +9893,7 @@
         <v>109752</v>
       </c>
       <c r="H216">
-        <v>30308</v>
+        <v>30342</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,19 +9927,19 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>89375</v>
+        <v>89432</v>
       </c>
       <c r="E217">
         <v>101622</v>
       </c>
       <c r="F217">
-        <v>104375</v>
+        <v>0</v>
       </c>
       <c r="G217">
-        <v>150300</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I217" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>110374</v>
       </c>
       <c r="E219">
         <v>130662</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>125374</v>
       </c>
       <c r="G219">
-        <v>0</v>
+        <v>180539</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>62709</v>
+        <v>62733</v>
       </c>
       <c r="E220">
         <v>81675</v>
       </c>
       <c r="F220">
-        <v>77709</v>
+        <v>0</v>
       </c>
       <c r="G220">
-        <v>111901</v>
+        <v>0</v>
       </c>
       <c r="H220">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>50921</v>
       </c>
       <c r="E221">
         <v>81675</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>65921</v>
       </c>
       <c r="G221">
-        <v>0</v>
+        <v>94926</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>74687</v>
+        <v>75365</v>
       </c>
       <c r="E222">
         <v>96195</v>
       </c>
       <c r="F222">
-        <v>89687</v>
+        <v>0</v>
       </c>
       <c r="G222">
-        <v>129149</v>
+        <v>0</v>
       </c>
       <c r="H222">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>0</v>
+        <v>94368</v>
       </c>
       <c r="E223">
         <v>96195</v>
       </c>
       <c r="F223">
-        <v>0</v>
+        <v>109368</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>157490</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16422</v>
+        <v>16196</v>
       </c>
       <c r="E224">
         <v>59877</v>
       </c>
       <c r="F224">
-        <v>44905</v>
+        <v>44901</v>
       </c>
       <c r="G224">
-        <v>64663</v>
+        <v>64657</v>
       </c>
       <c r="H224">
-        <v>28483</v>
+        <v>28705</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10417</v>
+        <v>10408</v>
       </c>
       <c r="E225">
         <v>59877</v>
       </c>
       <c r="F225">
-        <v>33519</v>
+        <v>33515</v>
       </c>
       <c r="G225">
-        <v>48267</v>
+        <v>48262</v>
       </c>
       <c r="H225">
-        <v>23102</v>
+        <v>23107</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10329,19 +10329,19 @@
         <v>15</v>
       </c>
       <c r="D226">
-        <v>38013</v>
+        <v>0</v>
       </c>
       <c r="E226">
         <v>72582</v>
       </c>
       <c r="F226">
-        <v>53867</v>
+        <v>0</v>
       </c>
       <c r="G226">
-        <v>77568</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>15854</v>
+        <v>0</v>
       </c>
       <c r="I226" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10375,19 +10375,19 @@
         <v>17</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>23497</v>
       </c>
       <c r="E227">
         <v>72582</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>43706</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>62937</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>20209</v>
       </c>
       <c r="I227" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10418,19 +10418,19 @@
         <v>15</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>83991</v>
       </c>
       <c r="E228">
         <v>108882</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>98991</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>142547</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I228" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>0</v>
+        <v>19287</v>
       </c>
       <c r="E231">
         <v>181482</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>46287</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>66653</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9440</v>
+        <v>9415</v>
       </c>
       <c r="E232">
         <v>52635</v>
       </c>
       <c r="F232">
-        <v>34528</v>
+        <v>38540</v>
       </c>
       <c r="G232">
-        <v>49720</v>
+        <v>55498</v>
       </c>
       <c r="H232">
-        <v>25088</v>
+        <v>29125</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>10030</v>
       </c>
       <c r="E233">
         <v>52635</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>30540</v>
       </c>
       <c r="G233">
-        <v>0</v>
+        <v>43978</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>20510</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,16 +10677,16 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>11946</v>
+        <v>12048</v>
       </c>
       <c r="E234">
         <v>70785</v>
       </c>
       <c r="F234">
-        <v>38946</v>
+        <v>39048</v>
       </c>
       <c r="G234">
-        <v>56082</v>
+        <v>56229</v>
       </c>
       <c r="H234">
         <v>27000</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>8479</v>
+        <v>8500</v>
       </c>
       <c r="E236">
         <v>52635</v>
       </c>
       <c r="F236">
-        <v>37251</v>
+        <v>35758</v>
       </c>
       <c r="G236">
-        <v>53641</v>
+        <v>51492</v>
       </c>
       <c r="H236">
-        <v>28772</v>
+        <v>27258</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>6808</v>
+        <v>3075</v>
       </c>
       <c r="E237">
         <v>52635</v>
       </c>
       <c r="F237">
-        <v>29251</v>
+        <v>27758</v>
       </c>
       <c r="G237">
-        <v>42121</v>
+        <v>39972</v>
       </c>
       <c r="H237">
-        <v>22443</v>
+        <v>24683</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>0</v>
+        <v>11386</v>
       </c>
       <c r="E239">
         <v>52635</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>31082</v>
       </c>
       <c r="G239">
-        <v>0</v>
+        <v>44758</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>19696</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>20249</v>
       </c>
       <c r="E240">
         <v>70785</v>
       </c>
       <c r="F240">
-        <v>0</v>
+        <v>53089</v>
       </c>
       <c r="G240">
-        <v>0</v>
+        <v>76448</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>32840</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>0</v>
+        <v>70382</v>
       </c>
       <c r="E241">
         <v>70785</v>
       </c>
       <c r="F241">
-        <v>0</v>
+        <v>85382</v>
       </c>
       <c r="G241">
-        <v>0</v>
+        <v>122950</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34231</v>
+        <v>34252</v>
       </c>
       <c r="E242">
         <v>70785</v>
       </c>
       <c r="F242">
-        <v>51546</v>
+        <v>51554</v>
       </c>
       <c r="G242">
-        <v>74226</v>
+        <v>74238</v>
       </c>
       <c r="H242">
-        <v>17315</v>
+        <v>17302</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9803</v>
+        <v>9904</v>
       </c>
       <c r="E244">
         <v>27225</v>
       </c>
       <c r="F244">
-        <v>24803</v>
+        <v>0</v>
       </c>
       <c r="G244">
-        <v>35716</v>
+        <v>0</v>
       </c>
       <c r="H244">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11915</v>
+        <v>11938</v>
       </c>
       <c r="E246">
         <v>108882</v>
       </c>
       <c r="F246">
-        <v>38915</v>
+        <v>38938</v>
       </c>
       <c r="G246">
-        <v>56038</v>
+        <v>56071</v>
       </c>
       <c r="H246">
         <v>27000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>58974</v>
+        <v>59122</v>
       </c>
       <c r="E248">
         <v>96195</v>
       </c>
       <c r="F248">
-        <v>73974</v>
+        <v>0</v>
       </c>
       <c r="G248">
-        <v>106523</v>
+        <v>0</v>
       </c>
       <c r="H248">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I248" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11337,19 +11337,19 @@
         <v>17</v>
       </c>
       <c r="D249">
-        <v>0</v>
+        <v>48067</v>
       </c>
       <c r="E249">
         <v>96195</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>63067</v>
       </c>
       <c r="G249">
-        <v>0</v>
+        <v>90816</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I249" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11380,19 +11380,19 @@
         <v>15</v>
       </c>
       <c r="D250">
-        <v>70731</v>
+        <v>70602</v>
       </c>
       <c r="E250">
         <v>108882</v>
       </c>
       <c r="F250">
-        <v>85731</v>
+        <v>103448</v>
       </c>
       <c r="G250">
-        <v>123453</v>
+        <v>148965</v>
       </c>
       <c r="H250">
-        <v>15000</v>
+        <v>32846</v>
       </c>
       <c r="I250" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11426,19 +11426,19 @@
         <v>17</v>
       </c>
       <c r="D251">
-        <v>0</v>
+        <v>74955</v>
       </c>
       <c r="E251">
         <v>108882</v>
       </c>
       <c r="F251">
-        <v>0</v>
+        <v>89955</v>
       </c>
       <c r="G251">
-        <v>0</v>
+        <v>129535</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I251" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3764200/Resident_Evil_Requiem/","Abrir Steam")</f>
@@ -11469,19 +11469,19 @@
         <v>15</v>
       </c>
       <c r="D252">
-        <v>11930</v>
+        <v>11938</v>
       </c>
       <c r="E252">
         <v>52635</v>
       </c>
       <c r="F252">
-        <v>34528</v>
+        <v>39476</v>
       </c>
       <c r="G252">
-        <v>49720</v>
+        <v>56845</v>
       </c>
       <c r="H252">
-        <v>22598</v>
+        <v>27538</v>
       </c>
       <c r="I252" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11515,19 +11515,19 @@
         <v>17</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>38826</v>
       </c>
       <c r="E253">
         <v>52635</v>
       </c>
       <c r="F253">
-        <v>0</v>
+        <v>53826</v>
       </c>
       <c r="G253">
-        <v>0</v>
+        <v>77509</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I253" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11558,19 +11558,19 @@
         <v>15</v>
       </c>
       <c r="D254">
-        <v>17226</v>
+        <v>17189</v>
       </c>
       <c r="E254">
         <v>70785</v>
       </c>
       <c r="F254">
-        <v>44226</v>
+        <v>52189</v>
       </c>
       <c r="G254">
-        <v>63685</v>
+        <v>75152</v>
       </c>
       <c r="H254">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I254" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11604,19 +11604,19 @@
         <v>17</v>
       </c>
       <c r="D255">
-        <v>0</v>
+        <v>67701</v>
       </c>
       <c r="E255">
         <v>70785</v>
       </c>
       <c r="F255">
-        <v>0</v>
+        <v>82701</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>119089</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I255" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11776,19 +11776,19 @@
         <v>17</v>
       </c>
       <c r="D259">
-        <v>12561</v>
+        <v>12553</v>
       </c>
       <c r="E259">
         <v>50802</v>
       </c>
       <c r="F259">
-        <v>30837</v>
+        <v>30834</v>
       </c>
       <c r="G259">
-        <v>44405</v>
+        <v>44401</v>
       </c>
       <c r="H259">
-        <v>18276</v>
+        <v>18281</v>
       </c>
       <c r="I259" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1172620/Sea_of_Thieves_2026_Edition/","Abrir Steam")</f>
@@ -11862,16 +11862,16 @@
         <v>17</v>
       </c>
       <c r="D261">
-        <v>62725</v>
+        <v>62686</v>
       </c>
       <c r="E261">
         <v>63507</v>
       </c>
       <c r="F261">
-        <v>77725</v>
+        <v>77686</v>
       </c>
       <c r="G261">
-        <v>111924</v>
+        <v>111868</v>
       </c>
       <c r="H261">
         <v>15000</v>
@@ -11948,16 +11948,16 @@
         <v>17</v>
       </c>
       <c r="D263">
-        <v>75459</v>
+        <v>75412</v>
       </c>
       <c r="E263">
         <v>72582</v>
       </c>
       <c r="F263">
-        <v>90459</v>
+        <v>90412</v>
       </c>
       <c r="G263">
-        <v>130261</v>
+        <v>130193</v>
       </c>
       <c r="H263">
         <v>15000</v>
@@ -11992,19 +11992,19 @@
         <v>15</v>
       </c>
       <c r="D264">
-        <v>40298</v>
+        <v>40324</v>
       </c>
       <c r="E264">
         <v>59877</v>
       </c>
       <c r="F264">
-        <v>55298</v>
+        <v>0</v>
       </c>
       <c r="G264">
-        <v>79629</v>
+        <v>0</v>
       </c>
       <c r="H264">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I264" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2124490/SILENT_HILL_2/","Abrir Steam")</f>
@@ -12038,16 +12038,16 @@
         <v>17</v>
       </c>
       <c r="D265">
-        <v>25531</v>
+        <v>25516</v>
       </c>
       <c r="E265">
         <v>59877</v>
       </c>
       <c r="F265">
-        <v>40531</v>
+        <v>40516</v>
       </c>
       <c r="G265">
-        <v>58365</v>
+        <v>58343</v>
       </c>
       <c r="H265">
         <v>15000</v>
@@ -12171,19 +12171,19 @@
         <v>15</v>
       </c>
       <c r="D268">
-        <v>34987</v>
+        <v>35009</v>
       </c>
       <c r="E268">
         <v>59877</v>
       </c>
       <c r="F268">
-        <v>49987</v>
+        <v>0</v>
       </c>
       <c r="G268">
-        <v>71981</v>
+        <v>0</v>
       </c>
       <c r="H268">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I268" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12216,19 +12216,19 @@
         <v>17</v>
       </c>
       <c r="D269">
-        <v>23041</v>
+        <v>23024</v>
       </c>
       <c r="E269">
         <v>59877</v>
       </c>
       <c r="F269">
-        <v>38568</v>
+        <v>38562</v>
       </c>
       <c r="G269">
-        <v>55538</v>
+        <v>55529</v>
       </c>
       <c r="H269">
-        <v>15527</v>
+        <v>15538</v>
       </c>
       <c r="I269" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12305,19 +12305,19 @@
         <v>17</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>29285</v>
       </c>
       <c r="E271">
         <v>67137</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>44285</v>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>63770</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I271" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2947440/SILENT_HILL_f/","Abrir Steam")</f>
@@ -12349,16 +12349,16 @@
         <v>15</v>
       </c>
       <c r="D272">
-        <v>71393</v>
+        <v>71391</v>
       </c>
       <c r="E272">
         <v>90732</v>
       </c>
       <c r="F272">
-        <v>86393</v>
+        <v>86391</v>
       </c>
       <c r="G272">
-        <v>124406</v>
+        <v>124403</v>
       </c>
       <c r="H272">
         <v>15000</v>
@@ -12394,16 +12394,16 @@
         <v>17</v>
       </c>
       <c r="D273">
-        <v>21292</v>
+        <v>21274</v>
       </c>
       <c r="E273">
         <v>90732</v>
       </c>
       <c r="F273">
-        <v>48292</v>
+        <v>48274</v>
       </c>
       <c r="G273">
-        <v>69540</v>
+        <v>69515</v>
       </c>
       <c r="H273">
         <v>27000</v>
@@ -12438,19 +12438,19 @@
         <v>15</v>
       </c>
       <c r="D274">
-        <v>17336</v>
+        <v>17347</v>
       </c>
       <c r="E274">
         <v>127032</v>
       </c>
       <c r="F274">
-        <v>52336</v>
+        <v>51414</v>
       </c>
       <c r="G274">
-        <v>75364</v>
+        <v>74036</v>
       </c>
       <c r="H274">
-        <v>35000</v>
+        <v>34067</v>
       </c>
       <c r="I274" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12481,16 +12481,16 @@
         <v>17</v>
       </c>
       <c r="D275">
-        <v>12907</v>
+        <v>11985</v>
       </c>
       <c r="E275">
         <v>127032</v>
       </c>
       <c r="F275">
-        <v>39907</v>
+        <v>38985</v>
       </c>
       <c r="G275">
-        <v>57466</v>
+        <v>56138</v>
       </c>
       <c r="H275">
         <v>27000</v>
@@ -12525,19 +12525,19 @@
         <v>15</v>
       </c>
       <c r="D276">
-        <v>152809</v>
+        <v>152890</v>
       </c>
       <c r="E276">
         <v>163332</v>
       </c>
       <c r="F276">
-        <v>167809</v>
+        <v>0</v>
       </c>
       <c r="G276">
-        <v>241645</v>
+        <v>0</v>
       </c>
       <c r="H276">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I276" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12569,19 +12569,19 @@
         <v>17</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>102473</v>
       </c>
       <c r="E277">
         <v>163332</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>117473</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>169161</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I277" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1774580/STAR_WARS_Jedi_Survivor/?curator_clanid=4777282","Abrir Steam")</f>
@@ -12612,19 +12612,19 @@
         <v>15</v>
       </c>
       <c r="D278">
-        <v>46571</v>
+        <v>46537</v>
       </c>
       <c r="E278">
         <v>108882</v>
       </c>
       <c r="F278">
-        <v>78390</v>
+        <v>78383</v>
       </c>
       <c r="G278">
-        <v>112882</v>
+        <v>112872</v>
       </c>
       <c r="H278">
-        <v>31819</v>
+        <v>31846</v>
       </c>
       <c r="I278" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12658,19 +12658,19 @@
         <v>17</v>
       </c>
       <c r="D279">
-        <v>49250</v>
+        <v>49234</v>
       </c>
       <c r="E279">
         <v>108882</v>
       </c>
       <c r="F279">
-        <v>68164</v>
+        <v>68157</v>
       </c>
       <c r="G279">
-        <v>98156</v>
+        <v>98146</v>
       </c>
       <c r="H279">
-        <v>18914</v>
+        <v>18923</v>
       </c>
       <c r="I279" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12701,7 +12701,7 @@
         <v>15</v>
       </c>
       <c r="D280">
-        <v>63576</v>
+        <v>62465</v>
       </c>
       <c r="E280">
         <v>127032</v>
@@ -12713,7 +12713,7 @@
         <v>137195</v>
       </c>
       <c r="H280">
-        <v>31698</v>
+        <v>32809</v>
       </c>
       <c r="I280" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3489700/Stellar_Blade/","Abrir Steam")</f>
@@ -12747,16 +12747,16 @@
         <v>17</v>
       </c>
       <c r="D281">
-        <v>106081</v>
+        <v>77273</v>
       </c>
       <c r="E281">
         <v>127032</v>
       </c>
       <c r="F281">
-        <v>121081</v>
+        <v>92273</v>
       </c>
       <c r="G281">
-        <v>174357</v>
+        <v>132873</v>
       </c>
       <c r="H281">
         <v>15000</v>
@@ -12791,19 +12791,19 @@
         <v>15</v>
       </c>
       <c r="D282">
-        <v>23214</v>
+        <v>23371</v>
       </c>
       <c r="E282">
         <v>54432</v>
       </c>
       <c r="F282">
-        <v>39780</v>
+        <v>40824</v>
       </c>
       <c r="G282">
-        <v>57283</v>
+        <v>58787</v>
       </c>
       <c r="H282">
-        <v>16566</v>
+        <v>17453</v>
       </c>
       <c r="I282" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12835,19 +12835,19 @@
         <v>17</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>24838</v>
       </c>
       <c r="E283">
         <v>54432</v>
       </c>
       <c r="F283">
-        <v>0</v>
+        <v>39838</v>
       </c>
       <c r="G283">
-        <v>0</v>
+        <v>57367</v>
       </c>
       <c r="H283">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I283" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -12878,19 +12878,19 @@
         <v>15</v>
       </c>
       <c r="D284">
-        <v>65152</v>
+        <v>66061</v>
       </c>
       <c r="E284">
         <v>81675</v>
       </c>
       <c r="F284">
-        <v>80152</v>
+        <v>0</v>
       </c>
       <c r="G284">
-        <v>115419</v>
+        <v>0</v>
       </c>
       <c r="H284">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I284" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1364780/Street_Fighter_6/","Abrir Steam")</f>
@@ -13009,16 +13009,16 @@
         <v>17</v>
       </c>
       <c r="D287">
-        <v>20441</v>
+        <v>20438</v>
       </c>
       <c r="E287">
         <v>38097</v>
       </c>
       <c r="F287">
-        <v>35441</v>
+        <v>35438</v>
       </c>
       <c r="G287">
-        <v>51035</v>
+        <v>51031</v>
       </c>
       <c r="H287">
         <v>15000</v>
@@ -13053,19 +13053,19 @@
         <v>15</v>
       </c>
       <c r="D288">
-        <v>31977</v>
+        <v>31997</v>
       </c>
       <c r="E288">
         <v>58062</v>
       </c>
       <c r="F288">
-        <v>62759</v>
+        <v>49049</v>
       </c>
       <c r="G288">
-        <v>90373</v>
+        <v>70631</v>
       </c>
       <c r="H288">
-        <v>30782</v>
+        <v>17052</v>
       </c>
       <c r="I288" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1778820/TEKKEN_8/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13099,16 +13099,16 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>39573</v>
+        <v>25863</v>
       </c>
       <c r="E289">
         <v>58062</v>
       </c>
       <c r="F289">
-        <v>54573</v>
+        <v>40863</v>
       </c>
       <c r="G289">
-        <v>78585</v>
+        <v>58843</v>
       </c>
       <c r="H289">
         <v>15000</v>
@@ -13143,7 +13143,7 @@
         <v>15</v>
       </c>
       <c r="D290">
-        <v>10780</v>
+        <v>10787</v>
       </c>
       <c r="E290">
         <v>43542</v>
@@ -13155,7 +13155,7 @@
         <v>47026</v>
       </c>
       <c r="H290">
-        <v>21877</v>
+        <v>21870</v>
       </c>
       <c r="I290" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/489830/The_Elder_Scrolls_V_Skyrim_Special_Edition/","Abrir Steam")</f>
@@ -13189,16 +13189,16 @@
         <v>17</v>
       </c>
       <c r="D291">
-        <v>45625</v>
+        <v>34300</v>
       </c>
       <c r="E291">
         <v>43542</v>
       </c>
       <c r="F291">
-        <v>60625</v>
+        <v>49300</v>
       </c>
       <c r="G291">
-        <v>87300</v>
+        <v>70992</v>
       </c>
       <c r="H291">
         <v>15000</v>
@@ -13233,19 +13233,19 @@
         <v>15</v>
       </c>
       <c r="D292">
-        <v>41543</v>
+        <v>0</v>
       </c>
       <c r="E292">
         <v>108882</v>
       </c>
       <c r="F292">
-        <v>68543</v>
+        <v>0</v>
       </c>
       <c r="G292">
-        <v>98702</v>
+        <v>0</v>
       </c>
       <c r="H292">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I292" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13279,19 +13279,19 @@
         <v>17</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>38179</v>
       </c>
       <c r="E293">
         <v>108882</v>
       </c>
       <c r="F293">
-        <v>0</v>
+        <v>63735</v>
       </c>
       <c r="G293">
-        <v>0</v>
+        <v>91778</v>
       </c>
       <c r="H293">
-        <v>0</v>
+        <v>25556</v>
       </c>
       <c r="I293" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1888930/The_Last_of_Us_Parte_I/","Abrir Steam")</f>
@@ -13409,19 +13409,19 @@
         <v>15</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>47783</v>
       </c>
       <c r="E296">
         <v>72582</v>
       </c>
       <c r="F296">
-        <v>0</v>
+        <v>82783</v>
       </c>
       <c r="G296">
-        <v>0</v>
+        <v>119208</v>
       </c>
       <c r="H296">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I296" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13455,19 +13455,19 @@
         <v>17</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>64752</v>
       </c>
       <c r="E297">
         <v>72582</v>
       </c>
       <c r="F297">
-        <v>0</v>
+        <v>79752</v>
       </c>
       <c r="G297">
-        <v>0</v>
+        <v>114843</v>
       </c>
       <c r="H297">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I297" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2531310/The_Last_of_Us_Parte_II_Remastered/","Abrir Steam")</f>
@@ -13540,19 +13540,19 @@
         <v>17</v>
       </c>
       <c r="D299">
-        <v>4744</v>
+        <v>4684</v>
       </c>
       <c r="E299">
         <v>54432</v>
       </c>
       <c r="F299">
-        <v>29126</v>
+        <v>29102</v>
       </c>
       <c r="G299">
-        <v>41941</v>
+        <v>41907</v>
       </c>
       <c r="H299">
-        <v>24382</v>
+        <v>24418</v>
       </c>
       <c r="I299" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/292030/The_Witcher_3_Wild_Hunt/","Abrir Steam")</f>
@@ -13668,16 +13668,16 @@
         <v>15</v>
       </c>
       <c r="D302">
-        <v>20472</v>
+        <v>19397</v>
       </c>
       <c r="E302">
         <v>90732</v>
       </c>
       <c r="F302">
-        <v>47472</v>
+        <v>46397</v>
       </c>
       <c r="G302">
-        <v>68360</v>
+        <v>66812</v>
       </c>
       <c r="H302">
         <v>27000</v>
@@ -13756,19 +13756,19 @@
         <v>15</v>
       </c>
       <c r="D304">
-        <v>38722</v>
+        <v>37675</v>
       </c>
       <c r="E304">
         <v>108882</v>
       </c>
       <c r="F304">
-        <v>65722</v>
+        <v>72675</v>
       </c>
       <c r="G304">
-        <v>94640</v>
+        <v>104652</v>
       </c>
       <c r="H304">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I304" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13801,19 +13801,19 @@
         <v>17</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>88848</v>
       </c>
       <c r="E305">
         <v>108882</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>103848</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>149541</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I305" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2172010/Until_Dawn/?curator_clanid=4777282","Abrir Steam")</f>
@@ -13844,19 +13844,19 @@
         <v>15</v>
       </c>
       <c r="D306">
-        <v>23861</v>
+        <v>23844</v>
       </c>
       <c r="E306">
         <v>108882</v>
       </c>
       <c r="F306">
-        <v>50861</v>
+        <v>58844</v>
       </c>
       <c r="G306">
-        <v>73240</v>
+        <v>84735</v>
       </c>
       <c r="H306">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="I306" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13889,19 +13889,19 @@
         <v>17</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>33574</v>
       </c>
       <c r="E307">
         <v>108882</v>
       </c>
       <c r="F307">
-        <v>0</v>
+        <v>60574</v>
       </c>
       <c r="G307">
-        <v>0</v>
+        <v>87227</v>
       </c>
       <c r="H307">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I307" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -13932,16 +13932,16 @@
         <v>15</v>
       </c>
       <c r="D308">
-        <v>185653</v>
+        <v>185613</v>
       </c>
       <c r="E308">
         <v>235932</v>
       </c>
       <c r="F308">
-        <v>200653</v>
+        <v>200613</v>
       </c>
       <c r="G308">
-        <v>288940</v>
+        <v>288883</v>
       </c>
       <c r="H308">
         <v>15000</v>
@@ -13976,19 +13976,19 @@
         <v>17</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>142561</v>
       </c>
       <c r="E309">
         <v>235932</v>
       </c>
       <c r="F309">
-        <v>0</v>
+        <v>157561</v>
       </c>
       <c r="G309">
-        <v>0</v>
+        <v>226888</v>
       </c>
       <c r="H309">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I309" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2878960/WWE_2K25/","Abrir Steam")</f>
@@ -14020,19 +14020,19 @@
         <v>15</v>
       </c>
       <c r="D310">
-        <v>65057</v>
+        <v>64641</v>
       </c>
       <c r="E310">
         <v>127032</v>
       </c>
       <c r="F310">
-        <v>89187</v>
+        <v>89021</v>
       </c>
       <c r="G310">
-        <v>128429</v>
+        <v>128190</v>
       </c>
       <c r="H310">
-        <v>24130</v>
+        <v>24380</v>
       </c>
       <c r="I310" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14064,19 +14064,19 @@
         <v>17</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>54138</v>
       </c>
       <c r="E311">
         <v>127032</v>
       </c>
       <c r="F311">
-        <v>0</v>
+        <v>77198</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>111165</v>
       </c>
       <c r="H311">
-        <v>0</v>
+        <v>23060</v>
       </c>
       <c r="I311" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14149,19 +14149,19 @@
         <v>17</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>109381</v>
       </c>
       <c r="E313">
         <v>181482</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>124381</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>179109</v>
       </c>
       <c r="H313">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I313" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3717070/WWE_2K26/","Abrir Steam")</f>
@@ -14192,16 +14192,16 @@
         <v>15</v>
       </c>
       <c r="D314">
-        <v>124993</v>
+        <v>125072</v>
       </c>
       <c r="E314">
         <v>235932</v>
       </c>
       <c r="F314">
-        <v>151993</v>
+        <v>152072</v>
       </c>
       <c r="G314">
-        <v>218870</v>
+        <v>218984</v>
       </c>
       <c r="H314">
         <v>27000</v>

--- a/GAMES LIST - AUTO.xlsx
+++ b/GAMES LIST - AUTO.xlsx
@@ -481,19 +481,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>72053</v>
+        <v>72100</v>
       </c>
       <c r="E2">
         <v>72582</v>
       </c>
       <c r="F2">
-        <v>87068</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>125378</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>15015</v>
+        <v>0</v>
       </c>
       <c r="I2" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -527,19 +527,19 @@
         <v>17</v>
       </c>
       <c r="D3">
-        <v>46679</v>
+        <v>46727</v>
       </c>
       <c r="E3">
         <v>72582</v>
       </c>
       <c r="F3">
-        <v>61679</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>88818</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I3" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -577,13 +577,13 @@
         <v>83472</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>97414</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>140276</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I4" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -617,19 +617,19 @@
         <v>17</v>
       </c>
       <c r="D5">
-        <v>84732</v>
+        <v>84780</v>
       </c>
       <c r="E5">
         <v>83472</v>
       </c>
       <c r="F5">
-        <v>99732</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>143614</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I5" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3768760/007_First_Light/","Abrir Steam")</f>
@@ -747,19 +747,19 @@
         <v>15</v>
       </c>
       <c r="D8">
-        <v>34442</v>
+        <v>37186</v>
       </c>
       <c r="E8">
         <v>72582</v>
       </c>
       <c r="F8">
-        <v>52439</v>
+        <v>54437</v>
       </c>
       <c r="G8">
-        <v>75512</v>
+        <v>78389</v>
       </c>
       <c r="H8">
-        <v>17997</v>
+        <v>17251</v>
       </c>
       <c r="I8" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -793,19 +793,19 @@
         <v>17</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>30941</v>
       </c>
       <c r="E9">
         <v>72582</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>46683</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>67224</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>15742</v>
       </c>
       <c r="I9" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1808500/ARC_Raiders/","Abrir Steam")</f>
@@ -925,19 +925,19 @@
         <v>15</v>
       </c>
       <c r="D12">
-        <v>78992</v>
+        <v>71880</v>
       </c>
       <c r="E12">
         <v>81657</v>
       </c>
       <c r="F12">
-        <v>97098</v>
+        <v>97114</v>
       </c>
       <c r="G12">
-        <v>139821</v>
+        <v>139844</v>
       </c>
       <c r="H12">
-        <v>18106</v>
+        <v>25234</v>
       </c>
       <c r="I12" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2399830/ARK_Survival_Ascended/","Abrir Steam")</f>
@@ -970,16 +970,16 @@
         <v>17</v>
       </c>
       <c r="D13">
-        <v>11780</v>
+        <v>11796</v>
       </c>
       <c r="E13">
         <v>81657</v>
       </c>
       <c r="F13">
-        <v>38780</v>
+        <v>38796</v>
       </c>
       <c r="G13">
-        <v>55843</v>
+        <v>55866</v>
       </c>
       <c r="H13">
         <v>27000</v>
@@ -1056,19 +1056,19 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>44929</v>
+        <v>44945</v>
       </c>
       <c r="E15">
         <v>72582</v>
       </c>
       <c r="F15">
-        <v>59929</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>86298</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I15" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3035570/Assassins_Creed_Mirage/","Abrir Steam")</f>
@@ -1315,19 +1315,19 @@
         <v>17</v>
       </c>
       <c r="D21">
-        <v>35656</v>
+        <v>35688</v>
       </c>
       <c r="E21">
         <v>101622</v>
       </c>
       <c r="F21">
-        <v>59895</v>
+        <v>59908</v>
       </c>
       <c r="G21">
-        <v>86249</v>
+        <v>86268</v>
       </c>
       <c r="H21">
-        <v>24239</v>
+        <v>24220</v>
       </c>
       <c r="I21" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3159330/Assassins_Creed_Shadows/","Abrir Steam")</f>
@@ -1575,19 +1575,19 @@
         <v>17</v>
       </c>
       <c r="D27">
-        <v>20201</v>
+        <v>20217</v>
       </c>
       <c r="E27">
         <v>63507</v>
       </c>
       <c r="F27">
-        <v>38848</v>
+        <v>38855</v>
       </c>
       <c r="G27">
-        <v>55941</v>
+        <v>55951</v>
       </c>
       <c r="H27">
-        <v>18647</v>
+        <v>18638</v>
       </c>
       <c r="I27" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1086940/Baldurs_Gate_3/","Abrir Steam")</f>
@@ -1619,19 +1619,19 @@
         <v>15</v>
       </c>
       <c r="D28">
-        <v>74971</v>
+        <v>75034</v>
       </c>
       <c r="E28">
         <v>127032</v>
       </c>
       <c r="F28">
-        <v>95014</v>
+        <v>95046</v>
       </c>
       <c r="G28">
-        <v>136820</v>
+        <v>136866</v>
       </c>
       <c r="H28">
-        <v>20043</v>
+        <v>20012</v>
       </c>
       <c r="I28" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1665,16 +1665,16 @@
         <v>17</v>
       </c>
       <c r="D29">
-        <v>28969</v>
+        <v>29001</v>
       </c>
       <c r="E29">
         <v>127032</v>
       </c>
       <c r="F29">
-        <v>55969</v>
+        <v>56001</v>
       </c>
       <c r="G29">
-        <v>80595</v>
+        <v>80641</v>
       </c>
       <c r="H29">
         <v>27000</v>
@@ -1709,19 +1709,19 @@
         <v>15</v>
       </c>
       <c r="D30">
-        <v>125908</v>
+        <v>126002</v>
       </c>
       <c r="E30">
         <v>181482</v>
       </c>
       <c r="F30">
-        <v>141035</v>
+        <v>141083</v>
       </c>
       <c r="G30">
-        <v>203090</v>
+        <v>203160</v>
       </c>
       <c r="H30">
-        <v>15127</v>
+        <v>15081</v>
       </c>
       <c r="I30" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2807960/Battlefield_6/","Abrir Steam")</f>
@@ -1755,16 +1755,16 @@
         <v>17</v>
       </c>
       <c r="D31">
-        <v>78203</v>
+        <v>78251</v>
       </c>
       <c r="E31">
         <v>181482</v>
       </c>
       <c r="F31">
-        <v>105203</v>
+        <v>105251</v>
       </c>
       <c r="G31">
-        <v>151492</v>
+        <v>151561</v>
       </c>
       <c r="H31">
         <v>27000</v>
@@ -1799,19 +1799,19 @@
         <v>15</v>
       </c>
       <c r="D32">
-        <v>81515</v>
+        <v>81499</v>
       </c>
       <c r="E32">
         <v>108882</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>96499</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>138959</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I32" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1845,19 +1845,19 @@
         <v>17</v>
       </c>
       <c r="D33">
-        <v>47673</v>
+        <v>47704</v>
       </c>
       <c r="E33">
         <v>108882</v>
       </c>
       <c r="F33">
-        <v>67533</v>
+        <v>67545</v>
       </c>
       <c r="G33">
-        <v>97248</v>
+        <v>97265</v>
       </c>
       <c r="H33">
-        <v>19860</v>
+        <v>19841</v>
       </c>
       <c r="I33" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -1935,19 +1935,19 @@
         <v>17</v>
       </c>
       <c r="D35">
-        <v>82114</v>
+        <v>0</v>
       </c>
       <c r="E35">
         <v>127032</v>
       </c>
       <c r="F35">
-        <v>97114</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>139844</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I35" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2358720/Black_Myth_Wukong/","Abrir Steam")</f>
@@ -2068,16 +2068,16 @@
         <v>15</v>
       </c>
       <c r="D38">
-        <v>64736</v>
+        <v>64783</v>
       </c>
       <c r="E38">
         <v>235932</v>
       </c>
       <c r="F38">
-        <v>91736</v>
+        <v>91783</v>
       </c>
       <c r="G38">
-        <v>132100</v>
+        <v>132168</v>
       </c>
       <c r="H38">
         <v>27000</v>
@@ -2156,16 +2156,16 @@
         <v>15</v>
       </c>
       <c r="D40">
-        <v>84291</v>
+        <v>84354</v>
       </c>
       <c r="E40">
         <v>235932</v>
       </c>
       <c r="F40">
-        <v>111291</v>
+        <v>111354</v>
       </c>
       <c r="G40">
-        <v>160259</v>
+        <v>160350</v>
       </c>
       <c r="H40">
         <v>27000</v>
@@ -2286,16 +2286,16 @@
         <v>17</v>
       </c>
       <c r="D43">
-        <v>38952</v>
+        <v>38983</v>
       </c>
       <c r="E43">
         <v>127032</v>
       </c>
       <c r="F43">
-        <v>65952</v>
+        <v>65983</v>
       </c>
       <c r="G43">
-        <v>94971</v>
+        <v>95016</v>
       </c>
       <c r="H43">
         <v>27000</v>
@@ -2457,16 +2457,16 @@
         <v>17</v>
       </c>
       <c r="D47">
-        <v>27598</v>
+        <v>27629</v>
       </c>
       <c r="E47">
         <v>108882</v>
       </c>
       <c r="F47">
-        <v>54598</v>
+        <v>54629</v>
       </c>
       <c r="G47">
-        <v>78621</v>
+        <v>78666</v>
       </c>
       <c r="H47">
         <v>27000</v>
@@ -2593,13 +2593,13 @@
         <v>63507</v>
       </c>
       <c r="F50">
-        <v>58893</v>
+        <v>58924</v>
       </c>
       <c r="G50">
-        <v>84806</v>
+        <v>84851</v>
       </c>
       <c r="H50">
-        <v>22638</v>
+        <v>22669</v>
       </c>
       <c r="I50" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2633,19 +2633,19 @@
         <v>17</v>
       </c>
       <c r="D51">
-        <v>35893</v>
+        <v>35924</v>
       </c>
       <c r="E51">
         <v>63507</v>
       </c>
       <c r="F51">
-        <v>50893</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>73286</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I51" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2677,19 +2677,19 @@
         <v>15</v>
       </c>
       <c r="D52">
-        <v>61645</v>
+        <v>61692</v>
       </c>
       <c r="E52">
         <v>76212</v>
       </c>
       <c r="F52">
-        <v>76645</v>
+        <v>0</v>
       </c>
       <c r="G52">
-        <v>110369</v>
+        <v>0</v>
       </c>
       <c r="H52">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I52" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2723,19 +2723,19 @@
         <v>17</v>
       </c>
       <c r="D53">
-        <v>57261</v>
+        <v>69940</v>
       </c>
       <c r="E53">
         <v>76212</v>
       </c>
       <c r="F53">
-        <v>72261</v>
+        <v>0</v>
       </c>
       <c r="G53">
-        <v>104056</v>
+        <v>0</v>
       </c>
       <c r="H53">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I53" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1903340/Clair_Obscur_Expedition_33/","Abrir Steam")</f>
@@ -2767,19 +2767,19 @@
         <v>15</v>
       </c>
       <c r="D54">
-        <v>54075</v>
+        <v>49187</v>
       </c>
       <c r="E54">
         <v>127032</v>
       </c>
       <c r="F54">
-        <v>87987</v>
+        <v>84187</v>
       </c>
       <c r="G54">
-        <v>126701</v>
+        <v>121229</v>
       </c>
       <c r="H54">
-        <v>33912</v>
+        <v>35000</v>
       </c>
       <c r="I54" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2813,19 +2813,19 @@
         <v>17</v>
       </c>
       <c r="D55">
-        <v>52419</v>
+        <v>52451</v>
       </c>
       <c r="E55">
         <v>127032</v>
       </c>
       <c r="F55">
-        <v>76510</v>
+        <v>76523</v>
       </c>
       <c r="G55">
-        <v>110174</v>
+        <v>110193</v>
       </c>
       <c r="H55">
-        <v>24091</v>
+        <v>24072</v>
       </c>
       <c r="I55" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2857,19 +2857,19 @@
         <v>15</v>
       </c>
       <c r="D56">
-        <v>70665</v>
+        <v>53445</v>
       </c>
       <c r="E56">
         <v>145182</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>80445</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>115841</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I56" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2903,19 +2903,19 @@
         <v>17</v>
       </c>
       <c r="D57">
-        <v>63033</v>
+        <v>63080</v>
       </c>
       <c r="E57">
         <v>145182</v>
       </c>
       <c r="F57">
-        <v>87834</v>
+        <v>87853</v>
       </c>
       <c r="G57">
-        <v>126481</v>
+        <v>126508</v>
       </c>
       <c r="H57">
-        <v>24801</v>
+        <v>24773</v>
       </c>
       <c r="I57" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3321460/Crimson_Desert/","Abrir Steam")</f>
@@ -2947,19 +2947,19 @@
         <v>15</v>
       </c>
       <c r="D58">
-        <v>23261</v>
+        <v>23277</v>
       </c>
       <c r="E58">
         <v>36282</v>
       </c>
       <c r="F58">
-        <v>38381</v>
+        <v>38387</v>
       </c>
       <c r="G58">
-        <v>55269</v>
+        <v>55277</v>
       </c>
       <c r="H58">
-        <v>15120</v>
+        <v>15110</v>
       </c>
       <c r="I58" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -2992,19 +2992,19 @@
         <v>17</v>
       </c>
       <c r="D59">
-        <v>6245</v>
+        <v>6261</v>
       </c>
       <c r="E59">
         <v>36282</v>
       </c>
       <c r="F59">
-        <v>22648</v>
+        <v>22654</v>
       </c>
       <c r="G59">
-        <v>32613</v>
+        <v>32622</v>
       </c>
       <c r="H59">
-        <v>16403</v>
+        <v>16393</v>
       </c>
       <c r="I59" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3036,19 +3036,19 @@
         <v>15</v>
       </c>
       <c r="D60">
-        <v>26651</v>
+        <v>26667</v>
       </c>
       <c r="E60">
         <v>48987</v>
       </c>
       <c r="F60">
-        <v>41651</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>59977</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I60" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3081,19 +3081,19 @@
         <v>17</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>25106</v>
       </c>
       <c r="E61">
         <v>48987</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>40106</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>57753</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I61" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/268910/Cuphead/?curator_clanid=4777282","Abrir Steam")</f>
@@ -3166,16 +3166,16 @@
         <v>17</v>
       </c>
       <c r="D63">
-        <v>12916</v>
+        <v>12931</v>
       </c>
       <c r="E63">
         <v>81657</v>
       </c>
       <c r="F63">
-        <v>39916</v>
+        <v>39931</v>
       </c>
       <c r="G63">
-        <v>57479</v>
+        <v>57501</v>
       </c>
       <c r="H63">
         <v>27000</v>
@@ -3252,16 +3252,16 @@
         <v>17</v>
       </c>
       <c r="D65">
-        <v>27550</v>
+        <v>27566</v>
       </c>
       <c r="E65">
         <v>122476</v>
       </c>
       <c r="F65">
-        <v>54550</v>
+        <v>54566</v>
       </c>
       <c r="G65">
-        <v>78552</v>
+        <v>78575</v>
       </c>
       <c r="H65">
         <v>27000</v>
@@ -3302,13 +3302,13 @@
         <v>90732</v>
       </c>
       <c r="F66">
-        <v>53624</v>
+        <v>53577</v>
       </c>
       <c r="G66">
-        <v>77219</v>
+        <v>77151</v>
       </c>
       <c r="H66">
-        <v>29764</v>
+        <v>29717</v>
       </c>
       <c r="I66" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3341,16 +3341,16 @@
         <v>17</v>
       </c>
       <c r="D67">
-        <v>18624</v>
+        <v>18577</v>
       </c>
       <c r="E67">
         <v>90732</v>
       </c>
       <c r="F67">
-        <v>45624</v>
+        <v>45577</v>
       </c>
       <c r="G67">
-        <v>65699</v>
+        <v>65631</v>
       </c>
       <c r="H67">
         <v>27000</v>
@@ -3385,19 +3385,19 @@
         <v>15</v>
       </c>
       <c r="D68">
-        <v>34662</v>
+        <v>59753</v>
       </c>
       <c r="E68">
         <v>108882</v>
       </c>
       <c r="F68">
-        <v>61662</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>88793</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I68" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3474,19 +3474,19 @@
         <v>15</v>
       </c>
       <c r="D70">
-        <v>107914</v>
+        <v>17347</v>
       </c>
       <c r="E70">
         <v>127032</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>44347</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>63860</v>
       </c>
       <c r="H70">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="I70" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/221100/DayZ/","Abrir Steam")</f>
@@ -3734,19 +3734,19 @@
         <v>15</v>
       </c>
       <c r="D76">
-        <v>86152</v>
+        <v>85726</v>
       </c>
       <c r="E76">
         <v>127032</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>100726</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>145045</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I76" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3280350/DEATH_STRANDING_2_ON_THE_BEACH/","Abrir Steam")</f>
@@ -3779,16 +3779,16 @@
         <v>17</v>
       </c>
       <c r="D77">
-        <v>47184</v>
+        <v>47231</v>
       </c>
       <c r="E77">
         <v>127032</v>
       </c>
       <c r="F77">
-        <v>74184</v>
+        <v>74231</v>
       </c>
       <c r="G77">
-        <v>106825</v>
+        <v>106893</v>
       </c>
       <c r="H77">
         <v>27000</v>
@@ -3953,19 +3953,19 @@
         <v>17</v>
       </c>
       <c r="D81">
-        <v>37186</v>
+        <v>37217</v>
       </c>
       <c r="E81">
         <v>90732</v>
       </c>
       <c r="F81">
-        <v>56260</v>
+        <v>56272</v>
       </c>
       <c r="G81">
-        <v>81014</v>
+        <v>81032</v>
       </c>
       <c r="H81">
-        <v>19074</v>
+        <v>19055</v>
       </c>
       <c r="I81" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4039,19 +4039,19 @@
         <v>17</v>
       </c>
       <c r="D83">
-        <v>85000</v>
+        <v>85048</v>
       </c>
       <c r="E83">
         <v>127032</v>
       </c>
       <c r="F83">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>144000</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I83" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2344520/Diablo_IV/","Abrir Steam")</f>
@@ -4083,19 +4083,19 @@
         <v>15</v>
       </c>
       <c r="D84">
-        <v>94147</v>
+        <v>17347</v>
       </c>
       <c r="E84">
         <v>101622</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>52347</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>75380</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>35000</v>
       </c>
       <c r="I84" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4127,19 +4127,19 @@
         <v>17</v>
       </c>
       <c r="D85">
-        <v>32092</v>
+        <v>32108</v>
       </c>
       <c r="E85">
         <v>101622</v>
       </c>
       <c r="F85">
-        <v>58469</v>
+        <v>58476</v>
       </c>
       <c r="G85">
-        <v>84195</v>
+        <v>84205</v>
       </c>
       <c r="H85">
-        <v>26377</v>
+        <v>26368</v>
       </c>
       <c r="I85" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4171,19 +4171,19 @@
         <v>15</v>
       </c>
       <c r="D86">
-        <v>151550</v>
+        <v>151534</v>
       </c>
       <c r="E86">
         <v>145182</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>166534</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>239809</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I86" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4258,19 +4258,19 @@
         <v>15</v>
       </c>
       <c r="D88">
-        <v>171246</v>
+        <v>171215</v>
       </c>
       <c r="E88">
         <v>159702</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>186215</v>
       </c>
       <c r="G88">
-        <v>0</v>
+        <v>268150</v>
       </c>
       <c r="H88">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I88" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4302,19 +4302,19 @@
         <v>17</v>
       </c>
       <c r="D89">
-        <v>127217</v>
+        <v>127295</v>
       </c>
       <c r="E89">
         <v>159702</v>
       </c>
       <c r="F89">
-        <v>142217</v>
+        <v>0</v>
       </c>
       <c r="G89">
-        <v>204792</v>
+        <v>0</v>
       </c>
       <c r="H89">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I89" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1790600/DRAGON_BALL_Sparking_ZERO/","Abrir Steam")</f>
@@ -4608,19 +4608,19 @@
         <v>15</v>
       </c>
       <c r="D96">
-        <v>61945</v>
+        <v>61992</v>
       </c>
       <c r="E96">
         <v>81657</v>
       </c>
       <c r="F96">
-        <v>76979</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>110850</v>
+        <v>0</v>
       </c>
       <c r="H96">
-        <v>15034</v>
+        <v>0</v>
       </c>
       <c r="I96" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4654,19 +4654,19 @@
         <v>17</v>
       </c>
       <c r="D97">
-        <v>33700</v>
+        <v>33716</v>
       </c>
       <c r="E97">
         <v>81657</v>
       </c>
       <c r="F97">
-        <v>51326</v>
+        <v>51333</v>
       </c>
       <c r="G97">
-        <v>73909</v>
+        <v>73920</v>
       </c>
       <c r="H97">
-        <v>17626</v>
+        <v>17617</v>
       </c>
       <c r="I97" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4698,19 +4698,19 @@
         <v>15</v>
       </c>
       <c r="D98">
-        <v>82130</v>
+        <v>79260</v>
       </c>
       <c r="E98">
         <v>94362</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>96012</v>
       </c>
       <c r="G98">
-        <v>0</v>
+        <v>138257</v>
       </c>
       <c r="H98">
-        <v>0</v>
+        <v>16752</v>
       </c>
       <c r="I98" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4744,19 +4744,19 @@
         <v>17</v>
       </c>
       <c r="D99">
-        <v>68442</v>
+        <v>68489</v>
       </c>
       <c r="E99">
         <v>94362</v>
       </c>
       <c r="F99">
-        <v>83442</v>
+        <v>0</v>
       </c>
       <c r="G99">
-        <v>120156</v>
+        <v>0</v>
       </c>
       <c r="H99">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I99" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3008130/Dying_Light_The_Beast/","Abrir Steam")</f>
@@ -4788,19 +4788,19 @@
         <v>15</v>
       </c>
       <c r="D100">
-        <v>61676</v>
+        <v>61724</v>
       </c>
       <c r="E100">
         <v>105796</v>
       </c>
       <c r="F100">
-        <v>78279</v>
+        <v>78298</v>
       </c>
       <c r="G100">
-        <v>112722</v>
+        <v>112749</v>
       </c>
       <c r="H100">
-        <v>16603</v>
+        <v>16574</v>
       </c>
       <c r="I100" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2384580/DYNASTY_WARRIORS_ORIGINS/","Abrir Steam")</f>
@@ -5263,16 +5263,16 @@
         <v>17</v>
       </c>
       <c r="D111">
-        <v>14146</v>
+        <v>14161</v>
       </c>
       <c r="E111">
         <v>163332</v>
       </c>
       <c r="F111">
-        <v>41146</v>
+        <v>41161</v>
       </c>
       <c r="G111">
-        <v>59250</v>
+        <v>59272</v>
       </c>
       <c r="H111">
         <v>27000</v>
@@ -5307,19 +5307,19 @@
         <v>15</v>
       </c>
       <c r="D112">
-        <v>91119</v>
+        <v>91103</v>
       </c>
       <c r="E112">
         <v>87102</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>106103</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>152788</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I112" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5352,19 +5352,19 @@
         <v>17</v>
       </c>
       <c r="D113">
-        <v>52830</v>
+        <v>52861</v>
       </c>
       <c r="E113">
         <v>87102</v>
       </c>
       <c r="F113">
-        <v>67830</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>97675</v>
+        <v>0</v>
       </c>
       <c r="H113">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I113" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5439,19 +5439,19 @@
         <v>17</v>
       </c>
       <c r="D115">
-        <v>99572</v>
+        <v>85600</v>
       </c>
       <c r="E115">
         <v>116142</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>100600</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>144864</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I115" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5483,19 +5483,19 @@
         <v>15</v>
       </c>
       <c r="D116">
-        <v>169228</v>
+        <v>169196</v>
       </c>
       <c r="E116">
         <v>145182</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>184196</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>265242</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I116" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1245620/ELDEN_RING/","Abrir Steam")</f>
@@ -5569,19 +5569,19 @@
         <v>15</v>
       </c>
       <c r="D118">
-        <v>44235</v>
+        <v>44219</v>
       </c>
       <c r="E118">
         <v>58062</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>59219</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>85275</v>
       </c>
       <c r="H118">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I118" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5614,19 +5614,19 @@
         <v>17</v>
       </c>
       <c r="D119">
-        <v>33070</v>
+        <v>32470</v>
       </c>
       <c r="E119">
         <v>58062</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>47470</v>
       </c>
       <c r="G119">
-        <v>0</v>
+        <v>68357</v>
       </c>
       <c r="H119">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I119" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2622380/ELDEN_RING_NIGHTREIGN/","Abrir Steam")</f>
@@ -5658,16 +5658,16 @@
         <v>15</v>
       </c>
       <c r="D120">
-        <v>61298</v>
+        <v>61282</v>
       </c>
       <c r="E120">
         <v>79842</v>
       </c>
       <c r="F120">
-        <v>76298</v>
+        <v>76282</v>
       </c>
       <c r="G120">
-        <v>109869</v>
+        <v>109846</v>
       </c>
       <c r="H120">
         <v>15000</v>
@@ -5789,19 +5789,19 @@
         <v>17</v>
       </c>
       <c r="D123">
-        <v>44897</v>
+        <v>44929</v>
       </c>
       <c r="E123">
         <v>90732</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>59929</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>86298</v>
       </c>
       <c r="H123">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I123" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3059520/F1_25/","Abrir Steam")</f>
@@ -5833,7 +5833,7 @@
         <v>15</v>
       </c>
       <c r="D124">
-        <v>13562</v>
+        <v>13625</v>
       </c>
       <c r="E124">
         <v>43542</v>
@@ -5845,7 +5845,7 @@
         <v>47026</v>
       </c>
       <c r="H124">
-        <v>19095</v>
+        <v>19032</v>
       </c>
       <c r="I124" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5879,19 +5879,19 @@
         <v>17</v>
       </c>
       <c r="D125">
-        <v>8642</v>
+        <v>9840</v>
       </c>
       <c r="E125">
         <v>43542</v>
       </c>
       <c r="F125">
-        <v>26438</v>
+        <v>26917</v>
       </c>
       <c r="G125">
-        <v>38071</v>
+        <v>38760</v>
       </c>
       <c r="H125">
-        <v>17796</v>
+        <v>17077</v>
       </c>
       <c r="I125" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1151340/Fallout_76/?curator_clanid=4777282","Abrir Steam")</f>
@@ -5923,16 +5923,16 @@
         <v>15</v>
       </c>
       <c r="D126">
-        <v>30121</v>
+        <v>29790</v>
       </c>
       <c r="E126">
         <v>58062</v>
       </c>
       <c r="F126">
-        <v>45121</v>
+        <v>44790</v>
       </c>
       <c r="G126">
-        <v>64974</v>
+        <v>64498</v>
       </c>
       <c r="H126">
         <v>15000</v>
@@ -6055,19 +6055,19 @@
         <v>17</v>
       </c>
       <c r="D129">
-        <v>20264</v>
+        <v>20280</v>
       </c>
       <c r="E129">
         <v>59496</v>
       </c>
       <c r="F129">
-        <v>37309</v>
+        <v>37315</v>
       </c>
       <c r="G129">
-        <v>53725</v>
+        <v>53734</v>
       </c>
       <c r="H129">
-        <v>17045</v>
+        <v>17035</v>
       </c>
       <c r="I129" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6141,19 +6141,19 @@
         <v>17</v>
       </c>
       <c r="D131">
-        <v>36350</v>
+        <v>36366</v>
       </c>
       <c r="E131">
         <v>74125</v>
       </c>
       <c r="F131">
-        <v>51350</v>
+        <v>0</v>
       </c>
       <c r="G131">
-        <v>73944</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I131" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6228,19 +6228,19 @@
         <v>17</v>
       </c>
       <c r="D133">
-        <v>37816</v>
+        <v>37848</v>
       </c>
       <c r="E133">
         <v>93309</v>
       </c>
       <c r="F133">
-        <v>57517</v>
+        <v>57530</v>
       </c>
       <c r="G133">
-        <v>82824</v>
+        <v>82843</v>
       </c>
       <c r="H133">
-        <v>19701</v>
+        <v>19682</v>
       </c>
       <c r="I133" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1551360/Forza_Horizon_5/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6314,19 +6314,19 @@
         <v>17</v>
       </c>
       <c r="D135">
-        <v>53586</v>
+        <v>53618</v>
       </c>
       <c r="E135">
         <v>88917</v>
       </c>
       <c r="F135">
-        <v>68586</v>
+        <v>0</v>
       </c>
       <c r="G135">
-        <v>98764</v>
+        <v>0</v>
       </c>
       <c r="H135">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I135" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6400,19 +6400,19 @@
         <v>17</v>
       </c>
       <c r="D137">
-        <v>72148</v>
+        <v>72195</v>
       </c>
       <c r="E137">
         <v>127032</v>
       </c>
       <c r="F137">
-        <v>87148</v>
+        <v>0</v>
       </c>
       <c r="G137">
-        <v>125493</v>
+        <v>0</v>
       </c>
       <c r="H137">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I137" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6486,19 +6486,19 @@
         <v>17</v>
       </c>
       <c r="D139">
-        <v>91844</v>
+        <v>91908</v>
       </c>
       <c r="E139">
         <v>152442</v>
       </c>
       <c r="F139">
-        <v>106844</v>
+        <v>0</v>
       </c>
       <c r="G139">
-        <v>153855</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I139" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2483190/Forza_Horizon_6/","Abrir Steam")</f>
@@ -6530,19 +6530,19 @@
         <v>15</v>
       </c>
       <c r="D140">
-        <v>37375</v>
+        <v>37391</v>
       </c>
       <c r="E140">
         <v>90732</v>
       </c>
       <c r="F140">
-        <v>61779</v>
+        <v>61786</v>
       </c>
       <c r="G140">
-        <v>88962</v>
+        <v>88972</v>
       </c>
       <c r="H140">
-        <v>24404</v>
+        <v>24395</v>
       </c>
       <c r="I140" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215430/Ghost_of_Tsushima_VERSIN_DEL_DIRECTOR/?l=spanish","Abrir Steam")</f>
@@ -6618,16 +6618,16 @@
         <v>15</v>
       </c>
       <c r="D142">
-        <v>23229</v>
+        <v>23056</v>
       </c>
       <c r="E142">
         <v>90732</v>
       </c>
       <c r="F142">
-        <v>58229</v>
+        <v>58056</v>
       </c>
       <c r="G142">
-        <v>83850</v>
+        <v>83601</v>
       </c>
       <c r="H142">
         <v>35000</v>
@@ -6662,19 +6662,19 @@
         <v>17</v>
       </c>
       <c r="D143">
-        <v>28938</v>
+        <v>28954</v>
       </c>
       <c r="E143">
         <v>90732</v>
       </c>
       <c r="F143">
-        <v>52961</v>
+        <v>52967</v>
       </c>
       <c r="G143">
-        <v>76264</v>
+        <v>76272</v>
       </c>
       <c r="H143">
-        <v>24023</v>
+        <v>24013</v>
       </c>
       <c r="I143" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1593500/God_of_War/","Abrir Steam")</f>
@@ -6706,7 +6706,7 @@
         <v>15</v>
       </c>
       <c r="D144">
-        <v>45023</v>
+        <v>45638</v>
       </c>
       <c r="E144">
         <v>90732</v>
@@ -6718,7 +6718,7 @@
         <v>97991</v>
       </c>
       <c r="H144">
-        <v>23026</v>
+        <v>22411</v>
       </c>
       <c r="I144" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6751,19 +6751,19 @@
         <v>17</v>
       </c>
       <c r="D145">
-        <v>65240</v>
+        <v>65288</v>
       </c>
       <c r="E145">
         <v>90732</v>
       </c>
       <c r="F145">
-        <v>80240</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>115546</v>
+        <v>0</v>
       </c>
       <c r="H145">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I145" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2322010/God_of_War_Ragnark/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6795,16 +6795,16 @@
         <v>15</v>
       </c>
       <c r="D146">
-        <v>65461</v>
+        <v>61251</v>
       </c>
       <c r="E146">
         <v>90732</v>
       </c>
       <c r="F146">
-        <v>80461</v>
+        <v>76251</v>
       </c>
       <c r="G146">
-        <v>115864</v>
+        <v>109801</v>
       </c>
       <c r="H146">
         <v>15000</v>
@@ -6889,13 +6889,13 @@
         <v>61692</v>
       </c>
       <c r="F148">
-        <v>64460</v>
+        <v>64493</v>
       </c>
       <c r="G148">
-        <v>92822</v>
+        <v>92870</v>
       </c>
       <c r="H148">
-        <v>27495</v>
+        <v>27528</v>
       </c>
       <c r="I148" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -6929,19 +6929,19 @@
         <v>17</v>
       </c>
       <c r="D149">
-        <v>41049</v>
+        <v>41081</v>
       </c>
       <c r="E149">
         <v>61692</v>
       </c>
       <c r="F149">
-        <v>56049</v>
+        <v>0</v>
       </c>
       <c r="G149">
-        <v>80711</v>
+        <v>0</v>
       </c>
       <c r="H149">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I149" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1297900/Gothic_1_Remake/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7014,19 +7014,19 @@
         <v>17</v>
       </c>
       <c r="D151">
-        <v>15344</v>
+        <v>15060</v>
       </c>
       <c r="E151">
         <v>54432</v>
       </c>
       <c r="F151">
-        <v>33366</v>
+        <v>33253</v>
       </c>
       <c r="G151">
-        <v>48047</v>
+        <v>47884</v>
       </c>
       <c r="H151">
-        <v>18022</v>
+        <v>18193</v>
       </c>
       <c r="I151" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3240220/Grand_Theft_Auto_V_Enhanced/","Abrir Steam")</f>
@@ -7058,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="D152">
-        <v>37485</v>
+        <v>37470</v>
       </c>
       <c r="E152">
         <v>72582</v>
@@ -7070,7 +7070,7 @@
         <v>78389</v>
       </c>
       <c r="H152">
-        <v>16952</v>
+        <v>16967</v>
       </c>
       <c r="I152" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7104,19 +7104,19 @@
         <v>17</v>
       </c>
       <c r="D153">
-        <v>35419</v>
+        <v>33480</v>
       </c>
       <c r="E153">
         <v>72582</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>48480</v>
       </c>
       <c r="G153">
-        <v>0</v>
+        <v>69811</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I153" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7148,19 +7148,19 @@
         <v>15</v>
       </c>
       <c r="D154">
-        <v>56567</v>
+        <v>56756</v>
       </c>
       <c r="E154">
         <v>72582</v>
       </c>
       <c r="F154">
-        <v>71567</v>
+        <v>0</v>
       </c>
       <c r="G154">
-        <v>103056</v>
+        <v>0</v>
       </c>
       <c r="H154">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I154" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7194,19 +7194,19 @@
         <v>17</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>73346</v>
       </c>
       <c r="E155">
         <v>72582</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>88346</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>127218</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I155" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/553850/HELLDIVERS_2/","Abrir Steam")</f>
@@ -7237,19 +7237,19 @@
         <v>15</v>
       </c>
       <c r="D156">
-        <v>31572</v>
+        <v>35940</v>
       </c>
       <c r="E156">
-        <v>59877</v>
+        <v>27207</v>
       </c>
       <c r="F156">
-        <v>50343</v>
+        <v>0</v>
       </c>
       <c r="G156">
-        <v>72494</v>
+        <v>0</v>
       </c>
       <c r="H156">
-        <v>18771</v>
+        <v>0</v>
       </c>
       <c r="I156" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7281,19 +7281,19 @@
         <v>17</v>
       </c>
       <c r="D157">
-        <v>11670</v>
+        <v>11686</v>
       </c>
       <c r="E157">
-        <v>59877</v>
+        <v>27207</v>
       </c>
       <c r="F157">
-        <v>34020</v>
+        <v>26686</v>
       </c>
       <c r="G157">
-        <v>48989</v>
+        <v>38428</v>
       </c>
       <c r="H157">
-        <v>22350</v>
+        <v>15000</v>
       </c>
       <c r="I157" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7367,19 +7367,19 @@
         <v>17</v>
       </c>
       <c r="D159">
-        <v>36161</v>
+        <v>36192</v>
       </c>
       <c r="E159">
         <v>83472</v>
       </c>
       <c r="F159">
-        <v>53019</v>
+        <v>53031</v>
       </c>
       <c r="G159">
-        <v>76347</v>
+        <v>76365</v>
       </c>
       <c r="H159">
-        <v>16858</v>
+        <v>16839</v>
       </c>
       <c r="I159" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1659040/HITMAN_World_of_Assassination/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7417,13 +7417,13 @@
         <v>54450</v>
       </c>
       <c r="F160">
-        <v>38838</v>
+        <v>38636</v>
       </c>
       <c r="G160">
-        <v>55927</v>
+        <v>55636</v>
       </c>
       <c r="H160">
-        <v>31063</v>
+        <v>30861</v>
       </c>
       <c r="I160" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7457,19 +7457,19 @@
         <v>17</v>
       </c>
       <c r="D161">
-        <v>9005</v>
+        <v>8500</v>
       </c>
       <c r="E161">
         <v>54450</v>
       </c>
       <c r="F161">
-        <v>30838</v>
+        <v>30636</v>
       </c>
       <c r="G161">
-        <v>44407</v>
+        <v>44116</v>
       </c>
       <c r="H161">
-        <v>21833</v>
+        <v>22136</v>
       </c>
       <c r="I161" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/990080/Hogwarts_Legacy/?curator_clanid=4777282","Abrir Steam")</f>
@@ -7501,16 +7501,16 @@
         <v>15</v>
       </c>
       <c r="D162">
-        <v>9793</v>
+        <v>9714</v>
       </c>
       <c r="E162">
         <v>72582</v>
       </c>
       <c r="F162">
-        <v>44793</v>
+        <v>44714</v>
       </c>
       <c r="G162">
-        <v>64502</v>
+        <v>64388</v>
       </c>
       <c r="H162">
         <v>35000</v>
@@ -7547,16 +7547,16 @@
         <v>17</v>
       </c>
       <c r="D163">
-        <v>10456</v>
+        <v>10314</v>
       </c>
       <c r="E163">
         <v>72582</v>
       </c>
       <c r="F163">
-        <v>37456</v>
+        <v>37314</v>
       </c>
       <c r="G163">
-        <v>53937</v>
+        <v>53732</v>
       </c>
       <c r="H163">
         <v>27000</v>
@@ -7591,7 +7591,7 @@
         <v>15</v>
       </c>
       <c r="D164">
-        <v>68426</v>
+        <v>0</v>
       </c>
       <c r="E164">
         <v>68063</v>
@@ -7635,19 +7635,19 @@
         <v>17</v>
       </c>
       <c r="D165">
-        <v>21999</v>
+        <v>22015</v>
       </c>
       <c r="E165">
         <v>68063</v>
       </c>
       <c r="F165">
-        <v>41344</v>
+        <v>41351</v>
       </c>
       <c r="G165">
-        <v>59535</v>
+        <v>59545</v>
       </c>
       <c r="H165">
-        <v>19345</v>
+        <v>19336</v>
       </c>
       <c r="I165" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7679,7 +7679,7 @@
         <v>15</v>
       </c>
       <c r="D166">
-        <v>91923</v>
+        <v>0</v>
       </c>
       <c r="E166">
         <v>102548</v>
@@ -7722,19 +7722,19 @@
         <v>17</v>
       </c>
       <c r="D167">
-        <v>57150</v>
+        <v>57198</v>
       </c>
       <c r="E167">
         <v>102548</v>
       </c>
       <c r="F167">
-        <v>72150</v>
+        <v>0</v>
       </c>
       <c r="G167">
-        <v>103896</v>
+        <v>0</v>
       </c>
       <c r="H167">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I167" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2353060/Invincible_VS/","Abrir Steam")</f>
@@ -7811,16 +7811,16 @@
         <v>17</v>
       </c>
       <c r="D169">
-        <v>9005</v>
+        <v>9020</v>
       </c>
       <c r="E169">
         <v>72582</v>
       </c>
       <c r="F169">
-        <v>36005</v>
+        <v>36020</v>
       </c>
       <c r="G169">
-        <v>51847</v>
+        <v>51869</v>
       </c>
       <c r="H169">
         <v>27000</v>
@@ -7855,19 +7855,19 @@
         <v>15</v>
       </c>
       <c r="D170">
-        <v>59753</v>
+        <v>68852</v>
       </c>
       <c r="E170">
         <v>108882</v>
       </c>
       <c r="F170">
-        <v>78898</v>
+        <v>0</v>
       </c>
       <c r="G170">
-        <v>113613</v>
+        <v>0</v>
       </c>
       <c r="H170">
-        <v>19145</v>
+        <v>0</v>
       </c>
       <c r="I170" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7944,19 +7944,19 @@
         <v>15</v>
       </c>
       <c r="D172">
-        <v>91766</v>
+        <v>78992</v>
       </c>
       <c r="E172">
         <v>145182</v>
       </c>
       <c r="F172">
-        <v>0</v>
+        <v>102929</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>148218</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>23937</v>
       </c>
       <c r="I172" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -7990,19 +7990,19 @@
         <v>17</v>
       </c>
       <c r="D173">
-        <v>79008</v>
+        <v>0</v>
       </c>
       <c r="E173">
         <v>145182</v>
       </c>
       <c r="F173">
-        <v>94224</v>
+        <v>0</v>
       </c>
       <c r="G173">
-        <v>135683</v>
+        <v>0</v>
       </c>
       <c r="H173">
-        <v>15216</v>
+        <v>0</v>
       </c>
       <c r="I173" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2215200/LEGO_Batman_El_Legado_del_Caballero_Oscuro/","Abrir Steam")</f>
@@ -8033,7 +8033,7 @@
         <v>15</v>
       </c>
       <c r="D174">
-        <v>45386</v>
+        <v>45418</v>
       </c>
       <c r="E174">
         <v>90732</v>
@@ -8045,7 +8045,7 @@
         <v>97991</v>
       </c>
       <c r="H174">
-        <v>22663</v>
+        <v>22631</v>
       </c>
       <c r="I174" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8078,19 +8078,19 @@
         <v>17</v>
       </c>
       <c r="D175">
-        <v>67906</v>
+        <v>67953</v>
       </c>
       <c r="E175">
         <v>90732</v>
       </c>
       <c r="F175">
-        <v>82906</v>
+        <v>0</v>
       </c>
       <c r="G175">
-        <v>119385</v>
+        <v>0</v>
       </c>
       <c r="H175">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I175" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8122,19 +8122,19 @@
         <v>15</v>
       </c>
       <c r="D176">
-        <v>61771</v>
+        <v>68331</v>
       </c>
       <c r="E176">
         <v>90732</v>
       </c>
       <c r="F176">
-        <v>76771</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>110550</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I176" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2651280/Marvels_SpiderMan_2/","Abrir Steam")</f>
@@ -8209,16 +8209,16 @@
         <v>15</v>
       </c>
       <c r="D178">
-        <v>26509</v>
+        <v>28181</v>
       </c>
       <c r="E178">
         <v>108882</v>
       </c>
       <c r="F178">
-        <v>53509</v>
+        <v>55181</v>
       </c>
       <c r="G178">
-        <v>77053</v>
+        <v>79461</v>
       </c>
       <c r="H178">
         <v>27000</v>
@@ -8298,16 +8298,16 @@
         <v>15</v>
       </c>
       <c r="D180">
-        <v>24664</v>
+        <v>26399</v>
       </c>
       <c r="E180">
         <v>90732</v>
       </c>
       <c r="F180">
-        <v>51664</v>
+        <v>53399</v>
       </c>
       <c r="G180">
-        <v>74396</v>
+        <v>76895</v>
       </c>
       <c r="H180">
         <v>27000</v>
@@ -8430,19 +8430,19 @@
         <v>17</v>
       </c>
       <c r="D183">
-        <v>64610</v>
+        <v>64657</v>
       </c>
       <c r="E183">
         <v>127032</v>
       </c>
       <c r="F183">
-        <v>81387</v>
+        <v>81405</v>
       </c>
       <c r="G183">
-        <v>117197</v>
+        <v>117223</v>
       </c>
       <c r="H183">
-        <v>16777</v>
+        <v>16748</v>
       </c>
       <c r="I183" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8654,13 +8654,13 @@
         <v>362982</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>306729</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>441690</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I188" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2537590/Microsoft_Flight_Simulator_2024/","Abrir Steam")</f>
@@ -8734,16 +8734,16 @@
         <v>15</v>
       </c>
       <c r="D190">
-        <v>29758</v>
+        <v>29742</v>
       </c>
       <c r="E190">
         <v>95269</v>
       </c>
       <c r="F190">
-        <v>64758</v>
+        <v>64742</v>
       </c>
       <c r="G190">
-        <v>93252</v>
+        <v>93228</v>
       </c>
       <c r="H190">
         <v>35000</v>
@@ -8779,19 +8779,19 @@
         <v>17</v>
       </c>
       <c r="D191">
-        <v>44676</v>
+        <v>74103</v>
       </c>
       <c r="E191">
         <v>95269</v>
       </c>
       <c r="F191">
-        <v>61025</v>
+        <v>0</v>
       </c>
       <c r="G191">
-        <v>87876</v>
+        <v>0</v>
       </c>
       <c r="H191">
-        <v>16349</v>
+        <v>0</v>
       </c>
       <c r="I191" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8823,19 +8823,19 @@
         <v>15</v>
       </c>
       <c r="D192">
-        <v>40939</v>
+        <v>40734</v>
       </c>
       <c r="E192">
         <v>122494</v>
       </c>
       <c r="F192">
-        <v>75939</v>
+        <v>67734</v>
       </c>
       <c r="G192">
-        <v>109352</v>
+        <v>97537</v>
       </c>
       <c r="H192">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I192" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8868,19 +8868,19 @@
         <v>17</v>
       </c>
       <c r="D193">
-        <v>146377</v>
+        <v>0</v>
       </c>
       <c r="E193">
         <v>122494</v>
       </c>
       <c r="F193">
-        <v>161377</v>
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>232383</v>
+        <v>0</v>
       </c>
       <c r="H193">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I193" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8911,19 +8911,19 @@
         <v>15</v>
       </c>
       <c r="D194">
-        <v>24428</v>
+        <v>0</v>
       </c>
       <c r="E194">
         <v>149901</v>
       </c>
       <c r="F194">
-        <v>51428</v>
+        <v>0</v>
       </c>
       <c r="G194">
-        <v>74056</v>
+        <v>0</v>
       </c>
       <c r="H194">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I194" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8955,19 +8955,19 @@
         <v>17</v>
       </c>
       <c r="D195">
-        <v>146377</v>
+        <v>0</v>
       </c>
       <c r="E195">
         <v>122494</v>
       </c>
       <c r="F195">
-        <v>161377</v>
+        <v>0</v>
       </c>
       <c r="G195">
-        <v>232383</v>
+        <v>0</v>
       </c>
       <c r="H195">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I195" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2246340/Monster_Hunter_Wilds/?curator_clanid=4777282","Abrir Steam")</f>
@@ -8998,19 +8998,19 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>14225</v>
+        <v>13089</v>
       </c>
       <c r="E196">
         <v>72582</v>
       </c>
       <c r="F196">
-        <v>49225</v>
+        <v>40089</v>
       </c>
       <c r="G196">
-        <v>70884</v>
+        <v>57728</v>
       </c>
       <c r="H196">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I196" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9044,19 +9044,19 @@
         <v>17</v>
       </c>
       <c r="D197">
-        <v>32565</v>
+        <v>0</v>
       </c>
       <c r="E197">
         <v>72582</v>
       </c>
       <c r="F197">
-        <v>47565</v>
+        <v>0</v>
       </c>
       <c r="G197">
-        <v>68494</v>
+        <v>0</v>
       </c>
       <c r="H197">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I197" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1971870/Mortal_Kombat_1/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9087,16 +9087,16 @@
         <v>15</v>
       </c>
       <c r="D198">
-        <v>20517</v>
+        <v>22141</v>
       </c>
       <c r="E198">
         <v>108882</v>
       </c>
       <c r="F198">
-        <v>47517</v>
+        <v>49141</v>
       </c>
       <c r="G198">
-        <v>68424</v>
+        <v>70763</v>
       </c>
       <c r="H198">
         <v>27000</v>
@@ -9176,19 +9176,19 @@
         <v>15</v>
       </c>
       <c r="D200">
-        <v>13058</v>
+        <v>12837</v>
       </c>
       <c r="E200">
         <v>127032</v>
       </c>
       <c r="F200">
-        <v>46638</v>
+        <v>46481</v>
       </c>
       <c r="G200">
-        <v>67159</v>
+        <v>66933</v>
       </c>
       <c r="H200">
-        <v>33580</v>
+        <v>33644</v>
       </c>
       <c r="I200" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9222,16 +9222,16 @@
         <v>17</v>
       </c>
       <c r="D201">
-        <v>11638</v>
+        <v>11481</v>
       </c>
       <c r="E201">
         <v>127032</v>
       </c>
       <c r="F201">
-        <v>38638</v>
+        <v>38481</v>
       </c>
       <c r="G201">
-        <v>55639</v>
+        <v>55413</v>
       </c>
       <c r="H201">
         <v>27000</v>
@@ -9266,16 +9266,16 @@
         <v>15</v>
       </c>
       <c r="D202">
-        <v>22378</v>
+        <v>22661</v>
       </c>
       <c r="E202">
         <v>145182</v>
       </c>
       <c r="F202">
-        <v>57378</v>
+        <v>57661</v>
       </c>
       <c r="G202">
-        <v>82624</v>
+        <v>83032</v>
       </c>
       <c r="H202">
         <v>35000</v>
@@ -9312,19 +9312,19 @@
         <v>17</v>
       </c>
       <c r="D203">
-        <v>22756</v>
+        <v>82793</v>
       </c>
       <c r="E203">
         <v>145182</v>
       </c>
       <c r="F203">
-        <v>49756</v>
+        <v>0</v>
       </c>
       <c r="G203">
-        <v>71649</v>
+        <v>0</v>
       </c>
       <c r="H203">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I203" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9356,19 +9356,19 @@
         <v>15</v>
       </c>
       <c r="D204">
-        <v>25043</v>
+        <v>25059</v>
       </c>
       <c r="E204">
         <v>181482</v>
       </c>
       <c r="F204">
-        <v>60043</v>
+        <v>52059</v>
       </c>
       <c r="G204">
-        <v>86462</v>
+        <v>74965</v>
       </c>
       <c r="H204">
-        <v>35000</v>
+        <v>27000</v>
       </c>
       <c r="I204" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9402,19 +9402,19 @@
         <v>17</v>
       </c>
       <c r="D205">
-        <v>26446</v>
+        <v>0</v>
       </c>
       <c r="E205">
         <v>181482</v>
       </c>
       <c r="F205">
-        <v>53446</v>
+        <v>0</v>
       </c>
       <c r="G205">
-        <v>76962</v>
+        <v>0</v>
       </c>
       <c r="H205">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I205" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3472040/NBA_2K26/","Abrir Steam")</f>
@@ -9664,19 +9664,19 @@
         <v>17</v>
       </c>
       <c r="D211">
-        <v>40497</v>
+        <v>0</v>
       </c>
       <c r="E211">
         <v>108882</v>
       </c>
       <c r="F211">
-        <v>64663</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>93115</v>
+        <v>0</v>
       </c>
       <c r="H211">
-        <v>24166</v>
+        <v>0</v>
       </c>
       <c r="I211" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2694490/Path_of_Exile_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -9792,19 +9792,19 @@
         <v>15</v>
       </c>
       <c r="D214">
-        <v>27897</v>
+        <v>29301</v>
       </c>
       <c r="E214">
         <v>87102</v>
       </c>
       <c r="F214">
-        <v>60510</v>
+        <v>56301</v>
       </c>
       <c r="G214">
-        <v>87134</v>
+        <v>81073</v>
       </c>
       <c r="H214">
-        <v>32613</v>
+        <v>27000</v>
       </c>
       <c r="I214" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9838,19 +9838,19 @@
         <v>17</v>
       </c>
       <c r="D215">
-        <v>31351</v>
+        <v>0</v>
       </c>
       <c r="E215">
         <v>87102</v>
       </c>
       <c r="F215">
-        <v>52510</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>75614</v>
+        <v>0</v>
       </c>
       <c r="H215">
-        <v>21159</v>
+        <v>0</v>
       </c>
       <c r="I215" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9881,19 +9881,19 @@
         <v>15</v>
       </c>
       <c r="D216">
-        <v>45875</v>
+        <v>45906</v>
       </c>
       <c r="E216">
         <v>101622</v>
       </c>
       <c r="F216">
-        <v>76217</v>
+        <v>70093</v>
       </c>
       <c r="G216">
-        <v>109752</v>
+        <v>100934</v>
       </c>
       <c r="H216">
-        <v>30342</v>
+        <v>24187</v>
       </c>
       <c r="I216" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -9927,7 +9927,7 @@
         <v>17</v>
       </c>
       <c r="D217">
-        <v>89432</v>
+        <v>0</v>
       </c>
       <c r="E217">
         <v>101622</v>
@@ -10016,19 +10016,19 @@
         <v>17</v>
       </c>
       <c r="D219">
-        <v>110374</v>
+        <v>0</v>
       </c>
       <c r="E219">
         <v>130662</v>
       </c>
       <c r="F219">
-        <v>125374</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>180539</v>
+        <v>0</v>
       </c>
       <c r="H219">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I219" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2161700/Persona_3_Reload/","Abrir Steam")</f>
@@ -10059,19 +10059,19 @@
         <v>15</v>
       </c>
       <c r="D220">
-        <v>62733</v>
+        <v>62717</v>
       </c>
       <c r="E220">
         <v>81675</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>77717</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>111912</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I220" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10105,19 +10105,19 @@
         <v>17</v>
       </c>
       <c r="D221">
-        <v>50921</v>
+        <v>0</v>
       </c>
       <c r="E221">
         <v>81675</v>
       </c>
       <c r="F221">
-        <v>65921</v>
+        <v>0</v>
       </c>
       <c r="G221">
-        <v>94926</v>
+        <v>0</v>
       </c>
       <c r="H221">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I221" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10149,19 +10149,19 @@
         <v>15</v>
       </c>
       <c r="D222">
-        <v>75365</v>
+        <v>74734</v>
       </c>
       <c r="E222">
         <v>96195</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>89734</v>
       </c>
       <c r="G222">
-        <v>0</v>
+        <v>129217</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I222" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10195,19 +10195,19 @@
         <v>17</v>
       </c>
       <c r="D223">
-        <v>94368</v>
+        <v>0</v>
       </c>
       <c r="E223">
         <v>96195</v>
       </c>
       <c r="F223">
-        <v>109368</v>
+        <v>0</v>
       </c>
       <c r="G223">
-        <v>157490</v>
+        <v>0</v>
       </c>
       <c r="H223">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I223" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/3357650/PRAGMATA/","Abrir Steam")</f>
@@ -10239,19 +10239,19 @@
         <v>15</v>
       </c>
       <c r="D224">
-        <v>16196</v>
+        <v>16606</v>
       </c>
       <c r="E224">
         <v>59877</v>
       </c>
       <c r="F224">
-        <v>44901</v>
+        <v>44908</v>
       </c>
       <c r="G224">
-        <v>64657</v>
+        <v>64668</v>
       </c>
       <c r="H224">
-        <v>28705</v>
+        <v>28302</v>
       </c>
       <c r="I224" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10285,19 +10285,19 @@
         <v>17</v>
       </c>
       <c r="D225">
-        <v>10408</v>
+        <v>11181</v>
       </c>
       <c r="E225">
         <v>59877</v>
       </c>
       <c r="F225">
-        <v>33515</v>
+        <v>33824</v>
       </c>
       <c r="G225">
-        <v>48262</v>
+        <v>48707</v>
       </c>
       <c r="H225">
-        <v>23107</v>
+        <v>22643</v>
       </c>
       <c r="I225" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1144200/Ready_or_Not/","Abrir Steam")</f>
@@ -10546,19 +10546,19 @@
         <v>17</v>
       </c>
       <c r="D231">
-        <v>19287</v>
+        <v>0</v>
       </c>
       <c r="E231">
         <v>181482</v>
       </c>
       <c r="F231">
-        <v>46287</v>
+        <v>0</v>
       </c>
       <c r="G231">
-        <v>66653</v>
+        <v>0</v>
       </c>
       <c r="H231">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="I231" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1174180/Red_Dead_Redemption_2/","Abrir Steam")</f>
@@ -10589,19 +10589,19 @@
         <v>15</v>
       </c>
       <c r="D232">
-        <v>9415</v>
+        <v>9446</v>
       </c>
       <c r="E232">
         <v>52635</v>
       </c>
       <c r="F232">
-        <v>38540</v>
+        <v>34528</v>
       </c>
       <c r="G232">
-        <v>55498</v>
+        <v>49720</v>
       </c>
       <c r="H232">
-        <v>29125</v>
+        <v>25082</v>
       </c>
       <c r="I232" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10634,19 +10634,19 @@
         <v>17</v>
       </c>
       <c r="D233">
-        <v>10030</v>
+        <v>0</v>
       </c>
       <c r="E233">
         <v>52635</v>
       </c>
       <c r="F233">
-        <v>30540</v>
+        <v>0</v>
       </c>
       <c r="G233">
-        <v>43978</v>
+        <v>0</v>
       </c>
       <c r="H233">
-        <v>20510</v>
+        <v>0</v>
       </c>
       <c r="I233" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/883710/Resident_Evil_2/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10677,16 +10677,16 @@
         <v>15</v>
       </c>
       <c r="D234">
-        <v>12048</v>
+        <v>11938</v>
       </c>
       <c r="E234">
         <v>70785</v>
       </c>
       <c r="F234">
-        <v>39048</v>
+        <v>38938</v>
       </c>
       <c r="G234">
-        <v>56229</v>
+        <v>56071</v>
       </c>
       <c r="H234">
         <v>27000</v>
@@ -10764,19 +10764,19 @@
         <v>15</v>
       </c>
       <c r="D236">
-        <v>8500</v>
+        <v>8484</v>
       </c>
       <c r="E236">
         <v>52635</v>
       </c>
       <c r="F236">
-        <v>35758</v>
+        <v>37228</v>
       </c>
       <c r="G236">
-        <v>51492</v>
+        <v>53608</v>
       </c>
       <c r="H236">
-        <v>27258</v>
+        <v>28744</v>
       </c>
       <c r="I236" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10809,19 +10809,19 @@
         <v>17</v>
       </c>
       <c r="D237">
-        <v>3075</v>
+        <v>6750</v>
       </c>
       <c r="E237">
         <v>52635</v>
       </c>
       <c r="F237">
-        <v>27758</v>
+        <v>29228</v>
       </c>
       <c r="G237">
-        <v>39972</v>
+        <v>42088</v>
       </c>
       <c r="H237">
-        <v>24683</v>
+        <v>22478</v>
       </c>
       <c r="I237" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/952060/Resident_Evil_3/?curator_clanid=4777282","Abrir Steam")</f>
@@ -10898,19 +10898,19 @@
         <v>17</v>
       </c>
       <c r="D239">
-        <v>11386</v>
+        <v>0</v>
       </c>
       <c r="E239">
         <v>52635</v>
       </c>
       <c r="F239">
-        <v>31082</v>
+        <v>0</v>
       </c>
       <c r="G239">
-        <v>44758</v>
+        <v>0</v>
       </c>
       <c r="H239">
-        <v>19696</v>
+        <v>0</v>
       </c>
       <c r="I239" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10941,19 +10941,19 @@
         <v>15</v>
       </c>
       <c r="D240">
-        <v>20249</v>
+        <v>0</v>
       </c>
       <c r="E240">
         <v>70785</v>
       </c>
       <c r="F240">
-        <v>53089</v>
+        <v>0</v>
       </c>
       <c r="G240">
-        <v>76448</v>
+        <v>0</v>
       </c>
       <c r="H240">
-        <v>32840</v>
+        <v>0</v>
       </c>
       <c r="I240" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -10985,19 +10985,19 @@
         <v>17</v>
       </c>
       <c r="D241">
-        <v>70382</v>
+        <v>0</v>
       </c>
       <c r="E241">
         <v>70785</v>
       </c>
       <c r="F241">
-        <v>85382</v>
+        <v>0</v>
       </c>
       <c r="G241">
-        <v>122950</v>
+        <v>0</v>
       </c>
       <c r="H241">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="I241" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/2050650/Resident_Evil_4/","Abrir Steam")</f>
@@ -11028,19 +11028,19 @@
         <v>15</v>
       </c>
       <c r="D242">
-        <v>34252</v>
+        <v>34205</v>
       </c>
       <c r="E242">
         <v>70785</v>
       </c>
       <c r="F242">
-        <v>51554</v>
+        <v>51535</v>
       </c>
       <c r="G242">
-        <v>74238</v>
+        <v>74210</v>
       </c>
       <c r="H242">
-        <v>17302</v>
+        <v>17330</v>
       </c>
       <c r="I242" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/1196590/Resident_Evil_Village/?l=spanish","Abrir Steam")</f>
@@ -11116,19 +11116,19 @@
         <v>15</v>
       </c>
       <c r="D244">
-        <v>9904</v>
+        <v>9809</v>
       </c>
       <c r="E244">
         <v>27225</v>
       </c>
       <c r="F244">
-        <v>0</v>
+        <v>24809</v>
       </c>
       <c r="G244">
-        <v>0</v>
+        <v>35725</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="I244" t="str">
         <f>HYPERLINK("https://store.steampowered.com/app/418370/Resident_Evil_7_Biohazard/","Abrir Steam")</f>
@@ -11204,16 +11204,16 @@
         <v>15</v>
       </c>
       <c r="D246">
-        <v>11938</v>
+        <v>11922</v>
       </c>
       <c r="E246">
         <v>108882</v>
       </c>
       <c r="F246">
-        <v>38938</v>
+        <v>38922</v>
       </c>
       <c r="G246">
-        <v>56071</v>
+        <v>56048</v>
       </c>
       <c r="H246">
         <v>27000</v>
@@ -11291,19 +11291,19 @@
         <v>15</v>
       </c>
       <c r="D248">
-        <v>59122</v>
+        <v>59090</v>
       </c>
       <c r="E248">
         <v>96195</v>
       </c>
       <c r="F248">
